--- a/data/review/audit_T3.xlsx
+++ b/data/review/audit_T3.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R71"/>
+  <dimension ref="A1:S80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -494,15 +494,20 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>fix</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>audit</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>auditor</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>audit_note</t>
         </is>
@@ -521,7 +526,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Nếu cơ quan thuế nhận được thông tin về thửa đất phải nộp tiền sử dụng đất, thì cơ quan thuế xác định và thông báo số tiền phải nộp dựa trên phiếu chuyển thông tin từ những cơ quan nào?</t>
+          <t>Căn cứ phiếu chuyển thông tin về đất đai, cơ quan thuế phải tính những khoản tiền nào để thông báo cho người sử dụng đất, và phiếu đó do những cơ quan nào chuyển đến?</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -561,24 +566,21 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>group_mismatch</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Câu hỏi hỏi phiếu chuyển thông tin đến từ cơ quan nào: mốc 1 và 2 như nhau (cơ quan quản lý đất đai và các cơ quan khác); lần sửa 2025 chỉ mở rộng các khoản tiền phải tính. Chỉ hai đáp án</t>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Nếu cơ quan thuế nhận được thông tin về thửa đất phải nộp tiền sử dụng đất, thì cơ quan thuế xác định và thông báo số tiền phải nộp dựa trên phiếu chuyển thông tin từ những cơ quan nào?»; nhãn cũ khong_dat group_mismatch: Câu hỏi hỏi phiếu chuyển thông tin đến từ cơ quan nào: mốc 1 và 2 như nhau (cơ quan quản lý đất đai và các cơ quan khác); lần sửa 2025 chỉ mở rộng các khoản tiền phải tính. Chỉ hai đáp án). Hỏi cả khoản tiền phải tính và nguồn phiếu: mốc 1–2 khác về khoản tiền, mốc 3 khác về cơ quan chuyển phiếu; ba đáp án</t>
         </is>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -593,7 +595,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Nếu cơ quan thuế nhận được thông tin về thửa đất phải nộp tiền sử dụng đất, thì cơ quan thuế xác định và thông báo số tiền phải nộp dựa trên phiếu chuyển thông tin từ những cơ quan nào?</t>
+          <t>Căn cứ phiếu chuyển thông tin về đất đai, cơ quan thuế phải tính những khoản tiền nào để thông báo cho người sử dụng đất, và phiếu đó do những cơ quan nào chuyển đến?</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -633,24 +635,21 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>group_mismatch</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Câu hỏi hỏi phiếu chuyển thông tin đến từ cơ quan nào: mốc 1 và 2 như nhau (cơ quan quản lý đất đai và các cơ quan khác); lần sửa 2025 chỉ mở rộng các khoản tiền phải tính. Chỉ hai đáp án</t>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Nếu cơ quan thuế nhận được thông tin về thửa đất phải nộp tiền sử dụng đất, thì cơ quan thuế xác định và thông báo số tiền phải nộp dựa trên phiếu chuyển thông tin từ những cơ quan nào?»; nhãn cũ khong_dat group_mismatch: Câu hỏi hỏi phiếu chuyển thông tin đến từ cơ quan nào: mốc 1 và 2 như nhau (cơ quan quản lý đất đai và các cơ quan khác); lần sửa 2025 chỉ mở rộng các khoản tiền phải tính. Chỉ hai đáp án). Hỏi cả khoản tiền phải tính và nguồn phiếu: mốc 1–2 khác về khoản tiền, mốc 3 khác về cơ quan chuyển phiếu; ba đáp án</t>
         </is>
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -665,7 +664,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Nếu cơ quan thuế nhận được thông tin về thửa đất phải nộp tiền sử dụng đất, thì cơ quan thuế xác định và thông báo số tiền phải nộp dựa trên phiếu chuyển thông tin từ những cơ quan nào?</t>
+          <t>Căn cứ phiếu chuyển thông tin về đất đai, cơ quan thuế phải tính những khoản tiền nào để thông báo cho người sử dụng đất, và phiếu đó do những cơ quan nào chuyển đến?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -705,24 +704,21 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>group_mismatch</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Câu hỏi hỏi phiếu chuyển thông tin đến từ cơ quan nào: mốc 1 và 2 như nhau (cơ quan quản lý đất đai và các cơ quan khác); lần sửa 2025 chỉ mở rộng các khoản tiền phải tính. Chỉ hai đáp án</t>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Nếu cơ quan thuế nhận được thông tin về thửa đất phải nộp tiền sử dụng đất, thì cơ quan thuế xác định và thông báo số tiền phải nộp dựa trên phiếu chuyển thông tin từ những cơ quan nào?»; nhãn cũ khong_dat group_mismatch: Câu hỏi hỏi phiếu chuyển thông tin đến từ cơ quan nào: mốc 1 và 2 như nhau (cơ quan quản lý đất đai và các cơ quan khác); lần sửa 2025 chỉ mở rộng các khoản tiền phải tính. Chỉ hai đáp án). Hỏi cả khoản tiền phải tính và nguồn phiếu: mốc 1–2 khác về khoản tiền, mốc 3 khác về cơ quan chuyển phiếu; ba đáp án</t>
         </is>
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -795,6 +791,7 @@
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -864,9 +861,14 @@
         </is>
       </c>
       <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>loại lineage (group_mismatch): Mốc 1→2 chỉ đổi 'bán' thành 'bán đấu giá' và bỏ chữ 'bán đấu giá' ở cuối — cùng một bước; chỉ mốc 3 thêm việc chọn tổ chức đấu giá. Chỉ hai đáp án; 'bước xử lý đầu tiên' cũng mơ hồ</t>
+        </is>
+      </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -936,9 +938,14 @@
         </is>
       </c>
       <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>loại lineage (group_mismatch): Mốc 1→2 chỉ đổi 'bán' thành 'bán đấu giá' và bỏ chữ 'bán đấu giá' ở cuối — cùng một bước; chỉ mốc 3 thêm việc chọn tổ chức đấu giá. Chỉ hai đáp án; 'bước xử lý đầu tiên' cũng mơ hồ</t>
+        </is>
+      </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1008,9 +1015,14 @@
         </is>
       </c>
       <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>loại lineage (group_mismatch): Mốc 1→2 chỉ đổi 'bán' thành 'bán đấu giá' và bỏ chữ 'bán đấu giá' ở cuối — cùng một bước; chỉ mốc 3 thêm việc chọn tổ chức đấu giá. Chỉ hai đáp án; 'bước xử lý đầu tiên' cũng mơ hồ</t>
+        </is>
+      </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1080,9 +1092,14 @@
         </is>
       </c>
       <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>loại lineage (group_mismatch): Mốc 2 và 3 cùng loại tờ khai (trị giá thấp theo Phụ lục II Danh mục 2, hoặc tờ khai giấy HQ/2015); mốc 3 chỉ thêm 'nhóm 2' và đổi 'phần A, mục II' thành 'mục II'. Chỉ hai đáp án</t>
+        </is>
+      </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1152,9 +1169,14 @@
         </is>
       </c>
       <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>loại lineage (group_mismatch): Mốc 2 và 3 cùng loại tờ khai (trị giá thấp theo Phụ lục II Danh mục 2, hoặc tờ khai giấy HQ/2015); mốc 3 chỉ thêm 'nhóm 2' và đổi 'phần A, mục II' thành 'mục II'. Chỉ hai đáp án</t>
+        </is>
+      </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1224,9 +1246,14 @@
         </is>
       </c>
       <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>loại lineage (group_mismatch): Mốc 2 và 3 cùng loại tờ khai (trị giá thấp theo Phụ lục II Danh mục 2, hoặc tờ khai giấy HQ/2015); mốc 3 chỉ thêm 'nhóm 2' và đổi 'phần A, mục II' thành 'mục II'. Chỉ hai đáp án</t>
+        </is>
+      </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1291,6 +1318,7 @@
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1355,6 +1383,7 @@
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1419,6 +1448,7 @@
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1483,6 +1513,7 @@
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1547,6 +1578,7 @@
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1611,6 +1643,7 @@
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1675,6 +1708,7 @@
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1739,11 +1773,12 @@
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>vilextime:T3:provision:3ebea3e0-2d54-11f1-99aa-5169be827cf7:2011-05-09</t>
+          <t>vilextime:T3:provision:3bf55600-e172-11f0-a444-b39f8b678525#k1:2021-11-21</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1753,37 +1788,37 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Một cặp vợ chồng đăng ký nuôi con nuôi tại Cơ quan đại diện thì nếu đủ điều kiện, việc xin ý kiến cơ quan trong nước được thực hiện trong thời hạn bao lâu và gửi cơ quan nào?</t>
+          <t>Một doanh nghiệp cần nhập vàng nguyên liệu phục vụ sản xuất đồ trang sức, mỹ nghệ thì phải nộp mấy bộ hồ sơ xin giấy phép, nộp tại đâu và bằng những cách nào?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2011-05-09</t>
+          <t>2021-11-21</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Điều 27. Thủ tục nộp hồ sơ và đăng ký việc nuôi con nuôi tại Cơ quan đại diện</t>
+          <t>Điều 17. Thủ tục cấp Giấy phép nhập khẩu vàng nguyên liệu để sản xuất vàng trang sức, mỹ nghệ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>3. Nếu xét thấy các bên có đủ điều kiện theo quy định tại Điều 14 của Luật Nuôi con nuôi, thì trong thời hạn 20 ngày, kể từ ngày lấy ý kiến của những người liên quan, Cơ quan đại diện đăng ký việc nuôi con nuôi. Khi đăng ký nuôi con nuôi, cha mẹ nuôi, cha mẹ đẻ, người giám hộ và người được nhận làm con nuôi phải có mặt. Cơ quan đại diện ghi vào Sổ đăng ký nuôi con nuôi và trao Giấy chứng nhận nuôi con nuôi cho các bên, đồng thời gửi văn bản thông báo cho Cục Con nuôi và Cục Lãnh sự kèm theo bản sao Giấy chứng nhận nuôi con nuôi.</t>
+          <t>1. Doanh nghiệp có nhu cầu nhập khẩu vàng nguyên liệu để sản xuất vàng trang sức, mỹ nghệ nộp trực tiếp tại Bộ phận một cửa hoặc qua dịch vụ bưu chính 02 (hai) bộ hồ sơ quy định tại Điều 10 Thông tư này đến Ngân hàng Nhà nước chi nhánh tỉnh, thành phố để được cấp Giấy phép nhập khẩu vàng nguyên liệu.</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Khoản 3 Điều 27</t>
+          <t>Khoản 1 Điều 17</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>19/2011/NĐ-CP</t>
+          <t>16/2012/TT-NHNN</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=26222</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=27581</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1793,33 +1828,22 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>question_ambiguous</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>Khoản 3 là đăng ký nuôi con nuôi rồi gửi văn bản thông báo; câu hỏi gọi đó là 'xin ý kiến cơ quan trong nước', vốn là việc của khoản 4 (yêu cầu cơ quan trong nước kiểm tra, xác minh). Đề xuất hỏi thời hạn đăng ký và nơi gửi thông báo</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>4. Trường hợp hồ sơ nuôi con nuôi không rõ ràng, cần yêu cầu cơ quan trong nước kiểm tra, xác minh, Cơ quan đạ...</t>
-        </is>
-      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>vilextime:T3:provision:3ebea3e0-2d54-11f1-99aa-5169be827cf7:2025-01-09</t>
+          <t>vilextime:T3:provision:3ebea3e0-2d54-11f1-99aa-5169be827cf7:2011-05-09</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1829,12 +1853,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Một cặp vợ chồng đăng ký nuôi con nuôi tại Cơ quan đại diện thì nếu đủ điều kiện, việc xin ý kiến cơ quan trong nước được thực hiện trong thời hạn bao lâu và gửi cơ quan nào?</t>
+          <t>Khi nhận hồ sơ nuôi con nuôi tại Cơ quan đại diện, nếu các bên đủ điều kiện thì Cơ quan đại diện phải đăng ký việc nuôi con nuôi trong thời hạn bao lâu và gửi văn bản thông báo cho những cơ quan nào?</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025-01-09</t>
+          <t>2011-05-09</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1844,7 +1868,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>3. Nếu xét thấy các bên có đủ điều kiện theo quy định tại Điều 14 của Luật Nuôi con nuôi, thì trong thời hạn 20 ngày, kể từ ngày lấy ý kiến của những người liên quan, Cơ quan đại diện đăng ký việc nuôi con nuôi. Khi đăng ký nuôi con nuôi, cha mẹ nuôi, cha mẹ đẻ, người giám hộ và người được nhận làm con nuôi phải có mặt. Cơ quan đại diện ghi vào Sổ đăng ký nuôi con nuôi và trao Giấy chứng nhận nuôi con nuôi cho các bên, đồng thời gửi văn bản thông báo cho Bộ Tư pháp và Cục Lãnh sự kèm theo bản sao Giấy chứng nhận nuôi con nuôi.</t>
+          <t>3. Nếu xét thấy các bên có đủ điều kiện theo quy định tại Điều 14 của Luật Nuôi con nuôi, thì trong thời hạn 20 ngày, kể từ ngày lấy ý kiến của những người liên quan, Cơ quan đại diện đăng ký việc nuôi con nuôi. Khi đăng ký nuôi con nuôi, cha mẹ nuôi, cha mẹ đẻ, người giám hộ và người được nhận làm con nuôi phải có mặt. Cơ quan đại diện ghi vào Sổ đăng ký nuôi con nuôi và trao Giấy chứng nhận nuôi con nuôi cho các bên, đồng thời gửi văn bản thông báo cho Cục Con nuôi và Cục Lãnh sự kèm theo bản sao Giấy chứng nhận nuôi con nuôi.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1869,33 +1893,26 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>question_ambiguous</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Khoản 3 là đăng ký nuôi con nuôi rồi gửi văn bản thông báo; câu hỏi gọi đó là 'xin ý kiến cơ quan trong nước', vốn là việc của khoản 4 (yêu cầu cơ quan trong nước kiểm tra, xác minh). Đề xuất hỏi thời hạn đăng ký và nơi gửi thông báo</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>4. Trường hợp hồ sơ nuôi con nuôi không rõ ràng, cần yêu cầu cơ quan trong nước kiểm tra, xác minh, Cơ quan đạ...</t>
-        </is>
-      </c>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Một cặp vợ chồng đăng ký nuôi con nuôi tại Cơ quan đại diện thì nếu đủ điều kiện, việc xin ý kiến cơ quan trong nước được thực hiện trong thời hạn bao lâu và gửi cơ quan nào?»; nhãn cũ khong_dat question_ambiguous: Khoản 3 là đăng ký nuôi con nuôi rồi gửi văn bản thông báo; câu hỏi gọi đó là 'xin ý kiến cơ quan trong nước', vốn là việc của khoản 4 (yêu cầu cơ quan trong nước kiểm tra, xác minh). Đề xuất hỏi thời hạn đăng ký và nơi gửi thông báo). Hỏi thời hạn đăng ký và nơi nhận thông báo: 20 ngày/Cục Con nuôi, 20 ngày/Bộ Tư pháp, 15 ngày làm việc/Bộ Tư pháp; ba đáp án</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>vilextime:T3:provision:3ebea3e0-2d54-11f1-99aa-5169be827cf7:2026-01-16</t>
+          <t>vilextime:T3:provision:3ebea3e0-2d54-11f1-99aa-5169be827cf7:2025-01-09</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1905,12 +1922,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Một cặp vợ chồng đăng ký nuôi con nuôi tại Cơ quan đại diện thì nếu đủ điều kiện, việc xin ý kiến cơ quan trong nước được thực hiện trong thời hạn bao lâu và gửi cơ quan nào?</t>
+          <t>Khi nhận hồ sơ nuôi con nuôi tại Cơ quan đại diện, nếu các bên đủ điều kiện thì Cơ quan đại diện phải đăng ký việc nuôi con nuôi trong thời hạn bao lâu và gửi văn bản thông báo cho những cơ quan nào?</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2025-01-09</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1920,7 +1937,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>3. Nếu xét thấy các bên có đủ điều kiện theo quy định tại Điều 14 của Luật Nuôi con nuôi, thì trong thời hạn 15 ngày làm việc, kể từ ngày lấy ý kiến của những người liên quan, Cơ quan đại diện đăng ký việc nuôi con nuôi. Khi đăng ký nuôi con nuôi, cha mẹ nuôi, cha mẹ đẻ, người giám hộ và người được nhận làm con nuôi phải có mặt. Cơ quan đại diện ghi vào Sổ đăng ký nuôi con nuôi và trao Giấy chứng nhận nuôi con nuôi cho các bên, đồng thời gửi văn bản thông báo cho Bộ Tư pháp và Cục Lãnh sự kèm theo bản sao Giấy chứng nhận nuôi con nuôi.</t>
+          <t>3. Nếu xét thấy các bên có đủ điều kiện theo quy định tại Điều 14 của Luật Nuôi con nuôi, thì trong thời hạn 20 ngày, kể từ ngày lấy ý kiến của những người liên quan, Cơ quan đại diện đăng ký việc nuôi con nuôi. Khi đăng ký nuôi con nuôi, cha mẹ nuôi, cha mẹ đẻ, người giám hộ và người được nhận làm con nuôi phải có mặt. Cơ quan đại diện ghi vào Sổ đăng ký nuôi con nuôi và trao Giấy chứng nhận nuôi con nuôi cho các bên, đồng thời gửi văn bản thông báo cho Bộ Tư pháp và Cục Lãnh sự kèm theo bản sao Giấy chứng nhận nuôi con nuôi.</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1945,33 +1962,26 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>question_ambiguous</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Khoản 3 là đăng ký nuôi con nuôi rồi gửi văn bản thông báo; câu hỏi gọi đó là 'xin ý kiến cơ quan trong nước', vốn là việc của khoản 4 (yêu cầu cơ quan trong nước kiểm tra, xác minh). Đề xuất hỏi thời hạn đăng ký và nơi gửi thông báo</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>4. Trường hợp hồ sơ nuôi con nuôi không rõ ràng, cần yêu cầu cơ quan trong nước kiểm tra, xác minh, Cơ quan đạ...</t>
-        </is>
-      </c>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Một cặp vợ chồng đăng ký nuôi con nuôi tại Cơ quan đại diện thì nếu đủ điều kiện, việc xin ý kiến cơ quan trong nước được thực hiện trong thời hạn bao lâu và gửi cơ quan nào?»; nhãn cũ khong_dat question_ambiguous: Khoản 3 là đăng ký nuôi con nuôi rồi gửi văn bản thông báo; câu hỏi gọi đó là 'xin ý kiến cơ quan trong nước', vốn là việc của khoản 4 (yêu cầu cơ quan trong nước kiểm tra, xác minh). Đề xuất hỏi thời hạn đăng ký và nơi gửi thông báo). Hỏi thời hạn đăng ký và nơi nhận thông báo: 20 ngày/Cục Con nuôi, 20 ngày/Bộ Tư pháp, 15 ngày làm việc/Bộ Tư pháp; ba đáp án</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>vilextime:T3:provision:40778740-2c7f-11f1-abee-c9b7a53cf5c7:2025-02-22</t>
+          <t>vilextime:T3:provision:3ebea3e0-2d54-11f1-99aa-5169be827cf7:2026-01-16</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1981,37 +1991,37 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Khi Cục trưởng Cục điều tra chống buôn lậu xử phạt vi phạm về hàng giả, hàng cấm, người này được áp dụng những biện pháp khắc phục hậu quả nào?</t>
+          <t>Khi nhận hồ sơ nuôi con nuôi tại Cơ quan đại diện, nếu các bên đủ điều kiện thì Cơ quan đại diện phải đăng ký việc nuôi con nuôi trong thời hạn bao lâu và gửi văn bản thông báo cho những cơ quan nào?</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025-02-22</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>4. Cục trưởng Cục điều tra chống buôn lậu, Cục trưởng Cục kiểm tra sau thông quan thuộc Tổng cục Hải quan, Cục trưởng Cục Hải quan tỉnh, liên tỉnh, thành phố trực thuộc trung ương có quyền:</t>
+          <t>Điều 27. Thủ tục nộp hồ sơ và đăng ký việc nuôi con nuôi tại Cơ quan đại diện</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>đ) Áp dụng các biện pháp khắc phục hậu quả quy định tại các điểm d, đ, g, i khoản 1 Điều 28 của Luật Xử lý vi phạm hành chính và khoản 3 Điều 4 của Nghị định này.</t>
+          <t>3. Nếu xét thấy các bên có đủ điều kiện theo quy định tại Điều 14 của Luật Nuôi con nuôi, thì trong thời hạn 15 ngày làm việc, kể từ ngày lấy ý kiến của những người liên quan, Cơ quan đại diện đăng ký việc nuôi con nuôi. Khi đăng ký nuôi con nuôi, cha mẹ nuôi, cha mẹ đẻ, người giám hộ và người được nhận làm con nuôi phải có mặt. Cơ quan đại diện ghi vào Sổ đăng ký nuôi con nuôi và trao Giấy chứng nhận nuôi con nuôi cho các bên, đồng thời gửi văn bản thông báo cho Bộ Tư pháp và Cục Lãnh sự kèm theo bản sao Giấy chứng nhận nuôi con nuôi.</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Điểm đ Khoản 4 Điều 84</t>
+          <t>Khoản 3 Điều 27</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>98/2020/NĐ-CP</t>
+          <t>19/2011/NĐ-CP</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=143881</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=26222</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2026,16 +2036,21 @@
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Một cặp vợ chồng đăng ký nuôi con nuôi tại Cơ quan đại diện thì nếu đủ điều kiện, việc xin ý kiến cơ quan trong nước được thực hiện trong thời hạn bao lâu và gửi cơ quan nào?»; nhãn cũ khong_dat question_ambiguous: Khoản 3 là đăng ký nuôi con nuôi rồi gửi văn bản thông báo; câu hỏi gọi đó là 'xin ý kiến cơ quan trong nước', vốn là việc của khoản 4 (yêu cầu cơ quan trong nước kiểm tra, xác minh). Đề xuất hỏi thời hạn đăng ký và nơi gửi thông báo). Hỏi thời hạn đăng ký và nơi nhận thông báo: 20 ngày/Cục Con nuôi, 20 ngày/Bộ Tư pháp, 15 ngày làm việc/Bộ Tư pháp; ba đáp án</t>
+        </is>
+      </c>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>vilextime:T3:provision:52a1bca6-eb7f-11f0-bacc-3745bc0439a2:2020-06-16</t>
+          <t>vilextime:T3:provision:406c63b0-2c7f-11f1-9540-7d73c403d1d2:2022-02-01</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2045,37 +2060,37 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Nếu một tàu bay hoạt động gần sân bay, thì theo quy định về quản lý hoạt động bay, phạm vi của khái niệm hoạt động tại sân bay được xác định như thế nào?</t>
+          <t>Chủ tịch Ủy ban nhân dân cấp huyện xử phạt vi phạm hành chính về thương mại, hàng giả, hàng cấm và bảo vệ quyền lợi người tiêu dùng thì được áp dụng những biện pháp khắc phục hậu quả nào?</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2020-06-16</t>
+          <t>2022-02-01</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Trong Thông tư này, các từ ngữ dưới đây được hiểu như sau:</t>
+          <t>2. Chủ tịch Ủy ban nhân dân cấp huyện có quyền:</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>52. Hoạt động tại sân bay là tất cả hoạt động trên khu vực di chuyển tại sân bay và tất cả hoạt động bay trong vùng trời sân bay.</t>
+          <t>đ) Áp dụng các biện pháp khắc phục hậu quả quy định tại các điểm b, c, đ, e, g, h, i, k và l khoản 3 Điều 4 của Nghị định này.</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Khoản 52 Điều 4</t>
+          <t>Điểm đ Khoản 2 Điều 81</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>19/2017/TT-BGTVT</t>
+          <t>98/2020/NĐ-CP</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=122388</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=143881</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2090,16 +2105,21 @@
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Đáp án là danh sách dẫn chiếu điểm, khoản (như nhãn dat của 38/2024 Điều 51 ở T2); ba đáp án khác nhau</t>
+        </is>
+      </c>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>vilextime:T3:provision:5d48bef2-df54-11f0-abca-45ca78a631ce:2025-07-02</t>
+          <t>vilextime:T3:provision:40778740-2c7f-11f1-abee-c9b7a53cf5c7:2025-02-22</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2109,37 +2129,37 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Nếu hàng hóa của Trung Quốc quá cảnh qua lãnh thổ Việt Nam, thì cơ quan nào tổ chức thực hiện việc cấp giấy phép quá cảnh?</t>
+          <t>Khi Cục trưởng Cục điều tra chống buôn lậu xử phạt vi phạm về hàng giả, hàng cấm, người này được áp dụng những biện pháp khắc phục hậu quả nào?</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-02-22</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Điều 18. Tổ chức thực hiện</t>
+          <t>4. Cục trưởng Cục điều tra chống buôn lậu, Cục trưởng Cục kiểm tra sau thông quan thuộc Tổng cục Hải quan, Cục trưởng Cục Hải quan tỉnh, liên tỉnh, thành phố trực thuộc trung ương có quyền:</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1. Cục Xuất nhập khẩu - Bộ Công Thương thực hiện việc cấp giấy phép quá cảnh hàng hóa quy định tại Khoản 1 Điều 6 Thông tư này.</t>
+          <t>đ) Áp dụng các biện pháp khắc phục hậu quả quy định tại các điểm d, đ, g, i khoản 1 Điều 28 của Luật Xử lý vi phạm hành chính và khoản 3 Điều 4 của Nghị định này.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Khoản 1 Điều 18</t>
+          <t>Điểm đ Khoản 4 Điều 84</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>11/2015/TT-BCT</t>
+          <t>98/2020/NĐ-CP</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=67521</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=143881</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2159,11 +2179,12 @@
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>vilextime:T3:provision:64015f1e-2c85-11f1-bf18-f11eea13dfa4:2014-04-11</t>
+          <t>vilextime:T3:provision:52a1bca6-eb7f-11f0-bacc-3745bc0439a2:2020-06-16</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2173,37 +2194,37 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Trường hợp cần bồi dưỡng kiến thức quốc phòng và an ninh cho già làng, trưởng bản và người có uy tín trong cộng đồng, ai có thẩm quyền triệu tập và đối tượng gồm những ai?</t>
+          <t>Nếu một tàu bay hoạt động gần sân bay, thì theo quy định về quản lý hoạt động bay, phạm vi của khái niệm hoạt động tại sân bay được xác định như thế nào?</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2014-04-11</t>
+          <t>2020-06-16</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>3. Đối tượng là cá nhân tiêu biểu, người có uy tín trong cộng đồng dân cư</t>
+          <t>Trong Thông tư này, các từ ngữ dưới đây được hiểu như sau:</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>b) Chủ tịch Hội đồng giáo dục và an ninh cấp huyện triệu tập bồi dưỡng kiến thức quốc phòng và an ninh cho chức việc tôn giáo, già làng, trưởng họ tộc trên địa bàn theo kế hoạch được Chủ tịch Ủy ban nhân dân cấp huyện phê duyệt.</t>
+          <t>52. Hoạt động tại sân bay là tất cả hoạt động trên khu vực di chuyển tại sân bay và tất cả hoạt động bay trong vùng trời sân bay.</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Điểm b Khoản 3 Điều 2</t>
+          <t>Khoản 52 Điều 4</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>13/2014/NĐ-CP</t>
+          <t>19/2017/TT-BGTVT</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=33548</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=122388</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2213,33 +2234,22 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>question_ambiguous</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>'Người có uy tín trong cộng đồng' là tên cả khoản 3; điểm a cùng khoản (Chủ tịch Hội đồng cấp tỉnh triệu tập) cũng thuộc nhóm này. Câu hỏi còn nói 'trưởng bản' trong khi văn bản là 'trưởng họ tộc'</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>a) Chủ tịch Hội đồng giáo dục quốc phòng và an ninh cấp tỉnh quyết định triệu tập bồi dưỡng kiến thức quốc phò...</t>
-        </is>
-      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>vilextime:T3:provision:64015f1e-2c85-11f1-bf18-f11eea13dfa4:2021-01-16</t>
+          <t>vilextime:T3:provision:5d48bef2-df54-11f0-abca-45ca78a631ce:2025-07-02</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2249,37 +2259,37 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Trường hợp cần bồi dưỡng kiến thức quốc phòng và an ninh cho già làng, trưởng bản và người có uy tín trong cộng đồng, ai có thẩm quyền triệu tập và đối tượng gồm những ai?</t>
+          <t>Nếu hàng hóa của Trung Quốc quá cảnh qua lãnh thổ Việt Nam, thì cơ quan nào tổ chức thực hiện việc cấp giấy phép quá cảnh?</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2021-01-16</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>3. Đối tượng là cá nhân tiêu biểu, người có uy tín trong cộng đồng dân cư</t>
+          <t>Điều 18. Tổ chức thực hiện</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>b) Chủ tịch Hội đồng giáo dục quốc phòng và an ninh cấp huyện triệu tập bồi dưỡng kiến thức quốc phòng và an ninh cho già làng, trưởng họ tộc trên địa bàn theo kế hoạch được Chủ tịch Ủy ban nhân dân cấp huyện phê duyệt.</t>
+          <t>1. Cục Xuất nhập khẩu - Bộ Công Thương thực hiện việc cấp giấy phép quá cảnh hàng hóa quy định tại Khoản 1 Điều 6 Thông tư này.</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Điểm b Khoản 3 Điều 2</t>
+          <t>Khoản 1 Điều 18</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>13/2014/NĐ-CP</t>
+          <t>11/2015/TT-BCT</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=33548</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=67521</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2289,33 +2299,22 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>question_ambiguous</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>'Người có uy tín trong cộng đồng' là tên cả khoản 3; điểm a cùng khoản (Chủ tịch Hội đồng cấp tỉnh triệu tập) cũng thuộc nhóm này. Câu hỏi còn nói 'trưởng bản' trong khi văn bản là 'trưởng họ tộc'</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>a) Chủ tịch Hội đồng giáo dục quốc phòng và an ninh cấp tỉnh quyết định triệu tập bồi dưỡng kiến thức quốc phò...</t>
-        </is>
-      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>vilextime:T3:provision:64015f1e-2c85-11f1-bf18-f11eea13dfa4:2025-08-08</t>
+          <t>vilextime:T3:provision:64015f1e-2c85-11f1-bf18-f11eea13dfa4:2014-04-11</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2325,12 +2324,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Trường hợp cần bồi dưỡng kiến thức quốc phòng và an ninh cho già làng, trưởng bản và người có uy tín trong cộng đồng, ai có thẩm quyền triệu tập và đối tượng gồm những ai?</t>
+          <t>Ở địa bàn dưới cấp tỉnh, việc bồi dưỡng kiến thức quốc phòng và an ninh cho người có uy tín như già làng, trưởng họ tộc, chức việc tôn giáo do Chủ tịch Hội đồng cấp nào triệu tập và theo kế hoạch do ai phê duyệt?</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025-08-08</t>
+          <t>2014-04-11</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2340,7 +2339,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>b) Chủ tịch Hội đồng giáo dục và an ninh cấp xã triệu tập bồi dưỡng kiến thức quốc phòng và an ninh cho già làng, trưởng họ tộc trên địa bàn theo kế hoạch được Chủ tịch Ủy ban nhân dân cấp xã phê duyệt.</t>
+          <t>b) Chủ tịch Hội đồng giáo dục và an ninh cấp huyện triệu tập bồi dưỡng kiến thức quốc phòng và an ninh cho chức việc tôn giáo, già làng, trưởng họ tộc trên địa bàn theo kế hoạch được Chủ tịch Ủy ban nhân dân cấp huyện phê duyệt.</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2365,33 +2364,26 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>question_ambiguous</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
-          <t>'Người có uy tín trong cộng đồng' là tên cả khoản 3; điểm a cùng khoản (Chủ tịch Hội đồng cấp tỉnh triệu tập) cũng thuộc nhóm này. Câu hỏi còn nói 'trưởng bản' trong khi văn bản là 'trưởng họ tộc'</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>a) Chủ tịch Hội đồng giáo dục quốc phòng và an ninh cấp tỉnh quyết định triệu tập bồi dưỡng kiến thức quốc phò...</t>
-        </is>
-      </c>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Trường hợp cần bồi dưỡng kiến thức quốc phòng và an ninh cho già làng, trưởng bản và người có uy tín trong cộng đồng, ai có thẩm quyền triệu tập và đối tượng gồm những ai?»; nhãn cũ khong_dat question_ambiguous: 'Người có uy tín trong cộng đồng' là tên cả khoản 3; điểm a cùng khoản (Chủ tịch Hội đồng cấp tỉnh triệu tập) cũng thuộc nhóm này. Câu hỏi còn nói 'trưởng bản' trong khi văn bản là 'trưởng họ tộc'). Câu hỏi nêu cả chức việc tôn giáo nên chạm lần sửa 2021 (bỏ chức việc tôn giáo khỏi điểm b) và lần sửa 2025 (cấp huyện → cấp xã); ba đáp án. 'Dưới cấp tỉnh' loại điểm a</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>vilextime:T3:provision:6ab23f90-eb76-11f0-9edf-679bcacb72e6#k3:2011-09-06</t>
+          <t>vilextime:T3:provision:64015f1e-2c85-11f1-bf18-f11eea13dfa4:2021-01-16</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2401,37 +2393,37 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Trường hợp cổ phần hóa doanh nghiệp 100% vốn nhà nước, việc lựa chọn tổ chức tư vấn định giá được thực hiện theo nguyên tắc nào?</t>
+          <t>Ở địa bàn dưới cấp tỉnh, việc bồi dưỡng kiến thức quốc phòng và an ninh cho người có uy tín như già làng, trưởng họ tộc, chức việc tôn giáo do Chủ tịch Hội đồng cấp nào triệu tập và theo kế hoạch do ai phê duyệt?</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2011-09-06</t>
+          <t>2021-01-16</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Điều 22. Tư vấn xác định giá trị doanh nghiệp</t>
+          <t>3. Đối tượng là cá nhân tiêu biểu, người có uy tín trong cộng đồng dân cư</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>3. Cơ quan có thẩm quyền quyết định phương án cổ phần hóa lựa chọn tổ chức tư vấn định giá thực hiện tư vấn xác định giá trị doanh nghiệp. Trường hợp có từ 02 tổ chức tư vấn định giá đăng ký tham gia cung cấp dịch vụ tư vấn định giá trở lên thì phải tổ chức đấu thầu lựa chọn đơn vị thực hiện tư vấn định giá theo quy định hiện hành.</t>
+          <t>b) Chủ tịch Hội đồng giáo dục quốc phòng và an ninh cấp huyện triệu tập bồi dưỡng kiến thức quốc phòng và an ninh cho già làng, trưởng họ tộc trên địa bàn theo kế hoạch được Chủ tịch Ủy ban nhân dân cấp huyện phê duyệt.</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Khoản 3 Điều 22</t>
+          <t>Điểm b Khoản 3 Điều 2</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>59/2011/NĐ-CP</t>
+          <t>13/2014/NĐ-CP</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=26691</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=33548</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2441,29 +2433,26 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>group_mismatch</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Mốc 2 và 3 cùng nguyên tắc (không quá 03 tỷ đồng có thể chỉ định thầu, còn lại đấu thầu); mốc 3 chỉ sửa câu chữ ('hình thức tư vấn', 'Điểm a nói trên'). Chỉ hai đáp án; có thể chuyển T2 (mốc 1–2)</t>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Trường hợp cần bồi dưỡng kiến thức quốc phòng và an ninh cho già làng, trưởng bản và người có uy tín trong cộng đồng, ai có thẩm quyền triệu tập và đối tượng gồm những ai?»; nhãn cũ khong_dat question_ambiguous: 'Người có uy tín trong cộng đồng' là tên cả khoản 3; điểm a cùng khoản (Chủ tịch Hội đồng cấp tỉnh triệu tập) cũng thuộc nhóm này. Câu hỏi còn nói 'trưởng bản' trong khi văn bản là 'trưởng họ tộc'). Câu hỏi nêu cả chức việc tôn giáo nên chạm lần sửa 2021 (bỏ chức việc tôn giáo khỏi điểm b) và lần sửa 2025 (cấp huyện → cấp xã); ba đáp án. 'Dưới cấp tỉnh' loại điểm a</t>
         </is>
       </c>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>vilextime:T3:provision:6ab23f90-eb76-11f0-9edf-679bcacb72e6#k3:2014-01-16</t>
+          <t>vilextime:T3:provision:64015f1e-2c85-11f1-bf18-f11eea13dfa4:2025-08-08</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2473,37 +2462,37 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Trường hợp cổ phần hóa doanh nghiệp 100% vốn nhà nước, việc lựa chọn tổ chức tư vấn định giá được thực hiện theo nguyên tắc nào?</t>
+          <t>Ở địa bàn dưới cấp tỉnh, việc bồi dưỡng kiến thức quốc phòng và an ninh cho người có uy tín như già làng, trưởng họ tộc, chức việc tôn giáo do Chủ tịch Hội đồng cấp nào triệu tập và theo kế hoạch do ai phê duyệt?</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2014-01-16</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Điều 22. Tư vấn xác định giá trị doanh nghiệp</t>
+          <t>3. Đối tượng là cá nhân tiêu biểu, người có uy tín trong cộng đồng dân cư</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>3. Cơ quan có thẩm quyền quyết định phương án cổ phần hóa lựa chọn tổ chức tư vấn định giá thực hiện tư vấn xác định giá trị doanh nghiệp theo nguyên tắc: a) Đối với các gói thầu, tư vấn định giá có giá trị không quá 03 tỷ đồng thì cơ quan có thẩm quyền quyết định phương án cổ phần hóa có thể lựa chọn hình thức chỉ định thầu để lựa chọn tổ chức tư vấn định giá trong danh sách do Bộ Tài chính công bố; trường hợp xét thấy cần phải tổ chức đấu thầu thì thực hiện đấu thầu theo quy định của pháp luật về đấu thầu. b) Đối với các gói thầu tư vấn không thuộc quy định tại điểm a khoản 3 Điều này thì cơ quan có thẩm quyền quyết định phương án cổ phần hóa quyết định tổ chức đấu thầu lựa chọn đơn vị thực hiện tư vấn định giá theo quy định</t>
+          <t>b) Chủ tịch Hội đồng giáo dục và an ninh cấp xã triệu tập bồi dưỡng kiến thức quốc phòng và an ninh cho già làng, trưởng họ tộc trên địa bàn theo kế hoạch được Chủ tịch Ủy ban nhân dân cấp xã phê duyệt.</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Khoản 3 Điều 22</t>
+          <t>Điểm b Khoản 3 Điều 2</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>59/2011/NĐ-CP</t>
+          <t>13/2014/NĐ-CP</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=26691</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=33548</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2513,29 +2502,26 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>group_mismatch</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Mốc 2 và 3 cùng nguyên tắc (không quá 03 tỷ đồng có thể chỉ định thầu, còn lại đấu thầu); mốc 3 chỉ sửa câu chữ ('hình thức tư vấn', 'Điểm a nói trên'). Chỉ hai đáp án; có thể chuyển T2 (mốc 1–2)</t>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Trường hợp cần bồi dưỡng kiến thức quốc phòng và an ninh cho già làng, trưởng bản và người có uy tín trong cộng đồng, ai có thẩm quyền triệu tập và đối tượng gồm những ai?»; nhãn cũ khong_dat question_ambiguous: 'Người có uy tín trong cộng đồng' là tên cả khoản 3; điểm a cùng khoản (Chủ tịch Hội đồng cấp tỉnh triệu tập) cũng thuộc nhóm này. Câu hỏi còn nói 'trưởng bản' trong khi văn bản là 'trưởng họ tộc'). Câu hỏi nêu cả chức việc tôn giáo nên chạm lần sửa 2021 (bỏ chức việc tôn giáo khỏi điểm b) và lần sửa 2025 (cấp huyện → cấp xã); ba đáp án. 'Dưới cấp tỉnh' loại điểm a</t>
         </is>
       </c>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>vilextime:T3:provision:6ab23f90-eb76-11f0-9edf-679bcacb72e6#k3:2015-11-12</t>
+          <t>vilextime:T3:provision:6ab23f90-eb76-11f0-9edf-679bcacb72e6#k3:2011-09-06</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2550,7 +2536,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2015-11-12</t>
+          <t>2011-09-06</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2560,7 +2546,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>3. Cơ quan có thẩm quyền quyết định phương án cổ phần hóa lựa chọn tổ chức tư vấn định giá thực hiện tư vấn xác định giá trị doanh nghiệp theo nguyên tắc: a) Đối với các gói thầu, tư vấn định giá có giá trị không quá 03 tỷ đồng thì cơ quan có thẩm quyền quyết định phương án cổ phần hóa có thể lựa chọn hình thức chỉ định thầu để lựa chọn hình thức tư vấn định giá trong danh sách do Bộ Tài chính công bố; trường hợp xét thấy cần phải tổ chức đấu thầu thì thực hiện đấu thầu theo quy định của pháp luật về đấu thầu. b) Đối với các gói thầu tư vấn không thuộc quy định tại Điểm a nói trên thì cơ quan có thẩm quyền quyết định phương án cổ phần hóa quyết định tổ chức đấu thầu lựa chọn đơn vị thực hiện tư vấn định giá theo quy định</t>
+          <t>3. Cơ quan có thẩm quyền quyết định phương án cổ phần hóa lựa chọn tổ chức tư vấn định giá thực hiện tư vấn xác định giá trị doanh nghiệp. Trường hợp có từ 02 tổ chức tư vấn định giá đăng ký tham gia cung cấp dịch vụ tư vấn định giá trở lên thì phải tổ chức đấu thầu lựa chọn đơn vị thực hiện tư vấn định giá theo quy định hiện hành.</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2600,14 +2586,19 @@
         </is>
       </c>
       <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>loại lineage (group_mismatch): Mốc 2 và 3 cùng nguyên tắc (không quá 03 tỷ đồng có thể chỉ định thầu, còn lại đấu thầu); mốc 3 chỉ sửa câu chữ ('hình thức tư vấn', 'Điểm a nói trên'). Chỉ hai đáp án; có thể chuyển T2 (mốc 1–2)</t>
+        </is>
+      </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>vilextime:T3:provision:6ece9720-1edb-11f1-b5ee-25d1c75e0691:2022-01-02</t>
+          <t>vilextime:T3:provision:6ab23f90-eb76-11f0-9edf-679bcacb72e6#k3:2014-01-16</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2617,37 +2608,37 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Khi Chủ tịch Ủy ban nhân dân cấp huyện xử phạt vi phạm về quản lý, sử dụng tài sản công, quyền tịch thu tang vật, phương tiện của người này có bị giới hạn về giá trị không?</t>
+          <t>Trường hợp cổ phần hóa doanh nghiệp 100% vốn nhà nước, việc lựa chọn tổ chức tư vấn định giá được thực hiện theo nguyên tắc nào?</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2022-01-02</t>
+          <t>2014-01-16</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1. Chủ tịch Ủy ban nhân dân cấp huyện có quyền:</t>
+          <t>Điều 22. Tư vấn xác định giá trị doanh nghiệp</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>c) Tịch thu tang vật, phương tiện vi phạm hành chính có giá trị không vượt quá 100.000.000 đồng</t>
+          <t>3. Cơ quan có thẩm quyền quyết định phương án cổ phần hóa lựa chọn tổ chức tư vấn định giá thực hiện tư vấn xác định giá trị doanh nghiệp theo nguyên tắc: a) Đối với các gói thầu, tư vấn định giá có giá trị không quá 03 tỷ đồng thì cơ quan có thẩm quyền quyết định phương án cổ phần hóa có thể lựa chọn hình thức chỉ định thầu để lựa chọn tổ chức tư vấn định giá trong danh sách do Bộ Tài chính công bố; trường hợp xét thấy cần phải tổ chức đấu thầu thì thực hiện đấu thầu theo quy định của pháp luật về đấu thầu. b) Đối với các gói thầu tư vấn không thuộc quy định tại điểm a khoản 3 Điều này thì cơ quan có thẩm quyền quyết định phương án cổ phần hóa quyết định tổ chức đấu thầu lựa chọn đơn vị thực hiện tư vấn định giá theo quy định</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Điểm c Khoản 1 Điều 51</t>
+          <t>Khoản 3 Điều 22</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>63/2019/NĐ-CP</t>
+          <t>59/2011/NĐ-CP</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=136309</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=26691</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2657,21 +2648,34 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>dat</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr"/>
+          <t>khong_dat</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>group_mismatch</t>
+        </is>
+      </c>
       <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Mốc 2 và 3 cùng nguyên tắc (không quá 03 tỷ đồng có thể chỉ định thầu, còn lại đấu thầu); mốc 3 chỉ sửa câu chữ ('hình thức tư vấn', 'Điểm a nói trên'). Chỉ hai đáp án; có thể chuyển T2 (mốc 1–2)</t>
+        </is>
+      </c>
       <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>loại lineage (group_mismatch): Mốc 2 và 3 cùng nguyên tắc (không quá 03 tỷ đồng có thể chỉ định thầu, còn lại đấu thầu); mốc 3 chỉ sửa câu chữ ('hình thức tư vấn', 'Điểm a nói trên'). Chỉ hai đáp án; có thể chuyển T2 (mốc 1–2)</t>
+        </is>
+      </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>vilextime:T3:provision:6ece9720-1edb-11f1-b5ee-25d1c75e0691:2026-02-10</t>
+          <t>vilextime:T3:provision:6ab23f90-eb76-11f0-9edf-679bcacb72e6#k3:2015-11-12</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2681,37 +2685,37 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Khi Chủ tịch Ủy ban nhân dân cấp huyện xử phạt vi phạm về quản lý, sử dụng tài sản công, quyền tịch thu tang vật, phương tiện của người này có bị giới hạn về giá trị không?</t>
+          <t>Trường hợp cổ phần hóa doanh nghiệp 100% vốn nhà nước, việc lựa chọn tổ chức tư vấn định giá được thực hiện theo nguyên tắc nào?</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2015-11-12</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1. Chủ tịch Ủy ban nhân dân cấp xã có quyền:</t>
+          <t>Điều 22. Tư vấn xác định giá trị doanh nghiệp</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>c) Tịch thu tang vật, phương tiện vi phạm hành chính;</t>
+          <t>3. Cơ quan có thẩm quyền quyết định phương án cổ phần hóa lựa chọn tổ chức tư vấn định giá thực hiện tư vấn xác định giá trị doanh nghiệp theo nguyên tắc: a) Đối với các gói thầu, tư vấn định giá có giá trị không quá 03 tỷ đồng thì cơ quan có thẩm quyền quyết định phương án cổ phần hóa có thể lựa chọn hình thức chỉ định thầu để lựa chọn hình thức tư vấn định giá trong danh sách do Bộ Tài chính công bố; trường hợp xét thấy cần phải tổ chức đấu thầu thì thực hiện đấu thầu theo quy định của pháp luật về đấu thầu. b) Đối với các gói thầu tư vấn không thuộc quy định tại Điểm a nói trên thì cơ quan có thẩm quyền quyết định phương án cổ phần hóa quyết định tổ chức đấu thầu lựa chọn đơn vị thực hiện tư vấn định giá theo quy định</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Điểm c Khoản 1 Điều 51</t>
+          <t>Khoản 3 Điều 22</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>63/2019/NĐ-CP</t>
+          <t>59/2011/NĐ-CP</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=136309</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=26691</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2726,24 +2730,29 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>unanswerable_as_asked</t>
+          <t>group_mismatch</t>
         </is>
       </c>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Từ 2026-02-10 khoản 1 trao quyền cho Chủ tịch Ủy ban nhân dân cấp xã (cấp huyện không còn); câu hỏi vẫn hỏi Chủ tịch cấp huyện. Đề xuất sửa câu hỏi thành 'Chủ tịch Ủy ban nhân dân theo khoản 1 Điều 51'</t>
+          <t>Mốc 2 và 3 cùng nguyên tắc (không quá 03 tỷ đồng có thể chỉ định thầu, còn lại đấu thầu); mốc 3 chỉ sửa câu chữ ('hình thức tư vấn', 'Điểm a nói trên'). Chỉ hai đáp án; có thể chuyển T2 (mốc 1–2)</t>
         </is>
       </c>
       <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>loại lineage (group_mismatch): Mốc 2 và 3 cùng nguyên tắc (không quá 03 tỷ đồng có thể chỉ định thầu, còn lại đấu thầu); mốc 3 chỉ sửa câu chữ ('hình thức tư vấn', 'Điểm a nói trên'). Chỉ hai đáp án; có thể chuyển T2 (mốc 1–2)</t>
+        </is>
+      </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>vilextime:T3:provision:6fbb0706-2c80-11f1-af00-8de7411db35a:2013-09-16</t>
+          <t>vilextime:T3:provision:6ece9720-1edb-11f1-b5ee-25d1c75e0691:2019-09-02</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2753,37 +2762,37 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Trong lĩnh vực mua, bán nợ xấu của công ty quản lý tài sản, hồ sơ đề nghị bán nợ phải kèm bản sao những loại hợp đồng nào?</t>
+          <t>Khi Chủ tịch Ủy ban nhân dân dưới cấp tỉnh xử phạt trong lĩnh vực dự trữ quốc gia, người này được áp dụng hình thức xử phạt bổ sung nào đối với tang vật, phương tiện vi phạm và có bị giới hạn về giá trị không?</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2013-09-16</t>
+          <t>2019-09-02</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1. Tổ chức tín dụng rà soát các khoản nợ xấu đáp ứng các điều kiện quy định tại khoản 1 Điều 16 Thông tư này và lập hồ sơ đề nghị mua nợ gửi Công ty Quản lý tài sản. Hồ sơ bao gồm:</t>
+          <t>1. Chủ tịch Ủy ban nhân dân cấp huyện có quyền:</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>d) Bản sao hợp đồng tín dụng, hợp đồng ủy thác, hợp đồng mua trái phiếu doanh nghiệp, hợp đồng bảo đảm tài sản do người đại diện hợp pháp của tổ chức tín dụng bán nợ xác nhận;</t>
+          <t>c) Tịch thu tang vật, phương tiện vi phạm hành chính có giá trị không vượt quá mức phạt tiền quy định tại điểm b khoản này;</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Điểm d Khoản 1 Điều 17</t>
+          <t>Điểm c Khoản 1 Điều 51</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>19/2013/TT-NHNN</t>
+          <t>63/2019/NĐ-CP</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=43247</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=136309</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2793,29 +2802,26 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>group_mismatch</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
-          <t>Chỉ hai đáp án: danh sách hợp đồng của mốc 1 và danh sách mở rộng từ 2020; lần sửa 2024 chỉ thêm 'Việt Nam' sau 'tổ chức tín dụng'. Có thể chuyển T2 (mốc 1–2)</t>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Khi Chủ tịch Ủy ban nhân dân cấp huyện xử phạt vi phạm về quản lý, sử dụng tài sản công, quyền tịch thu tang vật, phương tiện của người này có bị giới hạn về giá trị không?»; nhãn cũ dat: ). Sửa lỗi gán trước: Điều 51 NĐ 63/2019 là lĩnh vực dự trữ quốc gia, câu hỏi cũ nói tài sản công. Câu mới gọi 'Chủ tịch UBND dưới cấp tỉnh' đúng cho cả cấp huyện (mốc 1–2) và cấp xã (mốc 3); ba đáp án: giới hạn theo điểm b, giới hạn 100 triệu, không giới hạn</t>
         </is>
       </c>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>vilextime:T3:provision:6fbb0706-2c80-11f1-af00-8de7411db35a:2020-02-15</t>
+          <t>vilextime:T3:provision:6ece9720-1edb-11f1-b5ee-25d1c75e0691:2022-01-02</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2825,37 +2831,37 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Trong lĩnh vực mua, bán nợ xấu của công ty quản lý tài sản, hồ sơ đề nghị bán nợ phải kèm bản sao những loại hợp đồng nào?</t>
+          <t>Khi Chủ tịch Ủy ban nhân dân dưới cấp tỉnh xử phạt trong lĩnh vực dự trữ quốc gia, người này được áp dụng hình thức xử phạt bổ sung nào đối với tang vật, phương tiện vi phạm và có bị giới hạn về giá trị không?</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2020-02-15</t>
+          <t>2022-01-02</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1. Tổ chức tín dụng rà soát các khoản nợ xấu đáp ứng các điều kiện quy định tại khoản 1 Điều 16 Thông tư này và lập hồ sơ đề nghị mua nợ gửi Công ty Quản lý tài sản. Hồ sơ bao gồm:</t>
+          <t>1. Chủ tịch Ủy ban nhân dân cấp huyện có quyền:</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>d) Bản sao hợp đồng tín dụng hoặc thỏa thuận cho vay, hợp đồng ủy thác cấp tín dụng, hợp đồng mua bán nợ, hợp đồng mua, ủy thác mua trái phiếu doanh nghiệp, hợp đồng bảo đảm do người đại diện hợp pháp của tổ chức tín dụng bán nợ xác nhận;</t>
+          <t>c) Tịch thu tang vật, phương tiện vi phạm hành chính có giá trị không vượt quá 100.000.000 đồng</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Điểm d Khoản 1 Điều 17</t>
+          <t>Điểm c Khoản 1 Điều 51</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>19/2013/TT-NHNN</t>
+          <t>63/2019/NĐ-CP</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=43247</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=136309</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2865,29 +2871,26 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>group_mismatch</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
-          <t>Chỉ hai đáp án: danh sách hợp đồng của mốc 1 và danh sách mở rộng từ 2020; lần sửa 2024 chỉ thêm 'Việt Nam' sau 'tổ chức tín dụng'. Có thể chuyển T2 (mốc 1–2)</t>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Khi Chủ tịch Ủy ban nhân dân cấp huyện xử phạt vi phạm về quản lý, sử dụng tài sản công, quyền tịch thu tang vật, phương tiện của người này có bị giới hạn về giá trị không?»; nhãn cũ dat: ). Sửa lỗi gán trước: Điều 51 NĐ 63/2019 là lĩnh vực dự trữ quốc gia, câu hỏi cũ nói tài sản công. Câu mới gọi 'Chủ tịch UBND dưới cấp tỉnh' đúng cho cả cấp huyện (mốc 1–2) và cấp xã (mốc 3); ba đáp án: giới hạn theo điểm b, giới hạn 100 triệu, không giới hạn</t>
         </is>
       </c>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>vilextime:T3:provision:6fbb0706-2c80-11f1-af00-8de7411db35a:2024-07-02</t>
+          <t>vilextime:T3:provision:6ece9720-1edb-11f1-b5ee-25d1c75e0691:2026-02-10</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2897,37 +2900,37 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Trong lĩnh vực mua, bán nợ xấu của công ty quản lý tài sản, hồ sơ đề nghị bán nợ phải kèm bản sao những loại hợp đồng nào?</t>
+          <t>Khi Chủ tịch Ủy ban nhân dân dưới cấp tỉnh xử phạt trong lĩnh vực dự trữ quốc gia, người này được áp dụng hình thức xử phạt bổ sung nào đối với tang vật, phương tiện vi phạm và có bị giới hạn về giá trị không?</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1. Tổ chức tín dụng rà soát các khoản nợ xấu đáp ứng các điều kiện quy định tại khoản 1 Điều 16 Thông tư này và lập hồ sơ đề nghị mua nợ gửi Công ty Quản lý tài sản. Hồ sơ bao gồm:</t>
+          <t>1. Chủ tịch Ủy ban nhân dân cấp xã có quyền:</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>d) Bản sao hợp đồng tín dụng hoặc thỏa thuận cho vay, hợp đồng ủy thác cấp tín dụng, hợp đồng mua bán nợ, hợp đồng mua, ủy thác mua trái phiếu doanh nghiệp, hợp đồng bảo đảm do người đại diện hợp pháp của tổ chức tín dụng Việt Nam bán nợ xác nhận;</t>
+          <t>c) Tịch thu tang vật, phương tiện vi phạm hành chính;</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Điểm d Khoản 1 Điều 17</t>
+          <t>Điểm c Khoản 1 Điều 51</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>19/2013/TT-NHNN</t>
+          <t>63/2019/NĐ-CP</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=43247</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=136309</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2937,29 +2940,26 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>group_mismatch</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
-          <t>Chỉ hai đáp án: danh sách hợp đồng của mốc 1 và danh sách mở rộng từ 2020; lần sửa 2024 chỉ thêm 'Việt Nam' sau 'tổ chức tín dụng'. Có thể chuyển T2 (mốc 1–2)</t>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Khi Chủ tịch Ủy ban nhân dân cấp huyện xử phạt vi phạm về quản lý, sử dụng tài sản công, quyền tịch thu tang vật, phương tiện của người này có bị giới hạn về giá trị không?»; nhãn cũ khong_dat unanswerable_as_asked: Từ 2026-02-10 khoản 1 trao quyền cho Chủ tịch Ủy ban nhân dân cấp xã (cấp huyện không còn); câu hỏi vẫn hỏi Chủ tịch cấp huyện. Đề xuất sửa câu hỏi thành 'Chủ tịch Ủy ban nhân dân theo khoản 1 Điều 51'). Sửa lỗi gán trước: Điều 51 NĐ 63/2019 là lĩnh vực dự trữ quốc gia, câu hỏi cũ nói tài sản công. Câu mới gọi 'Chủ tịch UBND dưới cấp tỉnh' đúng cho cả cấp huyện (mốc 1–2) và cấp xã (mốc 3); ba đáp án: giới hạn theo điểm b, giới hạn 100 triệu, không giới hạn</t>
         </is>
       </c>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>vilextime:T3:provision:746ee898-eb72-11f0-a645-6bade352d545#k3:2022-03-02</t>
+          <t>vilextime:T3:provision:6fbb0706-2c80-11f1-af00-8de7411db35a:2013-09-16</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2969,37 +2969,37 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Trong lĩnh vực phòng, chống thiên tai đường bộ, cơ quan quản lý đường bộ bao gồm những cơ quan nào?</t>
+          <t>Trong lĩnh vực mua, bán nợ xấu của công ty quản lý tài sản, hồ sơ đề nghị bán nợ phải kèm bản sao những loại hợp đồng nào?</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2022-03-02</t>
+          <t>2013-09-16</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Điều 3. Giải thích từ ngữ</t>
+          <t>1. Tổ chức tín dụng rà soát các khoản nợ xấu đáp ứng các điều kiện quy định tại khoản 1 Điều 16 Thông tư này và lập hồ sơ đề nghị mua nợ gửi Công ty Quản lý tài sản. Hồ sơ bao gồm:</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>3. Cơ quan quản lý đường bộ là Tổng cục Đường bộ Việt Nam, Cục Quản lý đường bộ; cơ quan chuyên môn về giao thông vận tải thuộc Ủy ban nhân dân cấp tỉnh (sau đây gọi là Sở Giao thông vận tải), Ủy ban nhân dân cấp huyện, Ủy ban nhân dân cấp xã.</t>
+          <t>d) Bản sao hợp đồng tín dụng, hợp đồng ủy thác, hợp đồng mua trái phiếu doanh nghiệp, hợp đồng bảo đảm tài sản do người đại diện hợp pháp của tổ chức tín dụng bán nợ xác nhận;</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Khoản 3 Điều 3</t>
+          <t>Điểm d Khoản 1 Điều 17</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>03/2019/TT-BGTVT</t>
+          <t>19/2013/TT-NHNN</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=136091</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=43247</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -3009,21 +3009,34 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>dat</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr"/>
+          <t>khong_dat</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>group_mismatch</t>
+        </is>
+      </c>
       <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Chỉ hai đáp án: danh sách hợp đồng của mốc 1 và danh sách mở rộng từ 2020; lần sửa 2024 chỉ thêm 'Việt Nam' sau 'tổ chức tín dụng'. Có thể chuyển T2 (mốc 1–2)</t>
+        </is>
+      </c>
       <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>loại lineage (group_mismatch): Chỉ hai đáp án: danh sách hợp đồng của mốc 1 và danh sách mở rộng từ 2020; lần sửa 2024 chỉ thêm 'Việt Nam' sau 'tổ chức tín dụng'. Có thể chuyển T2 (mốc 1–2)</t>
+        </is>
+      </c>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>vilextime:T3:provision:938c3d26-eb99-11f0-bfb4-15b5584e2964:2016-02-02</t>
+          <t>vilextime:T3:provision:6fbb0706-2c80-11f1-af00-8de7411db35a:2020-02-15</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3033,37 +3046,37 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Pháp luật về chữ ký số của Ngân hàng Nhà nước quy định chứng thư số bị tạm dừng do sai sót, sự cố được khôi phục như thế nào?</t>
+          <t>Trong lĩnh vực mua, bán nợ xấu của công ty quản lý tài sản, hồ sơ đề nghị bán nợ phải kèm bản sao những loại hợp đồng nào?</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2016-02-02</t>
+          <t>2020-02-15</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2. Chứng thư số của thuê bao được khôi phục trong các trường hợp sau:</t>
+          <t>1. Tổ chức tín dụng rà soát các khoản nợ xấu đáp ứng các điều kiện quy định tại khoản 1 Điều 16 Thông tư này và lập hồ sơ đề nghị mua nợ gửi Công ty Quản lý tài sản. Hồ sơ bao gồm:</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>d) Chứng thư số bị tạm dừng theo quy định tại điểm d Khoản 1 Điều 7 Thông tư này và những sai sót, sự cố đó đã được khắc phục.</t>
+          <t>d) Bản sao hợp đồng tín dụng hoặc thỏa thuận cho vay, hợp đồng ủy thác cấp tín dụng, hợp đồng mua bán nợ, hợp đồng mua, ủy thác mua trái phiếu doanh nghiệp, hợp đồng bảo đảm do người đại diện hợp pháp của tổ chức tín dụng bán nợ xác nhận;</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Điểm d Khoản 2 Điều 8</t>
+          <t>Điểm d Khoản 1 Điều 17</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>28/2015/TT-NHNN</t>
+          <t>19/2013/TT-NHNN</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=94467</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=43247</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -3084,18 +3097,23 @@
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
-          <t>Điều kiện khôi phục không đổi qua ba mốc (sai sót, sự cố đã được khắc phục); mốc 2 chỉ đổi dẫn chiếu điểm d thành điểm c do Điều 7 đánh số lại</t>
+          <t>Chỉ hai đáp án: danh sách hợp đồng của mốc 1 và danh sách mở rộng từ 2020; lần sửa 2024 chỉ thêm 'Việt Nam' sau 'tổ chức tín dụng'. Có thể chuyển T2 (mốc 1–2)</t>
         </is>
       </c>
       <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>loại lineage (group_mismatch): Chỉ hai đáp án: danh sách hợp đồng của mốc 1 và danh sách mở rộng từ 2020; lần sửa 2024 chỉ thêm 'Việt Nam' sau 'tổ chức tín dụng'. Có thể chuyển T2 (mốc 1–2)</t>
+        </is>
+      </c>
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>vilextime:T3:provision:938c3d26-eb99-11f0-bfb4-15b5584e2964:2021-01-02</t>
+          <t>vilextime:T3:provision:6fbb0706-2c80-11f1-af00-8de7411db35a:2024-07-02</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3105,37 +3123,37 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Pháp luật về chữ ký số của Ngân hàng Nhà nước quy định chứng thư số bị tạm dừng do sai sót, sự cố được khôi phục như thế nào?</t>
+          <t>Trong lĩnh vực mua, bán nợ xấu của công ty quản lý tài sản, hồ sơ đề nghị bán nợ phải kèm bản sao những loại hợp đồng nào?</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2021-01-02</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2. Chứng thư số của thuê bao được khôi phục trong các trường hợp sau:</t>
+          <t>1. Tổ chức tín dụng rà soát các khoản nợ xấu đáp ứng các điều kiện quy định tại khoản 1 Điều 16 Thông tư này và lập hồ sơ đề nghị mua nợ gửi Công ty Quản lý tài sản. Hồ sơ bao gồm:</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>d) Chứng thư số bị tạm dừng theo quy định tại điểm c khoản 1 Điều 7 Thông tư này và những sai sót, sự cố đó đã được khắc phục.</t>
+          <t>d) Bản sao hợp đồng tín dụng hoặc thỏa thuận cho vay, hợp đồng ủy thác cấp tín dụng, hợp đồng mua bán nợ, hợp đồng mua, ủy thác mua trái phiếu doanh nghiệp, hợp đồng bảo đảm do người đại diện hợp pháp của tổ chức tín dụng Việt Nam bán nợ xác nhận;</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Điểm d Khoản 2 Điều 8</t>
+          <t>Điểm d Khoản 1 Điều 17</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>28/2015/TT-NHNN</t>
+          <t>19/2013/TT-NHNN</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=94467</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=43247</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -3156,18 +3174,23 @@
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
-          <t>Như mốc 1</t>
+          <t>Chỉ hai đáp án: danh sách hợp đồng của mốc 1 và danh sách mở rộng từ 2020; lần sửa 2024 chỉ thêm 'Việt Nam' sau 'tổ chức tín dụng'. Có thể chuyển T2 (mốc 1–2)</t>
         </is>
       </c>
       <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>loại lineage (group_mismatch): Chỉ hai đáp án: danh sách hợp đồng của mốc 1 và danh sách mở rộng từ 2020; lần sửa 2024 chỉ thêm 'Việt Nam' sau 'tổ chức tín dụng'. Có thể chuyển T2 (mốc 1–2)</t>
+        </is>
+      </c>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>vilextime:T3:provision:938c3d26-eb99-11f0-bfb4-15b5584e2964:2024-07-02</t>
+          <t>vilextime:T3:provision:746ee898-eb72-11f0-a645-6bade352d545#k3:2022-03-02</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3177,37 +3200,37 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Pháp luật về chữ ký số của Ngân hàng Nhà nước quy định chứng thư số bị tạm dừng do sai sót, sự cố được khôi phục như thế nào?</t>
+          <t>Trong lĩnh vực phòng, chống thiên tai đường bộ, cơ quan quản lý đường bộ bao gồm những cơ quan nào?</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
+          <t>2022-03-02</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2. Chứng thư số của thuê bao được khôi phục trong các trường hợp sau:</t>
+          <t>Điều 3. Giải thích từ ngữ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>d) Chứng thư số bị tạm dừng theo quy định tại điểm c khoản 1 Điều 7 Thông tư này và những sai sót, sự cố đó đã được khắc phục." "3. Tổ chức quản lý thuê bao gửi 01 (một) bộ hồ sơ đề nghị khôi phục chứng thư số theo quy định tại điểm b khoản 2 Điều này gồm Giấy đề nghị khôi phục chứng thư số theo Phụ lục 05 ban hành kèm theo Thông tư này. 4. Thời hạn giải quyết và kết quả thực hiện a) Trong thời hạn 01 ngày làm việc kể từ ngày nhận được văn bản đề nghị theo quy định tại điểm a khoản 2 Điều này hoặc hồ sơ đề nghị khôi phục chứng thư số hợp lệ theo quy định tại điểm b khoản 2 Điều này, Cục Công nghệ thông tin thực hiện khôi phục chứng thư số cho thuê bao. Trường hợp hồ sơ không hợp lệ, Cục Công nghệ thông tin từ chối xử lý hồ sơ và nêu rõ lý do trong thời hạn 01 ngày làm việc kể từ ngày nhận được hồ sơ. Thông tin phản hồi và kết quả xử lý được thực hiện theo quy định tại khoản 3 Điều 4a Thông tư này;</t>
+          <t>3. Cơ quan quản lý đường bộ là Tổng cục Đường bộ Việt Nam, Cục Quản lý đường bộ; cơ quan chuyên môn về giao thông vận tải thuộc Ủy ban nhân dân cấp tỉnh (sau đây gọi là Sở Giao thông vận tải), Ủy ban nhân dân cấp huyện, Ủy ban nhân dân cấp xã.</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Điểm d Khoản 2 Điều 8</t>
+          <t>Khoản 3 Điều 3</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>28/2015/TT-NHNN</t>
+          <t>03/2019/TT-BGTVT</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=94467</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=136091</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3217,33 +3240,22 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>group_mismatch</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>Như mốc 1. Văn bản đáp án mốc 3 dính cả khoản 3, 4 của lời văn sửa đổi (…đã được khắc phục." "3. Tổ chức quản lý thuê bao…)</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>vilextime:T3:provision:938c3da8-eb99-11f0-b3df-b36a9bf88f4b:2021-01-02</t>
+          <t>vilextime:T3:provision:938c3d26-eb99-11f0-bfb4-15b5584e2964:2016-02-02</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3253,27 +3265,27 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Thời hạn tạo cặp khóa và cách xử lý khi thuê bao không kịp tạo khóa được xác định ra sao trong quy định về chữ ký số của Ngân hàng Nhà nước?</t>
+          <t>Pháp luật về chữ ký số của Ngân hàng Nhà nước quy định chứng thư số bị tạm dừng do sai sót, sự cố được khôi phục như thế nào?</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2021-01-02</t>
+          <t>2016-02-02</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Điều 10. Tạo khóa và phân phối khóa</t>
+          <t>2. Chứng thư số của thuê bao được khôi phục trong các trường hợp sau:</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2. Thuê bao phải tạo cặp khóa trước ngày hết hạn của mã kích hoạt nêu tại thông báo cấp chứng thư số. Trường hợp bị lộ, nghi bị lộ mã kích hoạt hoặc quá ngày hết hạn kích hoạt tại thông báo cấp chứng thư số, thuê bao chưa tạo được cặp khóa và có nhu cầu tiếp tục sử dụng chứng thư số, tổ chức quản lý thuê bao gửi 01 (một) bộ hồ sơ gồm Giấy đề nghị thay đổi mã kích hoạt chứng thư số theo Phụ lục 08 ban hành kèm theo Thông tư này.</t>
+          <t>d) Chứng thư số bị tạm dừng theo quy định tại điểm d Khoản 1 Điều 7 Thông tư này và những sai sót, sự cố đó đã được khắc phục.</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Khoản 2 Điều 10</t>
+          <t>Điểm d Khoản 2 Điều 8</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3293,21 +3305,34 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>dat</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr"/>
+          <t>khong_dat</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>group_mismatch</t>
+        </is>
+      </c>
       <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Điều kiện khôi phục không đổi qua ba mốc (sai sót, sự cố đã được khắc phục); mốc 2 chỉ đổi dẫn chiếu điểm d thành điểm c do Điều 7 đánh số lại</t>
+        </is>
+      </c>
       <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>loại lineage (group_mismatch): Điều kiện khôi phục không đổi qua ba mốc (sai sót, sự cố đã được khắc phục); mốc 2 chỉ đổi dẫn chiếu điểm d thành điểm c do Điều 7 đánh số lại</t>
+        </is>
+      </c>
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
+      <c r="S41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>vilextime:T3:provision:96eb9928-2c7e-11f1-82dd-c36c58de53fd:2017-07-02</t>
+          <t>vilextime:T3:provision:938c3d26-eb99-11f0-bfb4-15b5584e2964:2021-01-02</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3317,37 +3342,37 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Nếu một tàu biển nước ngoài xin Giấy phép vận tải biển nội địa thông qua đại lý, thì hợp đồng đại lý trong hồ sơ được nộp dưới hình thức bản nào?</t>
+          <t>Pháp luật về chữ ký số của Ngân hàng Nhà nước quy định chứng thư số bị tạm dừng do sai sót, sự cố được khôi phục như thế nào?</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2017-07-02</t>
+          <t>2021-01-02</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Điều 6. Hồ sơ đề nghị cấp Giấy phép vận tải biển nội địa Hồ sơ đề nghị cấp Giấy phép vận tải biển nội địa bao gồm:</t>
+          <t>2. Chứng thư số của thuê bao được khôi phục trong các trường hợp sau:</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>4. 01 (một) bản sao có công chứng Hợp đồng đại lý hoặc 01 (một) bản sao có chứng thực giấy chỉ định đại lý đại diện cho chủ tàu nước ngoài (trong trường hợp tổ chức đề nghị là đại lý đại diện cho chủ tàu nước ngoài) hoặc 01 (một) bản sao có công chứng Hợp đồng thuê tàu giữa chủ tàu nước ngoài với pháp nhân Việt Nam.</t>
+          <t>d) Chứng thư số bị tạm dừng theo quy định tại điểm c khoản 1 Điều 7 Thông tư này và những sai sót, sự cố đó đã được khắc phục.</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Khoản 4 Điều 6</t>
+          <t>Điểm d Khoản 2 Điều 8</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>50/2016/TT-BGTVT</t>
+          <t>28/2015/TT-NHNN</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=118533</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=94467</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3357,21 +3382,34 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>dat</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr"/>
+          <t>khong_dat</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>group_mismatch</t>
+        </is>
+      </c>
       <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Như mốc 1</t>
+        </is>
+      </c>
       <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>loại lineage (group_mismatch): Điều kiện khôi phục không đổi qua ba mốc (sai sót, sự cố đã được khắc phục); mốc 2 chỉ đổi dẫn chiếu điểm d thành điểm c do Điều 7 đánh số lại</t>
+        </is>
+      </c>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr"/>
+      <c r="S42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>vilextime:T3:provision:a3e3a25a-ec3d-11f0-ab79-a33691076a8e:2025-07-02</t>
+          <t>vilextime:T3:provision:938c3d26-eb99-11f0-bfb4-15b5584e2964:2024-07-02</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3381,33 +3419,37 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Khi một tổ chức hoặc cá nhân ngừng sử dụng tần số vô tuyến điện trước thời hạn quy định trong giấy phép, họ được hoàn trả phần phí sử dụng tần số vô tuyến điện như thế nào?</t>
+          <t>Pháp luật về chữ ký số của Ngân hàng Nhà nước quy định chứng thư số bị tạm dừng do sai sót, sự cố được khôi phục như thế nào?</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr"/>
+          <t>2024-07-02</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2. Chứng thư số của thuê bao được khôi phục trong các trường hợp sau:</t>
+        </is>
+      </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Điều 7. Hoàn trả phí 1. Tổ chức, cá nhân ngừng sử dụng tần số vô tuyến điện trước thời hạn quy định tại giấy phép sử dụng tần số vô tuyến điện được hoàn trả phần phí sử dụng tần số vô tuyến điện đã nộp cho thời gian còn lại của giấy phép (làm tròn theo tháng) theo quy định của pháp luật trong trường hợp giấy phép được cấp không gắn với cam kết triển khai mạng viễn thông và thời gian còn lại của giấy phép từ 30 ngày trở lên kể từ cơ quan nhà nước có thẩm quyền cấp giấy phép sử dụng tần số vô tuyến điện nhận được văn bản đề nghị của tổ chức, cá nhân. 2. Thời gian còn lại của giấy phép để tính số phí được hoàn trả được tính kể từ ngày tổ chức, cá nhân chính thức ngừng sử dụng nhưng không trước ngày cơ quan nhà nước có thẩm quyền cấp giấy phép sử dụng tần số vô tuyến điện nhận được văn bản đề nghị của tổ chức, cá nhân.</t>
+          <t>d) Chứng thư số bị tạm dừng theo quy định tại điểm c khoản 1 Điều 7 Thông tư này và những sai sót, sự cố đó đã được khắc phục." "3. Tổ chức quản lý thuê bao gửi 01 (một) bộ hồ sơ đề nghị khôi phục chứng thư số theo quy định tại điểm b khoản 2 Điều này gồm Giấy đề nghị khôi phục chứng thư số theo Phụ lục 05 ban hành kèm theo Thông tư này. 4. Thời hạn giải quyết và kết quả thực hiện a) Trong thời hạn 01 ngày làm việc kể từ ngày nhận được văn bản đề nghị theo quy định tại điểm a khoản 2 Điều này hoặc hồ sơ đề nghị khôi phục chứng thư số hợp lệ theo quy định tại điểm b khoản 2 Điều này, Cục Công nghệ thông tin thực hiện khôi phục chứng thư số cho thuê bao. Trường hợp hồ sơ không hợp lệ, Cục Công nghệ thông tin từ chối xử lý hồ sơ và nêu rõ lý do trong thời hạn 01 ngày làm việc kể từ ngày nhận được hồ sơ. Thông tin phản hồi và kết quả xử lý được thực hiện theo quy định tại khoản 3 Điều 4a Thông tư này;</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Điều 7</t>
+          <t>Điểm d Khoản 2 Điều 8</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>265/2016/TT-BTC</t>
+          <t>28/2015/TT-NHNN</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=119140</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=94467</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3417,21 +3459,38 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>dat</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
+          <t>khong_dat</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>group_mismatch</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Như mốc 1. Văn bản đáp án mốc 3 dính cả khoản 3, 4 của lời văn sửa đổi (…đã được khắc phục." "3. Tổ chức quản lý thuê bao…)</t>
+        </is>
+      </c>
       <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>loại lineage (group_mismatch): Điều kiện khôi phục không đổi qua ba mốc (sai sót, sự cố đã được khắc phục); mốc 2 chỉ đổi dẫn chiếu điểm d thành điểm c do Điều 7 đánh số lại</t>
+        </is>
+      </c>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
+      <c r="S43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>vilextime:T3:provision:c7f12dfe-df43-11f0-b0e9-95ce281f9970#k2#a:2016-07-02</t>
+          <t>vilextime:T3:provision:938c3da8-eb99-11f0-b3df-b36a9bf88f4b:2021-01-02</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3441,37 +3500,37 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Điều kiện về xe tập lái đối với cơ sở kinh doanh dịch vụ đào tạo lái xe ô tô được xác định ra sao?</t>
+          <t>Thời hạn tạo cặp khóa và cách xử lý khi thuê bao không kịp tạo khóa được xác định ra sao trong quy định về chữ ký số của Ngân hàng Nhà nước?</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2016-07-02</t>
+          <t>2021-01-02</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2. Xe tập lái</t>
+          <t>Điều 10. Tạo khóa và phân phối khóa</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>a) Có đủ xe tập lái các hạng tương ứng với lưu lượng đào tạo ghi trong giấy phép đào tạo lái xe;</t>
+          <t>2. Thuê bao phải tạo cặp khóa trước ngày hết hạn của mã kích hoạt nêu tại thông báo cấp chứng thư số. Trường hợp bị lộ, nghi bị lộ mã kích hoạt hoặc quá ngày hết hạn kích hoạt tại thông báo cấp chứng thư số, thuê bao chưa tạo được cặp khóa và có nhu cầu tiếp tục sử dụng chứng thư số, tổ chức quản lý thuê bao gửi 01 (một) bộ hồ sơ gồm Giấy đề nghị thay đổi mã kích hoạt chứng thư số theo Phụ lục 08 ban hành kèm theo Thông tư này.</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Điểm a Khoản 2 Điều 6</t>
+          <t>Khoản 2 Điều 10</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>65/2016/NĐ-CP</t>
+          <t>28/2015/TT-NHNN</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=111606</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=94467</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3481,33 +3540,22 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>question_ambiguous</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>Khoản 2 'Xe tập lái' có các điểm a đến k (sở hữu, trọng tải, kiểm định, phanh phụ, mui che, biển TẬP LÁI…); câu hỏi chung 'điều kiện về xe tập lái' khớp cả khoản, đáp án chỉ là điểm a</t>
-        </is>
-      </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>b) Thuộc sở hữu của cơ sở đào tạo lái xe. Có thể sử dụng xe hợp đồng thời hạn từ 01 năm trở lên với số lượng k...</t>
-        </is>
-      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>vilextime:T3:provision:c7f12dfe-df43-11f0-b0e9-95ce281f9970#k2#a:2018-12-02</t>
+          <t>vilextime:T3:provision:96eb9928-2c7e-11f1-82dd-c36c58de53fd:2017-07-02</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3517,37 +3565,37 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Điều kiện về xe tập lái đối với cơ sở kinh doanh dịch vụ đào tạo lái xe ô tô được xác định ra sao?</t>
+          <t>Nếu một tàu biển nước ngoài xin Giấy phép vận tải biển nội địa thông qua đại lý, thì hợp đồng đại lý trong hồ sơ được nộp dưới hình thức bản nào?</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2018-12-02</t>
+          <t>2017-07-02</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2. Xe tập lái</t>
+          <t>Điều 6. Hồ sơ đề nghị cấp Giấy phép vận tải biển nội địa Hồ sơ đề nghị cấp Giấy phép vận tải biển nội địa bao gồm:</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>a) Có xe tập lái các hạng được cơ quan có thẩm quyền cấp giấy phép xe tập lái; trường hợp cơ sở đào tạo có dịch vụ sát hạch lái xe, căn cứ thời gian sử dụng xe sát hạch vào mục đích sát hạch, được phép sử dụng xe sát hạch để vừa thực hiện sát hạch lái xe, vừa đào tạo lái xe nhưng số lượng xe sát hạch dùng để tính lưu lượng đào tạo không quá 50% số xe sát hạch sử dụng để dạy lái;</t>
+          <t>4. 01 (một) bản sao có công chứng Hợp đồng đại lý hoặc 01 (một) bản sao có chứng thực giấy chỉ định đại lý đại diện cho chủ tàu nước ngoài (trong trường hợp tổ chức đề nghị là đại lý đại diện cho chủ tàu nước ngoài) hoặc 01 (một) bản sao có công chứng Hợp đồng thuê tàu giữa chủ tàu nước ngoài với pháp nhân Việt Nam.</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Điểm a Khoản 2 Điều 6</t>
+          <t>Khoản 4 Điều 6</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>65/2016/NĐ-CP</t>
+          <t>50/2016/TT-BGTVT</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=111606</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=118533</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3557,33 +3605,22 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>question_ambiguous</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>Khoản 2 'Xe tập lái' có các điểm a đến k (sở hữu, trọng tải, kiểm định, phanh phụ, mui che, biển TẬP LÁI…); câu hỏi chung 'điều kiện về xe tập lái' khớp cả khoản, đáp án chỉ là điểm a</t>
-        </is>
-      </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>b) Thuộc sở hữu của cơ sở đào tạo lái xe. Có thể sử dụng xe hợp đồng thời hạn từ 01 năm trở lên với số lượng k...</t>
-        </is>
-      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
+      <c r="S45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>vilextime:T3:provision:c7f12dfe-df43-11f0-b0e9-95ce281f9970#k2#a:2022-11-02</t>
+          <t>vilextime:T3:provision:9fdf6804-2d53-11f1-ad2a-cf0eedd8b394:2025-05-20</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3593,37 +3630,37 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Điều kiện về xe tập lái đối với cơ sở kinh doanh dịch vụ đào tạo lái xe ô tô được xác định ra sao?</t>
+          <t>Việc giao nhận tiền mặt theo lệnh điều chuyển giữa kho tiền Trung ương với đơn vị của Ngân hàng Nhà nước theo bó, túi nguyên niêm phong được xác định ra sao về phạm vi áp dụng?</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2022-11-02</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2. Xe tập lái</t>
+          <t>1. Giao nhận tiền mặt theo bó tiền đủ 10 thếp nguyên niêm phong hoặc túi tiền nguyên niêm phong trong các trường hợp:</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>a) Có xe tập lái các hạng thuộc quyền sử dụng hợp pháp của cơ sở đào tạo lái xe; được cơ quan có thẩm quyền cấp giấy phép xe tập lái; trường hợp cơ sở đào tạo có dịch vụ sát hạch lái xe, căn cứ thời gian sử dụng xe sát hạch vào mục đích sát hạch, được phép sử dụng xe sát hạch để vừa thực hiện sát hạch lái xe, vừa đào tạo lái xe nhưng số lượng xe sát hạch dùng để tính lưu lượng đào tạo không quá 50% số xe sát hạch sử dụng để dạy lái;</t>
+          <t>b) Giao nhận tiền mặt loại mệnh giá từ 50.000 đồng trở lên theo lệnh điều chuyển giữa kho tiền Trung ương với Sở Giao dịch, Ngân hàng Nhà nước Khu vực và ngược lại; giữa các kho tiền Trung ương với nhau; giữa các Ngân hàng Nhà nước Khu vực với nhau, trừ trường hợp quy định tại điểm đ khoản 2 Điều này;</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Điểm a Khoản 2 Điều 6</t>
+          <t>Điểm b Khoản 1 Điều 11</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>65/2016/NĐ-CP</t>
+          <t>01/2014/TT-NHNN</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=111606</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=44209</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3633,33 +3670,26 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>question_ambiguous</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr">
         <is>
-          <t>Khoản 2 'Xe tập lái' có các điểm a đến k (sở hữu, trọng tải, kiểm định, phanh phụ, mui che, biển TẬP LÁI…); câu hỏi chung 'điều kiện về xe tập lái' khớp cả khoản, đáp án chỉ là điểm a</t>
-        </is>
-      </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>b) Thuộc sở hữu của cơ sở đào tạo lái xe. Có thể sử dụng xe hợp đồng thời hạn từ 01 năm trở lên với số lượng k...</t>
-        </is>
-      </c>
+          <t>Bốn đáp án khác nhau (thêm ngoại lệ, thêm ngưỡng mệnh giá, đổi chi nhánh thành Khu vực)</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
+      <c r="S46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>vilextime:T3:provision:ceb9e5a6-df50-11f0-857c-4791e49360cb#k2#a:2015-06-02</t>
+          <t>vilextime:T3:provision:a3e3a25a-ec3d-11f0-ab79-a33691076a8e:2025-07-02</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3669,37 +3699,33 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Trong lĩnh vực quỹ tín dụng nhân dân, hộ gia đình muốn trở thành thành viên phải đáp ứng điều kiện gì về nơi cư trú của các thành viên trong hộ?</t>
+          <t>Khi một tổ chức hoặc cá nhân ngừng sử dụng tần số vô tuyến điện trước thời hạn quy định trong giấy phép, họ được hoàn trả phần phí sử dụng tần số vô tuyến điện như thế nào?</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2015-06-02</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>2. Đối với hộ gia đình:</t>
-        </is>
-      </c>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>a) Là hộ gia đình có hộ khẩu thường trú trên địa bàn hoạt động của quỹ tín dụng nhân dân; các thành viên trong hộ có chung tài sản để phục vụ sản xuất, kinh doanh dịch vụ của hộ gia đình;</t>
+          <t>Điều 7. Hoàn trả phí 1. Tổ chức, cá nhân ngừng sử dụng tần số vô tuyến điện trước thời hạn quy định tại giấy phép sử dụng tần số vô tuyến điện được hoàn trả phần phí sử dụng tần số vô tuyến điện đã nộp cho thời gian còn lại của giấy phép (làm tròn theo tháng) theo quy định của pháp luật trong trường hợp giấy phép được cấp không gắn với cam kết triển khai mạng viễn thông và thời gian còn lại của giấy phép từ 30 ngày trở lên kể từ cơ quan nhà nước có thẩm quyền cấp giấy phép sử dụng tần số vô tuyến điện nhận được văn bản đề nghị của tổ chức, cá nhân. 2. Thời gian còn lại của giấy phép để tính số phí được hoàn trả được tính kể từ ngày tổ chức, cá nhân chính thức ngừng sử dụng nhưng không trước ngày cơ quan nhà nước có thẩm quyền cấp giấy phép sử dụng tần số vô tuyến điện nhận được văn bản đề nghị của tổ chức, cá nhân.</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Điểm a Khoản 2 Điều 31</t>
+          <t>Điều 7</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>04/2015/TT-NHNN</t>
+          <t>265/2016/TT-BTC</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=66424</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=119140</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3719,11 +3745,12 @@
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
+      <c r="S47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>vilextime:T3:provision:ceb9e5a6-df50-11f0-857c-4791e49360cb#k2#a:2020-01-02</t>
+          <t>vilextime:T3:provision:a8ca5070-eb7f-11f0-8a66-6b570669d487:2022-08-16</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3733,37 +3760,37 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Trong lĩnh vực quỹ tín dụng nhân dân, hộ gia đình muốn trở thành thành viên phải đáp ứng điều kiện gì về nơi cư trú của các thành viên trong hộ?</t>
+          <t>Theo quy định về đăng kiểm tàu biển, khi đề nghị kiểm định công-te-nơ, máy, vật liệu hoặc trang thiết bị, bộ hồ sơ kỹ thuật kèm theo phải là bản chính hay bản sao và có thể nộp dưới dạng nào?</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2020-01-02</t>
+          <t>2022-08-16</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2. Đối với hộ gia đình:</t>
+          <t>2. Hồ sơ đề nghị kiểm định bao gồm:</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>a) Là hộ gia đình có các thành viên thường trú trên địa bàn hoạt động của quỹ tín dụng nhân dân; các thành viên trong hộ có chung tài sản để phục vụ sản xuất, kinh doanh dịch vụ của hộ gia đình;</t>
+          <t>b) 01 (một) bộ hồ sơ kỹ thuật (bản sao), bao gồm thông số kỹ thuật và các báo cáo kiểm tra, thử công-te-nơ, máy, vật liệu, trang thiết bị.</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Điểm a Khoản 2 Điều 31</t>
+          <t>Điểm b Khoản 2 Điều 16</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>04/2015/TT-NHNN</t>
+          <t>40/2016/TT-BGTVT</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=66424</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=116454</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3783,11 +3810,12 @@
       <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr"/>
+      <c r="S48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>vilextime:T3:provision:db5da940-2d53-11f1-b8ea-772cb5c62cab:2025-05-30</t>
+          <t>vilextime:T3:provision:af4d1140-2cf1-11f1-b242-937670925a25:2019-02-20</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3797,37 +3825,37 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Trường hợp công ty luật thay đổi người đại diện theo pháp luật, công ty phải thông báo cho cơ quan nào, trong thời hạn bao lâu và bằng hình thức nào?</t>
+          <t>Theo thông tư quy định chi tiết về kinh doanh thuốc lá, các mẫu hồ sơ xin giấy phép sản xuất thuốc lá và mẫu giấy phép mới bắt đầu có hiệu lực từ ngày nào?</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2019-02-20</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Điều 11. Thay đổi người đại diện theo pháp luật của tổ chức hành nghề luật sư</t>
+          <t>Điều 22. Hiệu lực thi hành</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>1. Người đại diện theo pháp luật của công ty luật trách nhiệm hữu hạn hai thành viên trở lên, công ty luật hợp danh phải là luật sư và là thành viên của công ty luật. Công ty luật trách nhiệm hữu hạn hai thành viên trở lên và công ty luật hợp danh thay đổi người đại diện theo pháp luật thì trong thời hạn 10 ngày kể từ ngày quyết định thay đổi, phải đề nghị thay đổi người đại diện theo pháp luật và Giấy đăng ký hoạt động của công ty luật qua dịch vụ bưu chính hoặc trực tiếp đến Sở Tư pháp tỉnh, thành phố trực thuộc trung ương nơi đăng ký hoạt động hoặc trực tuyến trên Cổng Dịch vụ công quốc gia.</t>
+          <t>2. Quy định về mẫu đơn, bảng kê đề nghị cấp Giấy phép sản xuất sản phẩm thuốc lá và mẫu Giấy phép sản xuất sản phẩm thuốc lá của Thông tư này có hiệu lực kể từ ngày 01 tháng 01 năm 2020.</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Khoản 1 Điều 11</t>
+          <t>Khoản 2 Điều 22</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>123/2013/NĐ-CP</t>
+          <t>57/2018/TT-BCT</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=32496</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=133903</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3841,21 +3869,26 @@
         </is>
       </c>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>Khoản 1 áp cho công ty luật TNHH hai thành viên trở lên và công ty luật hợp danh; khoản 2 là văn phòng luật sư, công ty luật TNHH một thành viên — audit xem câu hỏi 'công ty luật' có cần nêu loại hình</t>
+          <t>Bốn đáp án khác nhau. Đáp án phiên bản 2 dính nội dung khoản 4 ('2021.4. Quy định … Thông tư số 21/2013/TT-BCT được tiếp tục áp dụng …') do tách khoản lỗi</t>
         </is>
       </c>
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
+      <c r="S49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>vilextime:T3:provision:db5da940-2d53-11f1-b8ea-772cb5c62cab:2026-01-16</t>
+          <t>vilextime:T3:provision:af4d1140-2cf1-11f1-b242-937670925a25:2020-01-02</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3865,37 +3898,37 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Trường hợp công ty luật thay đổi người đại diện theo pháp luật, công ty phải thông báo cho cơ quan nào, trong thời hạn bao lâu và bằng hình thức nào?</t>
+          <t>Theo thông tư quy định chi tiết về kinh doanh thuốc lá, các mẫu hồ sơ xin giấy phép sản xuất thuốc lá và mẫu giấy phép mới bắt đầu có hiệu lực từ ngày nào?</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2020-01-02</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Điều 11. Thay đổi người đại diện theo pháp luật của tổ chức hành nghề luật sư</t>
+          <t>Điều 22. Hiệu lực thi hành</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>1. Người đại diện theo pháp luật của công ty luật trách nhiệm hữu hạn hai thành viên trở lên, công ty luật hợp danh phải là luật sư và là thành viên của công ty luật. Công ty luật trách nhiệm hữu hạn hai thành viên trở lên và công ty luật hợp danh thay đổi người đại diện theo pháp luật thì trong thời hạn 08 ngày làm việc kể từ ngày quyết định thay đổi, phải đề nghị thay đổi người đại diện theo pháp luật và Giấy đăng ký hoạt động của công ty luật qua dịch vụ bưu chính hoặc trực tiếp đến Sở Tư pháp tỉnh, thành phố trực thuộc trung ương nơi đăng ký hoạt động hoặc trực tuyến trên Cổng Dịch vụ công quốc gia.</t>
+          <t>2. Quy định về mẫu đơn, bảng kê đề nghị cấp Giấy phép sản xuất sản phẩm thuốc lá và mẫu Giấy phép sản xuất sản phẩm thuốc lá của Thông tư này có hiệu lực kể từ ngày 01 tháng 01 năm 2021.4. Quy định về mẫu đơn, bảng kê đề nghị cấp Giấy phép sản xuất sản phẩm thuốc lá và mẫu Giấy phép sản xuất sản phẩm thuốc lá của Thông tư số 21/2013/TT-BCT được tiếp tục áp dụng đến hết ngày 31 tháng 12 năm 2020.</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Khoản 1 Điều 11</t>
+          <t>Khoản 2 Điều 22</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>123/2013/NĐ-CP</t>
+          <t>57/2018/TT-BCT</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=32496</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=133903</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3909,21 +3942,26 @@
         </is>
       </c>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>Khoản 1 áp cho công ty luật TNHH hai thành viên trở lên và công ty luật hợp danh; khoản 2 là văn phòng luật sư, công ty luật TNHH một thành viên — audit xem câu hỏi 'công ty luật' có cần nêu loại hình</t>
+          <t>Bốn đáp án khác nhau. Đáp án phiên bản 2 dính nội dung khoản 4 ('2021.4. Quy định … Thông tư số 21/2013/TT-BCT được tiếp tục áp dụng …') do tách khoản lỗi</t>
         </is>
       </c>
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr"/>
+      <c r="S50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>vilextime:T3:provision:de0f8ef2-2c85-11f1-b16a-0dee4373a04b:2022-01-02</t>
+          <t>vilextime:T3:provision:af4d1140-2cf1-11f1-b242-937670925a25:2021-01-02</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3933,37 +3971,37 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Trường hợp kinh doanh hàng hóa xâm phạm quyền sở hữu công nghiệp có giá trị nhỏ, những hành vi cụ thể nào bị phạt cảnh cáo hoặc phạt tiền từ 500.000 đồng đến 2.000.000 đồng?</t>
+          <t>Theo thông tư quy định chi tiết về kinh doanh thuốc lá, các mẫu hồ sơ xin giấy phép sản xuất thuốc lá và mẫu giấy phép mới bắt đầu có hiệu lực từ ngày nào?</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2022-01-02</t>
+          <t>2021-01-02</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1. Phạt cảnh cáo hoặc phạt tiền từ 500.000 đồng đến 2.000.000 đồng đối với một trong các hành vi sau đây vì mục đích kinh doanh trong trường hợp giá trị hàng hóa, dịch vụ vi phạm đến 3.000.000 đồng:</t>
+          <t>Điều 22. Hiệu lực thi hành</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>a) Buôn bán; chào hàng; vận chuyển, kể cả quá cảnh; tàng trữ; trưng bày để bán hàng hóa, dịch vụ xâm phạm quyền đối với nhãn hiệu, tên thương mại, chỉ dẫn địa lý, kiểu dáng công nghiệp;</t>
+          <t>2. Quy định về mẫu đơn, bảng kê đề nghị cấp Giấy phép sản xuất sản phẩm thuốc lá và mẫu Giấy phép sản xuất sản phẩm thuốc lá của Thông tư này có hiệu lực kể từ ngày 01 tháng 01 năm 2023.</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Điểm a Khoản 1 Điều 11</t>
+          <t>Khoản 2 Điều 22</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>99/2013/NĐ-CP</t>
+          <t>57/2018/TT-BCT</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=31905</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=133903</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3977,21 +4015,26 @@
         </is>
       </c>
       <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>Mốc 1→2 chỉ đổi 'Bán' thành 'Buôn bán' — khác biệt nhỏ nhưng có nghĩa pháp lý; audit xem có coi là đổi đáp án không</t>
+          <t>Bốn đáp án khác nhau. Đáp án phiên bản 2 dính nội dung khoản 4 ('2021.4. Quy định … Thông tư số 21/2013/TT-BCT được tiếp tục áp dụng …') do tách khoản lỗi</t>
         </is>
       </c>
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
+      <c r="S51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>vilextime:T3:provision:e6c5d5d4-df40-11f0-a50d-ddac3e38e697:2013-01-02</t>
+          <t>vilextime:T3:provision:af4d1140-2cf1-11f1-b242-937670925a25:2022-12-11</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4001,37 +4044,37 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Nếu một tổ chức mở lớp cập nhật kiến thức cho kiểm toán viên để tính giờ cập nhật, thì hành vi nào của tổ chức đó bị coi là vi phạm về cập nhật kiến thức?</t>
+          <t>Theo thông tư quy định chi tiết về kinh doanh thuốc lá, các mẫu hồ sơ xin giấy phép sản xuất thuốc lá và mẫu giấy phép mới bắt đầu có hiệu lực từ ngày nào?</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2013-01-02</t>
+          <t>2022-12-11</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Điều 18. Các hành vi vi phạm về cập nhật kiến thức</t>
+          <t>Điều 22. Hiệu lực thi hành</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>1. Tổ chức cập nhật kiến thức cho kiểm toán viên hành nghề để tính giờ cập nhật kiến thức theo quy định tại Điều 11 Thông tư này khi chưa đăng ký với Bộ Tài chính hoặc đã đăng ký nhưng chưa được Bộ Tài chính chấp thuận.</t>
+          <t>2. Quy định về mẫu đơn, bảng kê đề nghị cấp Giấy phép sản xuất sản phẩm thuốc lá và mẫu Giấy phép sản xuất sản phẩm thuốc lá của Thông tư này có hiệu lực kể từ ngày 01 tháng 01 năm 2028.</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Khoản 1 Điều 18</t>
+          <t>Khoản 2 Điều 22</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>150/2012/TT-BTC</t>
+          <t>57/2018/TT-BCT</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=27855</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=133903</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -4041,33 +4084,30 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>question_ambiguous</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr"/>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>Câu hỏi 'hành vi nào của tổ chức đó bị coi là vi phạm' khớp cả khoản 2 (cập nhật nội dung không phù hợp nội dung đã đăng ký), khoản 3 (báo cáo không trung thực), khoản 5 cùng Điều; khoản 1 chỉ là một hành vi</t>
-        </is>
-      </c>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t>2. Tổ chức cập nhật kiến thức cho kiểm toán viên hành nghề những nội dung không phù hợp với nội dung đã đăng k...</t>
-        </is>
-      </c>
+          <t>Bốn đáp án khác nhau. Đáp án phiên bản 2 dính nội dung khoản 4 ('2021.4. Quy định … Thông tư số 21/2013/TT-BCT được tiếp tục áp dụng …') do tách khoản lỗi</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr"/>
       <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr"/>
+      <c r="S52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>vilextime:T3:provision:e6c5d5d4-df40-11f0-a50d-ddac3e38e697:2024-05-02</t>
+          <t>vilextime:T3:provision:c7f12dfe-df43-11f0-b0e9-95ce281f9970#k2#a:2016-07-02</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4077,37 +4117,37 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Nếu một tổ chức mở lớp cập nhật kiến thức cho kiểm toán viên để tính giờ cập nhật, thì hành vi nào của tổ chức đó bị coi là vi phạm về cập nhật kiến thức?</t>
+          <t>Điều kiện về xe tập lái đối với cơ sở kinh doanh dịch vụ đào tạo lái xe ô tô được xác định ra sao?</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2016-07-02</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Điều 18. Các hành vi vi phạm về cập nhật kiến thức</t>
+          <t>2. Xe tập lái</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>1. Tổ chức cập nhật kiến thức cho kiểm toán viên hành nghề để tính giờ cập nhật kiến thức theo quy định tại Điều 11 Thông tư này khi chưa đăng ký với Cục Quản lý giám sát kế toán, kiểm toán - Bộ Tài chính hoặc đã đăng ký nhưng chưa được Cục Quản lý giám sát kế toán, kiểm toán - Bộ Tài chính chấp thuận.</t>
+          <t>a) Có đủ xe tập lái các hạng tương ứng với lưu lượng đào tạo ghi trong giấy phép đào tạo lái xe;</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Khoản 1 Điều 18</t>
+          <t>Điểm a Khoản 2 Điều 6</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>150/2012/TT-BTC</t>
+          <t>65/2016/NĐ-CP</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=27855</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=111606</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -4128,22 +4168,27 @@
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr">
         <is>
-          <t>Câu hỏi 'hành vi nào của tổ chức đó bị coi là vi phạm' khớp cả khoản 2 (cập nhật nội dung không phù hợp nội dung đã đăng ký), khoản 3 (báo cáo không trung thực), khoản 5 cùng Điều; khoản 1 chỉ là một hành vi</t>
+          <t>Khoản 2 'Xe tập lái' có các điểm a đến k (sở hữu, trọng tải, kiểm định, phanh phụ, mui che, biển TẬP LÁI…); câu hỏi chung 'điều kiện về xe tập lái' khớp cả khoản, đáp án chỉ là điểm a</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>2. Tổ chức cập nhật kiến thức cho kiểm toán viên hành nghề những nội dung không phù hợp với nội dung đã đăng k...</t>
-        </is>
-      </c>
-      <c r="P53" t="inlineStr"/>
+          <t>b) Thuộc sở hữu của cơ sở đào tạo lái xe. Có thể sử dụng xe hợp đồng thời hạn từ 01 năm trở lên với số lượng k...</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>loại lineage (question_ambiguous): Khoản 2 'Xe tập lái' có các điểm a đến k (sở hữu, trọng tải, kiểm định, phanh phụ, mui che, biển TẬP LÁI…); câu hỏi chung 'điều kiện về xe tập lái' khớp cả khoản, đáp án chỉ là điểm a</t>
+        </is>
+      </c>
       <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr"/>
+      <c r="S53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>vilextime:T3:provision:e6c5d5d4-df40-11f0-a50d-ddac3e38e697:2025-07-02</t>
+          <t>vilextime:T3:provision:c7f12dfe-df43-11f0-b0e9-95ce281f9970#k2#a:2018-12-02</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4153,37 +4198,37 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Nếu một tổ chức mở lớp cập nhật kiến thức cho kiểm toán viên để tính giờ cập nhật, thì hành vi nào của tổ chức đó bị coi là vi phạm về cập nhật kiến thức?</t>
+          <t>Điều kiện về xe tập lái đối với cơ sở kinh doanh dịch vụ đào tạo lái xe ô tô được xác định ra sao?</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2018-12-02</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Điều 18. Các hành vi vi phạm về cập nhật kiến thức</t>
+          <t>2. Xe tập lái</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>1. Tổ chức cập nhật kiến thức cho kiểm toán viên hành nghề để tính giờ cập nhật kiến thức theo quy định tại Điều 11 Thông tư này khi không đảm bảo điều kiện quy định tại Điều 7 Thông tư này hoặc đã đủ điều kiện nhưng chưa thông báo cho Cục Quản lý, giám sát kế toán, kiểm toán - Bộ Tài chính</t>
+          <t>a) Có xe tập lái các hạng được cơ quan có thẩm quyền cấp giấy phép xe tập lái; trường hợp cơ sở đào tạo có dịch vụ sát hạch lái xe, căn cứ thời gian sử dụng xe sát hạch vào mục đích sát hạch, được phép sử dụng xe sát hạch để vừa thực hiện sát hạch lái xe, vừa đào tạo lái xe nhưng số lượng xe sát hạch dùng để tính lưu lượng đào tạo không quá 50% số xe sát hạch sử dụng để dạy lái;</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Khoản 1 Điều 18</t>
+          <t>Điểm a Khoản 2 Điều 6</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>150/2012/TT-BTC</t>
+          <t>65/2016/NĐ-CP</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=27855</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=111606</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -4204,22 +4249,27 @@
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
-          <t>Câu hỏi 'hành vi nào của tổ chức đó bị coi là vi phạm' khớp cả khoản 2 (cập nhật nội dung không phù hợp nội dung đã đăng ký), khoản 3 (báo cáo không trung thực), khoản 5 cùng Điều; khoản 1 chỉ là một hành vi</t>
+          <t>Khoản 2 'Xe tập lái' có các điểm a đến k (sở hữu, trọng tải, kiểm định, phanh phụ, mui che, biển TẬP LÁI…); câu hỏi chung 'điều kiện về xe tập lái' khớp cả khoản, đáp án chỉ là điểm a</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>2. Tổ chức cập nhật kiến thức cho kiểm toán viên hành nghề những nội dung không phù hợp với nội dung đã đăng k...</t>
-        </is>
-      </c>
-      <c r="P54" t="inlineStr"/>
+          <t>b) Thuộc sở hữu của cơ sở đào tạo lái xe. Có thể sử dụng xe hợp đồng thời hạn từ 01 năm trở lên với số lượng k...</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>loại lineage (question_ambiguous): Khoản 2 'Xe tập lái' có các điểm a đến k (sở hữu, trọng tải, kiểm định, phanh phụ, mui che, biển TẬP LÁI…); câu hỏi chung 'điều kiện về xe tập lái' khớp cả khoản, đáp án chỉ là điểm a</t>
+        </is>
+      </c>
       <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr"/>
+      <c r="S54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>vilextime:T3:provision:eaad2c74-df45-11f0-8793-1d800b3bbbe4:2017-07-02</t>
+          <t>vilextime:T3:provision:c7f12dfe-df43-11f0-b0e9-95ce281f9970#k2#a:2022-11-02</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4229,37 +4279,37 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Khi đăng ký tàu vào Sổ đăng ký tàu biển quốc gia Việt Nam, sổ này dùng để ghi thông tin của những loại tàu, phương tiện nào và được lập dưới hình thức nào?</t>
+          <t>Điều kiện về xe tập lái đối với cơ sở kinh doanh dịch vụ đào tạo lái xe ô tô được xác định ra sao?</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2017-07-02</t>
+          <t>2022-11-02</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Điều 6. Sổ đăng ký tàu biển quốc gia Việt Nam</t>
+          <t>2. Xe tập lái</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>1. Sổ đăng ký tàu biển quốc gia Việt Nam được sử dụng để ghi lại các thông tin liên quan đến tàu biển đã được đăng ký hoặc xóa đăng ký theo quy định. Nội dung chủ yếu của Sổ đăng ký tàu biển quốc gia Việt Nam được thực hiện theo quy định tại Điều 24 của Bộ Luật hàng hải Việt Nam năm 2015.</t>
+          <t>a) Có xe tập lái các hạng thuộc quyền sử dụng hợp pháp của cơ sở đào tạo lái xe; được cơ quan có thẩm quyền cấp giấy phép xe tập lái; trường hợp cơ sở đào tạo có dịch vụ sát hạch lái xe, căn cứ thời gian sử dụng xe sát hạch vào mục đích sát hạch, được phép sử dụng xe sát hạch để vừa thực hiện sát hạch lái xe, vừa đào tạo lái xe nhưng số lượng xe sát hạch dùng để tính lưu lượng đào tạo không quá 50% số xe sát hạch sử dụng để dạy lái;</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Khoản 1 Điều 6</t>
+          <t>Điểm a Khoản 2 Điều 6</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>171/2016/NĐ-CP</t>
+          <t>65/2016/NĐ-CP</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=118563</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=111606</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -4274,24 +4324,33 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>group_mismatch</t>
+          <t>question_ambiguous</t>
         </is>
       </c>
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr">
         <is>
-          <t>Mốc 2 và 3 trả lời như nhau cho câu hỏi (cùng các loại tàu, cùng hình thức sổ giấy và cơ sở dữ liệu); chỉ hai đáp án. Văn bản mốc 3 kết thúc ở 'cơ sở dữ liệu' (có thể thiếu 'điện tử')</t>
-        </is>
-      </c>
-      <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr"/>
+          <t>Khoản 2 'Xe tập lái' có các điểm a đến k (sở hữu, trọng tải, kiểm định, phanh phụ, mui che, biển TẬP LÁI…); câu hỏi chung 'điều kiện về xe tập lái' khớp cả khoản, đáp án chỉ là điểm a</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>b) Thuộc sở hữu của cơ sở đào tạo lái xe. Có thể sử dụng xe hợp đồng thời hạn từ 01 năm trở lên với số lượng k...</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>loại lineage (question_ambiguous): Khoản 2 'Xe tập lái' có các điểm a đến k (sở hữu, trọng tải, kiểm định, phanh phụ, mui che, biển TẬP LÁI…); câu hỏi chung 'điều kiện về xe tập lái' khớp cả khoản, đáp án chỉ là điểm a</t>
+        </is>
+      </c>
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
+      <c r="S55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>vilextime:T3:provision:eaad2c74-df45-11f0-8793-1d800b3bbbe4:2020-09-16</t>
+          <t>vilextime:T3:provision:ceb9e5a6-df50-11f0-857c-4791e49360cb#k2#a:2015-06-02</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4301,37 +4360,37 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Khi đăng ký tàu vào Sổ đăng ký tàu biển quốc gia Việt Nam, sổ này dùng để ghi thông tin của những loại tàu, phương tiện nào và được lập dưới hình thức nào?</t>
+          <t>Trong lĩnh vực quỹ tín dụng nhân dân, hộ gia đình muốn trở thành thành viên phải đáp ứng điều kiện gì về nơi cư trú của các thành viên trong hộ?</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2020-09-16</t>
+          <t>2015-06-02</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Điều 6. Sổ đăng ký tàu biển quốc gia Việt Nam</t>
+          <t>2. Đối với hộ gia đình:</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>1. Sổ đăng ký tàu biển quốc gia Việt Nam được sử dụng để ghi lại các thông tin liên quan đến tàu biển, tàu biển công vụ, tàu ngầm, tàu lặn, kho chứa nổi, giàn di động đã được đăng ký hoặc xóa đăng ký theo quy định, sổ đăng ký tàu biển quốc gia Việt Nam được lập dưới dạng sổ ghi chép trên giấy và cơ sở dữ liệu điện tử. Nội dung chủ yếu của sổ đăng ký tàu biển quốc gia Việt Nam được thực hiện theo quy định tại Điều 24 của Bộ luật Hàng hải Việt Nam.</t>
+          <t>a) Là hộ gia đình có hộ khẩu thường trú trên địa bàn hoạt động của quỹ tín dụng nhân dân; các thành viên trong hộ có chung tài sản để phục vụ sản xuất, kinh doanh dịch vụ của hộ gia đình;</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Khoản 1 Điều 6</t>
+          <t>Điểm a Khoản 2 Điều 31</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>171/2016/NĐ-CP</t>
+          <t>04/2015/TT-NHNN</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=118563</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=66424</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -4341,29 +4400,22 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>group_mismatch</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>Mốc 2 và 3 trả lời như nhau cho câu hỏi (cùng các loại tàu, cùng hình thức sổ giấy và cơ sở dữ liệu); chỉ hai đáp án. Văn bản mốc 3 kết thúc ở 'cơ sở dữ liệu' (có thể thiếu 'điện tử')</t>
-        </is>
-      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr"/>
       <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr"/>
+      <c r="S56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>vilextime:T3:provision:eaad2c74-df45-11f0-8793-1d800b3bbbe4:2025-10-31</t>
+          <t>vilextime:T3:provision:ceb9e5a6-df50-11f0-857c-4791e49360cb#k2#a:2020-01-02</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4373,37 +4425,37 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Khi đăng ký tàu vào Sổ đăng ký tàu biển quốc gia Việt Nam, sổ này dùng để ghi thông tin của những loại tàu, phương tiện nào và được lập dưới hình thức nào?</t>
+          <t>Trong lĩnh vực quỹ tín dụng nhân dân, hộ gia đình muốn trở thành thành viên phải đáp ứng điều kiện gì về nơi cư trú của các thành viên trong hộ?</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2020-01-02</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Điều 6. Sổ đăng ký tàu biển quốc gia Việt Nam</t>
+          <t>2. Đối với hộ gia đình:</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>1. Sổ đăng ký tàu biển quốc gia Việt Nam được sử dụng để ghi lại các thông tin liên quan đến tàu biển, tàu biển công vụ, tàu ngầm, tàu lặn, kho chứa nổi, giàn di động đã được đăng ký hoặc xóa đăng ký theo quy định. Sổ đăng ký tàu biển quốc gia Việt Nam được lập dưới dạng sổ ghi chép trên giấy và cơ sở dữ liệu</t>
+          <t>a) Là hộ gia đình có các thành viên thường trú trên địa bàn hoạt động của quỹ tín dụng nhân dân; các thành viên trong hộ có chung tài sản để phục vụ sản xuất, kinh doanh dịch vụ của hộ gia đình;</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Khoản 1 Điều 6</t>
+          <t>Điểm a Khoản 2 Điều 31</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>171/2016/NĐ-CP</t>
+          <t>04/2015/TT-NHNN</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=118563</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=66424</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -4413,29 +4465,22 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>group_mismatch</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>Mốc 2 và 3 trả lời như nhau cho câu hỏi (cùng các loại tàu, cùng hình thức sổ giấy và cơ sở dữ liệu); chỉ hai đáp án. Văn bản mốc 3 kết thúc ở 'cơ sở dữ liệu' (có thể thiếu 'điện tử')</t>
-        </is>
-      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr"/>
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr"/>
+      <c r="S57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>vilextime:T3:provision:ec4a7a6e-df40-11f0-9161-ff81534d3941:2014-10-21</t>
+          <t>vilextime:T3:provision:db5da940-2d53-11f1-b8ea-772cb5c62cab:2025-05-30</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4445,37 +4490,37 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Theo quy định về quá cảnh hàng hóa của Campuchia qua lãnh thổ Việt Nam, hàng hóa khác khi quá cảnh phải xin giấy phép của cơ quan nào?</t>
+          <t>Trường hợp công ty luật thay đổi người đại diện theo pháp luật, công ty phải thông báo cho cơ quan nào, trong thời hạn bao lâu và bằng hình thức nào?</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2014-10-21</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>THỦ TỤC CẤP, GIA HẠN GIẤY PHÉP QUÁ CẢNH HÀNG HÓA</t>
+          <t>Điều 11. Thay đổi người đại diện theo pháp luật của tổ chức hành nghề luật sư</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Các loại hàng hóa khác không thuộc trường hợp quy định tại Điều 4 và Khoản 1, Khoản 2 Điều 5 Hiệp định, khi quá cảnh theo đường bộ, đường thủy hoặc đường sắt qua các cặp cửa khẩu quy định tại Điều 7 Hiệp định, chủ hàng hoặc người chuyên chở được ủy quyền hợp pháp làm thủ tục quá cảnh tại cơ quan Hải quan, không phải xin giấy phép quá cảnh hàng hóa của Bộ Công Thương hoặc Phòng Quản lý Xuất nhập khẩu khu vực thành phố Hồ Chí Minh (Cục Xuất nhập khẩu - Bộ Công Thương).</t>
+          <t>1. Người đại diện theo pháp luật của công ty luật trách nhiệm hữu hạn hai thành viên trở lên, công ty luật hợp danh phải là luật sư và là thành viên của công ty luật. Công ty luật trách nhiệm hữu hạn hai thành viên trở lên và công ty luật hợp danh thay đổi người đại diện theo pháp luật thì trong thời hạn 10 ngày kể từ ngày quyết định thay đổi, phải đề nghị thay đổi người đại diện theo pháp luật và Giấy đăng ký hoạt động của công ty luật qua dịch vụ bưu chính hoặc trực tiếp đến Sở Tư pháp tỉnh, thành phố trực thuộc trung ương nơi đăng ký hoạt động hoặc trực tuyến trên Cổng Dịch vụ công quốc gia.</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Điều 5</t>
+          <t>Khoản 1 Điều 11</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>27/2014/TT-BCT</t>
+          <t>123/2013/NĐ-CP</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=46098</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=32496</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -4485,29 +4530,26 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>group_mismatch</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr">
         <is>
-          <t>Ở cả ba mốc câu trả lời như nhau: hàng hóa khác không phải xin giấy phép, chỉ làm thủ tục tại Hải quan; chỗ đổi chỉ là tên cơ quan cấp phép không cần xin. Câu hỏi còn giả định sai là phải xin giấy phép</t>
+          <t>Khoản 1 áp cho công ty luật TNHH hai thành viên trở lên và công ty luật hợp danh; khoản 2 là văn phòng luật sư, công ty luật TNHH một thành viên — audit xem câu hỏi 'công ty luật' có cần nêu loại hình</t>
         </is>
       </c>
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr"/>
       <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr"/>
+      <c r="S58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>vilextime:T3:provision:ec4a7a6e-df40-11f0-9161-ff81534d3941:2025-07-02</t>
+          <t>vilextime:T3:provision:db5da940-2d53-11f1-b8ea-772cb5c62cab:2026-01-16</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4517,37 +4559,37 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Theo quy định về quá cảnh hàng hóa của Campuchia qua lãnh thổ Việt Nam, hàng hóa khác khi quá cảnh phải xin giấy phép của cơ quan nào?</t>
+          <t>Trường hợp công ty luật thay đổi người đại diện theo pháp luật, công ty phải thông báo cho cơ quan nào, trong thời hạn bao lâu và bằng hình thức nào?</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>THỦ TỤC CẤP, GIA HẠN GIẤY PHÉP QUÁ CẢNH HÀNG HÓA</t>
+          <t>Điều 11. Thay đổi người đại diện theo pháp luật của tổ chức hành nghề luật sư</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Các loại hàng hóa khác không thuộc trường hợp quy định tại Điều 4 và Khoản 1, Khoản 2 Điều 5 Hiệp định, khi quá cảnh theo đường bộ, đường thủy hoặc đường sắt qua các cặp cửa khẩu quy định tại Điều 7 Hiệp định, chủ hàng hoặc người chuyên chở được ủy quyền hợp pháp làm thủ tục quá cảnh tại cơ quan Hải quan, không phải xin giấy phép quá cảnh hàng hóa của Bộ Công Thương hoặc Cục Xuất nhập khẩu - Bộ Công Thương.</t>
+          <t>1. Người đại diện theo pháp luật của công ty luật trách nhiệm hữu hạn hai thành viên trở lên, công ty luật hợp danh phải là luật sư và là thành viên của công ty luật. Công ty luật trách nhiệm hữu hạn hai thành viên trở lên và công ty luật hợp danh thay đổi người đại diện theo pháp luật thì trong thời hạn 08 ngày làm việc kể từ ngày quyết định thay đổi, phải đề nghị thay đổi người đại diện theo pháp luật và Giấy đăng ký hoạt động của công ty luật qua dịch vụ bưu chính hoặc trực tiếp đến Sở Tư pháp tỉnh, thành phố trực thuộc trung ương nơi đăng ký hoạt động hoặc trực tuyến trên Cổng Dịch vụ công quốc gia.</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Điều 5</t>
+          <t>Khoản 1 Điều 11</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>27/2014/TT-BCT</t>
+          <t>123/2013/NĐ-CP</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=46098</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=32496</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -4557,29 +4599,26 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>group_mismatch</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr">
         <is>
-          <t>Ở cả ba mốc câu trả lời như nhau: hàng hóa khác không phải xin giấy phép, chỉ làm thủ tục tại Hải quan; chỗ đổi chỉ là tên cơ quan cấp phép không cần xin. Câu hỏi còn giả định sai là phải xin giấy phép</t>
+          <t>Khoản 1 áp cho công ty luật TNHH hai thành viên trở lên và công ty luật hợp danh; khoản 2 là văn phòng luật sư, công ty luật TNHH một thành viên — audit xem câu hỏi 'công ty luật' có cần nêu loại hình</t>
         </is>
       </c>
       <c r="O59" t="inlineStr"/>
       <c r="P59" t="inlineStr"/>
       <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr"/>
+      <c r="S59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>vilextime:T3:provision:ec4a7a6e-df40-11f0-9161-ff81534d3941:2026-05-30</t>
+          <t>vilextime:T3:provision:de0f8ef2-2c85-11f1-b16a-0dee4373a04b:2022-01-02</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4589,37 +4628,37 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Theo quy định về quá cảnh hàng hóa của Campuchia qua lãnh thổ Việt Nam, hàng hóa khác khi quá cảnh phải xin giấy phép của cơ quan nào?</t>
+          <t>Trường hợp kinh doanh hàng hóa xâm phạm quyền sở hữu công nghiệp có giá trị nhỏ, những hành vi cụ thể nào bị phạt cảnh cáo hoặc phạt tiền từ 500.000 đồng đến 2.000.000 đồng?</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2022-01-02</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>THỦ TỤC CẤP, GIA HẠN GIẤY PHÉP QUÁ CẢNH HÀNG HÓA</t>
+          <t>1. Phạt cảnh cáo hoặc phạt tiền từ 500.000 đồng đến 2.000.000 đồng đối với một trong các hành vi sau đây vì mục đích kinh doanh trong trường hợp giá trị hàng hóa, dịch vụ vi phạm đến 3.000.000 đồng:</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Điều 5. Quá cảnh hàng hóa khác Các loại hàng hóa khác không thuộc trường hợp quy định tại Điều 4 và khoản 1, khoản 2 Điều 5 Hiệp định, khi quá cảnh theo đường bộ, đường thủy hoặc đường sắt qua các cặp cửa khẩu quy định tại Điều 7 Hiệp định, chủ hàng hoặc người chuyên chở được ủy quyền hợp pháp làm thủ tục quá cảnh tại cơ quan Hải quan, không phải xin giấy phép quá cảnh hàng hóa</t>
+          <t>a) Buôn bán; chào hàng; vận chuyển, kể cả quá cảnh; tàng trữ; trưng bày để bán hàng hóa, dịch vụ xâm phạm quyền đối với nhãn hiệu, tên thương mại, chỉ dẫn địa lý, kiểu dáng công nghiệp;</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Điều 5</t>
+          <t>Điểm a Khoản 1 Điều 11</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>27/2014/TT-BCT</t>
+          <t>99/2013/NĐ-CP</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=46098</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=31905</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -4629,29 +4668,26 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>group_mismatch</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr">
         <is>
-          <t>Ở cả ba mốc câu trả lời như nhau: hàng hóa khác không phải xin giấy phép, chỉ làm thủ tục tại Hải quan; chỗ đổi chỉ là tên cơ quan cấp phép không cần xin. Câu hỏi còn giả định sai là phải xin giấy phép</t>
+          <t>Mốc 1→2 chỉ đổi 'Bán' thành 'Buôn bán' — khác biệt nhỏ nhưng có nghĩa pháp lý; audit xem có coi là đổi đáp án không</t>
         </is>
       </c>
       <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr"/>
       <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr"/>
+      <c r="S60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>vilextime:T3:provision:f2947168-df4f-11f0-b8a1-cba0d0f18fba:2019-02-16</t>
+          <t>vilextime:T3:provision:e6c5d5d4-df40-11f0-a50d-ddac3e38e697:2013-01-02</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4661,37 +4697,37 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Việc mua cổ phần dẫn đến trở thành cổ đông lớn của ngân hàng thương mại cần Ngân hàng Nhà nước chấp thuận trong những trường hợp nào?</t>
+          <t>Nếu một tổ chức mở lớp cập nhật kiến thức cho kiểm toán viên để tính giờ cập nhật khi chưa hoàn tất thủ tục đăng ký, đáp ứng điều kiện hoặc thông báo với cơ quan quản lý, thì những trường hợp nào bị coi là vi phạm?</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2019-02-16</t>
+          <t>2013-01-02</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Điều 17. Mua, bán, chuyển nhượng cổ phần của cổ đông lớn; mua, bán, chuyển nhượng cổ phần dẫn đến trở thành cổ đông lớn</t>
+          <t>Điều 18. Các hành vi vi phạm về cập nhật kiến thức</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>3. Việc mua cổ phần của tổ chức, cá nhân dẫn đến tổ chức, cá nhân đó trở thành cổ đông lớn trong trường hợp ngân hàng thương mại cổ phần tăng mức vốn điều lệ, hồ sơ, trình tự, thủ tục thực hiện theo quy định tại Điều 12 Thông tư này.</t>
+          <t>1. Tổ chức cập nhật kiến thức cho kiểm toán viên hành nghề để tính giờ cập nhật kiến thức theo quy định tại Điều 11 Thông tư này khi chưa đăng ký với Bộ Tài chính hoặc đã đăng ký nhưng chưa được Bộ Tài chính chấp thuận.</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Khoản 3 Điều 17</t>
+          <t>Khoản 1 Điều 18</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>50/2018/TT-NHNN</t>
+          <t>150/2012/TT-BTC</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=133844</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=27855</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -4701,33 +4737,26 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>question_ambiguous</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr">
         <is>
-          <t>Khoản 3 chỉ nói trường hợp mua cổ phần khi ngân hàng tăng vốn điều lệ; câu hỏi không nêu trường hợp đó, và khoản 2 cùng Điều là hồ sơ chấp thuận mua, nhận chuyển nhượng cổ phần dẫn đến trở thành cổ đông lớn nói chung</t>
-        </is>
-      </c>
-      <c r="O61" t="inlineStr">
-        <is>
-          <t>2. Hồ sơ đề nghị chấp thuận mua, nhận chuyển nhượng cổ phần dẫn đến trở thành cổ đông lớn: Văn bản đề nghị của...</t>
-        </is>
-      </c>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Nếu một tổ chức mở lớp cập nhật kiến thức cho kiểm toán viên để tính giờ cập nhật, thì hành vi nào của tổ chức đó bị coi là vi phạm về cập nhật kiến thức?»; nhãn cũ khong_dat question_ambiguous: Câu hỏi 'hành vi nào của tổ chức đó bị coi là vi phạm' khớp cả khoản 2 (cập nhật nội dung không phù hợp nội dung đã đăng ký), khoản 3 (báo cáo không trung thực), khoản 5 cùng Điều; khoản 1 chỉ là một hành vi). Câu hỏi chốt tổ chức lớp khi chưa hoàn tất đăng ký/điều kiện/thông báo, chỉ khớp khoản 1; ba đáp án khác nhau</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr"/>
+      <c r="S61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>vilextime:T3:provision:f2947168-df4f-11f0-b8a1-cba0d0f18fba:2022-08-16</t>
+          <t>vilextime:T3:provision:e6c5d5d4-df40-11f0-a50d-ddac3e38e697:2024-05-02</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4737,37 +4766,37 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Việc mua cổ phần dẫn đến trở thành cổ đông lớn của ngân hàng thương mại cần Ngân hàng Nhà nước chấp thuận trong những trường hợp nào?</t>
+          <t>Nếu một tổ chức mở lớp cập nhật kiến thức cho kiểm toán viên để tính giờ cập nhật khi chưa hoàn tất thủ tục đăng ký, đáp ứng điều kiện hoặc thông báo với cơ quan quản lý, thì những trường hợp nào bị coi là vi phạm?</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2022-08-16</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Điều 17. Mua, bán, chuyển nhượng cổ phần của cổ đông lớn; mua, bán, chuyển nhượng cổ phần dẫn đến trở thành cổ đông lớn</t>
+          <t>Điều 18. Các hành vi vi phạm về cập nhật kiến thức</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>3. Việc mua cổ phần của tổ chức, cá nhân dẫn đến tổ chức, cá nhân đó trở thành cổ đông lớn hoặc mua cổ phần của cổ đông lớn trong trường hợp ngân hàng thương mại cổ phần tăng mức vốn điều lệ, hồ sơ, trình tự, thủ tục thực hiện theo quy định tại Điều 12 Thông tư này.Việc mua cổ phần của tổ chức, cá nhân dẫn đến tổ chức, cá nhân đó trở thành cổ đông lớn hoặc mua cổ phần của cổ đông lớn trong trường hợp ngân hàng thương mại cổ phần tăng mức vốn điều lệ mà tổ chức, cá nhân hoặc cổ đông lớn đó không thuộc danh sách cổ đông mua cổ phần của ngân hàng thương mại cổ phần tại điểm d khoản 1 Điều 12 Thông tư này đã được Ngân hàng Nhà nước chấp thuận thì thực hiện theo quy định tại khoản 1, khoản 2 Điều này và khoản 2 Điều 15 Thông tư này. Văn bản chấp thuận của Ngân hàng Nhà nước về việc mua cổ phần này là bộ phận không tách rời của văn bản chấp thuận tăng mức vốn điều lệ.</t>
+          <t>1. Tổ chức cập nhật kiến thức cho kiểm toán viên hành nghề để tính giờ cập nhật kiến thức theo quy định tại Điều 11 Thông tư này khi chưa đăng ký với Cục Quản lý giám sát kế toán, kiểm toán - Bộ Tài chính hoặc đã đăng ký nhưng chưa được Cục Quản lý giám sát kế toán, kiểm toán - Bộ Tài chính chấp thuận.</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Khoản 3 Điều 17</t>
+          <t>Khoản 1 Điều 18</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>50/2018/TT-NHNN</t>
+          <t>150/2012/TT-BTC</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=133844</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=27855</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -4777,33 +4806,26 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>question_ambiguous</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr">
         <is>
-          <t>Khoản 3 chỉ nói trường hợp mua cổ phần khi ngân hàng tăng vốn điều lệ; câu hỏi không nêu trường hợp đó, và khoản 2 cùng Điều là hồ sơ chấp thuận mua, nhận chuyển nhượng cổ phần dẫn đến trở thành cổ đông lớn nói chung</t>
-        </is>
-      </c>
-      <c r="O62" t="inlineStr">
-        <is>
-          <t>2. Hồ sơ đề nghị chấp thuận mua, nhận chuyển nhượng cổ phần dẫn đến trở thành cổ đông lớn: Văn bản đề nghị của...</t>
-        </is>
-      </c>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Nếu một tổ chức mở lớp cập nhật kiến thức cho kiểm toán viên để tính giờ cập nhật, thì hành vi nào của tổ chức đó bị coi là vi phạm về cập nhật kiến thức?»; nhãn cũ khong_dat question_ambiguous: Câu hỏi 'hành vi nào của tổ chức đó bị coi là vi phạm' khớp cả khoản 2 (cập nhật nội dung không phù hợp nội dung đã đăng ký), khoản 3 (báo cáo không trung thực), khoản 5 cùng Điều; khoản 1 chỉ là một hành vi). Câu hỏi chốt tổ chức lớp khi chưa hoàn tất đăng ký/điều kiện/thông báo, chỉ khớp khoản 1; ba đáp án khác nhau</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr"/>
+      <c r="S62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>vilextime:T3:provision:f2947168-df4f-11f0-b8a1-cba0d0f18fba:2024-07-02</t>
+          <t>vilextime:T3:provision:e6c5d5d4-df40-11f0-a50d-ddac3e38e697:2025-07-02</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4813,37 +4835,37 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Việc mua cổ phần dẫn đến trở thành cổ đông lớn của ngân hàng thương mại cần Ngân hàng Nhà nước chấp thuận trong những trường hợp nào?</t>
+          <t>Nếu một tổ chức mở lớp cập nhật kiến thức cho kiểm toán viên để tính giờ cập nhật khi chưa hoàn tất thủ tục đăng ký, đáp ứng điều kiện hoặc thông báo với cơ quan quản lý, thì những trường hợp nào bị coi là vi phạm?</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Điều 17. Mua, bán, chuyển nhượng cổ phần của cổ đông lớn; mua, bán, chuyển nhượng cổ phần dẫn đến trở thành cổ đông lớn</t>
+          <t>Điều 18. Các hành vi vi phạm về cập nhật kiến thức</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>3. Việc mua cổ phần của tổ chức, cá nhân dẫn đến tổ chức, cá nhân đó trở thành cổ đông lớn trong trường hợp ngân hàng thương mại cổ phần tăng mức vốn điều lệ, hồ sơ, thủ tục thực hiện theo quy định tại Điều 12 Thông tư này. Việc mua cổ phần của tổ chức, cá nhân dẫn đến tổ chức, cá nhân đó trở thành cổ đông lớn trong trường hợp ngân hàng thương mại cổ phần tăng mức vốn điều lệ mà tổ chức, cá nhân đó không thuộc danh sách cổ đông mua cổ phần của ngân hàng thương mại cổ phần tại điểm d khoản 1 Điều 12 Thông tư này đã được Ngân hàng Nhà nước chấp thuận thì thực hiện theo quy định tại khoản 1, khoản 2 Điều này và khoản 2 Điều 15 Thông tư này. Văn bản chấp thuận của Ngân hàng Nhà nước về việc mua cổ phần này là bộ phận không tách rời của văn bản chấp thuận tăng mức vốn điều lệ.</t>
+          <t>1. Tổ chức cập nhật kiến thức cho kiểm toán viên hành nghề để tính giờ cập nhật kiến thức theo quy định tại Điều 11 Thông tư này khi không đảm bảo điều kiện quy định tại Điều 7 Thông tư này hoặc đã đủ điều kiện nhưng chưa thông báo cho Cục Quản lý, giám sát kế toán, kiểm toán - Bộ Tài chính</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Khoản 3 Điều 17</t>
+          <t>Khoản 1 Điều 18</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>50/2018/TT-NHNN</t>
+          <t>150/2012/TT-BTC</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=133844</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=27855</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -4853,33 +4875,26 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>question_ambiguous</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr">
         <is>
-          <t>Khoản 3 chỉ nói trường hợp mua cổ phần khi ngân hàng tăng vốn điều lệ; câu hỏi không nêu trường hợp đó, và khoản 2 cùng Điều là hồ sơ chấp thuận mua, nhận chuyển nhượng cổ phần dẫn đến trở thành cổ đông lớn nói chung</t>
-        </is>
-      </c>
-      <c r="O63" t="inlineStr">
-        <is>
-          <t>2. Hồ sơ đề nghị chấp thuận mua, nhận chuyển nhượng cổ phần dẫn đến trở thành cổ đông lớn: Văn bản đề nghị của...</t>
-        </is>
-      </c>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Nếu một tổ chức mở lớp cập nhật kiến thức cho kiểm toán viên để tính giờ cập nhật, thì hành vi nào của tổ chức đó bị coi là vi phạm về cập nhật kiến thức?»; nhãn cũ khong_dat question_ambiguous: Câu hỏi 'hành vi nào của tổ chức đó bị coi là vi phạm' khớp cả khoản 2 (cập nhật nội dung không phù hợp nội dung đã đăng ký), khoản 3 (báo cáo không trung thực), khoản 5 cùng Điều; khoản 1 chỉ là một hành vi). Câu hỏi chốt tổ chức lớp khi chưa hoàn tất đăng ký/điều kiện/thông báo, chỉ khớp khoản 1; ba đáp án khác nhau</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr"/>
       <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr"/>
+      <c r="S63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>vilextime:T3:provision:f5c84a24-df38-11f0-94cb-634e6f8d12a0:2016-07-02</t>
+          <t>vilextime:T3:provision:eaad2c74-df45-11f0-8793-1d800b3bbbe4:2017-07-02</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4889,37 +4904,37 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Khi nhận được thông báo có động vật thủy sản mắc bệnh, Trạm Thú y có trách nhiệm gì đối với việc hướng dẫn và giám sát thu hoạch tại cơ sở nuôi?</t>
+          <t>Khi đăng ký tàu vào Sổ đăng ký tàu biển quốc gia Việt Nam, sổ này dùng để ghi thông tin của những loại tàu, phương tiện nào và được lập dưới hình thức nào?</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2016-07-02</t>
+          <t>2017-07-02</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2. Ngay sau khi nhận được thông báo của chủ cơ sở, Trạm Thú y có trách nhiệm:</t>
+          <t>Điều 6. Sổ đăng ký tàu biển quốc gia Việt Nam</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>a) Phân công cán bộ hướng dẫn, giám sát việc thu hoạch, bảo quản, vận chuyển của cơ sở nuôi có động vật thủy sản mắc bệnh;</t>
+          <t>1. Sổ đăng ký tàu biển quốc gia Việt Nam được sử dụng để ghi lại các thông tin liên quan đến tàu biển đã được đăng ký hoặc xóa đăng ký theo quy định. Nội dung chủ yếu của Sổ đăng ký tàu biển quốc gia Việt Nam được thực hiện theo quy định tại Điều 24 của Bộ Luật hàng hải Việt Nam năm 2015.</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Điểm a Khoản 2 Điều 16</t>
+          <t>Khoản 1 Điều 6</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>04/2016/TT-BNNPTNT</t>
+          <t>171/2016/NĐ-CP</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=106174</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=118563</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -4929,25 +4944,34 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>dat</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr"/>
+          <t>khong_dat</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>group_mismatch</t>
+        </is>
+      </c>
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr">
         <is>
-          <t>Từ mốc 2 câu dẫn gọi Trạm Thú y là 'Cơ quan quản lý chuyên ngành thú y cấp huyện'</t>
+          <t>Mốc 2 và 3 trả lời như nhau cho câu hỏi (cùng các loại tàu, cùng hình thức sổ giấy và cơ sở dữ liệu); chỉ hai đáp án. Văn bản mốc 3 kết thúc ở 'cơ sở dữ liệu' (có thể thiếu 'điện tử')</t>
         </is>
       </c>
       <c r="O64" t="inlineStr"/>
-      <c r="P64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>loại lineage (group_mismatch): Mốc 2 và 3 trả lời như nhau cho câu hỏi (cùng các loại tàu, cùng hình thức sổ giấy và cơ sở dữ liệu); chỉ hai đáp án. Văn bản mốc 3 kết thúc ở 'cơ sở dữ liệu' (có thể thiếu 'điện tử')</t>
+        </is>
+      </c>
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr"/>
+      <c r="S64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>vilextime:T3:provision:f5c84a24-df38-11f0-94cb-634e6f8d12a0:2025-07-02</t>
+          <t>vilextime:T3:provision:eaad2c74-df45-11f0-8793-1d800b3bbbe4:2020-09-16</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4957,37 +4981,37 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Khi nhận được thông báo có động vật thủy sản mắc bệnh, Trạm Thú y có trách nhiệm gì đối với việc hướng dẫn và giám sát thu hoạch tại cơ sở nuôi?</t>
+          <t>Khi đăng ký tàu vào Sổ đăng ký tàu biển quốc gia Việt Nam, sổ này dùng để ghi thông tin của những loại tàu, phương tiện nào và được lập dưới hình thức nào?</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2020-09-16</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2. Ngay sau khi nhận được thông báo của chủ cơ sở, Cơ quan quản lý chuyên ngành thú y cấp huyện có trách nhiệm:</t>
+          <t>Điều 6. Sổ đăng ký tàu biển quốc gia Việt Nam</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>a) Hướng dẫn nhân viên thú y xã và chủ cơ sở nuôi trồng thủy sản thu hoạch động vật thủy sản, giám sát việc thu hoạch và áp dụng các biện pháp phòng chống dịch bệnh động vật theo quy định tại các khoản 1, 2 và khoản 4 Điều 33 Luật Thú y, bảo đảm không làm lây lan dịch bệnh;</t>
+          <t>1. Sổ đăng ký tàu biển quốc gia Việt Nam được sử dụng để ghi lại các thông tin liên quan đến tàu biển, tàu biển công vụ, tàu ngầm, tàu lặn, kho chứa nổi, giàn di động đã được đăng ký hoặc xóa đăng ký theo quy định, sổ đăng ký tàu biển quốc gia Việt Nam được lập dưới dạng sổ ghi chép trên giấy và cơ sở dữ liệu điện tử. Nội dung chủ yếu của sổ đăng ký tàu biển quốc gia Việt Nam được thực hiện theo quy định tại Điều 24 của Bộ luật Hàng hải Việt Nam.</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Điểm a Khoản 2 Điều 16</t>
+          <t>Khoản 1 Điều 6</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>04/2016/TT-BNNPTNT</t>
+          <t>171/2016/NĐ-CP</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=106174</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=118563</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -4997,25 +5021,34 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>dat</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr"/>
+          <t>khong_dat</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>group_mismatch</t>
+        </is>
+      </c>
       <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr">
         <is>
-          <t>Từ mốc 2 câu dẫn gọi Trạm Thú y là 'Cơ quan quản lý chuyên ngành thú y cấp huyện'</t>
+          <t>Mốc 2 và 3 trả lời như nhau cho câu hỏi (cùng các loại tàu, cùng hình thức sổ giấy và cơ sở dữ liệu); chỉ hai đáp án. Văn bản mốc 3 kết thúc ở 'cơ sở dữ liệu' (có thể thiếu 'điện tử')</t>
         </is>
       </c>
       <c r="O65" t="inlineStr"/>
-      <c r="P65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>loại lineage (group_mismatch): Mốc 2 và 3 trả lời như nhau cho câu hỏi (cùng các loại tàu, cùng hình thức sổ giấy và cơ sở dữ liệu); chỉ hai đáp án. Văn bản mốc 3 kết thúc ở 'cơ sở dữ liệu' (có thể thiếu 'điện tử')</t>
+        </is>
+      </c>
       <c r="Q65" t="inlineStr"/>
       <c r="R65" t="inlineStr"/>
+      <c r="S65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>vilextime:T3:provision:f7a7b860-24e9-11f1-80fb-911f0cd7b0b5:2025-01-02</t>
+          <t>vilextime:T3:provision:eaad2c74-df45-11f0-8793-1d800b3bbbe4:2025-10-31</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5025,37 +5058,37 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Theo nguyên tắc đăng ký xe, người trúng đấu giá biển số được lựa chọn đăng ký biển số trúng đấu giá tại những cơ quan nào và áp dụng cho loại xe nào?</t>
+          <t>Khi đăng ký tàu vào Sổ đăng ký tàu biển quốc gia Việt Nam, sổ này dùng để ghi thông tin của những loại tàu, phương tiện nào và được lập dưới hình thức nào?</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025-01-02</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Điều 3. Nguyên tắc đăng ký xe</t>
+          <t>Điều 6. Sổ đăng ký tàu biển quốc gia Việt Nam</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>8. Tổ chức, cá nhân trúng đấu giá biển số xe ô tô được lựa chọn đăng ký, cấp biển số xe trúng đấu giá tại Phòng Cảnh sát giao thông Công an tỉnh, thành phố trực thuộc Trung ương (sau đây viết gọn là Phòng Cảnh sát giao thông) nơi tổ chức, cá nhân có trụ sở, cư trú hoặc tại Phòng Cảnh sát giao thông quản lý biển số xe trúng đấu giá đó.</t>
+          <t>1. Sổ đăng ký tàu biển quốc gia Việt Nam được sử dụng để ghi lại các thông tin liên quan đến tàu biển, tàu biển công vụ, tàu ngầm, tàu lặn, kho chứa nổi, giàn di động đã được đăng ký hoặc xóa đăng ký theo quy định. Sổ đăng ký tàu biển quốc gia Việt Nam được lập dưới dạng sổ ghi chép trên giấy và cơ sở dữ liệu</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Khoản 8 Điều 3</t>
+          <t>Khoản 1 Điều 6</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>79/2024/TT-BCA</t>
+          <t>171/2016/NĐ-CP</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=174894</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=118563</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -5070,28 +5103,29 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>question_ambiguous</t>
+          <t>group_mismatch</t>
         </is>
       </c>
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr">
         <is>
-          <t>Ở mốc 1 khoản 8 chỉ nói xe ô tô; biển số mô tô, xe gắn máy trúng đấu giá ở khoản 9. Câu hỏi 'áp dụng cho loại xe nào' khớp cả hai khoản</t>
-        </is>
-      </c>
-      <c r="O66" t="inlineStr">
-        <is>
-          <t>9. Tổ chức, cá nhân trúng đấu giá biển số xe mô tô, xe gắn máy được lựa chọn đăng ký, cấp biển số xe trúng đấu...</t>
-        </is>
-      </c>
-      <c r="P66" t="inlineStr"/>
+          <t>Mốc 2 và 3 trả lời như nhau cho câu hỏi (cùng các loại tàu, cùng hình thức sổ giấy và cơ sở dữ liệu); chỉ hai đáp án. Văn bản mốc 3 kết thúc ở 'cơ sở dữ liệu' (có thể thiếu 'điện tử')</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>loại lineage (group_mismatch): Mốc 2 và 3 trả lời như nhau cho câu hỏi (cùng các loại tàu, cùng hình thức sổ giấy và cơ sở dữ liệu); chỉ hai đáp án. Văn bản mốc 3 kết thúc ở 'cơ sở dữ liệu' (có thể thiếu 'điện tử')</t>
+        </is>
+      </c>
       <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr"/>
+      <c r="S66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>vilextime:T3:provision:f7a7b860-24e9-11f1-80fb-911f0cd7b0b5:2025-07-02</t>
+          <t>vilextime:T3:provision:ec4a7a6e-df40-11f0-9161-ff81534d3941:2014-10-21</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5101,37 +5135,37 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Theo nguyên tắc đăng ký xe, người trúng đấu giá biển số được lựa chọn đăng ký biển số trúng đấu giá tại những cơ quan nào và áp dụng cho loại xe nào?</t>
+          <t>Theo quy định về quá cảnh hàng hóa của Campuchia qua lãnh thổ Việt Nam, hàng hóa khác khi quá cảnh phải xin giấy phép của cơ quan nào?</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2014-10-21</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Điều 3. Nguyên tắc đăng ký xe</t>
+          <t>THỦ TỤC CẤP, GIA HẠN GIẤY PHÉP QUÁ CẢNH HÀNG HÓA</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>8. Tổ chức, cá nhân trúng đấu giá biển số xe được lựa chọn đăng ký, cấp biển số xe trúng đấu giá tại các cơ quan đăng ký xe trong tỉnh, thành phố nơi tổ chức, cá nhân có trụ sở, cư trú hoặc tại Phòng Cảnh sát giao thông quản lý biển số xe trúng đấu giá đó.</t>
+          <t>Các loại hàng hóa khác không thuộc trường hợp quy định tại Điều 4 và Khoản 1, Khoản 2 Điều 5 Hiệp định, khi quá cảnh theo đường bộ, đường thủy hoặc đường sắt qua các cặp cửa khẩu quy định tại Điều 7 Hiệp định, chủ hàng hoặc người chuyên chở được ủy quyền hợp pháp làm thủ tục quá cảnh tại cơ quan Hải quan, không phải xin giấy phép quá cảnh hàng hóa của Bộ Công Thương hoặc Phòng Quản lý Xuất nhập khẩu khu vực thành phố Hồ Chí Minh (Cục Xuất nhập khẩu - Bộ Công Thương).</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Khoản 8 Điều 3</t>
+          <t>Điều 5</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>79/2024/TT-BCA</t>
+          <t>27/2014/TT-BCT</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=174894</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=46098</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -5141,21 +5175,34 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>dat</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr"/>
+          <t>khong_dat</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>group_mismatch</t>
+        </is>
+      </c>
       <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>Ở cả ba mốc câu trả lời như nhau: hàng hóa khác không phải xin giấy phép, chỉ làm thủ tục tại Hải quan; chỗ đổi chỉ là tên cơ quan cấp phép không cần xin. Câu hỏi còn giả định sai là phải xin giấy phép</t>
+        </is>
+      </c>
       <c r="O67" t="inlineStr"/>
-      <c r="P67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>loại lineage (group_mismatch): Ở cả ba mốc câu trả lời như nhau: hàng hóa khác không phải xin giấy phép, chỉ làm thủ tục tại Hải quan; chỗ đổi chỉ là tên cơ quan cấp phép không cần xin. Câu hỏi còn giả định sai là phải xin giấy phép</t>
+        </is>
+      </c>
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr"/>
+      <c r="S67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>vilextime:T3:provision:f8d931e0-1df6-11f1-a901-7169bc99fc94:2023-11-28</t>
+          <t>vilextime:T3:provision:ec4a7a6e-df40-11f0-9161-ff81534d3941:2025-07-02</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5165,37 +5212,37 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Nếu một tổ chức tuyển dụng, cung ứng thuyền viên hàng hải đề nghị cấp lại Giấy xác nhận, thì hồ sơ phải gửi đến cơ quan nào và bằng những hình thức nào?</t>
+          <t>Theo quy định về quá cảnh hàng hóa của Campuchia qua lãnh thổ Việt Nam, hàng hóa khác khi quá cảnh phải xin giấy phép của cơ quan nào?</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2023-11-28</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Điều 14. Cấp lại Giấy xác nhận</t>
+          <t>THỦ TỤC CẤP, GIA HẠN GIẤY PHÉP QUÁ CẢNH HÀNG HÓA</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2. Tổ chức tuyển dụng, cung ứng thuyền viên hàng hải gửi trực tiếp hoặc qua hệ thống bưu chính hoặc qua hệ thống dịch vụ công trực tuyến đến Chi cục Hàng hải Việt Nam 01 bộ hồ sơ đề nghị cấp lại Giấy xác nhận. Hồ sơ bao gồm: a) Tờ khai đề nghị cấp lại Giấy xác nhận theo Mẫu số 04 quy định tại Phụ lục ban hành kèm theo Nghị định này; b) Bản sao có chứng thực hoặc bản sao kèm bản chính để đối chiếu hoặc bản sao điện tử hoặc bản sao điện tử từ sổ gốc hoặc bản sao điện tử có chứng thực từ bản chính Giấy chứng nhận đăng ký doanh nghiệp (đối với trường hợp thay đổi thông tin về doanh nghiệp); Trong thời hạn 03 ngày làm việc, kể từ ngày nhận được văn bản đề nghị, Chi cục Hàng hải Việt Nam cấp lại Giấy xác nhận và trả kết quả trực tiếp hoặc qua hệ thống bưu chính hoặc qua hệ thống dịch vụ công trực tuyến đến tổ chức tuyển dụng, cung ứng thuyền viên hàng hải; trường hợp không chấp thuận, Chi cục Hàng hải Việt Nam phải có văn bản trả lời và nêu rõ lý do.3. Khi cấp lại Giấy xác nhận, Chi cục Hàng hải Việt Nam phải ghi rõ trong Giấy xác nhận mới về việc thay thế Giấy xác nhận cũ và thông báo trên Cổng thông tin điện tử của Chi cục Hàng hải Việt Nam.</t>
+          <t>Các loại hàng hóa khác không thuộc trường hợp quy định tại Điều 4 và Khoản 1, Khoản 2 Điều 5 Hiệp định, khi quá cảnh theo đường bộ, đường thủy hoặc đường sắt qua các cặp cửa khẩu quy định tại Điều 7 Hiệp định, chủ hàng hoặc người chuyên chở được ủy quyền hợp pháp làm thủ tục quá cảnh tại cơ quan Hải quan, không phải xin giấy phép quá cảnh hàng hóa của Bộ Công Thương hoặc Cục Xuất nhập khẩu - Bộ Công Thương.</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Khoản 2 Điều 14</t>
+          <t>Điều 5</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>29/2017/NĐ-CP</t>
+          <t>27/2014/TT-BCT</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=120772</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=46098</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -5205,29 +5252,34 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>dat</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
+          <t>khong_dat</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>group_mismatch</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr">
         <is>
-          <t>Văn bản đáp án mốc 3 dính cả khoản 3 ('…nêu rõ lý do.3. Khi cấp lại Giấy xác nhận…')</t>
+          <t>Ở cả ba mốc câu trả lời như nhau: hàng hóa khác không phải xin giấy phép, chỉ làm thủ tục tại Hải quan; chỗ đổi chỉ là tên cơ quan cấp phép không cần xin. Câu hỏi còn giả định sai là phải xin giấy phép</t>
         </is>
       </c>
       <c r="O68" t="inlineStr"/>
-      <c r="P68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>loại lineage (group_mismatch): Ở cả ba mốc câu trả lời như nhau: hàng hóa khác không phải xin giấy phép, chỉ làm thủ tục tại Hải quan; chỗ đổi chỉ là tên cơ quan cấp phép không cần xin. Câu hỏi còn giả định sai là phải xin giấy phép</t>
+        </is>
+      </c>
       <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr"/>
+      <c r="S68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>vilextime:T3:provision:fc52f300-eb84-11f0-ab2c-4f4961cea41c:2017-08-16</t>
+          <t>vilextime:T3:provision:ec4a7a6e-df40-11f0-9161-ff81534d3941:2026-05-30</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5237,37 +5289,37 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Pháp luật về cơ sở dữ liệu quốc gia về khoa học và công nghệ quy định cơ sở dữ liệu tiêu chuẩn đo lường chất lượng do cơ quan nào xây dựng, vận hành?</t>
+          <t>Theo quy định về quá cảnh hàng hóa của Campuchia qua lãnh thổ Việt Nam, hàng hóa khác khi quá cảnh phải xin giấy phép của cơ quan nào?</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2017-08-16</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Điều 17. Cơ sở dữ liệu tiêu chuẩn đo lường chất lượng</t>
+          <t>THỦ TỤC CẤP, GIA HẠN GIẤY PHÉP QUÁ CẢNH HÀNG HÓA</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2. Cơ sở dữ liệu tiêu chuẩn đo lường chất lượng được xây dựng, quản trị, vận hành và phát triển tại Tổng cục Tiêu chuẩn Đo lường Chất lượng, Bộ Khoa học và Công nghệ và được kết nối với Cơ sở dữ liệu quốc gia về khoa học và công nghệ.</t>
+          <t>Điều 5. Quá cảnh hàng hóa khác Các loại hàng hóa khác không thuộc trường hợp quy định tại Điều 4 và khoản 1, khoản 2 Điều 5 Hiệp định, khi quá cảnh theo đường bộ, đường thủy hoặc đường sắt qua các cặp cửa khẩu quy định tại Điều 7 Hiệp định, chủ hàng hoặc người chuyên chở được ủy quyền hợp pháp làm thủ tục quá cảnh tại cơ quan Hải quan, không phải xin giấy phép quá cảnh hàng hóa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Khoản 2 Điều 17</t>
+          <t>Điều 5</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>10/2017/TT-BKHCN</t>
+          <t>27/2014/TT-BCT</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=122964</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=46098</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -5288,18 +5340,23 @@
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr">
         <is>
-          <t>Câu hỏi hỏi cơ quan xây dựng, vận hành: mốc 1 và 2 cùng là Tổng cục Tiêu chuẩn Đo lường Chất lượng (lần sửa 2023 chỉ thêm 'chia sẻ … trực tuyến'), mốc 3 là Ủy ban. Chỉ hai đáp án; có thể chuyển T2 (mốc 2–3)</t>
+          <t>Ở cả ba mốc câu trả lời như nhau: hàng hóa khác không phải xin giấy phép, chỉ làm thủ tục tại Hải quan; chỗ đổi chỉ là tên cơ quan cấp phép không cần xin. Câu hỏi còn giả định sai là phải xin giấy phép</t>
         </is>
       </c>
       <c r="O69" t="inlineStr"/>
-      <c r="P69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>loại lineage (group_mismatch): Ở cả ba mốc câu trả lời như nhau: hàng hóa khác không phải xin giấy phép, chỉ làm thủ tục tại Hải quan; chỗ đổi chỉ là tên cơ quan cấp phép không cần xin. Câu hỏi còn giả định sai là phải xin giấy phép</t>
+        </is>
+      </c>
       <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr"/>
+      <c r="S69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>vilextime:T3:provision:fc52f300-eb84-11f0-ab2c-4f4961cea41c:2023-08-11</t>
+          <t>vilextime:T3:provision:f2947168-df4f-11f0-b8a1-cba0d0f18fba:2019-02-16</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5309,37 +5366,37 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Pháp luật về cơ sở dữ liệu quốc gia về khoa học và công nghệ quy định cơ sở dữ liệu tiêu chuẩn đo lường chất lượng do cơ quan nào xây dựng, vận hành?</t>
+          <t>Khi ngân hàng thương mại cổ phần tăng vốn điều lệ, những trường hợp mua cổ phần nào liên quan đến cổ đông lớn thực hiện theo hồ sơ, thủ tục được dẫn chiếu, và trường hợp nào phải theo thủ tục khác?</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2023-08-11</t>
+          <t>2019-02-16</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Điều 17. Cơ sở dữ liệu tiêu chuẩn đo lường chất lượng</t>
+          <t>Điều 17. Mua, bán, chuyển nhượng cổ phần của cổ đông lớn; mua, bán, chuyển nhượng cổ phần dẫn đến trở thành cổ đông lớn</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2. Cơ sở dữ liệu về tiêu chuẩn đo lường chất lượng được xây dựng, quản trị, vận hành và phát triển tại Tổng cục Tiêu chuẩn Đo lường Chất lượng, Bộ Khoa học và Công nghệ và được kết nối, chia sẻ với Cơ sở dữ liệu quốc gia về khoa học và công nghệ thông qua phương thức trực tuyến trên môi trường mạng.</t>
+          <t>3. Việc mua cổ phần của tổ chức, cá nhân dẫn đến tổ chức, cá nhân đó trở thành cổ đông lớn trong trường hợp ngân hàng thương mại cổ phần tăng mức vốn điều lệ, hồ sơ, trình tự, thủ tục thực hiện theo quy định tại Điều 12 Thông tư này.</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Khoản 2 Điều 17</t>
+          <t>Khoản 3 Điều 17</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>10/2017/TT-BKHCN</t>
+          <t>50/2018/TT-NHNN</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=122964</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=133844</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -5349,29 +5406,26 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>group_mismatch</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr">
         <is>
-          <t>Câu hỏi hỏi cơ quan xây dựng, vận hành: mốc 1 và 2 cùng là Tổng cục Tiêu chuẩn Đo lường Chất lượng (lần sửa 2023 chỉ thêm 'chia sẻ … trực tuyến'), mốc 3 là Ủy ban. Chỉ hai đáp án; có thể chuyển T2 (mốc 2–3)</t>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Việc mua cổ phần dẫn đến trở thành cổ đông lớn của ngân hàng thương mại cần Ngân hàng Nhà nước chấp thuận trong những trường hợp nào?»; nhãn cũ khong_dat question_ambiguous: Khoản 3 chỉ nói trường hợp mua cổ phần khi ngân hàng tăng vốn điều lệ; câu hỏi không nêu trường hợp đó, và khoản 2 cùng Điều là hồ sơ chấp thuận mua, nhận chuyển nhượng cổ phần dẫn đến trở thành cổ đông lớn nói chung). Ba đáp án khác nhau: mốc 1 chỉ mua dẫn tới cổ đông lớn theo Điều 12; mốc 2 thêm mua của cổ đông lớn và ngoại lệ ngoài danh sách đã chấp thuận; mốc 3 bỏ lại trường hợp mua của cổ đông lớn</t>
         </is>
       </c>
       <c r="O70" t="inlineStr"/>
       <c r="P70" t="inlineStr"/>
       <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr"/>
+      <c r="S70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>vilextime:T3:provision:fc52f300-eb84-11f0-ab2c-4f4961cea41c:2024-11-23</t>
+          <t>vilextime:T3:provision:f2947168-df4f-11f0-b8a1-cba0d0f18fba:2022-08-16</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5381,37 +5435,37 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Pháp luật về cơ sở dữ liệu quốc gia về khoa học và công nghệ quy định cơ sở dữ liệu tiêu chuẩn đo lường chất lượng do cơ quan nào xây dựng, vận hành?</t>
+          <t>Khi ngân hàng thương mại cổ phần tăng vốn điều lệ, những trường hợp mua cổ phần nào liên quan đến cổ đông lớn thực hiện theo hồ sơ, thủ tục được dẫn chiếu, và trường hợp nào phải theo thủ tục khác?</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2024-11-23</t>
+          <t>2022-08-16</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Điều 17. Cơ sở dữ liệu tiêu chuẩn đo lường chất lượng</t>
+          <t>Điều 17. Mua, bán, chuyển nhượng cổ phần của cổ đông lớn; mua, bán, chuyển nhượng cổ phần dẫn đến trở thành cổ đông lớn</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2. Cơ sở dữ liệu về tiêu chuẩn đo lường chất lượng được xây dựng, quản trị, vận hành và phát triển tại Ủy ban Tiêu chuẩn Đo lường Chất lượng Quốc gia, Bộ Khoa học và Công nghệ và được kết nối, chia sẻ với Cơ sở dữ liệu quốc gia về khoa học và công nghệ thông qua phương thức trực tuyến trên môi trường mạng.</t>
+          <t>3. Việc mua cổ phần của tổ chức, cá nhân dẫn đến tổ chức, cá nhân đó trở thành cổ đông lớn hoặc mua cổ phần của cổ đông lớn trong trường hợp ngân hàng thương mại cổ phần tăng mức vốn điều lệ, hồ sơ, trình tự, thủ tục thực hiện theo quy định tại Điều 12 Thông tư này.Việc mua cổ phần của tổ chức, cá nhân dẫn đến tổ chức, cá nhân đó trở thành cổ đông lớn hoặc mua cổ phần của cổ đông lớn trong trường hợp ngân hàng thương mại cổ phần tăng mức vốn điều lệ mà tổ chức, cá nhân hoặc cổ đông lớn đó không thuộc danh sách cổ đông mua cổ phần của ngân hàng thương mại cổ phần tại điểm d khoản 1 Điều 12 Thông tư này đã được Ngân hàng Nhà nước chấp thuận thì thực hiện theo quy định tại khoản 1, khoản 2 Điều này và khoản 2 Điều 15 Thông tư này. Văn bản chấp thuận của Ngân hàng Nhà nước về việc mua cổ phần này là bộ phận không tách rời của văn bản chấp thuận tăng mức vốn điều lệ.</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Khoản 2 Điều 17</t>
+          <t>Khoản 3 Điều 17</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>10/2017/TT-BKHCN</t>
+          <t>50/2018/TT-NHNN</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=122964</t>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=133844</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -5421,24 +5475,658 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>khong_dat</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>group_mismatch</t>
-        </is>
-      </c>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr">
         <is>
-          <t>Câu hỏi hỏi cơ quan xây dựng, vận hành: mốc 1 và 2 cùng là Tổng cục Tiêu chuẩn Đo lường Chất lượng (lần sửa 2023 chỉ thêm 'chia sẻ … trực tuyến'), mốc 3 là Ủy ban. Chỉ hai đáp án; có thể chuyển T2 (mốc 2–3)</t>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Việc mua cổ phần dẫn đến trở thành cổ đông lớn của ngân hàng thương mại cần Ngân hàng Nhà nước chấp thuận trong những trường hợp nào?»; nhãn cũ khong_dat question_ambiguous: Khoản 3 chỉ nói trường hợp mua cổ phần khi ngân hàng tăng vốn điều lệ; câu hỏi không nêu trường hợp đó, và khoản 2 cùng Điều là hồ sơ chấp thuận mua, nhận chuyển nhượng cổ phần dẫn đến trở thành cổ đông lớn nói chung). Ba đáp án khác nhau: mốc 1 chỉ mua dẫn tới cổ đông lớn theo Điều 12; mốc 2 thêm mua của cổ đông lớn và ngoại lệ ngoài danh sách đã chấp thuận; mốc 3 bỏ lại trường hợp mua của cổ đông lớn</t>
         </is>
       </c>
       <c r="O71" t="inlineStr"/>
       <c r="P71" t="inlineStr"/>
       <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr"/>
+      <c r="S71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>vilextime:T3:provision:f2947168-df4f-11f0-b8a1-cba0d0f18fba:2024-07-02</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Khi ngân hàng thương mại cổ phần tăng vốn điều lệ, những trường hợp mua cổ phần nào liên quan đến cổ đông lớn thực hiện theo hồ sơ, thủ tục được dẫn chiếu, và trường hợp nào phải theo thủ tục khác?</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2024-07-02</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Điều 17. Mua, bán, chuyển nhượng cổ phần của cổ đông lớn; mua, bán, chuyển nhượng cổ phần dẫn đến trở thành cổ đông lớn</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>3. Việc mua cổ phần của tổ chức, cá nhân dẫn đến tổ chức, cá nhân đó trở thành cổ đông lớn trong trường hợp ngân hàng thương mại cổ phần tăng mức vốn điều lệ, hồ sơ, thủ tục thực hiện theo quy định tại Điều 12 Thông tư này. Việc mua cổ phần của tổ chức, cá nhân dẫn đến tổ chức, cá nhân đó trở thành cổ đông lớn trong trường hợp ngân hàng thương mại cổ phần tăng mức vốn điều lệ mà tổ chức, cá nhân đó không thuộc danh sách cổ đông mua cổ phần của ngân hàng thương mại cổ phần tại điểm d khoản 1 Điều 12 Thông tư này đã được Ngân hàng Nhà nước chấp thuận thì thực hiện theo quy định tại khoản 1, khoản 2 Điều này và khoản 2 Điều 15 Thông tư này. Văn bản chấp thuận của Ngân hàng Nhà nước về việc mua cổ phần này là bộ phận không tách rời của văn bản chấp thuận tăng mức vốn điều lệ.</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Khoản 3 Điều 17</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>50/2018/TT-NHNN</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=133844</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Việc mua cổ phần dẫn đến trở thành cổ đông lớn của ngân hàng thương mại cần Ngân hàng Nhà nước chấp thuận trong những trường hợp nào?»; nhãn cũ khong_dat question_ambiguous: Khoản 3 chỉ nói trường hợp mua cổ phần khi ngân hàng tăng vốn điều lệ; câu hỏi không nêu trường hợp đó, và khoản 2 cùng Điều là hồ sơ chấp thuận mua, nhận chuyển nhượng cổ phần dẫn đến trở thành cổ đông lớn nói chung). Ba đáp án khác nhau: mốc 1 chỉ mua dẫn tới cổ đông lớn theo Điều 12; mốc 2 thêm mua của cổ đông lớn và ngoại lệ ngoài danh sách đã chấp thuận; mốc 3 bỏ lại trường hợp mua của cổ đông lớn</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr"/>
+      <c r="Q72" t="inlineStr"/>
+      <c r="R72" t="inlineStr"/>
+      <c r="S72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>vilextime:T3:provision:f5c84a24-df38-11f0-94cb-634e6f8d12a0:2016-07-02</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Khi nhận được thông báo có động vật thủy sản mắc bệnh, Trạm Thú y có trách nhiệm gì đối với việc hướng dẫn và giám sát thu hoạch tại cơ sở nuôi?</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2016-07-02</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>2. Ngay sau khi nhận được thông báo của chủ cơ sở, Trạm Thú y có trách nhiệm:</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>a) Phân công cán bộ hướng dẫn, giám sát việc thu hoạch, bảo quản, vận chuyển của cơ sở nuôi có động vật thủy sản mắc bệnh;</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Điểm a Khoản 2 Điều 16</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>04/2016/TT-BNNPTNT</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=106174</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>Từ mốc 2 câu dẫn gọi Trạm Thú y là 'Cơ quan quản lý chuyên ngành thú y cấp huyện'</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr"/>
+      <c r="Q73" t="inlineStr"/>
+      <c r="R73" t="inlineStr"/>
+      <c r="S73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>vilextime:T3:provision:f5c84a24-df38-11f0-94cb-634e6f8d12a0:2025-07-02</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Khi nhận được thông báo có động vật thủy sản mắc bệnh, Trạm Thú y có trách nhiệm gì đối với việc hướng dẫn và giám sát thu hoạch tại cơ sở nuôi?</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>2. Ngay sau khi nhận được thông báo của chủ cơ sở, Cơ quan quản lý chuyên ngành thú y cấp huyện có trách nhiệm:</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>a) Hướng dẫn nhân viên thú y xã và chủ cơ sở nuôi trồng thủy sản thu hoạch động vật thủy sản, giám sát việc thu hoạch và áp dụng các biện pháp phòng chống dịch bệnh động vật theo quy định tại các khoản 1, 2 và khoản 4 Điều 33 Luật Thú y, bảo đảm không làm lây lan dịch bệnh;</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Điểm a Khoản 2 Điều 16</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>04/2016/TT-BNNPTNT</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=106174</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>Từ mốc 2 câu dẫn gọi Trạm Thú y là 'Cơ quan quản lý chuyên ngành thú y cấp huyện'</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr"/>
+      <c r="R74" t="inlineStr"/>
+      <c r="S74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>vilextime:T3:provision:f7a7b860-24e9-11f1-80fb-911f0cd7b0b5:2025-01-02</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Theo nguyên tắc đăng ký xe, người trúng đấu giá biển số được lựa chọn đăng ký biển số trúng đấu giá tại những cơ quan nào và áp dụng cho loại xe nào?</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2025-01-02</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Điều 3. Nguyên tắc đăng ký xe</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>8. Tổ chức, cá nhân trúng đấu giá biển số xe ô tô được lựa chọn đăng ký, cấp biển số xe trúng đấu giá tại Phòng Cảnh sát giao thông Công an tỉnh, thành phố trực thuộc Trung ương (sau đây viết gọn là Phòng Cảnh sát giao thông) nơi tổ chức, cá nhân có trụ sở, cư trú hoặc tại Phòng Cảnh sát giao thông quản lý biển số xe trúng đấu giá đó.</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Khoản 8 Điều 3</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>79/2024/TT-BCA</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=174894</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>khong_dat</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>question_ambiguous</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>Ở mốc 1 khoản 8 chỉ nói xe ô tô; biển số mô tô, xe gắn máy trúng đấu giá ở khoản 9. Câu hỏi 'áp dụng cho loại xe nào' khớp cả hai khoản</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>9. Tổ chức, cá nhân trúng đấu giá biển số xe mô tô, xe gắn máy được lựa chọn đăng ký, cấp biển số xe trúng đấu...</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>loại lineage (question_ambiguous): Ở mốc 1 khoản 8 chỉ nói xe ô tô; biển số mô tô, xe gắn máy trúng đấu giá ở khoản 9. Câu hỏi 'áp dụng cho loại xe nào' khớp cả hai khoản</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr"/>
+      <c r="R75" t="inlineStr"/>
+      <c r="S75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>vilextime:T3:provision:f7a7b860-24e9-11f1-80fb-911f0cd7b0b5:2025-07-02</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Theo nguyên tắc đăng ký xe, người trúng đấu giá biển số được lựa chọn đăng ký biển số trúng đấu giá tại những cơ quan nào và áp dụng cho loại xe nào?</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Điều 3. Nguyên tắc đăng ký xe</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>8. Tổ chức, cá nhân trúng đấu giá biển số xe được lựa chọn đăng ký, cấp biển số xe trúng đấu giá tại các cơ quan đăng ký xe trong tỉnh, thành phố nơi tổ chức, cá nhân có trụ sở, cư trú hoặc tại Phòng Cảnh sát giao thông quản lý biển số xe trúng đấu giá đó.</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Khoản 8 Điều 3</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>79/2024/TT-BCA</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=174894</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>loại lineage (question_ambiguous): Ở mốc 1 khoản 8 chỉ nói xe ô tô; biển số mô tô, xe gắn máy trúng đấu giá ở khoản 9. Câu hỏi 'áp dụng cho loại xe nào' khớp cả hai khoản</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr"/>
+      <c r="R76" t="inlineStr"/>
+      <c r="S76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>vilextime:T3:provision:f8d931e0-1df6-11f1-a901-7169bc99fc94:2023-11-28</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Nếu một tổ chức tuyển dụng, cung ứng thuyền viên hàng hải đề nghị cấp lại Giấy xác nhận, thì hồ sơ phải gửi đến cơ quan nào và bằng những hình thức nào?</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2023-11-28</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Điều 14. Cấp lại Giấy xác nhận</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2. Tổ chức tuyển dụng, cung ứng thuyền viên hàng hải gửi trực tiếp hoặc qua hệ thống bưu chính hoặc qua hệ thống dịch vụ công trực tuyến đến Chi cục Hàng hải Việt Nam 01 bộ hồ sơ đề nghị cấp lại Giấy xác nhận. Hồ sơ bao gồm: a) Tờ khai đề nghị cấp lại Giấy xác nhận theo Mẫu số 04 quy định tại Phụ lục ban hành kèm theo Nghị định này; b) Bản sao có chứng thực hoặc bản sao kèm bản chính để đối chiếu hoặc bản sao điện tử hoặc bản sao điện tử từ sổ gốc hoặc bản sao điện tử có chứng thực từ bản chính Giấy chứng nhận đăng ký doanh nghiệp (đối với trường hợp thay đổi thông tin về doanh nghiệp); Trong thời hạn 03 ngày làm việc, kể từ ngày nhận được văn bản đề nghị, Chi cục Hàng hải Việt Nam cấp lại Giấy xác nhận và trả kết quả trực tiếp hoặc qua hệ thống bưu chính hoặc qua hệ thống dịch vụ công trực tuyến đến tổ chức tuyển dụng, cung ứng thuyền viên hàng hải; trường hợp không chấp thuận, Chi cục Hàng hải Việt Nam phải có văn bản trả lời và nêu rõ lý do.3. Khi cấp lại Giấy xác nhận, Chi cục Hàng hải Việt Nam phải ghi rõ trong Giấy xác nhận mới về việc thay thế Giấy xác nhận cũ và thông báo trên Cổng thông tin điện tử của Chi cục Hàng hải Việt Nam.</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Khoản 2 Điều 14</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>29/2017/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=120772</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>Văn bản đáp án mốc 3 dính cả khoản 3 ('…nêu rõ lý do.3. Khi cấp lại Giấy xác nhận…')</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr"/>
+      <c r="P77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr"/>
+      <c r="R77" t="inlineStr"/>
+      <c r="S77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>vilextime:T3:provision:fc52f300-eb84-11f0-ab2c-4f4961cea41c:2017-08-16</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Theo quy định về cơ sở dữ liệu quốc gia về khoa học và công nghệ, cơ sở dữ liệu tiêu chuẩn đo lường chất lượng do cơ quan nào xây dựng, vận hành và được kết nối với cơ sở dữ liệu quốc gia theo cách nào?</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2017-08-16</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Điều 17. Cơ sở dữ liệu tiêu chuẩn đo lường chất lượng</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2. Cơ sở dữ liệu tiêu chuẩn đo lường chất lượng được xây dựng, quản trị, vận hành và phát triển tại Tổng cục Tiêu chuẩn Đo lường Chất lượng, Bộ Khoa học và Công nghệ và được kết nối với Cơ sở dữ liệu quốc gia về khoa học và công nghệ.</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Khoản 2 Điều 17</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>10/2017/TT-BKHCN</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=122964</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Pháp luật về cơ sở dữ liệu quốc gia về khoa học và công nghệ quy định cơ sở dữ liệu tiêu chuẩn đo lường chất lượng do cơ quan nào xây dựng, vận hành?»; nhãn cũ khong_dat group_mismatch: Câu hỏi hỏi cơ quan xây dựng, vận hành: mốc 1 và 2 cùng là Tổng cục Tiêu chuẩn Đo lường Chất lượng (lần sửa 2023 chỉ thêm 'chia sẻ … trực tuyến'), mốc 3 là Ủy ban. Chỉ hai đáp án; có thể chuyển T2 (mốc 2–3)). Hỏi cả cơ quan và cách kết nối: ba đáp án khác nhau</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" t="inlineStr"/>
+      <c r="Q78" t="inlineStr"/>
+      <c r="R78" t="inlineStr"/>
+      <c r="S78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>vilextime:T3:provision:fc52f300-eb84-11f0-ab2c-4f4961cea41c:2023-08-11</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Theo quy định về cơ sở dữ liệu quốc gia về khoa học và công nghệ, cơ sở dữ liệu tiêu chuẩn đo lường chất lượng do cơ quan nào xây dựng, vận hành và được kết nối với cơ sở dữ liệu quốc gia theo cách nào?</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2023-08-11</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Điều 17. Cơ sở dữ liệu tiêu chuẩn đo lường chất lượng</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2. Cơ sở dữ liệu về tiêu chuẩn đo lường chất lượng được xây dựng, quản trị, vận hành và phát triển tại Tổng cục Tiêu chuẩn Đo lường Chất lượng, Bộ Khoa học và Công nghệ và được kết nối, chia sẻ với Cơ sở dữ liệu quốc gia về khoa học và công nghệ thông qua phương thức trực tuyến trên môi trường mạng.</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Khoản 2 Điều 17</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>10/2017/TT-BKHCN</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=122964</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Pháp luật về cơ sở dữ liệu quốc gia về khoa học và công nghệ quy định cơ sở dữ liệu tiêu chuẩn đo lường chất lượng do cơ quan nào xây dựng, vận hành?»; nhãn cũ khong_dat group_mismatch: Câu hỏi hỏi cơ quan xây dựng, vận hành: mốc 1 và 2 cùng là Tổng cục Tiêu chuẩn Đo lường Chất lượng (lần sửa 2023 chỉ thêm 'chia sẻ … trực tuyến'), mốc 3 là Ủy ban. Chỉ hai đáp án; có thể chuyển T2 (mốc 2–3)). Hỏi cả cơ quan và cách kết nối: ba đáp án khác nhau</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr"/>
+      <c r="P79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr"/>
+      <c r="R79" t="inlineStr"/>
+      <c r="S79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>vilextime:T3:provision:fc52f300-eb84-11f0-ab2c-4f4961cea41c:2024-11-23</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Theo quy định về cơ sở dữ liệu quốc gia về khoa học và công nghệ, cơ sở dữ liệu tiêu chuẩn đo lường chất lượng do cơ quan nào xây dựng, vận hành và được kết nối với cơ sở dữ liệu quốc gia theo cách nào?</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2024-11-23</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Điều 17. Cơ sở dữ liệu tiêu chuẩn đo lường chất lượng</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2. Cơ sở dữ liệu về tiêu chuẩn đo lường chất lượng được xây dựng, quản trị, vận hành và phát triển tại Ủy ban Tiêu chuẩn Đo lường Chất lượng Quốc gia, Bộ Khoa học và Công nghệ và được kết nối, chia sẻ với Cơ sở dữ liệu quốc gia về khoa học và công nghệ thông qua phương thức trực tuyến trên môi trường mạng.</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Khoản 2 Điều 17</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>10/2017/TT-BKHCN</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>https://vbpl.vn/TW/Pages/vbpq-toanvan.aspx?ItemID=122964</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>claude-opus-5-5</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>dat</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Pháp luật về cơ sở dữ liệu quốc gia về khoa học và công nghệ quy định cơ sở dữ liệu tiêu chuẩn đo lường chất lượng do cơ quan nào xây dựng, vận hành?»; nhãn cũ khong_dat group_mismatch: Câu hỏi hỏi cơ quan xây dựng, vận hành: mốc 1 và 2 cùng là Tổng cục Tiêu chuẩn Đo lường Chất lượng (lần sửa 2023 chỉ thêm 'chia sẻ … trực tuyến'), mốc 3 là Ủy ban. Chỉ hai đáp án; có thể chuyển T2 (mốc 2–3)). Hỏi cả cơ quan và cách kết nối: ba đáp án khác nhau</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr"/>
+      <c r="P80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr"/>
+      <c r="R80" t="inlineStr"/>
+      <c r="S80" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/review/audit_T3.xlsx
+++ b/data/review/audit_T3.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,13 +25,25 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007F3F00"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +58,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,8 +429,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W108"/>
+  <dimension ref="A1:Y108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="80" customWidth="1" min="24" max="24"/>
+    <col width="80" customWidth="1" min="25" max="25"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -532,6 +552,16 @@
           <t>audit_note</t>
         </is>
       </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>trich_van_ban_goc</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>trich_van_ban_tac_dong</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -594,7 +624,6 @@
           <t>actor_has_transitional</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -605,18 +634,39 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
           <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Nếu cơ quan thuế nhận được thông tin về thửa đất phải nộp tiền sử dụng đất, thì cơ quan thuế xác định và thông báo số tiền phải nộp dựa trên phiếu chuyển thông tin từ những cơ quan nào?»; nhãn cũ khong_dat group_mismatch: Câu hỏi hỏi phiếu chuyển thông tin đến từ cơ quan nào: mốc 1 và 2 như nhau (cơ quan quản lý đất đai và các cơ quan khác); lần sửa 2025 chỉ mở rộng các khoản tiền phải tính. Chỉ hai đáp án). Hỏi cả khoản tiền phải tính và nguồn phiếu: mốc 1–2 khác về khoản tiền, mốc 3 khác về cơ quan chuyển phiếu; ba đáp án; id cũ vilextime:T3:provision:054aaf90-3188-11f1-9b71-9161173b0ca7:2024-08-02 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
+      <c r="X2" s="2" t="inlineStr">
+        <is>
+          <t>103/2024/NĐ-CP · hiệu lực 2024-08-01 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 44. Trách nhiệm của cơ quan và người sử dụng đất
+3. Cơ quan thuế:
+a) Căn cứ quy định tại Nghị định này và Phiếu chuyển thông tin do cơ quan có chức năng quản lý đất đai và các cơ quan khác chuyển đến để tính tiền sử dụng đất, tiền thuê đất, tiền thuê đất có mặt nước, tiền thuê đất để xây dựng công trình ngầm, công trình ngầm nằm ngoài phần không gian sử dụng đất theo quy định tại khoản 3 Điều 27 Nghị định này, số tiền sử dụng đất, tiền thuê đất được giảm và thông báo cho người sử dụng đất theo quy định tại Nghị định này.
+b) Tổ chức thực hiện, hướng dẫn, giải đáp vướng mắc, giải quyết khiếu nại về tính, thu, nộp tiền sử dụng đất, tiền thuê đất theo quy định tại Nghị định này, pháp luật về quản lý thuế và pháp luật khác có liên quan.
+c) Xác định đơn giá thuê đất trả tiền thuê đất hàng năm, đơn giá thuê đất trả tiền thuê đất một lần cho cả thời gian thuê quy định tại Điều 26 Nghị định này.
+d) Rà soát các trường hợp đã ghi nợ nhưng đến nay chưa hoàn thành việc trả nợ để thông báo đến các trường hợp còn nợ tiền sử dụng đất về việc ghi nợ, thanh toán nợ và xóa nợ tiền sử dụng đất theo đúng quy định tại Nghị định này.
+đ) Thực hiện các nhiệm vụ khác theo quy định tại Nghị định này và pháp luật khác có liên quan.</t>
+        </is>
+      </c>
+      <c r="Y2" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 291/2025/NĐ-CP · hiệu lực 2025-11-06
+b) Sửa đổi, bổ sung điểm a khoản 3 như sau:
+“a) Căn cứ quy định tại Nghị định này và Phiếu chuyển thông tin do cơ quan có chức năng quản lý đất đai và các cơ quan khác chuyển đến, thực hiện tính tiền sử dụng đất, tiền thuê đất (bao gồm cả tiền thuê đất có mặt nước, tiền thuê đất để xây dựng công trình ngầm, công trình ngầm nằm ngoài phần không gian sử dụng đất theo quy định tại khoản 3 Điều 27 Nghị định này); tiền đất trước khi chuyển mục đích sử dụng đất theo quy định tại Điều 7, Điều 8, Điều 34; khoản tiền bổ sung theo quy định tại Điều 15, khoản 4 Điều 30, khoản 2 Điều 50, khoản 9 Điều 51; số tiền sử dụng đất, tiền thuê đất được miễn, giảm phải thu hồi theo quy định tại Điều 17, Điều 38 Nghị định này; số tiền sử dụng đất, tiền thuê đất được giảm và thông báo cho người sử dụng đất theo quy định tại Nghị định này.”
+CHUYỂN TIẾP: Điều 3. Điều khoản chuyển tiếp
+1. Việc xử lý chuyển tiếp đối với các trường hợp đã có quyết định giá đất để tính thu tiền sử dụng đất, tiền thuê đất và khoản tiền nộp bổ sung theo quy định tại khoản 2 Điều 257 Luật Đất đai năm 2024, khoản 1, khoản 2 Điều 50, khoản 7, khoản 9 Điều 51 Nghị định số 103/2024/NĐ-CP từ ngày 01 tháng 8 năm 2024 đến trước ngày Nghị định này có hiệu lực thi hành được thực hiện như sau:
+a) Trường hợp người sử dụng đất đã nộp khoản thu bổ sung theo quy định tại khoản 1 Điều 9, khoản 1, khoản 2 Điều 50, khoản 7, khoản 9 Điều 51 Nghị định số 103/2024/NĐ-CP thì được tính lại khoản tiền nộp bổ sung theo quy định tại Nghị định này. Trường hợp phát sinh chênh lệch tăng giữa số tiền tính lại và số tiền đã nộp thì người sử dụng đất phải nộp thêm số tiền chênh lệch. Trường hợp khoản tiền nộp bổ sung sau khi tính lại nhỏ hơn so với số tiền đã nộp thì người sử dụng đất được Nhà nước hoàn trả bằng cách trừ vào nghĩa vụ tiền sử dụng đất, tiền thuê đất; trường hợp không phát sinh nghĩa vụ tiền sử dụng đất, tiền thuê đất thì trừ vào nghĩa vụ tài chính khác theo quy định của pháp luật về quản lý thuế; trường hợp không còn nghĩa vụ tài chính nào khác để trừ thì hoàn trả bằng tiền theo quy định của pháp luật về ngân sách nhà nước hoặc pháp luật khác có liên quan.
+b) Trường hợp cơ quan thuế đã tính và thông báo số tiền phải nộp bổ sung theo quy định tại khoản 1 Điều 9, khoản 1, khoản 2 Điều 50, khoản 7, khoản 9 Điều 51 Nghị định số 103/2024/NĐ-CP nhưng đến ngày Nghị định này có hiệu lực thi hành người sử dụng đất chưa nộp khoản thu bổ sung theo thông báo của cơ quan thuế thì thực hiện tính lại khoản tiền nộp bổ sung theo quy định tại Nghị định này và điều chỉnh Thông báo số tiền phải nộp bổ sung theo quy định của pháp luật về quản lý thuế. Người sử dụng đất phải nộp khoản tiền chậm nộp khoản thu bổ sung (nếu có) theo quy định của pháp luật về quản lý thuế.
+2. Trường hợp thời gian ổn định đơn giá thuê đất tiếp theo của dự án trong khoảng thời gian từ ngày 01 tháng 8 năm 2024 đến ngày Nghị định này có hiệu lực thi hành và cơ quan nhà nước có thẩm quyền đã điều chỉnh đơn giá thuê đất theo quy định tại khoản 10, khoản 11 Điều 51 Nghị định số 103/2024/NĐ-CP thì kể từ ngày Nghị định này có hiệu lực thi hành, người sử dụng đất được tính lại tiền thuê đất theo nguyên tắc điều chỉnh đơn giá thuê đất theo quy định tại khoản 10a Điều 51 Nghị định số 103/2024/NĐ-CP (được bổ sung theo quy định tại khoản 28 Điều 1 Nghị định này); trường hợp số tiền thuê đất đã nộp của năm 2024 và năm 2025 (nếu có) cao hơn số tiền thuê đất tính lại thì được Nhà nước hoàn trả bằng cách trừ vào nghĩa vụ tiền thuê đất; trường hợp không phát sinh nghĩa vụ tiền thuê đất thì trừ vào nghĩa vụ tài chính khác theo quy định của pháp luật về quản lý thuế; trường hợp không còn nghĩa vụ tài chính nào khác để trừ thì hoàn trả bằng tiền theo quy định của pháp luật về ngân sách nhà nước hoặc pháp luật khác có liên quan.
+3. Trường hợp dự án đầu tư có nhiều hình thức sử dụng đất (giao đất không thu tiền sử dụng đất, giao đất có thu tiền sử dụng đất, cho thuê đất) hoặc dự án có hình thức thuê đất trả tiền hằng năm và thuê đất trả tiền một lần cho cả thời gian thuê, nếu người thực hiện dự án đầu tư đã tự nguyện ứng trước kinh phí bồi thường, hỗ trợ, tái định cư theo phương án được cơ quan nhà nước có thẩm quyền phê duyệt theo quy định của pháp luật về đất đai trước ngày Nghị định này có hiệu lực thi hành nhưng đến ngày Nghị định này có hiệu lực thi hành chưa được trừ (hoặc chưa trừ hết) kinh phí bồi thường, hỗ trợ, tái định cư vào tiền sử dụng đất, tiền thuê đất phải nộp và người sử dụng đất chưa hoàn thành nghĩa vụ về tiền sử dụng đất, tiền thuê đất thì được thực hiện khấu trừ kinh phí bồi thường, hỗ trợ, tái định cư theo quy định tại khoản 4, điểm l khoản 22 Điều 1 Nghị định này.
+1. Việc xử lý chuyển tiếp đối với các trường hợp đã có quyết định giá đất để tính thu tiền sử dụng đất, tiền thuê đất và khoản tiền nộp bổ sung theo quy định tại khoản 2 Điều 257 Luật Đất đai năm 2024, khoản 1, khoản 2 Điều 50, khoản 7, khoản 9 Điều 51 Nghị định số 103/2024/NĐ-CP từ ngày 01 tháng 8 năm 2024 đến trước ngày Nghị định này có hiệu lực thi hành được thực hiện như sau:
+a) Trường hợp người sử dụng đất đã nộp khoản thu bổ sung theo quy định tại khoản 1 Điều 9, khoản 1, khoản 2 Điều 50, khoản 7, khoản 9 Điều 51 Nghị định số 103/2024/NĐ-CP thì được tính lại khoản tiền nộp bổ sung theo quy định tại Nghị định này. Trường hợp phát sinh chênh lệch tăng giữa số tiền tính lại và số tiền đã nộp thì người sử dụng đất phải nộp thêm số tiền chênh lệch. Trường hợp khoản tiền nộp bổ sung sau khi tính lại nhỏ hơn so với số tiền đã nộp thì người sử dụng đất được Nhà nước hoàn trả bằng cách trừ vào nghĩa vụ tiền sử dụng đất, tiền thuê đất; trường hợp không phát sinh nghĩa vụ tiền sử dụng đất, tiền thuê đất thì trừ vào nghĩa vụ tài chính khác theo quy định của pháp luật về quản lý thuế; trường hợp không còn nghĩa vụ tài chính nào khác để trừ thì hoàn trả bằng tiền theo quy định của pháp luật về ngân sách nhà nước hoặc pháp luật khác có liên quan.
+b) Trường hợp cơ quan thuế đã tính và thông báo số</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -679,7 +729,6 @@
           <t>actor_has_transitional</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -690,18 +739,39 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
           <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Nếu cơ quan thuế nhận được thông tin về thửa đất phải nộp tiền sử dụng đất, thì cơ quan thuế xác định và thông báo số tiền phải nộp dựa trên phiếu chuyển thông tin từ những cơ quan nào?»; nhãn cũ khong_dat group_mismatch: Câu hỏi hỏi phiếu chuyển thông tin đến từ cơ quan nào: mốc 1 và 2 như nhau (cơ quan quản lý đất đai và các cơ quan khác); lần sửa 2025 chỉ mở rộng các khoản tiền phải tính. Chỉ hai đáp án). Hỏi cả khoản tiền phải tính và nguồn phiếu: mốc 1–2 khác về khoản tiền, mốc 3 khác về cơ quan chuyển phiếu; ba đáp án; id cũ vilextime:T3:provision:054aaf90-3188-11f1-9b71-9161173b0ca7:2025-11-07 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
+      <c r="X3" s="2" t="inlineStr">
+        <is>
+          <t>103/2024/NĐ-CP · hiệu lực 2024-08-01 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 44. Trách nhiệm của cơ quan và người sử dụng đất
+3. Cơ quan thuế:
+a) Căn cứ quy định tại Nghị định này và Phiếu chuyển thông tin do cơ quan có chức năng quản lý đất đai và các cơ quan khác chuyển đến để tính tiền sử dụng đất, tiền thuê đất, tiền thuê đất có mặt nước, tiền thuê đất để xây dựng công trình ngầm, công trình ngầm nằm ngoài phần không gian sử dụng đất theo quy định tại khoản 3 Điều 27 Nghị định này, số tiền sử dụng đất, tiền thuê đất được giảm và thông báo cho người sử dụng đất theo quy định tại Nghị định này.
+b) Tổ chức thực hiện, hướng dẫn, giải đáp vướng mắc, giải quyết khiếu nại về tính, thu, nộp tiền sử dụng đất, tiền thuê đất theo quy định tại Nghị định này, pháp luật về quản lý thuế và pháp luật khác có liên quan.
+c) Xác định đơn giá thuê đất trả tiền thuê đất hàng năm, đơn giá thuê đất trả tiền thuê đất một lần cho cả thời gian thuê quy định tại Điều 26 Nghị định này.
+d) Rà soát các trường hợp đã ghi nợ nhưng đến nay chưa hoàn thành việc trả nợ để thông báo đến các trường hợp còn nợ tiền sử dụng đất về việc ghi nợ, thanh toán nợ và xóa nợ tiền sử dụng đất theo đúng quy định tại Nghị định này.
+đ) Thực hiện các nhiệm vụ khác theo quy định tại Nghị định này và pháp luật khác có liên quan.</t>
+        </is>
+      </c>
+      <c r="Y3" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 291/2025/NĐ-CP · hiệu lực 2025-11-06
+b) Sửa đổi, bổ sung điểm a khoản 3 như sau:
+“a) Căn cứ quy định tại Nghị định này và Phiếu chuyển thông tin do cơ quan có chức năng quản lý đất đai và các cơ quan khác chuyển đến, thực hiện tính tiền sử dụng đất, tiền thuê đất (bao gồm cả tiền thuê đất có mặt nước, tiền thuê đất để xây dựng công trình ngầm, công trình ngầm nằm ngoài phần không gian sử dụng đất theo quy định tại khoản 3 Điều 27 Nghị định này); tiền đất trước khi chuyển mục đích sử dụng đất theo quy định tại Điều 7, Điều 8, Điều 34; khoản tiền bổ sung theo quy định tại Điều 15, khoản 4 Điều 30, khoản 2 Điều 50, khoản 9 Điều 51; số tiền sử dụng đất, tiền thuê đất được miễn, giảm phải thu hồi theo quy định tại Điều 17, Điều 38 Nghị định này; số tiền sử dụng đất, tiền thuê đất được giảm và thông báo cho người sử dụng đất theo quy định tại Nghị định này.”
+CHUYỂN TIẾP: Điều 3. Điều khoản chuyển tiếp
+1. Việc xử lý chuyển tiếp đối với các trường hợp đã có quyết định giá đất để tính thu tiền sử dụng đất, tiền thuê đất và khoản tiền nộp bổ sung theo quy định tại khoản 2 Điều 257 Luật Đất đai năm 2024, khoản 1, khoản 2 Điều 50, khoản 7, khoản 9 Điều 51 Nghị định số 103/2024/NĐ-CP từ ngày 01 tháng 8 năm 2024 đến trước ngày Nghị định này có hiệu lực thi hành được thực hiện như sau:
+a) Trường hợp người sử dụng đất đã nộp khoản thu bổ sung theo quy định tại khoản 1 Điều 9, khoản 1, khoản 2 Điều 50, khoản 7, khoản 9 Điều 51 Nghị định số 103/2024/NĐ-CP thì được tính lại khoản tiền nộp bổ sung theo quy định tại Nghị định này. Trường hợp phát sinh chênh lệch tăng giữa số tiền tính lại và số tiền đã nộp thì người sử dụng đất phải nộp thêm số tiền chênh lệch. Trường hợp khoản tiền nộp bổ sung sau khi tính lại nhỏ hơn so với số tiền đã nộp thì người sử dụng đất được Nhà nước hoàn trả bằng cách trừ vào nghĩa vụ tiền sử dụng đất, tiền thuê đất; trường hợp không phát sinh nghĩa vụ tiền sử dụng đất, tiền thuê đất thì trừ vào nghĩa vụ tài chính khác theo quy định của pháp luật về quản lý thuế; trường hợp không còn nghĩa vụ tài chính nào khác để trừ thì hoàn trả bằng tiền theo quy định của pháp luật về ngân sách nhà nước hoặc pháp luật khác có liên quan.
+b) Trường hợp cơ quan thuế đã tính và thông báo số tiền phải nộp bổ sung theo quy định tại khoản 1 Điều 9, khoản 1, khoản 2 Điều 50, khoản 7, khoản 9 Điều 51 Nghị định số 103/2024/NĐ-CP nhưng đến ngày Nghị định này có hiệu lực thi hành người sử dụng đất chưa nộp khoản thu bổ sung theo thông báo của cơ quan thuế thì thực hiện tính lại khoản tiền nộp bổ sung theo quy định tại Nghị định này và điều chỉnh Thông báo số tiền phải nộp bổ sung theo quy định của pháp luật về quản lý thuế. Người sử dụng đất phải nộp khoản tiền chậm nộp khoản thu bổ sung (nếu có) theo quy định của pháp luật về quản lý thuế.
+2. Trường hợp thời gian ổn định đơn giá thuê đất tiếp theo của dự án trong khoảng thời gian từ ngày 01 tháng 8 năm 2024 đến ngày Nghị định này có hiệu lực thi hành và cơ quan nhà nước có thẩm quyền đã điều chỉnh đơn giá thuê đất theo quy định tại khoản 10, khoản 11 Điều 51 Nghị định số 103/2024/NĐ-CP thì kể từ ngày Nghị định này có hiệu lực thi hành, người sử dụng đất được tính lại tiền thuê đất theo nguyên tắc điều chỉnh đơn giá thuê đất theo quy định tại khoản 10a Điều 51 Nghị định số 103/2024/NĐ-CP (được bổ sung theo quy định tại khoản 28 Điều 1 Nghị định này); trường hợp số tiền thuê đất đã nộp của năm 2024 và năm 2025 (nếu có) cao hơn số tiền thuê đất tính lại thì được Nhà nước hoàn trả bằng cách trừ vào nghĩa vụ tiền thuê đất; trường hợp không phát sinh nghĩa vụ tiền thuê đất thì trừ vào nghĩa vụ tài chính khác theo quy định của pháp luật về quản lý thuế; trường hợp không còn nghĩa vụ tài chính nào khác để trừ thì hoàn trả bằng tiền theo quy định của pháp luật về ngân sách nhà nước hoặc pháp luật khác có liên quan.
+3. Trường hợp dự án đầu tư có nhiều hình thức sử dụng đất (giao đất không thu tiền sử dụng đất, giao đất có thu tiền sử dụng đất, cho thuê đất) hoặc dự án có hình thức thuê đất trả tiền hằng năm và thuê đất trả tiền một lần cho cả thời gian thuê, nếu người thực hiện dự án đầu tư đã tự nguyện ứng trước kinh phí bồi thường, hỗ trợ, tái định cư theo phương án được cơ quan nhà nước có thẩm quyền phê duyệt theo quy định của pháp luật về đất đai trước ngày Nghị định này có hiệu lực thi hành nhưng đến ngày Nghị định này có hiệu lực thi hành chưa được trừ (hoặc chưa trừ hết) kinh phí bồi thường, hỗ trợ, tái định cư vào tiền sử dụng đất, tiền thuê đất phải nộp và người sử dụng đất chưa hoàn thành nghĩa vụ về tiền sử dụng đất, tiền thuê đất thì được thực hiện khấu trừ kinh phí bồi thường, hỗ trợ, tái định cư theo quy định tại khoản 4, điểm l khoản 22 Điều 1 Nghị định này.
+1. Việc xử lý chuyển tiếp đối với các trường hợp đã có quyết định giá đất để tính thu tiền sử dụng đất, tiền thuê đất và khoản tiền nộp bổ sung theo quy định tại khoản 2 Điều 257 Luật Đất đai năm 2024, khoản 1, khoản 2 Điều 50, khoản 7, khoản 9 Điều 51 Nghị định số 103/2024/NĐ-CP từ ngày 01 tháng 8 năm 2024 đến trước ngày Nghị định này có hiệu lực thi hành được thực hiện như sau:
+a) Trường hợp người sử dụng đất đã nộp khoản thu bổ sung theo quy định tại khoản 1 Điều 9, khoản 1, khoản 2 Điều 50, khoản 7, khoản 9 Điều 51 Nghị định số 103/2024/NĐ-CP thì được tính lại khoản tiền nộp bổ sung theo quy định tại Nghị định này. Trường hợp phát sinh chênh lệch tăng giữa số tiền tính lại và số tiền đã nộp thì người sử dụng đất phải nộp thêm số tiền chênh lệch. Trường hợp khoản tiền nộp bổ sung sau khi tính lại nhỏ hơn so với số tiền đã nộp thì người sử dụng đất được Nhà nước hoàn trả bằng cách trừ vào nghĩa vụ tiền sử dụng đất, tiền thuê đất; trường hợp không phát sinh nghĩa vụ tiền sử dụng đất, tiền thuê đất thì trừ vào nghĩa vụ tài chính khác theo quy định của pháp luật về quản lý thuế; trường hợp không còn nghĩa vụ tài chính nào khác để trừ thì hoàn trả bằng tiền theo quy định của pháp luật về ngân sách nhà nước hoặc pháp luật khác có liên quan.
+b) Trường hợp cơ quan thuế đã tính và thông báo số</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -764,7 +834,6 @@
           <t>actor_has_transitional</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -775,18 +844,39 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
           <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Nếu cơ quan thuế nhận được thông tin về thửa đất phải nộp tiền sử dụng đất, thì cơ quan thuế xác định và thông báo số tiền phải nộp dựa trên phiếu chuyển thông tin từ những cơ quan nào?»; nhãn cũ khong_dat group_mismatch: Câu hỏi hỏi phiếu chuyển thông tin đến từ cơ quan nào: mốc 1 và 2 như nhau (cơ quan quản lý đất đai và các cơ quan khác); lần sửa 2025 chỉ mở rộng các khoản tiền phải tính. Chỉ hai đáp án). Hỏi cả khoản tiền phải tính và nguồn phiếu: mốc 1–2 khác về khoản tiền, mốc 3 khác về cơ quan chuyển phiếu; ba đáp án; id cũ vilextime:T3:provision:054aaf90-3188-11f1-9b71-9161173b0ca7:2026-02-01 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
+      <c r="X4" s="2" t="inlineStr">
+        <is>
+          <t>103/2024/NĐ-CP · hiệu lực 2024-08-01 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 44. Trách nhiệm của cơ quan và người sử dụng đất
+3. Cơ quan thuế:
+a) Căn cứ quy định tại Nghị định này và Phiếu chuyển thông tin do cơ quan có chức năng quản lý đất đai và các cơ quan khác chuyển đến để tính tiền sử dụng đất, tiền thuê đất, tiền thuê đất có mặt nước, tiền thuê đất để xây dựng công trình ngầm, công trình ngầm nằm ngoài phần không gian sử dụng đất theo quy định tại khoản 3 Điều 27 Nghị định này, số tiền sử dụng đất, tiền thuê đất được giảm và thông báo cho người sử dụng đất theo quy định tại Nghị định này.
+b) Tổ chức thực hiện, hướng dẫn, giải đáp vướng mắc, giải quyết khiếu nại về tính, thu, nộp tiền sử dụng đất, tiền thuê đất theo quy định tại Nghị định này, pháp luật về quản lý thuế và pháp luật khác có liên quan.
+c) Xác định đơn giá thuê đất trả tiền thuê đất hàng năm, đơn giá thuê đất trả tiền thuê đất một lần cho cả thời gian thuê quy định tại Điều 26 Nghị định này.
+d) Rà soát các trường hợp đã ghi nợ nhưng đến nay chưa hoàn thành việc trả nợ để thông báo đến các trường hợp còn nợ tiền sử dụng đất về việc ghi nợ, thanh toán nợ và xóa nợ tiền sử dụng đất theo đúng quy định tại Nghị định này.
+đ) Thực hiện các nhiệm vụ khác theo quy định tại Nghị định này và pháp luật khác có liên quan.</t>
+        </is>
+      </c>
+      <c r="Y4" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 291/2025/NĐ-CP · hiệu lực 2025-11-06
+b) Sửa đổi, bổ sung điểm a khoản 3 như sau:
+“a) Căn cứ quy định tại Nghị định này và Phiếu chuyển thông tin do cơ quan có chức năng quản lý đất đai và các cơ quan khác chuyển đến, thực hiện tính tiền sử dụng đất, tiền thuê đất (bao gồm cả tiền thuê đất có mặt nước, tiền thuê đất để xây dựng công trình ngầm, công trình ngầm nằm ngoài phần không gian sử dụng đất theo quy định tại khoản 3 Điều 27 Nghị định này); tiền đất trước khi chuyển mục đích sử dụng đất theo quy định tại Điều 7, Điều 8, Điều 34; khoản tiền bổ sung theo quy định tại Điều 15, khoản 4 Điều 30, khoản 2 Điều 50, khoản 9 Điều 51; số tiền sử dụng đất, tiền thuê đất được miễn, giảm phải thu hồi theo quy định tại Điều 17, Điều 38 Nghị định này; số tiền sử dụng đất, tiền thuê đất được giảm và thông báo cho người sử dụng đất theo quy định tại Nghị định này.”
+CHUYỂN TIẾP: Điều 3. Điều khoản chuyển tiếp
+1. Việc xử lý chuyển tiếp đối với các trường hợp đã có quyết định giá đất để tính thu tiền sử dụng đất, tiền thuê đất và khoản tiền nộp bổ sung theo quy định tại khoản 2 Điều 257 Luật Đất đai năm 2024, khoản 1, khoản 2 Điều 50, khoản 7, khoản 9 Điều 51 Nghị định số 103/2024/NĐ-CP từ ngày 01 tháng 8 năm 2024 đến trước ngày Nghị định này có hiệu lực thi hành được thực hiện như sau:
+a) Trường hợp người sử dụng đất đã nộp khoản thu bổ sung theo quy định tại khoản 1 Điều 9, khoản 1, khoản 2 Điều 50, khoản 7, khoản 9 Điều 51 Nghị định số 103/2024/NĐ-CP thì được tính lại khoản tiền nộp bổ sung theo quy định tại Nghị định này. Trường hợp phát sinh chênh lệch tăng giữa số tiền tính lại và số tiền đã nộp thì người sử dụng đất phải nộp thêm số tiền chênh lệch. Trường hợp khoản tiền nộp bổ sung sau khi tính lại nhỏ hơn so với số tiền đã nộp thì người sử dụng đất được Nhà nước hoàn trả bằng cách trừ vào nghĩa vụ tiền sử dụng đất, tiền thuê đất; trường hợp không phát sinh nghĩa vụ tiền sử dụng đất, tiền thuê đất thì trừ vào nghĩa vụ tài chính khác theo quy định của pháp luật về quản lý thuế; trường hợp không còn nghĩa vụ tài chính nào khác để trừ thì hoàn trả bằng tiền theo quy định của pháp luật về ngân sách nhà nước hoặc pháp luật khác có liên quan.
+b) Trường hợp cơ quan thuế đã tính và thông báo số tiền phải nộp bổ sung theo quy định tại khoản 1 Điều 9, khoản 1, khoản 2 Điều 50, khoản 7, khoản 9 Điều 51 Nghị định số 103/2024/NĐ-CP nhưng đến ngày Nghị định này có hiệu lực thi hành người sử dụng đất chưa nộp khoản thu bổ sung theo thông báo của cơ quan thuế thì thực hiện tính lại khoản tiền nộp bổ sung theo quy định tại Nghị định này và điều chỉnh Thông báo số tiền phải nộp bổ sung theo quy định của pháp luật về quản lý thuế. Người sử dụng đất phải nộp khoản tiền chậm nộp khoản thu bổ sung (nếu có) theo quy định của pháp luật về quản lý thuế.
+2. Trường hợp thời gian ổn định đơn giá thuê đất tiếp theo của dự án trong khoảng thời gian từ ngày 01 tháng 8 năm 2024 đến ngày Nghị định này có hiệu lực thi hành và cơ quan nhà nước có thẩm quyền đã điều chỉnh đơn giá thuê đất theo quy định tại khoản 10, khoản 11 Điều 51 Nghị định số 103/2024/NĐ-CP thì kể từ ngày Nghị định này có hiệu lực thi hành, người sử dụng đất được tính lại tiền thuê đất theo nguyên tắc điều chỉnh đơn giá thuê đất theo quy định tại khoản 10a Điều 51 Nghị định số 103/2024/NĐ-CP (được bổ sung theo quy định tại khoản 28 Điều 1 Nghị định này); trường hợp số tiền thuê đất đã nộp của năm 2024 và năm 2025 (nếu có) cao hơn số tiền thuê đất tính lại thì được Nhà nước hoàn trả bằng cách trừ vào nghĩa vụ tiền thuê đất; trường hợp không phát sinh nghĩa vụ tiền thuê đất thì trừ vào nghĩa vụ tài chính khác theo quy định của pháp luật về quản lý thuế; trường hợp không còn nghĩa vụ tài chính nào khác để trừ thì hoàn trả bằng tiền theo quy định của pháp luật về ngân sách nhà nước hoặc pháp luật khác có liên quan.
+3. Trường hợp dự án đầu tư có nhiều hình thức sử dụng đất (giao đất không thu tiền sử dụng đất, giao đất có thu tiền sử dụng đất, cho thuê đất) hoặc dự án có hình thức thuê đất trả tiền hằng năm và thuê đất trả tiền một lần cho cả thời gian thuê, nếu người thực hiện dự án đầu tư đã tự nguyện ứng trước kinh phí bồi thường, hỗ trợ, tái định cư theo phương án được cơ quan nhà nước có thẩm quyền phê duyệt theo quy định của pháp luật về đất đai trước ngày Nghị định này có hiệu lực thi hành nhưng đến ngày Nghị định này có hiệu lực thi hành chưa được trừ (hoặc chưa trừ hết) kinh phí bồi thường, hỗ trợ, tái định cư vào tiền sử dụng đất, tiền thuê đất phải nộp và người sử dụng đất chưa hoàn thành nghĩa vụ về tiền sử dụng đất, tiền thuê đất thì được thực hiện khấu trừ kinh phí bồi thường, hỗ trợ, tái định cư theo quy định tại khoản 4, điểm l khoản 22 Điều 1 Nghị định này.
+1. Việc xử lý chuyển tiếp đối với các trường hợp đã có quyết định giá đất để tính thu tiền sử dụng đất, tiền thuê đất và khoản tiền nộp bổ sung theo quy định tại khoản 2 Điều 257 Luật Đất đai năm 2024, khoản 1, khoản 2 Điều 50, khoản 7, khoản 9 Điều 51 Nghị định số 103/2024/NĐ-CP từ ngày 01 tháng 8 năm 2024 đến trước ngày Nghị định này có hiệu lực thi hành được thực hiện như sau:
+a) Trường hợp người sử dụng đất đã nộp khoản thu bổ sung theo quy định tại khoản 1 Điều 9, khoản 1, khoản 2 Điều 50, khoản 7, khoản 9 Điều 51 Nghị định số 103/2024/NĐ-CP thì được tính lại khoản tiền nộp bổ sung theo quy định tại Nghị định này. Trường hợp phát sinh chênh lệch tăng giữa số tiền tính lại và số tiền đã nộp thì người sử dụng đất phải nộp thêm số tiền chênh lệch. Trường hợp khoản tiền nộp bổ sung sau khi tính lại nhỏ hơn so với số tiền đã nộp thì người sử dụng đất được Nhà nước hoàn trả bằng cách trừ vào nghĩa vụ tiền sử dụng đất, tiền thuê đất; trường hợp không phát sinh nghĩa vụ tiền sử dụng đất, tiền thuê đất thì trừ vào nghĩa vụ tài chính khác theo quy định của pháp luật về quản lý thuế; trường hợp không còn nghĩa vụ tài chính nào khác để trừ thì hoàn trả bằng tiền theo quy định của pháp luật về ngân sách nhà nước hoặc pháp luật khác có liên quan.
+b) Trường hợp cơ quan thuế đã tính và thông báo số</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -849,7 +939,6 @@
           <t>actor_has_transitional, split_effective_date</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -860,18 +949,59 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
           <t>id cũ vilextime:T3:provision:11c19b26-e183-11f0-a1fe-6192bcf0213f#k4#g:2019-09-02 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
+      <c r="X5" s="2" t="inlineStr">
+        <is>
+          <t>32/2018/TT-BYT · hiệu lực 2019-09-01 → 2022-10-20 · lúc thu thập: Hết hiệu lực toàn bộ
+Điều 23. Quy định đối với các tài liệu trong hồ sơ đề nghị cấp, gia hạn, thay đổi, bổ sung giấy đăng ký lưu hành thuốc, nguyên liệu làm thuốc
+4. Quy định đối với CPP:
+a) CPP phải có chữ ký, tên người ký, ngày cấp và dấu của cơ quan cấp CPP;
+b) CPP phải được cấp bởi cơ quan quản lý về dược phẩm có thẩm quyền cấp quốc gia.
+Trường hợp CPP được cấp bởi cơ quan quản lý dược phẩm nhưng không phải là cơ quan quản lý dược phẩm cấp quốc gia: Cơ sở đăng ký thuốc phải cung cấp tài liệu pháp lý chứng minh cơ quan này là cơ quan có thẩm quyền và cơ quan quản lý dược phẩm quốc gia tại nước đó không thực hiện việc cấp CPP theo quy định của pháp luật nước sở tại.
+Trường hợp CPP được cấp bởi cơ quan không phải cơ quan quản lý dược phẩm: Cơ sở đăng ký thuốc phải cung cấp tài liệu chứng minh cơ quan này là cơ quan có thẩm quyền và cơ quan quản lý dược phẩm tại nước đó không thực hiện việc cấp CPP theo quy định của pháp luật nước sở tại.
+c) Chữ ký, tên người ký và dấu của cơ quan cấp CPP phải được chứng thực bởi cơ quan có thẩm quyền; Trường hợp nội dung xác nhận này không được thể hiện bằng tiếng Anh thì phải dịch công chứng sang tiếng Việt hoặc tiếng Anh;
+d) Nội dung của CPP phải có đầy đủ thông tin theo quy định tại Mẫu 7/TT ban hành kèm theo Thông tư này và các nội dung sau:
+- Công thức bào chế của thuốc, trong đó nêu rõ tên, thành phần, nồng độ, hàm lượng của từng dược chất, dược liệu, tá dược; đối với dạng bào chế viên nang mềm, viên nang cứng phải có thêm thông tin về thành phần công thức của vỏ nang;
+- Tiêu chuẩn thành phẩm, tiêu chuẩn dược chất, dược liệu, tên, địa chỉ cơ sở sản xuất dược chất, dược liệu;
+- Trường hợp thuốc có sự tham gia sản xuất bởi nhiều cơ sở sản xuất khác nhau thì CPP phải ghi rõ tên, địa chỉ, vai trò của từng cơ sở;
+- Trường hợp CPP không có thông tin cơ sở sản xuất thuốc đáp ứng thực hành tốt sản xuất thuốc (GMP), cơ sở đăng ký phải nộp kèm giấy chứng nhận GMP của tất cả các cơ sở sản xuất đáp ứng quy định tại khoản 1, 2, 3 Điều này;
+- Các phụ lục kèm theo CPP (nếu có) phải có xác nhận của cơ quan cấp CPP.
+đ) Đối với thuốc generic, thuốc dược liệu, sinh phẩm probiotics (men tiêu hóa), thuốc gia hạn, thay đổi, bổ sung giấy đăng ký lưu hành: CPP xác nhận thuốc được cấp phép và lưu hành ở nước sản xuất. Trường hợp thuốc không được cấp phép lưu hành ở nước sản xuất hoặc được cấp phép nhưng không lưu hành thực tế ở nước sản xuất, cơ sở đăng ký phải cung cấp CPP có xác nhận thuốc được cấp phép và lưu hành ở một trong các nước quy định tại khoản 10 Điều 2 Thông tư này;
+e) Đối với thuốc hóa dược mới và sinh phẩm nhập khẩu, trừ sinh phẩm probiotics (men tiêu hóa): CPP được cấp bởi nước sản xuất và CPP được cấp bởi một trong các cơ quan quản lý khác quy định tại khoản 10 Điều 2 Thông tư này có xác nhận thuốc được cấp phép và lưu hành thực tế;
+g) Đối với vắc xin nhập khẩu: CPP được cấp bởi nước sản xuất và CPP được cấp bởi một trong các cơ quan quản lý khác quy định tại khoản 9 Điều 2 Thông tư này có xác nhận vắc xin được cấp phép và lưu hành thực tế;
+h) Đối với thuốc generic có báo cáo nghiên cứu tương đương sinh học: CPP được cấp bởi một trong các cơ quan quản lý quy định tại khoản 10 Điều 2 Thông tư này có xác nhận thuốc được cấp phép và lưu hành thực tế;
+Trường hợp không có CPP đáp ứng quy định này, phải có báo cáo nghiên cứu tương đương sinh học của thuốc được thực hiện tại cơ sở kinh doanh dịch vụ thử tương đương sinh học của thuốc tại Việt Nam hoặc tại các cơ sở thử tương tương sinh học mà Việt Nam công nhận theo quy định của Bộ trưởng Bộ Y tế hoặc theo các thỏa thuận quốc tế mà Việt Nam đã tham gia ký kết.
+i) Đối với thuốc đề nghị được phân loại biệt dược gốc, CPP được cấp bởi một trong các cơ quan quản lý quy định tại khoản 9, 10 Điều 2 Thông tư này, trừ thuốc sản xuất tại Việt Nam;
+k) Đối với thuốc, vắc xin, sinh phẩm nhập khẩu không cung cấp được CPP đáp ứng quy định tại điểm đ, e, g, h khoản này, Bộ trưởng Bộ Y tế xem xét quyết định trên cơ sở ý kiến tư vấn của Hội đồng tư vấn cấp giấy đăng ký lưu hành thuốc, nguyên liệu làm thuốc khi thuốc được cấp phép lưu hành bởi ít nhất một cơ quan quản lý trên thế giới và thuộc một trong các trường hợp sau:
+- Thuốc, vắc xin, sinh phẩm để đáp ứng nhu cầu cho quốc phòng, an ninh; phòng, chống dịch, bệnh, khắc phục hậu quả thiên tai, thảm họa, thuốc phục vụ cho chương trình y tế của nhà nước;
+- Vắc xin dùng cho chương trình tiêm chủng mở rộng quốc gia mà trên thị trường không sẵn có vắc xin khác có khả năng thay thế về mặt số lượng, chất lượng, an toàn, hiệu quả hoặc chi phí sử dụng vắc xin;
+- Các trường hợp đặc biệt khác có văn bản thỏa thuận, công nhận lẫn nhau giữa các cơ quan quản lý Nhà nước về Dược về điều kiện sản xuất, lưu hành thuốc, vắc xin, sinh phẩm.
+l) Các thông tin thể hiện trên CPP phải thống nhất với các thông tin có liên quan trong hồ sơ đăng ký thuốc.</t>
+        </is>
+      </c>
+      <c r="Y5" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 29/2020/TT-BYT · hiệu lực 2021-02-15
+c) Sửa đổi, bổ sung các điểm e, g khoản 4 Điều 23 như sau:
+“e) Đối với hồ sơ cấp giấy đăng ký lưu hành thuốc hóa dược mới, sinh phẩm nhập khẩu, trừ sinh phẩm probiotics (men tiêu hóa): phải có CPP được cấp bởi cơ quan có thẩm quyền của nước sản xuất có xác nhận thuốc được cấp phép và lưu hành thực tế tại nước đó. Trường hợp CPP này không được cấp bởi EMA thì phải có thêm giấy tờ pháp lý được cấp bởi một trong các cơ quan quản lý khác quy định tại khoản 9 hoặc khoản 10 Điều 2 Thông tư này. Giấy tờ pháp lý bao gồm nội dung tối thiểu sau: tên thuốc, hoạt chất, nồng độ hoặc hàm lượng hoạt chất, dạng bào chế, tên và địa chỉ cơ sở sản xuất, có xác nhận thuốc được cấp phép và lưu hành thực tế tại nước đó;
+g) Đối với hồ sơ cấp giấy đăng ký lưu hành vắc xin nhập khẩu: phải có CPP được cấp bởi cơ quan có thẩm quyền của nước sản xuất có xác nhận thuốc được cấp phép và lưu hành thực tế tại nước đó. Trường hợp CPP này không được cấp bởi EMA thì phải có thêm giấy tờ pháp lý được cấp bởi một trong các cơ quan quản lý khác quy định tại khoản 9 Điều 2 Thông tư này. Giấy tờ pháp lý bao gồm nội dung tối thiểu sau: tên thuốc, hoạt chất, nồng độ hoặc hàm lượng hoạt chất, dạng bào chế, tên và địa chỉ cơ sở sản xuất, có xác nhận thuốc được cấp phép và lưu hành thực tế tại nước đó.”;
+CHUYỂN TIẾP: Điều 4. Quy định chuyển tiếp
+1. Các hồ sơ đã nộp cho cơ quan tiếp nhận hồ sơ trước ngày Thông tư này có hiệu lực nhưng đang trong quá trình giải quyết được áp dụng theo quy định có liên quan tại Thông tư này hoặc các quy định trước ngày Thông tư này có hiệu lực theo hướng thuận tiện cho doanh nghiệp, tổ chức, cá nhân.
+2. Các quy định về công bố thông tin, cập nhật, khai báo và báo cáo theo hình thức trực tuyến tại Thông tư này được áp dụng theo triển khai của cơ quan nhà nước có thẩm quyền.
+[amend] 23/2021/TT-BYT · hiệu lực 2022-01-25
+a) Sửa đổi, bổ sung các điểm e, g khoản 4 Điều 23 như sau:
+"e) Đối với hồ sơ cấp giấy đăng ký lưu hành thuốc hóa dược mới, sinh phẩm nhập khẩu, trừ sinh phẩm probiotics (men tiêu hóa):
+Phải có CPP được cấp bởi cơ quan quản lý có thẩm quyền của nước sản xuất có xác nhận thuốc được cấp phép và lưu hành thực tế tại nước đó. Trường hợp CPP này không được cấp bởi EMA thì phải có thêm giấy tờ pháp lý được cấp bởi cơ quan quản lý có thẩm quyền của nước thứ hai xác nhận thuốc được cấp phép và lưu hành thực tế tại nước đó với các nội dung tối thiểu về: tên thuốc, hoạt chất, nồng độ hoặc hàm lượng hoạt chất, dạng bào chế, tên và địa chỉ cơ sở sản xuất. Cơ quan quản lý có thẩm quyền của nước sản xuất cấp CPP hoặc cơ quan có thẩm quyền của nước thứ hai cấp giấy tờ pháp lý xác nhận thuốc được cấp phép và lưu hành thực tế tại nước đó phải thuộc một trong các cơ quan quản lý quy định tại khoản 9 hoặc khoản 10 Điều 2 Thông tư này;
+g) Đối với hồ sơ cấp giấy đăng ký lưu hành vắc xin nhập khẩu:
+Phải có CPP được cấp bởi cơ quan quản lý có thẩm quyền của nước sản xuất có xác nhận vắc xin được cấp phép và lưu hành thực tế tại nước đó. Trường hợp CPP này không được cấp bởi EMA thì phải có thêm giấy tờ pháp lý được cấp bởi cơ quan quản lý có thẩm quyền của nước thứ hai xác nhận vắc xin được cấp phép và lưu hành thực tế tại nước đó với các nội dung tối thiểu về: tên vắc xin, hoạt chất, nồng độ hoặc hàm lượng hoạt chất, dạng bào chế, tên và địa chỉ cơ sở sản xuất. Cơ quan quản lý có thẩm quyền của nước sản xuất cấp CPP hoặc cơ quan có thẩm quyền của nước thứ hai cấp giấy tờ pháp lý xác nhận vắc xin được cấp phép và lưu hành thực tế tại nước đó phải thuộc một trong các cơ quan quản lý quy định tại khoản 9 Điều 2 Thông tư này."
+CHUYỂN TIẾP: Điều 3. Điều khoản chuyển tiếp
+Các hồ sơ đã nộp cho cơ quan tiếp nhận hồ sơ trước ngày Thông tư này có hiệu lực nhưng đang trong quá trình giải quyết được áp dụng theo quy định có liên quan tại Thông tư này hoặc các quy định trước ngày Thông tư này có hiệu lực theo hướng thuận tiện cho doanh nghiệp, tổ chức, cá nhân.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -934,7 +1064,6 @@
           <t>actor_has_transitional, split_effective_date</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -945,18 +1074,59 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
           <t>id cũ vilextime:T3:provision:11c19b26-e183-11f0-a1fe-6192bcf0213f#k4#g:2021-02-16 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t>32/2018/TT-BYT · hiệu lực 2019-09-01 → 2022-10-20 · lúc thu thập: Hết hiệu lực toàn bộ
+Điều 23. Quy định đối với các tài liệu trong hồ sơ đề nghị cấp, gia hạn, thay đổi, bổ sung giấy đăng ký lưu hành thuốc, nguyên liệu làm thuốc
+4. Quy định đối với CPP:
+a) CPP phải có chữ ký, tên người ký, ngày cấp và dấu của cơ quan cấp CPP;
+b) CPP phải được cấp bởi cơ quan quản lý về dược phẩm có thẩm quyền cấp quốc gia.
+Trường hợp CPP được cấp bởi cơ quan quản lý dược phẩm nhưng không phải là cơ quan quản lý dược phẩm cấp quốc gia: Cơ sở đăng ký thuốc phải cung cấp tài liệu pháp lý chứng minh cơ quan này là cơ quan có thẩm quyền và cơ quan quản lý dược phẩm quốc gia tại nước đó không thực hiện việc cấp CPP theo quy định của pháp luật nước sở tại.
+Trường hợp CPP được cấp bởi cơ quan không phải cơ quan quản lý dược phẩm: Cơ sở đăng ký thuốc phải cung cấp tài liệu chứng minh cơ quan này là cơ quan có thẩm quyền và cơ quan quản lý dược phẩm tại nước đó không thực hiện việc cấp CPP theo quy định của pháp luật nước sở tại.
+c) Chữ ký, tên người ký và dấu của cơ quan cấp CPP phải được chứng thực bởi cơ quan có thẩm quyền; Trường hợp nội dung xác nhận này không được thể hiện bằng tiếng Anh thì phải dịch công chứng sang tiếng Việt hoặc tiếng Anh;
+d) Nội dung của CPP phải có đầy đủ thông tin theo quy định tại Mẫu 7/TT ban hành kèm theo Thông tư này và các nội dung sau:
+- Công thức bào chế của thuốc, trong đó nêu rõ tên, thành phần, nồng độ, hàm lượng của từng dược chất, dược liệu, tá dược; đối với dạng bào chế viên nang mềm, viên nang cứng phải có thêm thông tin về thành phần công thức của vỏ nang;
+- Tiêu chuẩn thành phẩm, tiêu chuẩn dược chất, dược liệu, tên, địa chỉ cơ sở sản xuất dược chất, dược liệu;
+- Trường hợp thuốc có sự tham gia sản xuất bởi nhiều cơ sở sản xuất khác nhau thì CPP phải ghi rõ tên, địa chỉ, vai trò của từng cơ sở;
+- Trường hợp CPP không có thông tin cơ sở sản xuất thuốc đáp ứng thực hành tốt sản xuất thuốc (GMP), cơ sở đăng ký phải nộp kèm giấy chứng nhận GMP của tất cả các cơ sở sản xuất đáp ứng quy định tại khoản 1, 2, 3 Điều này;
+- Các phụ lục kèm theo CPP (nếu có) phải có xác nhận của cơ quan cấp CPP.
+đ) Đối với thuốc generic, thuốc dược liệu, sinh phẩm probiotics (men tiêu hóa), thuốc gia hạn, thay đổi, bổ sung giấy đăng ký lưu hành: CPP xác nhận thuốc được cấp phép và lưu hành ở nước sản xuất. Trường hợp thuốc không được cấp phép lưu hành ở nước sản xuất hoặc được cấp phép nhưng không lưu hành thực tế ở nước sản xuất, cơ sở đăng ký phải cung cấp CPP có xác nhận thuốc được cấp phép và lưu hành ở một trong các nước quy định tại khoản 10 Điều 2 Thông tư này;
+e) Đối với thuốc hóa dược mới và sinh phẩm nhập khẩu, trừ sinh phẩm probiotics (men tiêu hóa): CPP được cấp bởi nước sản xuất và CPP được cấp bởi một trong các cơ quan quản lý khác quy định tại khoản 10 Điều 2 Thông tư này có xác nhận thuốc được cấp phép và lưu hành thực tế;
+g) Đối với vắc xin nhập khẩu: CPP được cấp bởi nước sản xuất và CPP được cấp bởi một trong các cơ quan quản lý khác quy định tại khoản 9 Điều 2 Thông tư này có xác nhận vắc xin được cấp phép và lưu hành thực tế;
+h) Đối với thuốc generic có báo cáo nghiên cứu tương đương sinh học: CPP được cấp bởi một trong các cơ quan quản lý quy định tại khoản 10 Điều 2 Thông tư này có xác nhận thuốc được cấp phép và lưu hành thực tế;
+Trường hợp không có CPP đáp ứng quy định này, phải có báo cáo nghiên cứu tương đương sinh học của thuốc được thực hiện tại cơ sở kinh doanh dịch vụ thử tương đương sinh học của thuốc tại Việt Nam hoặc tại các cơ sở thử tương tương sinh học mà Việt Nam công nhận theo quy định của Bộ trưởng Bộ Y tế hoặc theo các thỏa thuận quốc tế mà Việt Nam đã tham gia ký kết.
+i) Đối với thuốc đề nghị được phân loại biệt dược gốc, CPP được cấp bởi một trong các cơ quan quản lý quy định tại khoản 9, 10 Điều 2 Thông tư này, trừ thuốc sản xuất tại Việt Nam;
+k) Đối với thuốc, vắc xin, sinh phẩm nhập khẩu không cung cấp được CPP đáp ứng quy định tại điểm đ, e, g, h khoản này, Bộ trưởng Bộ Y tế xem xét quyết định trên cơ sở ý kiến tư vấn của Hội đồng tư vấn cấp giấy đăng ký lưu hành thuốc, nguyên liệu làm thuốc khi thuốc được cấp phép lưu hành bởi ít nhất một cơ quan quản lý trên thế giới và thuộc một trong các trường hợp sau:
+- Thuốc, vắc xin, sinh phẩm để đáp ứng nhu cầu cho quốc phòng, an ninh; phòng, chống dịch, bệnh, khắc phục hậu quả thiên tai, thảm họa, thuốc phục vụ cho chương trình y tế của nhà nước;
+- Vắc xin dùng cho chương trình tiêm chủng mở rộng quốc gia mà trên thị trường không sẵn có vắc xin khác có khả năng thay thế về mặt số lượng, chất lượng, an toàn, hiệu quả hoặc chi phí sử dụng vắc xin;
+- Các trường hợp đặc biệt khác có văn bản thỏa thuận, công nhận lẫn nhau giữa các cơ quan quản lý Nhà nước về Dược về điều kiện sản xuất, lưu hành thuốc, vắc xin, sinh phẩm.
+l) Các thông tin thể hiện trên CPP phải thống nhất với các thông tin có liên quan trong hồ sơ đăng ký thuốc.</t>
+        </is>
+      </c>
+      <c r="Y6" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 29/2020/TT-BYT · hiệu lực 2021-02-15
+c) Sửa đổi, bổ sung các điểm e, g khoản 4 Điều 23 như sau:
+“e) Đối với hồ sơ cấp giấy đăng ký lưu hành thuốc hóa dược mới, sinh phẩm nhập khẩu, trừ sinh phẩm probiotics (men tiêu hóa): phải có CPP được cấp bởi cơ quan có thẩm quyền của nước sản xuất có xác nhận thuốc được cấp phép và lưu hành thực tế tại nước đó. Trường hợp CPP này không được cấp bởi EMA thì phải có thêm giấy tờ pháp lý được cấp bởi một trong các cơ quan quản lý khác quy định tại khoản 9 hoặc khoản 10 Điều 2 Thông tư này. Giấy tờ pháp lý bao gồm nội dung tối thiểu sau: tên thuốc, hoạt chất, nồng độ hoặc hàm lượng hoạt chất, dạng bào chế, tên và địa chỉ cơ sở sản xuất, có xác nhận thuốc được cấp phép và lưu hành thực tế tại nước đó;
+g) Đối với hồ sơ cấp giấy đăng ký lưu hành vắc xin nhập khẩu: phải có CPP được cấp bởi cơ quan có thẩm quyền của nước sản xuất có xác nhận thuốc được cấp phép và lưu hành thực tế tại nước đó. Trường hợp CPP này không được cấp bởi EMA thì phải có thêm giấy tờ pháp lý được cấp bởi một trong các cơ quan quản lý khác quy định tại khoản 9 Điều 2 Thông tư này. Giấy tờ pháp lý bao gồm nội dung tối thiểu sau: tên thuốc, hoạt chất, nồng độ hoặc hàm lượng hoạt chất, dạng bào chế, tên và địa chỉ cơ sở sản xuất, có xác nhận thuốc được cấp phép và lưu hành thực tế tại nước đó.”;
+CHUYỂN TIẾP: Điều 4. Quy định chuyển tiếp
+1. Các hồ sơ đã nộp cho cơ quan tiếp nhận hồ sơ trước ngày Thông tư này có hiệu lực nhưng đang trong quá trình giải quyết được áp dụng theo quy định có liên quan tại Thông tư này hoặc các quy định trước ngày Thông tư này có hiệu lực theo hướng thuận tiện cho doanh nghiệp, tổ chức, cá nhân.
+2. Các quy định về công bố thông tin, cập nhật, khai báo và báo cáo theo hình thức trực tuyến tại Thông tư này được áp dụng theo triển khai của cơ quan nhà nước có thẩm quyền.
+[amend] 23/2021/TT-BYT · hiệu lực 2022-01-25
+a) Sửa đổi, bổ sung các điểm e, g khoản 4 Điều 23 như sau:
+"e) Đối với hồ sơ cấp giấy đăng ký lưu hành thuốc hóa dược mới, sinh phẩm nhập khẩu, trừ sinh phẩm probiotics (men tiêu hóa):
+Phải có CPP được cấp bởi cơ quan quản lý có thẩm quyền của nước sản xuất có xác nhận thuốc được cấp phép và lưu hành thực tế tại nước đó. Trường hợp CPP này không được cấp bởi EMA thì phải có thêm giấy tờ pháp lý được cấp bởi cơ quan quản lý có thẩm quyền của nước thứ hai xác nhận thuốc được cấp phép và lưu hành thực tế tại nước đó với các nội dung tối thiểu về: tên thuốc, hoạt chất, nồng độ hoặc hàm lượng hoạt chất, dạng bào chế, tên và địa chỉ cơ sở sản xuất. Cơ quan quản lý có thẩm quyền của nước sản xuất cấp CPP hoặc cơ quan có thẩm quyền của nước thứ hai cấp giấy tờ pháp lý xác nhận thuốc được cấp phép và lưu hành thực tế tại nước đó phải thuộc một trong các cơ quan quản lý quy định tại khoản 9 hoặc khoản 10 Điều 2 Thông tư này;
+g) Đối với hồ sơ cấp giấy đăng ký lưu hành vắc xin nhập khẩu:
+Phải có CPP được cấp bởi cơ quan quản lý có thẩm quyền của nước sản xuất có xác nhận vắc xin được cấp phép và lưu hành thực tế tại nước đó. Trường hợp CPP này không được cấp bởi EMA thì phải có thêm giấy tờ pháp lý được cấp bởi cơ quan quản lý có thẩm quyền của nước thứ hai xác nhận vắc xin được cấp phép và lưu hành thực tế tại nước đó với các nội dung tối thiểu về: tên vắc xin, hoạt chất, nồng độ hoặc hàm lượng hoạt chất, dạng bào chế, tên và địa chỉ cơ sở sản xuất. Cơ quan quản lý có thẩm quyền của nước sản xuất cấp CPP hoặc cơ quan có thẩm quyền của nước thứ hai cấp giấy tờ pháp lý xác nhận vắc xin được cấp phép và lưu hành thực tế tại nước đó phải thuộc một trong các cơ quan quản lý quy định tại khoản 9 Điều 2 Thông tư này."
+CHUYỂN TIẾP: Điều 3. Điều khoản chuyển tiếp
+Các hồ sơ đã nộp cho cơ quan tiếp nhận hồ sơ trước ngày Thông tư này có hiệu lực nhưng đang trong quá trình giải quyết được áp dụng theo quy định có liên quan tại Thông tư này hoặc các quy định trước ngày Thông tư này có hiệu lực theo hướng thuận tiện cho doanh nghiệp, tổ chức, cá nhân.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1019,7 +1189,6 @@
           <t>actor_has_transitional, split_effective_date</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -1030,18 +1199,59 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
           <t>id cũ vilextime:T3:provision:11c19b26-e183-11f0-a1fe-6192bcf0213f#k4#g:2022-01-26 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
+      <c r="X7" s="2" t="inlineStr">
+        <is>
+          <t>32/2018/TT-BYT · hiệu lực 2019-09-01 → 2022-10-20 · lúc thu thập: Hết hiệu lực toàn bộ
+Điều 23. Quy định đối với các tài liệu trong hồ sơ đề nghị cấp, gia hạn, thay đổi, bổ sung giấy đăng ký lưu hành thuốc, nguyên liệu làm thuốc
+4. Quy định đối với CPP:
+a) CPP phải có chữ ký, tên người ký, ngày cấp và dấu của cơ quan cấp CPP;
+b) CPP phải được cấp bởi cơ quan quản lý về dược phẩm có thẩm quyền cấp quốc gia.
+Trường hợp CPP được cấp bởi cơ quan quản lý dược phẩm nhưng không phải là cơ quan quản lý dược phẩm cấp quốc gia: Cơ sở đăng ký thuốc phải cung cấp tài liệu pháp lý chứng minh cơ quan này là cơ quan có thẩm quyền và cơ quan quản lý dược phẩm quốc gia tại nước đó không thực hiện việc cấp CPP theo quy định của pháp luật nước sở tại.
+Trường hợp CPP được cấp bởi cơ quan không phải cơ quan quản lý dược phẩm: Cơ sở đăng ký thuốc phải cung cấp tài liệu chứng minh cơ quan này là cơ quan có thẩm quyền và cơ quan quản lý dược phẩm tại nước đó không thực hiện việc cấp CPP theo quy định của pháp luật nước sở tại.
+c) Chữ ký, tên người ký và dấu của cơ quan cấp CPP phải được chứng thực bởi cơ quan có thẩm quyền; Trường hợp nội dung xác nhận này không được thể hiện bằng tiếng Anh thì phải dịch công chứng sang tiếng Việt hoặc tiếng Anh;
+d) Nội dung của CPP phải có đầy đủ thông tin theo quy định tại Mẫu 7/TT ban hành kèm theo Thông tư này và các nội dung sau:
+- Công thức bào chế của thuốc, trong đó nêu rõ tên, thành phần, nồng độ, hàm lượng của từng dược chất, dược liệu, tá dược; đối với dạng bào chế viên nang mềm, viên nang cứng phải có thêm thông tin về thành phần công thức của vỏ nang;
+- Tiêu chuẩn thành phẩm, tiêu chuẩn dược chất, dược liệu, tên, địa chỉ cơ sở sản xuất dược chất, dược liệu;
+- Trường hợp thuốc có sự tham gia sản xuất bởi nhiều cơ sở sản xuất khác nhau thì CPP phải ghi rõ tên, địa chỉ, vai trò của từng cơ sở;
+- Trường hợp CPP không có thông tin cơ sở sản xuất thuốc đáp ứng thực hành tốt sản xuất thuốc (GMP), cơ sở đăng ký phải nộp kèm giấy chứng nhận GMP của tất cả các cơ sở sản xuất đáp ứng quy định tại khoản 1, 2, 3 Điều này;
+- Các phụ lục kèm theo CPP (nếu có) phải có xác nhận của cơ quan cấp CPP.
+đ) Đối với thuốc generic, thuốc dược liệu, sinh phẩm probiotics (men tiêu hóa), thuốc gia hạn, thay đổi, bổ sung giấy đăng ký lưu hành: CPP xác nhận thuốc được cấp phép và lưu hành ở nước sản xuất. Trường hợp thuốc không được cấp phép lưu hành ở nước sản xuất hoặc được cấp phép nhưng không lưu hành thực tế ở nước sản xuất, cơ sở đăng ký phải cung cấp CPP có xác nhận thuốc được cấp phép và lưu hành ở một trong các nước quy định tại khoản 10 Điều 2 Thông tư này;
+e) Đối với thuốc hóa dược mới và sinh phẩm nhập khẩu, trừ sinh phẩm probiotics (men tiêu hóa): CPP được cấp bởi nước sản xuất và CPP được cấp bởi một trong các cơ quan quản lý khác quy định tại khoản 10 Điều 2 Thông tư này có xác nhận thuốc được cấp phép và lưu hành thực tế;
+g) Đối với vắc xin nhập khẩu: CPP được cấp bởi nước sản xuất và CPP được cấp bởi một trong các cơ quan quản lý khác quy định tại khoản 9 Điều 2 Thông tư này có xác nhận vắc xin được cấp phép và lưu hành thực tế;
+h) Đối với thuốc generic có báo cáo nghiên cứu tương đương sinh học: CPP được cấp bởi một trong các cơ quan quản lý quy định tại khoản 10 Điều 2 Thông tư này có xác nhận thuốc được cấp phép và lưu hành thực tế;
+Trường hợp không có CPP đáp ứng quy định này, phải có báo cáo nghiên cứu tương đương sinh học của thuốc được thực hiện tại cơ sở kinh doanh dịch vụ thử tương đương sinh học của thuốc tại Việt Nam hoặc tại các cơ sở thử tương tương sinh học mà Việt Nam công nhận theo quy định của Bộ trưởng Bộ Y tế hoặc theo các thỏa thuận quốc tế mà Việt Nam đã tham gia ký kết.
+i) Đối với thuốc đề nghị được phân loại biệt dược gốc, CPP được cấp bởi một trong các cơ quan quản lý quy định tại khoản 9, 10 Điều 2 Thông tư này, trừ thuốc sản xuất tại Việt Nam;
+k) Đối với thuốc, vắc xin, sinh phẩm nhập khẩu không cung cấp được CPP đáp ứng quy định tại điểm đ, e, g, h khoản này, Bộ trưởng Bộ Y tế xem xét quyết định trên cơ sở ý kiến tư vấn của Hội đồng tư vấn cấp giấy đăng ký lưu hành thuốc, nguyên liệu làm thuốc khi thuốc được cấp phép lưu hành bởi ít nhất một cơ quan quản lý trên thế giới và thuộc một trong các trường hợp sau:
+- Thuốc, vắc xin, sinh phẩm để đáp ứng nhu cầu cho quốc phòng, an ninh; phòng, chống dịch, bệnh, khắc phục hậu quả thiên tai, thảm họa, thuốc phục vụ cho chương trình y tế của nhà nước;
+- Vắc xin dùng cho chương trình tiêm chủng mở rộng quốc gia mà trên thị trường không sẵn có vắc xin khác có khả năng thay thế về mặt số lượng, chất lượng, an toàn, hiệu quả hoặc chi phí sử dụng vắc xin;
+- Các trường hợp đặc biệt khác có văn bản thỏa thuận, công nhận lẫn nhau giữa các cơ quan quản lý Nhà nước về Dược về điều kiện sản xuất, lưu hành thuốc, vắc xin, sinh phẩm.
+l) Các thông tin thể hiện trên CPP phải thống nhất với các thông tin có liên quan trong hồ sơ đăng ký thuốc.</t>
+        </is>
+      </c>
+      <c r="Y7" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 29/2020/TT-BYT · hiệu lực 2021-02-15
+c) Sửa đổi, bổ sung các điểm e, g khoản 4 Điều 23 như sau:
+“e) Đối với hồ sơ cấp giấy đăng ký lưu hành thuốc hóa dược mới, sinh phẩm nhập khẩu, trừ sinh phẩm probiotics (men tiêu hóa): phải có CPP được cấp bởi cơ quan có thẩm quyền của nước sản xuất có xác nhận thuốc được cấp phép và lưu hành thực tế tại nước đó. Trường hợp CPP này không được cấp bởi EMA thì phải có thêm giấy tờ pháp lý được cấp bởi một trong các cơ quan quản lý khác quy định tại khoản 9 hoặc khoản 10 Điều 2 Thông tư này. Giấy tờ pháp lý bao gồm nội dung tối thiểu sau: tên thuốc, hoạt chất, nồng độ hoặc hàm lượng hoạt chất, dạng bào chế, tên và địa chỉ cơ sở sản xuất, có xác nhận thuốc được cấp phép và lưu hành thực tế tại nước đó;
+g) Đối với hồ sơ cấp giấy đăng ký lưu hành vắc xin nhập khẩu: phải có CPP được cấp bởi cơ quan có thẩm quyền của nước sản xuất có xác nhận thuốc được cấp phép và lưu hành thực tế tại nước đó. Trường hợp CPP này không được cấp bởi EMA thì phải có thêm giấy tờ pháp lý được cấp bởi một trong các cơ quan quản lý khác quy định tại khoản 9 Điều 2 Thông tư này. Giấy tờ pháp lý bao gồm nội dung tối thiểu sau: tên thuốc, hoạt chất, nồng độ hoặc hàm lượng hoạt chất, dạng bào chế, tên và địa chỉ cơ sở sản xuất, có xác nhận thuốc được cấp phép và lưu hành thực tế tại nước đó.”;
+CHUYỂN TIẾP: Điều 4. Quy định chuyển tiếp
+1. Các hồ sơ đã nộp cho cơ quan tiếp nhận hồ sơ trước ngày Thông tư này có hiệu lực nhưng đang trong quá trình giải quyết được áp dụng theo quy định có liên quan tại Thông tư này hoặc các quy định trước ngày Thông tư này có hiệu lực theo hướng thuận tiện cho doanh nghiệp, tổ chức, cá nhân.
+2. Các quy định về công bố thông tin, cập nhật, khai báo và báo cáo theo hình thức trực tuyến tại Thông tư này được áp dụng theo triển khai của cơ quan nhà nước có thẩm quyền.
+[amend] 23/2021/TT-BYT · hiệu lực 2022-01-25
+a) Sửa đổi, bổ sung các điểm e, g khoản 4 Điều 23 như sau:
+"e) Đối với hồ sơ cấp giấy đăng ký lưu hành thuốc hóa dược mới, sinh phẩm nhập khẩu, trừ sinh phẩm probiotics (men tiêu hóa):
+Phải có CPP được cấp bởi cơ quan quản lý có thẩm quyền của nước sản xuất có xác nhận thuốc được cấp phép và lưu hành thực tế tại nước đó. Trường hợp CPP này không được cấp bởi EMA thì phải có thêm giấy tờ pháp lý được cấp bởi cơ quan quản lý có thẩm quyền của nước thứ hai xác nhận thuốc được cấp phép và lưu hành thực tế tại nước đó với các nội dung tối thiểu về: tên thuốc, hoạt chất, nồng độ hoặc hàm lượng hoạt chất, dạng bào chế, tên và địa chỉ cơ sở sản xuất. Cơ quan quản lý có thẩm quyền của nước sản xuất cấp CPP hoặc cơ quan có thẩm quyền của nước thứ hai cấp giấy tờ pháp lý xác nhận thuốc được cấp phép và lưu hành thực tế tại nước đó phải thuộc một trong các cơ quan quản lý quy định tại khoản 9 hoặc khoản 10 Điều 2 Thông tư này;
+g) Đối với hồ sơ cấp giấy đăng ký lưu hành vắc xin nhập khẩu:
+Phải có CPP được cấp bởi cơ quan quản lý có thẩm quyền của nước sản xuất có xác nhận vắc xin được cấp phép và lưu hành thực tế tại nước đó. Trường hợp CPP này không được cấp bởi EMA thì phải có thêm giấy tờ pháp lý được cấp bởi cơ quan quản lý có thẩm quyền của nước thứ hai xác nhận vắc xin được cấp phép và lưu hành thực tế tại nước đó với các nội dung tối thiểu về: tên vắc xin, hoạt chất, nồng độ hoặc hàm lượng hoạt chất, dạng bào chế, tên và địa chỉ cơ sở sản xuất. Cơ quan quản lý có thẩm quyền của nước sản xuất cấp CPP hoặc cơ quan có thẩm quyền của nước thứ hai cấp giấy tờ pháp lý xác nhận vắc xin được cấp phép và lưu hành thực tế tại nước đó phải thuộc một trong các cơ quan quản lý quy định tại khoản 9 Điều 2 Thông tư này."
+CHUYỂN TIẾP: Điều 3. Điều khoản chuyển tiếp
+Các hồ sơ đã nộp cho cơ quan tiếp nhận hồ sơ trước ngày Thông tư này có hiệu lực nhưng đang trong quá trình giải quyết được áp dụng theo quy định có liên quan tại Thông tư này hoặc các quy định trước ngày Thông tư này có hiệu lực theo hướng thuận tiện cho doanh nghiệp, tổ chức, cá nhân.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1104,7 +1314,6 @@
           <t>actor_has_transitional</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -1115,18 +1324,52 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
           <t>id cũ vilextime:T3:provision:226dbd28-df45-11f0-84f9-87051d7f496f:2013-06-02 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
+          <t>11/2013/TT-NHNN · hiệu lực 2013-06-01 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 1. Phạm vi điều chỉnh và đối tượng áp dụng
+1. Phạm vi điều chỉnh:
+a) Thông tư này quy định về cho vay hỗ trợ nhà ở từ nguồn tái cấp vốn của Ngân hàng Nhà nước Việt Nam (sau đây gọi là Ngân hàng Nhà nước) theo Nghị quyết số 02/NQ-CP ngày 07 tháng 01 năm 2013 của Chính phủ về một số giải pháp tháo gỡ khó khăn cho sản xuất kinh doanh, hỗ trợ thị trường, giải quyết nợ xấu và Nghị quyết số 48/NQ-CP ngày 04 tháng 4 năm 2013 của Chính phủ về phiên họp thường kỳ Chính phủ tháng 3 năm 2013;
+b) Ngân hàng thương mại nhà nước, ngân hàng thương mại cổ phần do Nhà nước nắm giữ trên 50% vốn điều lệ (sau đây gọi là ngân hàng) dành một lượng vốn tối thiểu 3% tổng dư nợ cho vay tại thời điểm cuối năm trước để cho vay các đối tượng được quy định tại điểm a khoản 2 Điều này. Đối với các khoản cho vay không từ nguồn hỗ trợ tái cấp vốn của Ngân hàng Nhà nước, ngân hàng thực hiện cho vay theo quy định của pháp luật hiện hành với lãi suất và thời hạn phù hợp với khả năng trả nợ của khách hàng và tình hình tài chính của ngân hàng.</t>
+        </is>
+      </c>
+      <c r="Y8" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 32/2014/TT-NHNN · hiệu lực 2014-11-25
+1. Chỉnh sửa, bổ sung Điều 1 như sau:
+"Điều 1. Phạm vi điều chỉnh và áp dụng đối tượng
+1. Phạm vi điều chỉnh:
+a) Thông tư này quy định về cho vay hỗ trợ nhà ở từ nguồn tái cấp vốn của Ngân hàng Nhà nước Việt Nam (sau đây gọi là hàng Nhà nước) theo Nghị quyết số 02/NQ-CP ngày 07 tháng 01 năm 2013 của Chính phủ về một số giải pháp giải quyết khó khăn cho sản xuất kinh doanh, hỗ trợ thị trường giải quyết nợ xấu, hỗ trợ số 48/NQ-CP ngày 04 tháng 4 năm 2013 của Chính phủ Trưng bày thường kỳ Chính phủ tháng 3 năm 2013 và Nghị quyết số 61/NQ-CP ngày 21 phiên tháng 8 năm 2014 của Chính phủ về việc sửa đổi bổ sung Nghị quyết số 02/NQ-CP;
+b) Ngân hàng thương mại nhà nước, ngân hàng thương mại cổ phần do Nhà nước nắm giữ trên 50% vốn điều chỉnh dành một lượng vốn tối thiểu tối thiểu 3% tổng dư nợ cho vay tại thời điểm cuối năm trước để vay các đối tượng được quy định tại điểm 2 Điều này.
+2. Ứng dụng đối tượng:
+a) Đối tượng vay vốn (sau đây gọi là khách hàng) bao gồm:
+- Cán bộ công chức, viên chức, năng lượng vũ trang và đối tượng thu nhập thấp vay vốn để mua, thuê, thuê mua nhà ở xã hội và thuê, mua nhà thương mại có diện tích nhỏ hơn 70 m2, giá bán dưới 15.000.000 đồng/m2;
+- Cán bộ công chức, viên chức, năng lượng vũ trang, công nhân, người lao động có thu nhập thấp nhưng khó khăn về nhà ở, khi mua nhà thương mại tại các dự án phát triển nhà ở, dự án đầu tư xây dựng khu đô thị trên địa bàn đã được cấp phép phê duyệt có tổng giá trị đồng mua bán (giá nhà cả và đất) không vượt quá 1.050.000.000 đồng;
+- Cán bộ công chức, viên chức, lực lượng vũ trang và người lao động tại đô thị đã có đất ở phù hợp với kế hoạch đang gặp khó khăn về nhà ở nhưng chưa được nhà nước hỗ trợ dưới mọi hình thức được vay để xây dựng mới hoặc cải tạo sửa chữa nhà ở của mình;
+- Hộ gia đình, cá nhân có phương án đầu tư cải tạo hoặc xây dựng mới nhà ở xã hội phù hợp với quy định pháp luật để cho thuê, cho thuê mua và để bán các đối tượng là công nhân, người động lao tại các khu công nghiệp, đúc công nghiệp vừa và nhỏ, khu chế xuất, kinh tế, khu công nghệ cao, các cơ sở sản xuất công nghiệp, thủ công nghiệp, nhà máy, xí nghiệp (dành cho tất cả các bên, các kinh doanh) tế; người lao động thuộc các thành phần kinh tế tại khu vực đô thị; viên, học sinh các trường đại học, cao đẳng, trung học chuyên nghiệp, cao đẳng nghề, trung cấp nghề và trường dạy nghề cho công nhân (không phân biệt công lập hay ngoài công lập) và các đối tượng khác được giải quyết ở xã hội theo quy định của Nghị định số 188/2013/ND-CP ngày 20 tháng 11 năm 2013 của Chính phủ về phát và quản lý nhà ở xã hội;
+- Doanh nghiệp là chủ dự án xây dựng nhà ở xã hội, doanh nghiệp là chủ đầu tư dự án nhà ở thương mại được chuyển đổi công năng sang dự án nhà ở xã hội Xây dựng công trình xây dựng trong mọi thời kỳ (sau đây gọi là doanh nghiệp).
+b) Ngân hàng cho vay theo quy định tại Thông tư này (sau đây gọi là ngân hàng) bao gồm:
+- Các ngân hàng thương mại do Nhà nước nắm giữ trên 50% vốn điều lệ, bao gồm: Ngân hàng Nông nghiệp và Phát triển nông thôn Việt Nam; Ngân hàng thương mại cổ phần Tư vấn và Phát triển Việt Nam; Ngân hàng thương mại cổ phần Công thương Việt Nam; Ngân hàng thương mại cổ phần Ngoại thương Việt Nam; Ngân hàng thương mại cổ phần Phát triển nhà đồng bằng sông Cửu Long;
+- Các ngân hàng thương mại cổ phần khác của Ngân hàng Nhà nước chỉ định. Trong thời hạn 30 ngày kể từ khi Thông tư này có hiệu lực, các ngân hàng thương mại cổ phần có nhu cầu đăng ký tham gia gửi công văn đề nghị tham gia chương trình cho vay hỗ trợ nhà ở theo mẫu tại Phụ lục số 04 đính kèm Thông tư này về Ngân hàng Nhà nước. Ngân hàng Nhà nước cơ sở vào quy mô, phạm vi hoạt động và kinh nghiệm trong cho vay đối với lĩnh vực đầu tư, kinh doanh bất động sản của các ngân hàng để xem xét, quyết định.
+c) Các tổ chức, cá nhân có liên quan."
+2. Chỉnh sửa, bổ sung Điều 3 như sau:
+"Điều 3. Điều kiện cho vay
+Ngoài ra, các điều kiện cho vay theo quy định của pháp luật hiện hành cho vay của tổ chức tín dụng dành cho khách hàng; quy định tại Thông tư số 07/2013/TT-BXD ngày 15 tháng 05 năm 2013 của Bộ Xây dựng về hướng dẫn xác định các đối tượng được vay hỗ trợ nhà ở theo Nghị quyết số 02/NQ-CP ngày 07 tháng 01 năm 2013 của Chính phủ và các bản sửa đổi văn bản, bổ sung thay thế Thông số 07/2013/TT-BXD, khách hàng phải đáp ứng thêm các điều kiện sau:
+1. Đối với khách hàng cá nhân vay để mua, thuê, thuê mua nhà ở xã hội; thuê, mua nhà ở thương mại:
+a) Có hợp đồng mua, thuê, thuê mua nhà ở xã hội; hợp đồng thuê, mua nhà ở thương mại với chủ tư;
+b) Có mục đích vay vốn để thanh toán các khoản tiền chưa thanh toán mua, thuê, thuê mua nhà ở xã hội; thuê, mua nhà thương mại có diện tích nhỏ hơn 70m2, giá bán dưới 15.000.000 đồng/m2 đối với các hợp đồng ký kết với chủ đầu tư kể từ ngày 07 tháng 01 năm 2013; hoặc có mục đích vay vốn để thanh toán các tài khoản chưa được thanh toán với chủ nhà phát sinh kể từ ngày 21 tháng 8 năm 2014 để mua nhà ở thương mại có tổng giá trị hợp lý đồng mua bán (bán cả nhà và đất) không quá 1.050.000.0 [...cắt bớt]
+[amend] 25/2016/TT_NHNN · hiệu lực 2016-08-01
+1. Sửa đổi, bổ sung điểm a khoản 1 Điều 1 như sau:
+"a) Thông tư này quy định về cho vay hỗ trợ nhà ở từ nguồn tái cấp vốn của Ngân hàng Nhà nước Việt Nam (sau đây gọi là Ngân hàng Nhà nước) theo Nghị quyết số 02/NQ-CP ngày 07 tháng 01 năm 2013 của Chính phủ về một số giải pháp tháo gỡ khó khăn cho sản xuất kinh doanh, hỗ trợ thị trường, giải quyết nợ xấu; Nghị quyết số 48/NQ-CP ngày 04 tháng 04 năm 2013 của Chính phủ về phiên họp thường kỳ Chính phủ tháng 3 năm 2013; Nghị quyết số 61/NQ-CP ngày 21 tháng 08 năm 2014 của Chính phủ về việc sửa đổi, bổ sung Nghị quyết số 02/NQ-CP và Nghị quyết số 23/NQ-CP ngày 30 tháng 03 năm 2016 của Chính phủ về phiên họp Chính phủ thường kỳ tháng 3 năm 2016.".
+CHUYỂN TIẾP: Điều 2. Quy định chuyển tiếp
+1. Các khoản giải ngân của ngân hàng trong thời gian từ ngày 01 tháng 06 năm 2016 đến ngày Thông tư này có hiệu lực được Ngân hàng Nhà nước tái cấp v</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1189,7 +1432,6 @@
           <t>actor_has_transitional</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -1200,7 +1442,6 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr">
         <is>
           <t>other</t>
@@ -1211,11 +1452,47 @@
           <t>Văn bản mốc 2 lỗi chữ ở nguồn ('sau đây gọi là hàng Nhà nước', 'Trưng bày thường kỳ', 'ngày 21 phiên tháng 8'); danh sách nghị quyết vẫn đọc được; id cũ vilextime:T3:provision:226dbd28-df45-11f0-84f9-87051d7f496f:2014-11-26 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t>11/2013/TT-NHNN · hiệu lực 2013-06-01 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 1. Phạm vi điều chỉnh và đối tượng áp dụng
+1. Phạm vi điều chỉnh:
+a) Thông tư này quy định về cho vay hỗ trợ nhà ở từ nguồn tái cấp vốn của Ngân hàng Nhà nước Việt Nam (sau đây gọi là Ngân hàng Nhà nước) theo Nghị quyết số 02/NQ-CP ngày 07 tháng 01 năm 2013 của Chính phủ về một số giải pháp tháo gỡ khó khăn cho sản xuất kinh doanh, hỗ trợ thị trường, giải quyết nợ xấu và Nghị quyết số 48/NQ-CP ngày 04 tháng 4 năm 2013 của Chính phủ về phiên họp thường kỳ Chính phủ tháng 3 năm 2013;
+b) Ngân hàng thương mại nhà nước, ngân hàng thương mại cổ phần do Nhà nước nắm giữ trên 50% vốn điều lệ (sau đây gọi là ngân hàng) dành một lượng vốn tối thiểu 3% tổng dư nợ cho vay tại thời điểm cuối năm trước để cho vay các đối tượng được quy định tại điểm a khoản 2 Điều này. Đối với các khoản cho vay không từ nguồn hỗ trợ tái cấp vốn của Ngân hàng Nhà nước, ngân hàng thực hiện cho vay theo quy định của pháp luật hiện hành với lãi suất và thời hạn phù hợp với khả năng trả nợ của khách hàng và tình hình tài chính của ngân hàng.</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 32/2014/TT-NHNN · hiệu lực 2014-11-25
+1. Chỉnh sửa, bổ sung Điều 1 như sau:
+"Điều 1. Phạm vi điều chỉnh và áp dụng đối tượng
+1. Phạm vi điều chỉnh:
+a) Thông tư này quy định về cho vay hỗ trợ nhà ở từ nguồn tái cấp vốn của Ngân hàng Nhà nước Việt Nam (sau đây gọi là hàng Nhà nước) theo Nghị quyết số 02/NQ-CP ngày 07 tháng 01 năm 2013 của Chính phủ về một số giải pháp giải quyết khó khăn cho sản xuất kinh doanh, hỗ trợ thị trường giải quyết nợ xấu, hỗ trợ số 48/NQ-CP ngày 04 tháng 4 năm 2013 của Chính phủ Trưng bày thường kỳ Chính phủ tháng 3 năm 2013 và Nghị quyết số 61/NQ-CP ngày 21 phiên tháng 8 năm 2014 của Chính phủ về việc sửa đổi bổ sung Nghị quyết số 02/NQ-CP;
+b) Ngân hàng thương mại nhà nước, ngân hàng thương mại cổ phần do Nhà nước nắm giữ trên 50% vốn điều chỉnh dành một lượng vốn tối thiểu tối thiểu 3% tổng dư nợ cho vay tại thời điểm cuối năm trước để vay các đối tượng được quy định tại điểm 2 Điều này.
+2. Ứng dụng đối tượng:
+a) Đối tượng vay vốn (sau đây gọi là khách hàng) bao gồm:
+- Cán bộ công chức, viên chức, năng lượng vũ trang và đối tượng thu nhập thấp vay vốn để mua, thuê, thuê mua nhà ở xã hội và thuê, mua nhà thương mại có diện tích nhỏ hơn 70 m2, giá bán dưới 15.000.000 đồng/m2;
+- Cán bộ công chức, viên chức, năng lượng vũ trang, công nhân, người lao động có thu nhập thấp nhưng khó khăn về nhà ở, khi mua nhà thương mại tại các dự án phát triển nhà ở, dự án đầu tư xây dựng khu đô thị trên địa bàn đã được cấp phép phê duyệt có tổng giá trị đồng mua bán (giá nhà cả và đất) không vượt quá 1.050.000.000 đồng;
+- Cán bộ công chức, viên chức, lực lượng vũ trang và người lao động tại đô thị đã có đất ở phù hợp với kế hoạch đang gặp khó khăn về nhà ở nhưng chưa được nhà nước hỗ trợ dưới mọi hình thức được vay để xây dựng mới hoặc cải tạo sửa chữa nhà ở của mình;
+- Hộ gia đình, cá nhân có phương án đầu tư cải tạo hoặc xây dựng mới nhà ở xã hội phù hợp với quy định pháp luật để cho thuê, cho thuê mua và để bán các đối tượng là công nhân, người động lao tại các khu công nghiệp, đúc công nghiệp vừa và nhỏ, khu chế xuất, kinh tế, khu công nghệ cao, các cơ sở sản xuất công nghiệp, thủ công nghiệp, nhà máy, xí nghiệp (dành cho tất cả các bên, các kinh doanh) tế; người lao động thuộc các thành phần kinh tế tại khu vực đô thị; viên, học sinh các trường đại học, cao đẳng, trung học chuyên nghiệp, cao đẳng nghề, trung cấp nghề và trường dạy nghề cho công nhân (không phân biệt công lập hay ngoài công lập) và các đối tượng khác được giải quyết ở xã hội theo quy định của Nghị định số 188/2013/ND-CP ngày 20 tháng 11 năm 2013 của Chính phủ về phát và quản lý nhà ở xã hội;
+- Doanh nghiệp là chủ dự án xây dựng nhà ở xã hội, doanh nghiệp là chủ đầu tư dự án nhà ở thương mại được chuyển đổi công năng sang dự án nhà ở xã hội Xây dựng công trình xây dựng trong mọi thời kỳ (sau đây gọi là doanh nghiệp).
+b) Ngân hàng cho vay theo quy định tại Thông tư này (sau đây gọi là ngân hàng) bao gồm:
+- Các ngân hàng thương mại do Nhà nước nắm giữ trên 50% vốn điều lệ, bao gồm: Ngân hàng Nông nghiệp và Phát triển nông thôn Việt Nam; Ngân hàng thương mại cổ phần Tư vấn và Phát triển Việt Nam; Ngân hàng thương mại cổ phần Công thương Việt Nam; Ngân hàng thương mại cổ phần Ngoại thương Việt Nam; Ngân hàng thương mại cổ phần Phát triển nhà đồng bằng sông Cửu Long;
+- Các ngân hàng thương mại cổ phần khác của Ngân hàng Nhà nước chỉ định. Trong thời hạn 30 ngày kể từ khi Thông tư này có hiệu lực, các ngân hàng thương mại cổ phần có nhu cầu đăng ký tham gia gửi công văn đề nghị tham gia chương trình cho vay hỗ trợ nhà ở theo mẫu tại Phụ lục số 04 đính kèm Thông tư này về Ngân hàng Nhà nước. Ngân hàng Nhà nước cơ sở vào quy mô, phạm vi hoạt động và kinh nghiệm trong cho vay đối với lĩnh vực đầu tư, kinh doanh bất động sản của các ngân hàng để xem xét, quyết định.
+c) Các tổ chức, cá nhân có liên quan."
+2. Chỉnh sửa, bổ sung Điều 3 như sau:
+"Điều 3. Điều kiện cho vay
+Ngoài ra, các điều kiện cho vay theo quy định của pháp luật hiện hành cho vay của tổ chức tín dụng dành cho khách hàng; quy định tại Thông tư số 07/2013/TT-BXD ngày 15 tháng 05 năm 2013 của Bộ Xây dựng về hướng dẫn xác định các đối tượng được vay hỗ trợ nhà ở theo Nghị quyết số 02/NQ-CP ngày 07 tháng 01 năm 2013 của Chính phủ và các bản sửa đổi văn bản, bổ sung thay thế Thông số 07/2013/TT-BXD, khách hàng phải đáp ứng thêm các điều kiện sau:
+1. Đối với khách hàng cá nhân vay để mua, thuê, thuê mua nhà ở xã hội; thuê, mua nhà ở thương mại:
+a) Có hợp đồng mua, thuê, thuê mua nhà ở xã hội; hợp đồng thuê, mua nhà ở thương mại với chủ tư;
+b) Có mục đích vay vốn để thanh toán các khoản tiền chưa thanh toán mua, thuê, thuê mua nhà ở xã hội; thuê, mua nhà thương mại có diện tích nhỏ hơn 70m2, giá bán dưới 15.000.000 đồng/m2 đối với các hợp đồng ký kết với chủ đầu tư kể từ ngày 07 tháng 01 năm 2013; hoặc có mục đích vay vốn để thanh toán các tài khoản chưa được thanh toán với chủ nhà phát sinh kể từ ngày 21 tháng 8 năm 2014 để mua nhà ở thương mại có tổng giá trị hợp lý đồng mua bán (bán cả nhà và đất) không quá 1.050.000.0 [...cắt bớt]
+[amend] 25/2016/TT_NHNN · hiệu lực 2016-08-01
+1. Sửa đổi, bổ sung điểm a khoản 1 Điều 1 như sau:
+"a) Thông tư này quy định về cho vay hỗ trợ nhà ở từ nguồn tái cấp vốn của Ngân hàng Nhà nước Việt Nam (sau đây gọi là Ngân hàng Nhà nước) theo Nghị quyết số 02/NQ-CP ngày 07 tháng 01 năm 2013 của Chính phủ về một số giải pháp tháo gỡ khó khăn cho sản xuất kinh doanh, hỗ trợ thị trường, giải quyết nợ xấu; Nghị quyết số 48/NQ-CP ngày 04 tháng 04 năm 2013 của Chính phủ về phiên họp thường kỳ Chính phủ tháng 3 năm 2013; Nghị quyết số 61/NQ-CP ngày 21 tháng 08 năm 2014 của Chính phủ về việc sửa đổi, bổ sung Nghị quyết số 02/NQ-CP và Nghị quyết số 23/NQ-CP ngày 30 tháng 03 năm 2016 của Chính phủ về phiên họp Chính phủ thường kỳ tháng 3 năm 2016.".
+CHUYỂN TIẾP: Điều 2. Quy định chuyển tiếp
+1. Các khoản giải ngân của ngân hàng trong thời gian từ ngày 01 tháng 06 năm 2016 đến ngày Thông tư này có hiệu lực được Ngân hàng Nhà nước tái cấp v</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1278,7 +1555,6 @@
           <t>actor_has_transitional</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -1289,18 +1565,52 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
           <t>id cũ vilextime:T3:provision:226dbd28-df45-11f0-84f9-87051d7f496f:2016-08-02 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>11/2013/TT-NHNN · hiệu lực 2013-06-01 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 1. Phạm vi điều chỉnh và đối tượng áp dụng
+1. Phạm vi điều chỉnh:
+a) Thông tư này quy định về cho vay hỗ trợ nhà ở từ nguồn tái cấp vốn của Ngân hàng Nhà nước Việt Nam (sau đây gọi là Ngân hàng Nhà nước) theo Nghị quyết số 02/NQ-CP ngày 07 tháng 01 năm 2013 của Chính phủ về một số giải pháp tháo gỡ khó khăn cho sản xuất kinh doanh, hỗ trợ thị trường, giải quyết nợ xấu và Nghị quyết số 48/NQ-CP ngày 04 tháng 4 năm 2013 của Chính phủ về phiên họp thường kỳ Chính phủ tháng 3 năm 2013;
+b) Ngân hàng thương mại nhà nước, ngân hàng thương mại cổ phần do Nhà nước nắm giữ trên 50% vốn điều lệ (sau đây gọi là ngân hàng) dành một lượng vốn tối thiểu 3% tổng dư nợ cho vay tại thời điểm cuối năm trước để cho vay các đối tượng được quy định tại điểm a khoản 2 Điều này. Đối với các khoản cho vay không từ nguồn hỗ trợ tái cấp vốn của Ngân hàng Nhà nước, ngân hàng thực hiện cho vay theo quy định của pháp luật hiện hành với lãi suất và thời hạn phù hợp với khả năng trả nợ của khách hàng và tình hình tài chính của ngân hàng.</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 32/2014/TT-NHNN · hiệu lực 2014-11-25
+1. Chỉnh sửa, bổ sung Điều 1 như sau:
+"Điều 1. Phạm vi điều chỉnh và áp dụng đối tượng
+1. Phạm vi điều chỉnh:
+a) Thông tư này quy định về cho vay hỗ trợ nhà ở từ nguồn tái cấp vốn của Ngân hàng Nhà nước Việt Nam (sau đây gọi là hàng Nhà nước) theo Nghị quyết số 02/NQ-CP ngày 07 tháng 01 năm 2013 của Chính phủ về một số giải pháp giải quyết khó khăn cho sản xuất kinh doanh, hỗ trợ thị trường giải quyết nợ xấu, hỗ trợ số 48/NQ-CP ngày 04 tháng 4 năm 2013 của Chính phủ Trưng bày thường kỳ Chính phủ tháng 3 năm 2013 và Nghị quyết số 61/NQ-CP ngày 21 phiên tháng 8 năm 2014 của Chính phủ về việc sửa đổi bổ sung Nghị quyết số 02/NQ-CP;
+b) Ngân hàng thương mại nhà nước, ngân hàng thương mại cổ phần do Nhà nước nắm giữ trên 50% vốn điều chỉnh dành một lượng vốn tối thiểu tối thiểu 3% tổng dư nợ cho vay tại thời điểm cuối năm trước để vay các đối tượng được quy định tại điểm 2 Điều này.
+2. Ứng dụng đối tượng:
+a) Đối tượng vay vốn (sau đây gọi là khách hàng) bao gồm:
+- Cán bộ công chức, viên chức, năng lượng vũ trang và đối tượng thu nhập thấp vay vốn để mua, thuê, thuê mua nhà ở xã hội và thuê, mua nhà thương mại có diện tích nhỏ hơn 70 m2, giá bán dưới 15.000.000 đồng/m2;
+- Cán bộ công chức, viên chức, năng lượng vũ trang, công nhân, người lao động có thu nhập thấp nhưng khó khăn về nhà ở, khi mua nhà thương mại tại các dự án phát triển nhà ở, dự án đầu tư xây dựng khu đô thị trên địa bàn đã được cấp phép phê duyệt có tổng giá trị đồng mua bán (giá nhà cả và đất) không vượt quá 1.050.000.000 đồng;
+- Cán bộ công chức, viên chức, lực lượng vũ trang và người lao động tại đô thị đã có đất ở phù hợp với kế hoạch đang gặp khó khăn về nhà ở nhưng chưa được nhà nước hỗ trợ dưới mọi hình thức được vay để xây dựng mới hoặc cải tạo sửa chữa nhà ở của mình;
+- Hộ gia đình, cá nhân có phương án đầu tư cải tạo hoặc xây dựng mới nhà ở xã hội phù hợp với quy định pháp luật để cho thuê, cho thuê mua và để bán các đối tượng là công nhân, người động lao tại các khu công nghiệp, đúc công nghiệp vừa và nhỏ, khu chế xuất, kinh tế, khu công nghệ cao, các cơ sở sản xuất công nghiệp, thủ công nghiệp, nhà máy, xí nghiệp (dành cho tất cả các bên, các kinh doanh) tế; người lao động thuộc các thành phần kinh tế tại khu vực đô thị; viên, học sinh các trường đại học, cao đẳng, trung học chuyên nghiệp, cao đẳng nghề, trung cấp nghề và trường dạy nghề cho công nhân (không phân biệt công lập hay ngoài công lập) và các đối tượng khác được giải quyết ở xã hội theo quy định của Nghị định số 188/2013/ND-CP ngày 20 tháng 11 năm 2013 của Chính phủ về phát và quản lý nhà ở xã hội;
+- Doanh nghiệp là chủ dự án xây dựng nhà ở xã hội, doanh nghiệp là chủ đầu tư dự án nhà ở thương mại được chuyển đổi công năng sang dự án nhà ở xã hội Xây dựng công trình xây dựng trong mọi thời kỳ (sau đây gọi là doanh nghiệp).
+b) Ngân hàng cho vay theo quy định tại Thông tư này (sau đây gọi là ngân hàng) bao gồm:
+- Các ngân hàng thương mại do Nhà nước nắm giữ trên 50% vốn điều lệ, bao gồm: Ngân hàng Nông nghiệp và Phát triển nông thôn Việt Nam; Ngân hàng thương mại cổ phần Tư vấn và Phát triển Việt Nam; Ngân hàng thương mại cổ phần Công thương Việt Nam; Ngân hàng thương mại cổ phần Ngoại thương Việt Nam; Ngân hàng thương mại cổ phần Phát triển nhà đồng bằng sông Cửu Long;
+- Các ngân hàng thương mại cổ phần khác của Ngân hàng Nhà nước chỉ định. Trong thời hạn 30 ngày kể từ khi Thông tư này có hiệu lực, các ngân hàng thương mại cổ phần có nhu cầu đăng ký tham gia gửi công văn đề nghị tham gia chương trình cho vay hỗ trợ nhà ở theo mẫu tại Phụ lục số 04 đính kèm Thông tư này về Ngân hàng Nhà nước. Ngân hàng Nhà nước cơ sở vào quy mô, phạm vi hoạt động và kinh nghiệm trong cho vay đối với lĩnh vực đầu tư, kinh doanh bất động sản của các ngân hàng để xem xét, quyết định.
+c) Các tổ chức, cá nhân có liên quan."
+2. Chỉnh sửa, bổ sung Điều 3 như sau:
+"Điều 3. Điều kiện cho vay
+Ngoài ra, các điều kiện cho vay theo quy định của pháp luật hiện hành cho vay của tổ chức tín dụng dành cho khách hàng; quy định tại Thông tư số 07/2013/TT-BXD ngày 15 tháng 05 năm 2013 của Bộ Xây dựng về hướng dẫn xác định các đối tượng được vay hỗ trợ nhà ở theo Nghị quyết số 02/NQ-CP ngày 07 tháng 01 năm 2013 của Chính phủ và các bản sửa đổi văn bản, bổ sung thay thế Thông số 07/2013/TT-BXD, khách hàng phải đáp ứng thêm các điều kiện sau:
+1. Đối với khách hàng cá nhân vay để mua, thuê, thuê mua nhà ở xã hội; thuê, mua nhà ở thương mại:
+a) Có hợp đồng mua, thuê, thuê mua nhà ở xã hội; hợp đồng thuê, mua nhà ở thương mại với chủ tư;
+b) Có mục đích vay vốn để thanh toán các khoản tiền chưa thanh toán mua, thuê, thuê mua nhà ở xã hội; thuê, mua nhà thương mại có diện tích nhỏ hơn 70m2, giá bán dưới 15.000.000 đồng/m2 đối với các hợp đồng ký kết với chủ đầu tư kể từ ngày 07 tháng 01 năm 2013; hoặc có mục đích vay vốn để thanh toán các tài khoản chưa được thanh toán với chủ nhà phát sinh kể từ ngày 21 tháng 8 năm 2014 để mua nhà ở thương mại có tổng giá trị hợp lý đồng mua bán (bán cả nhà và đất) không quá 1.050.000.0 [...cắt bớt]
+[amend] 25/2016/TT_NHNN · hiệu lực 2016-08-01
+1. Sửa đổi, bổ sung điểm a khoản 1 Điều 1 như sau:
+"a) Thông tư này quy định về cho vay hỗ trợ nhà ở từ nguồn tái cấp vốn của Ngân hàng Nhà nước Việt Nam (sau đây gọi là Ngân hàng Nhà nước) theo Nghị quyết số 02/NQ-CP ngày 07 tháng 01 năm 2013 của Chính phủ về một số giải pháp tháo gỡ khó khăn cho sản xuất kinh doanh, hỗ trợ thị trường, giải quyết nợ xấu; Nghị quyết số 48/NQ-CP ngày 04 tháng 04 năm 2013 của Chính phủ về phiên họp thường kỳ Chính phủ tháng 3 năm 2013; Nghị quyết số 61/NQ-CP ngày 21 tháng 08 năm 2014 của Chính phủ về việc sửa đổi, bổ sung Nghị quyết số 02/NQ-CP và Nghị quyết số 23/NQ-CP ngày 30 tháng 03 năm 2016 của Chính phủ về phiên họp Chính phủ thường kỳ tháng 3 năm 2016.".
+CHUYỂN TIẾP: Điều 2. Quy định chuyển tiếp
+1. Các khoản giải ngân của ngân hàng trong thời gian từ ngày 01 tháng 06 năm 2016 đến ngày Thông tư này có hiệu lực được Ngân hàng Nhà nước tái cấp v</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1363,7 +1673,6 @@
           <t>actor_has_transitional</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -1374,18 +1683,80 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
           <t>id cũ vilextime:T3:provision:31d98de0-1f97-11f1-bcba-c5e53edd89aa:2016-01-02 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>191/2015/TT-BTC · hiệu lực 2016-01-01 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 12. Thủ tục hải quan, giám sát hải quan đối với hàng hóa lạc tuyến quốc tế (hàng hóa từ nước này lạc tuyến sang nước khác); hàng xuất khẩu nhưng không phát được cho người nhận, phải nhập khẩu trở lại để trả cho người gửi; hàng hóa nhập khẩu không phát được cho người nhận, phải hoàn nước gốc
+2. Đối với hàng hóa xuất khẩu nhưng không phát được cho người nhận, phải nhập khẩu trở lại để trả cho người gửi.
+a) Trách nhiệm của doanh nghiệp chuyển phát nhanh:
+a.1) Thực hiện thủ tục hải quan như đối với hàng hóa nhập khẩu theo quy định tại Điều 9, Điều 10 và Điều 11 Thông tư này;
+a.2) Ngoài hồ sơ hải quan quy định tại Điều 8 Thông tư này, doanh nghiệp chuyển phát nhanh phải nộp cho cơ quan hải quan:
+a.2.1) Văn bản của doanh nghiệp chuyển phát nhanh nước ngoài thông báo hàng hóa bị trả lại do không có người nhận hàng: 01 bản chụp;
+a.2.2) Tờ khai hải quan xuất khẩu ban đầu: 01 bản chụp đối với trường hợp khai trên tờ khai hải quan giấy.
+a.3) Thực hiện thủ tục hoàn thuế, không thu thuế (nếu có) theo quy định tại Thông tư số 38/2015/TT-BTC.
+b) Trách nhiệm của Chi cục Hải quan:
+b.1) Tiếp nhận hồ sơ do doanh nghiệp chuyển phát nhanh nộp;
+b.2) Thực hiện thủ tục hải quan đối với hàng hóa nhập khẩu quy định tại Điều 9, Điều 10 và Điều 11 Thông tư này (trừ giấy phép nhập khẩu, văn bản thông báo kết quả kiểm tra chuyên ngành);
+b.3) Thực hiện thủ tục hoàn thuế, không thu thuế (nếu có) theo quy định tại Thông tư số 38/2015/TT-BTC.</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[amend] 56/2019/TT-BTC · hiệu lực 2019-10-15
+11. Sửa đổi khoản 2, 3 Điều 12 như sau:
+“2. Đối với hàng hóa xuất khẩu nhưng không phát được cho người nhận, phải nhập khẩu trở lại để trả cho người gửi
+a) Trách nhiệm của doanh nghiệp chuyển phát nhanh:
+a.1) Thực hiện thủ tục hải quan như đối với hàng hóa nhập khẩu quy định tại Điều 11 Thông tư này. Khi khai tờ khai hải quan, ghi rõ số tờ khai xuất khẩu ban đầu tại ô số 32 trên Mẫu số HQ/2015/NK Phụ lục IV ban hành kèm theo Thông tư số 38/2015/TT-BTC (đối với tờ khai hải quan giấy), tại chỉ tiêu thông tin Phần ghi chú (đối với tờ khai điện tử).
+a.2) Nộp hồ sơ cho cơ quan hải quan:
+a.2.1) Hồ sơ hải quan quy định tại khoản 3 Điều 8 Thông tư này, trừ giấy phép nhập khẩu, văn bản thông báo kết quả kiểm tra chuyên ngành;
+a.2.2) Văn bản của doanh nghiệp chuyển phát nhanh nước ngoài thông báo hàng hóa bị trả lại do không có người nhận lại: 01 bản chụp;
+a.2.3) Tờ khai hải quan xuất khẩu ban đầu: 01 bản chụp đối với trường hợp khai trên tờ khai hải quan giấy.
+a.3) Thực hiện thủ tục hoàn thuế, không thu thuế, xử lý thuế nộp thừa (nếu có) theo quy định.
+b) Trách nhiệm của Chi cục Hải quan:
+b.1) Tiếp nhận hồ sơ do doanh nghiệp chuyển phát nhanh nộp;
+b.2) Kiểm tra, đối chiếu thông tin tờ khai xuất khẩu ban đầu với thông tin khai báo trên tờ khai nhập khẩu. Trường hợp kết quả kiểm tra phù hợp, thực hiện quy định tại điểm b.3 và điểm b.4 khoản này. Trường hợp kết quả kiểm tra không phù hợp, yêu cầu doanh nghiệp bổ sung, hoàn thiện hồ sơ. Doanh nghiệp không bổ sung, hoàn thiện được hồ sơ thì thực hiện thủ tục như đối với hàng hóa nhập khẩu bao gồm các quy định về chính sách thuế, chính sách mặt hàng đối với hàng hóa nhập khẩu;
+b.3) Thực hiện thủ tục hải quan đối với hàng hóa nhập khẩu quy định tại Điều 11 Thông tư này;
+b.4) Thực hiện thủ tục hoàn thuế, không thu thuế, xử lý thuế nộp thừa (nếu có) theo quy định.
+3. Đối với hàng hóa nhập khẩu phải hoàn nước gốc:
+a) Trường hợp chưa đăng ký tờ khai hải quan hoặc Tờ khai hải quan đã được đăng ký nhưng chưa được thông quan:
+a.1) Trách nhiệm của doanh nghiệp chuyển phát nhanh
+a.1.1) Gửi văn bản cho Chi cục Hải quan nơi lưu giữ hàng hóa phải gửi hoàn nước gốc trong đó nêu rõ: lý do chuyển hoàn, đề nghị được tái xuất, số vận tải đơn khi đưa hàng vào Việt Nam (nếu có); dự kiến thời gian chuyển hoàn, cửa khẩu tái xuất, phương tiện vận tải vận chuyển hàng tái xuất.
+a.1.2) Trường hợp địa điểm lưu giữ hàng hóa phải gửi hoàn nước gốc không thuộc địa bàn quản lý của Chi cục Hải quan cửa khẩu xuất thì thực hiện khai báo tờ khai vận chuyển độc lập để vận chuyển hàng hóa từ địa điểm lưu giữ hàng hóa đến cửa khẩu xuất.
+a.2) Trách nhiệm của Chi cục Hải quan nơi lưu giữ hàng hóa phải gửi hoàn nước gốc
+a.2.1) Tiếp nhận, kiểm tra văn bản của doanh nghiệp;
+a.2.2) Địa điểm lưu giữ hàng hóa thuộc địa bàn quản lý của Chi cục Hải quan cửa khẩu xuất:
+a.2.2.1) Trường hợp không có nghi vấn, thực hiện giám sát việc tái xuất hàng hóa;
+a.2.2.2) Trường hợp có dấu hiệu nghi vấn, kiểm tra thực tế toàn bộ lô hàng: Kết quả kiểm tra phù hợp, không có thông tin nghi vấn khác thì chấp thuận tái xuất. Nếu hàng hóa không đúng nội dung trên vận tải đơn hoặc có thông tin khẳng định lô hàng có vi phạm thì xử lý theo quy định.
+a.2.3) Địa điểm lưu giữ hàng hóa không thuộc địa bàn quản lý của Chi cục Hải quan cửa khẩu xuất:
+a.2.3.1) Trường hợp không có nghi vấn, thực hiện thủ tục hải quan đối với hàng hóa vận chuyển độc lập để vận chuyển hàng hóa từ địa điểm lưu giữ hàng hóa đến cửa khẩu xuất;
+a.2.3.2) Trường hợp có dấu hiệu nghi vấn, kiểm tra thực tế toàn bộ lô hàng: Kết quả kiểm tra phù hợp và không có thông tin nghi vấn khác thì thực hiện thủ tục hải quan đối với hàng hóa vận chuyển độc lập để vận chuyển hàng hóa đến cửa khẩu xuất. Nếu hàng hóa không đúng nội dung trên vận tải đơn hoặc có thông tin khẳng định lô hàng có vi phạm thì xử lý theo quy định.
+a.2.4) Hủy tờ khai hải quan trong trường hợp đã đăng ký tờ khai hải quan nhưng chưa được thông quan theo quy định.
+b) Trường hợp tờ khai hải quan đã được thông quan
+b.1) Trách nhiệm của doanh nghiệp chuyển phát nhanh
+b.1.1) Gửi hồ sơ hải quan cho cơ quan hải quan:
+b.1.1.1) Hồ sơ hải quan quy định tại khoản 3 Điều 8 Thông tư này, trừ giấy phép xuất khẩu, văn bản thông báo kết quả kiểm tra chuyên ngành;
+b.1.1.2) Tờ khai hải quan nhập khẩu ban đầu: 01 bản chụp đối với trường hợp khai trên tờ khai hải quan giấy.
+b.1.2) Thực hiện thủ tục hải quan như đối với hàng hóa xuất khẩu theo quy định tại Điều 11 Thông tư này. Khi khai tờ khai hải quan, ghi rõ số tờ khai nhập khẩu ban đầu tại ô số 26 trên mẫu HQ/2015/XK Phụ lục IV ban hành kèm theo Thông tư số 38/2015/TT-BTC (đối với tờ khai hải quan giấy), tại chỉ tiêu thông tin Phần ghi chú (đối với tờ khai hải quan điện tử).
+b.1.3) Thực hiện thủ tục hoàn thuế, không thu thuế, xử lý thuế nộp thừa (nếu có) theo quy định.
+b.2) Trách nhiệm của Chi cục Hải quan nơi lưu giữ hàng hóa phải gửi hoàn nước gốc
+b.2.1) Tiếp nhận hồ sơ hải quan do doanh nghiệp chuyển phát nhanh nộp;
+b.2.2) Kiểm tra, đối chiếu thông tin tờ khai nhập khẩu ban đầu vớ [...cắt bớt]
+CHUYỂN TIẾP: Điều 3. Điều khoản chuyển tiếp
+Trong thời gian nâng cấp Hệ thống xử lý dữ liệu điện tử hải quan để đáp ứng các quy định tại Thông tư này:
+1. Đối với doanh nghiệp được chỉ định theo quy định của Luật Bưu chính:
+Thực hiện thủ tục hải quan đối với gói, kiện hàng hóa xuất khẩu, nhập khẩu nhóm 1 theo quy định tại khoản 4 Điều 1 Thông tư này.
+2. Đối với doanh nghiệp chuyển phát nhanh:
+a) Thực hiện khai hải quan đối với hàng hóa xuất khẩu, nhập khẩu nhóm 1 theo quy định về khai hải quan trong trường hợp Hệ thống xử lý dữ liệu điện tử hải quan gặp sự cố.
+b) Thực hiện khai hải quan đối với hàng hóa xuất khẩu, nhập khẩu nhóm 2 theo chỉ tiêu thông tin được hướng dẫn tại phần A Phụ lục II ban hành kèm theo Thông tư số 191/2015/TT-BTC ngày 24/11/2015 của Bộ trưởng Bộ Tài chính.
+[amend] 29/2025/TT-BTC · hiệu lực 2025-07-09
+2. Thay thế cụm từ “Chi cục Hải quan” thành “Hải quan cửa khẩu, Hải quan ngoài cửa khẩu” tại khoản 2 Điều </t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1448,7 +1819,6 @@
           <t>actor_has_transitional</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -1459,18 +1829,80 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
           <t>id cũ vilextime:T3:provision:31d98de0-1f97-11f1-bcba-c5e53edd89aa:2019-10-16 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>191/2015/TT-BTC · hiệu lực 2016-01-01 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 12. Thủ tục hải quan, giám sát hải quan đối với hàng hóa lạc tuyến quốc tế (hàng hóa từ nước này lạc tuyến sang nước khác); hàng xuất khẩu nhưng không phát được cho người nhận, phải nhập khẩu trở lại để trả cho người gửi; hàng hóa nhập khẩu không phát được cho người nhận, phải hoàn nước gốc
+2. Đối với hàng hóa xuất khẩu nhưng không phát được cho người nhận, phải nhập khẩu trở lại để trả cho người gửi.
+a) Trách nhiệm của doanh nghiệp chuyển phát nhanh:
+a.1) Thực hiện thủ tục hải quan như đối với hàng hóa nhập khẩu theo quy định tại Điều 9, Điều 10 và Điều 11 Thông tư này;
+a.2) Ngoài hồ sơ hải quan quy định tại Điều 8 Thông tư này, doanh nghiệp chuyển phát nhanh phải nộp cho cơ quan hải quan:
+a.2.1) Văn bản của doanh nghiệp chuyển phát nhanh nước ngoài thông báo hàng hóa bị trả lại do không có người nhận hàng: 01 bản chụp;
+a.2.2) Tờ khai hải quan xuất khẩu ban đầu: 01 bản chụp đối với trường hợp khai trên tờ khai hải quan giấy.
+a.3) Thực hiện thủ tục hoàn thuế, không thu thuế (nếu có) theo quy định tại Thông tư số 38/2015/TT-BTC.
+b) Trách nhiệm của Chi cục Hải quan:
+b.1) Tiếp nhận hồ sơ do doanh nghiệp chuyển phát nhanh nộp;
+b.2) Thực hiện thủ tục hải quan đối với hàng hóa nhập khẩu quy định tại Điều 9, Điều 10 và Điều 11 Thông tư này (trừ giấy phép nhập khẩu, văn bản thông báo kết quả kiểm tra chuyên ngành);
+b.3) Thực hiện thủ tục hoàn thuế, không thu thuế (nếu có) theo quy định tại Thông tư số 38/2015/TT-BTC.</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[amend] 56/2019/TT-BTC · hiệu lực 2019-10-15
+11. Sửa đổi khoản 2, 3 Điều 12 như sau:
+“2. Đối với hàng hóa xuất khẩu nhưng không phát được cho người nhận, phải nhập khẩu trở lại để trả cho người gửi
+a) Trách nhiệm của doanh nghiệp chuyển phát nhanh:
+a.1) Thực hiện thủ tục hải quan như đối với hàng hóa nhập khẩu quy định tại Điều 11 Thông tư này. Khi khai tờ khai hải quan, ghi rõ số tờ khai xuất khẩu ban đầu tại ô số 32 trên Mẫu số HQ/2015/NK Phụ lục IV ban hành kèm theo Thông tư số 38/2015/TT-BTC (đối với tờ khai hải quan giấy), tại chỉ tiêu thông tin Phần ghi chú (đối với tờ khai điện tử).
+a.2) Nộp hồ sơ cho cơ quan hải quan:
+a.2.1) Hồ sơ hải quan quy định tại khoản 3 Điều 8 Thông tư này, trừ giấy phép nhập khẩu, văn bản thông báo kết quả kiểm tra chuyên ngành;
+a.2.2) Văn bản của doanh nghiệp chuyển phát nhanh nước ngoài thông báo hàng hóa bị trả lại do không có người nhận lại: 01 bản chụp;
+a.2.3) Tờ khai hải quan xuất khẩu ban đầu: 01 bản chụp đối với trường hợp khai trên tờ khai hải quan giấy.
+a.3) Thực hiện thủ tục hoàn thuế, không thu thuế, xử lý thuế nộp thừa (nếu có) theo quy định.
+b) Trách nhiệm của Chi cục Hải quan:
+b.1) Tiếp nhận hồ sơ do doanh nghiệp chuyển phát nhanh nộp;
+b.2) Kiểm tra, đối chiếu thông tin tờ khai xuất khẩu ban đầu với thông tin khai báo trên tờ khai nhập khẩu. Trường hợp kết quả kiểm tra phù hợp, thực hiện quy định tại điểm b.3 và điểm b.4 khoản này. Trường hợp kết quả kiểm tra không phù hợp, yêu cầu doanh nghiệp bổ sung, hoàn thiện hồ sơ. Doanh nghiệp không bổ sung, hoàn thiện được hồ sơ thì thực hiện thủ tục như đối với hàng hóa nhập khẩu bao gồm các quy định về chính sách thuế, chính sách mặt hàng đối với hàng hóa nhập khẩu;
+b.3) Thực hiện thủ tục hải quan đối với hàng hóa nhập khẩu quy định tại Điều 11 Thông tư này;
+b.4) Thực hiện thủ tục hoàn thuế, không thu thuế, xử lý thuế nộp thừa (nếu có) theo quy định.
+3. Đối với hàng hóa nhập khẩu phải hoàn nước gốc:
+a) Trường hợp chưa đăng ký tờ khai hải quan hoặc Tờ khai hải quan đã được đăng ký nhưng chưa được thông quan:
+a.1) Trách nhiệm của doanh nghiệp chuyển phát nhanh
+a.1.1) Gửi văn bản cho Chi cục Hải quan nơi lưu giữ hàng hóa phải gửi hoàn nước gốc trong đó nêu rõ: lý do chuyển hoàn, đề nghị được tái xuất, số vận tải đơn khi đưa hàng vào Việt Nam (nếu có); dự kiến thời gian chuyển hoàn, cửa khẩu tái xuất, phương tiện vận tải vận chuyển hàng tái xuất.
+a.1.2) Trường hợp địa điểm lưu giữ hàng hóa phải gửi hoàn nước gốc không thuộc địa bàn quản lý của Chi cục Hải quan cửa khẩu xuất thì thực hiện khai báo tờ khai vận chuyển độc lập để vận chuyển hàng hóa từ địa điểm lưu giữ hàng hóa đến cửa khẩu xuất.
+a.2) Trách nhiệm của Chi cục Hải quan nơi lưu giữ hàng hóa phải gửi hoàn nước gốc
+a.2.1) Tiếp nhận, kiểm tra văn bản của doanh nghiệp;
+a.2.2) Địa điểm lưu giữ hàng hóa thuộc địa bàn quản lý của Chi cục Hải quan cửa khẩu xuất:
+a.2.2.1) Trường hợp không có nghi vấn, thực hiện giám sát việc tái xuất hàng hóa;
+a.2.2.2) Trường hợp có dấu hiệu nghi vấn, kiểm tra thực tế toàn bộ lô hàng: Kết quả kiểm tra phù hợp, không có thông tin nghi vấn khác thì chấp thuận tái xuất. Nếu hàng hóa không đúng nội dung trên vận tải đơn hoặc có thông tin khẳng định lô hàng có vi phạm thì xử lý theo quy định.
+a.2.3) Địa điểm lưu giữ hàng hóa không thuộc địa bàn quản lý của Chi cục Hải quan cửa khẩu xuất:
+a.2.3.1) Trường hợp không có nghi vấn, thực hiện thủ tục hải quan đối với hàng hóa vận chuyển độc lập để vận chuyển hàng hóa từ địa điểm lưu giữ hàng hóa đến cửa khẩu xuất;
+a.2.3.2) Trường hợp có dấu hiệu nghi vấn, kiểm tra thực tế toàn bộ lô hàng: Kết quả kiểm tra phù hợp và không có thông tin nghi vấn khác thì thực hiện thủ tục hải quan đối với hàng hóa vận chuyển độc lập để vận chuyển hàng hóa đến cửa khẩu xuất. Nếu hàng hóa không đúng nội dung trên vận tải đơn hoặc có thông tin khẳng định lô hàng có vi phạm thì xử lý theo quy định.
+a.2.4) Hủy tờ khai hải quan trong trường hợp đã đăng ký tờ khai hải quan nhưng chưa được thông quan theo quy định.
+b) Trường hợp tờ khai hải quan đã được thông quan
+b.1) Trách nhiệm của doanh nghiệp chuyển phát nhanh
+b.1.1) Gửi hồ sơ hải quan cho cơ quan hải quan:
+b.1.1.1) Hồ sơ hải quan quy định tại khoản 3 Điều 8 Thông tư này, trừ giấy phép xuất khẩu, văn bản thông báo kết quả kiểm tra chuyên ngành;
+b.1.1.2) Tờ khai hải quan nhập khẩu ban đầu: 01 bản chụp đối với trường hợp khai trên tờ khai hải quan giấy.
+b.1.2) Thực hiện thủ tục hải quan như đối với hàng hóa xuất khẩu theo quy định tại Điều 11 Thông tư này. Khi khai tờ khai hải quan, ghi rõ số tờ khai nhập khẩu ban đầu tại ô số 26 trên mẫu HQ/2015/XK Phụ lục IV ban hành kèm theo Thông tư số 38/2015/TT-BTC (đối với tờ khai hải quan giấy), tại chỉ tiêu thông tin Phần ghi chú (đối với tờ khai hải quan điện tử).
+b.1.3) Thực hiện thủ tục hoàn thuế, không thu thuế, xử lý thuế nộp thừa (nếu có) theo quy định.
+b.2) Trách nhiệm của Chi cục Hải quan nơi lưu giữ hàng hóa phải gửi hoàn nước gốc
+b.2.1) Tiếp nhận hồ sơ hải quan do doanh nghiệp chuyển phát nhanh nộp;
+b.2.2) Kiểm tra, đối chiếu thông tin tờ khai nhập khẩu ban đầu vớ [...cắt bớt]
+CHUYỂN TIẾP: Điều 3. Điều khoản chuyển tiếp
+Trong thời gian nâng cấp Hệ thống xử lý dữ liệu điện tử hải quan để đáp ứng các quy định tại Thông tư này:
+1. Đối với doanh nghiệp được chỉ định theo quy định của Luật Bưu chính:
+Thực hiện thủ tục hải quan đối với gói, kiện hàng hóa xuất khẩu, nhập khẩu nhóm 1 theo quy định tại khoản 4 Điều 1 Thông tư này.
+2. Đối với doanh nghiệp chuyển phát nhanh:
+a) Thực hiện khai hải quan đối với hàng hóa xuất khẩu, nhập khẩu nhóm 1 theo quy định về khai hải quan trong trường hợp Hệ thống xử lý dữ liệu điện tử hải quan gặp sự cố.
+b) Thực hiện khai hải quan đối với hàng hóa xuất khẩu, nhập khẩu nhóm 2 theo chỉ tiêu thông tin được hướng dẫn tại phần A Phụ lục II ban hành kèm theo Thông tư số 191/2015/TT-BTC ngày 24/11/2015 của Bộ trưởng Bộ Tài chính.
+[amend] 29/2025/TT-BTC · hiệu lực 2025-07-09
+2. Thay thế cụm từ “Chi cục Hải quan” thành “Hải quan cửa khẩu, Hải quan ngoài cửa khẩu” tại khoản 2 Điều </t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1533,7 +1965,6 @@
           <t>actor_has_transitional</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -1544,18 +1975,80 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
         <is>
           <t>id cũ vilextime:T3:provision:31d98de0-1f97-11f1-bcba-c5e53edd89aa:2025-07-10 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>191/2015/TT-BTC · hiệu lực 2016-01-01 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 12. Thủ tục hải quan, giám sát hải quan đối với hàng hóa lạc tuyến quốc tế (hàng hóa từ nước này lạc tuyến sang nước khác); hàng xuất khẩu nhưng không phát được cho người nhận, phải nhập khẩu trở lại để trả cho người gửi; hàng hóa nhập khẩu không phát được cho người nhận, phải hoàn nước gốc
+2. Đối với hàng hóa xuất khẩu nhưng không phát được cho người nhận, phải nhập khẩu trở lại để trả cho người gửi.
+a) Trách nhiệm của doanh nghiệp chuyển phát nhanh:
+a.1) Thực hiện thủ tục hải quan như đối với hàng hóa nhập khẩu theo quy định tại Điều 9, Điều 10 và Điều 11 Thông tư này;
+a.2) Ngoài hồ sơ hải quan quy định tại Điều 8 Thông tư này, doanh nghiệp chuyển phát nhanh phải nộp cho cơ quan hải quan:
+a.2.1) Văn bản của doanh nghiệp chuyển phát nhanh nước ngoài thông báo hàng hóa bị trả lại do không có người nhận hàng: 01 bản chụp;
+a.2.2) Tờ khai hải quan xuất khẩu ban đầu: 01 bản chụp đối với trường hợp khai trên tờ khai hải quan giấy.
+a.3) Thực hiện thủ tục hoàn thuế, không thu thuế (nếu có) theo quy định tại Thông tư số 38/2015/TT-BTC.
+b) Trách nhiệm của Chi cục Hải quan:
+b.1) Tiếp nhận hồ sơ do doanh nghiệp chuyển phát nhanh nộp;
+b.2) Thực hiện thủ tục hải quan đối với hàng hóa nhập khẩu quy định tại Điều 9, Điều 10 và Điều 11 Thông tư này (trừ giấy phép nhập khẩu, văn bản thông báo kết quả kiểm tra chuyên ngành);
+b.3) Thực hiện thủ tục hoàn thuế, không thu thuế (nếu có) theo quy định tại Thông tư số 38/2015/TT-BTC.</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[amend] 56/2019/TT-BTC · hiệu lực 2019-10-15
+11. Sửa đổi khoản 2, 3 Điều 12 như sau:
+“2. Đối với hàng hóa xuất khẩu nhưng không phát được cho người nhận, phải nhập khẩu trở lại để trả cho người gửi
+a) Trách nhiệm của doanh nghiệp chuyển phát nhanh:
+a.1) Thực hiện thủ tục hải quan như đối với hàng hóa nhập khẩu quy định tại Điều 11 Thông tư này. Khi khai tờ khai hải quan, ghi rõ số tờ khai xuất khẩu ban đầu tại ô số 32 trên Mẫu số HQ/2015/NK Phụ lục IV ban hành kèm theo Thông tư số 38/2015/TT-BTC (đối với tờ khai hải quan giấy), tại chỉ tiêu thông tin Phần ghi chú (đối với tờ khai điện tử).
+a.2) Nộp hồ sơ cho cơ quan hải quan:
+a.2.1) Hồ sơ hải quan quy định tại khoản 3 Điều 8 Thông tư này, trừ giấy phép nhập khẩu, văn bản thông báo kết quả kiểm tra chuyên ngành;
+a.2.2) Văn bản của doanh nghiệp chuyển phát nhanh nước ngoài thông báo hàng hóa bị trả lại do không có người nhận lại: 01 bản chụp;
+a.2.3) Tờ khai hải quan xuất khẩu ban đầu: 01 bản chụp đối với trường hợp khai trên tờ khai hải quan giấy.
+a.3) Thực hiện thủ tục hoàn thuế, không thu thuế, xử lý thuế nộp thừa (nếu có) theo quy định.
+b) Trách nhiệm của Chi cục Hải quan:
+b.1) Tiếp nhận hồ sơ do doanh nghiệp chuyển phát nhanh nộp;
+b.2) Kiểm tra, đối chiếu thông tin tờ khai xuất khẩu ban đầu với thông tin khai báo trên tờ khai nhập khẩu. Trường hợp kết quả kiểm tra phù hợp, thực hiện quy định tại điểm b.3 và điểm b.4 khoản này. Trường hợp kết quả kiểm tra không phù hợp, yêu cầu doanh nghiệp bổ sung, hoàn thiện hồ sơ. Doanh nghiệp không bổ sung, hoàn thiện được hồ sơ thì thực hiện thủ tục như đối với hàng hóa nhập khẩu bao gồm các quy định về chính sách thuế, chính sách mặt hàng đối với hàng hóa nhập khẩu;
+b.3) Thực hiện thủ tục hải quan đối với hàng hóa nhập khẩu quy định tại Điều 11 Thông tư này;
+b.4) Thực hiện thủ tục hoàn thuế, không thu thuế, xử lý thuế nộp thừa (nếu có) theo quy định.
+3. Đối với hàng hóa nhập khẩu phải hoàn nước gốc:
+a) Trường hợp chưa đăng ký tờ khai hải quan hoặc Tờ khai hải quan đã được đăng ký nhưng chưa được thông quan:
+a.1) Trách nhiệm của doanh nghiệp chuyển phát nhanh
+a.1.1) Gửi văn bản cho Chi cục Hải quan nơi lưu giữ hàng hóa phải gửi hoàn nước gốc trong đó nêu rõ: lý do chuyển hoàn, đề nghị được tái xuất, số vận tải đơn khi đưa hàng vào Việt Nam (nếu có); dự kiến thời gian chuyển hoàn, cửa khẩu tái xuất, phương tiện vận tải vận chuyển hàng tái xuất.
+a.1.2) Trường hợp địa điểm lưu giữ hàng hóa phải gửi hoàn nước gốc không thuộc địa bàn quản lý của Chi cục Hải quan cửa khẩu xuất thì thực hiện khai báo tờ khai vận chuyển độc lập để vận chuyển hàng hóa từ địa điểm lưu giữ hàng hóa đến cửa khẩu xuất.
+a.2) Trách nhiệm của Chi cục Hải quan nơi lưu giữ hàng hóa phải gửi hoàn nước gốc
+a.2.1) Tiếp nhận, kiểm tra văn bản của doanh nghiệp;
+a.2.2) Địa điểm lưu giữ hàng hóa thuộc địa bàn quản lý của Chi cục Hải quan cửa khẩu xuất:
+a.2.2.1) Trường hợp không có nghi vấn, thực hiện giám sát việc tái xuất hàng hóa;
+a.2.2.2) Trường hợp có dấu hiệu nghi vấn, kiểm tra thực tế toàn bộ lô hàng: Kết quả kiểm tra phù hợp, không có thông tin nghi vấn khác thì chấp thuận tái xuất. Nếu hàng hóa không đúng nội dung trên vận tải đơn hoặc có thông tin khẳng định lô hàng có vi phạm thì xử lý theo quy định.
+a.2.3) Địa điểm lưu giữ hàng hóa không thuộc địa bàn quản lý của Chi cục Hải quan cửa khẩu xuất:
+a.2.3.1) Trường hợp không có nghi vấn, thực hiện thủ tục hải quan đối với hàng hóa vận chuyển độc lập để vận chuyển hàng hóa từ địa điểm lưu giữ hàng hóa đến cửa khẩu xuất;
+a.2.3.2) Trường hợp có dấu hiệu nghi vấn, kiểm tra thực tế toàn bộ lô hàng: Kết quả kiểm tra phù hợp và không có thông tin nghi vấn khác thì thực hiện thủ tục hải quan đối với hàng hóa vận chuyển độc lập để vận chuyển hàng hóa đến cửa khẩu xuất. Nếu hàng hóa không đúng nội dung trên vận tải đơn hoặc có thông tin khẳng định lô hàng có vi phạm thì xử lý theo quy định.
+a.2.4) Hủy tờ khai hải quan trong trường hợp đã đăng ký tờ khai hải quan nhưng chưa được thông quan theo quy định.
+b) Trường hợp tờ khai hải quan đã được thông quan
+b.1) Trách nhiệm của doanh nghiệp chuyển phát nhanh
+b.1.1) Gửi hồ sơ hải quan cho cơ quan hải quan:
+b.1.1.1) Hồ sơ hải quan quy định tại khoản 3 Điều 8 Thông tư này, trừ giấy phép xuất khẩu, văn bản thông báo kết quả kiểm tra chuyên ngành;
+b.1.1.2) Tờ khai hải quan nhập khẩu ban đầu: 01 bản chụp đối với trường hợp khai trên tờ khai hải quan giấy.
+b.1.2) Thực hiện thủ tục hải quan như đối với hàng hóa xuất khẩu theo quy định tại Điều 11 Thông tư này. Khi khai tờ khai hải quan, ghi rõ số tờ khai nhập khẩu ban đầu tại ô số 26 trên mẫu HQ/2015/XK Phụ lục IV ban hành kèm theo Thông tư số 38/2015/TT-BTC (đối với tờ khai hải quan giấy), tại chỉ tiêu thông tin Phần ghi chú (đối với tờ khai hải quan điện tử).
+b.1.3) Thực hiện thủ tục hoàn thuế, không thu thuế, xử lý thuế nộp thừa (nếu có) theo quy định.
+b.2) Trách nhiệm của Chi cục Hải quan nơi lưu giữ hàng hóa phải gửi hoàn nước gốc
+b.2.1) Tiếp nhận hồ sơ hải quan do doanh nghiệp chuyển phát nhanh nộp;
+b.2.2) Kiểm tra, đối chiếu thông tin tờ khai nhập khẩu ban đầu vớ [...cắt bớt]
+CHUYỂN TIẾP: Điều 3. Điều khoản chuyển tiếp
+Trong thời gian nâng cấp Hệ thống xử lý dữ liệu điện tử hải quan để đáp ứng các quy định tại Thông tư này:
+1. Đối với doanh nghiệp được chỉ định theo quy định của Luật Bưu chính:
+Thực hiện thủ tục hải quan đối với gói, kiện hàng hóa xuất khẩu, nhập khẩu nhóm 1 theo quy định tại khoản 4 Điều 1 Thông tư này.
+2. Đối với doanh nghiệp chuyển phát nhanh:
+a) Thực hiện khai hải quan đối với hàng hóa xuất khẩu, nhập khẩu nhóm 1 theo quy định về khai hải quan trong trường hợp Hệ thống xử lý dữ liệu điện tử hải quan gặp sự cố.
+b) Thực hiện khai hải quan đối với hàng hóa xuất khẩu, nhập khẩu nhóm 2 theo chỉ tiêu thông tin được hướng dẫn tại phần A Phụ lục II ban hành kèm theo Thông tư số 191/2015/TT-BTC ngày 24/11/2015 của Bộ trưởng Bộ Tài chính.
+[amend] 29/2025/TT-BTC · hiệu lực 2025-07-09
+2. Thay thế cụm từ “Chi cục Hải quan” thành “Hải quan cửa khẩu, Hải quan ngoài cửa khẩu” tại khoản 2 Điều </t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1618,7 +2111,6 @@
           <t>actor_has_transitional</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -1629,18 +2121,59 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
         <is>
           <t>id cũ vilextime:T3:provision:35a63f90-2474-11f1-91a6-77384b04742d:2019-05-02 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>27/2019/NĐ-CP · hiệu lực 2019-05-01 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 33. Trình tự thủ tục cấp giấy phép hoạt động đo đạc và bản đồ
+4. Cấp giấy phép
+a) Trong thời hạn 02 ngày làm việc kể từ ngày nhận được biên bản thẩm định hồ sơ đề nghị cấp giấy phép hoạt động đo đạc và bản đồ, thủ trưởng cơ quan quản lý chuyên ngành về đo đạc và bản đồ thuộc Bộ Tài nguyên và Môi trường phê duyệt, cấp giấy phép hoạt động đo đạc và bản đồ;
+b) Cơ quan quản lý chuyên ngành về đo đạc và bản đồ thuộc Bộ Tài nguyên và Môi trường thông báo cho tổ chức về việc hoàn thành cấp giấy phép, trả giấy phép hoạt động đo đạc và bản đồ, hồ sơ đề nghị cấp giấy phép cho tổ chức, gửi tệp tin chứa bản chụp giấy phép cho cơ quan chuyên môn về tài nguyên và môi trường thuộc ủy ban nhân dân cấp tỉnh để phối hợp quản lý đối với các tổ chức do cơ quan chuyên môn về tài nguyên và môi trường thuộc ủy ban nhân dân cấp tỉnh thẩm định.</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 136/2021/NĐ-CP · hiệu lực 2022-02-15
+c) Sửa đổi, bổ sung khoản 4 như sau:
+"4. Cấp giấy phép
+a) Trong thời hạn 03 ngày làm việc kể từ ngày nhận được biên bản thẩm định kèm hồ sơ đề nghị cấp giấy phép hoạt động đo đạc và bản đồ, thủ trưởng cơ quan quản lý chuyên ngành về đo đạc và bản đồ thuộc Bộ Tài nguyên và Môi trường phê duyệt, cấp giấy phép hoạt động đo đạc và bản đồ;
+b) Cơ quan quản lý chuyên ngành về đo đạc và bản đồ thuộc Bộ Tài nguyên và Môi trường thông báo cho tổ chức về việc hoàn thành cấp giấy phép. Trong thời hạn 01 ngày làm việc kể từ ngày thông báo, cơ quan quản lý chuyên ngành về đo đạc và bản đồ thuộc Bộ Tài nguyên và Môi trường trả giấy phép hoạt động đo đạc và bản đồ cho tổ chức qua dịch vụ bưu chính, gửi tệp tin chứa bản chụp giấy phép cho cơ quan chuyên môn về tài nguyên và môi trường thuộc Ủy ban nhân dân cấp tỉnh để phối hợp quản lý đối với các tổ chức do cơ quan chuyên môn về tài nguyên và môi trường thuộc Ủy ban nhân dân cấp tỉnh thẩm định.".
+CHUYỂN TIẾP: Điều 3. Điều khoản chuyển tiếp
+Hồ sơ đề nghị cấp giấy phép hoạt động đo đạc và bản đồ, chứng chỉ hành nghề đo đạc và bản đồ đã được cơ quan nhà nước có thẩm quyền tiếp nhận để giải quyết theo thủ tục hành chính về đo đạc và bản đồ trước ngày Nghị định này có hiệu lực thi hành thì được giải quyết theo quy định tại Nghị định số 27/2019/NĐ-CP ngày 13 tháng 3 năm 2019 của Chính phủ quy định chi tiết một số điều của Luật Đo đạc và bản đồ.
+[amend] 39/2026/NĐ-CP · hiệu lực 2026-01-25
+a) Thay thế cụm từ “Bộ Tài nguyên và Môi trường” bằng cụm từ “Bộ Nông nghiệp và Môi trường” tại khoản 4 Điều 4 (được sửa đổi, bổ sung bởi khoản 1 Điều 1 Nghị định số 136/2021/NĐ-CP); khoản 1 và khoản 2 Điều 9; khoản 2 Điều 14; điểm b khoản 6 và điểm d khoản 7 Điều 17; khoản 2 và khoản 3 Điều 18; khoản 3 Điều 24; khoản 3 Điều 26; khoản 10 Điều 27; khoản 3 và khoản 4 Điều 28; khoản 1, khoản 3 và khoản 4 Điều 33 (được sửa đổi, bổ sung bởi khoản 8 Điều 1 Nghị định số 136/2021/NĐ-CP); điểm c khoản 2 Điều 34 (được sửa đổi, bổ sung bởi khoản 9 Điều 1 Nghị định số 136/2021/NĐ-CP); Điều 36 (được sửa đổi, bổ sung bởi khoản 11 Điều 1 Nghị định số 136/2021/NĐ-CP); khoản 3 Điều 37 (được sửa đổi, bổ sung bởi điểm b khoản 12 Điều 1 Nghị định số 136/2021/NĐ-CP); khoản 1 Điều 39 (được sửa đổi, bổ sung bởi khoản 14 Điều 1 Nghị định số 136/2021/NĐ-CP); khoản 2 Điều 40; khoản 2 Điều 41; điểm a khoản 2 Điều 43; khoản 2 Điều 45; điểm a khoản 3 Điều 46 (được sửa đổi, bổ sung bởi điểm b khoản 16 Điều 1 Nghị định số 136/2021/NĐ-CP); khoản 2 Điều 51; khoản 2 Điều 52 của Nghị định số 27/2019/NĐ-CP; khoản 1 Điều 4 Nghị định số 136/2021/NĐ-CP; Phụ lục I ban hành kèm theo Nghị định số 27/2019/NĐ-CP;
+CHUYỂN TIẾP: 3. Điều khoản chuyển tiếp:
+a) Hồ sơ đề nghị cấp giấy phép hoạt động đo đạc và bản đồ, chứng chỉ hành nghề đo đạc và bản đồ đã được cơ quan nhà nước có thẩm quyền tiếp nhận để giải quyết theo thủ tục hành chính về đo đạc và bản đồ trước ngày Nghị định này có hiệu lực thi hành thì được giải quyết theo quy định tại Nghị định số 27/2019/NĐ-CP ngày 13 tháng 3 năm 2019 của Chính phủ quy định chi tiết một số điều của Luật Đo đạc và bản đồ, Nghị định số 136/2021/NĐ-CP ngày 31 tháng 12 năm 2021 của Chính phủ sửa đổi, bổ sung một số điều của Nghị định số 27/2019/NĐ-CP ngày 13 tháng 3 năm 2019 của Chính phủ quy định chi tiết một số điều của Luật Đo đạc và bản đồ, Nghị định số 22/2023/NĐ-CP ngày 12 tháng 5 năm 2023 của Chính phủ sửa đổi, bổ sung một số điều của các Nghị định liên quan đến hoạt động kinh doanh trong lĩnh vực tài nguyên và môi trường.
+b) Trường hợp tổ chức lại các đơn vị sự nghiệp công lập theo hình thức hợp nhất, sáp nhập mà trong đó một hoặc nhiều đơn vị sự nghiệp công lập đã được cấp giấy phép hoạt động đo đạc và bản đồ thì tổ chức sau hợp nhất, sáp nhập được tiếp tục sử dụng giấy phép để thực hiện quyền và nghĩa vụ trong phạm vi giấy phép theo thời hạn của giấy phép hoạt động đo đạc và bản đồ đã cấp nhưng không quá 01 năm kể từ ngày tổ chức lại đơn vị sự nghiệp công lập.
+Nơi nhận:
+- Ban Bí thư Trung ương Đảng;
+- Thủ tướng, các Phó Thủ tướng Chính phủ;
+- Các bộ, cơ quan ngang bộ, cơ quan thuộc Chính phủ;
+- HĐND, UBND các tỉnh, thành phố trực thuộc trung ương;
+- Văn phòng Trung ương và các Ban của Đảng;
+- Văn phòng Tổng Bí thư;
+- Văn phòng Chủ tịch nước;
+- Hội đồng Dân tộc và các Ủy ban của Quốc hội;
+- Văn phòng Quốc hội;
+- Tòa án nhân dân tối cao;
+- Viện kiểm sát nhân dân tối cao;
+- Kiểm toán nhà nước;
+- Ủy ban Trung ương Mặt trận Tổ quốc Việt Nam;
+- Cơ quan trung ương của các tổ chức chính trị - xã hội;
+- VPCP: BTCN, các PCN, Trợ lý TTg, TGĐ Cổng TTĐT,
+các Vụ, Cục, đơn vị trực thuộc, Công báo;
+- Lưu: VT, NN (2b).
+TM. CHÍNH PHỦ
+KT. THỦ TƯỚNG
+PHÓ THỦ TƯỚNG
+(Đã ký)
+Trần Hồng Hà</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1703,7 +2236,6 @@
           <t>actor_has_transitional</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -1714,18 +2246,59 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
         <is>
           <t>id cũ vilextime:T3:provision:35a63f90-2474-11f1-91a6-77384b04742d:2022-02-16 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>27/2019/NĐ-CP · hiệu lực 2019-05-01 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 33. Trình tự thủ tục cấp giấy phép hoạt động đo đạc và bản đồ
+4. Cấp giấy phép
+a) Trong thời hạn 02 ngày làm việc kể từ ngày nhận được biên bản thẩm định hồ sơ đề nghị cấp giấy phép hoạt động đo đạc và bản đồ, thủ trưởng cơ quan quản lý chuyên ngành về đo đạc và bản đồ thuộc Bộ Tài nguyên và Môi trường phê duyệt, cấp giấy phép hoạt động đo đạc và bản đồ;
+b) Cơ quan quản lý chuyên ngành về đo đạc và bản đồ thuộc Bộ Tài nguyên và Môi trường thông báo cho tổ chức về việc hoàn thành cấp giấy phép, trả giấy phép hoạt động đo đạc và bản đồ, hồ sơ đề nghị cấp giấy phép cho tổ chức, gửi tệp tin chứa bản chụp giấy phép cho cơ quan chuyên môn về tài nguyên và môi trường thuộc ủy ban nhân dân cấp tỉnh để phối hợp quản lý đối với các tổ chức do cơ quan chuyên môn về tài nguyên và môi trường thuộc ủy ban nhân dân cấp tỉnh thẩm định.</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 136/2021/NĐ-CP · hiệu lực 2022-02-15
+c) Sửa đổi, bổ sung khoản 4 như sau:
+"4. Cấp giấy phép
+a) Trong thời hạn 03 ngày làm việc kể từ ngày nhận được biên bản thẩm định kèm hồ sơ đề nghị cấp giấy phép hoạt động đo đạc và bản đồ, thủ trưởng cơ quan quản lý chuyên ngành về đo đạc và bản đồ thuộc Bộ Tài nguyên và Môi trường phê duyệt, cấp giấy phép hoạt động đo đạc và bản đồ;
+b) Cơ quan quản lý chuyên ngành về đo đạc và bản đồ thuộc Bộ Tài nguyên và Môi trường thông báo cho tổ chức về việc hoàn thành cấp giấy phép. Trong thời hạn 01 ngày làm việc kể từ ngày thông báo, cơ quan quản lý chuyên ngành về đo đạc và bản đồ thuộc Bộ Tài nguyên và Môi trường trả giấy phép hoạt động đo đạc và bản đồ cho tổ chức qua dịch vụ bưu chính, gửi tệp tin chứa bản chụp giấy phép cho cơ quan chuyên môn về tài nguyên và môi trường thuộc Ủy ban nhân dân cấp tỉnh để phối hợp quản lý đối với các tổ chức do cơ quan chuyên môn về tài nguyên và môi trường thuộc Ủy ban nhân dân cấp tỉnh thẩm định.".
+CHUYỂN TIẾP: Điều 3. Điều khoản chuyển tiếp
+Hồ sơ đề nghị cấp giấy phép hoạt động đo đạc và bản đồ, chứng chỉ hành nghề đo đạc và bản đồ đã được cơ quan nhà nước có thẩm quyền tiếp nhận để giải quyết theo thủ tục hành chính về đo đạc và bản đồ trước ngày Nghị định này có hiệu lực thi hành thì được giải quyết theo quy định tại Nghị định số 27/2019/NĐ-CP ngày 13 tháng 3 năm 2019 của Chính phủ quy định chi tiết một số điều của Luật Đo đạc và bản đồ.
+[amend] 39/2026/NĐ-CP · hiệu lực 2026-01-25
+a) Thay thế cụm từ “Bộ Tài nguyên và Môi trường” bằng cụm từ “Bộ Nông nghiệp và Môi trường” tại khoản 4 Điều 4 (được sửa đổi, bổ sung bởi khoản 1 Điều 1 Nghị định số 136/2021/NĐ-CP); khoản 1 và khoản 2 Điều 9; khoản 2 Điều 14; điểm b khoản 6 và điểm d khoản 7 Điều 17; khoản 2 và khoản 3 Điều 18; khoản 3 Điều 24; khoản 3 Điều 26; khoản 10 Điều 27; khoản 3 và khoản 4 Điều 28; khoản 1, khoản 3 và khoản 4 Điều 33 (được sửa đổi, bổ sung bởi khoản 8 Điều 1 Nghị định số 136/2021/NĐ-CP); điểm c khoản 2 Điều 34 (được sửa đổi, bổ sung bởi khoản 9 Điều 1 Nghị định số 136/2021/NĐ-CP); Điều 36 (được sửa đổi, bổ sung bởi khoản 11 Điều 1 Nghị định số 136/2021/NĐ-CP); khoản 3 Điều 37 (được sửa đổi, bổ sung bởi điểm b khoản 12 Điều 1 Nghị định số 136/2021/NĐ-CP); khoản 1 Điều 39 (được sửa đổi, bổ sung bởi khoản 14 Điều 1 Nghị định số 136/2021/NĐ-CP); khoản 2 Điều 40; khoản 2 Điều 41; điểm a khoản 2 Điều 43; khoản 2 Điều 45; điểm a khoản 3 Điều 46 (được sửa đổi, bổ sung bởi điểm b khoản 16 Điều 1 Nghị định số 136/2021/NĐ-CP); khoản 2 Điều 51; khoản 2 Điều 52 của Nghị định số 27/2019/NĐ-CP; khoản 1 Điều 4 Nghị định số 136/2021/NĐ-CP; Phụ lục I ban hành kèm theo Nghị định số 27/2019/NĐ-CP;
+CHUYỂN TIẾP: 3. Điều khoản chuyển tiếp:
+a) Hồ sơ đề nghị cấp giấy phép hoạt động đo đạc và bản đồ, chứng chỉ hành nghề đo đạc và bản đồ đã được cơ quan nhà nước có thẩm quyền tiếp nhận để giải quyết theo thủ tục hành chính về đo đạc và bản đồ trước ngày Nghị định này có hiệu lực thi hành thì được giải quyết theo quy định tại Nghị định số 27/2019/NĐ-CP ngày 13 tháng 3 năm 2019 của Chính phủ quy định chi tiết một số điều của Luật Đo đạc và bản đồ, Nghị định số 136/2021/NĐ-CP ngày 31 tháng 12 năm 2021 của Chính phủ sửa đổi, bổ sung một số điều của Nghị định số 27/2019/NĐ-CP ngày 13 tháng 3 năm 2019 của Chính phủ quy định chi tiết một số điều của Luật Đo đạc và bản đồ, Nghị định số 22/2023/NĐ-CP ngày 12 tháng 5 năm 2023 của Chính phủ sửa đổi, bổ sung một số điều của các Nghị định liên quan đến hoạt động kinh doanh trong lĩnh vực tài nguyên và môi trường.
+b) Trường hợp tổ chức lại các đơn vị sự nghiệp công lập theo hình thức hợp nhất, sáp nhập mà trong đó một hoặc nhiều đơn vị sự nghiệp công lập đã được cấp giấy phép hoạt động đo đạc và bản đồ thì tổ chức sau hợp nhất, sáp nhập được tiếp tục sử dụng giấy phép để thực hiện quyền và nghĩa vụ trong phạm vi giấy phép theo thời hạn của giấy phép hoạt động đo đạc và bản đồ đã cấp nhưng không quá 01 năm kể từ ngày tổ chức lại đơn vị sự nghiệp công lập.
+Nơi nhận:
+- Ban Bí thư Trung ương Đảng;
+- Thủ tướng, các Phó Thủ tướng Chính phủ;
+- Các bộ, cơ quan ngang bộ, cơ quan thuộc Chính phủ;
+- HĐND, UBND các tỉnh, thành phố trực thuộc trung ương;
+- Văn phòng Trung ương và các Ban của Đảng;
+- Văn phòng Tổng Bí thư;
+- Văn phòng Chủ tịch nước;
+- Hội đồng Dân tộc và các Ủy ban của Quốc hội;
+- Văn phòng Quốc hội;
+- Tòa án nhân dân tối cao;
+- Viện kiểm sát nhân dân tối cao;
+- Kiểm toán nhà nước;
+- Ủy ban Trung ương Mặt trận Tổ quốc Việt Nam;
+- Cơ quan trung ương của các tổ chức chính trị - xã hội;
+- VPCP: BTCN, các PCN, Trợ lý TTg, TGĐ Cổng TTĐT,
+các Vụ, Cục, đơn vị trực thuộc, Công báo;
+- Lưu: VT, NN (2b).
+TM. CHÍNH PHỦ
+KT. THỦ TƯỚNG
+PHÓ THỦ TƯỚNG
+(Đã ký)
+Trần Hồng Hà</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1788,7 +2361,6 @@
           <t>actor_has_transitional</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -1799,18 +2371,59 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
         <is>
           <t>id cũ vilextime:T3:provision:35a63f90-2474-11f1-91a6-77384b04742d:2026-01-26 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>27/2019/NĐ-CP · hiệu lực 2019-05-01 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 33. Trình tự thủ tục cấp giấy phép hoạt động đo đạc và bản đồ
+4. Cấp giấy phép
+a) Trong thời hạn 02 ngày làm việc kể từ ngày nhận được biên bản thẩm định hồ sơ đề nghị cấp giấy phép hoạt động đo đạc và bản đồ, thủ trưởng cơ quan quản lý chuyên ngành về đo đạc và bản đồ thuộc Bộ Tài nguyên và Môi trường phê duyệt, cấp giấy phép hoạt động đo đạc và bản đồ;
+b) Cơ quan quản lý chuyên ngành về đo đạc và bản đồ thuộc Bộ Tài nguyên và Môi trường thông báo cho tổ chức về việc hoàn thành cấp giấy phép, trả giấy phép hoạt động đo đạc và bản đồ, hồ sơ đề nghị cấp giấy phép cho tổ chức, gửi tệp tin chứa bản chụp giấy phép cho cơ quan chuyên môn về tài nguyên và môi trường thuộc ủy ban nhân dân cấp tỉnh để phối hợp quản lý đối với các tổ chức do cơ quan chuyên môn về tài nguyên và môi trường thuộc ủy ban nhân dân cấp tỉnh thẩm định.</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 136/2021/NĐ-CP · hiệu lực 2022-02-15
+c) Sửa đổi, bổ sung khoản 4 như sau:
+"4. Cấp giấy phép
+a) Trong thời hạn 03 ngày làm việc kể từ ngày nhận được biên bản thẩm định kèm hồ sơ đề nghị cấp giấy phép hoạt động đo đạc và bản đồ, thủ trưởng cơ quan quản lý chuyên ngành về đo đạc và bản đồ thuộc Bộ Tài nguyên và Môi trường phê duyệt, cấp giấy phép hoạt động đo đạc và bản đồ;
+b) Cơ quan quản lý chuyên ngành về đo đạc và bản đồ thuộc Bộ Tài nguyên và Môi trường thông báo cho tổ chức về việc hoàn thành cấp giấy phép. Trong thời hạn 01 ngày làm việc kể từ ngày thông báo, cơ quan quản lý chuyên ngành về đo đạc và bản đồ thuộc Bộ Tài nguyên và Môi trường trả giấy phép hoạt động đo đạc và bản đồ cho tổ chức qua dịch vụ bưu chính, gửi tệp tin chứa bản chụp giấy phép cho cơ quan chuyên môn về tài nguyên và môi trường thuộc Ủy ban nhân dân cấp tỉnh để phối hợp quản lý đối với các tổ chức do cơ quan chuyên môn về tài nguyên và môi trường thuộc Ủy ban nhân dân cấp tỉnh thẩm định.".
+CHUYỂN TIẾP: Điều 3. Điều khoản chuyển tiếp
+Hồ sơ đề nghị cấp giấy phép hoạt động đo đạc và bản đồ, chứng chỉ hành nghề đo đạc và bản đồ đã được cơ quan nhà nước có thẩm quyền tiếp nhận để giải quyết theo thủ tục hành chính về đo đạc và bản đồ trước ngày Nghị định này có hiệu lực thi hành thì được giải quyết theo quy định tại Nghị định số 27/2019/NĐ-CP ngày 13 tháng 3 năm 2019 của Chính phủ quy định chi tiết một số điều của Luật Đo đạc và bản đồ.
+[amend] 39/2026/NĐ-CP · hiệu lực 2026-01-25
+a) Thay thế cụm từ “Bộ Tài nguyên và Môi trường” bằng cụm từ “Bộ Nông nghiệp và Môi trường” tại khoản 4 Điều 4 (được sửa đổi, bổ sung bởi khoản 1 Điều 1 Nghị định số 136/2021/NĐ-CP); khoản 1 và khoản 2 Điều 9; khoản 2 Điều 14; điểm b khoản 6 và điểm d khoản 7 Điều 17; khoản 2 và khoản 3 Điều 18; khoản 3 Điều 24; khoản 3 Điều 26; khoản 10 Điều 27; khoản 3 và khoản 4 Điều 28; khoản 1, khoản 3 và khoản 4 Điều 33 (được sửa đổi, bổ sung bởi khoản 8 Điều 1 Nghị định số 136/2021/NĐ-CP); điểm c khoản 2 Điều 34 (được sửa đổi, bổ sung bởi khoản 9 Điều 1 Nghị định số 136/2021/NĐ-CP); Điều 36 (được sửa đổi, bổ sung bởi khoản 11 Điều 1 Nghị định số 136/2021/NĐ-CP); khoản 3 Điều 37 (được sửa đổi, bổ sung bởi điểm b khoản 12 Điều 1 Nghị định số 136/2021/NĐ-CP); khoản 1 Điều 39 (được sửa đổi, bổ sung bởi khoản 14 Điều 1 Nghị định số 136/2021/NĐ-CP); khoản 2 Điều 40; khoản 2 Điều 41; điểm a khoản 2 Điều 43; khoản 2 Điều 45; điểm a khoản 3 Điều 46 (được sửa đổi, bổ sung bởi điểm b khoản 16 Điều 1 Nghị định số 136/2021/NĐ-CP); khoản 2 Điều 51; khoản 2 Điều 52 của Nghị định số 27/2019/NĐ-CP; khoản 1 Điều 4 Nghị định số 136/2021/NĐ-CP; Phụ lục I ban hành kèm theo Nghị định số 27/2019/NĐ-CP;
+CHUYỂN TIẾP: 3. Điều khoản chuyển tiếp:
+a) Hồ sơ đề nghị cấp giấy phép hoạt động đo đạc và bản đồ, chứng chỉ hành nghề đo đạc và bản đồ đã được cơ quan nhà nước có thẩm quyền tiếp nhận để giải quyết theo thủ tục hành chính về đo đạc và bản đồ trước ngày Nghị định này có hiệu lực thi hành thì được giải quyết theo quy định tại Nghị định số 27/2019/NĐ-CP ngày 13 tháng 3 năm 2019 của Chính phủ quy định chi tiết một số điều của Luật Đo đạc và bản đồ, Nghị định số 136/2021/NĐ-CP ngày 31 tháng 12 năm 2021 của Chính phủ sửa đổi, bổ sung một số điều của Nghị định số 27/2019/NĐ-CP ngày 13 tháng 3 năm 2019 của Chính phủ quy định chi tiết một số điều của Luật Đo đạc và bản đồ, Nghị định số 22/2023/NĐ-CP ngày 12 tháng 5 năm 2023 của Chính phủ sửa đổi, bổ sung một số điều của các Nghị định liên quan đến hoạt động kinh doanh trong lĩnh vực tài nguyên và môi trường.
+b) Trường hợp tổ chức lại các đơn vị sự nghiệp công lập theo hình thức hợp nhất, sáp nhập mà trong đó một hoặc nhiều đơn vị sự nghiệp công lập đã được cấp giấy phép hoạt động đo đạc và bản đồ thì tổ chức sau hợp nhất, sáp nhập được tiếp tục sử dụng giấy phép để thực hiện quyền và nghĩa vụ trong phạm vi giấy phép theo thời hạn của giấy phép hoạt động đo đạc và bản đồ đã cấp nhưng không quá 01 năm kể từ ngày tổ chức lại đơn vị sự nghiệp công lập.
+Nơi nhận:
+- Ban Bí thư Trung ương Đảng;
+- Thủ tướng, các Phó Thủ tướng Chính phủ;
+- Các bộ, cơ quan ngang bộ, cơ quan thuộc Chính phủ;
+- HĐND, UBND các tỉnh, thành phố trực thuộc trung ương;
+- Văn phòng Trung ương và các Ban của Đảng;
+- Văn phòng Tổng Bí thư;
+- Văn phòng Chủ tịch nước;
+- Hội đồng Dân tộc và các Ủy ban của Quốc hội;
+- Văn phòng Quốc hội;
+- Tòa án nhân dân tối cao;
+- Viện kiểm sát nhân dân tối cao;
+- Kiểm toán nhà nước;
+- Ủy ban Trung ương Mặt trận Tổ quốc Việt Nam;
+- Cơ quan trung ương của các tổ chức chính trị - xã hội;
+- VPCP: BTCN, các PCN, Trợ lý TTg, TGĐ Cổng TTĐT,
+các Vụ, Cục, đơn vị trực thuộc, Công báo;
+- Lưu: VT, NN (2b).
+TM. CHÍNH PHỦ
+KT. THỦ TƯỚNG
+PHÓ THỦ TƯỚNG
+(Đã ký)
+Trần Hồng Hà</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1868,7 +2481,6 @@
           <t>227/2025/NĐ-CP; 91/2024/NĐ-CP</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>document_ended 2024-07-15 bao_dong_gia; document_ended 2025-08-16 bao_dong_gia</t>
@@ -1884,18 +2496,62 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
         <is>
           <t>id cũ vilextime:T3:provision:387a3620-2c82-11f1-8d74-79a15475fa71:2019-01-02 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr"/>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>156/2018/NĐ-CP · hiệu lực 2019-01-01 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 28. Khai thác lâm sản trong rừng sản xuất là rừng tự nhiên
+2. Khai thác tận dụng gỗ rừng tự nhiên
+a) Đối tượng: trên diện tích rừng chuyển mục đích sử dụng rừng sang mục đích khác; khi thực hiện các biện pháp lâm sinh; phục vụ công tác đào tạo và nhiệm vụ nghiên cứu khoa học;
+b) Điều kiện: phải có quyết định phê duyệt của cơ quan có thẩm quyền về chuyển mục đích sử dụng rừng sang mục đích khác; dự án lâm sinh; chương trình, đề tài nghiên cứu khoa học.</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[amend] 91/2024/NĐ-CP · hiệu lực 2024-07-18
+14. Sửa đổi, bổ sung khoản 2 Điều 28 như sau:
+“2. Khai thác tận dụng gỗ rừng tự nhiên
+a) Đối tượng: cây gỗ trên diện tích rừng được cấp có thẩm quyền quyết định chuyển mục đích sử dụng rừng sang mục đích khác theo quy định; cây gỗ chặt hạ khi thực hiện các biện pháp kỹ thuật lâm sinh, phục vụ công tác đào tạo và nhiệm vụ nghiên cứu khoa học; cây gỗ trên diện tích rừng trồng thanh lý; cây gỗ trên diện tích rừng được sử dụng để xây dựng công trình kết cấu hạ tầng phục vụ bảo vệ và phát triển rừng và trên diện tích rừng tạm sử dụng để thi công công trình tạm phục vụ thi công dự án lưới điện theo quy định.
+b) Điều kiện: có quyết định của cấp có thẩm quyền cho phép chuyển mục đích sử dụng rừng sang mục đích khác; quyết định phê duyệt dự án lâm sinh, chương trình, đề tài nghiên cứu khoa học, quyết định thanh lý rừng trồng; quyết định phê duyệt dự án, công trình kết cấu hạ tầng phục vụ bảo vệ và phát triển rừng; quyết định phê duyệt phương án tạm sử dụng rừng để thi công công trình tạm phục vụ thi công dự án lưới điện của cơ quan nhà nước có thẩm quyền.”.
+CHUYỂN TIẾP: 3. Quy định chuyển tiếp
+a) Đối với dự án có đề xuất chuyển mục đích sử dụng rừng sang mục đích khác đã được Quốc hội, Thủ tướng Chính phủ quyết định chủ trương chuyển mục đích sử dụng rừng sang mục đích khác trước ngày Nghị định này có hiệu lực thi hành nhưng cần thiết phải điều chỉnh chủ trương chuyển mục đích sử dụng rừng sang mục đích khác thì Hội đồng nhân dân cấp tỉnh quyết định điều chỉnh chủ trương chuyển mục đích sử dụng rừng sang mục đích khác; trình tự, thủ tục thực hiện theo quy định tại Điều 41b Nghị định này.
+b) Đối với dự án có đề xuất chuyển mục đích sử dụng rừng sang mục đích khác đã được cấp có thẩm quyền chấp thuận hoặc quyết định chủ trương đầu tư trước ngày Nghị định này có hiệu lực thi hành nhưng chưa được cấp thẩm quyền quyết định chủ trương chuyển mục đích sử dụng rừng sang mục đích khác, chủ dự án lập hồ sơ trình Hội đồng nhân dân cấp tỉnh quyết định chủ trương chuyển mục đích sử dụng rừng sang mục đích khác; trình tự, thủ tục thực hiện theo quy định tại Điều 41 Nghị định này.
+c) Đối với các hồ sơ đề nghị quyết định chủ trương chuyển mục đích sử dụng rừng sang mục đích khác hợp lệ, đã được Bộ Nông nghiệp và Phát triển nông thôn tiếp nhận nhưng chưa trình hoặc đã trình và chưa được cấp có thẩm quyền phê duyệt trước ngày 01 tháng 4 năm 2024: trong thời gian 30 ngày kể từ ngày Nghị định này có hiệu lực thi hành, Bộ Nông nghiệp và Phát triển nông thôn hoàn thành việc thẩm định hồ sơ theo quy định tại Nghị định số 83/2020/NĐ-CP ngày 15 tháng 7 năm 2020:
+Đối với hồ sơ đủ điều kiện để cấp có thẩm quyền quyết định chủ trương chuyển mục đích sử dụng rừng sang mục đích khác: Bộ Nông nghiệp và Phát triển nông thôn trình cấp có thẩm quyền xem xét, quyết định;
+Đối với hồ sơ không đủ điều kiện để cấp có thẩm quyền quyết định chủ trương chuyển mục đích sử dụng rừng sang mục đích khác: Bộ Nông nghiệp và Phát triển nông thôn có văn bản gửi trả Ủy ban nhân dân cấp tỉnh (trong đó nêu rõ lý do) để rà soát, hoàn thiện hồ sơ, tổ chức thẩm định, trình Hội đồng nhân dân cấp tỉnh xem xét, quyết định theo quy định tại Nghị định này.
+d) Đối với hồ sơ đề nghị quyết định chủ trương chuyển mục đích sử dụng rừng sang mục đích khác thuộc thẩm quyền của Hội đồng nhân dân cấp tỉnh đã được Ủy ban nhân dân cấp tỉnh thẩm định, trình Hội đồng nhân dân cấp tỉnh hoặc hồ sơ hợp lệ đã được cấp có thẩm quyền tiếp nhận, thẩm định trước ngày 01 tháng 4 năm 2024 thì tiếp tục thực hiện trình tự, thủ tục theo quy định tại Nghị định số 83/2020/NĐ-CP ngày 15 tháng 7 năm 2020.
+đ) Tổ chức, cá nhân được lựa chọn và đã ký hợp đồng cho thuê môi trường rừng theo đúng thẩm quyền và quy định của pháp luật để kinh doanh dịch vụ du lịch sinh thái, nghỉ dưỡng, giải trí trước ngày Nghị định này có hiệu lực thi hành, thì được tiếp tục thực hiện theo thời gian của hợp đồng đã ký và nội dung quy định tại Nghị định này.
+e) Đối với hồ sơ đề nghị giao rừng, cho thuê rừng, thu hồi rừng, chuyển loại rừng, quyết định chuyển mục đích sử dụng rừng sang mục đích khác hợp lệ, đã được cơ quan nhà nước có thẩm quyền tiếp nhận, thẩm định, trình cấp có thẩm quyền trước ngày Nghị định này có hiệu lực thi hành thì được tiếp tục thực hiện và hoàn thành trong thời gian 60 ngày kể từ ngày Nghị định này có hiệu lực thi hành. Trường hợp quá thời gian này mà không hoàn thành thì thực hiện theo quy định tại Nghị định này./.
+Nơi nhận:
+- Ban Bí thư Trung ương Đảng;
+- Thủ tướng, các Phó Thủ tướng Chính phủ;
+- Các bộ, cơ quan ngang bộ, cơ quan thuộc Chính phủ;
+- HĐND, UBND các tỉnh, thành phố trực thuộc trung ương;
+- Văn phòng Trung ương và các Ban của Đảng;
+- Văn phòng Tổng Bí thư;
+- Văn phòng Chủ tịch nước;
+- Hội đồng Dân tộc và các Ủy ban của Quốc hội;
+- Văn phòng Quốc hội;
+- Tòa án nhân dân tối cao;
+- Viện kiểm sát nhân dân tối cao;
+- Kiểm toán nhà nước;
+- Ủy ban Giám sát tài chính Quốc gia;
+- Ngân hàng Chính sách xã hội;
+- Ngân hàng Phát triển Việt Nam;
+- Ủy ban trung ương Mặt trận Tổ quốc Việt Nam;
+- Cơ quan trung ương của các đoàn thể;
+- VPCP: BTCN, các PCN, Trợ lý TTg, TGĐ Cổng TTĐT, c [...cắt bớt]
+[amend] 227/2025/NĐ-CP · hiệu lực 2025-08-16
+4. Sửa đổi, bổ sung khoản 2 Điều 28 Nghị định số 156/2018/NĐ-CP được sửa đổi, bổ sung tại khoản 14 Điều 1 Nghị định số 91/2024/NĐ-CP, như sau:
+“2. Khai thác tận dụng gỗ rừng tự nhiên
+a) Đối tượng: Cây gỗ trên diện tích rừng được cấp có thẩm quyền quyết định chuyển mục đích sử dụng rừng sang mục đích khác; cây gỗ ảnh hưởng đến hành lang an toàn lưới điện; cây gỗ chặt hạ khi thực hiện các biện pháp kỹ thuật lâm sinh, phục vụ công tác đào tạo và nhiệm vụ nghiên cứu khoa học; cây gỗ trên diện tích rừng trồng thanh lý; cây gỗ trên diện tích rừng được sử dụng để xây dựng công trình kết cấu hạ tầng phục vụ bảo vệ và phát triển rừng và trên diện tích rừng tạm sử dụng để thi công công trình tạm phục vụ thi công dự án theo quy định tại khoản 1 Điều 42a Nghị định này.
+b) Điều kiện: Có quyết định của cấp có thẩm quyền </t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1953,7 +2609,6 @@
           <t>227/2025/NĐ-CP; 91/2024/NĐ-CP</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>document_ended 2024-07-15 bao_dong_gia; document_ended 2025-08-16 bao_dong_gia</t>
@@ -1969,18 +2624,62 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
         <is>
           <t>id cũ vilextime:T3:provision:387a3620-2c82-11f1-8d74-79a15475fa71:2024-07-19 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>156/2018/NĐ-CP · hiệu lực 2019-01-01 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 28. Khai thác lâm sản trong rừng sản xuất là rừng tự nhiên
+2. Khai thác tận dụng gỗ rừng tự nhiên
+a) Đối tượng: trên diện tích rừng chuyển mục đích sử dụng rừng sang mục đích khác; khi thực hiện các biện pháp lâm sinh; phục vụ công tác đào tạo và nhiệm vụ nghiên cứu khoa học;
+b) Điều kiện: phải có quyết định phê duyệt của cơ quan có thẩm quyền về chuyển mục đích sử dụng rừng sang mục đích khác; dự án lâm sinh; chương trình, đề tài nghiên cứu khoa học.</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[amend] 91/2024/NĐ-CP · hiệu lực 2024-07-18
+14. Sửa đổi, bổ sung khoản 2 Điều 28 như sau:
+“2. Khai thác tận dụng gỗ rừng tự nhiên
+a) Đối tượng: cây gỗ trên diện tích rừng được cấp có thẩm quyền quyết định chuyển mục đích sử dụng rừng sang mục đích khác theo quy định; cây gỗ chặt hạ khi thực hiện các biện pháp kỹ thuật lâm sinh, phục vụ công tác đào tạo và nhiệm vụ nghiên cứu khoa học; cây gỗ trên diện tích rừng trồng thanh lý; cây gỗ trên diện tích rừng được sử dụng để xây dựng công trình kết cấu hạ tầng phục vụ bảo vệ và phát triển rừng và trên diện tích rừng tạm sử dụng để thi công công trình tạm phục vụ thi công dự án lưới điện theo quy định.
+b) Điều kiện: có quyết định của cấp có thẩm quyền cho phép chuyển mục đích sử dụng rừng sang mục đích khác; quyết định phê duyệt dự án lâm sinh, chương trình, đề tài nghiên cứu khoa học, quyết định thanh lý rừng trồng; quyết định phê duyệt dự án, công trình kết cấu hạ tầng phục vụ bảo vệ và phát triển rừng; quyết định phê duyệt phương án tạm sử dụng rừng để thi công công trình tạm phục vụ thi công dự án lưới điện của cơ quan nhà nước có thẩm quyền.”.
+CHUYỂN TIẾP: 3. Quy định chuyển tiếp
+a) Đối với dự án có đề xuất chuyển mục đích sử dụng rừng sang mục đích khác đã được Quốc hội, Thủ tướng Chính phủ quyết định chủ trương chuyển mục đích sử dụng rừng sang mục đích khác trước ngày Nghị định này có hiệu lực thi hành nhưng cần thiết phải điều chỉnh chủ trương chuyển mục đích sử dụng rừng sang mục đích khác thì Hội đồng nhân dân cấp tỉnh quyết định điều chỉnh chủ trương chuyển mục đích sử dụng rừng sang mục đích khác; trình tự, thủ tục thực hiện theo quy định tại Điều 41b Nghị định này.
+b) Đối với dự án có đề xuất chuyển mục đích sử dụng rừng sang mục đích khác đã được cấp có thẩm quyền chấp thuận hoặc quyết định chủ trương đầu tư trước ngày Nghị định này có hiệu lực thi hành nhưng chưa được cấp thẩm quyền quyết định chủ trương chuyển mục đích sử dụng rừng sang mục đích khác, chủ dự án lập hồ sơ trình Hội đồng nhân dân cấp tỉnh quyết định chủ trương chuyển mục đích sử dụng rừng sang mục đích khác; trình tự, thủ tục thực hiện theo quy định tại Điều 41 Nghị định này.
+c) Đối với các hồ sơ đề nghị quyết định chủ trương chuyển mục đích sử dụng rừng sang mục đích khác hợp lệ, đã được Bộ Nông nghiệp và Phát triển nông thôn tiếp nhận nhưng chưa trình hoặc đã trình và chưa được cấp có thẩm quyền phê duyệt trước ngày 01 tháng 4 năm 2024: trong thời gian 30 ngày kể từ ngày Nghị định này có hiệu lực thi hành, Bộ Nông nghiệp và Phát triển nông thôn hoàn thành việc thẩm định hồ sơ theo quy định tại Nghị định số 83/2020/NĐ-CP ngày 15 tháng 7 năm 2020:
+Đối với hồ sơ đủ điều kiện để cấp có thẩm quyền quyết định chủ trương chuyển mục đích sử dụng rừng sang mục đích khác: Bộ Nông nghiệp và Phát triển nông thôn trình cấp có thẩm quyền xem xét, quyết định;
+Đối với hồ sơ không đủ điều kiện để cấp có thẩm quyền quyết định chủ trương chuyển mục đích sử dụng rừng sang mục đích khác: Bộ Nông nghiệp và Phát triển nông thôn có văn bản gửi trả Ủy ban nhân dân cấp tỉnh (trong đó nêu rõ lý do) để rà soát, hoàn thiện hồ sơ, tổ chức thẩm định, trình Hội đồng nhân dân cấp tỉnh xem xét, quyết định theo quy định tại Nghị định này.
+d) Đối với hồ sơ đề nghị quyết định chủ trương chuyển mục đích sử dụng rừng sang mục đích khác thuộc thẩm quyền của Hội đồng nhân dân cấp tỉnh đã được Ủy ban nhân dân cấp tỉnh thẩm định, trình Hội đồng nhân dân cấp tỉnh hoặc hồ sơ hợp lệ đã được cấp có thẩm quyền tiếp nhận, thẩm định trước ngày 01 tháng 4 năm 2024 thì tiếp tục thực hiện trình tự, thủ tục theo quy định tại Nghị định số 83/2020/NĐ-CP ngày 15 tháng 7 năm 2020.
+đ) Tổ chức, cá nhân được lựa chọn và đã ký hợp đồng cho thuê môi trường rừng theo đúng thẩm quyền và quy định của pháp luật để kinh doanh dịch vụ du lịch sinh thái, nghỉ dưỡng, giải trí trước ngày Nghị định này có hiệu lực thi hành, thì được tiếp tục thực hiện theo thời gian của hợp đồng đã ký và nội dung quy định tại Nghị định này.
+e) Đối với hồ sơ đề nghị giao rừng, cho thuê rừng, thu hồi rừng, chuyển loại rừng, quyết định chuyển mục đích sử dụng rừng sang mục đích khác hợp lệ, đã được cơ quan nhà nước có thẩm quyền tiếp nhận, thẩm định, trình cấp có thẩm quyền trước ngày Nghị định này có hiệu lực thi hành thì được tiếp tục thực hiện và hoàn thành trong thời gian 60 ngày kể từ ngày Nghị định này có hiệu lực thi hành. Trường hợp quá thời gian này mà không hoàn thành thì thực hiện theo quy định tại Nghị định này./.
+Nơi nhận:
+- Ban Bí thư Trung ương Đảng;
+- Thủ tướng, các Phó Thủ tướng Chính phủ;
+- Các bộ, cơ quan ngang bộ, cơ quan thuộc Chính phủ;
+- HĐND, UBND các tỉnh, thành phố trực thuộc trung ương;
+- Văn phòng Trung ương và các Ban của Đảng;
+- Văn phòng Tổng Bí thư;
+- Văn phòng Chủ tịch nước;
+- Hội đồng Dân tộc và các Ủy ban của Quốc hội;
+- Văn phòng Quốc hội;
+- Tòa án nhân dân tối cao;
+- Viện kiểm sát nhân dân tối cao;
+- Kiểm toán nhà nước;
+- Ủy ban Giám sát tài chính Quốc gia;
+- Ngân hàng Chính sách xã hội;
+- Ngân hàng Phát triển Việt Nam;
+- Ủy ban trung ương Mặt trận Tổ quốc Việt Nam;
+- Cơ quan trung ương của các đoàn thể;
+- VPCP: BTCN, các PCN, Trợ lý TTg, TGĐ Cổng TTĐT, c [...cắt bớt]
+[amend] 227/2025/NĐ-CP · hiệu lực 2025-08-16
+4. Sửa đổi, bổ sung khoản 2 Điều 28 Nghị định số 156/2018/NĐ-CP được sửa đổi, bổ sung tại khoản 14 Điều 1 Nghị định số 91/2024/NĐ-CP, như sau:
+“2. Khai thác tận dụng gỗ rừng tự nhiên
+a) Đối tượng: Cây gỗ trên diện tích rừng được cấp có thẩm quyền quyết định chuyển mục đích sử dụng rừng sang mục đích khác; cây gỗ ảnh hưởng đến hành lang an toàn lưới điện; cây gỗ chặt hạ khi thực hiện các biện pháp kỹ thuật lâm sinh, phục vụ công tác đào tạo và nhiệm vụ nghiên cứu khoa học; cây gỗ trên diện tích rừng trồng thanh lý; cây gỗ trên diện tích rừng được sử dụng để xây dựng công trình kết cấu hạ tầng phục vụ bảo vệ và phát triển rừng và trên diện tích rừng tạm sử dụng để thi công công trình tạm phục vụ thi công dự án theo quy định tại khoản 1 Điều 42a Nghị định này.
+b) Điều kiện: Có quyết định của cấp có thẩm quyền </t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2038,7 +2737,6 @@
           <t>227/2025/NĐ-CP; 91/2024/NĐ-CP</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
           <t>document_ended 2024-07-15 bao_dong_gia; document_ended 2025-08-16 bao_dong_gia</t>
@@ -2054,18 +2752,62 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
         <is>
           <t>id cũ vilextime:T3:provision:387a3620-2c82-11f1-8d74-79a15475fa71:2025-08-17 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
-      <c r="W19" t="inlineStr"/>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>156/2018/NĐ-CP · hiệu lực 2019-01-01 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 28. Khai thác lâm sản trong rừng sản xuất là rừng tự nhiên
+2. Khai thác tận dụng gỗ rừng tự nhiên
+a) Đối tượng: trên diện tích rừng chuyển mục đích sử dụng rừng sang mục đích khác; khi thực hiện các biện pháp lâm sinh; phục vụ công tác đào tạo và nhiệm vụ nghiên cứu khoa học;
+b) Điều kiện: phải có quyết định phê duyệt của cơ quan có thẩm quyền về chuyển mục đích sử dụng rừng sang mục đích khác; dự án lâm sinh; chương trình, đề tài nghiên cứu khoa học.</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[amend] 91/2024/NĐ-CP · hiệu lực 2024-07-18
+14. Sửa đổi, bổ sung khoản 2 Điều 28 như sau:
+“2. Khai thác tận dụng gỗ rừng tự nhiên
+a) Đối tượng: cây gỗ trên diện tích rừng được cấp có thẩm quyền quyết định chuyển mục đích sử dụng rừng sang mục đích khác theo quy định; cây gỗ chặt hạ khi thực hiện các biện pháp kỹ thuật lâm sinh, phục vụ công tác đào tạo và nhiệm vụ nghiên cứu khoa học; cây gỗ trên diện tích rừng trồng thanh lý; cây gỗ trên diện tích rừng được sử dụng để xây dựng công trình kết cấu hạ tầng phục vụ bảo vệ và phát triển rừng và trên diện tích rừng tạm sử dụng để thi công công trình tạm phục vụ thi công dự án lưới điện theo quy định.
+b) Điều kiện: có quyết định của cấp có thẩm quyền cho phép chuyển mục đích sử dụng rừng sang mục đích khác; quyết định phê duyệt dự án lâm sinh, chương trình, đề tài nghiên cứu khoa học, quyết định thanh lý rừng trồng; quyết định phê duyệt dự án, công trình kết cấu hạ tầng phục vụ bảo vệ và phát triển rừng; quyết định phê duyệt phương án tạm sử dụng rừng để thi công công trình tạm phục vụ thi công dự án lưới điện của cơ quan nhà nước có thẩm quyền.”.
+CHUYỂN TIẾP: 3. Quy định chuyển tiếp
+a) Đối với dự án có đề xuất chuyển mục đích sử dụng rừng sang mục đích khác đã được Quốc hội, Thủ tướng Chính phủ quyết định chủ trương chuyển mục đích sử dụng rừng sang mục đích khác trước ngày Nghị định này có hiệu lực thi hành nhưng cần thiết phải điều chỉnh chủ trương chuyển mục đích sử dụng rừng sang mục đích khác thì Hội đồng nhân dân cấp tỉnh quyết định điều chỉnh chủ trương chuyển mục đích sử dụng rừng sang mục đích khác; trình tự, thủ tục thực hiện theo quy định tại Điều 41b Nghị định này.
+b) Đối với dự án có đề xuất chuyển mục đích sử dụng rừng sang mục đích khác đã được cấp có thẩm quyền chấp thuận hoặc quyết định chủ trương đầu tư trước ngày Nghị định này có hiệu lực thi hành nhưng chưa được cấp thẩm quyền quyết định chủ trương chuyển mục đích sử dụng rừng sang mục đích khác, chủ dự án lập hồ sơ trình Hội đồng nhân dân cấp tỉnh quyết định chủ trương chuyển mục đích sử dụng rừng sang mục đích khác; trình tự, thủ tục thực hiện theo quy định tại Điều 41 Nghị định này.
+c) Đối với các hồ sơ đề nghị quyết định chủ trương chuyển mục đích sử dụng rừng sang mục đích khác hợp lệ, đã được Bộ Nông nghiệp và Phát triển nông thôn tiếp nhận nhưng chưa trình hoặc đã trình và chưa được cấp có thẩm quyền phê duyệt trước ngày 01 tháng 4 năm 2024: trong thời gian 30 ngày kể từ ngày Nghị định này có hiệu lực thi hành, Bộ Nông nghiệp và Phát triển nông thôn hoàn thành việc thẩm định hồ sơ theo quy định tại Nghị định số 83/2020/NĐ-CP ngày 15 tháng 7 năm 2020:
+Đối với hồ sơ đủ điều kiện để cấp có thẩm quyền quyết định chủ trương chuyển mục đích sử dụng rừng sang mục đích khác: Bộ Nông nghiệp và Phát triển nông thôn trình cấp có thẩm quyền xem xét, quyết định;
+Đối với hồ sơ không đủ điều kiện để cấp có thẩm quyền quyết định chủ trương chuyển mục đích sử dụng rừng sang mục đích khác: Bộ Nông nghiệp và Phát triển nông thôn có văn bản gửi trả Ủy ban nhân dân cấp tỉnh (trong đó nêu rõ lý do) để rà soát, hoàn thiện hồ sơ, tổ chức thẩm định, trình Hội đồng nhân dân cấp tỉnh xem xét, quyết định theo quy định tại Nghị định này.
+d) Đối với hồ sơ đề nghị quyết định chủ trương chuyển mục đích sử dụng rừng sang mục đích khác thuộc thẩm quyền của Hội đồng nhân dân cấp tỉnh đã được Ủy ban nhân dân cấp tỉnh thẩm định, trình Hội đồng nhân dân cấp tỉnh hoặc hồ sơ hợp lệ đã được cấp có thẩm quyền tiếp nhận, thẩm định trước ngày 01 tháng 4 năm 2024 thì tiếp tục thực hiện trình tự, thủ tục theo quy định tại Nghị định số 83/2020/NĐ-CP ngày 15 tháng 7 năm 2020.
+đ) Tổ chức, cá nhân được lựa chọn và đã ký hợp đồng cho thuê môi trường rừng theo đúng thẩm quyền và quy định của pháp luật để kinh doanh dịch vụ du lịch sinh thái, nghỉ dưỡng, giải trí trước ngày Nghị định này có hiệu lực thi hành, thì được tiếp tục thực hiện theo thời gian của hợp đồng đã ký và nội dung quy định tại Nghị định này.
+e) Đối với hồ sơ đề nghị giao rừng, cho thuê rừng, thu hồi rừng, chuyển loại rừng, quyết định chuyển mục đích sử dụng rừng sang mục đích khác hợp lệ, đã được cơ quan nhà nước có thẩm quyền tiếp nhận, thẩm định, trình cấp có thẩm quyền trước ngày Nghị định này có hiệu lực thi hành thì được tiếp tục thực hiện và hoàn thành trong thời gian 60 ngày kể từ ngày Nghị định này có hiệu lực thi hành. Trường hợp quá thời gian này mà không hoàn thành thì thực hiện theo quy định tại Nghị định này./.
+Nơi nhận:
+- Ban Bí thư Trung ương Đảng;
+- Thủ tướng, các Phó Thủ tướng Chính phủ;
+- Các bộ, cơ quan ngang bộ, cơ quan thuộc Chính phủ;
+- HĐND, UBND các tỉnh, thành phố trực thuộc trung ương;
+- Văn phòng Trung ương và các Ban của Đảng;
+- Văn phòng Tổng Bí thư;
+- Văn phòng Chủ tịch nước;
+- Hội đồng Dân tộc và các Ủy ban của Quốc hội;
+- Văn phòng Quốc hội;
+- Tòa án nhân dân tối cao;
+- Viện kiểm sát nhân dân tối cao;
+- Kiểm toán nhà nước;
+- Ủy ban Giám sát tài chính Quốc gia;
+- Ngân hàng Chính sách xã hội;
+- Ngân hàng Phát triển Việt Nam;
+- Ủy ban trung ương Mặt trận Tổ quốc Việt Nam;
+- Cơ quan trung ương của các đoàn thể;
+- VPCP: BTCN, các PCN, Trợ lý TTg, TGĐ Cổng TTĐT, c [...cắt bớt]
+[amend] 227/2025/NĐ-CP · hiệu lực 2025-08-16
+4. Sửa đổi, bổ sung khoản 2 Điều 28 Nghị định số 156/2018/NĐ-CP được sửa đổi, bổ sung tại khoản 14 Điều 1 Nghị định số 91/2024/NĐ-CP, như sau:
+“2. Khai thác tận dụng gỗ rừng tự nhiên
+a) Đối tượng: Cây gỗ trên diện tích rừng được cấp có thẩm quyền quyết định chuyển mục đích sử dụng rừng sang mục đích khác; cây gỗ ảnh hưởng đến hành lang an toàn lưới điện; cây gỗ chặt hạ khi thực hiện các biện pháp kỹ thuật lâm sinh, phục vụ công tác đào tạo và nhiệm vụ nghiên cứu khoa học; cây gỗ trên diện tích rừng trồng thanh lý; cây gỗ trên diện tích rừng được sử dụng để xây dựng công trình kết cấu hạ tầng phục vụ bảo vệ và phát triển rừng và trên diện tích rừng tạm sử dụng để thi công công trình tạm phục vụ thi công dự án theo quy định tại khoản 1 Điều 42a Nghị định này.
+b) Điều kiện: Có quyết định của cấp có thẩm quyền </t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2123,7 +2865,6 @@
           <t>227/2025/NĐ-CP; 91/2024/NĐ-CP</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
           <t>document_ended 2024-07-15 bao_dong_gia; document_ended 2025-08-16 bao_dong_gia</t>
@@ -2139,18 +2880,62 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
         <is>
           <t>id cũ vilextime:T3:provision:387cf540-2c82-11f1-8aba-550abdbfe211:2019-01-02 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr"/>
-      <c r="W20" t="inlineStr"/>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>156/2018/NĐ-CP · hiệu lực 2019-01-01 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 29. Khai thác lâm sản trong rừng sản xuất là rừng trồng
+2. Khai thác tận dụng gỗ rừng trồng
+a) Đối tượng: là cây gỗ trên diện tích rừng chuyển mục đích sử dụng rừng, khi thực hiện các biện pháp lâm sinh, phục vụ cho công tác đào tạo và nghiên cứu khoa học;
+b) Điều kiện: rừng trồng bằng nguồn vốn ngân sách nhà nước phải có quyết định phê duyệt của cơ quan có thẩm quyền về chuyển mục đích sử dụng rừng sang mục đích khác; dự án lâm sinh; chương trình, đề tài nghiên cứu khoa học.</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[amend] 91/2024/NĐ-CP · hiệu lực 2024-07-18
+15. Sửa đổi, bổ sung khoản 2 Điều 29 như sau:
+“2. Khai thác tận dụng gỗ rừng trồng
+a) Đối tượng: cây gỗ trên diện tích rừng được cấp có thẩm quyền quyết định chuyển mục đích sử dụng rừng sang mục đích khác theo quy định; cây gỗ chặt hạ khi thực hiện các biện pháp kỹ thuật lâm sinh, phục vụ công tác đào tạo và nhiệm vụ nghiên cứu khoa học; cây gỗ trên diện tích rừng trồng thanh lý; cây gỗ trên diện tích rừng được sử dụng để xây dựng công trình kết cấu hạ tầng phục vụ bảo vệ và phát triển rừng và trên diện tích rừng tạm sử dụng để thi công công trình tạm phục vụ thi công dự án lưới điện theo quy định.
+b) Điều kiện: rừng trồng do Nhà nước là đại diện chủ sở hữu phải có quyết định của cấp có thẩm quyền cho phép chuyển mục đích sử dụng rừng sang mục đích khác; quyết định phê duyệt dự án lâm sinh, chương trình, đề tài nghiên cứu khoa học; quyết định thanh lý rừng trồng; quyết định phê duyệt dự án, công trình kết cấu hạ tầng phục vụ bảo vệ và phát triển rừng và quyết định phê duyệt phương án tạm sử dụng rừng để thi công công trình tạm phục vụ thi công dự án lưới điện của cơ quan nhà nước có thẩm quyền.”.
+CHUYỂN TIẾP: 3. Quy định chuyển tiếp
+a) Đối với dự án có đề xuất chuyển mục đích sử dụng rừng sang mục đích khác đã được Quốc hội, Thủ tướng Chính phủ quyết định chủ trương chuyển mục đích sử dụng rừng sang mục đích khác trước ngày Nghị định này có hiệu lực thi hành nhưng cần thiết phải điều chỉnh chủ trương chuyển mục đích sử dụng rừng sang mục đích khác thì Hội đồng nhân dân cấp tỉnh quyết định điều chỉnh chủ trương chuyển mục đích sử dụng rừng sang mục đích khác; trình tự, thủ tục thực hiện theo quy định tại Điều 41b Nghị định này.
+b) Đối với dự án có đề xuất chuyển mục đích sử dụng rừng sang mục đích khác đã được cấp có thẩm quyền chấp thuận hoặc quyết định chủ trương đầu tư trước ngày Nghị định này có hiệu lực thi hành nhưng chưa được cấp thẩm quyền quyết định chủ trương chuyển mục đích sử dụng rừng sang mục đích khác, chủ dự án lập hồ sơ trình Hội đồng nhân dân cấp tỉnh quyết định chủ trương chuyển mục đích sử dụng rừng sang mục đích khác; trình tự, thủ tục thực hiện theo quy định tại Điều 41 Nghị định này.
+c) Đối với các hồ sơ đề nghị quyết định chủ trương chuyển mục đích sử dụng rừng sang mục đích khác hợp lệ, đã được Bộ Nông nghiệp và Phát triển nông thôn tiếp nhận nhưng chưa trình hoặc đã trình và chưa được cấp có thẩm quyền phê duyệt trước ngày 01 tháng 4 năm 2024: trong thời gian 30 ngày kể từ ngày Nghị định này có hiệu lực thi hành, Bộ Nông nghiệp và Phát triển nông thôn hoàn thành việc thẩm định hồ sơ theo quy định tại Nghị định số 83/2020/NĐ-CP ngày 15 tháng 7 năm 2020:
+Đối với hồ sơ đủ điều kiện để cấp có thẩm quyền quyết định chủ trương chuyển mục đích sử dụng rừng sang mục đích khác: Bộ Nông nghiệp và Phát triển nông thôn trình cấp có thẩm quyền xem xét, quyết định;
+Đối với hồ sơ không đủ điều kiện để cấp có thẩm quyền quyết định chủ trương chuyển mục đích sử dụng rừng sang mục đích khác: Bộ Nông nghiệp và Phát triển nông thôn có văn bản gửi trả Ủy ban nhân dân cấp tỉnh (trong đó nêu rõ lý do) để rà soát, hoàn thiện hồ sơ, tổ chức thẩm định, trình Hội đồng nhân dân cấp tỉnh xem xét, quyết định theo quy định tại Nghị định này.
+d) Đối với hồ sơ đề nghị quyết định chủ trương chuyển mục đích sử dụng rừng sang mục đích khác thuộc thẩm quyền của Hội đồng nhân dân cấp tỉnh đã được Ủy ban nhân dân cấp tỉnh thẩm định, trình Hội đồng nhân dân cấp tỉnh hoặc hồ sơ hợp lệ đã được cấp có thẩm quyền tiếp nhận, thẩm định trước ngày 01 tháng 4 năm 2024 thì tiếp tục thực hiện trình tự, thủ tục theo quy định tại Nghị định số 83/2020/NĐ-CP ngày 15 tháng 7 năm 2020.
+đ) Tổ chức, cá nhân được lựa chọn và đã ký hợp đồng cho thuê môi trường rừng theo đúng thẩm quyền và quy định của pháp luật để kinh doanh dịch vụ du lịch sinh thái, nghỉ dưỡng, giải trí trước ngày Nghị định này có hiệu lực thi hành, thì được tiếp tục thực hiện theo thời gian của hợp đồng đã ký và nội dung quy định tại Nghị định này.
+e) Đối với hồ sơ đề nghị giao rừng, cho thuê rừng, thu hồi rừng, chuyển loại rừng, quyết định chuyển mục đích sử dụng rừng sang mục đích khác hợp lệ, đã được cơ quan nhà nước có thẩm quyền tiếp nhận, thẩm định, trình cấp có thẩm quyền trước ngày Nghị định này có hiệu lực thi hành thì được tiếp tục thực hiện và hoàn thành trong thời gian 60 ngày kể từ ngày Nghị định này có hiệu lực thi hành. Trường hợp quá thời gian này mà không hoàn thành thì thực hiện theo quy định tại Nghị định này./.
+Nơi nhận:
+- Ban Bí thư Trung ương Đảng;
+- Thủ tướng, các Phó Thủ tướng Chính phủ;
+- Các bộ, cơ quan ngang bộ, cơ quan thuộc Chính phủ;
+- HĐND, UBND các tỉnh, thành phố trực thuộc trung ương;
+- Văn phòng Trung ương và các Ban của Đảng;
+- Văn phòng Tổng Bí thư;
+- Văn phòng Chủ tịch nước;
+- Hội đồng Dân tộc và các Ủy ban của Quốc hội;
+- Văn phòng Quốc hội;
+- Tòa án nhân dân tối cao;
+- Viện kiểm sát nhân dân tối cao;
+- Kiểm toán nhà nước;
+- Ủy ban Giám sát tài chính Quốc gia;
+- Ngân hàng Chính sách xã hội;
+- Ngân hàng Phát triển Việt Nam;
+- Ủy ban trung ương Mặt trận Tổ quốc Việt Nam;
+- Cơ quan trung ương của các đoàn thể;
+- VPCP: BTCN, các PCN, Trợ lý TTg, TGĐ Cổng TTĐT, c [...cắt bớt]
+[amend] 227/2025/NĐ-CP · hiệu lực 2025-08-16
+5. Sửa đổi, bổ sung khoản 2 Điều 29 Nghị định số 156/2018/NĐ-CP được sửa đổi, bổ sung tại khoản 15 Điều 1 Nghị định số 91/2024/NĐ-CP, như sau:
+“2. Khai thác tận dụng gỗ rừng trồng
+a) Đối tượng: Cây gỗ trên diện tích rừng được cấp có thẩm quyền quyết định chuyển mục đích sử dụng rừng sang mục đích khác; cây gỗ ảnh hưởng đến hành lang an toàn lưới điện; cây gỗ chặt hạ khi thực hiện các biện pháp kỹ thuật lâm sinh, phục vụ công tác đào tạo và nhiệm vụ nghiên cứu khoa học; cây gỗ trên diện tích rừng trồng thanh lý; cây gỗ trên diện tích rừng được sử dụng để xây dựng công trình kết cấu hạ tầng phục vụ bảo vệ và phát triển rừng và trên diện tích rừng tạm sử dụng để thi công công trình tạm phục vụ thi công dự án theo quy định tại khoản 1 Điều 42a Nghị định này.
+b) </t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2213,7 +2998,6 @@
           <t>actor_has_transitional</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -2224,18 +3008,38 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
         <is>
           <t>id cũ vilextime:T3:provision:393dc8e0-eac6-11f0-bb51-7b4ee690de15#k1:2018-11-02 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
-      <c r="W21" t="inlineStr"/>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>22/2018/TT-NHNN · hiệu lực 2018-11-01 → 2025-08-10 · lúc thu thập: Hết hiệu lực toàn bộ
+Điều 12. Trách nhiệm của Cơ quan thanh tra, giám sát ngân hàng
+1. Trong thời hạn 20 ngày làm việc kể từ ngày tiếp nhận đầy đủ hồ sơ của tổ chức tín dụng, chi nhánh ngân hàng nước ngoài theo quy định, Cơ quan Thanh tra, giám sát ngân hàng có trách nhiệm là đầu mối đánh giá việc đáp ứng hồ sơ, tiêu chuẩn, điều kiện của nhân sự dự kiến của tổ chức tín dụng, chi nhánh ngân hàng nước ngoài theo quy định tại Luật Các tổ chức tín dụng và Thông tư này; lấy ý kiến đơn vị liên quan; tổng hợp và trình Thống đốc Ngân hàng Nhà nước xem xét, có văn bản chấp thuận hoặc không chấp thuận dự kiến nhân sự của tổ chức tín dụng, chi nhánh ngân hàng nước ngoài.</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 13/2019/TT-NHNN · hiệu lực 2019-10-05
+10. Khoản 1 Điều 12 được sửa đổi, bổ sung như sau:
+“1. Cơ quan Thanh tra, giám sát ngân hàng có trách nhiệm là đầu mối đánh giá việc đáp ứng hồ sơ, tiêu chuẩn, điều kiện của nhân sự dự kiến của tổ chức tín dụng, chi nhánh ngân hàng nước ngoài thuộc đối tượng quy định tại khoản 1 Điều 4 Thông tư này theo quy định tại Luật các tổ chức tín dụng và Thông tư này; lấy ý kiến các đơn vị liên quan; tổng hợp và trình Thống đốc Ngân hàng Nhà nước xem xét, có văn bản chấp thuận hoặc không chấp thuận dự kiến nhân sự của tổ chức tín dụng, chi nhánh ngân hàng nước ngoài.”.
+11. Khoản 3 Điều 12 được sửa đổi, bổ sung như sau:
+“3. Tiếp nhận, rà soát thông báo của tổ chức tín dụng, chi nhánh ngân hàng nước ngoài quy định tại khoản 2 Điều 11 Thông tư này. Trường hợp phát hiện sai sót, Cơ quan Thanh tra, giám sát ngân hàng yêu cầu tổ chức tín dụng, chi nhánh ngân hàng nước ngoài xử lý hoặc đề xuất Thống đốc Ngân hàng Nhà nước biện pháp xử lý.”.
+12. Điều 13 được sửa đổi, bổ sung như sau:
+“ Điều 13. Trách nhiệm của Ngân hàng Nhà nước chi nhánh
+1. Trong thời hạn 30 ngày làm việc kể từ ngày tiếp nhận đầy đủ hồ sơ của chi nhánh ngân hàng nước ngoài thuộc đối tượng quy định tại khoản 2 Điều 4 Thông tư này, Ngân hàng Nhà nước chi nhánh có trách nhiệm đánh giá việc đáp ứng hồ sơ, tiêu chuẩn, điều kiện của nhân sự dự kiến của chi nhánh ngân hàng nước ngoài theo quy định tại Luật các tổ chức tín dụng và Thông tư này; lấy ý kiến các đơn vị liên quan; có văn bản chấp thuận hoặc không chấp thuận dự kiến nhân sự của chi nhánh ngân hàng nước ngoài.
+2. Ngân hàng Nhà nước chi nhánh có trách nhiệm tham gia ý kiến bằng văn bản theo đề nghị của Cơ quan Thanh tra, giám sát ngân hàng trong thời hạn 05 ngày làm việc kể từ ngày nhận được văn bản đề nghị.
+3. Tiếp nhận thông báo của chi nhánh ngân hàng nước ngoài quy định tại khoản 1 Điều 11 Thông tư này; xem xét việc đáp ứng tiêu chuẩn, điều kiện của nhân sự dự kiến hoặc biện pháp xử lý.
+4. Tiếp nhận, rà soát thông báo của chi nhánh ngân hàng nước ngoài quy định tại khoản 2 Điều 11 Thông tư này. Trường hợp phát hiện sai sót, Ngân hàng Nhà nước chi nhánh yêu cầu chi nhánh ngân hàng nước ngoài xử lý hoặc đề xuất Thống đốc Ngân hàng Nhà nước biện pháp xử lý nếu vượt thẩm quyền.”.
+CHUYỂN TIẾP: Điều 5. Điều khoản chuyển tiếp
+Đối với các hồ sơ đề nghị chấp thuận danh sách dự kiến nhân sự của chi nhánh ngân hàng nước ngoài đã được Cơ quan Thanh tra, giám sát ngân hàng tiếp nhận trước ngày 26 tháng 8 năm 2019, Cơ quan Thanh tra, giám sát ngân hàng tiếp tục xử lý, trình Thống đốc Ngân hàng Nhà nước xem xét, chấp thuận theo quy định tại Thông tư số 22/2018/TT-NHNN được sửa đổi, bổ sung theo Điều 2 Thông tư này.
+[amend] 10/2024/TT-NHNN · hiệu lực 2024-07-01
+12. Sửa đổi, bổ sung khoản 1 Điều 12 Thông tư số 22/2018/TT-NHNN như sau:
+“1. Cơ quan Thanh tra, giám sát ngân hàng có trách nhiệm là đầu mối đánh giá việc đáp ứng hồ sơ, tiêu chuẩn, điều kiện của nhân sự dự kiến của tổ chức tín dụng, chi nhánh ngân hàng nước ngoài thuộc đối tượng quy định tại khoản 1, khoản 2 Điều 4 Thông tư này theo quy định tại Luật Các tổ chức tín dụng và Thông tư này; lấy ý kiến các đơn vị liên quan; tổng hợp và trình Thống đốc Ngân hàng Nhà nước xem xét, có văn bản chấp thuận hoặc không chấp thuận dự kiến nhân sự của ngân hàng thương mại nêu tại khoản 1 Điều 4 Thông tư này; có văn bản chấp thuận hoặc không chấp thuận dự kiến nhân sự của tổ chức tín dụng phi ngân hàng, chi nhánh ngân hàng nước ngoài nêu tại khoản 2 Điều 4 Thông tư này.”.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2298,7 +3102,6 @@
           <t>actor_has_transitional</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -2309,18 +3112,38 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
         <is>
           <t>id cũ vilextime:T3:provision:393dc8e0-eac6-11f0-bb51-7b4ee690de15#k1:2019-10-06 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr"/>
-      <c r="W22" t="inlineStr"/>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>22/2018/TT-NHNN · hiệu lực 2018-11-01 → 2025-08-10 · lúc thu thập: Hết hiệu lực toàn bộ
+Điều 12. Trách nhiệm của Cơ quan thanh tra, giám sát ngân hàng
+1. Trong thời hạn 20 ngày làm việc kể từ ngày tiếp nhận đầy đủ hồ sơ của tổ chức tín dụng, chi nhánh ngân hàng nước ngoài theo quy định, Cơ quan Thanh tra, giám sát ngân hàng có trách nhiệm là đầu mối đánh giá việc đáp ứng hồ sơ, tiêu chuẩn, điều kiện của nhân sự dự kiến của tổ chức tín dụng, chi nhánh ngân hàng nước ngoài theo quy định tại Luật Các tổ chức tín dụng và Thông tư này; lấy ý kiến đơn vị liên quan; tổng hợp và trình Thống đốc Ngân hàng Nhà nước xem xét, có văn bản chấp thuận hoặc không chấp thuận dự kiến nhân sự của tổ chức tín dụng, chi nhánh ngân hàng nước ngoài.</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 13/2019/TT-NHNN · hiệu lực 2019-10-05
+10. Khoản 1 Điều 12 được sửa đổi, bổ sung như sau:
+“1. Cơ quan Thanh tra, giám sát ngân hàng có trách nhiệm là đầu mối đánh giá việc đáp ứng hồ sơ, tiêu chuẩn, điều kiện của nhân sự dự kiến của tổ chức tín dụng, chi nhánh ngân hàng nước ngoài thuộc đối tượng quy định tại khoản 1 Điều 4 Thông tư này theo quy định tại Luật các tổ chức tín dụng và Thông tư này; lấy ý kiến các đơn vị liên quan; tổng hợp và trình Thống đốc Ngân hàng Nhà nước xem xét, có văn bản chấp thuận hoặc không chấp thuận dự kiến nhân sự của tổ chức tín dụng, chi nhánh ngân hàng nước ngoài.”.
+11. Khoản 3 Điều 12 được sửa đổi, bổ sung như sau:
+“3. Tiếp nhận, rà soát thông báo của tổ chức tín dụng, chi nhánh ngân hàng nước ngoài quy định tại khoản 2 Điều 11 Thông tư này. Trường hợp phát hiện sai sót, Cơ quan Thanh tra, giám sát ngân hàng yêu cầu tổ chức tín dụng, chi nhánh ngân hàng nước ngoài xử lý hoặc đề xuất Thống đốc Ngân hàng Nhà nước biện pháp xử lý.”.
+12. Điều 13 được sửa đổi, bổ sung như sau:
+“ Điều 13. Trách nhiệm của Ngân hàng Nhà nước chi nhánh
+1. Trong thời hạn 30 ngày làm việc kể từ ngày tiếp nhận đầy đủ hồ sơ của chi nhánh ngân hàng nước ngoài thuộc đối tượng quy định tại khoản 2 Điều 4 Thông tư này, Ngân hàng Nhà nước chi nhánh có trách nhiệm đánh giá việc đáp ứng hồ sơ, tiêu chuẩn, điều kiện của nhân sự dự kiến của chi nhánh ngân hàng nước ngoài theo quy định tại Luật các tổ chức tín dụng và Thông tư này; lấy ý kiến các đơn vị liên quan; có văn bản chấp thuận hoặc không chấp thuận dự kiến nhân sự của chi nhánh ngân hàng nước ngoài.
+2. Ngân hàng Nhà nước chi nhánh có trách nhiệm tham gia ý kiến bằng văn bản theo đề nghị của Cơ quan Thanh tra, giám sát ngân hàng trong thời hạn 05 ngày làm việc kể từ ngày nhận được văn bản đề nghị.
+3. Tiếp nhận thông báo của chi nhánh ngân hàng nước ngoài quy định tại khoản 1 Điều 11 Thông tư này; xem xét việc đáp ứng tiêu chuẩn, điều kiện của nhân sự dự kiến hoặc biện pháp xử lý.
+4. Tiếp nhận, rà soát thông báo của chi nhánh ngân hàng nước ngoài quy định tại khoản 2 Điều 11 Thông tư này. Trường hợp phát hiện sai sót, Ngân hàng Nhà nước chi nhánh yêu cầu chi nhánh ngân hàng nước ngoài xử lý hoặc đề xuất Thống đốc Ngân hàng Nhà nước biện pháp xử lý nếu vượt thẩm quyền.”.
+CHUYỂN TIẾP: Điều 5. Điều khoản chuyển tiếp
+Đối với các hồ sơ đề nghị chấp thuận danh sách dự kiến nhân sự của chi nhánh ngân hàng nước ngoài đã được Cơ quan Thanh tra, giám sát ngân hàng tiếp nhận trước ngày 26 tháng 8 năm 2019, Cơ quan Thanh tra, giám sát ngân hàng tiếp tục xử lý, trình Thống đốc Ngân hàng Nhà nước xem xét, chấp thuận theo quy định tại Thông tư số 22/2018/TT-NHNN được sửa đổi, bổ sung theo Điều 2 Thông tư này.
+[amend] 10/2024/TT-NHNN · hiệu lực 2024-07-01
+12. Sửa đổi, bổ sung khoản 1 Điều 12 Thông tư số 22/2018/TT-NHNN như sau:
+“1. Cơ quan Thanh tra, giám sát ngân hàng có trách nhiệm là đầu mối đánh giá việc đáp ứng hồ sơ, tiêu chuẩn, điều kiện của nhân sự dự kiến của tổ chức tín dụng, chi nhánh ngân hàng nước ngoài thuộc đối tượng quy định tại khoản 1, khoản 2 Điều 4 Thông tư này theo quy định tại Luật Các tổ chức tín dụng và Thông tư này; lấy ý kiến các đơn vị liên quan; tổng hợp và trình Thống đốc Ngân hàng Nhà nước xem xét, có văn bản chấp thuận hoặc không chấp thuận dự kiến nhân sự của ngân hàng thương mại nêu tại khoản 1 Điều 4 Thông tư này; có văn bản chấp thuận hoặc không chấp thuận dự kiến nhân sự của tổ chức tín dụng phi ngân hàng, chi nhánh ngân hàng nước ngoài nêu tại khoản 2 Điều 4 Thông tư này.”.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2383,7 +3206,6 @@
           <t>actor_has_transitional</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -2394,18 +3216,38 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
         <is>
           <t>id cũ vilextime:T3:provision:393dc8e0-eac6-11f0-bb51-7b4ee690de15#k1:2024-07-02 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr"/>
-      <c r="W23" t="inlineStr"/>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>22/2018/TT-NHNN · hiệu lực 2018-11-01 → 2025-08-10 · lúc thu thập: Hết hiệu lực toàn bộ
+Điều 12. Trách nhiệm của Cơ quan thanh tra, giám sát ngân hàng
+1. Trong thời hạn 20 ngày làm việc kể từ ngày tiếp nhận đầy đủ hồ sơ của tổ chức tín dụng, chi nhánh ngân hàng nước ngoài theo quy định, Cơ quan Thanh tra, giám sát ngân hàng có trách nhiệm là đầu mối đánh giá việc đáp ứng hồ sơ, tiêu chuẩn, điều kiện của nhân sự dự kiến của tổ chức tín dụng, chi nhánh ngân hàng nước ngoài theo quy định tại Luật Các tổ chức tín dụng và Thông tư này; lấy ý kiến đơn vị liên quan; tổng hợp và trình Thống đốc Ngân hàng Nhà nước xem xét, có văn bản chấp thuận hoặc không chấp thuận dự kiến nhân sự của tổ chức tín dụng, chi nhánh ngân hàng nước ngoài.</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 13/2019/TT-NHNN · hiệu lực 2019-10-05
+10. Khoản 1 Điều 12 được sửa đổi, bổ sung như sau:
+“1. Cơ quan Thanh tra, giám sát ngân hàng có trách nhiệm là đầu mối đánh giá việc đáp ứng hồ sơ, tiêu chuẩn, điều kiện của nhân sự dự kiến của tổ chức tín dụng, chi nhánh ngân hàng nước ngoài thuộc đối tượng quy định tại khoản 1 Điều 4 Thông tư này theo quy định tại Luật các tổ chức tín dụng và Thông tư này; lấy ý kiến các đơn vị liên quan; tổng hợp và trình Thống đốc Ngân hàng Nhà nước xem xét, có văn bản chấp thuận hoặc không chấp thuận dự kiến nhân sự của tổ chức tín dụng, chi nhánh ngân hàng nước ngoài.”.
+11. Khoản 3 Điều 12 được sửa đổi, bổ sung như sau:
+“3. Tiếp nhận, rà soát thông báo của tổ chức tín dụng, chi nhánh ngân hàng nước ngoài quy định tại khoản 2 Điều 11 Thông tư này. Trường hợp phát hiện sai sót, Cơ quan Thanh tra, giám sát ngân hàng yêu cầu tổ chức tín dụng, chi nhánh ngân hàng nước ngoài xử lý hoặc đề xuất Thống đốc Ngân hàng Nhà nước biện pháp xử lý.”.
+12. Điều 13 được sửa đổi, bổ sung như sau:
+“ Điều 13. Trách nhiệm của Ngân hàng Nhà nước chi nhánh
+1. Trong thời hạn 30 ngày làm việc kể từ ngày tiếp nhận đầy đủ hồ sơ của chi nhánh ngân hàng nước ngoài thuộc đối tượng quy định tại khoản 2 Điều 4 Thông tư này, Ngân hàng Nhà nước chi nhánh có trách nhiệm đánh giá việc đáp ứng hồ sơ, tiêu chuẩn, điều kiện của nhân sự dự kiến của chi nhánh ngân hàng nước ngoài theo quy định tại Luật các tổ chức tín dụng và Thông tư này; lấy ý kiến các đơn vị liên quan; có văn bản chấp thuận hoặc không chấp thuận dự kiến nhân sự của chi nhánh ngân hàng nước ngoài.
+2. Ngân hàng Nhà nước chi nhánh có trách nhiệm tham gia ý kiến bằng văn bản theo đề nghị của Cơ quan Thanh tra, giám sát ngân hàng trong thời hạn 05 ngày làm việc kể từ ngày nhận được văn bản đề nghị.
+3. Tiếp nhận thông báo của chi nhánh ngân hàng nước ngoài quy định tại khoản 1 Điều 11 Thông tư này; xem xét việc đáp ứng tiêu chuẩn, điều kiện của nhân sự dự kiến hoặc biện pháp xử lý.
+4. Tiếp nhận, rà soát thông báo của chi nhánh ngân hàng nước ngoài quy định tại khoản 2 Điều 11 Thông tư này. Trường hợp phát hiện sai sót, Ngân hàng Nhà nước chi nhánh yêu cầu chi nhánh ngân hàng nước ngoài xử lý hoặc đề xuất Thống đốc Ngân hàng Nhà nước biện pháp xử lý nếu vượt thẩm quyền.”.
+CHUYỂN TIẾP: Điều 5. Điều khoản chuyển tiếp
+Đối với các hồ sơ đề nghị chấp thuận danh sách dự kiến nhân sự của chi nhánh ngân hàng nước ngoài đã được Cơ quan Thanh tra, giám sát ngân hàng tiếp nhận trước ngày 26 tháng 8 năm 2019, Cơ quan Thanh tra, giám sát ngân hàng tiếp tục xử lý, trình Thống đốc Ngân hàng Nhà nước xem xét, chấp thuận theo quy định tại Thông tư số 22/2018/TT-NHNN được sửa đổi, bổ sung theo Điều 2 Thông tư này.
+[amend] 10/2024/TT-NHNN · hiệu lực 2024-07-01
+12. Sửa đổi, bổ sung khoản 1 Điều 12 Thông tư số 22/2018/TT-NHNN như sau:
+“1. Cơ quan Thanh tra, giám sát ngân hàng có trách nhiệm là đầu mối đánh giá việc đáp ứng hồ sơ, tiêu chuẩn, điều kiện của nhân sự dự kiến của tổ chức tín dụng, chi nhánh ngân hàng nước ngoài thuộc đối tượng quy định tại khoản 1, khoản 2 Điều 4 Thông tư này theo quy định tại Luật Các tổ chức tín dụng và Thông tư này; lấy ý kiến các đơn vị liên quan; tổng hợp và trình Thống đốc Ngân hàng Nhà nước xem xét, có văn bản chấp thuận hoặc không chấp thuận dự kiến nhân sự của ngân hàng thương mại nêu tại khoản 1 Điều 4 Thông tư này; có văn bản chấp thuận hoặc không chấp thuận dự kiến nhân sự của tổ chức tín dụng phi ngân hàng, chi nhánh ngân hàng nước ngoài nêu tại khoản 2 Điều 4 Thông tư này.”.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2463,7 +3305,6 @@
           <t>15/2021/TT-NHNN; 24/2022/TT-NHNN</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
           <t>missed_event 2016-02-15 bao_dong_gia</t>
@@ -2479,18 +3320,26 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
         <is>
           <t>id cũ vilextime:T3:provision:3bf55600-e172-11f0-a444-b39f8b678525#k1:2012-07-11 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr"/>
-      <c r="W24" t="inlineStr"/>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>16/2012/TT-NHNN · hiệu lực 2012-07-10 → 2025-10-10 · lúc thu thập: Hết hiệu lực toàn bộ
+Điều 17. Thủ tục cấp Giấy phép nhập khẩu vàng nguyên liệu để sản xuất vàng trang sức, mỹ nghệ
+1. Doanh nghiệp có nhu cầu nhập khẩu vàng nguyên liệu để sản xuất vàng trang sức, mỹ nghệ nộp trực tiếp hoặc gửi qua đường bưu điện 02 (hai) bộ hồ sơ quy định tại Điều 10 Thông tư này đến Ngân hàng Nhà nước chi nhánh tỉnh, thành phố để được cấp Giấy phép nhập khẩu vàng nguyên liệu.</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 15/2021/TT-NHNN · hiệu lực 2021-11-20
+2. Thay thế cụm từ “nộp trực tiếp hoặc gửi qua đường bưu điện” bằng cụm từ “nộp trực tiếp tại Bộ phận một cửa hoặc qua dịch vụ bưu chính” tại khoản 1 Điều 15, khoản 1, khoản 2 Điều 16, khoản 1 Điều 17 Thông tư 16/2012/TT-NHNN.
+[amend] 24/2022/TT-NHNN · hiệu lực 2023-02-15
+(không tìm được đoạn)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2548,7 +3397,6 @@
           <t>15/2021/TT-NHNN; 24/2022/TT-NHNN</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
           <t>missed_event 2016-02-15 bao_dong_gia</t>
@@ -2564,18 +3412,26 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
         <is>
           <t>id cũ vilextime:T3:provision:3bf55600-e172-11f0-a444-b39f8b678525#k1:2021-11-21 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr"/>
-      <c r="W25" t="inlineStr"/>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>16/2012/TT-NHNN · hiệu lực 2012-07-10 → 2025-10-10 · lúc thu thập: Hết hiệu lực toàn bộ
+Điều 17. Thủ tục cấp Giấy phép nhập khẩu vàng nguyên liệu để sản xuất vàng trang sức, mỹ nghệ
+1. Doanh nghiệp có nhu cầu nhập khẩu vàng nguyên liệu để sản xuất vàng trang sức, mỹ nghệ nộp trực tiếp hoặc gửi qua đường bưu điện 02 (hai) bộ hồ sơ quy định tại Điều 10 Thông tư này đến Ngân hàng Nhà nước chi nhánh tỉnh, thành phố để được cấp Giấy phép nhập khẩu vàng nguyên liệu.</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 15/2021/TT-NHNN · hiệu lực 2021-11-20
+2. Thay thế cụm từ “nộp trực tiếp hoặc gửi qua đường bưu điện” bằng cụm từ “nộp trực tiếp tại Bộ phận một cửa hoặc qua dịch vụ bưu chính” tại khoản 1 Điều 15, khoản 1, khoản 2 Điều 16, khoản 1 Điều 17 Thông tư 16/2012/TT-NHNN.
+[amend] 24/2022/TT-NHNN · hiệu lực 2023-02-15
+(không tìm được đoạn)</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2638,7 +3494,6 @@
           <t>actor_has_transitional</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -2649,18 +3504,35 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
         <is>
           <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Một cặp vợ chồng đăng ký nuôi con nuôi tại Cơ quan đại diện thì nếu đủ điều kiện, việc xin ý kiến cơ quan trong nước được thực hiện trong thời hạn bao lâu và gửi cơ quan nào?»; nhãn cũ khong_dat question_ambiguous: Khoản 3 là đăng ký nuôi con nuôi rồi gửi văn bản thông báo; câu hỏi gọi đó là 'xin ý kiến cơ quan trong nước', vốn là việc của khoản 4 (yêu cầu cơ quan trong nước kiểm tra, xác minh). Đề xuất hỏi thời hạn đăng ký và nơi gửi thông báo). Hỏi thời hạn đăng ký và nơi nhận thông báo: 20 ngày/Cục Con nuôi, 20 ngày/Bộ Tư pháp, 15 ngày làm việc/Bộ Tư pháp; ba đáp án; id cũ vilextime:T3:provision:3ebea3e0-2d54-11f1-99aa-5169be827cf7:2011-05-09 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr"/>
-      <c r="W26" t="inlineStr"/>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>19/2011/NĐ-CP · hiệu lực 2011-05-08 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 27. Thủ tục nộp hồ sơ và đăng ký việc nuôi con nuôi tại Cơ quan đại diện
+3. Nếu xét thấy các bên có đủ điều kiện theo quy định tại Điều 14 của Luật Nuôi con nuôi, thì trong thời hạn 20 ngày, kể từ ngày lấy ý kiến của những người liên quan, Cơ quan đại diện đăng ký việc nuôi con nuôi.
+Khi đăng ký nuôi con nuôi, cha mẹ nuôi, cha mẹ đẻ, người giám hộ và người được nhận làm con nuôi phải có mặt. Cơ quan đại diện ghi vào Sổ đăng ký nuôi con nuôi và trao Giấy chứng nhận nuôi con nuôi cho các bên, đồng thời gửi văn bản thông báo cho Cục Con nuôi và Cục Lãnh sự kèm theo bản sao Giấy chứng nhận nuôi con nuôi.</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 06/2025/NĐ-CP · hiệu lực 2025-01-08
+a) Thay thế cụm từ "Cục Con nuôi" bằng cụm từ "Bộ Tư pháp" tại Điều 13, khoản 3 Điều 17, khoản 1, khoản 2 và khoản 3 Điều 18, khoản 2 Điều 20, khoản 3 và khoản 4 Điều 27, khoản 2 Điều 31, khoản 2 và khoản 3 Điều 36, khoản 2 Điều 47 của Nghị định số 19/2011/NĐ-CP ;
+[amend] 18/2026/NĐ-CP · hiệu lực 2026-01-15
+c) Thay thế cụm từ “trong thời hạn 20 ngày” thành “trong thời hạn 15 ngày làm việc” tại khoản 3 Điều 27;
+CHUYỂN TIẾP: Điều 16. Điều khoản chuyển tiếp
+1. Đối với hồ sơ đề nghị giải quyết thủ tục hành chính được quy định tại các Điều 1, 2, 3, 4, 5, 6, 7, 8, 9, 10 và 12 Nghị định này đã được cơ quan có thẩm quyền tiếp nhận hoặc đã được đóng dấu bưu chính trước ngày Nghị định này có hiệu lực thì thực hiện theo quy định của pháp luật đang có hiệu lực điều chỉnh trong lĩnh vực đó tại thời điểm hồ sơ được tiếp nhận.
+2. Đối với các hồ sơ đề nghị giải quyết thủ tục hành chính quy định tại Điều 11 Nghị định này:
+a) Trường hợp hồ sơ đăng ký đối với quyền sử dụng đất, tài sản gắn liền với đất, chuyển tiếp đăng ký thế chấp quyền tài sản phát sinh từ hợp đồng mua bán nhà ở hoặc từ hợp đồng mua bán tài sản khác gắn liền với đất có bản gốc Giấy chứng nhận thuộc thành phần hồ sơ đã được tiếp nhận trước ngày Nghị định này có hiệu lực thi hành mà chưa được giải quyết thì khi giải quyết hồ sơ đăng ký, Văn phòng đăng ký đất đai cập nhật nội dung đăng ký vào Cơ sở dữ liệu mà không ghi nội dung đăng ký trên Giấy chứng nhận.
+b) Trường hợp nội dung đăng ký biện pháp bảo đảm bằng quyền sử dụng đất, tài sản gắn liền với đất đã được ghi trên Giấy chứng nhận trước ngày Nghị định này có hiệu lực thi hành thì khi có yêu cầu đăng ký thay đổi để rút bớt quyền sử dụng đất hoặc rút bớt tài sản gắn liền với đất, khi có yêu cầu xóa đăng ký hoặc khi thực hiện hủy đăng ký, người yêu cầu đăng ký nộp bản gốc Giấy chứng nhận trong hồ sơ đăng ký. Việc giải quyết hồ sơ đăng ký, việc hủy đăng ký được thực hiện như sau:
+Đối với trường hợp đăng ký thay đổi để rút bớt quyền sử dụng đất hoặc rút bớt tài sản gắn liền với đất hoặc xóa đăng ký thì Văn phòng đăng ký đất đai cập nhật nội dung xóa đăng ký đối với tài sản được rút bớt hoặc cập nhật nội dung xóa đăng ký biện pháp bảo đảm vào Cơ sở dữ liệu; ghi nội dung xóa đăng ký đối với tài sản được rút bớt hoặc ghi nội dung xóa đăng ký biện pháp bảo đảm trên Giấy chứng nhận;
+Đối với trường hợp hủy đăng ký thì Văn phòng đăng ký đất đai cập nhật nội dung hủy đăng ký vào Cơ sở dữ liệu; ghi nội dung hủy đăng ký trên Giấy chứng nhận; đồng thời thực hiện thông báo về việc hủy đăng ký theo quy định tại Điều 21 Nghị định này;
+c) Trường hợp thực hiện việc đăng ký thay đổi, xóa đăng ký hoặc hủy đăng ký quy định tại điểm a và điểm b khoản này mà Giấy chứng nhận không còn dòng trống để ghi nội dung xóa đăng ký, nội dung hủy đăng ký thì Văn phòng đăng ký đất đai cập nhật nội dung xóa đăng ký hoặc hủy đăng ký vào Cơ sở dữ liệu đất đai và cấp mới Giấy chứng nhận trả cho người sử dụng đất, chủ sở hữu tài sản gắn liền với đất theo quy định của pháp luật về đất đai.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2723,7 +3595,6 @@
           <t>actor_has_transitional</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -2734,18 +3605,35 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
         <is>
           <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Một cặp vợ chồng đăng ký nuôi con nuôi tại Cơ quan đại diện thì nếu đủ điều kiện, việc xin ý kiến cơ quan trong nước được thực hiện trong thời hạn bao lâu và gửi cơ quan nào?»; nhãn cũ khong_dat question_ambiguous: Khoản 3 là đăng ký nuôi con nuôi rồi gửi văn bản thông báo; câu hỏi gọi đó là 'xin ý kiến cơ quan trong nước', vốn là việc của khoản 4 (yêu cầu cơ quan trong nước kiểm tra, xác minh). Đề xuất hỏi thời hạn đăng ký và nơi gửi thông báo). Hỏi thời hạn đăng ký và nơi nhận thông báo: 20 ngày/Cục Con nuôi, 20 ngày/Bộ Tư pháp, 15 ngày làm việc/Bộ Tư pháp; ba đáp án; id cũ vilextime:T3:provision:3ebea3e0-2d54-11f1-99aa-5169be827cf7:2025-01-09 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr"/>
-      <c r="W27" t="inlineStr"/>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>19/2011/NĐ-CP · hiệu lực 2011-05-08 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 27. Thủ tục nộp hồ sơ và đăng ký việc nuôi con nuôi tại Cơ quan đại diện
+3. Nếu xét thấy các bên có đủ điều kiện theo quy định tại Điều 14 của Luật Nuôi con nuôi, thì trong thời hạn 20 ngày, kể từ ngày lấy ý kiến của những người liên quan, Cơ quan đại diện đăng ký việc nuôi con nuôi.
+Khi đăng ký nuôi con nuôi, cha mẹ nuôi, cha mẹ đẻ, người giám hộ và người được nhận làm con nuôi phải có mặt. Cơ quan đại diện ghi vào Sổ đăng ký nuôi con nuôi và trao Giấy chứng nhận nuôi con nuôi cho các bên, đồng thời gửi văn bản thông báo cho Cục Con nuôi và Cục Lãnh sự kèm theo bản sao Giấy chứng nhận nuôi con nuôi.</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 06/2025/NĐ-CP · hiệu lực 2025-01-08
+a) Thay thế cụm từ "Cục Con nuôi" bằng cụm từ "Bộ Tư pháp" tại Điều 13, khoản 3 Điều 17, khoản 1, khoản 2 và khoản 3 Điều 18, khoản 2 Điều 20, khoản 3 và khoản 4 Điều 27, khoản 2 Điều 31, khoản 2 và khoản 3 Điều 36, khoản 2 Điều 47 của Nghị định số 19/2011/NĐ-CP ;
+[amend] 18/2026/NĐ-CP · hiệu lực 2026-01-15
+c) Thay thế cụm từ “trong thời hạn 20 ngày” thành “trong thời hạn 15 ngày làm việc” tại khoản 3 Điều 27;
+CHUYỂN TIẾP: Điều 16. Điều khoản chuyển tiếp
+1. Đối với hồ sơ đề nghị giải quyết thủ tục hành chính được quy định tại các Điều 1, 2, 3, 4, 5, 6, 7, 8, 9, 10 và 12 Nghị định này đã được cơ quan có thẩm quyền tiếp nhận hoặc đã được đóng dấu bưu chính trước ngày Nghị định này có hiệu lực thì thực hiện theo quy định của pháp luật đang có hiệu lực điều chỉnh trong lĩnh vực đó tại thời điểm hồ sơ được tiếp nhận.
+2. Đối với các hồ sơ đề nghị giải quyết thủ tục hành chính quy định tại Điều 11 Nghị định này:
+a) Trường hợp hồ sơ đăng ký đối với quyền sử dụng đất, tài sản gắn liền với đất, chuyển tiếp đăng ký thế chấp quyền tài sản phát sinh từ hợp đồng mua bán nhà ở hoặc từ hợp đồng mua bán tài sản khác gắn liền với đất có bản gốc Giấy chứng nhận thuộc thành phần hồ sơ đã được tiếp nhận trước ngày Nghị định này có hiệu lực thi hành mà chưa được giải quyết thì khi giải quyết hồ sơ đăng ký, Văn phòng đăng ký đất đai cập nhật nội dung đăng ký vào Cơ sở dữ liệu mà không ghi nội dung đăng ký trên Giấy chứng nhận.
+b) Trường hợp nội dung đăng ký biện pháp bảo đảm bằng quyền sử dụng đất, tài sản gắn liền với đất đã được ghi trên Giấy chứng nhận trước ngày Nghị định này có hiệu lực thi hành thì khi có yêu cầu đăng ký thay đổi để rút bớt quyền sử dụng đất hoặc rút bớt tài sản gắn liền với đất, khi có yêu cầu xóa đăng ký hoặc khi thực hiện hủy đăng ký, người yêu cầu đăng ký nộp bản gốc Giấy chứng nhận trong hồ sơ đăng ký. Việc giải quyết hồ sơ đăng ký, việc hủy đăng ký được thực hiện như sau:
+Đối với trường hợp đăng ký thay đổi để rút bớt quyền sử dụng đất hoặc rút bớt tài sản gắn liền với đất hoặc xóa đăng ký thì Văn phòng đăng ký đất đai cập nhật nội dung xóa đăng ký đối với tài sản được rút bớt hoặc cập nhật nội dung xóa đăng ký biện pháp bảo đảm vào Cơ sở dữ liệu; ghi nội dung xóa đăng ký đối với tài sản được rút bớt hoặc ghi nội dung xóa đăng ký biện pháp bảo đảm trên Giấy chứng nhận;
+Đối với trường hợp hủy đăng ký thì Văn phòng đăng ký đất đai cập nhật nội dung hủy đăng ký vào Cơ sở dữ liệu; ghi nội dung hủy đăng ký trên Giấy chứng nhận; đồng thời thực hiện thông báo về việc hủy đăng ký theo quy định tại Điều 21 Nghị định này;
+c) Trường hợp thực hiện việc đăng ký thay đổi, xóa đăng ký hoặc hủy đăng ký quy định tại điểm a và điểm b khoản này mà Giấy chứng nhận không còn dòng trống để ghi nội dung xóa đăng ký, nội dung hủy đăng ký thì Văn phòng đăng ký đất đai cập nhật nội dung xóa đăng ký hoặc hủy đăng ký vào Cơ sở dữ liệu đất đai và cấp mới Giấy chứng nhận trả cho người sử dụng đất, chủ sở hữu tài sản gắn liền với đất theo quy định của pháp luật về đất đai.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2808,7 +3696,6 @@
           <t>actor_has_transitional</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -2819,18 +3706,35 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
         <is>
           <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Một cặp vợ chồng đăng ký nuôi con nuôi tại Cơ quan đại diện thì nếu đủ điều kiện, việc xin ý kiến cơ quan trong nước được thực hiện trong thời hạn bao lâu và gửi cơ quan nào?»; nhãn cũ khong_dat question_ambiguous: Khoản 3 là đăng ký nuôi con nuôi rồi gửi văn bản thông báo; câu hỏi gọi đó là 'xin ý kiến cơ quan trong nước', vốn là việc của khoản 4 (yêu cầu cơ quan trong nước kiểm tra, xác minh). Đề xuất hỏi thời hạn đăng ký và nơi gửi thông báo). Hỏi thời hạn đăng ký và nơi nhận thông báo: 20 ngày/Cục Con nuôi, 20 ngày/Bộ Tư pháp, 15 ngày làm việc/Bộ Tư pháp; ba đáp án; id cũ vilextime:T3:provision:3ebea3e0-2d54-11f1-99aa-5169be827cf7:2026-01-16 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr"/>
-      <c r="W28" t="inlineStr"/>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>19/2011/NĐ-CP · hiệu lực 2011-05-08 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 27. Thủ tục nộp hồ sơ và đăng ký việc nuôi con nuôi tại Cơ quan đại diện
+3. Nếu xét thấy các bên có đủ điều kiện theo quy định tại Điều 14 của Luật Nuôi con nuôi, thì trong thời hạn 20 ngày, kể từ ngày lấy ý kiến của những người liên quan, Cơ quan đại diện đăng ký việc nuôi con nuôi.
+Khi đăng ký nuôi con nuôi, cha mẹ nuôi, cha mẹ đẻ, người giám hộ và người được nhận làm con nuôi phải có mặt. Cơ quan đại diện ghi vào Sổ đăng ký nuôi con nuôi và trao Giấy chứng nhận nuôi con nuôi cho các bên, đồng thời gửi văn bản thông báo cho Cục Con nuôi và Cục Lãnh sự kèm theo bản sao Giấy chứng nhận nuôi con nuôi.</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 06/2025/NĐ-CP · hiệu lực 2025-01-08
+a) Thay thế cụm từ "Cục Con nuôi" bằng cụm từ "Bộ Tư pháp" tại Điều 13, khoản 3 Điều 17, khoản 1, khoản 2 và khoản 3 Điều 18, khoản 2 Điều 20, khoản 3 và khoản 4 Điều 27, khoản 2 Điều 31, khoản 2 và khoản 3 Điều 36, khoản 2 Điều 47 của Nghị định số 19/2011/NĐ-CP ;
+[amend] 18/2026/NĐ-CP · hiệu lực 2026-01-15
+c) Thay thế cụm từ “trong thời hạn 20 ngày” thành “trong thời hạn 15 ngày làm việc” tại khoản 3 Điều 27;
+CHUYỂN TIẾP: Điều 16. Điều khoản chuyển tiếp
+1. Đối với hồ sơ đề nghị giải quyết thủ tục hành chính được quy định tại các Điều 1, 2, 3, 4, 5, 6, 7, 8, 9, 10 và 12 Nghị định này đã được cơ quan có thẩm quyền tiếp nhận hoặc đã được đóng dấu bưu chính trước ngày Nghị định này có hiệu lực thì thực hiện theo quy định của pháp luật đang có hiệu lực điều chỉnh trong lĩnh vực đó tại thời điểm hồ sơ được tiếp nhận.
+2. Đối với các hồ sơ đề nghị giải quyết thủ tục hành chính quy định tại Điều 11 Nghị định này:
+a) Trường hợp hồ sơ đăng ký đối với quyền sử dụng đất, tài sản gắn liền với đất, chuyển tiếp đăng ký thế chấp quyền tài sản phát sinh từ hợp đồng mua bán nhà ở hoặc từ hợp đồng mua bán tài sản khác gắn liền với đất có bản gốc Giấy chứng nhận thuộc thành phần hồ sơ đã được tiếp nhận trước ngày Nghị định này có hiệu lực thi hành mà chưa được giải quyết thì khi giải quyết hồ sơ đăng ký, Văn phòng đăng ký đất đai cập nhật nội dung đăng ký vào Cơ sở dữ liệu mà không ghi nội dung đăng ký trên Giấy chứng nhận.
+b) Trường hợp nội dung đăng ký biện pháp bảo đảm bằng quyền sử dụng đất, tài sản gắn liền với đất đã được ghi trên Giấy chứng nhận trước ngày Nghị định này có hiệu lực thi hành thì khi có yêu cầu đăng ký thay đổi để rút bớt quyền sử dụng đất hoặc rút bớt tài sản gắn liền với đất, khi có yêu cầu xóa đăng ký hoặc khi thực hiện hủy đăng ký, người yêu cầu đăng ký nộp bản gốc Giấy chứng nhận trong hồ sơ đăng ký. Việc giải quyết hồ sơ đăng ký, việc hủy đăng ký được thực hiện như sau:
+Đối với trường hợp đăng ký thay đổi để rút bớt quyền sử dụng đất hoặc rút bớt tài sản gắn liền với đất hoặc xóa đăng ký thì Văn phòng đăng ký đất đai cập nhật nội dung xóa đăng ký đối với tài sản được rút bớt hoặc cập nhật nội dung xóa đăng ký biện pháp bảo đảm vào Cơ sở dữ liệu; ghi nội dung xóa đăng ký đối với tài sản được rút bớt hoặc ghi nội dung xóa đăng ký biện pháp bảo đảm trên Giấy chứng nhận;
+Đối với trường hợp hủy đăng ký thì Văn phòng đăng ký đất đai cập nhật nội dung hủy đăng ký vào Cơ sở dữ liệu; ghi nội dung hủy đăng ký trên Giấy chứng nhận; đồng thời thực hiện thông báo về việc hủy đăng ký theo quy định tại Điều 21 Nghị định này;
+c) Trường hợp thực hiện việc đăng ký thay đổi, xóa đăng ký hoặc hủy đăng ký quy định tại điểm a và điểm b khoản này mà Giấy chứng nhận không còn dòng trống để ghi nội dung xóa đăng ký, nội dung hủy đăng ký thì Văn phòng đăng ký đất đai cập nhật nội dung xóa đăng ký hoặc hủy đăng ký vào Cơ sở dữ liệu đất đai và cấp mới Giấy chứng nhận trả cho người sử dụng đất, chủ sở hữu tài sản gắn liền với đất theo quy định của pháp luật về đất đai.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2893,7 +3797,6 @@
           <t>actor_has_transitional</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -2904,18 +3807,35 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
         <is>
           <t>id cũ vilextime:T3:provision:3ec22650-2d54-11f1-a21d-01a2a81c6434:2011-05-09 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
-      <c r="W29" t="inlineStr"/>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>19/2011/NĐ-CP · hiệu lực 2011-05-08 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 31. Hồ sơ của tổ chức con nuôi nước ngoài xin cấp phép hoạt động tại Việt Nam
+2. Giấy tờ quy định tại khoản 1 Điều này được lập thành 02 bộ hồ sơ và nộp tại Cục Con nuôi.</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 06/2025/NĐ-CP · hiệu lực 2025-01-08
+a) Thay thế cụm từ "Cục Con nuôi" bằng cụm từ "Bộ Tư pháp" tại Điều 13, khoản 3 Điều 17, khoản 1, khoản 2 và khoản 3 Điều 18, khoản 2 Điều 20, khoản 3 và khoản 4 Điều 27, khoản 2 Điều 31, khoản 2 và khoản 3 Điều 36, khoản 2 Điều 47 của Nghị định số 19/2011/NĐ-CP ;
+[amend] 18/2026/NĐ-CP · hiệu lực 2026-01-15
+3. Sửa đổi, bổ sung khoản 2 Điều 31 như sau:
+“2. Giấy tờ quy định tại khoản 1 Điều này được lập thành 01 bộ hồ sơ và nộp tại Bộ Tư pháp.”
+CHUYỂN TIẾP: Điều 16. Điều khoản chuyển tiếp
+1. Đối với hồ sơ đề nghị giải quyết thủ tục hành chính được quy định tại các Điều 1, 2, 3, 4, 5, 6, 7, 8, 9, 10 và 12 Nghị định này đã được cơ quan có thẩm quyền tiếp nhận hoặc đã được đóng dấu bưu chính trước ngày Nghị định này có hiệu lực thì thực hiện theo quy định của pháp luật đang có hiệu lực điều chỉnh trong lĩnh vực đó tại thời điểm hồ sơ được tiếp nhận.
+2. Đối với các hồ sơ đề nghị giải quyết thủ tục hành chính quy định tại Điều 11 Nghị định này:
+a) Trường hợp hồ sơ đăng ký đối với quyền sử dụng đất, tài sản gắn liền với đất, chuyển tiếp đăng ký thế chấp quyền tài sản phát sinh từ hợp đồng mua bán nhà ở hoặc từ hợp đồng mua bán tài sản khác gắn liền với đất có bản gốc Giấy chứng nhận thuộc thành phần hồ sơ đã được tiếp nhận trước ngày Nghị định này có hiệu lực thi hành mà chưa được giải quyết thì khi giải quyết hồ sơ đăng ký, Văn phòng đăng ký đất đai cập nhật nội dung đăng ký vào Cơ sở dữ liệu mà không ghi nội dung đăng ký trên Giấy chứng nhận.
+b) Trường hợp nội dung đăng ký biện pháp bảo đảm bằng quyền sử dụng đất, tài sản gắn liền với đất đã được ghi trên Giấy chứng nhận trước ngày Nghị định này có hiệu lực thi hành thì khi có yêu cầu đăng ký thay đổi để rút bớt quyền sử dụng đất hoặc rút bớt tài sản gắn liền với đất, khi có yêu cầu xóa đăng ký hoặc khi thực hiện hủy đăng ký, người yêu cầu đăng ký nộp bản gốc Giấy chứng nhận trong hồ sơ đăng ký. Việc giải quyết hồ sơ đăng ký, việc hủy đăng ký được thực hiện như sau:
+Đối với trường hợp đăng ký thay đổi để rút bớt quyền sử dụng đất hoặc rút bớt tài sản gắn liền với đất hoặc xóa đăng ký thì Văn phòng đăng ký đất đai cập nhật nội dung xóa đăng ký đối với tài sản được rút bớt hoặc cập nhật nội dung xóa đăng ký biện pháp bảo đảm vào Cơ sở dữ liệu; ghi nội dung xóa đăng ký đối với tài sản được rút bớt hoặc ghi nội dung xóa đăng ký biện pháp bảo đảm trên Giấy chứng nhận;
+Đối với trường hợp hủy đăng ký thì Văn phòng đăng ký đất đai cập nhật nội dung hủy đăng ký vào Cơ sở dữ liệu; ghi nội dung hủy đăng ký trên Giấy chứng nhận; đồng thời thực hiện thông báo về việc hủy đăng ký theo quy định tại Điều 21 Nghị định này;
+c) Trường hợp thực hiện việc đăng ký thay đổi, xóa đăng ký hoặc hủy đăng ký quy định tại điểm a và điểm b khoản này mà Giấy chứng nhận không còn dòng trống để ghi nội dung xóa đăng ký, nội dung hủy đăng ký thì Văn phòng đăng ký đất đai cập nhật nội dung xóa đăng ký hoặc hủy đăng ký vào Cơ sở dữ liệu đất đai và cấp mới Giấy chứng nhận trả cho người sử dụng đất, chủ sở hữu tài sản gắn liền với đất theo quy định của pháp luật về đất đai.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2978,7 +3898,6 @@
           <t>actor_has_transitional</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -2989,18 +3908,35 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
         <is>
           <t>id cũ vilextime:T3:provision:3ec22650-2d54-11f1-a21d-01a2a81c6434:2025-01-09 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr"/>
-      <c r="W30" t="inlineStr"/>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>19/2011/NĐ-CP · hiệu lực 2011-05-08 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 31. Hồ sơ của tổ chức con nuôi nước ngoài xin cấp phép hoạt động tại Việt Nam
+2. Giấy tờ quy định tại khoản 1 Điều này được lập thành 02 bộ hồ sơ và nộp tại Cục Con nuôi.</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 06/2025/NĐ-CP · hiệu lực 2025-01-08
+a) Thay thế cụm từ "Cục Con nuôi" bằng cụm từ "Bộ Tư pháp" tại Điều 13, khoản 3 Điều 17, khoản 1, khoản 2 và khoản 3 Điều 18, khoản 2 Điều 20, khoản 3 và khoản 4 Điều 27, khoản 2 Điều 31, khoản 2 và khoản 3 Điều 36, khoản 2 Điều 47 của Nghị định số 19/2011/NĐ-CP ;
+[amend] 18/2026/NĐ-CP · hiệu lực 2026-01-15
+3. Sửa đổi, bổ sung khoản 2 Điều 31 như sau:
+“2. Giấy tờ quy định tại khoản 1 Điều này được lập thành 01 bộ hồ sơ và nộp tại Bộ Tư pháp.”
+CHUYỂN TIẾP: Điều 16. Điều khoản chuyển tiếp
+1. Đối với hồ sơ đề nghị giải quyết thủ tục hành chính được quy định tại các Điều 1, 2, 3, 4, 5, 6, 7, 8, 9, 10 và 12 Nghị định này đã được cơ quan có thẩm quyền tiếp nhận hoặc đã được đóng dấu bưu chính trước ngày Nghị định này có hiệu lực thì thực hiện theo quy định của pháp luật đang có hiệu lực điều chỉnh trong lĩnh vực đó tại thời điểm hồ sơ được tiếp nhận.
+2. Đối với các hồ sơ đề nghị giải quyết thủ tục hành chính quy định tại Điều 11 Nghị định này:
+a) Trường hợp hồ sơ đăng ký đối với quyền sử dụng đất, tài sản gắn liền với đất, chuyển tiếp đăng ký thế chấp quyền tài sản phát sinh từ hợp đồng mua bán nhà ở hoặc từ hợp đồng mua bán tài sản khác gắn liền với đất có bản gốc Giấy chứng nhận thuộc thành phần hồ sơ đã được tiếp nhận trước ngày Nghị định này có hiệu lực thi hành mà chưa được giải quyết thì khi giải quyết hồ sơ đăng ký, Văn phòng đăng ký đất đai cập nhật nội dung đăng ký vào Cơ sở dữ liệu mà không ghi nội dung đăng ký trên Giấy chứng nhận.
+b) Trường hợp nội dung đăng ký biện pháp bảo đảm bằng quyền sử dụng đất, tài sản gắn liền với đất đã được ghi trên Giấy chứng nhận trước ngày Nghị định này có hiệu lực thi hành thì khi có yêu cầu đăng ký thay đổi để rút bớt quyền sử dụng đất hoặc rút bớt tài sản gắn liền với đất, khi có yêu cầu xóa đăng ký hoặc khi thực hiện hủy đăng ký, người yêu cầu đăng ký nộp bản gốc Giấy chứng nhận trong hồ sơ đăng ký. Việc giải quyết hồ sơ đăng ký, việc hủy đăng ký được thực hiện như sau:
+Đối với trường hợp đăng ký thay đổi để rút bớt quyền sử dụng đất hoặc rút bớt tài sản gắn liền với đất hoặc xóa đăng ký thì Văn phòng đăng ký đất đai cập nhật nội dung xóa đăng ký đối với tài sản được rút bớt hoặc cập nhật nội dung xóa đăng ký biện pháp bảo đảm vào Cơ sở dữ liệu; ghi nội dung xóa đăng ký đối với tài sản được rút bớt hoặc ghi nội dung xóa đăng ký biện pháp bảo đảm trên Giấy chứng nhận;
+Đối với trường hợp hủy đăng ký thì Văn phòng đăng ký đất đai cập nhật nội dung hủy đăng ký vào Cơ sở dữ liệu; ghi nội dung hủy đăng ký trên Giấy chứng nhận; đồng thời thực hiện thông báo về việc hủy đăng ký theo quy định tại Điều 21 Nghị định này;
+c) Trường hợp thực hiện việc đăng ký thay đổi, xóa đăng ký hoặc hủy đăng ký quy định tại điểm a và điểm b khoản này mà Giấy chứng nhận không còn dòng trống để ghi nội dung xóa đăng ký, nội dung hủy đăng ký thì Văn phòng đăng ký đất đai cập nhật nội dung xóa đăng ký hoặc hủy đăng ký vào Cơ sở dữ liệu đất đai và cấp mới Giấy chứng nhận trả cho người sử dụng đất, chủ sở hữu tài sản gắn liền với đất theo quy định của pháp luật về đất đai.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3063,7 +3999,6 @@
           <t>actor_has_transitional</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -3074,18 +4009,35 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
         <is>
           <t>id cũ vilextime:T3:provision:3ec22650-2d54-11f1-a21d-01a2a81c6434:2026-01-16 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr"/>
-      <c r="W31" t="inlineStr"/>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>19/2011/NĐ-CP · hiệu lực 2011-05-08 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 31. Hồ sơ của tổ chức con nuôi nước ngoài xin cấp phép hoạt động tại Việt Nam
+2. Giấy tờ quy định tại khoản 1 Điều này được lập thành 02 bộ hồ sơ và nộp tại Cục Con nuôi.</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 06/2025/NĐ-CP · hiệu lực 2025-01-08
+a) Thay thế cụm từ "Cục Con nuôi" bằng cụm từ "Bộ Tư pháp" tại Điều 13, khoản 3 Điều 17, khoản 1, khoản 2 và khoản 3 Điều 18, khoản 2 Điều 20, khoản 3 và khoản 4 Điều 27, khoản 2 Điều 31, khoản 2 và khoản 3 Điều 36, khoản 2 Điều 47 của Nghị định số 19/2011/NĐ-CP ;
+[amend] 18/2026/NĐ-CP · hiệu lực 2026-01-15
+3. Sửa đổi, bổ sung khoản 2 Điều 31 như sau:
+“2. Giấy tờ quy định tại khoản 1 Điều này được lập thành 01 bộ hồ sơ và nộp tại Bộ Tư pháp.”
+CHUYỂN TIẾP: Điều 16. Điều khoản chuyển tiếp
+1. Đối với hồ sơ đề nghị giải quyết thủ tục hành chính được quy định tại các Điều 1, 2, 3, 4, 5, 6, 7, 8, 9, 10 và 12 Nghị định này đã được cơ quan có thẩm quyền tiếp nhận hoặc đã được đóng dấu bưu chính trước ngày Nghị định này có hiệu lực thì thực hiện theo quy định của pháp luật đang có hiệu lực điều chỉnh trong lĩnh vực đó tại thời điểm hồ sơ được tiếp nhận.
+2. Đối với các hồ sơ đề nghị giải quyết thủ tục hành chính quy định tại Điều 11 Nghị định này:
+a) Trường hợp hồ sơ đăng ký đối với quyền sử dụng đất, tài sản gắn liền với đất, chuyển tiếp đăng ký thế chấp quyền tài sản phát sinh từ hợp đồng mua bán nhà ở hoặc từ hợp đồng mua bán tài sản khác gắn liền với đất có bản gốc Giấy chứng nhận thuộc thành phần hồ sơ đã được tiếp nhận trước ngày Nghị định này có hiệu lực thi hành mà chưa được giải quyết thì khi giải quyết hồ sơ đăng ký, Văn phòng đăng ký đất đai cập nhật nội dung đăng ký vào Cơ sở dữ liệu mà không ghi nội dung đăng ký trên Giấy chứng nhận.
+b) Trường hợp nội dung đăng ký biện pháp bảo đảm bằng quyền sử dụng đất, tài sản gắn liền với đất đã được ghi trên Giấy chứng nhận trước ngày Nghị định này có hiệu lực thi hành thì khi có yêu cầu đăng ký thay đổi để rút bớt quyền sử dụng đất hoặc rút bớt tài sản gắn liền với đất, khi có yêu cầu xóa đăng ký hoặc khi thực hiện hủy đăng ký, người yêu cầu đăng ký nộp bản gốc Giấy chứng nhận trong hồ sơ đăng ký. Việc giải quyết hồ sơ đăng ký, việc hủy đăng ký được thực hiện như sau:
+Đối với trường hợp đăng ký thay đổi để rút bớt quyền sử dụng đất hoặc rút bớt tài sản gắn liền với đất hoặc xóa đăng ký thì Văn phòng đăng ký đất đai cập nhật nội dung xóa đăng ký đối với tài sản được rút bớt hoặc cập nhật nội dung xóa đăng ký biện pháp bảo đảm vào Cơ sở dữ liệu; ghi nội dung xóa đăng ký đối với tài sản được rút bớt hoặc ghi nội dung xóa đăng ký biện pháp bảo đảm trên Giấy chứng nhận;
+Đối với trường hợp hủy đăng ký thì Văn phòng đăng ký đất đai cập nhật nội dung hủy đăng ký vào Cơ sở dữ liệu; ghi nội dung hủy đăng ký trên Giấy chứng nhận; đồng thời thực hiện thông báo về việc hủy đăng ký theo quy định tại Điều 21 Nghị định này;
+c) Trường hợp thực hiện việc đăng ký thay đổi, xóa đăng ký hoặc hủy đăng ký quy định tại điểm a và điểm b khoản này mà Giấy chứng nhận không còn dòng trống để ghi nội dung xóa đăng ký, nội dung hủy đăng ký thì Văn phòng đăng ký đất đai cập nhật nội dung xóa đăng ký hoặc hủy đăng ký vào Cơ sở dữ liệu đất đai và cấp mới Giấy chứng nhận trả cho người sử dụng đất, chủ sở hữu tài sản gắn liền với đất theo quy định của pháp luật về đất đai.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3163,18 +4115,55 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
         <is>
           <t>Đáp án là danh sách dẫn chiếu điểm, khoản (như nhãn dat của 38/2024 Điều 51 ở T2); ba đáp án khác nhau; id cũ vilextime:T3:provision:406c63b0-2c7f-11f1-9540-7d73c403d1d2:2020-10-16 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr"/>
-      <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
-      <c r="V32" t="inlineStr"/>
-      <c r="W32" t="inlineStr"/>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>98/2020/NĐ-CP · hiệu lực 2020-10-15 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 81. Thẩm quyền xử phạt của Chủ tịch Ủy ban nhân dân các cấp
+2. Chủ tịch Ủy ban nhân dân cấp huyện có quyền:
+a) Phạt cảnh cáo;
+b) Phạt tiền đến 50.000.000 đồng đối với cá nhân và phạt tiền đến 100.000.000 đồng đối với tổ chức;
+c) Tước quyền sử dụng giấy phép, chứng chỉ hành nghề có thời hạn hoặc đình chỉ hoạt động có thời hạn;
+d) Tịch thu tang vật, phương tiện vi phạm hành chính có giá trị không vượt quá mức tiền phạt được quy định tại điểm b khoản này;
+đ) Áp dụng các biện pháp khắc phục hậu quả quy định tại các điểm b, c, đ, e, g, h, i và k khoản 3 Điều 4 của Nghị định này.</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 17/2022/NĐ-CP · hiệu lực 2022-01-31
+44. Sửa đổi, bổ sung Điều 81 như sau:
+“ Điều 81. Thẩm quyền xử phạt của Chủ tịch Ủy ban nhân dân các cấp
+1. Chủ tịch Ủy ban nhân dân cấp xã có quyền:
+a) Phạt cảnh cáo;
+b) Phạt tiền đến 5.000.000 đồng;
+c) Tịch thu tang vật, phương tiện vi phạm hành chính có giá trị không vượt quá 10.000.000 đồng;
+d) Áp dụng biện pháp khắc phục hậu quả quy định tại điểm b khoản 3 Điều 4 của Nghị định này.
+2. Chủ tịch Ủy ban nhân dân cấp huyện có quyền:
+a) Phạt cảnh cáo;
+b) Phạt tiền đến 100.000.000 đồng đối với các hành vi vi phạm quy định tại Mục 2 và Mục 9 Chương II của Nghị định này; phạt tiền đến 50.000.000 đồng đối với các hành vi vi phạm khác quy định tại Nghị định này;
+c) Tước quyền sử dụng giấy phép, chứng chỉ hành nghề có thời hạn hoặc đình chỉ hoạt động có thời hạn;
+d) Tịch thu tang vật, phương tiện vi phạm hành chính;
+đ) Áp dụng các biện pháp khắc phục hậu quả quy định tại các điểm b, c, đ, e, g, h, i, k và l khoản 3 Điều 4 của Nghị định này.
+3. Chủ tịch Ủy ban nhân dân cấp tỉnh có quyền:
+a) Phạt cảnh cáo;
+b) Phạt tiền đến mức tối đa quy định tại Nghị định này;
+c) Tước quyền sử dụng giấy phép, chứng chỉ hành nghề có thời hạn hoặc đình chỉ hoạt động có thời hạn;
+d) Tịch thu tang vật, phương tiện vi phạm hành chính;
+đ) Áp dụng các biện pháp khắc phục hậu quả quy định tại Nghị định này.”.
+CHUYỂN TIẾP: Điều 5. Điều khoản chuyển tiếp
+Đối với các hành vi vi phạm hành chính trong lĩnh vực hóa chất và vật liệu nổ công nghiệp; điện lực, sử dụng năng lượng tiết kiệm và hiệu quả; hoạt động thương mại, sản xuất, buôn bán hàng giả, hàng cấm và bảo vệ quyền lợi người tiêu dùng; hoạt động dầu khí, kinh doanh xăng dầu và khí xảy ra trước ngày Nghị định này có hiệu lực thi hành mà sau đó mới bị phát hiện thì áp dụng quy định tại Nghị định này để xử phạt vi phạm hành chính nếu Nghị định này không quy định trách nhiệm pháp lý hoặc quy định trách nhiệm pháp lý nhẹ hơn cho cá nhân, tổ chức vi phạm.
+[amend] 24/2025/NĐ-CP · hiệu lực 2025-02-21
+b) Sửa đổi điểm đ khoản 2 như sau:
+"đ) Áp dụng các biện pháp khắc phục hậu quả quy định tại các điểm đ, e, h, i khoản 1 Điều 28 của Luật Xử lý vi phạm hành chính và khoản 3 Điều 4 của Nghị định này.".
+CHUYỂN TIẾP: Điều 3. Điều khoản chuyển tiếp
+1. Đối với các hành vi vi phạm hành chính trong hoạt động thương mại, sản xuất, buôn bán hàng giả, hàng cấm và bảo vệ quyền lợi người tiêu dùng xảy ra trước ngày Nghị định này có hiệu lực thi hành mà sau đó mới bị phát hiện hoặc đang xem xét, giải quyết thì áp dụng Nghị định của Chính phủ về xử phạt vi phạm hành chính có hiệu lực tại thời điểm thực hiện hành vi vi phạm để xử lý. Trường hợp Nghị định này không quy định trách nhiệm pháp lý hoặc quy định trách nhiệm pháp lý nhẹ hơn đối với hành vi đã xảy ra thì áp dụng các quy định của Nghị định này để xử lý.
+2. Đối với quyết định xử phạt vi phạm hành chính đã được ban hành trước ngày Nghị định này có hiệu lực thi hành, mà tổ chức, cá nhân bị xử phạt vi phạm hành chính còn khiếu nại thì áp dụng quy định của Luật Xử lý vi phạm hành chính, Nghị định số 98/2020/NĐ-CP ngày 26 tháng 8 năm 2020 của Chính phủ quy định xử phạt vi phạm hành chính trong hoạt động thương mại, sản xuất, buôn bán hàng giả, hàng cấm và bảo vệ quyền lợi người tiêu dùng, Nghị định số 17/2022/NĐ-CP ngày 31 tháng 01 năm 2022 của Chính phủ sửa đổi, bổ sung một số điều của các Nghị định quy định về xử phạt vi phạm hành chính trong lĩnh vực hóa chất và vật liệu nổ công nghiệp; điện lực, an toàn đập thủy điện, sử dụng năng lượng tiết kiệm và hiệu quả; hoạt động thương mại, sản xuất, buôn bán hàng giả, hàng cấm và bảo vệ quyền lợi người tiêu dùng, hoạt động dầu khí, kinh doanh xăng dầu và khí.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3252,18 +4241,55 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
         <is>
           <t>Đáp án là danh sách dẫn chiếu điểm, khoản (như nhãn dat của 38/2024 Điều 51 ở T2); ba đáp án khác nhau; id cũ vilextime:T3:provision:406c63b0-2c7f-11f1-9540-7d73c403d1d2:2022-02-01 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr"/>
-      <c r="T33" t="inlineStr"/>
-      <c r="U33" t="inlineStr"/>
-      <c r="V33" t="inlineStr"/>
-      <c r="W33" t="inlineStr"/>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>98/2020/NĐ-CP · hiệu lực 2020-10-15 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 81. Thẩm quyền xử phạt của Chủ tịch Ủy ban nhân dân các cấp
+2. Chủ tịch Ủy ban nhân dân cấp huyện có quyền:
+a) Phạt cảnh cáo;
+b) Phạt tiền đến 50.000.000 đồng đối với cá nhân và phạt tiền đến 100.000.000 đồng đối với tổ chức;
+c) Tước quyền sử dụng giấy phép, chứng chỉ hành nghề có thời hạn hoặc đình chỉ hoạt động có thời hạn;
+d) Tịch thu tang vật, phương tiện vi phạm hành chính có giá trị không vượt quá mức tiền phạt được quy định tại điểm b khoản này;
+đ) Áp dụng các biện pháp khắc phục hậu quả quy định tại các điểm b, c, đ, e, g, h, i và k khoản 3 Điều 4 của Nghị định này.</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 17/2022/NĐ-CP · hiệu lực 2022-01-31
+44. Sửa đổi, bổ sung Điều 81 như sau:
+“ Điều 81. Thẩm quyền xử phạt của Chủ tịch Ủy ban nhân dân các cấp
+1. Chủ tịch Ủy ban nhân dân cấp xã có quyền:
+a) Phạt cảnh cáo;
+b) Phạt tiền đến 5.000.000 đồng;
+c) Tịch thu tang vật, phương tiện vi phạm hành chính có giá trị không vượt quá 10.000.000 đồng;
+d) Áp dụng biện pháp khắc phục hậu quả quy định tại điểm b khoản 3 Điều 4 của Nghị định này.
+2. Chủ tịch Ủy ban nhân dân cấp huyện có quyền:
+a) Phạt cảnh cáo;
+b) Phạt tiền đến 100.000.000 đồng đối với các hành vi vi phạm quy định tại Mục 2 và Mục 9 Chương II của Nghị định này; phạt tiền đến 50.000.000 đồng đối với các hành vi vi phạm khác quy định tại Nghị định này;
+c) Tước quyền sử dụng giấy phép, chứng chỉ hành nghề có thời hạn hoặc đình chỉ hoạt động có thời hạn;
+d) Tịch thu tang vật, phương tiện vi phạm hành chính;
+đ) Áp dụng các biện pháp khắc phục hậu quả quy định tại các điểm b, c, đ, e, g, h, i, k và l khoản 3 Điều 4 của Nghị định này.
+3. Chủ tịch Ủy ban nhân dân cấp tỉnh có quyền:
+a) Phạt cảnh cáo;
+b) Phạt tiền đến mức tối đa quy định tại Nghị định này;
+c) Tước quyền sử dụng giấy phép, chứng chỉ hành nghề có thời hạn hoặc đình chỉ hoạt động có thời hạn;
+d) Tịch thu tang vật, phương tiện vi phạm hành chính;
+đ) Áp dụng các biện pháp khắc phục hậu quả quy định tại Nghị định này.”.
+CHUYỂN TIẾP: Điều 5. Điều khoản chuyển tiếp
+Đối với các hành vi vi phạm hành chính trong lĩnh vực hóa chất và vật liệu nổ công nghiệp; điện lực, sử dụng năng lượng tiết kiệm và hiệu quả; hoạt động thương mại, sản xuất, buôn bán hàng giả, hàng cấm và bảo vệ quyền lợi người tiêu dùng; hoạt động dầu khí, kinh doanh xăng dầu và khí xảy ra trước ngày Nghị định này có hiệu lực thi hành mà sau đó mới bị phát hiện thì áp dụng quy định tại Nghị định này để xử phạt vi phạm hành chính nếu Nghị định này không quy định trách nhiệm pháp lý hoặc quy định trách nhiệm pháp lý nhẹ hơn cho cá nhân, tổ chức vi phạm.
+[amend] 24/2025/NĐ-CP · hiệu lực 2025-02-21
+b) Sửa đổi điểm đ khoản 2 như sau:
+"đ) Áp dụng các biện pháp khắc phục hậu quả quy định tại các điểm đ, e, h, i khoản 1 Điều 28 của Luật Xử lý vi phạm hành chính và khoản 3 Điều 4 của Nghị định này.".
+CHUYỂN TIẾP: Điều 3. Điều khoản chuyển tiếp
+1. Đối với các hành vi vi phạm hành chính trong hoạt động thương mại, sản xuất, buôn bán hàng giả, hàng cấm và bảo vệ quyền lợi người tiêu dùng xảy ra trước ngày Nghị định này có hiệu lực thi hành mà sau đó mới bị phát hiện hoặc đang xem xét, giải quyết thì áp dụng Nghị định của Chính phủ về xử phạt vi phạm hành chính có hiệu lực tại thời điểm thực hiện hành vi vi phạm để xử lý. Trường hợp Nghị định này không quy định trách nhiệm pháp lý hoặc quy định trách nhiệm pháp lý nhẹ hơn đối với hành vi đã xảy ra thì áp dụng các quy định của Nghị định này để xử lý.
+2. Đối với quyết định xử phạt vi phạm hành chính đã được ban hành trước ngày Nghị định này có hiệu lực thi hành, mà tổ chức, cá nhân bị xử phạt vi phạm hành chính còn khiếu nại thì áp dụng quy định của Luật Xử lý vi phạm hành chính, Nghị định số 98/2020/NĐ-CP ngày 26 tháng 8 năm 2020 của Chính phủ quy định xử phạt vi phạm hành chính trong hoạt động thương mại, sản xuất, buôn bán hàng giả, hàng cấm và bảo vệ quyền lợi người tiêu dùng, Nghị định số 17/2022/NĐ-CP ngày 31 tháng 01 năm 2022 của Chính phủ sửa đổi, bổ sung một số điều của các Nghị định quy định về xử phạt vi phạm hành chính trong lĩnh vực hóa chất và vật liệu nổ công nghiệp; điện lực, an toàn đập thủy điện, sử dụng năng lượng tiết kiệm và hiệu quả; hoạt động thương mại, sản xuất, buôn bán hàng giả, hàng cấm và bảo vệ quyền lợi người tiêu dùng, hoạt động dầu khí, kinh doanh xăng dầu và khí.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3341,18 +4367,55 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
         <is>
           <t>Đáp án là danh sách dẫn chiếu điểm, khoản (như nhãn dat của 38/2024 Điều 51 ở T2); ba đáp án khác nhau; id cũ vilextime:T3:provision:406c63b0-2c7f-11f1-9540-7d73c403d1d2:2025-02-22 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S34" t="inlineStr"/>
-      <c r="T34" t="inlineStr"/>
-      <c r="U34" t="inlineStr"/>
-      <c r="V34" t="inlineStr"/>
-      <c r="W34" t="inlineStr"/>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>98/2020/NĐ-CP · hiệu lực 2020-10-15 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 81. Thẩm quyền xử phạt của Chủ tịch Ủy ban nhân dân các cấp
+2. Chủ tịch Ủy ban nhân dân cấp huyện có quyền:
+a) Phạt cảnh cáo;
+b) Phạt tiền đến 50.000.000 đồng đối với cá nhân và phạt tiền đến 100.000.000 đồng đối với tổ chức;
+c) Tước quyền sử dụng giấy phép, chứng chỉ hành nghề có thời hạn hoặc đình chỉ hoạt động có thời hạn;
+d) Tịch thu tang vật, phương tiện vi phạm hành chính có giá trị không vượt quá mức tiền phạt được quy định tại điểm b khoản này;
+đ) Áp dụng các biện pháp khắc phục hậu quả quy định tại các điểm b, c, đ, e, g, h, i và k khoản 3 Điều 4 của Nghị định này.</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 17/2022/NĐ-CP · hiệu lực 2022-01-31
+44. Sửa đổi, bổ sung Điều 81 như sau:
+“ Điều 81. Thẩm quyền xử phạt của Chủ tịch Ủy ban nhân dân các cấp
+1. Chủ tịch Ủy ban nhân dân cấp xã có quyền:
+a) Phạt cảnh cáo;
+b) Phạt tiền đến 5.000.000 đồng;
+c) Tịch thu tang vật, phương tiện vi phạm hành chính có giá trị không vượt quá 10.000.000 đồng;
+d) Áp dụng biện pháp khắc phục hậu quả quy định tại điểm b khoản 3 Điều 4 của Nghị định này.
+2. Chủ tịch Ủy ban nhân dân cấp huyện có quyền:
+a) Phạt cảnh cáo;
+b) Phạt tiền đến 100.000.000 đồng đối với các hành vi vi phạm quy định tại Mục 2 và Mục 9 Chương II của Nghị định này; phạt tiền đến 50.000.000 đồng đối với các hành vi vi phạm khác quy định tại Nghị định này;
+c) Tước quyền sử dụng giấy phép, chứng chỉ hành nghề có thời hạn hoặc đình chỉ hoạt động có thời hạn;
+d) Tịch thu tang vật, phương tiện vi phạm hành chính;
+đ) Áp dụng các biện pháp khắc phục hậu quả quy định tại các điểm b, c, đ, e, g, h, i, k và l khoản 3 Điều 4 của Nghị định này.
+3. Chủ tịch Ủy ban nhân dân cấp tỉnh có quyền:
+a) Phạt cảnh cáo;
+b) Phạt tiền đến mức tối đa quy định tại Nghị định này;
+c) Tước quyền sử dụng giấy phép, chứng chỉ hành nghề có thời hạn hoặc đình chỉ hoạt động có thời hạn;
+d) Tịch thu tang vật, phương tiện vi phạm hành chính;
+đ) Áp dụng các biện pháp khắc phục hậu quả quy định tại Nghị định này.”.
+CHUYỂN TIẾP: Điều 5. Điều khoản chuyển tiếp
+Đối với các hành vi vi phạm hành chính trong lĩnh vực hóa chất và vật liệu nổ công nghiệp; điện lực, sử dụng năng lượng tiết kiệm và hiệu quả; hoạt động thương mại, sản xuất, buôn bán hàng giả, hàng cấm và bảo vệ quyền lợi người tiêu dùng; hoạt động dầu khí, kinh doanh xăng dầu và khí xảy ra trước ngày Nghị định này có hiệu lực thi hành mà sau đó mới bị phát hiện thì áp dụng quy định tại Nghị định này để xử phạt vi phạm hành chính nếu Nghị định này không quy định trách nhiệm pháp lý hoặc quy định trách nhiệm pháp lý nhẹ hơn cho cá nhân, tổ chức vi phạm.
+[amend] 24/2025/NĐ-CP · hiệu lực 2025-02-21
+b) Sửa đổi điểm đ khoản 2 như sau:
+"đ) Áp dụng các biện pháp khắc phục hậu quả quy định tại các điểm đ, e, h, i khoản 1 Điều 28 của Luật Xử lý vi phạm hành chính và khoản 3 Điều 4 của Nghị định này.".
+CHUYỂN TIẾP: Điều 3. Điều khoản chuyển tiếp
+1. Đối với các hành vi vi phạm hành chính trong hoạt động thương mại, sản xuất, buôn bán hàng giả, hàng cấm và bảo vệ quyền lợi người tiêu dùng xảy ra trước ngày Nghị định này có hiệu lực thi hành mà sau đó mới bị phát hiện hoặc đang xem xét, giải quyết thì áp dụng Nghị định của Chính phủ về xử phạt vi phạm hành chính có hiệu lực tại thời điểm thực hiện hành vi vi phạm để xử lý. Trường hợp Nghị định này không quy định trách nhiệm pháp lý hoặc quy định trách nhiệm pháp lý nhẹ hơn đối với hành vi đã xảy ra thì áp dụng các quy định của Nghị định này để xử lý.
+2. Đối với quyết định xử phạt vi phạm hành chính đã được ban hành trước ngày Nghị định này có hiệu lực thi hành, mà tổ chức, cá nhân bị xử phạt vi phạm hành chính còn khiếu nại thì áp dụng quy định của Luật Xử lý vi phạm hành chính, Nghị định số 98/2020/NĐ-CP ngày 26 tháng 8 năm 2020 của Chính phủ quy định xử phạt vi phạm hành chính trong hoạt động thương mại, sản xuất, buôn bán hàng giả, hàng cấm và bảo vệ quyền lợi người tiêu dùng, Nghị định số 17/2022/NĐ-CP ngày 31 tháng 01 năm 2022 của Chính phủ sửa đổi, bổ sung một số điều của các Nghị định quy định về xử phạt vi phạm hành chính trong lĩnh vực hóa chất và vật liệu nổ công nghiệp; điện lực, an toàn đập thủy điện, sử dụng năng lượng tiết kiệm và hiệu quả; hoạt động thương mại, sản xuất, buôn bán hàng giả, hàng cấm và bảo vệ quyền lợi người tiêu dùng, hoạt động dầu khí, kinh doanh xăng dầu và khí.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3415,7 +4478,6 @@
           <t>actor_has_transitional</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -3426,18 +4488,60 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr">
         <is>
           <t>id cũ vilextime:T3:provision:40778740-2c7f-11f1-abee-c9b7a53cf5c7:2020-10-16 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S35" t="inlineStr"/>
-      <c r="T35" t="inlineStr"/>
-      <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr"/>
-      <c r="W35" t="inlineStr"/>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>98/2020/NĐ-CP · hiệu lực 2020-10-15 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 84. Thẩm quyền xử phạt của Hải quan
+4. Cục trưởng Cục điều tra chống buôn lậu, Cục trưởng Cục kiểm tra sau thông quan thuộc Tổng cục Hải quan, Cục trưởng Cục Hải quan tỉnh, liên tỉnh, thành phố trực thuộc trung ương có quyền:
+a) Phạt cảnh cáo;
+b) Phạt tiền đến 50.000.000 đồng đối với cá nhân và phạt tiền đến 100.000.000 đồng đối với tổ chức;
+c) Tước quyền sử dụng giấy phép, chứng chỉ hành nghề có thời hạn hoặc đình chỉ hoạt động có thời hạn;
+d) Tịch thu tang vật, phương tiện vi phạm hành chính có giá trị không vượt quá mức tiền phạt được quy định tại điểm b khoản này;
+đ) Áp dụng các biện pháp khắc phục hậu quả quy định tại các điểm a, b, d và e khoản 3 Điều 4 của Nghị định này.</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 17/2022/NĐ-CP · hiệu lực 2022-01-31
+47. Sửa đổi, bổ sung Điều 84 như sau:
+“ Điều 84. Thẩm quyền xử phạt của Hải quan
+1. Công chức Hải quan đang thi hành công vụ có quyền:
+a) Phạt cảnh cáo;
+b) Phạt tiền đến 500.000 đồng.
+2. Đội trưởng, Tổ trưởng thuộc Chi cục Hải quan; Tổ trưởng thuộc Đội Kiểm soát thuộc Cục Hải quan tỉnh, liên tỉnh, thành phố trực thuộc trung ương; Đội trưởng thuộc Chi cục Kiểm tra sau thông quan có quyền:
+a) Phạt cảnh cáo;
+b) Phạt tiền đến 5.000.000 đồng.
+3. Chi cục trưởng Chi cục Hải quan; Chi cục trưởng Chi cục Kiểm tra sau thông quan, Đội trưởng Đội kiểm soát thuộc Cục Hải quan tỉnh, liên tỉnh, thành phố trực thuộc trung ương; Đội trưởng Đội Điều tra hình sự, Đội trưởng Đội kiểm soát chống buôn lậu, Hải đội trưởng Hải đội kiểm soát trên biển và Đội trưởng Đội kiểm soát chống buôn lậu hàng giả và bảo vệ quyền sở hữu trí tuệ thuộc Cục Điều tra chống buôn lậu; Chi cục trưởng Chi cục Kiểm tra sau thông quan thuộc Cục Kiểm tra sau thông quan có quyền:
+a) Phạt cảnh cáo;
+b) Phạt tiền đến 25.000.000 đồng;
+c) Tịch thu tang vật, phương tiện vi phạm hành chính có giá trị không vượt quá 50.000.000 đồng;
+d) Áp dụng các biện pháp khắc phục hậu quả quy định tại các điểm a, b, d, e và l khoản 3 Điều 4 của Nghị định này.
+4. Cục trưởng Cục điều tra chống buôn lậu, Cục trưởng Cục kiểm tra sau thông quan thuộc Tổng cục Hải quan, Cục trưởng Cục Hải quan tỉnh, liên tỉnh, thành phố trực thuộc trung ương có quyền:
+a) Phạt cảnh cáo;
+b) Phạt tiền đến 50.000.000 đồng;
+c) Tước quyền sử dụng giấy phép, chứng chỉ hành nghề có thời hạn hoặc đình chỉ hoạt động có thời hạn;
+d) Tịch thu tang vật, phương tiện vi phạm hành chính;
+đ) Áp dụng các biện pháp khắc phục hậu quả quy định tại các điểm a, b, d, e và l khoản 3 Điều 4 của Nghị định này.
+5. Tổng cục trưởng Tổng cục Hải quan có quyền:
+a) Phạt cảnh cáo;
+b) Phạt tiền đến mức tối đa quy định tại Nghị định này;
+c) Tịch thu tang vật, phương tiện vi phạm hành chính;
+d) Áp dụng các biện pháp khắc phục hậu quả quy định tại các điểm a, b, d, e và l khoản 3 Điều 4 của Nghị định này.”.
+CHUYỂN TIẾP: Điều 5. Điều khoản chuyển tiếp
+Đối với các hành vi vi phạm hành chính trong lĩnh vực hóa chất và vật liệu nổ công nghiệp; điện lực, sử dụng năng lượng tiết kiệm và hiệu quả; hoạt động thương mại, sản xuất, buôn bán hàng giả, hàng cấm và bảo vệ quyền lợi người tiêu dùng; hoạt động dầu khí, kinh doanh xăng dầu và khí xảy ra trước ngày Nghị định này có hiệu lực thi hành mà sau đó mới bị phát hiện thì áp dụng quy định tại Nghị định này để xử phạt vi phạm hành chính nếu Nghị định này không quy định trách nhiệm pháp lý hoặc quy định trách nhiệm pháp lý nhẹ hơn cho cá nhân, tổ chức vi phạm.
+[amend] 24/2025/NĐ-CP · hiệu lực 2025-02-21
+b) Sửa đổi điểm đ khoản 4 như sau:
+"đ) Áp dụng các biện pháp khắc phục hậu quả quy định tại điểm đ khoản 1 Điều 28 của Luật Xử lý vi phạm hành chính và khoản 3 Điều 4 của Nghị định này.";
+CHUYỂN TIẾP: Điều 3. Điều khoản chuyển tiếp
+1. Đối với các hành vi vi phạm hành chính trong hoạt động thương mại, sản xuất, buôn bán hàng giả, hàng cấm và bảo vệ quyền lợi người tiêu dùng xảy ra trước ngày Nghị định này có hiệu lực thi hành mà sau đó mới bị phát hiện hoặc đang xem xét, giải quyết thì áp dụng Nghị định của Chính phủ về xử phạt vi phạm hành chính có hiệu lực tại thời điểm thực hiện hành vi vi phạm để xử lý. Trường hợp Nghị định này không quy định trách nhiệm pháp lý hoặc quy định trách nhiệm pháp lý nhẹ hơn đối với hành vi đã xảy ra thì áp dụng các quy định của Nghị định này để xử lý.
+2. Đối với quyết định xử phạt vi phạm hành chính đã được ban hành trước ngày Nghị định này có hiệu lực thi hành, mà tổ chức, cá nhân bị xử phạt vi phạm hành chính còn khiếu nại thì áp dụng quy định của Luật Xử lý vi phạm hành chính, Nghị định số 98/2020/NĐ-CP ngày 26 tháng 8 năm 2020 của Chính phủ quy định xử phạt vi phạm hành chính trong hoạt động thương mại, sản xuất, buôn bán hàng giả, hàng cấm và bảo vệ quyền lợi người tiêu dùng, Nghị định số 17/2022/NĐ-CP ngày 31 tháng 01 năm 2022 của Chính phủ sửa đổi, bổ sung một số điều của các Nghị định quy định về xử phạt vi phạm hành chính trong lĩnh vực hóa chất và vật liệu nổ công nghiệp; điện lực, an toàn đập thủy điện, sử dụng năng lượng tiết kiệm và hiệu quả; hoạt động thương mại, sản xuất, buôn bán hàng giả, hàng cấm và bảo vệ quyền lợi người tiêu dùng, hoạt động dầu khí, kinh doanh xăng dầu và khí.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3500,7 +4604,6 @@
           <t>actor_has_transitional</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -3511,18 +4614,60 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr">
         <is>
           <t>id cũ vilextime:T3:provision:40778740-2c7f-11f1-abee-c9b7a53cf5c7:2022-02-01 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S36" t="inlineStr"/>
-      <c r="T36" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr"/>
-      <c r="W36" t="inlineStr"/>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>98/2020/NĐ-CP · hiệu lực 2020-10-15 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 84. Thẩm quyền xử phạt của Hải quan
+4. Cục trưởng Cục điều tra chống buôn lậu, Cục trưởng Cục kiểm tra sau thông quan thuộc Tổng cục Hải quan, Cục trưởng Cục Hải quan tỉnh, liên tỉnh, thành phố trực thuộc trung ương có quyền:
+a) Phạt cảnh cáo;
+b) Phạt tiền đến 50.000.000 đồng đối với cá nhân và phạt tiền đến 100.000.000 đồng đối với tổ chức;
+c) Tước quyền sử dụng giấy phép, chứng chỉ hành nghề có thời hạn hoặc đình chỉ hoạt động có thời hạn;
+d) Tịch thu tang vật, phương tiện vi phạm hành chính có giá trị không vượt quá mức tiền phạt được quy định tại điểm b khoản này;
+đ) Áp dụng các biện pháp khắc phục hậu quả quy định tại các điểm a, b, d và e khoản 3 Điều 4 của Nghị định này.</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 17/2022/NĐ-CP · hiệu lực 2022-01-31
+47. Sửa đổi, bổ sung Điều 84 như sau:
+“ Điều 84. Thẩm quyền xử phạt của Hải quan
+1. Công chức Hải quan đang thi hành công vụ có quyền:
+a) Phạt cảnh cáo;
+b) Phạt tiền đến 500.000 đồng.
+2. Đội trưởng, Tổ trưởng thuộc Chi cục Hải quan; Tổ trưởng thuộc Đội Kiểm soát thuộc Cục Hải quan tỉnh, liên tỉnh, thành phố trực thuộc trung ương; Đội trưởng thuộc Chi cục Kiểm tra sau thông quan có quyền:
+a) Phạt cảnh cáo;
+b) Phạt tiền đến 5.000.000 đồng.
+3. Chi cục trưởng Chi cục Hải quan; Chi cục trưởng Chi cục Kiểm tra sau thông quan, Đội trưởng Đội kiểm soát thuộc Cục Hải quan tỉnh, liên tỉnh, thành phố trực thuộc trung ương; Đội trưởng Đội Điều tra hình sự, Đội trưởng Đội kiểm soát chống buôn lậu, Hải đội trưởng Hải đội kiểm soát trên biển và Đội trưởng Đội kiểm soát chống buôn lậu hàng giả và bảo vệ quyền sở hữu trí tuệ thuộc Cục Điều tra chống buôn lậu; Chi cục trưởng Chi cục Kiểm tra sau thông quan thuộc Cục Kiểm tra sau thông quan có quyền:
+a) Phạt cảnh cáo;
+b) Phạt tiền đến 25.000.000 đồng;
+c) Tịch thu tang vật, phương tiện vi phạm hành chính có giá trị không vượt quá 50.000.000 đồng;
+d) Áp dụng các biện pháp khắc phục hậu quả quy định tại các điểm a, b, d, e và l khoản 3 Điều 4 của Nghị định này.
+4. Cục trưởng Cục điều tra chống buôn lậu, Cục trưởng Cục kiểm tra sau thông quan thuộc Tổng cục Hải quan, Cục trưởng Cục Hải quan tỉnh, liên tỉnh, thành phố trực thuộc trung ương có quyền:
+a) Phạt cảnh cáo;
+b) Phạt tiền đến 50.000.000 đồng;
+c) Tước quyền sử dụng giấy phép, chứng chỉ hành nghề có thời hạn hoặc đình chỉ hoạt động có thời hạn;
+d) Tịch thu tang vật, phương tiện vi phạm hành chính;
+đ) Áp dụng các biện pháp khắc phục hậu quả quy định tại các điểm a, b, d, e và l khoản 3 Điều 4 của Nghị định này.
+5. Tổng cục trưởng Tổng cục Hải quan có quyền:
+a) Phạt cảnh cáo;
+b) Phạt tiền đến mức tối đa quy định tại Nghị định này;
+c) Tịch thu tang vật, phương tiện vi phạm hành chính;
+d) Áp dụng các biện pháp khắc phục hậu quả quy định tại các điểm a, b, d, e và l khoản 3 Điều 4 của Nghị định này.”.
+CHUYỂN TIẾP: Điều 5. Điều khoản chuyển tiếp
+Đối với các hành vi vi phạm hành chính trong lĩnh vực hóa chất và vật liệu nổ công nghiệp; điện lực, sử dụng năng lượng tiết kiệm và hiệu quả; hoạt động thương mại, sản xuất, buôn bán hàng giả, hàng cấm và bảo vệ quyền lợi người tiêu dùng; hoạt động dầu khí, kinh doanh xăng dầu và khí xảy ra trước ngày Nghị định này có hiệu lực thi hành mà sau đó mới bị phát hiện thì áp dụng quy định tại Nghị định này để xử phạt vi phạm hành chính nếu Nghị định này không quy định trách nhiệm pháp lý hoặc quy định trách nhiệm pháp lý nhẹ hơn cho cá nhân, tổ chức vi phạm.
+[amend] 24/2025/NĐ-CP · hiệu lực 2025-02-21
+b) Sửa đổi điểm đ khoản 4 như sau:
+"đ) Áp dụng các biện pháp khắc phục hậu quả quy định tại điểm đ khoản 1 Điều 28 của Luật Xử lý vi phạm hành chính và khoản 3 Điều 4 của Nghị định này.";
+CHUYỂN TIẾP: Điều 3. Điều khoản chuyển tiếp
+1. Đối với các hành vi vi phạm hành chính trong hoạt động thương mại, sản xuất, buôn bán hàng giả, hàng cấm và bảo vệ quyền lợi người tiêu dùng xảy ra trước ngày Nghị định này có hiệu lực thi hành mà sau đó mới bị phát hiện hoặc đang xem xét, giải quyết thì áp dụng Nghị định của Chính phủ về xử phạt vi phạm hành chính có hiệu lực tại thời điểm thực hiện hành vi vi phạm để xử lý. Trường hợp Nghị định này không quy định trách nhiệm pháp lý hoặc quy định trách nhiệm pháp lý nhẹ hơn đối với hành vi đã xảy ra thì áp dụng các quy định của Nghị định này để xử lý.
+2. Đối với quyết định xử phạt vi phạm hành chính đã được ban hành trước ngày Nghị định này có hiệu lực thi hành, mà tổ chức, cá nhân bị xử phạt vi phạm hành chính còn khiếu nại thì áp dụng quy định của Luật Xử lý vi phạm hành chính, Nghị định số 98/2020/NĐ-CP ngày 26 tháng 8 năm 2020 của Chính phủ quy định xử phạt vi phạm hành chính trong hoạt động thương mại, sản xuất, buôn bán hàng giả, hàng cấm và bảo vệ quyền lợi người tiêu dùng, Nghị định số 17/2022/NĐ-CP ngày 31 tháng 01 năm 2022 của Chính phủ sửa đổi, bổ sung một số điều của các Nghị định quy định về xử phạt vi phạm hành chính trong lĩnh vực hóa chất và vật liệu nổ công nghiệp; điện lực, an toàn đập thủy điện, sử dụng năng lượng tiết kiệm và hiệu quả; hoạt động thương mại, sản xuất, buôn bán hàng giả, hàng cấm và bảo vệ quyền lợi người tiêu dùng, hoạt động dầu khí, kinh doanh xăng dầu và khí.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3585,7 +4730,6 @@
           <t>actor_has_transitional</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -3596,18 +4740,60 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr">
         <is>
           <t>id cũ vilextime:T3:provision:40778740-2c7f-11f1-abee-c9b7a53cf5c7:2025-02-22 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S37" t="inlineStr"/>
-      <c r="T37" t="inlineStr"/>
-      <c r="U37" t="inlineStr"/>
-      <c r="V37" t="inlineStr"/>
-      <c r="W37" t="inlineStr"/>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>98/2020/NĐ-CP · hiệu lực 2020-10-15 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 84. Thẩm quyền xử phạt của Hải quan
+4. Cục trưởng Cục điều tra chống buôn lậu, Cục trưởng Cục kiểm tra sau thông quan thuộc Tổng cục Hải quan, Cục trưởng Cục Hải quan tỉnh, liên tỉnh, thành phố trực thuộc trung ương có quyền:
+a) Phạt cảnh cáo;
+b) Phạt tiền đến 50.000.000 đồng đối với cá nhân và phạt tiền đến 100.000.000 đồng đối với tổ chức;
+c) Tước quyền sử dụng giấy phép, chứng chỉ hành nghề có thời hạn hoặc đình chỉ hoạt động có thời hạn;
+d) Tịch thu tang vật, phương tiện vi phạm hành chính có giá trị không vượt quá mức tiền phạt được quy định tại điểm b khoản này;
+đ) Áp dụng các biện pháp khắc phục hậu quả quy định tại các điểm a, b, d và e khoản 3 Điều 4 của Nghị định này.</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 17/2022/NĐ-CP · hiệu lực 2022-01-31
+47. Sửa đổi, bổ sung Điều 84 như sau:
+“ Điều 84. Thẩm quyền xử phạt của Hải quan
+1. Công chức Hải quan đang thi hành công vụ có quyền:
+a) Phạt cảnh cáo;
+b) Phạt tiền đến 500.000 đồng.
+2. Đội trưởng, Tổ trưởng thuộc Chi cục Hải quan; Tổ trưởng thuộc Đội Kiểm soát thuộc Cục Hải quan tỉnh, liên tỉnh, thành phố trực thuộc trung ương; Đội trưởng thuộc Chi cục Kiểm tra sau thông quan có quyền:
+a) Phạt cảnh cáo;
+b) Phạt tiền đến 5.000.000 đồng.
+3. Chi cục trưởng Chi cục Hải quan; Chi cục trưởng Chi cục Kiểm tra sau thông quan, Đội trưởng Đội kiểm soát thuộc Cục Hải quan tỉnh, liên tỉnh, thành phố trực thuộc trung ương; Đội trưởng Đội Điều tra hình sự, Đội trưởng Đội kiểm soát chống buôn lậu, Hải đội trưởng Hải đội kiểm soát trên biển và Đội trưởng Đội kiểm soát chống buôn lậu hàng giả và bảo vệ quyền sở hữu trí tuệ thuộc Cục Điều tra chống buôn lậu; Chi cục trưởng Chi cục Kiểm tra sau thông quan thuộc Cục Kiểm tra sau thông quan có quyền:
+a) Phạt cảnh cáo;
+b) Phạt tiền đến 25.000.000 đồng;
+c) Tịch thu tang vật, phương tiện vi phạm hành chính có giá trị không vượt quá 50.000.000 đồng;
+d) Áp dụng các biện pháp khắc phục hậu quả quy định tại các điểm a, b, d, e và l khoản 3 Điều 4 của Nghị định này.
+4. Cục trưởng Cục điều tra chống buôn lậu, Cục trưởng Cục kiểm tra sau thông quan thuộc Tổng cục Hải quan, Cục trưởng Cục Hải quan tỉnh, liên tỉnh, thành phố trực thuộc trung ương có quyền:
+a) Phạt cảnh cáo;
+b) Phạt tiền đến 50.000.000 đồng;
+c) Tước quyền sử dụng giấy phép, chứng chỉ hành nghề có thời hạn hoặc đình chỉ hoạt động có thời hạn;
+d) Tịch thu tang vật, phương tiện vi phạm hành chính;
+đ) Áp dụng các biện pháp khắc phục hậu quả quy định tại các điểm a, b, d, e và l khoản 3 Điều 4 của Nghị định này.
+5. Tổng cục trưởng Tổng cục Hải quan có quyền:
+a) Phạt cảnh cáo;
+b) Phạt tiền đến mức tối đa quy định tại Nghị định này;
+c) Tịch thu tang vật, phương tiện vi phạm hành chính;
+d) Áp dụng các biện pháp khắc phục hậu quả quy định tại các điểm a, b, d, e và l khoản 3 Điều 4 của Nghị định này.”.
+CHUYỂN TIẾP: Điều 5. Điều khoản chuyển tiếp
+Đối với các hành vi vi phạm hành chính trong lĩnh vực hóa chất và vật liệu nổ công nghiệp; điện lực, sử dụng năng lượng tiết kiệm và hiệu quả; hoạt động thương mại, sản xuất, buôn bán hàng giả, hàng cấm và bảo vệ quyền lợi người tiêu dùng; hoạt động dầu khí, kinh doanh xăng dầu và khí xảy ra trước ngày Nghị định này có hiệu lực thi hành mà sau đó mới bị phát hiện thì áp dụng quy định tại Nghị định này để xử phạt vi phạm hành chính nếu Nghị định này không quy định trách nhiệm pháp lý hoặc quy định trách nhiệm pháp lý nhẹ hơn cho cá nhân, tổ chức vi phạm.
+[amend] 24/2025/NĐ-CP · hiệu lực 2025-02-21
+b) Sửa đổi điểm đ khoản 4 như sau:
+"đ) Áp dụng các biện pháp khắc phục hậu quả quy định tại điểm đ khoản 1 Điều 28 của Luật Xử lý vi phạm hành chính và khoản 3 Điều 4 của Nghị định này.";
+CHUYỂN TIẾP: Điều 3. Điều khoản chuyển tiếp
+1. Đối với các hành vi vi phạm hành chính trong hoạt động thương mại, sản xuất, buôn bán hàng giả, hàng cấm và bảo vệ quyền lợi người tiêu dùng xảy ra trước ngày Nghị định này có hiệu lực thi hành mà sau đó mới bị phát hiện hoặc đang xem xét, giải quyết thì áp dụng Nghị định của Chính phủ về xử phạt vi phạm hành chính có hiệu lực tại thời điểm thực hiện hành vi vi phạm để xử lý. Trường hợp Nghị định này không quy định trách nhiệm pháp lý hoặc quy định trách nhiệm pháp lý nhẹ hơn đối với hành vi đã xảy ra thì áp dụng các quy định của Nghị định này để xử lý.
+2. Đối với quyết định xử phạt vi phạm hành chính đã được ban hành trước ngày Nghị định này có hiệu lực thi hành, mà tổ chức, cá nhân bị xử phạt vi phạm hành chính còn khiếu nại thì áp dụng quy định của Luật Xử lý vi phạm hành chính, Nghị định số 98/2020/NĐ-CP ngày 26 tháng 8 năm 2020 của Chính phủ quy định xử phạt vi phạm hành chính trong hoạt động thương mại, sản xuất, buôn bán hàng giả, hàng cấm và bảo vệ quyền lợi người tiêu dùng, Nghị định số 17/2022/NĐ-CP ngày 31 tháng 01 năm 2022 của Chính phủ sửa đổi, bổ sung một số điều của các Nghị định quy định về xử phạt vi phạm hành chính trong lĩnh vực hóa chất và vật liệu nổ công nghiệp; điện lực, an toàn đập thủy điện, sử dụng năng lượng tiết kiệm và hiệu quả; hoạt động thương mại, sản xuất, buôn bán hàng giả, hàng cấm và bảo vệ quyền lợi người tiêu dùng, hoạt động dầu khí, kinh doanh xăng dầu và khí.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3665,8 +4851,6 @@
           <t>08/2018/TT-BKHĐT; 09/2019/TT-BKHĐT</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -3677,18 +4861,37 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr">
         <is>
           <t>id cũ vilextime:T3:provision:43d5c1fe-2c89-11f1-8be5-39da3bf77b9b:2010-04-15 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S38" t="inlineStr"/>
-      <c r="T38" t="inlineStr"/>
-      <c r="U38" t="inlineStr"/>
-      <c r="V38" t="inlineStr"/>
-      <c r="W38" t="inlineStr"/>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>07/2010/TT-BKH · hiệu lực 2010-04-14 → nay · lúc thu thập: Còn hiệu lực
+Điều 9. Chế độ báo cáo và mẫu biểu báo cáo đối với Ban QLDA (quy định tại Điều 27 của Quy chế)
+2. Chế độ báo cáo
+Chế độ báo cáo do Cơ quan phê duyệt khoản viện trợ PCPNN quy định.</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 08/2018/TT-BKHĐT · hiệu lực 2019-02-11
+Điều 1. Sửa đổi, bổ sung Khoản 2 Điều 9 Thông tư số 07/2010/TT-BKH ngày 20 tháng 3 năm 2010 của Bộ Kế hoạch và Đầu tư hướng dẫn thi hành Nghị định số 93/2009/NĐ-CP ngày 22 tháng 10 năm 2009 của Chính phủ ban hành Quy chế quản lý và sử dụng viện trợ phi Chính phủ nước ngoài như sau:
+"2. Chế độ báo cáo
+Chế độ báo cáo do Cơ quan phê duyệt khoản viện trợ phi chính phủ nước ngoài (PCPNN) quy định.
+a) Báo cáo 6 tháng: Chậm nhất vào ngày 10 tháng 7, Ban Quản lý dự án phải gửi báo cáo về Cơ quan phê duyệt khoản viện trợ PCPNN.
+b) Báo cáo năm: Chậm nhất vào ngày 31 tháng 01 năm tiếp sau, Ban Quản lý dự án phải gửi báo cáo về Cơ quan phê duyệt khoản viện trợ PCPNN.
+c) Báo cáo kết thúc dự án: Chậm nhất 6 tháng kể từ ngày kết thúc thực hiện chương trình, dự án, Ban Quản lý dự án phải gửi báo cáo theo mẫu Báo cáo kết thúc chương trình, dự án viện trợ PCPNN bằng văn bản, fax và thư điện tử về Cơ quan phê duyệt khoản viện trợ PCPNN."
+[amend] 09/2019/TT-BKHĐT · hiệu lực 2019-09-16
+1. Sửa đổi, bổ sung Khoản 2 Điều 9 như sau:
+“2. Chế độ báo cáo
+Chế độ báo cáo do Cơ quan phê duyệt khoản viện trợ phi chính phủ nước ngoài (PCPNN) quy định.
+a) Báo cáo 6 tháng: Chậm nhất vào ngày 18 tháng 6, Ban Quản lý dự án phải gửi báo cáo về Cơ quan phê duyệt khoản viện trợ PCPNN. Thời gian chốt số liệu được tính từ ngày 15 tháng 12 năm trước kỳ báo cáo đến ngày 14 tháng 6 của năm báo cáo.
+b) Báo cáo năm: Chậm nhất vào ngày 18 tháng 12, Ban Quản lý dự án phải gửi báo cáo về Cơ quan phê duyệt khoản viện trợ PCPNN. Thời gian chốt số liệu được tính từ ngày 15 tháng 12 năm trước kỳ báo cáo đến ngày 14 tháng 12.
+c) Báo cáo kết thúc dự án: Chậm nhất 6 tháng kể từ ngày kết thúc thực hiện chương trình, dự án, Ban Quản lý dự án phải gửi báo cáo theo mẫu Báo cáo kết thúc chương trình, dự án viện trợ PCPNN bằng văn bản, fax và thư điện tử về Cơ quan phê duyệt khoản viện trợ PCPNN.”</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3746,8 +4949,6 @@
           <t>08/2018/TT-BKHĐT; 09/2019/TT-BKHĐT</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -3758,18 +4959,37 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr">
         <is>
           <t>id cũ vilextime:T3:provision:43d5c1fe-2c89-11f1-8be5-39da3bf77b9b:2019-02-12 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S39" t="inlineStr"/>
-      <c r="T39" t="inlineStr"/>
-      <c r="U39" t="inlineStr"/>
-      <c r="V39" t="inlineStr"/>
-      <c r="W39" t="inlineStr"/>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>07/2010/TT-BKH · hiệu lực 2010-04-14 → nay · lúc thu thập: Còn hiệu lực
+Điều 9. Chế độ báo cáo và mẫu biểu báo cáo đối với Ban QLDA (quy định tại Điều 27 của Quy chế)
+2. Chế độ báo cáo
+Chế độ báo cáo do Cơ quan phê duyệt khoản viện trợ PCPNN quy định.</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 08/2018/TT-BKHĐT · hiệu lực 2019-02-11
+Điều 1. Sửa đổi, bổ sung Khoản 2 Điều 9 Thông tư số 07/2010/TT-BKH ngày 20 tháng 3 năm 2010 của Bộ Kế hoạch và Đầu tư hướng dẫn thi hành Nghị định số 93/2009/NĐ-CP ngày 22 tháng 10 năm 2009 của Chính phủ ban hành Quy chế quản lý và sử dụng viện trợ phi Chính phủ nước ngoài như sau:
+"2. Chế độ báo cáo
+Chế độ báo cáo do Cơ quan phê duyệt khoản viện trợ phi chính phủ nước ngoài (PCPNN) quy định.
+a) Báo cáo 6 tháng: Chậm nhất vào ngày 10 tháng 7, Ban Quản lý dự án phải gửi báo cáo về Cơ quan phê duyệt khoản viện trợ PCPNN.
+b) Báo cáo năm: Chậm nhất vào ngày 31 tháng 01 năm tiếp sau, Ban Quản lý dự án phải gửi báo cáo về Cơ quan phê duyệt khoản viện trợ PCPNN.
+c) Báo cáo kết thúc dự án: Chậm nhất 6 tháng kể từ ngày kết thúc thực hiện chương trình, dự án, Ban Quản lý dự án phải gửi báo cáo theo mẫu Báo cáo kết thúc chương trình, dự án viện trợ PCPNN bằng văn bản, fax và thư điện tử về Cơ quan phê duyệt khoản viện trợ PCPNN."
+[amend] 09/2019/TT-BKHĐT · hiệu lực 2019-09-16
+1. Sửa đổi, bổ sung Khoản 2 Điều 9 như sau:
+“2. Chế độ báo cáo
+Chế độ báo cáo do Cơ quan phê duyệt khoản viện trợ phi chính phủ nước ngoài (PCPNN) quy định.
+a) Báo cáo 6 tháng: Chậm nhất vào ngày 18 tháng 6, Ban Quản lý dự án phải gửi báo cáo về Cơ quan phê duyệt khoản viện trợ PCPNN. Thời gian chốt số liệu được tính từ ngày 15 tháng 12 năm trước kỳ báo cáo đến ngày 14 tháng 6 của năm báo cáo.
+b) Báo cáo năm: Chậm nhất vào ngày 18 tháng 12, Ban Quản lý dự án phải gửi báo cáo về Cơ quan phê duyệt khoản viện trợ PCPNN. Thời gian chốt số liệu được tính từ ngày 15 tháng 12 năm trước kỳ báo cáo đến ngày 14 tháng 12.
+c) Báo cáo kết thúc dự án: Chậm nhất 6 tháng kể từ ngày kết thúc thực hiện chương trình, dự án, Ban Quản lý dự án phải gửi báo cáo theo mẫu Báo cáo kết thúc chương trình, dự án viện trợ PCPNN bằng văn bản, fax và thư điện tử về Cơ quan phê duyệt khoản viện trợ PCPNN.”</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3827,8 +5047,6 @@
           <t>09/2020/TT-BGTVT; 32/2021/TT-BGTVT</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -3839,18 +5057,28 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr">
         <is>
           <t>id cũ vilextime:T3:provision:52a19514-eb7f-11f0-834c-df767891920b:2022-02-03 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S40" t="inlineStr"/>
-      <c r="T40" t="inlineStr"/>
-      <c r="U40" t="inlineStr"/>
-      <c r="V40" t="inlineStr"/>
-      <c r="W40" t="inlineStr"/>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>19/2017/TT-BGTVT · hiệu lực 2017-08-01 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 3. Quy ước viết tắt
+46. METAR (Aerodrome routine meteorological reports): Bản tin báo cáo thời tiết thường lệ tại sân bay dạng mã hóa.</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 09/2020/TT-BGTVT · hiệu lực 2020-06-15
+a) Sửa đổi, bổ sung khoản 46 Điều 3 như sau:
+“46. METAR (Routine aerodrome meteorological report): Bản tin báo cáo thời tiết thường lệ để phát ra ngoài sân bay.”.
+[amend] 32/2021/TT-BGTVT · hiệu lực 2022-02-02
+a) Sửa đổi, bổ sung khoản 46 Điều 3 như sau:
+"46. METAR (Aerodrome routine meteorological report in meteorological code): Bản tin báo cáo khí tượng thường lệ tại sân bay dạng mã hóa.";</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3908,8 +5136,6 @@
           <t>09/2020/TT-BGTVT; 32/2021/TT-BGTVT</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -3920,18 +5146,28 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr">
         <is>
           <t>id cũ vilextime:T3:provision:52a1bca6-eb7f-11f0-bacc-3745bc0439a2:2020-06-16 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S41" t="inlineStr"/>
-      <c r="T41" t="inlineStr"/>
-      <c r="U41" t="inlineStr"/>
-      <c r="V41" t="inlineStr"/>
-      <c r="W41" t="inlineStr"/>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>19/2017/TT-BGTVT · hiệu lực 2017-08-01 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 4. Giải thích từ ngữ
+52. Hoạt động bay tại sân bay là hoạt động bay trên khu vực di chuyển tại sân bay và trong vùng trời sân bay.</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 09/2020/TT-BGTVT · hiệu lực 2020-06-15
+d) Sửa đổi, bổ sung khoản 52 Điều 4 như sau:
+“52. Hoạt động tại sân bay là tất cả hoạt động trên khu vực di chuyển tại sân bay và tất cả hoạt động bay trong vùng trời sân bay.”.
+[amend] 32/2021/TT-BGTVT · hiệu lực 2022-02-02
+d) Sửa đổi, bổ sung khoản 52 Điều 4 như sau:
+"52. Hoạt động tại sân bay là tất cả hoạt động trên khu vực di chuyển tại sân bay và tất cả hoạt động bay trong khu vực lân cận sân bay.";</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3989,8 +5225,6 @@
           <t>30/2020/TT-BGTVT; 51/2018/TT-BGTVT</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -4001,18 +5235,28 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr">
         <is>
           <t>id cũ vilextime:T3:provision:53c9f49c-e17d-11f0-b95f-77080cf1bb2c#k5:2018-11-06 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S42" t="inlineStr"/>
-      <c r="T42" t="inlineStr"/>
-      <c r="U42" t="inlineStr"/>
-      <c r="V42" t="inlineStr"/>
-      <c r="W42" t="inlineStr"/>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>17/2016/TT-BGTVT · hiệu lực 2016-12-15 → 2022-01-15 · lúc thu thập: Hết hiệu lực toàn bộ
+Điều 20. Gia hạn cho thuê đất
+5. Trong thời hạn không quá 05 ngày làm việc, kể từ ngày nhận được thông báo đơn giá thuê đất của cơ quan thuế, Cảng vụ hàng không ban hành quyết định gia hạn cho thuê đất, ký hợp đồng thuê đất với tổ chức, cá nhân sử dụng đất.</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 51/2018/TT-BGTVT · hiệu lực 2018-11-05
+d) Sửa đổi, bổ sung khoản 5 Điều 20 như sau:
+“5. Sau thời hạn 03 ngày làm việc kể từ ngày nhận được đơn giá thuê đất, Cảng vụ hàng không ký hợp đồng thuê đất theo Mẫu số 05 quy định tại Phụ lục ban hành kèm theo Thông tư này.”
+[amend] 30/2020/TT-BGTVT · hiệu lực 2021-01-15
+d) Sửa đổi, bổ sung khoản 5 Điều 20 như sau:
+“5. Sau thời hạn 03 ngày kể từ ngày nhận được đơn giá thuê đất, Cảng vụ hàng không ký hợp đồng thuê đất theo Mẫu số 05 quy định tại Phụ lục ban hành kèm theo Thông tư này.”.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4070,8 +5314,6 @@
           <t>20/2024/NĐ-CP; 64/2022/NĐ-CP</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -4082,18 +5324,30 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr">
         <is>
           <t>lineage thay thế 29/09; câu hỏi và đáp án ngắn do cùng model viết</t>
         </is>
       </c>
-      <c r="S43" t="inlineStr"/>
-      <c r="T43" t="inlineStr"/>
-      <c r="U43" t="inlineStr"/>
-      <c r="V43" t="inlineStr"/>
-      <c r="W43" t="inlineStr"/>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>05/2021/NĐ-CP · hiệu lực 2021-03-10 → 2026-07-01 · lúc thu thập: Hết hiệu lực toàn bộ
+Điều 53. Sửa đổi nội dung giấy chứng nhận đăng ký cảng hàng không, sân bay
+3. Trong thời hạn 05 ngày làm việc, kể từ ngày nhận đủ hồ sơ theo quy định, Cục Hàng không Việt Nam thẩm định việc sửa đổi nội dung giấy chứng nhận đăng ký cảng hàng không, sân bay; cấp mới giấy chứng nhận đăng ký cảng hàng không, sân bay; thu hồi giấy chứng nhận đăng ký đã cấp hoặc thông báo bằng văn bản lý do từ chối sửa đổi.</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 64/2022/NĐ-CP · hiệu lực 2022-09-15
+b) Sửa đổi, bổ sung khoản 3 Điều 53 như sau:
+"3. Trong thời hạn 05 ngày làm việc, kể từ ngày nhận đủ hồ sơ theo quy định, Cục Hàng không Việt Nam thẩm định việc sửa đổi nội dung giấy chứng nhận đăng ký cảng hàng không, sân bay; cấp mới giấy chứng nhận đăng ký cảng hàng không, sân bay và gửi trực tiếp hoặc qua hệ thống bưu chính hoặc trên môi trường điện tử hoặc bằng các hình thức khác đến người đề nghị; thu hồi giấy chứng nhận đăng ký đã cấp. Trường hợp từ chối sửa đổi, Cục Hàng không Việt Nam phải thông báo bằng văn bản lý do từ chối."
+[amend] 20/2024/NĐ-CP · hiệu lực 2024-04-10
+9. Thay thế cụm từ "Cục Hàng không Việt Nam" thành "Cảng vụ hàng không" tại khoản 2, khoản 3 Điều 53.
+CHUYỂN TIẾP: 2. Điều khoản chuyển tiếp:
+a) Các Giấy chứng nhận đã được cơ quan có thẩm quyền cấp theo quy định của pháp luật trước thời điểm Nghị định này có hiệu lực thi hành thì tiếp tục có giá trị cho đến khi được cấp lại, sửa đổi, bổ sung hoặc bị thu hồi theo quy định của pháp luật.
+b) Đối với hồ sơ các thủ tục hành chính đã được cơ quan có thẩm quyền tiếp nhận hồ sơ trước ngày Nghị định này có hiệu lực thi hành thì cơ quan có thẩm quyền đã tiếp nhận hồ sơ tiếp tục thực hiện theo quy định của văn bản quy phạm pháp luật tại thời điểm tiếp nhận hồ sơ.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4151,8 +5405,6 @@
           <t>20/2024/NĐ-CP; 64/2022/NĐ-CP</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -4163,18 +5415,30 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr">
         <is>
           <t>lineage thay thế 29/09; câu hỏi và đáp án ngắn do cùng model viết</t>
         </is>
       </c>
-      <c r="S44" t="inlineStr"/>
-      <c r="T44" t="inlineStr"/>
-      <c r="U44" t="inlineStr"/>
-      <c r="V44" t="inlineStr"/>
-      <c r="W44" t="inlineStr"/>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>05/2021/NĐ-CP · hiệu lực 2021-03-10 → 2026-07-01 · lúc thu thập: Hết hiệu lực toàn bộ
+Điều 53. Sửa đổi nội dung giấy chứng nhận đăng ký cảng hàng không, sân bay
+3. Trong thời hạn 05 ngày làm việc, kể từ ngày nhận đủ hồ sơ theo quy định, Cục Hàng không Việt Nam thẩm định việc sửa đổi nội dung giấy chứng nhận đăng ký cảng hàng không, sân bay; cấp mới giấy chứng nhận đăng ký cảng hàng không, sân bay; thu hồi giấy chứng nhận đăng ký đã cấp hoặc thông báo bằng văn bản lý do từ chối sửa đổi.</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 64/2022/NĐ-CP · hiệu lực 2022-09-15
+b) Sửa đổi, bổ sung khoản 3 Điều 53 như sau:
+"3. Trong thời hạn 05 ngày làm việc, kể từ ngày nhận đủ hồ sơ theo quy định, Cục Hàng không Việt Nam thẩm định việc sửa đổi nội dung giấy chứng nhận đăng ký cảng hàng không, sân bay; cấp mới giấy chứng nhận đăng ký cảng hàng không, sân bay và gửi trực tiếp hoặc qua hệ thống bưu chính hoặc trên môi trường điện tử hoặc bằng các hình thức khác đến người đề nghị; thu hồi giấy chứng nhận đăng ký đã cấp. Trường hợp từ chối sửa đổi, Cục Hàng không Việt Nam phải thông báo bằng văn bản lý do từ chối."
+[amend] 20/2024/NĐ-CP · hiệu lực 2024-04-10
+9. Thay thế cụm từ "Cục Hàng không Việt Nam" thành "Cảng vụ hàng không" tại khoản 2, khoản 3 Điều 53.
+CHUYỂN TIẾP: 2. Điều khoản chuyển tiếp:
+a) Các Giấy chứng nhận đã được cơ quan có thẩm quyền cấp theo quy định của pháp luật trước thời điểm Nghị định này có hiệu lực thi hành thì tiếp tục có giá trị cho đến khi được cấp lại, sửa đổi, bổ sung hoặc bị thu hồi theo quy định của pháp luật.
+b) Đối với hồ sơ các thủ tục hành chính đã được cơ quan có thẩm quyền tiếp nhận hồ sơ trước ngày Nghị định này có hiệu lực thi hành thì cơ quan có thẩm quyền đã tiếp nhận hồ sơ tiếp tục thực hiện theo quy định của văn bản quy phạm pháp luật tại thời điểm tiếp nhận hồ sơ.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4232,8 +5496,6 @@
           <t>20/2024/NĐ-CP; 64/2022/NĐ-CP</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -4244,18 +5506,30 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr">
         <is>
           <t>lineage thay thế 29/09; câu hỏi và đáp án ngắn do cùng model viết</t>
         </is>
       </c>
-      <c r="S45" t="inlineStr"/>
-      <c r="T45" t="inlineStr"/>
-      <c r="U45" t="inlineStr"/>
-      <c r="V45" t="inlineStr"/>
-      <c r="W45" t="inlineStr"/>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>05/2021/NĐ-CP · hiệu lực 2021-03-10 → 2026-07-01 · lúc thu thập: Hết hiệu lực toàn bộ
+Điều 53. Sửa đổi nội dung giấy chứng nhận đăng ký cảng hàng không, sân bay
+3. Trong thời hạn 05 ngày làm việc, kể từ ngày nhận đủ hồ sơ theo quy định, Cục Hàng không Việt Nam thẩm định việc sửa đổi nội dung giấy chứng nhận đăng ký cảng hàng không, sân bay; cấp mới giấy chứng nhận đăng ký cảng hàng không, sân bay; thu hồi giấy chứng nhận đăng ký đã cấp hoặc thông báo bằng văn bản lý do từ chối sửa đổi.</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 64/2022/NĐ-CP · hiệu lực 2022-09-15
+b) Sửa đổi, bổ sung khoản 3 Điều 53 như sau:
+"3. Trong thời hạn 05 ngày làm việc, kể từ ngày nhận đủ hồ sơ theo quy định, Cục Hàng không Việt Nam thẩm định việc sửa đổi nội dung giấy chứng nhận đăng ký cảng hàng không, sân bay; cấp mới giấy chứng nhận đăng ký cảng hàng không, sân bay và gửi trực tiếp hoặc qua hệ thống bưu chính hoặc trên môi trường điện tử hoặc bằng các hình thức khác đến người đề nghị; thu hồi giấy chứng nhận đăng ký đã cấp. Trường hợp từ chối sửa đổi, Cục Hàng không Việt Nam phải thông báo bằng văn bản lý do từ chối."
+[amend] 20/2024/NĐ-CP · hiệu lực 2024-04-10
+9. Thay thế cụm từ "Cục Hàng không Việt Nam" thành "Cảng vụ hàng không" tại khoản 2, khoản 3 Điều 53.
+CHUYỂN TIẾP: 2. Điều khoản chuyển tiếp:
+a) Các Giấy chứng nhận đã được cơ quan có thẩm quyền cấp theo quy định của pháp luật trước thời điểm Nghị định này có hiệu lực thi hành thì tiếp tục có giá trị cho đến khi được cấp lại, sửa đổi, bổ sung hoặc bị thu hồi theo quy định của pháp luật.
+b) Đối với hồ sơ các thủ tục hành chính đã được cơ quan có thẩm quyền tiếp nhận hồ sơ trước ngày Nghị định này có hiệu lực thi hành thì cơ quan có thẩm quyền đã tiếp nhận hồ sơ tiếp tục thực hiện theo quy định của văn bản quy phạm pháp luật tại thời điểm tiếp nhận hồ sơ.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4333,18 +5607,44 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr">
         <is>
           <t>id cũ vilextime:T3:provision:59915bf0-2d53-11f1-bf60-a9df1703fcab:2015-04-07 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S46" t="inlineStr"/>
-      <c r="T46" t="inlineStr"/>
-      <c r="U46" t="inlineStr"/>
-      <c r="V46" t="inlineStr"/>
-      <c r="W46" t="inlineStr"/>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>22/2015/NĐ-CP · hiệu lực 2015-04-06 → 2026-03-01 · lúc thu thập: Hết hiệu lực toàn bộ
+Điều 15. Thay đổi thông tin đăng ký hành nghề của Quản tài viên, doanh nghiệp hành nghề quản lý, thanh lý tài sản
+1. Khi có thay đổi về địa chỉ giao dịch trong hồ sơ đăng ký hành nghề quản lý, thanh lý tài sản thì trong thời hạn 07 ngày, kể từ ngày thay đổi, Quản tài viên hành nghề với tư cách cá nhân gửi văn bản đề nghị điều chỉnh thông tin đăng ký hành nghề quản lý, thanh lý tài sản qua đường bưu điện hoặc trực tiếp đến Sở Tư pháp tỉnh, thành phố trực thuộc Trung ương nơi Quản tài viên đăng ký hành nghề.
+Trong thời hạn 03 ngày làm việc, kể từ ngày nhận được văn bản đề nghị của Quản tài viên, Sở Tư pháp thay đổi thông tin về địa chỉ giao dịch của Quản tài viên trong danh sách Quản tài viên, doanh nghiệp hành nghề quản lý, thanh lý tài sản.</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 112/2025/NĐ-CP · hiệu lực 2025-05-29
+7. Sửa đổi, bổ sung khoản 1 và khoản 2 Điều 15 như sau:
+“1. Khi có thay đổi về địa chỉ giao dịch trong hồ sơ đăng ký hành nghề quản lý, thanh lý tài sản thì trong thời hạn 07 ngày kể từ ngày thay đổi, Quản tài viên hành nghề với tư cách cá nhân gửi văn bản đề nghị điều chỉnh thông tin đăng ký hành nghề quản lý, thanh lý tài sản qua dịch vụ bưu chính hoặc trực tiếp đến Sở Tư pháp nơi Quản tài viên đăng ký hành nghề hoặc trực tuyến trên Cổng Dịch vụ công quốc gia.
+Trong thời hạn 03 ngày làm việc kể từ ngày nhận được văn bản đề nghị của Quản tài viên, Sở Tư pháp thay đổi thông tin về địa chỉ giao dịch của Quản tài viên trong danh sách Quản tài viên, doanh nghiệp hành nghề quản lý, thanh lý tài sản.
+2. Khi có thay đổi tên, địa chỉ trụ sở, văn phòng đại diện, chi nhánh, người đại diện theo pháp luật, danh sách Quản tài viên hành nghề trong doanh nghiệp quản lý, thanh lý tài sản thì trong thời hạn 07 ngày kể từ ngày được bổ sung vào hồ sơ đăng ký doanh nghiệp theo quy định của pháp luật về doanh nghiệp, doanh nghiệp quản lý, thanh lý tài sản gửi văn bản đề nghị điều chỉnh thông tin đăng ký hành nghề quản lý, thanh lý tài sản qua dịch vụ bưu chính hoặc trực tiếp đến Sở Tư pháp nơi doanh nghiệp đăng ký hành nghề hoặc trực tuyến trên Cổng Dịch vụ công quốc gia.
+Trong thời hạn 03 ngày làm việc kể từ ngày nhận được văn bản của doanh nghiệp, Sở Tư pháp thay đổi thông tin về tên, địa chỉ trụ sở, văn phòng đại diện, chi nhánh, người đại diện theo pháp luật, danh sách Quản tài viên hành nghề trong doanh nghiệp trong danh sách Quản tài viên, doanh nghiệp hành nghề quản lý, thanh lý tài sản.
+Trong trường hợp doanh nghiệp quản lý, thanh lý tài sản bổ sung Quản tài viên hành nghề trong doanh nghiệp thì doanh nghiệp phải đăng ký hành nghề cho người được bổ sung. Trình tự, thủ tục đăng ký cho những người được bổ sung vào danh sách Quản tài viên hành nghề trong doanh nghiệp được thực hiện theo quy định tại khoản 2, khoản 3 Điều 12 của Nghị định này.”.
+CHUYỂN TIẾP: Điều 5. Quy định chuyển tiếp
+1. Trường hợp trước ngày Nghị định này có hiệu lực thi hành, cơ quan có thẩm quyền đã tiếp nhận hồ sơ quy định tại khoản này thì tiếp tục thực hiện theo quy định của văn bản quy phạm pháp luật tại thời điểm tiếp nhận hồ sơ, bao gồm các hồ sơ sau đây:
+a) Cấp, cấp lại, thay đổi nội dung, thu hồi Giấy phép thành lập, Giấy đăng ký hoạt động của Trung tâm trọng tài, Chi nhánh, Văn phòng đại diện của tổ chức trọng tài nước ngoài tại Việt Nam; đăng ký hoạt động, chấm dứt hoạt động của Trung tâm trọng tài, Chi nhánh, Văn phòng đại diện của tổ chức trọng tài nước ngoài tại Việt Nam;
+b) Cấp, cấp lại, thay đổi nội dung, thu hồi Giấy phép thành lập, Giấy đăng ký hoạt động của Trung tâm hoà giải thương mại, Giấy phép thành lập Chi nhánh, Văn phòng đại diện của tổ chức hoà giải thương mại nước ngoài tại Việt Nam; đăng ký hoạt động, chấm dứt hoạt động của Trung tâm hoà giải thương mại, Chi nhánh, Văn phòng đại diện của tổ chức hoà giải thương mại nước ngoài tại Việt Nam;
+c) Cấp, cấp lại, thu hồi Chứng chỉ hành nghề Quản tài viên; đăng ký hành nghề quản lý, thanh lý tài sản với tư cách cá nhân, đối với doanh nghiệp quản lý, thanh lý tài sản;
+d) Thay đổi người đại diện theo pháp luật của văn phòng luật sư, công ty luật trách nhiệm hữu hạn một thành viên, công ty luật trách nhiệm hữu hạn hai thành viên trở lên, công ty luật hợp danh; nội dung Giấy phép thành lập chi nhánh, công ty luật nước ngoài;
+đ) Hợp nhất, sáp nhập, chuyển đổi công ty luật; chuyển đổi văn phòng luật sư; chuyển đổi chi nhánh của tổ chức hành nghề luật sư nước ngoài tại Việt Nam, công ty luật nước ngoài.
+2. Trường hợp cấp lại, thay đổi, thu hồi Giấy phép thành lập Trung tâm hoà giải thương mại, Giấy phép thành lập Chi nhánh, Văn phòng đại diện của tổ chức hoà giải thương mại nước ngoài tại Việt Nam do Bộ Tư pháp cấp trước ngày Nghị định này có hiệu lực thi hành thì Chủ tịch Ủy ban nhân dân tỉnh, thành phố trực thuộc trung ương nơi Trung tâm hoà giải thương mại, Chi nhánh, Văn phòng đại diện của tổ chức hoà giải thương mại nước ngoài tại Việt Nam đặt trụ sở có thẩm quyền cấp lại, thay đổi, thu hồi Giấy phép thành lập trung tâm hoà giải thương mại, Giấy phép thành lập Chi nhánh, Văn phòng đại diện của tổ chức hoà giải thương mại nước ngoài tại Việt Nam đó theo quy định của Nghị định này.
+3. Trường hợp cấp lại, thu hồi chứng chỉ hành nghề Quản tài viên do Bộ Tư pháp cấp trước ngày Nghị định này có hiệu lực thi hành thì Chủ tịch Ủy ban nhân dân tỉnh, thành phố trực thuộc trung ương nơi người được cấp chứng chỉ hành nghề quản tài viên thường trú có thẩm quyền cấp lại, thu hồi chứng chỉ hành nghề Quản tài viên đó theo quy định của Nghị định này.
+4. Trường hợp hồ sơ thay đổi người đại diện theo pháp luật của tổ chức hành nghề luật sư, hợp nhất, sáp nhập công ty luật, chuyển đổi công ty luật, chuyển đổi văn phòng luật sư thành công ty luật, hợp nhất, sáp nhập công ty luật nước ngoài, chuyển đổi chi nhánh của tổ chức hành nghề luật sư nước ngoài thành công ty luật trách nhiệm hữu hạn 100% vốn nước ngoài tại Việt Nam, chuyển đổi công ty luật nước ngoài thành công ty luật Việt Nam, đăng ký thay đổi nội dung Giấy phép thành lập chi nhánh, công ty luật nước ngoài đã được cơ quan có thẩm quyền tiếp nhận trước ngày Nghị định này có hiệu lực thi hành thì cơ quan có thẩm quyền đã tiếp nhận hồ sơ tiếp tục thực hiện theo quy định của văn bản quy phạm pháp luật tại thời điểm tiếp nhận hồ sơ.
+[amend] 18/2026/NĐ-CP · hiệu lực 2026-01-15
+a) Thay thế cụm từ “trong thời hạn 07 ngày” thành “trong thời hạn 05 ngày làm việc” tại khoản 3 Điều 4, khoản 1 Điều 15, khoản 2 Điều 15;
+CHUYỂN TIẾP: Điều 16. Điều khoản chuyển tiếp
+1. Đối với hồ sơ đề nghị giải quyết thủ tục hành chính được quy định tại các Điều 1, 2, 3, 4, 5, 6, 7, 8, 9, 10 và 12 Nghị định này đã được cơ quan có thẩm quyền tiếp nhận hoặc đã được đóng dấu bưu chính trước ngày Nghị định này có hiệu lực thì thực hiện theo quy định của pháp luật đang có hiệu lực điều chỉnh trong lĩnh vực đó tại thờ</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4422,18 +5722,44 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr">
         <is>
           <t>id cũ vilextime:T3:provision:59915bf0-2d53-11f1-bf60-a9df1703fcab:2025-05-30 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S47" t="inlineStr"/>
-      <c r="T47" t="inlineStr"/>
-      <c r="U47" t="inlineStr"/>
-      <c r="V47" t="inlineStr"/>
-      <c r="W47" t="inlineStr"/>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>22/2015/NĐ-CP · hiệu lực 2015-04-06 → 2026-03-01 · lúc thu thập: Hết hiệu lực toàn bộ
+Điều 15. Thay đổi thông tin đăng ký hành nghề của Quản tài viên, doanh nghiệp hành nghề quản lý, thanh lý tài sản
+1. Khi có thay đổi về địa chỉ giao dịch trong hồ sơ đăng ký hành nghề quản lý, thanh lý tài sản thì trong thời hạn 07 ngày, kể từ ngày thay đổi, Quản tài viên hành nghề với tư cách cá nhân gửi văn bản đề nghị điều chỉnh thông tin đăng ký hành nghề quản lý, thanh lý tài sản qua đường bưu điện hoặc trực tiếp đến Sở Tư pháp tỉnh, thành phố trực thuộc Trung ương nơi Quản tài viên đăng ký hành nghề.
+Trong thời hạn 03 ngày làm việc, kể từ ngày nhận được văn bản đề nghị của Quản tài viên, Sở Tư pháp thay đổi thông tin về địa chỉ giao dịch của Quản tài viên trong danh sách Quản tài viên, doanh nghiệp hành nghề quản lý, thanh lý tài sản.</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 112/2025/NĐ-CP · hiệu lực 2025-05-29
+7. Sửa đổi, bổ sung khoản 1 và khoản 2 Điều 15 như sau:
+“1. Khi có thay đổi về địa chỉ giao dịch trong hồ sơ đăng ký hành nghề quản lý, thanh lý tài sản thì trong thời hạn 07 ngày kể từ ngày thay đổi, Quản tài viên hành nghề với tư cách cá nhân gửi văn bản đề nghị điều chỉnh thông tin đăng ký hành nghề quản lý, thanh lý tài sản qua dịch vụ bưu chính hoặc trực tiếp đến Sở Tư pháp nơi Quản tài viên đăng ký hành nghề hoặc trực tuyến trên Cổng Dịch vụ công quốc gia.
+Trong thời hạn 03 ngày làm việc kể từ ngày nhận được văn bản đề nghị của Quản tài viên, Sở Tư pháp thay đổi thông tin về địa chỉ giao dịch của Quản tài viên trong danh sách Quản tài viên, doanh nghiệp hành nghề quản lý, thanh lý tài sản.
+2. Khi có thay đổi tên, địa chỉ trụ sở, văn phòng đại diện, chi nhánh, người đại diện theo pháp luật, danh sách Quản tài viên hành nghề trong doanh nghiệp quản lý, thanh lý tài sản thì trong thời hạn 07 ngày kể từ ngày được bổ sung vào hồ sơ đăng ký doanh nghiệp theo quy định của pháp luật về doanh nghiệp, doanh nghiệp quản lý, thanh lý tài sản gửi văn bản đề nghị điều chỉnh thông tin đăng ký hành nghề quản lý, thanh lý tài sản qua dịch vụ bưu chính hoặc trực tiếp đến Sở Tư pháp nơi doanh nghiệp đăng ký hành nghề hoặc trực tuyến trên Cổng Dịch vụ công quốc gia.
+Trong thời hạn 03 ngày làm việc kể từ ngày nhận được văn bản của doanh nghiệp, Sở Tư pháp thay đổi thông tin về tên, địa chỉ trụ sở, văn phòng đại diện, chi nhánh, người đại diện theo pháp luật, danh sách Quản tài viên hành nghề trong doanh nghiệp trong danh sách Quản tài viên, doanh nghiệp hành nghề quản lý, thanh lý tài sản.
+Trong trường hợp doanh nghiệp quản lý, thanh lý tài sản bổ sung Quản tài viên hành nghề trong doanh nghiệp thì doanh nghiệp phải đăng ký hành nghề cho người được bổ sung. Trình tự, thủ tục đăng ký cho những người được bổ sung vào danh sách Quản tài viên hành nghề trong doanh nghiệp được thực hiện theo quy định tại khoản 2, khoản 3 Điều 12 của Nghị định này.”.
+CHUYỂN TIẾP: Điều 5. Quy định chuyển tiếp
+1. Trường hợp trước ngày Nghị định này có hiệu lực thi hành, cơ quan có thẩm quyền đã tiếp nhận hồ sơ quy định tại khoản này thì tiếp tục thực hiện theo quy định của văn bản quy phạm pháp luật tại thời điểm tiếp nhận hồ sơ, bao gồm các hồ sơ sau đây:
+a) Cấp, cấp lại, thay đổi nội dung, thu hồi Giấy phép thành lập, Giấy đăng ký hoạt động của Trung tâm trọng tài, Chi nhánh, Văn phòng đại diện của tổ chức trọng tài nước ngoài tại Việt Nam; đăng ký hoạt động, chấm dứt hoạt động của Trung tâm trọng tài, Chi nhánh, Văn phòng đại diện của tổ chức trọng tài nước ngoài tại Việt Nam;
+b) Cấp, cấp lại, thay đổi nội dung, thu hồi Giấy phép thành lập, Giấy đăng ký hoạt động của Trung tâm hoà giải thương mại, Giấy phép thành lập Chi nhánh, Văn phòng đại diện của tổ chức hoà giải thương mại nước ngoài tại Việt Nam; đăng ký hoạt động, chấm dứt hoạt động của Trung tâm hoà giải thương mại, Chi nhánh, Văn phòng đại diện của tổ chức hoà giải thương mại nước ngoài tại Việt Nam;
+c) Cấp, cấp lại, thu hồi Chứng chỉ hành nghề Quản tài viên; đăng ký hành nghề quản lý, thanh lý tài sản với tư cách cá nhân, đối với doanh nghiệp quản lý, thanh lý tài sản;
+d) Thay đổi người đại diện theo pháp luật của văn phòng luật sư, công ty luật trách nhiệm hữu hạn một thành viên, công ty luật trách nhiệm hữu hạn hai thành viên trở lên, công ty luật hợp danh; nội dung Giấy phép thành lập chi nhánh, công ty luật nước ngoài;
+đ) Hợp nhất, sáp nhập, chuyển đổi công ty luật; chuyển đổi văn phòng luật sư; chuyển đổi chi nhánh của tổ chức hành nghề luật sư nước ngoài tại Việt Nam, công ty luật nước ngoài.
+2. Trường hợp cấp lại, thay đổi, thu hồi Giấy phép thành lập Trung tâm hoà giải thương mại, Giấy phép thành lập Chi nhánh, Văn phòng đại diện của tổ chức hoà giải thương mại nước ngoài tại Việt Nam do Bộ Tư pháp cấp trước ngày Nghị định này có hiệu lực thi hành thì Chủ tịch Ủy ban nhân dân tỉnh, thành phố trực thuộc trung ương nơi Trung tâm hoà giải thương mại, Chi nhánh, Văn phòng đại diện của tổ chức hoà giải thương mại nước ngoài tại Việt Nam đặt trụ sở có thẩm quyền cấp lại, thay đổi, thu hồi Giấy phép thành lập trung tâm hoà giải thương mại, Giấy phép thành lập Chi nhánh, Văn phòng đại diện của tổ chức hoà giải thương mại nước ngoài tại Việt Nam đó theo quy định của Nghị định này.
+3. Trường hợp cấp lại, thu hồi chứng chỉ hành nghề Quản tài viên do Bộ Tư pháp cấp trước ngày Nghị định này có hiệu lực thi hành thì Chủ tịch Ủy ban nhân dân tỉnh, thành phố trực thuộc trung ương nơi người được cấp chứng chỉ hành nghề quản tài viên thường trú có thẩm quyền cấp lại, thu hồi chứng chỉ hành nghề Quản tài viên đó theo quy định của Nghị định này.
+4. Trường hợp hồ sơ thay đổi người đại diện theo pháp luật của tổ chức hành nghề luật sư, hợp nhất, sáp nhập công ty luật, chuyển đổi công ty luật, chuyển đổi văn phòng luật sư thành công ty luật, hợp nhất, sáp nhập công ty luật nước ngoài, chuyển đổi chi nhánh của tổ chức hành nghề luật sư nước ngoài thành công ty luật trách nhiệm hữu hạn 100% vốn nước ngoài tại Việt Nam, chuyển đổi công ty luật nước ngoài thành công ty luật Việt Nam, đăng ký thay đổi nội dung Giấy phép thành lập chi nhánh, công ty luật nước ngoài đã được cơ quan có thẩm quyền tiếp nhận trước ngày Nghị định này có hiệu lực thi hành thì cơ quan có thẩm quyền đã tiếp nhận hồ sơ tiếp tục thực hiện theo quy định của văn bản quy phạm pháp luật tại thời điểm tiếp nhận hồ sơ.
+[amend] 18/2026/NĐ-CP · hiệu lực 2026-01-15
+a) Thay thế cụm từ “trong thời hạn 07 ngày” thành “trong thời hạn 05 ngày làm việc” tại khoản 3 Điều 4, khoản 1 Điều 15, khoản 2 Điều 15;
+CHUYỂN TIẾP: Điều 16. Điều khoản chuyển tiếp
+1. Đối với hồ sơ đề nghị giải quyết thủ tục hành chính được quy định tại các Điều 1, 2, 3, 4, 5, 6, 7, 8, 9, 10 và 12 Nghị định này đã được cơ quan có thẩm quyền tiếp nhận hoặc đã được đóng dấu bưu chính trước ngày Nghị định này có hiệu lực thì thực hiện theo quy định của pháp luật đang có hiệu lực điều chỉnh trong lĩnh vực đó tại thờ</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4511,18 +5837,44 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr">
         <is>
           <t>id cũ vilextime:T3:provision:59915bf0-2d53-11f1-bf60-a9df1703fcab:2026-01-16 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S48" t="inlineStr"/>
-      <c r="T48" t="inlineStr"/>
-      <c r="U48" t="inlineStr"/>
-      <c r="V48" t="inlineStr"/>
-      <c r="W48" t="inlineStr"/>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>22/2015/NĐ-CP · hiệu lực 2015-04-06 → 2026-03-01 · lúc thu thập: Hết hiệu lực toàn bộ
+Điều 15. Thay đổi thông tin đăng ký hành nghề của Quản tài viên, doanh nghiệp hành nghề quản lý, thanh lý tài sản
+1. Khi có thay đổi về địa chỉ giao dịch trong hồ sơ đăng ký hành nghề quản lý, thanh lý tài sản thì trong thời hạn 07 ngày, kể từ ngày thay đổi, Quản tài viên hành nghề với tư cách cá nhân gửi văn bản đề nghị điều chỉnh thông tin đăng ký hành nghề quản lý, thanh lý tài sản qua đường bưu điện hoặc trực tiếp đến Sở Tư pháp tỉnh, thành phố trực thuộc Trung ương nơi Quản tài viên đăng ký hành nghề.
+Trong thời hạn 03 ngày làm việc, kể từ ngày nhận được văn bản đề nghị của Quản tài viên, Sở Tư pháp thay đổi thông tin về địa chỉ giao dịch của Quản tài viên trong danh sách Quản tài viên, doanh nghiệp hành nghề quản lý, thanh lý tài sản.</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 112/2025/NĐ-CP · hiệu lực 2025-05-29
+7. Sửa đổi, bổ sung khoản 1 và khoản 2 Điều 15 như sau:
+“1. Khi có thay đổi về địa chỉ giao dịch trong hồ sơ đăng ký hành nghề quản lý, thanh lý tài sản thì trong thời hạn 07 ngày kể từ ngày thay đổi, Quản tài viên hành nghề với tư cách cá nhân gửi văn bản đề nghị điều chỉnh thông tin đăng ký hành nghề quản lý, thanh lý tài sản qua dịch vụ bưu chính hoặc trực tiếp đến Sở Tư pháp nơi Quản tài viên đăng ký hành nghề hoặc trực tuyến trên Cổng Dịch vụ công quốc gia.
+Trong thời hạn 03 ngày làm việc kể từ ngày nhận được văn bản đề nghị của Quản tài viên, Sở Tư pháp thay đổi thông tin về địa chỉ giao dịch của Quản tài viên trong danh sách Quản tài viên, doanh nghiệp hành nghề quản lý, thanh lý tài sản.
+2. Khi có thay đổi tên, địa chỉ trụ sở, văn phòng đại diện, chi nhánh, người đại diện theo pháp luật, danh sách Quản tài viên hành nghề trong doanh nghiệp quản lý, thanh lý tài sản thì trong thời hạn 07 ngày kể từ ngày được bổ sung vào hồ sơ đăng ký doanh nghiệp theo quy định của pháp luật về doanh nghiệp, doanh nghiệp quản lý, thanh lý tài sản gửi văn bản đề nghị điều chỉnh thông tin đăng ký hành nghề quản lý, thanh lý tài sản qua dịch vụ bưu chính hoặc trực tiếp đến Sở Tư pháp nơi doanh nghiệp đăng ký hành nghề hoặc trực tuyến trên Cổng Dịch vụ công quốc gia.
+Trong thời hạn 03 ngày làm việc kể từ ngày nhận được văn bản của doanh nghiệp, Sở Tư pháp thay đổi thông tin về tên, địa chỉ trụ sở, văn phòng đại diện, chi nhánh, người đại diện theo pháp luật, danh sách Quản tài viên hành nghề trong doanh nghiệp trong danh sách Quản tài viên, doanh nghiệp hành nghề quản lý, thanh lý tài sản.
+Trong trường hợp doanh nghiệp quản lý, thanh lý tài sản bổ sung Quản tài viên hành nghề trong doanh nghiệp thì doanh nghiệp phải đăng ký hành nghề cho người được bổ sung. Trình tự, thủ tục đăng ký cho những người được bổ sung vào danh sách Quản tài viên hành nghề trong doanh nghiệp được thực hiện theo quy định tại khoản 2, khoản 3 Điều 12 của Nghị định này.”.
+CHUYỂN TIẾP: Điều 5. Quy định chuyển tiếp
+1. Trường hợp trước ngày Nghị định này có hiệu lực thi hành, cơ quan có thẩm quyền đã tiếp nhận hồ sơ quy định tại khoản này thì tiếp tục thực hiện theo quy định của văn bản quy phạm pháp luật tại thời điểm tiếp nhận hồ sơ, bao gồm các hồ sơ sau đây:
+a) Cấp, cấp lại, thay đổi nội dung, thu hồi Giấy phép thành lập, Giấy đăng ký hoạt động của Trung tâm trọng tài, Chi nhánh, Văn phòng đại diện của tổ chức trọng tài nước ngoài tại Việt Nam; đăng ký hoạt động, chấm dứt hoạt động của Trung tâm trọng tài, Chi nhánh, Văn phòng đại diện của tổ chức trọng tài nước ngoài tại Việt Nam;
+b) Cấp, cấp lại, thay đổi nội dung, thu hồi Giấy phép thành lập, Giấy đăng ký hoạt động của Trung tâm hoà giải thương mại, Giấy phép thành lập Chi nhánh, Văn phòng đại diện của tổ chức hoà giải thương mại nước ngoài tại Việt Nam; đăng ký hoạt động, chấm dứt hoạt động của Trung tâm hoà giải thương mại, Chi nhánh, Văn phòng đại diện của tổ chức hoà giải thương mại nước ngoài tại Việt Nam;
+c) Cấp, cấp lại, thu hồi Chứng chỉ hành nghề Quản tài viên; đăng ký hành nghề quản lý, thanh lý tài sản với tư cách cá nhân, đối với doanh nghiệp quản lý, thanh lý tài sản;
+d) Thay đổi người đại diện theo pháp luật của văn phòng luật sư, công ty luật trách nhiệm hữu hạn một thành viên, công ty luật trách nhiệm hữu hạn hai thành viên trở lên, công ty luật hợp danh; nội dung Giấy phép thành lập chi nhánh, công ty luật nước ngoài;
+đ) Hợp nhất, sáp nhập, chuyển đổi công ty luật; chuyển đổi văn phòng luật sư; chuyển đổi chi nhánh của tổ chức hành nghề luật sư nước ngoài tại Việt Nam, công ty luật nước ngoài.
+2. Trường hợp cấp lại, thay đổi, thu hồi Giấy phép thành lập Trung tâm hoà giải thương mại, Giấy phép thành lập Chi nhánh, Văn phòng đại diện của tổ chức hoà giải thương mại nước ngoài tại Việt Nam do Bộ Tư pháp cấp trước ngày Nghị định này có hiệu lực thi hành thì Chủ tịch Ủy ban nhân dân tỉnh, thành phố trực thuộc trung ương nơi Trung tâm hoà giải thương mại, Chi nhánh, Văn phòng đại diện của tổ chức hoà giải thương mại nước ngoài tại Việt Nam đặt trụ sở có thẩm quyền cấp lại, thay đổi, thu hồi Giấy phép thành lập trung tâm hoà giải thương mại, Giấy phép thành lập Chi nhánh, Văn phòng đại diện của tổ chức hoà giải thương mại nước ngoài tại Việt Nam đó theo quy định của Nghị định này.
+3. Trường hợp cấp lại, thu hồi chứng chỉ hành nghề Quản tài viên do Bộ Tư pháp cấp trước ngày Nghị định này có hiệu lực thi hành thì Chủ tịch Ủy ban nhân dân tỉnh, thành phố trực thuộc trung ương nơi người được cấp chứng chỉ hành nghề quản tài viên thường trú có thẩm quyền cấp lại, thu hồi chứng chỉ hành nghề Quản tài viên đó theo quy định của Nghị định này.
+4. Trường hợp hồ sơ thay đổi người đại diện theo pháp luật của tổ chức hành nghề luật sư, hợp nhất, sáp nhập công ty luật, chuyển đổi công ty luật, chuyển đổi văn phòng luật sư thành công ty luật, hợp nhất, sáp nhập công ty luật nước ngoài, chuyển đổi chi nhánh của tổ chức hành nghề luật sư nước ngoài thành công ty luật trách nhiệm hữu hạn 100% vốn nước ngoài tại Việt Nam, chuyển đổi công ty luật nước ngoài thành công ty luật Việt Nam, đăng ký thay đổi nội dung Giấy phép thành lập chi nhánh, công ty luật nước ngoài đã được cơ quan có thẩm quyền tiếp nhận trước ngày Nghị định này có hiệu lực thi hành thì cơ quan có thẩm quyền đã tiếp nhận hồ sơ tiếp tục thực hiện theo quy định của văn bản quy phạm pháp luật tại thời điểm tiếp nhận hồ sơ.
+[amend] 18/2026/NĐ-CP · hiệu lực 2026-01-15
+a) Thay thế cụm từ “trong thời hạn 07 ngày” thành “trong thời hạn 05 ngày làm việc” tại khoản 3 Điều 4, khoản 1 Điều 15, khoản 2 Điều 15;
+CHUYỂN TIẾP: Điều 16. Điều khoản chuyển tiếp
+1. Đối với hồ sơ đề nghị giải quyết thủ tục hành chính được quy định tại các Điều 1, 2, 3, 4, 5, 6, 7, 8, 9, 10 và 12 Nghị định này đã được cơ quan có thẩm quyền tiếp nhận hoặc đã được đóng dấu bưu chính trước ngày Nghị định này có hiệu lực thì thực hiện theo quy định của pháp luật đang có hiệu lực điều chỉnh trong lĩnh vực đó tại thờ</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -4585,7 +5937,6 @@
           <t>actor_has_transitional</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -4596,18 +5947,55 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr">
         <is>
           <t>id cũ vilextime:T3:provision:5d48bef2-df54-11f0-abca-45ca78a631ce:2015-07-21 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S49" t="inlineStr"/>
-      <c r="T49" t="inlineStr"/>
-      <c r="U49" t="inlineStr"/>
-      <c r="V49" t="inlineStr"/>
-      <c r="W49" t="inlineStr"/>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>11/2015/TT-BCT · hiệu lực 2015-07-20 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 18. Tổ chức thực hiện
+1. Phòng Quản lý Xuất nhập khẩu khu vực thành phố Hồ Chí Minh, Phòng Quản lý Xuất nhập khẩu khu vực Đà Nẵng, Phòng Quản lý Xuất nhập khẩu khu vực Hà Nội (Cục Xuất nhập khẩu - Bộ Công Thương) thực hiện việc cấp giấy phép quá cảnh hàng hóa quy định tại Khoản 1 Điều 6 Thông tư này.</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 38/2025/TT-BCT · hiệu lực 2025-07-01
+3. Sửa đổi, bổ sung khoản 1 Điều 18 như sau:
+“1. Cục Xuất nhập khẩu - Bộ Công Thương thực hiện việc cấp giấy phép quá cảnh hàng hóa quy định tại Khoản 1 Điều 6 Thông tư này.”
+CHUYỂN TIẾP: 3. Quy định chuyển tiếp
+Các Giấy phép, Giấy Chứng nhận, Chứng chỉ, văn bản phê duyệt, văn bản chấp thuận đối với các thủ tục hành chính trong các lĩnh vực đã được cơ quan quản lý nhà nước cấp, phê duyệt, chấp thuận trước ngày 01 tháng 7 năm 2025 tiếp tục có hiệu lực đến hết thời hạn tại Giấy phép, Giấy Chứng nhận, Chứng chỉ, văn bản phê duyệt, văn bản chấp thuận theo quy định.
+[amend] 26/2026/TT-BCT · hiệu lực 2026-05-29
+4. Sửa đổi, bổ sung Điều 18 như sau:
+“ Điều 18. Tổ chức thực hiện
+1. Ủy ban nhân dân cấp tỉnh tổ chức thực hiện việc cấp các giấy phép theo quy định tại khoản 1 Điều 5, Điều 13 và Điều 14 Thông tư này.
+2. Cục Xuất nhập khẩu tiếp nhận, thẩm định hồ sơ cấp giấy phép theo quy định tại khoản 2 Điều 5, Điều 13, Điều 14 và Điều 15 Thông tư này và trình Lãnh đạo Bộ Công Thương xem xét, quyết định”.
+CHUYỂN TIẾP: Điều 28. Điều khoản chuyển tiếp
+1. Đối với hồ sơ đề nghị giải quyết thủ tục hành chính thuộc các lĩnh vực được quy định tại Thông tư này đã được cơ quan có thẩm quyền tiếp nhận hoặc đã được đóng dấu bưu chính trước ngày Thông tư này có hiệu lực thì thực hiện theo quy định của pháp luật đang có hiệu lực điều chỉnh trong lĩnh vực đó tại thời điểm hồ sơ được tiếp nhận.
+2. Văn bản, giấy tờ đã được cơ quan, chức danh có thẩm quyền ban hành, cấp trước ngày Thông tư này có hiệu lực thi hành mà chưa hết hiệu lực hoặc chưa hết thời hạn sử dụng thì tiếp tục được áp dụng, sử dụng theo quy định của pháp luật cho đến khi hết thời hạn hoặc được sửa đổi, bổ sung, điều chỉnh, gia hạn, cấp lại, thay thế, bãi bỏ, hủy bỏ, thu hồi bởi cơ quan, chức danh tiếp nhận chức năng, nhiệm vụ, quyền hạn hoặc cơ quan, người có thẩm quyền./.
+Nơi nhận:
+- Văn phòng Tổng bí thư;
+- Văn phòng Chủ tịch nước;
+- Văn phòng Quốc hội;
+- Thủ tướng và các Phó Thủ tướng Chính phủ;
+- Các Bộ, cơ quan ngang Bộ, cơ quan thuộc CP;
+- Viện KSNDTC; Tòa án NDTC;
+- Kiểm toán Nhà nước;
+- Các Lãnh đạo Bộ; đơn vị thuộc Bộ;
+- UBND, HĐND các tỉnh, thành phố trực thuộc TW;
+- Các Sở Công Thương;
+- Cục Kiểm tra văn bản và Quản lý xử lý vi phạm hành chính, Bộ Tư pháp;
+- Cục Kiểm soát thủ tục hành chính, Bộ Tư pháp;
+- Website Chính phủ; Website Bộ Công Thương;
+- Công báo;
+- Lưu: VT, VPB (10).
+KT. BỘ TRƯỞNG
+THỨ TRƯỞNG
+(Đã ký)
+Phan Thị Thắng</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -4670,7 +6058,6 @@
           <t>actor_has_transitional</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -4681,18 +6068,55 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr">
         <is>
           <t>id cũ vilextime:T3:provision:5d48bef2-df54-11f0-abca-45ca78a631ce:2025-07-02 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S50" t="inlineStr"/>
-      <c r="T50" t="inlineStr"/>
-      <c r="U50" t="inlineStr"/>
-      <c r="V50" t="inlineStr"/>
-      <c r="W50" t="inlineStr"/>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>11/2015/TT-BCT · hiệu lực 2015-07-20 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 18. Tổ chức thực hiện
+1. Phòng Quản lý Xuất nhập khẩu khu vực thành phố Hồ Chí Minh, Phòng Quản lý Xuất nhập khẩu khu vực Đà Nẵng, Phòng Quản lý Xuất nhập khẩu khu vực Hà Nội (Cục Xuất nhập khẩu - Bộ Công Thương) thực hiện việc cấp giấy phép quá cảnh hàng hóa quy định tại Khoản 1 Điều 6 Thông tư này.</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 38/2025/TT-BCT · hiệu lực 2025-07-01
+3. Sửa đổi, bổ sung khoản 1 Điều 18 như sau:
+“1. Cục Xuất nhập khẩu - Bộ Công Thương thực hiện việc cấp giấy phép quá cảnh hàng hóa quy định tại Khoản 1 Điều 6 Thông tư này.”
+CHUYỂN TIẾP: 3. Quy định chuyển tiếp
+Các Giấy phép, Giấy Chứng nhận, Chứng chỉ, văn bản phê duyệt, văn bản chấp thuận đối với các thủ tục hành chính trong các lĩnh vực đã được cơ quan quản lý nhà nước cấp, phê duyệt, chấp thuận trước ngày 01 tháng 7 năm 2025 tiếp tục có hiệu lực đến hết thời hạn tại Giấy phép, Giấy Chứng nhận, Chứng chỉ, văn bản phê duyệt, văn bản chấp thuận theo quy định.
+[amend] 26/2026/TT-BCT · hiệu lực 2026-05-29
+4. Sửa đổi, bổ sung Điều 18 như sau:
+“ Điều 18. Tổ chức thực hiện
+1. Ủy ban nhân dân cấp tỉnh tổ chức thực hiện việc cấp các giấy phép theo quy định tại khoản 1 Điều 5, Điều 13 và Điều 14 Thông tư này.
+2. Cục Xuất nhập khẩu tiếp nhận, thẩm định hồ sơ cấp giấy phép theo quy định tại khoản 2 Điều 5, Điều 13, Điều 14 và Điều 15 Thông tư này và trình Lãnh đạo Bộ Công Thương xem xét, quyết định”.
+CHUYỂN TIẾP: Điều 28. Điều khoản chuyển tiếp
+1. Đối với hồ sơ đề nghị giải quyết thủ tục hành chính thuộc các lĩnh vực được quy định tại Thông tư này đã được cơ quan có thẩm quyền tiếp nhận hoặc đã được đóng dấu bưu chính trước ngày Thông tư này có hiệu lực thì thực hiện theo quy định của pháp luật đang có hiệu lực điều chỉnh trong lĩnh vực đó tại thời điểm hồ sơ được tiếp nhận.
+2. Văn bản, giấy tờ đã được cơ quan, chức danh có thẩm quyền ban hành, cấp trước ngày Thông tư này có hiệu lực thi hành mà chưa hết hiệu lực hoặc chưa hết thời hạn sử dụng thì tiếp tục được áp dụng, sử dụng theo quy định của pháp luật cho đến khi hết thời hạn hoặc được sửa đổi, bổ sung, điều chỉnh, gia hạn, cấp lại, thay thế, bãi bỏ, hủy bỏ, thu hồi bởi cơ quan, chức danh tiếp nhận chức năng, nhiệm vụ, quyền hạn hoặc cơ quan, người có thẩm quyền./.
+Nơi nhận:
+- Văn phòng Tổng bí thư;
+- Văn phòng Chủ tịch nước;
+- Văn phòng Quốc hội;
+- Thủ tướng và các Phó Thủ tướng Chính phủ;
+- Các Bộ, cơ quan ngang Bộ, cơ quan thuộc CP;
+- Viện KSNDTC; Tòa án NDTC;
+- Kiểm toán Nhà nước;
+- Các Lãnh đạo Bộ; đơn vị thuộc Bộ;
+- UBND, HĐND các tỉnh, thành phố trực thuộc TW;
+- Các Sở Công Thương;
+- Cục Kiểm tra văn bản và Quản lý xử lý vi phạm hành chính, Bộ Tư pháp;
+- Cục Kiểm soát thủ tục hành chính, Bộ Tư pháp;
+- Website Chính phủ; Website Bộ Công Thương;
+- Công báo;
+- Lưu: VT, VPB (10).
+KT. BỘ TRƯỞNG
+THỨ TRƯỞNG
+(Đã ký)
+Phan Thị Thắng</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -4755,7 +6179,6 @@
           <t>actor_has_transitional</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -4766,18 +6189,55 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr">
         <is>
           <t>id cũ vilextime:T3:provision:5d48bef2-df54-11f0-abca-45ca78a631ce:2026-05-30 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S51" t="inlineStr"/>
-      <c r="T51" t="inlineStr"/>
-      <c r="U51" t="inlineStr"/>
-      <c r="V51" t="inlineStr"/>
-      <c r="W51" t="inlineStr"/>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>11/2015/TT-BCT · hiệu lực 2015-07-20 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 18. Tổ chức thực hiện
+1. Phòng Quản lý Xuất nhập khẩu khu vực thành phố Hồ Chí Minh, Phòng Quản lý Xuất nhập khẩu khu vực Đà Nẵng, Phòng Quản lý Xuất nhập khẩu khu vực Hà Nội (Cục Xuất nhập khẩu - Bộ Công Thương) thực hiện việc cấp giấy phép quá cảnh hàng hóa quy định tại Khoản 1 Điều 6 Thông tư này.</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 38/2025/TT-BCT · hiệu lực 2025-07-01
+3. Sửa đổi, bổ sung khoản 1 Điều 18 như sau:
+“1. Cục Xuất nhập khẩu - Bộ Công Thương thực hiện việc cấp giấy phép quá cảnh hàng hóa quy định tại Khoản 1 Điều 6 Thông tư này.”
+CHUYỂN TIẾP: 3. Quy định chuyển tiếp
+Các Giấy phép, Giấy Chứng nhận, Chứng chỉ, văn bản phê duyệt, văn bản chấp thuận đối với các thủ tục hành chính trong các lĩnh vực đã được cơ quan quản lý nhà nước cấp, phê duyệt, chấp thuận trước ngày 01 tháng 7 năm 2025 tiếp tục có hiệu lực đến hết thời hạn tại Giấy phép, Giấy Chứng nhận, Chứng chỉ, văn bản phê duyệt, văn bản chấp thuận theo quy định.
+[amend] 26/2026/TT-BCT · hiệu lực 2026-05-29
+4. Sửa đổi, bổ sung Điều 18 như sau:
+“ Điều 18. Tổ chức thực hiện
+1. Ủy ban nhân dân cấp tỉnh tổ chức thực hiện việc cấp các giấy phép theo quy định tại khoản 1 Điều 5, Điều 13 và Điều 14 Thông tư này.
+2. Cục Xuất nhập khẩu tiếp nhận, thẩm định hồ sơ cấp giấy phép theo quy định tại khoản 2 Điều 5, Điều 13, Điều 14 và Điều 15 Thông tư này và trình Lãnh đạo Bộ Công Thương xem xét, quyết định”.
+CHUYỂN TIẾP: Điều 28. Điều khoản chuyển tiếp
+1. Đối với hồ sơ đề nghị giải quyết thủ tục hành chính thuộc các lĩnh vực được quy định tại Thông tư này đã được cơ quan có thẩm quyền tiếp nhận hoặc đã được đóng dấu bưu chính trước ngày Thông tư này có hiệu lực thì thực hiện theo quy định của pháp luật đang có hiệu lực điều chỉnh trong lĩnh vực đó tại thời điểm hồ sơ được tiếp nhận.
+2. Văn bản, giấy tờ đã được cơ quan, chức danh có thẩm quyền ban hành, cấp trước ngày Thông tư này có hiệu lực thi hành mà chưa hết hiệu lực hoặc chưa hết thời hạn sử dụng thì tiếp tục được áp dụng, sử dụng theo quy định của pháp luật cho đến khi hết thời hạn hoặc được sửa đổi, bổ sung, điều chỉnh, gia hạn, cấp lại, thay thế, bãi bỏ, hủy bỏ, thu hồi bởi cơ quan, chức danh tiếp nhận chức năng, nhiệm vụ, quyền hạn hoặc cơ quan, người có thẩm quyền./.
+Nơi nhận:
+- Văn phòng Tổng bí thư;
+- Văn phòng Chủ tịch nước;
+- Văn phòng Quốc hội;
+- Thủ tướng và các Phó Thủ tướng Chính phủ;
+- Các Bộ, cơ quan ngang Bộ, cơ quan thuộc CP;
+- Viện KSNDTC; Tòa án NDTC;
+- Kiểm toán Nhà nước;
+- Các Lãnh đạo Bộ; đơn vị thuộc Bộ;
+- UBND, HĐND các tỉnh, thành phố trực thuộc TW;
+- Các Sở Công Thương;
+- Cục Kiểm tra văn bản và Quản lý xử lý vi phạm hành chính, Bộ Tư pháp;
+- Cục Kiểm soát thủ tục hành chính, Bộ Tư pháp;
+- Website Chính phủ; Website Bộ Công Thương;
+- Công báo;
+- Lưu: VT, VPB (10).
+KT. BỘ TRƯỞNG
+THỨ TRƯỞNG
+(Đã ký)
+Phan Thị Thắng</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -4835,7 +6295,6 @@
           <t>139/2020/NĐ-CP; 220/2025/NĐ-CP</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
           <t>cap_huyen 2025-08-06 sau_D4</t>
@@ -4851,18 +6310,30 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr">
         <is>
           <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Trường hợp cần bồi dưỡng kiến thức quốc phòng và an ninh cho già làng, trưởng bản và người có uy tín trong cộng đồng, ai có thẩm quyền triệu tập và đối tượng gồm những ai?»; nhãn cũ khong_dat question_ambiguous: 'Người có uy tín trong cộng đồng' là tên cả khoản 3; điểm a cùng khoản (Chủ tịch Hội đồng cấp tỉnh triệu tập) cũng thuộc nhóm này. Câu hỏi còn nói 'trưởng bản' trong khi văn bản là 'trưởng họ tộc'). Câu hỏi nêu cả chức việc tôn giáo nên chạm lần sửa 2021 (bỏ chức việc tôn giáo khỏi điểm b) và lần sửa 2025 (cấp huyện → cấp xã); ba đáp án. 'Dưới cấp tỉnh' loại điểm a; id cũ vilextime:T3:provision:64015f1e-2c85-11f1-bf18-f11eea13dfa4:2014-04-11 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S52" t="inlineStr"/>
-      <c r="T52" t="inlineStr"/>
-      <c r="U52" t="inlineStr"/>
-      <c r="V52" t="inlineStr"/>
-      <c r="W52" t="inlineStr"/>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>13/2014/NĐ-CP · hiệu lực 2014-04-10 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 2. Thẩm quyền triệu tập đối tượng bồi dưỡng kiến thức quốc phòng và an ninh
+3. Đối tượng là cá nhân tiêu biểu, người có uy tín trong cộng đồng dân cư
+a) Chủ tịch Hội đồng giáo dục quốc phòng và an ninh cấp tỉnh quyết định triệu tập bồi dưỡng kiến thức quốc phòng và an ninh cho thành viên Hội đồng Chứng minh, Hội đồng Trị sự Trung ương Giáo hội Phật giáo Việt Nam, Hòa thượng, Thượng tọa, Đại đức, Ni trưởng, Ni sư của đạo Phật; thành viên Ban Thường vụ, Chủ tịch các Ủy ban Hội đồng Giám mục Việt Nam, Hồng y, Tổng giám mục, Giám mục, Giám mục phó, Giám mục phụ tá, Giám quản và người đứng đầu các dòng tu của đạo Công giáo; thành viên Ban Trị sự Trung ương của các hội thánh Tin lành; thành viên Hội đồng Chưởng quản, Hội đồng Hội thánh, Ban Thường trực Hội thánh, Phối sư và chức sắc tương đương trở lên của các hội thánh Cao đài; thành viên Ban Trị sự Trung ương Giáo hội Phật giáo Hòa Hảo; những chức vụ, phẩm trật tương đương của các tổ chức tôn giáo khác; người đứng đầu các trường đào tạo những người chuyên hoạt động tôn giáo không thuộc đối tượng quy định tại Khoản 1, Khoản 2 Điều này; các nhà hoạt động văn hóa, xã hội, khoa học, nghệ thuật trên địa bàn theo kế hoạch được Chủ tịch Ủy ban nhân dân cấp tỉnh phê duyệt;
+b) Chủ tịch Hội đồng giáo dục và an ninh cấp huyện triệu tập bồi dưỡng kiến thức quốc phòng và an ninh cho chức việc tôn giáo, già làng, trưởng họ tộc trên địa bàn theo kế hoạch được Chủ tịch Ủy ban nhân dân cấp huyện phê duyệt.</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 139/2020/NĐ-CP · hiệu lực 2021-01-15
+b) Sửa đổi, bổ sung điểm b khoản 3 Điều 2 như sau:
+"b) Chủ tịch Hội đồng giáo dục quốc phòng và an ninh cấp huyện triệu tập bồi dưỡng kiến thức quốc phòng và an ninh cho già làng, trưởng họ tộc trên địa bàn theo kế hoạch được Chủ tịch Ủy ban nhân dân cấp huyện phê duyệt."
+[amend] 220/2025/NĐ-CP · hiệu lực 2025-08-07
+đ) Sửa đổi, bổ sung điểm b khoản 3 Điều 2 Nghị định số 13/2014/NĐ-CP được sửa đổi, bổ sung tại điểm b khoản 2 Điều 1 Nghị định số 139/2020/NĐ-CP như sau:
+“b) Chủ tịch Hội đồng giáo dục và an ninh cấp xã triệu tập bồi dưỡng kiến thức quốc phòng và an ninh cho già làng, trưởng họ tộc trên địa bàn theo kế hoạch được Chủ tịch Ủy ban nhân dân cấp xã phê duyệt.”</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -4920,7 +6391,6 @@
           <t>139/2020/NĐ-CP; 220/2025/NĐ-CP</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
           <t>cap_huyen 2025-08-06 sau_D4</t>
@@ -4936,18 +6406,30 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr">
         <is>
           <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Trường hợp cần bồi dưỡng kiến thức quốc phòng và an ninh cho già làng, trưởng bản và người có uy tín trong cộng đồng, ai có thẩm quyền triệu tập và đối tượng gồm những ai?»; nhãn cũ khong_dat question_ambiguous: 'Người có uy tín trong cộng đồng' là tên cả khoản 3; điểm a cùng khoản (Chủ tịch Hội đồng cấp tỉnh triệu tập) cũng thuộc nhóm này. Câu hỏi còn nói 'trưởng bản' trong khi văn bản là 'trưởng họ tộc'). Câu hỏi nêu cả chức việc tôn giáo nên chạm lần sửa 2021 (bỏ chức việc tôn giáo khỏi điểm b) và lần sửa 2025 (cấp huyện → cấp xã); ba đáp án. 'Dưới cấp tỉnh' loại điểm a; id cũ vilextime:T3:provision:64015f1e-2c85-11f1-bf18-f11eea13dfa4:2021-01-16 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S53" t="inlineStr"/>
-      <c r="T53" t="inlineStr"/>
-      <c r="U53" t="inlineStr"/>
-      <c r="V53" t="inlineStr"/>
-      <c r="W53" t="inlineStr"/>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>13/2014/NĐ-CP · hiệu lực 2014-04-10 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 2. Thẩm quyền triệu tập đối tượng bồi dưỡng kiến thức quốc phòng và an ninh
+3. Đối tượng là cá nhân tiêu biểu, người có uy tín trong cộng đồng dân cư
+a) Chủ tịch Hội đồng giáo dục quốc phòng và an ninh cấp tỉnh quyết định triệu tập bồi dưỡng kiến thức quốc phòng và an ninh cho thành viên Hội đồng Chứng minh, Hội đồng Trị sự Trung ương Giáo hội Phật giáo Việt Nam, Hòa thượng, Thượng tọa, Đại đức, Ni trưởng, Ni sư của đạo Phật; thành viên Ban Thường vụ, Chủ tịch các Ủy ban Hội đồng Giám mục Việt Nam, Hồng y, Tổng giám mục, Giám mục, Giám mục phó, Giám mục phụ tá, Giám quản và người đứng đầu các dòng tu của đạo Công giáo; thành viên Ban Trị sự Trung ương của các hội thánh Tin lành; thành viên Hội đồng Chưởng quản, Hội đồng Hội thánh, Ban Thường trực Hội thánh, Phối sư và chức sắc tương đương trở lên của các hội thánh Cao đài; thành viên Ban Trị sự Trung ương Giáo hội Phật giáo Hòa Hảo; những chức vụ, phẩm trật tương đương của các tổ chức tôn giáo khác; người đứng đầu các trường đào tạo những người chuyên hoạt động tôn giáo không thuộc đối tượng quy định tại Khoản 1, Khoản 2 Điều này; các nhà hoạt động văn hóa, xã hội, khoa học, nghệ thuật trên địa bàn theo kế hoạch được Chủ tịch Ủy ban nhân dân cấp tỉnh phê duyệt;
+b) Chủ tịch Hội đồng giáo dục và an ninh cấp huyện triệu tập bồi dưỡng kiến thức quốc phòng và an ninh cho chức việc tôn giáo, già làng, trưởng họ tộc trên địa bàn theo kế hoạch được Chủ tịch Ủy ban nhân dân cấp huyện phê duyệt.</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 139/2020/NĐ-CP · hiệu lực 2021-01-15
+b) Sửa đổi, bổ sung điểm b khoản 3 Điều 2 như sau:
+"b) Chủ tịch Hội đồng giáo dục quốc phòng và an ninh cấp huyện triệu tập bồi dưỡng kiến thức quốc phòng và an ninh cho già làng, trưởng họ tộc trên địa bàn theo kế hoạch được Chủ tịch Ủy ban nhân dân cấp huyện phê duyệt."
+[amend] 220/2025/NĐ-CP · hiệu lực 2025-08-07
+đ) Sửa đổi, bổ sung điểm b khoản 3 Điều 2 Nghị định số 13/2014/NĐ-CP được sửa đổi, bổ sung tại điểm b khoản 2 Điều 1 Nghị định số 139/2020/NĐ-CP như sau:
+“b) Chủ tịch Hội đồng giáo dục và an ninh cấp xã triệu tập bồi dưỡng kiến thức quốc phòng và an ninh cho già làng, trưởng họ tộc trên địa bàn theo kế hoạch được Chủ tịch Ủy ban nhân dân cấp xã phê duyệt.”</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -5005,7 +6487,6 @@
           <t>139/2020/NĐ-CP; 220/2025/NĐ-CP</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
           <t>cap_huyen 2025-08-06 sau_D4</t>
@@ -5021,18 +6502,30 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr">
         <is>
           <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Trường hợp cần bồi dưỡng kiến thức quốc phòng và an ninh cho già làng, trưởng bản và người có uy tín trong cộng đồng, ai có thẩm quyền triệu tập và đối tượng gồm những ai?»; nhãn cũ khong_dat question_ambiguous: 'Người có uy tín trong cộng đồng' là tên cả khoản 3; điểm a cùng khoản (Chủ tịch Hội đồng cấp tỉnh triệu tập) cũng thuộc nhóm này. Câu hỏi còn nói 'trưởng bản' trong khi văn bản là 'trưởng họ tộc'). Câu hỏi nêu cả chức việc tôn giáo nên chạm lần sửa 2021 (bỏ chức việc tôn giáo khỏi điểm b) và lần sửa 2025 (cấp huyện → cấp xã); ba đáp án. 'Dưới cấp tỉnh' loại điểm a; id cũ vilextime:T3:provision:64015f1e-2c85-11f1-bf18-f11eea13dfa4:2025-08-08 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S54" t="inlineStr"/>
-      <c r="T54" t="inlineStr"/>
-      <c r="U54" t="inlineStr"/>
-      <c r="V54" t="inlineStr"/>
-      <c r="W54" t="inlineStr"/>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>13/2014/NĐ-CP · hiệu lực 2014-04-10 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 2. Thẩm quyền triệu tập đối tượng bồi dưỡng kiến thức quốc phòng và an ninh
+3. Đối tượng là cá nhân tiêu biểu, người có uy tín trong cộng đồng dân cư
+a) Chủ tịch Hội đồng giáo dục quốc phòng và an ninh cấp tỉnh quyết định triệu tập bồi dưỡng kiến thức quốc phòng và an ninh cho thành viên Hội đồng Chứng minh, Hội đồng Trị sự Trung ương Giáo hội Phật giáo Việt Nam, Hòa thượng, Thượng tọa, Đại đức, Ni trưởng, Ni sư của đạo Phật; thành viên Ban Thường vụ, Chủ tịch các Ủy ban Hội đồng Giám mục Việt Nam, Hồng y, Tổng giám mục, Giám mục, Giám mục phó, Giám mục phụ tá, Giám quản và người đứng đầu các dòng tu của đạo Công giáo; thành viên Ban Trị sự Trung ương của các hội thánh Tin lành; thành viên Hội đồng Chưởng quản, Hội đồng Hội thánh, Ban Thường trực Hội thánh, Phối sư và chức sắc tương đương trở lên của các hội thánh Cao đài; thành viên Ban Trị sự Trung ương Giáo hội Phật giáo Hòa Hảo; những chức vụ, phẩm trật tương đương của các tổ chức tôn giáo khác; người đứng đầu các trường đào tạo những người chuyên hoạt động tôn giáo không thuộc đối tượng quy định tại Khoản 1, Khoản 2 Điều này; các nhà hoạt động văn hóa, xã hội, khoa học, nghệ thuật trên địa bàn theo kế hoạch được Chủ tịch Ủy ban nhân dân cấp tỉnh phê duyệt;
+b) Chủ tịch Hội đồng giáo dục và an ninh cấp huyện triệu tập bồi dưỡng kiến thức quốc phòng và an ninh cho chức việc tôn giáo, già làng, trưởng họ tộc trên địa bàn theo kế hoạch được Chủ tịch Ủy ban nhân dân cấp huyện phê duyệt.</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 139/2020/NĐ-CP · hiệu lực 2021-01-15
+b) Sửa đổi, bổ sung điểm b khoản 3 Điều 2 như sau:
+"b) Chủ tịch Hội đồng giáo dục quốc phòng và an ninh cấp huyện triệu tập bồi dưỡng kiến thức quốc phòng và an ninh cho già làng, trưởng họ tộc trên địa bàn theo kế hoạch được Chủ tịch Ủy ban nhân dân cấp huyện phê duyệt."
+[amend] 220/2025/NĐ-CP · hiệu lực 2025-08-07
+đ) Sửa đổi, bổ sung điểm b khoản 3 Điều 2 Nghị định số 13/2014/NĐ-CP được sửa đổi, bổ sung tại điểm b khoản 2 Điều 1 Nghị định số 139/2020/NĐ-CP như sau:
+“b) Chủ tịch Hội đồng giáo dục và an ninh cấp xã triệu tập bồi dưỡng kiến thức quốc phòng và an ninh cho già làng, trưởng họ tộc trên địa bàn theo kế hoạch được Chủ tịch Ủy ban nhân dân cấp xã phê duyệt.”</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -5095,7 +6588,6 @@
           <t>actor_has_transitional</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -5106,18 +6598,43 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr">
         <is>
           <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Khi Chủ tịch Ủy ban nhân dân cấp huyện xử phạt vi phạm về quản lý, sử dụng tài sản công, quyền tịch thu tang vật, phương tiện của người này có bị giới hạn về giá trị không?»; nhãn cũ dat: ). Sửa lỗi gán trước: Điều 51 NĐ 63/2019 là lĩnh vực dự trữ quốc gia, câu hỏi cũ nói tài sản công. Câu mới gọi 'Chủ tịch UBND dưới cấp tỉnh' đúng cho cả cấp huyện (mốc 1–2) và cấp xã (mốc 3); ba đáp án: giới hạn theo điểm b, giới hạn 100 triệu, không giới hạn; id cũ vilextime:T3:provision:6ece9720-1edb-11f1-b5ee-25d1c75e0691:2019-09-02 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S55" t="inlineStr"/>
-      <c r="T55" t="inlineStr"/>
-      <c r="U55" t="inlineStr"/>
-      <c r="V55" t="inlineStr"/>
-      <c r="W55" t="inlineStr"/>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>63/2019/NĐ-CP · hiệu lực 2019-09-01 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 51. Thẩm quyền xử phạt của Chủ tịch Ủy ban nhân dân
+1. Chủ tịch Ủy ban nhân dân cấp huyện có quyền:
+a) Phạt cảnh cáo;
+b) Phạt tiền đến 50.000.000 đồng;
+c) Tịch thu tang vật, phương tiện vi phạm hành chính có giá trị không vượt quá mức phạt tiền quy định tại điểm b khoản này;
+d) Áp dụng các biện pháp khắc phục hậu quả theo quy định tại khoản 5 Điều 4 Nghị định này.</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 102/2021/NĐ-CP · hiệu lực 2022-01-01
+5. Sửa đổi, bổ sung điểm c khoản 1 Điều 51 như sau:
+"c) Tịch thu tang vật, phương tiện vi phạm hành chính có giá trị không vượt quá 100.000.000 đồng".
+CHUYỂN TIẾP: Điều 7. Quy định chuyển tiếp
+1. Đối với trường hợp quyết định xử phạt vi phạm hành chính đã được ban hành trước thời điểm Nghị định này có hiệu lực thi hành mà sau thời điểm có hiệu lực của Nghị định này, cá nhân, tổ chức bị xử phạt vi phạm hành chính còn khiếu nại thì được giải quyết theo Nghị định xử phạt vi phạm hành chính có hiệu lực tại thời điểm thực hiện hành vi vi phạm hành chính.
+2. Đối với các hành vi vi phạm hành chính trong lĩnh vực thuế, hóa đơn; hải quan; kinh doanh bảo hiểm, kinh doanh xổ số; quản lý, sử dụng tài sản công; thực hành tiết kiệm, chống lãng phí; dự trữ quốc gia; kho bạc nhà nước; kế toán, kiểm toán độc lập xảy ra trước ngày Nghị định này có hiệu lực thi hành mà sau đó mới bị phát hiện hoặc đang xem xét, giải quyết để xử phạt vi phạm hành chính thì áp dụng các quy định về xử phạt quy định tại Nghị định này nếu Nghị định này không quy định trách nhiệm pháp lý hoặc quy định trách nhiệm pháp lý nhẹ hơn cho cá nhân, tổ chức vi phạm.
+3. Đối với hồ sơ đề nghị miễn tiền phạt vi phạm hành chính về thuế, hóa đơn đã được cơ quan thuế tiếp nhận trước ngày Nghị định này có hiệu lực thi hành thì áp dụng Nghị định số 125/2020/NĐ-CP ngày 19 tháng 10 năm 2020 của Chính phủ quy định xử phạt vi phạm hành chính về thuế, hóa đơn để giải quyết theo quy định.
+[amend] 55/2026/NĐ-CP · hiệu lực 2026-02-09
+23. Sửa đổi, bổ sung khoản 1 Điều 51 như sau:
+"1. Chủ tịch Ủy ban nhân dân cấp xã có quyền:
+a) Phạt cảnh cáo;
+b) Phạt tiền đến 50.000.000 đồng;
+c) Tịch thu tang vật, phương tiện vi phạm hành chính;
+d) Áp dụng biện pháp khắc phục hậu quả quy định tại khoản 5 Điều 4 Nghị định này."
+CHUYỂN TIẾP: Điều 3. Quy định chuyển tiếp
+1. Đối với các hành vi vi phạm hành chính trong lĩnh vực quản lý tài sản công, dự trữ quốc gia, kho bạc nhà nước xảy ra trước ngày Nghị định này có hiệu lực thi hành mà sau đó mới bị phát hiện hoặc đang xem xét, giải quyết để xử phạt vi phạm hành chính thì áp dụng các quy định về xử phạt theo quy định tại Nghị định này.
+2. Trường hợp các văn bản quy phạm pháp luật dẫn chiếu tại Nghị định này được sửa đổi, bổ sung, thay thế thì thực hiện theo quy định tương ứng tại văn bản sửa đổi, bổ sung, thay thế đó.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -5180,7 +6697,6 @@
           <t>actor_has_transitional</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -5191,18 +6707,43 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr">
         <is>
           <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Khi Chủ tịch Ủy ban nhân dân cấp huyện xử phạt vi phạm về quản lý, sử dụng tài sản công, quyền tịch thu tang vật, phương tiện của người này có bị giới hạn về giá trị không?»; nhãn cũ dat: ). Sửa lỗi gán trước: Điều 51 NĐ 63/2019 là lĩnh vực dự trữ quốc gia, câu hỏi cũ nói tài sản công. Câu mới gọi 'Chủ tịch UBND dưới cấp tỉnh' đúng cho cả cấp huyện (mốc 1–2) và cấp xã (mốc 3); ba đáp án: giới hạn theo điểm b, giới hạn 100 triệu, không giới hạn; id cũ vilextime:T3:provision:6ece9720-1edb-11f1-b5ee-25d1c75e0691:2022-01-02 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S56" t="inlineStr"/>
-      <c r="T56" t="inlineStr"/>
-      <c r="U56" t="inlineStr"/>
-      <c r="V56" t="inlineStr"/>
-      <c r="W56" t="inlineStr"/>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>63/2019/NĐ-CP · hiệu lực 2019-09-01 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 51. Thẩm quyền xử phạt của Chủ tịch Ủy ban nhân dân
+1. Chủ tịch Ủy ban nhân dân cấp huyện có quyền:
+a) Phạt cảnh cáo;
+b) Phạt tiền đến 50.000.000 đồng;
+c) Tịch thu tang vật, phương tiện vi phạm hành chính có giá trị không vượt quá mức phạt tiền quy định tại điểm b khoản này;
+d) Áp dụng các biện pháp khắc phục hậu quả theo quy định tại khoản 5 Điều 4 Nghị định này.</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 102/2021/NĐ-CP · hiệu lực 2022-01-01
+5. Sửa đổi, bổ sung điểm c khoản 1 Điều 51 như sau:
+"c) Tịch thu tang vật, phương tiện vi phạm hành chính có giá trị không vượt quá 100.000.000 đồng".
+CHUYỂN TIẾP: Điều 7. Quy định chuyển tiếp
+1. Đối với trường hợp quyết định xử phạt vi phạm hành chính đã được ban hành trước thời điểm Nghị định này có hiệu lực thi hành mà sau thời điểm có hiệu lực của Nghị định này, cá nhân, tổ chức bị xử phạt vi phạm hành chính còn khiếu nại thì được giải quyết theo Nghị định xử phạt vi phạm hành chính có hiệu lực tại thời điểm thực hiện hành vi vi phạm hành chính.
+2. Đối với các hành vi vi phạm hành chính trong lĩnh vực thuế, hóa đơn; hải quan; kinh doanh bảo hiểm, kinh doanh xổ số; quản lý, sử dụng tài sản công; thực hành tiết kiệm, chống lãng phí; dự trữ quốc gia; kho bạc nhà nước; kế toán, kiểm toán độc lập xảy ra trước ngày Nghị định này có hiệu lực thi hành mà sau đó mới bị phát hiện hoặc đang xem xét, giải quyết để xử phạt vi phạm hành chính thì áp dụng các quy định về xử phạt quy định tại Nghị định này nếu Nghị định này không quy định trách nhiệm pháp lý hoặc quy định trách nhiệm pháp lý nhẹ hơn cho cá nhân, tổ chức vi phạm.
+3. Đối với hồ sơ đề nghị miễn tiền phạt vi phạm hành chính về thuế, hóa đơn đã được cơ quan thuế tiếp nhận trước ngày Nghị định này có hiệu lực thi hành thì áp dụng Nghị định số 125/2020/NĐ-CP ngày 19 tháng 10 năm 2020 của Chính phủ quy định xử phạt vi phạm hành chính về thuế, hóa đơn để giải quyết theo quy định.
+[amend] 55/2026/NĐ-CP · hiệu lực 2026-02-09
+23. Sửa đổi, bổ sung khoản 1 Điều 51 như sau:
+"1. Chủ tịch Ủy ban nhân dân cấp xã có quyền:
+a) Phạt cảnh cáo;
+b) Phạt tiền đến 50.000.000 đồng;
+c) Tịch thu tang vật, phương tiện vi phạm hành chính;
+d) Áp dụng biện pháp khắc phục hậu quả quy định tại khoản 5 Điều 4 Nghị định này."
+CHUYỂN TIẾP: Điều 3. Quy định chuyển tiếp
+1. Đối với các hành vi vi phạm hành chính trong lĩnh vực quản lý tài sản công, dự trữ quốc gia, kho bạc nhà nước xảy ra trước ngày Nghị định này có hiệu lực thi hành mà sau đó mới bị phát hiện hoặc đang xem xét, giải quyết để xử phạt vi phạm hành chính thì áp dụng các quy định về xử phạt theo quy định tại Nghị định này.
+2. Trường hợp các văn bản quy phạm pháp luật dẫn chiếu tại Nghị định này được sửa đổi, bổ sung, thay thế thì thực hiện theo quy định tương ứng tại văn bản sửa đổi, bổ sung, thay thế đó.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -5265,7 +6806,6 @@
           <t>actor_has_transitional</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -5276,18 +6816,43 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr">
         <is>
           <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Khi Chủ tịch Ủy ban nhân dân cấp huyện xử phạt vi phạm về quản lý, sử dụng tài sản công, quyền tịch thu tang vật, phương tiện của người này có bị giới hạn về giá trị không?»; nhãn cũ khong_dat unanswerable_as_asked: Từ 2026-02-10 khoản 1 trao quyền cho Chủ tịch Ủy ban nhân dân cấp xã (cấp huyện không còn); câu hỏi vẫn hỏi Chủ tịch cấp huyện. Đề xuất sửa câu hỏi thành 'Chủ tịch Ủy ban nhân dân theo khoản 1 Điều 51'). Sửa lỗi gán trước: Điều 51 NĐ 63/2019 là lĩnh vực dự trữ quốc gia, câu hỏi cũ nói tài sản công. Câu mới gọi 'Chủ tịch UBND dưới cấp tỉnh' đúng cho cả cấp huyện (mốc 1–2) và cấp xã (mốc 3); ba đáp án: giới hạn theo điểm b, giới hạn 100 triệu, không giới hạn; id cũ vilextime:T3:provision:6ece9720-1edb-11f1-b5ee-25d1c75e0691:2026-02-10 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S57" t="inlineStr"/>
-      <c r="T57" t="inlineStr"/>
-      <c r="U57" t="inlineStr"/>
-      <c r="V57" t="inlineStr"/>
-      <c r="W57" t="inlineStr"/>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>63/2019/NĐ-CP · hiệu lực 2019-09-01 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 51. Thẩm quyền xử phạt của Chủ tịch Ủy ban nhân dân
+1. Chủ tịch Ủy ban nhân dân cấp huyện có quyền:
+a) Phạt cảnh cáo;
+b) Phạt tiền đến 50.000.000 đồng;
+c) Tịch thu tang vật, phương tiện vi phạm hành chính có giá trị không vượt quá mức phạt tiền quy định tại điểm b khoản này;
+d) Áp dụng các biện pháp khắc phục hậu quả theo quy định tại khoản 5 Điều 4 Nghị định này.</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 102/2021/NĐ-CP · hiệu lực 2022-01-01
+5. Sửa đổi, bổ sung điểm c khoản 1 Điều 51 như sau:
+"c) Tịch thu tang vật, phương tiện vi phạm hành chính có giá trị không vượt quá 100.000.000 đồng".
+CHUYỂN TIẾP: Điều 7. Quy định chuyển tiếp
+1. Đối với trường hợp quyết định xử phạt vi phạm hành chính đã được ban hành trước thời điểm Nghị định này có hiệu lực thi hành mà sau thời điểm có hiệu lực của Nghị định này, cá nhân, tổ chức bị xử phạt vi phạm hành chính còn khiếu nại thì được giải quyết theo Nghị định xử phạt vi phạm hành chính có hiệu lực tại thời điểm thực hiện hành vi vi phạm hành chính.
+2. Đối với các hành vi vi phạm hành chính trong lĩnh vực thuế, hóa đơn; hải quan; kinh doanh bảo hiểm, kinh doanh xổ số; quản lý, sử dụng tài sản công; thực hành tiết kiệm, chống lãng phí; dự trữ quốc gia; kho bạc nhà nước; kế toán, kiểm toán độc lập xảy ra trước ngày Nghị định này có hiệu lực thi hành mà sau đó mới bị phát hiện hoặc đang xem xét, giải quyết để xử phạt vi phạm hành chính thì áp dụng các quy định về xử phạt quy định tại Nghị định này nếu Nghị định này không quy định trách nhiệm pháp lý hoặc quy định trách nhiệm pháp lý nhẹ hơn cho cá nhân, tổ chức vi phạm.
+3. Đối với hồ sơ đề nghị miễn tiền phạt vi phạm hành chính về thuế, hóa đơn đã được cơ quan thuế tiếp nhận trước ngày Nghị định này có hiệu lực thi hành thì áp dụng Nghị định số 125/2020/NĐ-CP ngày 19 tháng 10 năm 2020 của Chính phủ quy định xử phạt vi phạm hành chính về thuế, hóa đơn để giải quyết theo quy định.
+[amend] 55/2026/NĐ-CP · hiệu lực 2026-02-09
+23. Sửa đổi, bổ sung khoản 1 Điều 51 như sau:
+"1. Chủ tịch Ủy ban nhân dân cấp xã có quyền:
+a) Phạt cảnh cáo;
+b) Phạt tiền đến 50.000.000 đồng;
+c) Tịch thu tang vật, phương tiện vi phạm hành chính;
+d) Áp dụng biện pháp khắc phục hậu quả quy định tại khoản 5 Điều 4 Nghị định này."
+CHUYỂN TIẾP: Điều 3. Quy định chuyển tiếp
+1. Đối với các hành vi vi phạm hành chính trong lĩnh vực quản lý tài sản công, dự trữ quốc gia, kho bạc nhà nước xảy ra trước ngày Nghị định này có hiệu lực thi hành mà sau đó mới bị phát hiện hoặc đang xem xét, giải quyết để xử phạt vi phạm hành chính thì áp dụng các quy định về xử phạt theo quy định tại Nghị định này.
+2. Trường hợp các văn bản quy phạm pháp luật dẫn chiếu tại Nghị định này được sửa đổi, bổ sung, thay thế thì thực hiện theo quy định tương ứng tại văn bản sửa đổi, bổ sung, thay thế đó.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -5350,7 +6915,6 @@
           <t>actor_has_transitional</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -5361,18 +6925,29 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P58" t="inlineStr"/>
-      <c r="Q58" t="inlineStr"/>
       <c r="R58" t="inlineStr">
         <is>
           <t>id cũ vilextime:T3:provision:746ee898-eb72-11f0-a645-6bade352d545#k3:2019-03-29 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S58" t="inlineStr"/>
-      <c r="T58" t="inlineStr"/>
-      <c r="U58" t="inlineStr"/>
-      <c r="V58" t="inlineStr"/>
-      <c r="W58" t="inlineStr"/>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>03/2019/TT-BGTVT · hiệu lực 2019-03-28 → 2025-01-01 · lúc thu thập: Hết hiệu lực toàn bộ
+Điều 3. Giải thích từ ngữ
+3. Cơ quan quản lý đường bộ là Cục Quản lý đường bộ (đối với quốc lộ), Sở Giao thông vận tải (đối với công trình đường bộ được phân cấp, ủy quyền quản lý).</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 43/2021/TT-BGTVT · hiệu lực 2022-03-01
+2. Sửa đổi khoản 3 Điều 3 như sau:
+“3. Cơ quan quản lý đường bộ là Tổng cục Đường bộ Việt Nam, Cục Quản lý đường bộ; cơ quan chuyên môn về giao thông vận tải thuộc Ủy ban nhân dân cấp tỉnh (sau đây gọi là Sở Giao thông vận tải), Ủy ban nhân dân cấp huyện, Ủy ban nhân dân cấp xã.”.
+CHUYỂN TIẾP: Điều 3. Điều khoản chuyển tiếp
+Đối với các công trình khắc phục hậu quả thiên tai, bảo đảm giao thông bước 1 đã thực hiện trước ngày Thông tư này có hiệu lực thì việc lập, soát xét và thẩm định, phê duyệt tiếp tục được thực hiện theo quy định tại Điều 14 Thông tư số 03/2021/TT-BGTVT ngày 11 tháng 01 năm 2019 của Bộ trưởng Bộ Giao thông vận tải quy định về công tác phòng, chống và khắc phục hậu quả thiên tai trong lĩnh vực đường bộ.
+[amend] 22/2023/TT-BGTVT · hiệu lực 2023-08-15
+(không tìm được đoạn)</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -5435,7 +7010,6 @@
           <t>actor_has_transitional</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -5446,18 +7020,29 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P59" t="inlineStr"/>
-      <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr">
         <is>
           <t>id cũ vilextime:T3:provision:746ee898-eb72-11f0-a645-6bade352d545#k3:2022-03-02 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S59" t="inlineStr"/>
-      <c r="T59" t="inlineStr"/>
-      <c r="U59" t="inlineStr"/>
-      <c r="V59" t="inlineStr"/>
-      <c r="W59" t="inlineStr"/>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>03/2019/TT-BGTVT · hiệu lực 2019-03-28 → 2025-01-01 · lúc thu thập: Hết hiệu lực toàn bộ
+Điều 3. Giải thích từ ngữ
+3. Cơ quan quản lý đường bộ là Cục Quản lý đường bộ (đối với quốc lộ), Sở Giao thông vận tải (đối với công trình đường bộ được phân cấp, ủy quyền quản lý).</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 43/2021/TT-BGTVT · hiệu lực 2022-03-01
+2. Sửa đổi khoản 3 Điều 3 như sau:
+“3. Cơ quan quản lý đường bộ là Tổng cục Đường bộ Việt Nam, Cục Quản lý đường bộ; cơ quan chuyên môn về giao thông vận tải thuộc Ủy ban nhân dân cấp tỉnh (sau đây gọi là Sở Giao thông vận tải), Ủy ban nhân dân cấp huyện, Ủy ban nhân dân cấp xã.”.
+CHUYỂN TIẾP: Điều 3. Điều khoản chuyển tiếp
+Đối với các công trình khắc phục hậu quả thiên tai, bảo đảm giao thông bước 1 đã thực hiện trước ngày Thông tư này có hiệu lực thì việc lập, soát xét và thẩm định, phê duyệt tiếp tục được thực hiện theo quy định tại Điều 14 Thông tư số 03/2021/TT-BGTVT ngày 11 tháng 01 năm 2019 của Bộ trưởng Bộ Giao thông vận tải quy định về công tác phòng, chống và khắc phục hậu quả thiên tai trong lĩnh vực đường bộ.
+[amend] 22/2023/TT-BGTVT · hiệu lực 2023-08-15
+(không tìm được đoạn)</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -5520,7 +7105,6 @@
           <t>actor_has_transitional</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -5531,18 +7115,29 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P60" t="inlineStr"/>
-      <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr">
         <is>
           <t>id cũ vilextime:T3:provision:746ee898-eb72-11f0-a645-6bade352d545#k3:2023-08-16 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S60" t="inlineStr"/>
-      <c r="T60" t="inlineStr"/>
-      <c r="U60" t="inlineStr"/>
-      <c r="V60" t="inlineStr"/>
-      <c r="W60" t="inlineStr"/>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>03/2019/TT-BGTVT · hiệu lực 2019-03-28 → 2025-01-01 · lúc thu thập: Hết hiệu lực toàn bộ
+Điều 3. Giải thích từ ngữ
+3. Cơ quan quản lý đường bộ là Cục Quản lý đường bộ (đối với quốc lộ), Sở Giao thông vận tải (đối với công trình đường bộ được phân cấp, ủy quyền quản lý).</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 43/2021/TT-BGTVT · hiệu lực 2022-03-01
+2. Sửa đổi khoản 3 Điều 3 như sau:
+“3. Cơ quan quản lý đường bộ là Tổng cục Đường bộ Việt Nam, Cục Quản lý đường bộ; cơ quan chuyên môn về giao thông vận tải thuộc Ủy ban nhân dân cấp tỉnh (sau đây gọi là Sở Giao thông vận tải), Ủy ban nhân dân cấp huyện, Ủy ban nhân dân cấp xã.”.
+CHUYỂN TIẾP: Điều 3. Điều khoản chuyển tiếp
+Đối với các công trình khắc phục hậu quả thiên tai, bảo đảm giao thông bước 1 đã thực hiện trước ngày Thông tư này có hiệu lực thì việc lập, soát xét và thẩm định, phê duyệt tiếp tục được thực hiện theo quy định tại Điều 14 Thông tư số 03/2021/TT-BGTVT ngày 11 tháng 01 năm 2019 của Bộ trưởng Bộ Giao thông vận tải quy định về công tác phòng, chống và khắc phục hậu quả thiên tai trong lĩnh vực đường bộ.
+[amend] 22/2023/TT-BGTVT · hiệu lực 2023-08-15
+(không tìm được đoạn)</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -5605,7 +7200,6 @@
           <t>actor_has_transitional</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -5616,18 +7210,29 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P61" t="inlineStr"/>
-      <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr">
         <is>
           <t>lineage thay thế 29/09; câu hỏi và đáp án ngắn do cùng model viết</t>
         </is>
       </c>
-      <c r="S61" t="inlineStr"/>
-      <c r="T61" t="inlineStr"/>
-      <c r="U61" t="inlineStr"/>
-      <c r="V61" t="inlineStr"/>
-      <c r="W61" t="inlineStr"/>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>03/2019/TT-BGTVT · hiệu lực 2019-03-28 → 2025-01-01 · lúc thu thập: Hết hiệu lực toàn bộ
+Điều 9. Chỉ đạo, chỉ huy ứng phó sự cố, thiên tai và tìm kiếm cứu nạn
+1. Căn cứ vào bản tin dự báo, cảnh báo thiên tai, các văn bản chỉ đạo của cấp trên, Tổng cục Đường bộ Việt Nam (đối với hệ thống quốc lộ), Sở Giao thông vận tải (đối với các hệ thống đường địa phương), trong phạm vi chức năng, nhiệm vụ được giao chỉ đạo, chỉ huy triển khai thực hiện biện pháp ứng phó sự cố, thiên tai và tìm kiếm cứu nạn trong lĩnh vực giao thông đường bộ.</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 43/2021/TT-BGTVT · hiệu lực 2022-03-01
+4. Sửa đổi khoản 1 Điều 9 như sau:
+“1. Căn cứ vào bản tin dự báo, cảnh báo thiên tai, các văn bản chỉ đạo của cấp trên, Tổng cục Đường bộ Việt Nam (đối với hệ thống quốc lộ), Sở Giao thông vận tải (đối với các hệ thống đường địa phương; tuyến, đoạn tuyến quốc lộ được giao quản lý), trong phạm vi chức năng, nhiệm vụ được giao chỉ đạo, chỉ huy triển khai thực hiện biện pháp ứng phó sự cố, thiên tai và tìm kiếm cứu nạn trong lĩnh vực giao thông đường bộ.”.
+CHUYỂN TIẾP: Điều 3. Điều khoản chuyển tiếp
+Đối với các công trình khắc phục hậu quả thiên tai, bảo đảm giao thông bước 1 đã thực hiện trước ngày Thông tư này có hiệu lực thì việc lập, soát xét và thẩm định, phê duyệt tiếp tục được thực hiện theo quy định tại Điều 14 Thông tư số 03/2021/TT-BGTVT ngày 11 tháng 01 năm 2019 của Bộ trưởng Bộ Giao thông vận tải quy định về công tác phòng, chống và khắc phục hậu quả thiên tai trong lĩnh vực đường bộ.
+[amend] 22/2023/TT-BGTVT · hiệu lực 2023-08-15
+(không tìm được đoạn)</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -5690,7 +7295,6 @@
           <t>actor_has_transitional</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -5701,18 +7305,29 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P62" t="inlineStr"/>
-      <c r="Q62" t="inlineStr"/>
       <c r="R62" t="inlineStr">
         <is>
           <t>lineage thay thế 29/09; câu hỏi và đáp án ngắn do cùng model viết</t>
         </is>
       </c>
-      <c r="S62" t="inlineStr"/>
-      <c r="T62" t="inlineStr"/>
-      <c r="U62" t="inlineStr"/>
-      <c r="V62" t="inlineStr"/>
-      <c r="W62" t="inlineStr"/>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>03/2019/TT-BGTVT · hiệu lực 2019-03-28 → 2025-01-01 · lúc thu thập: Hết hiệu lực toàn bộ
+Điều 9. Chỉ đạo, chỉ huy ứng phó sự cố, thiên tai và tìm kiếm cứu nạn
+1. Căn cứ vào bản tin dự báo, cảnh báo thiên tai, các văn bản chỉ đạo của cấp trên, Tổng cục Đường bộ Việt Nam (đối với hệ thống quốc lộ), Sở Giao thông vận tải (đối với các hệ thống đường địa phương), trong phạm vi chức năng, nhiệm vụ được giao chỉ đạo, chỉ huy triển khai thực hiện biện pháp ứng phó sự cố, thiên tai và tìm kiếm cứu nạn trong lĩnh vực giao thông đường bộ.</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 43/2021/TT-BGTVT · hiệu lực 2022-03-01
+4. Sửa đổi khoản 1 Điều 9 như sau:
+“1. Căn cứ vào bản tin dự báo, cảnh báo thiên tai, các văn bản chỉ đạo của cấp trên, Tổng cục Đường bộ Việt Nam (đối với hệ thống quốc lộ), Sở Giao thông vận tải (đối với các hệ thống đường địa phương; tuyến, đoạn tuyến quốc lộ được giao quản lý), trong phạm vi chức năng, nhiệm vụ được giao chỉ đạo, chỉ huy triển khai thực hiện biện pháp ứng phó sự cố, thiên tai và tìm kiếm cứu nạn trong lĩnh vực giao thông đường bộ.”.
+CHUYỂN TIẾP: Điều 3. Điều khoản chuyển tiếp
+Đối với các công trình khắc phục hậu quả thiên tai, bảo đảm giao thông bước 1 đã thực hiện trước ngày Thông tư này có hiệu lực thì việc lập, soát xét và thẩm định, phê duyệt tiếp tục được thực hiện theo quy định tại Điều 14 Thông tư số 03/2021/TT-BGTVT ngày 11 tháng 01 năm 2019 của Bộ trưởng Bộ Giao thông vận tải quy định về công tác phòng, chống và khắc phục hậu quả thiên tai trong lĩnh vực đường bộ.
+[amend] 22/2023/TT-BGTVT · hiệu lực 2023-08-15
+(không tìm được đoạn)</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -5775,7 +7390,6 @@
           <t>actor_has_transitional</t>
         </is>
       </c>
-      <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -5786,18 +7400,29 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P63" t="inlineStr"/>
-      <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr">
         <is>
           <t>lineage thay thế 29/09; câu hỏi và đáp án ngắn do cùng model viết</t>
         </is>
       </c>
-      <c r="S63" t="inlineStr"/>
-      <c r="T63" t="inlineStr"/>
-      <c r="U63" t="inlineStr"/>
-      <c r="V63" t="inlineStr"/>
-      <c r="W63" t="inlineStr"/>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>03/2019/TT-BGTVT · hiệu lực 2019-03-28 → 2025-01-01 · lúc thu thập: Hết hiệu lực toàn bộ
+Điều 9. Chỉ đạo, chỉ huy ứng phó sự cố, thiên tai và tìm kiếm cứu nạn
+1. Căn cứ vào bản tin dự báo, cảnh báo thiên tai, các văn bản chỉ đạo của cấp trên, Tổng cục Đường bộ Việt Nam (đối với hệ thống quốc lộ), Sở Giao thông vận tải (đối với các hệ thống đường địa phương), trong phạm vi chức năng, nhiệm vụ được giao chỉ đạo, chỉ huy triển khai thực hiện biện pháp ứng phó sự cố, thiên tai và tìm kiếm cứu nạn trong lĩnh vực giao thông đường bộ.</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 43/2021/TT-BGTVT · hiệu lực 2022-03-01
+4. Sửa đổi khoản 1 Điều 9 như sau:
+“1. Căn cứ vào bản tin dự báo, cảnh báo thiên tai, các văn bản chỉ đạo của cấp trên, Tổng cục Đường bộ Việt Nam (đối với hệ thống quốc lộ), Sở Giao thông vận tải (đối với các hệ thống đường địa phương; tuyến, đoạn tuyến quốc lộ được giao quản lý), trong phạm vi chức năng, nhiệm vụ được giao chỉ đạo, chỉ huy triển khai thực hiện biện pháp ứng phó sự cố, thiên tai và tìm kiếm cứu nạn trong lĩnh vực giao thông đường bộ.”.
+CHUYỂN TIẾP: Điều 3. Điều khoản chuyển tiếp
+Đối với các công trình khắc phục hậu quả thiên tai, bảo đảm giao thông bước 1 đã thực hiện trước ngày Thông tư này có hiệu lực thì việc lập, soát xét và thẩm định, phê duyệt tiếp tục được thực hiện theo quy định tại Điều 14 Thông tư số 03/2021/TT-BGTVT ngày 11 tháng 01 năm 2019 của Bộ trưởng Bộ Giao thông vận tải quy định về công tác phòng, chống và khắc phục hậu quả thiên tai trong lĩnh vực đường bộ.
+[amend] 22/2023/TT-BGTVT · hiệu lực 2023-08-15
+(không tìm được đoạn)</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -5855,8 +7480,6 @@
           <t>10/2020/TT-NHNN; 16/2023/TT-NHNN</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -5867,18 +7490,51 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P64" t="inlineStr"/>
-      <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr">
         <is>
           <t>id cũ vilextime:T3:provision:938c3da8-eb99-11f0-b3df-b36a9bf88f4b:2016-02-02 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S64" t="inlineStr"/>
-      <c r="T64" t="inlineStr"/>
-      <c r="U64" t="inlineStr"/>
-      <c r="V64" t="inlineStr"/>
-      <c r="W64" t="inlineStr"/>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>28/2015/TT-NHNN · hiệu lực 2016-02-01 → 2026-03-01 · lúc thu thập: Hết hiệu lực toàn bộ
+Điều 10. Tạo khóa và phân phối khóa
+2. Trường hợp tự tạo cặp khóa, thuê bao phải tạo cặp khóa trước ngày hết hạn kích hoạt nêu tại thông báo cấp chứng thư số. Trường hợp thuê bao chưa tạo được cặp khóa trước ngày hết hạn kích hoạt, tổ chức quản lý thuê bao gửi Giấy đề nghị thay đổi mã kích hoạt trước ngày hết hạn kích hoạt tại thông báo cấp chứng thư số theo Mẫu biểu 08 gửi tổ chức cung cấp dịch vụ chữ ký số đề nghị gia hạn thời gian tạo khóa cho thuê bao. Trường hợp quá ngày hết hạn kích hoạt tại thông báo cấp chứng thư số, thuê bao có nhu cầu tiếp tục sử dụng chứng thư số thực hiện các thủ tục theo Điều 11 Thông tư này.</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 10/2020/TT-NHNN · hiệu lực 2021-01-01
+11.Khoản 2 Điều 10 được sửa đổi, bổ sung như sau:
+“2. Thuê bao phải tạo cặp khóa trước ngày hết hạn của mã kích hoạt nêu tại thông báo cấp chứng thư số. Trường hợp bị lộ, nghi bị lộ mã kích hoạt hoặc quá ngày hết hạn kích hoạt tại thông báo cấp chứng thư số, thuê bao chưa tạo được cặp khóa và có nhu cầu tiếp tục sử dụng chứng thư số, tổ chức quản lý thuê bao gửi 01 (một) bộ hồ sơ gồm Giấy đề nghị thay đổi mã kích hoạt chứng thư số theo Phụ lục 08 ban hành kèm theo Thông tư này.”
+12.Khoản 2, khoản 3 Điều 11 được sửa đổi, bổ sung như sau:
+“2. Tổ chức quản lý thuê bao gửi 01 (một) bộ hồ sơ đề nghị thay đổi cặp khóa gồm Giấy đề nghị thay đổi cặp khóa chứng thư số theo Phụ lục 07 ban hành kèm theo Thông tư này.
+3. Trong thời hạn 05 ngày làm việc kể từ ngày nhận được hồ sơ đề nghị thay đổi cặp khóa, Cục Công nghệ thông tin thực hiện kiểm tra hồ sơ, thay đổi cặp khóa, gửi thông báo thay đổi cặp khóa và mã kích hoạt chứng thư số đến địa chỉ thư điện tử và tin nhắn đến số điện thoại di động của thuê bao. Đối với chứng thư số cho tổ chức, Cục Công nghệ thông tin gửi thông báo thay đổi cặp khóa và mã kích hoạt chứng thư số đến địa chỉ thư điện tử và tin nhắn đến số điện thoại di động của cán bộ đầu mối phụ trách về chứng thư số của tổ chức quản lý thuê bao theo quy định tại khoản 1 Điều 14 Thông tư này.
+Trường hợp hồ sơ không hợp lệ, Cục Công nghệ thông tin từ chối xử lý hồ sơ và nêu rõ lý do. Thông tin phản hồi và kết quả xử lý hồ sơ được thực hiện theo quy định tại khoản 3 Điều 4a Thông tư này.
+Nhận được mã kích hoạt chứng thư số, thuê bao thực hiện kích hoạt chứng thư số để tạo cặp khóa mới trước thời điểm hết hiệu lực của mã kích hoạt theo tài liệu hướng dẫn kích hoạt, gia hạn chứng thư số được đăng tải trên Cổng thông tin điện tử Ngân hàng Nhà nước.”
+13.Điều 14 được sửa đổi, bổ sung như sau:
+“ Điều 14. Trách nhiệm của tổ chức quản lý thuê bao
+1. Chỉ định cá nhân hoặc bộ phận đầu mối phụ trách đăng ký, quản lý hồ sơ, văn bản, báo cáo liên quan đến chứng thư số, danh sách thuê bao của tổ chức; thông báo cho Cục Công nghệ thông tin lần đầu và khi có thay đổi cá nhân/bộ phận đầu mối.
+2. Đăng ký và chịu hoàn toàn trách nhiệm về tính chính xác của các thông tin tại văn bản, hồ sơ, báo cáo liên quan đến chứng thư số của thuê bao thuộc tổ chức quản lý gửi Cục Công nghệ thông tin.
+3. Quản lý, thống kê, cập nhật danh sách thuê bao trong tổ chức. Tối thiểu 6 tháng 1 lần, thực hiện rà soát, đối chiếu danh sách chứng thư số đã được Ngân hàng Nhà nước cấp so với nhu cầu sử dụng và thông tin thực tế tại tổ chức quản lý thuê bao. Các chứng thư số không khớp đúng thông tin, tổ chức quản lý thuê bao phải thực hiện ngay các thủ tục thay đổi thông tin, tạm dừng, thu hồi hoặc hủy bỏ nghiệp vụ chứng thư số.
+4. Báo cáo định kỳ và đột xuất theo quy định tại Thông tư này.
+5. Hướng dẫn, kiểm tra và tạo điều kiện cho các thuê bao thuộc tổ chức quản lý sử dụng chứng thư số và khoá bí mật theo đúng các quy định tại Thông tư này.
+6. Thông báo kịp thời cho Cục Công nghệ thông tin tạm dừng hoặc thu hồi chứng thư số của thuê bao trong các trường hợp:
+- Khóa bí mật của thuê bao nghi bị lộ, bị lộ, bị đánh cắp hoặc sử dụng trái phép;
+- Thiết bị lưu khóa bí mật của thuê bao bị thất lạc;
+- Thuê bao thay đổi vị trí công tác không cần sử dụng chứng thư số để phục vụ công việc;
+- Thuê bao tạm nghỉ việc, nghỉ việc, nghỉ hưu, từ trần;
+- Thuê bao thuộc chi nhánh/đơn vị của tổ chức quản lý thuê bao đã bị hủy mã ngân hàng;
+- Các trường hợp khác xuất phát từ nhu cầu của tổ chức quản lý thuê bao.
+7. Chứng thư số cấp cho tổ chức phải được giao cho cá nhân quản lý và sử dụng. Việc bàn giao phải được lập thành văn bản quy định rõ vai trò, trách nhiệm của cá nhân được giao quản lý. Cá nhân được giao quản lý phải thực hiện vai trò, trách nhiệm của thuê bao quy định tại Thông tư này.
+8. Tổ chức quản lý thuê bao là đơn vị hành chính thuộc Ngân hàng Nhà nước thu hồi kịp thời thiết bị lưu khóa bí mật của các thuê bao không còn sử dụng để sử dụng lại cho thuê bao khác.”
+14.Khoản 2 Điều 15 được sửa đổi, bổ sung như sau:
+“2. Bảo quản và sử dụng mã khoá truy cập thiết bị, các dữ liệu trong thiết bị lưu khoá bí mật một cách an toàn, bí mật trong suốt thời gian chứng thư số của mình có hiệu lực và bị tạm dừng; không chia sẻ, cho mượn mã khóa truy cập thiết bị, thiết bị lưu khóa bí mật của chứng thư số. Khi nghỉ việc, chuyển công tác hoặc thay đổi vị trí công tác, yêu cầu công việc không cần sử dụng chứng thư số phải bàn giao thiết bị lưu khóa bí mật cho tổ chức quản lý thuê bao.”
+[amend] 16/2023/TT-NHNN · hiệu lực 2024-07-01
+12. Sửa đổi, bổ sung khoản 2 Điều 10 Thông tư 28/2015/TT-NHNN (đã được sửa đổi, bổ sung bởi khoản 11 Điều 1 Thông tư 10/2020/TT-NHNN ) như sau:
+"2. Thuê bao phải tạo cặp khóa trước ngày hết hạn của mã kích hoạt nêu tại thông báo cấp chứng thư số. Trường hợp bị lộ, nghi bị lộ mã kích hoạt hoặc quá ngày hết hạn kích hoạt tại thông báo cấp chứng thư số, thuê bao chưa tạo được cặp khóa và có nhu cầu tiếp tục sử dụng chứng thư số, thực hiện thủ tục thay đổi mã kích hoạt chứng thư số theo Điều 10a Thông tư này."</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -5936,8 +7592,6 @@
           <t>10/2020/TT-NHNN; 16/2023/TT-NHNN</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -5948,18 +7602,51 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P65" t="inlineStr"/>
-      <c r="Q65" t="inlineStr"/>
       <c r="R65" t="inlineStr">
         <is>
           <t>id cũ vilextime:T3:provision:938c3da8-eb99-11f0-b3df-b36a9bf88f4b:2021-01-02 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S65" t="inlineStr"/>
-      <c r="T65" t="inlineStr"/>
-      <c r="U65" t="inlineStr"/>
-      <c r="V65" t="inlineStr"/>
-      <c r="W65" t="inlineStr"/>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>28/2015/TT-NHNN · hiệu lực 2016-02-01 → 2026-03-01 · lúc thu thập: Hết hiệu lực toàn bộ
+Điều 10. Tạo khóa và phân phối khóa
+2. Trường hợp tự tạo cặp khóa, thuê bao phải tạo cặp khóa trước ngày hết hạn kích hoạt nêu tại thông báo cấp chứng thư số. Trường hợp thuê bao chưa tạo được cặp khóa trước ngày hết hạn kích hoạt, tổ chức quản lý thuê bao gửi Giấy đề nghị thay đổi mã kích hoạt trước ngày hết hạn kích hoạt tại thông báo cấp chứng thư số theo Mẫu biểu 08 gửi tổ chức cung cấp dịch vụ chữ ký số đề nghị gia hạn thời gian tạo khóa cho thuê bao. Trường hợp quá ngày hết hạn kích hoạt tại thông báo cấp chứng thư số, thuê bao có nhu cầu tiếp tục sử dụng chứng thư số thực hiện các thủ tục theo Điều 11 Thông tư này.</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 10/2020/TT-NHNN · hiệu lực 2021-01-01
+11.Khoản 2 Điều 10 được sửa đổi, bổ sung như sau:
+“2. Thuê bao phải tạo cặp khóa trước ngày hết hạn của mã kích hoạt nêu tại thông báo cấp chứng thư số. Trường hợp bị lộ, nghi bị lộ mã kích hoạt hoặc quá ngày hết hạn kích hoạt tại thông báo cấp chứng thư số, thuê bao chưa tạo được cặp khóa và có nhu cầu tiếp tục sử dụng chứng thư số, tổ chức quản lý thuê bao gửi 01 (một) bộ hồ sơ gồm Giấy đề nghị thay đổi mã kích hoạt chứng thư số theo Phụ lục 08 ban hành kèm theo Thông tư này.”
+12.Khoản 2, khoản 3 Điều 11 được sửa đổi, bổ sung như sau:
+“2. Tổ chức quản lý thuê bao gửi 01 (một) bộ hồ sơ đề nghị thay đổi cặp khóa gồm Giấy đề nghị thay đổi cặp khóa chứng thư số theo Phụ lục 07 ban hành kèm theo Thông tư này.
+3. Trong thời hạn 05 ngày làm việc kể từ ngày nhận được hồ sơ đề nghị thay đổi cặp khóa, Cục Công nghệ thông tin thực hiện kiểm tra hồ sơ, thay đổi cặp khóa, gửi thông báo thay đổi cặp khóa và mã kích hoạt chứng thư số đến địa chỉ thư điện tử và tin nhắn đến số điện thoại di động của thuê bao. Đối với chứng thư số cho tổ chức, Cục Công nghệ thông tin gửi thông báo thay đổi cặp khóa và mã kích hoạt chứng thư số đến địa chỉ thư điện tử và tin nhắn đến số điện thoại di động của cán bộ đầu mối phụ trách về chứng thư số của tổ chức quản lý thuê bao theo quy định tại khoản 1 Điều 14 Thông tư này.
+Trường hợp hồ sơ không hợp lệ, Cục Công nghệ thông tin từ chối xử lý hồ sơ và nêu rõ lý do. Thông tin phản hồi và kết quả xử lý hồ sơ được thực hiện theo quy định tại khoản 3 Điều 4a Thông tư này.
+Nhận được mã kích hoạt chứng thư số, thuê bao thực hiện kích hoạt chứng thư số để tạo cặp khóa mới trước thời điểm hết hiệu lực của mã kích hoạt theo tài liệu hướng dẫn kích hoạt, gia hạn chứng thư số được đăng tải trên Cổng thông tin điện tử Ngân hàng Nhà nước.”
+13.Điều 14 được sửa đổi, bổ sung như sau:
+“ Điều 14. Trách nhiệm của tổ chức quản lý thuê bao
+1. Chỉ định cá nhân hoặc bộ phận đầu mối phụ trách đăng ký, quản lý hồ sơ, văn bản, báo cáo liên quan đến chứng thư số, danh sách thuê bao của tổ chức; thông báo cho Cục Công nghệ thông tin lần đầu và khi có thay đổi cá nhân/bộ phận đầu mối.
+2. Đăng ký và chịu hoàn toàn trách nhiệm về tính chính xác của các thông tin tại văn bản, hồ sơ, báo cáo liên quan đến chứng thư số của thuê bao thuộc tổ chức quản lý gửi Cục Công nghệ thông tin.
+3. Quản lý, thống kê, cập nhật danh sách thuê bao trong tổ chức. Tối thiểu 6 tháng 1 lần, thực hiện rà soát, đối chiếu danh sách chứng thư số đã được Ngân hàng Nhà nước cấp so với nhu cầu sử dụng và thông tin thực tế tại tổ chức quản lý thuê bao. Các chứng thư số không khớp đúng thông tin, tổ chức quản lý thuê bao phải thực hiện ngay các thủ tục thay đổi thông tin, tạm dừng, thu hồi hoặc hủy bỏ nghiệp vụ chứng thư số.
+4. Báo cáo định kỳ và đột xuất theo quy định tại Thông tư này.
+5. Hướng dẫn, kiểm tra và tạo điều kiện cho các thuê bao thuộc tổ chức quản lý sử dụng chứng thư số và khoá bí mật theo đúng các quy định tại Thông tư này.
+6. Thông báo kịp thời cho Cục Công nghệ thông tin tạm dừng hoặc thu hồi chứng thư số của thuê bao trong các trường hợp:
+- Khóa bí mật của thuê bao nghi bị lộ, bị lộ, bị đánh cắp hoặc sử dụng trái phép;
+- Thiết bị lưu khóa bí mật của thuê bao bị thất lạc;
+- Thuê bao thay đổi vị trí công tác không cần sử dụng chứng thư số để phục vụ công việc;
+- Thuê bao tạm nghỉ việc, nghỉ việc, nghỉ hưu, từ trần;
+- Thuê bao thuộc chi nhánh/đơn vị của tổ chức quản lý thuê bao đã bị hủy mã ngân hàng;
+- Các trường hợp khác xuất phát từ nhu cầu của tổ chức quản lý thuê bao.
+7. Chứng thư số cấp cho tổ chức phải được giao cho cá nhân quản lý và sử dụng. Việc bàn giao phải được lập thành văn bản quy định rõ vai trò, trách nhiệm của cá nhân được giao quản lý. Cá nhân được giao quản lý phải thực hiện vai trò, trách nhiệm của thuê bao quy định tại Thông tư này.
+8. Tổ chức quản lý thuê bao là đơn vị hành chính thuộc Ngân hàng Nhà nước thu hồi kịp thời thiết bị lưu khóa bí mật của các thuê bao không còn sử dụng để sử dụng lại cho thuê bao khác.”
+14.Khoản 2 Điều 15 được sửa đổi, bổ sung như sau:
+“2. Bảo quản và sử dụng mã khoá truy cập thiết bị, các dữ liệu trong thiết bị lưu khoá bí mật một cách an toàn, bí mật trong suốt thời gian chứng thư số của mình có hiệu lực và bị tạm dừng; không chia sẻ, cho mượn mã khóa truy cập thiết bị, thiết bị lưu khóa bí mật của chứng thư số. Khi nghỉ việc, chuyển công tác hoặc thay đổi vị trí công tác, yêu cầu công việc không cần sử dụng chứng thư số phải bàn giao thiết bị lưu khóa bí mật cho tổ chức quản lý thuê bao.”
+[amend] 16/2023/TT-NHNN · hiệu lực 2024-07-01
+12. Sửa đổi, bổ sung khoản 2 Điều 10 Thông tư 28/2015/TT-NHNN (đã được sửa đổi, bổ sung bởi khoản 11 Điều 1 Thông tư 10/2020/TT-NHNN ) như sau:
+"2. Thuê bao phải tạo cặp khóa trước ngày hết hạn của mã kích hoạt nêu tại thông báo cấp chứng thư số. Trường hợp bị lộ, nghi bị lộ mã kích hoạt hoặc quá ngày hết hạn kích hoạt tại thông báo cấp chứng thư số, thuê bao chưa tạo được cặp khóa và có nhu cầu tiếp tục sử dụng chứng thư số, thực hiện thủ tục thay đổi mã kích hoạt chứng thư số theo Điều 10a Thông tư này."</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -6017,8 +7704,6 @@
           <t>12/2018/TT-NHNN; 21/2015/TT-NHNN</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -6029,18 +7714,47 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P66" t="inlineStr"/>
-      <c r="Q66" t="inlineStr"/>
       <c r="R66" t="inlineStr">
         <is>
           <t>lineage thay thế 29/09; câu hỏi và đáp án ngắn do cùng model viết</t>
         </is>
       </c>
-      <c r="S66" t="inlineStr"/>
-      <c r="T66" t="inlineStr"/>
-      <c r="U66" t="inlineStr"/>
-      <c r="V66" t="inlineStr"/>
-      <c r="W66" t="inlineStr"/>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>22/2014/TT-NHNN · hiệu lực 2014-08-25 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 1. Phạm vi điều chỉnh và đối tượng áp dụng
+1. Phạm vi điều chỉnh:
+Thông tư này quy định việc cho vay đặt hàng đóng mới, nâng cấp tàu khai thác hải sản xa bờ, tàu dịch vụ hậu cần nghề cá; cho vay vốn lưu động để khai thác hải sản và cung cấp dịch vụ hậu cần khai thác hải sản xa bờ theo Nghị định số 67/2014/NĐ-CP ngày 07 tháng 7 năm 2014 của Chính phủ về một số chính sách phát triển thủy sản (sau đây gọi tắt là Nghị định số 67/2014/NĐ-CP).</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 21/2015/TT-NHNN · hiệu lực 2015-11-25
+1. Khoản 1 Điều 1 được sửa đổi, bổ sung như sau:
+"1. Phạm vi điều chỉnh:
+Thông tư này quy định việc cho vay đặt hàng đóng mới, nâng cấp tàu khai thác hải sản xa bờ, tàu dịch vụ hậu cần khai thác hải sản xa bờ; cho vay vốn lưu động để khai thác hải sản và cung cấp dịch vụ hậu cần khai thác hải sản xa bờ theo Nghị định số 67/2014/NĐ-CP ngày 07 tháng 7 năm 2014 của Chính phủ về một số chính sách phát triển thủy sản (sau đây gọi tắt là Nghị định số 67/2014/NĐ-CP ) và Nghị định số 89/2015/NĐ-CP ngày 07 tháng 10 năm 2015 của Chính phủ sửa đổi, bổ sung một số điều của Nghị định số 67/2014/NĐ-CP (sau đây gọi tắt là Nghị định số 89/2015/NĐ-CP )."
+2. Điểm a khoản 2 Điều 1 được sửa đổi, bổ sung như sau:
+"a) Chủ tàu theo quy định tại khoản 2 Điều 2 Nghị định số 67/2014/NĐ-CP (đã được sửa đổi, bổ sung bởi khoản 1 Điều 1 Nghị định số 89/2015/NĐ-CP )"
+3. Khoản 1 Điều 3 được sửa đổi, bổ sung như sau:
+"1. Cho vay để chủ tàu đặt hàng đóng mới, nâng cấp tàu khai thác hải sản xa bờ, tàu dịch vụ hậu cần khai thác hải sản xa bờ theo quy định tại điểm a khoản 1 Điều 4 Nghị định số 67/2014/NĐ-CP (đã được sửa đổi, bổ sung bởi khoản 2 Điều 1 Nghị định số 89/2015/NĐ-CP )."
+4. Khoản 1 Điều 5 được sửa đổi, bổ sung như sau:
+"1. Hạn mức, lãi suất cho vay được thực hiện theo quy định tại điểm e khoản 1, điểm c, điểm d khoản 3 Điều 4 Nghị định số 67/2014/NĐ-CP và điểm c khoản 1 Điều 4 Nghị định số 67/2014/NĐ-CP (đã được sửa đổi, bổ sung bởi khoản 3 Điều 1 Nghị định số 89/2015/NĐ-CP )."
+5. Điểm a khoản 4 Điều 5 được sửa đổi, bổ sung như sau:
+"a) Thời hạn cho vay hỗ trợ lãi suất đóng mới, nâng cấp tàu khai thác hải sản xa bờ, tàu dịch vụ hậu cần khai thác hải sản xa bờ được thực hiện theo quy định tại điểm d khoản 1 Điều 4 Nghị định số 67/2014/NĐ-CP (đã được sửa đổi, bổ sung bởi khoản 4 Điều 1 Nghị định số 89/2015/NĐ-CP )."
+[amend] 12/2018/TT-NHNN · hiệu lực 2018-04-27
+1. Khoản 1 Điều 1 được sửa đổi, bổ sung như sau:
+"1. Phạm vi điều chỉnh:
+Thông tư này quy định việc cho vay đặt hàng đóng mới, nâng cấp tàu khai thác hải sản xa bờ, tàu dịch vụ hậu cần khai thác hải sản xa bờ; cho vay vốn lưu động để khai thác hải sản xa bờ và cung cấp dịch vụ hậu cần khai thác hải sản xa bờ theo Nghị định số 67/2014/NĐ-CP ngày 07 tháng 7 năm 2014 của Chính phủ về một số chính sách phát triển thủy sản (sau đây gọi tắt là Nghị định số 67/2014/NĐ-CP ), Nghị định số 89/2015/NĐ-CP ngày 07 tháng 10 năm 2015 của Chính phủ sửa đổi, bổ sung một số điều của Nghị định số 67/2014/NĐ-CP (sau đây gọi tắt là Nghị định số 89/2015/NĐ-CP ) và Nghị định số 17/2018/NĐ-CP ngày 02 tháng 02 năm 2018 của Chính phủ sửa đổi, bổ sung một số điều của Nghị định số 67/2014/NĐ-CP (sau đây gọi tắt là Nghị định số 17/2018/NĐ-CP )."
+2. Khoản 2 Điều 3 được sửa đổi như sau:
+"2. Cho vay vốn lưu động đối với chủ tàu khai thác hải sản xa bờ và chủ tàu dịch vụ hậu cần khai thác hải sản xa bờ theo quy định tại khoản 3 Điều 4 Nghị định số 67/2014/NĐ-CP (đã được sửa đổi bởi khoản 4 Điều 1 Nghị định số 17/2018/NĐ-CP )."
+3. Khoản 2 Điều 4 được sửa đổi như sau:
+"2. Đối với cho vay vốn lưu động:Chủ tàu vay vốn lưu động đáp ứng các quy định của pháp luật hiện hành về hoạt động cho vay của tổ chức tín dụng đối với khách hàng trong lĩnh vực nông nghiệp, nông thôn."
+4. Khoản 1 Điều 5 được sửa đổi như sau:
+"1. Hạn mức, lãi suất cho vay được thực hiện theo quy định tại điểm e, điểm c khoản 1 Điều 4 Nghị định số 67/2014/NĐ-CP (đã được sửa đổi, bổ sung bởi khoản 3 Điều 1 Nghị định số 89/2015/NĐ-CP )."
+5. Khoản 1 Điều 7 được sửa đổi như sau:
+"1. Việc phân loại nợ, trích lập dự phòng rủi ro và sử dụng dự phòng để xử lý rủi ro thực hiện theo quy định hiện hành, bao gồm khoản nợ vay của chủ tàu mới khi nhận bàn giao từ chủ tàu cũ theo cơ chế chuyển đổi chủ tàu quy định tại khoản 3 Điều 1 Nghị định số 17/2018/NĐ-CP ."</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -6098,8 +7812,6 @@
           <t>12/2018/TT-NHNN; 21/2015/TT-NHNN</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -6110,18 +7822,47 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P67" t="inlineStr"/>
-      <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr">
         <is>
           <t>lineage thay thế 29/09; câu hỏi và đáp án ngắn do cùng model viết</t>
         </is>
       </c>
-      <c r="S67" t="inlineStr"/>
-      <c r="T67" t="inlineStr"/>
-      <c r="U67" t="inlineStr"/>
-      <c r="V67" t="inlineStr"/>
-      <c r="W67" t="inlineStr"/>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>22/2014/TT-NHNN · hiệu lực 2014-08-25 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 1. Phạm vi điều chỉnh và đối tượng áp dụng
+1. Phạm vi điều chỉnh:
+Thông tư này quy định việc cho vay đặt hàng đóng mới, nâng cấp tàu khai thác hải sản xa bờ, tàu dịch vụ hậu cần nghề cá; cho vay vốn lưu động để khai thác hải sản và cung cấp dịch vụ hậu cần khai thác hải sản xa bờ theo Nghị định số 67/2014/NĐ-CP ngày 07 tháng 7 năm 2014 của Chính phủ về một số chính sách phát triển thủy sản (sau đây gọi tắt là Nghị định số 67/2014/NĐ-CP).</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 21/2015/TT-NHNN · hiệu lực 2015-11-25
+1. Khoản 1 Điều 1 được sửa đổi, bổ sung như sau:
+"1. Phạm vi điều chỉnh:
+Thông tư này quy định việc cho vay đặt hàng đóng mới, nâng cấp tàu khai thác hải sản xa bờ, tàu dịch vụ hậu cần khai thác hải sản xa bờ; cho vay vốn lưu động để khai thác hải sản và cung cấp dịch vụ hậu cần khai thác hải sản xa bờ theo Nghị định số 67/2014/NĐ-CP ngày 07 tháng 7 năm 2014 của Chính phủ về một số chính sách phát triển thủy sản (sau đây gọi tắt là Nghị định số 67/2014/NĐ-CP ) và Nghị định số 89/2015/NĐ-CP ngày 07 tháng 10 năm 2015 của Chính phủ sửa đổi, bổ sung một số điều của Nghị định số 67/2014/NĐ-CP (sau đây gọi tắt là Nghị định số 89/2015/NĐ-CP )."
+2. Điểm a khoản 2 Điều 1 được sửa đổi, bổ sung như sau:
+"a) Chủ tàu theo quy định tại khoản 2 Điều 2 Nghị định số 67/2014/NĐ-CP (đã được sửa đổi, bổ sung bởi khoản 1 Điều 1 Nghị định số 89/2015/NĐ-CP )"
+3. Khoản 1 Điều 3 được sửa đổi, bổ sung như sau:
+"1. Cho vay để chủ tàu đặt hàng đóng mới, nâng cấp tàu khai thác hải sản xa bờ, tàu dịch vụ hậu cần khai thác hải sản xa bờ theo quy định tại điểm a khoản 1 Điều 4 Nghị định số 67/2014/NĐ-CP (đã được sửa đổi, bổ sung bởi khoản 2 Điều 1 Nghị định số 89/2015/NĐ-CP )."
+4. Khoản 1 Điều 5 được sửa đổi, bổ sung như sau:
+"1. Hạn mức, lãi suất cho vay được thực hiện theo quy định tại điểm e khoản 1, điểm c, điểm d khoản 3 Điều 4 Nghị định số 67/2014/NĐ-CP và điểm c khoản 1 Điều 4 Nghị định số 67/2014/NĐ-CP (đã được sửa đổi, bổ sung bởi khoản 3 Điều 1 Nghị định số 89/2015/NĐ-CP )."
+5. Điểm a khoản 4 Điều 5 được sửa đổi, bổ sung như sau:
+"a) Thời hạn cho vay hỗ trợ lãi suất đóng mới, nâng cấp tàu khai thác hải sản xa bờ, tàu dịch vụ hậu cần khai thác hải sản xa bờ được thực hiện theo quy định tại điểm d khoản 1 Điều 4 Nghị định số 67/2014/NĐ-CP (đã được sửa đổi, bổ sung bởi khoản 4 Điều 1 Nghị định số 89/2015/NĐ-CP )."
+[amend] 12/2018/TT-NHNN · hiệu lực 2018-04-27
+1. Khoản 1 Điều 1 được sửa đổi, bổ sung như sau:
+"1. Phạm vi điều chỉnh:
+Thông tư này quy định việc cho vay đặt hàng đóng mới, nâng cấp tàu khai thác hải sản xa bờ, tàu dịch vụ hậu cần khai thác hải sản xa bờ; cho vay vốn lưu động để khai thác hải sản xa bờ và cung cấp dịch vụ hậu cần khai thác hải sản xa bờ theo Nghị định số 67/2014/NĐ-CP ngày 07 tháng 7 năm 2014 của Chính phủ về một số chính sách phát triển thủy sản (sau đây gọi tắt là Nghị định số 67/2014/NĐ-CP ), Nghị định số 89/2015/NĐ-CP ngày 07 tháng 10 năm 2015 của Chính phủ sửa đổi, bổ sung một số điều của Nghị định số 67/2014/NĐ-CP (sau đây gọi tắt là Nghị định số 89/2015/NĐ-CP ) và Nghị định số 17/2018/NĐ-CP ngày 02 tháng 02 năm 2018 của Chính phủ sửa đổi, bổ sung một số điều của Nghị định số 67/2014/NĐ-CP (sau đây gọi tắt là Nghị định số 17/2018/NĐ-CP )."
+2. Khoản 2 Điều 3 được sửa đổi như sau:
+"2. Cho vay vốn lưu động đối với chủ tàu khai thác hải sản xa bờ và chủ tàu dịch vụ hậu cần khai thác hải sản xa bờ theo quy định tại khoản 3 Điều 4 Nghị định số 67/2014/NĐ-CP (đã được sửa đổi bởi khoản 4 Điều 1 Nghị định số 17/2018/NĐ-CP )."
+3. Khoản 2 Điều 4 được sửa đổi như sau:
+"2. Đối với cho vay vốn lưu động:Chủ tàu vay vốn lưu động đáp ứng các quy định của pháp luật hiện hành về hoạt động cho vay của tổ chức tín dụng đối với khách hàng trong lĩnh vực nông nghiệp, nông thôn."
+4. Khoản 1 Điều 5 được sửa đổi như sau:
+"1. Hạn mức, lãi suất cho vay được thực hiện theo quy định tại điểm e, điểm c khoản 1 Điều 4 Nghị định số 67/2014/NĐ-CP (đã được sửa đổi, bổ sung bởi khoản 3 Điều 1 Nghị định số 89/2015/NĐ-CP )."
+5. Khoản 1 Điều 7 được sửa đổi như sau:
+"1. Việc phân loại nợ, trích lập dự phòng rủi ro và sử dụng dự phòng để xử lý rủi ro thực hiện theo quy định hiện hành, bao gồm khoản nợ vay của chủ tàu mới khi nhận bàn giao từ chủ tàu cũ theo cơ chế chuyển đổi chủ tàu quy định tại khoản 3 Điều 1 Nghị định số 17/2018/NĐ-CP ."</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -6179,8 +7920,6 @@
           <t>12/2018/TT-NHNN; 21/2015/TT-NHNN</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -6191,18 +7930,47 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P68" t="inlineStr"/>
-      <c r="Q68" t="inlineStr"/>
       <c r="R68" t="inlineStr">
         <is>
           <t>lineage thay thế 29/09; câu hỏi và đáp án ngắn do cùng model viết</t>
         </is>
       </c>
-      <c r="S68" t="inlineStr"/>
-      <c r="T68" t="inlineStr"/>
-      <c r="U68" t="inlineStr"/>
-      <c r="V68" t="inlineStr"/>
-      <c r="W68" t="inlineStr"/>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>22/2014/TT-NHNN · hiệu lực 2014-08-25 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 1. Phạm vi điều chỉnh và đối tượng áp dụng
+1. Phạm vi điều chỉnh:
+Thông tư này quy định việc cho vay đặt hàng đóng mới, nâng cấp tàu khai thác hải sản xa bờ, tàu dịch vụ hậu cần nghề cá; cho vay vốn lưu động để khai thác hải sản và cung cấp dịch vụ hậu cần khai thác hải sản xa bờ theo Nghị định số 67/2014/NĐ-CP ngày 07 tháng 7 năm 2014 của Chính phủ về một số chính sách phát triển thủy sản (sau đây gọi tắt là Nghị định số 67/2014/NĐ-CP).</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 21/2015/TT-NHNN · hiệu lực 2015-11-25
+1. Khoản 1 Điều 1 được sửa đổi, bổ sung như sau:
+"1. Phạm vi điều chỉnh:
+Thông tư này quy định việc cho vay đặt hàng đóng mới, nâng cấp tàu khai thác hải sản xa bờ, tàu dịch vụ hậu cần khai thác hải sản xa bờ; cho vay vốn lưu động để khai thác hải sản và cung cấp dịch vụ hậu cần khai thác hải sản xa bờ theo Nghị định số 67/2014/NĐ-CP ngày 07 tháng 7 năm 2014 của Chính phủ về một số chính sách phát triển thủy sản (sau đây gọi tắt là Nghị định số 67/2014/NĐ-CP ) và Nghị định số 89/2015/NĐ-CP ngày 07 tháng 10 năm 2015 của Chính phủ sửa đổi, bổ sung một số điều của Nghị định số 67/2014/NĐ-CP (sau đây gọi tắt là Nghị định số 89/2015/NĐ-CP )."
+2. Điểm a khoản 2 Điều 1 được sửa đổi, bổ sung như sau:
+"a) Chủ tàu theo quy định tại khoản 2 Điều 2 Nghị định số 67/2014/NĐ-CP (đã được sửa đổi, bổ sung bởi khoản 1 Điều 1 Nghị định số 89/2015/NĐ-CP )"
+3. Khoản 1 Điều 3 được sửa đổi, bổ sung như sau:
+"1. Cho vay để chủ tàu đặt hàng đóng mới, nâng cấp tàu khai thác hải sản xa bờ, tàu dịch vụ hậu cần khai thác hải sản xa bờ theo quy định tại điểm a khoản 1 Điều 4 Nghị định số 67/2014/NĐ-CP (đã được sửa đổi, bổ sung bởi khoản 2 Điều 1 Nghị định số 89/2015/NĐ-CP )."
+4. Khoản 1 Điều 5 được sửa đổi, bổ sung như sau:
+"1. Hạn mức, lãi suất cho vay được thực hiện theo quy định tại điểm e khoản 1, điểm c, điểm d khoản 3 Điều 4 Nghị định số 67/2014/NĐ-CP và điểm c khoản 1 Điều 4 Nghị định số 67/2014/NĐ-CP (đã được sửa đổi, bổ sung bởi khoản 3 Điều 1 Nghị định số 89/2015/NĐ-CP )."
+5. Điểm a khoản 4 Điều 5 được sửa đổi, bổ sung như sau:
+"a) Thời hạn cho vay hỗ trợ lãi suất đóng mới, nâng cấp tàu khai thác hải sản xa bờ, tàu dịch vụ hậu cần khai thác hải sản xa bờ được thực hiện theo quy định tại điểm d khoản 1 Điều 4 Nghị định số 67/2014/NĐ-CP (đã được sửa đổi, bổ sung bởi khoản 4 Điều 1 Nghị định số 89/2015/NĐ-CP )."
+[amend] 12/2018/TT-NHNN · hiệu lực 2018-04-27
+1. Khoản 1 Điều 1 được sửa đổi, bổ sung như sau:
+"1. Phạm vi điều chỉnh:
+Thông tư này quy định việc cho vay đặt hàng đóng mới, nâng cấp tàu khai thác hải sản xa bờ, tàu dịch vụ hậu cần khai thác hải sản xa bờ; cho vay vốn lưu động để khai thác hải sản xa bờ và cung cấp dịch vụ hậu cần khai thác hải sản xa bờ theo Nghị định số 67/2014/NĐ-CP ngày 07 tháng 7 năm 2014 của Chính phủ về một số chính sách phát triển thủy sản (sau đây gọi tắt là Nghị định số 67/2014/NĐ-CP ), Nghị định số 89/2015/NĐ-CP ngày 07 tháng 10 năm 2015 của Chính phủ sửa đổi, bổ sung một số điều của Nghị định số 67/2014/NĐ-CP (sau đây gọi tắt là Nghị định số 89/2015/NĐ-CP ) và Nghị định số 17/2018/NĐ-CP ngày 02 tháng 02 năm 2018 của Chính phủ sửa đổi, bổ sung một số điều của Nghị định số 67/2014/NĐ-CP (sau đây gọi tắt là Nghị định số 17/2018/NĐ-CP )."
+2. Khoản 2 Điều 3 được sửa đổi như sau:
+"2. Cho vay vốn lưu động đối với chủ tàu khai thác hải sản xa bờ và chủ tàu dịch vụ hậu cần khai thác hải sản xa bờ theo quy định tại khoản 3 Điều 4 Nghị định số 67/2014/NĐ-CP (đã được sửa đổi bởi khoản 4 Điều 1 Nghị định số 17/2018/NĐ-CP )."
+3. Khoản 2 Điều 4 được sửa đổi như sau:
+"2. Đối với cho vay vốn lưu động:Chủ tàu vay vốn lưu động đáp ứng các quy định của pháp luật hiện hành về hoạt động cho vay của tổ chức tín dụng đối với khách hàng trong lĩnh vực nông nghiệp, nông thôn."
+4. Khoản 1 Điều 5 được sửa đổi như sau:
+"1. Hạn mức, lãi suất cho vay được thực hiện theo quy định tại điểm e, điểm c khoản 1 Điều 4 Nghị định số 67/2014/NĐ-CP (đã được sửa đổi, bổ sung bởi khoản 3 Điều 1 Nghị định số 89/2015/NĐ-CP )."
+5. Khoản 1 Điều 7 được sửa đổi như sau:
+"1. Việc phân loại nợ, trích lập dự phòng rủi ro và sử dụng dự phòng để xử lý rủi ro thực hiện theo quy định hiện hành, bao gồm khoản nợ vay của chủ tàu mới khi nhận bàn giao từ chủ tàu cũ theo cơ chế chuyển đổi chủ tàu quy định tại khoản 3 Điều 1 Nghị định số 17/2018/NĐ-CP ."</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -6260,8 +8028,6 @@
           <t>08/2022/TT-BGTVT; 48/2018/TT-BGTVT</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -6272,18 +8038,28 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P69" t="inlineStr"/>
-      <c r="Q69" t="inlineStr"/>
       <c r="R69" t="inlineStr">
         <is>
           <t>id cũ vilextime:T3:provision:96eb9928-2c7e-11f1-82dd-c36c58de53fd:2017-07-02 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S69" t="inlineStr"/>
-      <c r="T69" t="inlineStr"/>
-      <c r="U69" t="inlineStr"/>
-      <c r="V69" t="inlineStr"/>
-      <c r="W69" t="inlineStr"/>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>50/2016/TT-BGTVT · hiệu lực 2017-07-01 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 6. Hồ sơ đề nghị cấp Giấy phép vận tải biển nội địa
+4. 01 (một) bản sao có công chứng Hợp đồng đại lý hoặc 01 (một) bản sao có chứng thực giấy chỉ định đại lý đại diện cho chủ tàu nước ngoài (trong trường hợp tổ chức đề nghị là đại lý đại diện cho chủ tàu nước ngoài) hoặc 01 (một) bản sao có công chứng Hợp đồng thuê tàu giữa chủ tàu nước ngoài với pháp nhân Việt Nam.</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 48/2018/TT-BGTVT · hiệu lực 2018-11-09
+1. Sửa đổi khoản 4 Điều 6 như sau:
+"4. 01 (một) bản sao từ sổ gốc hoặc bản sao và xuất trình bản chính để đối chiếu hoặc bản sao có chứng thực (đối với trường hợp nộp hồ sơ trực tiếp), bản sao có chứng thực (đối với trường hợp nộp hồ sơ qua bưu điện) một trong các loại giấy tờ sau: Hợp đồng đại lý hoặc Giấy chỉ định đại lý đại diện cho chủ tàu nước ngoài (trong trường hợp tổ chức đề nghị là đại lý đại diện cho chủ tàu nước ngoài) hoặc Hợp đồng thuê tàu giữa chủ tàu nước ngoài với pháp nhân Việt Nam".
+[amend] 08/2022/TT-BGTVT · hiệu lực 2022-06-16
+1. Sửa đổi, bổ sung khoản 4 Điều 6 như sau:
+“4. 01 (một) bản sao từ sổ gốc hoặc bản sao và xuất trình bản chính để đối chiếu hoặc bản sao điện tử có giá trị pháp lý do cơ quan có thẩm quyền cấp một trong các loại giấy tờ sau: Hợp đồng đại lý hoặc Giấy chỉ định đại lý đại diện cho chủ tàu nước ngoài (trong trường hợp tổ chức đề nghị là đại lý đại diện cho chủ tàu nước ngoài) hoặc Hợp đồng thuê tàu giữa chủ tàu nước ngoài với pháp nhân Việt Nam.”.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -6341,7 +8117,6 @@
           <t>05/2025/TT-NHNN; 12/2017/TT-NHNN; 19/2021/TT-NHNN</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
           <t>missed_event 2023-11-27 bao_dong_gia</t>
@@ -6357,18 +8132,37 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P70" t="inlineStr"/>
-      <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr">
         <is>
           <t>Bốn đáp án khác nhau (thêm ngoại lệ, thêm ngưỡng mệnh giá, đổi chi nhánh thành Khu vực); id cũ vilextime:T3:provision:9fdf6804-2d53-11f1-ad2a-cf0eedd8b394:2014-02-21 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S70" t="inlineStr"/>
-      <c r="T70" t="inlineStr"/>
-      <c r="U70" t="inlineStr"/>
-      <c r="V70" t="inlineStr"/>
-      <c r="W70" t="inlineStr"/>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>01/2014/TT-NHNN · hiệu lực 2014-02-20 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 11. Giao nhận tiền mặt trong ngành Ngân hàng
+1. Giao nhận tiền mặt theo bó tiền đủ 10 thếp, nguyên niêm phong hoặc túi tiền nguyên niêm phong kẹp chì trong các trường hợp:
+a) Giao nhận tiền mặt trong nội bộ Sở Giao dịch, Ngân hàng Nhà nước chi nhánh đối với tiền đã qua lưu thông (trừ trường hợp quy định tại điểm c Khoản 2 Điều này);
+b) Giao nhận tiền mặt theo lệnh điều chuyển giữa kho tiền Trung ương với Sở Giao dịch, Ngân hàng Nhà nước chi nhánh và ngược lại; giữa các kho tiền Trung ương với nhau; giữa các Ngân hàng Nhà nước chi nhánh với nhau;
+c) Giao nhận tiền mặt giữa Sở Giao dịch, Ngân hàng Nhà nước chi nhánh với tổ chức tín dụng, chi nhánh ngân hàng nước ngoài và ngược lại; giữa các tổ chức tín dụng, chi nhánh ngân hàng nước ngoài trên địa bàn tỉnh, thành phố với nhau.</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 12/2017/TT-NHNN · hiệu lực 2017-10-16
+1. Điểm a, b khoản 1 Điều 11 được sửa đổi, bổ sung như sau:
+"a) Giao nhận tiền mặt trong nội bộ Sở Giao dịch, Ngân hàng Nhà nước chi nhánh đối với tiền đã qua lưu thông, trừ trường hợp quy định tại điểm c, đ khoản 2 Điều này;
+b) Giao nhận tiền mặt theo lệnh điều chuyển giữa kho tiền Trung ương với Sở Giao dịch, Ngân hàng Nhà nước chi nhánh và ngược lại; giữa các kho tiền Trung ương với nhau; giữa các Ngân hàng Nhà nước chi nhánh với nhau, trừ trường hợp quy định tại điểm d khoản 2 Điều này;"
+[amend] 19/2021/TT-NHNN · hiệu lực 2022-01-08
+1. Sửa đổi, bổ sung khoản 1 Điều 11 như sau:
+"1. Giao nhận tiền mặt theo bó tiền đủ 10 thếp nguyên niêm phong hoặc túi tiền nguyên niêm phong trong các trường hợp:
+a) Giao nhận tiền mặt trong nội bộ Sở Giao dịch, Ngân hàng Nhà nước chi nhánh đối với tiền đã qua lưu thông, trừ trường hợp quy định tại điểm c, g khoản 2 Điều này;
+b) Giao nhận tiền mặt loại mệnh giá từ 50.000 đồng trở lên theo lệnh điều chuyển giữa kho tiền Trung ương với Sở Giao dịch, Ngân hàng Nhà nước chi nhánh và ngược lại; giữa các kho tiền Trung ương với nhau; giữa các Ngân hàng Nhà nước chi nhánh với nhau, trừ trường hợp quy định tại điểm đ khoản 2 Điều này;
+c) Giao nhận tiền mặt giữa Sở Giao dịch, Ngân hàng Nhà nước chi nhánh với tổ chức tín dụng, chi nhánh ngân hàng nước ngoài và ngược lại; giữa các tổ chức tín dụng, chi nhánh ngân hàng nước ngoài trên địa bàn tỉnh, thành phố với nhau."
+[amend] 05/2025/TT-NHNN · hiệu lực 2025-05-19
+2. Thay thế cụm từ "Ngân hàng Nhà nước chi nhánh" bằng cụm từ "Ngân hàng Nhà nước Khu vực" quy định tại khoản 1 và điểm c khoản 2 Điều 11, khoản 1 và điểm a, điểm b khoản 2 Điều 13, Điều 14, khoản 1 Điều 15, khoản 1 Điều 17, khoản 2 Điều 18, khoản 1 và khoản 2 Điều 19, khoản 1 Điều 20, tên Điều 21, khoản 1 Điều 24, khoản 1 Điều 31, khoản 2 Điều 37, khoản 4 Điều 39, khoản 2 Điều 45, khoản 4 Điều 50, Điều 53, khoản 3 Điều 59, khoản 2 Điều 65, Điều 69.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -6426,7 +8220,6 @@
           <t>05/2025/TT-NHNN; 12/2017/TT-NHNN; 19/2021/TT-NHNN</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
           <t>missed_event 2023-11-27 bao_dong_gia</t>
@@ -6442,18 +8235,37 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P71" t="inlineStr"/>
-      <c r="Q71" t="inlineStr"/>
       <c r="R71" t="inlineStr">
         <is>
           <t>Bốn đáp án khác nhau (thêm ngoại lệ, thêm ngưỡng mệnh giá, đổi chi nhánh thành Khu vực); id cũ vilextime:T3:provision:9fdf6804-2d53-11f1-ad2a-cf0eedd8b394:2025-05-20 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S71" t="inlineStr"/>
-      <c r="T71" t="inlineStr"/>
-      <c r="U71" t="inlineStr"/>
-      <c r="V71" t="inlineStr"/>
-      <c r="W71" t="inlineStr"/>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>01/2014/TT-NHNN · hiệu lực 2014-02-20 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 11. Giao nhận tiền mặt trong ngành Ngân hàng
+1. Giao nhận tiền mặt theo bó tiền đủ 10 thếp, nguyên niêm phong hoặc túi tiền nguyên niêm phong kẹp chì trong các trường hợp:
+a) Giao nhận tiền mặt trong nội bộ Sở Giao dịch, Ngân hàng Nhà nước chi nhánh đối với tiền đã qua lưu thông (trừ trường hợp quy định tại điểm c Khoản 2 Điều này);
+b) Giao nhận tiền mặt theo lệnh điều chuyển giữa kho tiền Trung ương với Sở Giao dịch, Ngân hàng Nhà nước chi nhánh và ngược lại; giữa các kho tiền Trung ương với nhau; giữa các Ngân hàng Nhà nước chi nhánh với nhau;
+c) Giao nhận tiền mặt giữa Sở Giao dịch, Ngân hàng Nhà nước chi nhánh với tổ chức tín dụng, chi nhánh ngân hàng nước ngoài và ngược lại; giữa các tổ chức tín dụng, chi nhánh ngân hàng nước ngoài trên địa bàn tỉnh, thành phố với nhau.</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 12/2017/TT-NHNN · hiệu lực 2017-10-16
+1. Điểm a, b khoản 1 Điều 11 được sửa đổi, bổ sung như sau:
+"a) Giao nhận tiền mặt trong nội bộ Sở Giao dịch, Ngân hàng Nhà nước chi nhánh đối với tiền đã qua lưu thông, trừ trường hợp quy định tại điểm c, đ khoản 2 Điều này;
+b) Giao nhận tiền mặt theo lệnh điều chuyển giữa kho tiền Trung ương với Sở Giao dịch, Ngân hàng Nhà nước chi nhánh và ngược lại; giữa các kho tiền Trung ương với nhau; giữa các Ngân hàng Nhà nước chi nhánh với nhau, trừ trường hợp quy định tại điểm d khoản 2 Điều này;"
+[amend] 19/2021/TT-NHNN · hiệu lực 2022-01-08
+1. Sửa đổi, bổ sung khoản 1 Điều 11 như sau:
+"1. Giao nhận tiền mặt theo bó tiền đủ 10 thếp nguyên niêm phong hoặc túi tiền nguyên niêm phong trong các trường hợp:
+a) Giao nhận tiền mặt trong nội bộ Sở Giao dịch, Ngân hàng Nhà nước chi nhánh đối với tiền đã qua lưu thông, trừ trường hợp quy định tại điểm c, g khoản 2 Điều này;
+b) Giao nhận tiền mặt loại mệnh giá từ 50.000 đồng trở lên theo lệnh điều chuyển giữa kho tiền Trung ương với Sở Giao dịch, Ngân hàng Nhà nước chi nhánh và ngược lại; giữa các kho tiền Trung ương với nhau; giữa các Ngân hàng Nhà nước chi nhánh với nhau, trừ trường hợp quy định tại điểm đ khoản 2 Điều này;
+c) Giao nhận tiền mặt giữa Sở Giao dịch, Ngân hàng Nhà nước chi nhánh với tổ chức tín dụng, chi nhánh ngân hàng nước ngoài và ngược lại; giữa các tổ chức tín dụng, chi nhánh ngân hàng nước ngoài trên địa bàn tỉnh, thành phố với nhau."
+[amend] 05/2025/TT-NHNN · hiệu lực 2025-05-19
+2. Thay thế cụm từ "Ngân hàng Nhà nước chi nhánh" bằng cụm từ "Ngân hàng Nhà nước Khu vực" quy định tại khoản 1 và điểm c khoản 2 Điều 11, khoản 1 và điểm a, điểm b khoản 2 Điều 13, Điều 14, khoản 1 Điều 15, khoản 1 Điều 17, khoản 2 Điều 18, khoản 1 và khoản 2 Điều 19, khoản 1 Điều 20, tên Điều 21, khoản 1 Điều 24, khoản 1 Điều 31, khoản 2 Điều 37, khoản 4 Điều 39, khoản 2 Điều 45, khoản 4 Điều 50, Điều 53, khoản 3 Điều 59, khoản 2 Điều 65, Điều 69.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -6481,7 +8293,6 @@
           <t>2026-02-18 (giua_khoang)</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr">
         <is>
           <t>Điều 7. Hoàn trả phí 1. Tổ chức, cá nhân ngừng sử dụng tần số vô tuyến điện trước thời hạn quy định tại giấy phép sử dụng tần số vô tuyến điện được hoàn trả phần phí sử dụng tần số vô tuyến điện đã nộp cho thời gian còn lại của giấy phép (làm tròn theo tháng) theo quy định của pháp luật trong trường hợp giấy phép được cấp không gắn với cam kết triển khai mạng viễn thông và thời gian còn lại của giấy phép từ 30 ngày trở lên kể từ cơ quan nhà nước có thẩm quyền cấp giấy phép sử dụng tần số vô tuyến điện nhận được văn bản đề nghị của tổ chức, cá nhân. 2. Thời gian còn lại của giấy phép để tính số phí được hoàn trả được tính kể từ ngày tổ chức, cá nhân chính thức ngừng sử dụng nhưng không trước ngày cơ quan nhà nước có thẩm quyền cấp giấy phép sử dụng tần số vô tuyến điện nhận được văn bản đề nghị của tổ chức, cá nhân.</t>
@@ -6507,8 +8318,6 @@
           <t>11/2022/TT-BTC; 65/2025/TT-BTС</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -6519,18 +8328,35 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P72" t="inlineStr"/>
-      <c r="Q72" t="inlineStr"/>
       <c r="R72" t="inlineStr">
         <is>
           <t>id cũ vilextime:T3:provision:a3e3a25a-ec3d-11f0-ab79-a33691076a8e:2025-07-02 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S72" t="inlineStr"/>
-      <c r="T72" t="inlineStr"/>
-      <c r="U72" t="inlineStr"/>
-      <c r="V72" t="inlineStr"/>
-      <c r="W72" t="inlineStr"/>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>265/2016/TT-BTC · hiệu lực 2017-01-01 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 7. Hoàn trả phí
+Tổ chức, cá nhân ngừng sử dụng tần số và thiết bị vô tuyến điện trước thời hạn quy định tại giấy phép sử dụng tần số vô tuyến điện thì chỉ được hoàn trả phần phí sử dụng tần số vô tuyến điện cho thời gian còn lại của giấy phép nếu thời gian còn lại này từ 90 ngày trở lên.
+Thời gian còn lại của giấy phép được tính kể từ ngày tổ chức, cá nhân chính thức ngừng sử dụng nhưng không trước ngày Cục Tần số vô tuyến điện nhận được thông báo ngừng.</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 11/2022/TT-BTC · hiệu lực 2022-05-01
+4. Sửa đổi, bổ sung Điều 7 như sau:
+" Điều 7. Hoàn trả phí
+1. Tổ chức, cá nhân ngừng sử dụng tần số và thiết bị vô tuyến điện trước thời hạn quy định tại giấy phép sử dụng tần số vô tuyến điện thì chỉ được hoàn trả phần phí sử dụng tần số vô tuyến điện cho thời gian còn lại của giấy phép, trong trường hợp sau:
+a) Thời gian còn lại của giấy phép từ 30 ngày trở lên đối với giấy phép sử dụng tần số ngừng do đấu giá tần số hoặc thay đổi của quy hoạch tần số.
+b) Thời gian còn lại của giấy phép từ 90 ngày trở lên đối với các trường hợp còn lại.
+2. Thời gian còn lại của giấy phép được tính kể từ ngày tổ chức, cá nhân chính thức ngừng sử dụng nhưng không trước ngày Cục Tần số vô tuyến điện nhận được Thông báo ngừng".
+[amend] 65/2025/TT-BTС · hiệu lực 2025-07-01
+3. Sửa đổi, bổ sung Điều 7 Thông tư số 265/2016/TT-BTC đã được sửa đổi, bổ sung tại khoản 4 Điều 1 Thông tư số 11/2022/TT-BTC như sau:
+" Điều 7. Hoàn trả phí
+1. Tổ chức, cá nhân ngừng sử dụng tần số vô tuyến điện trước thời hạn quy định tại giấy phép sử dụng tần số vô tuyến điện được hoàn trả phần phí sử dụng tần số vô tuyến điện đã nộp cho thời gian còn lại của giấy phép (làm tròn theo tháng) theo quy định của pháp luật trong trường hợp giấy phép được cấp không gắn với cam kết triển khai mạng viễn thông và thời gian còn lại của giấy phép từ 30 ngày trở lên kể từ cơ quan nhà nước có thẩm quyền cấp giấy phép sử dụng tần số vô tuyến điện nhận được văn bản đề nghị của tổ chức, cá nhân.
+2. Thời gian còn lại của giấy phép để tính số phí được hoàn trả được tính kể từ ngày tổ chức, cá nhân chính thức ngừng sử dụng nhưng không trước ngày cơ quan nhà nước có thẩm quyền cấp giấy phép sử dụng tần số vô tuyến điện nhận được văn bản đề nghị của tổ chức, cá nhân. "</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -6588,8 +8414,6 @@
           <t>16/2022/TT-BGTVT; 17/2023/TT-BGTVT</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -6600,18 +8424,33 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P73" t="inlineStr"/>
-      <c r="Q73" t="inlineStr"/>
       <c r="R73" t="inlineStr">
         <is>
           <t>id cũ vilextime:T3:provision:a8ca5070-eb7f-11f0-8a66-6b570669d487:2022-08-16 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S73" t="inlineStr"/>
-      <c r="T73" t="inlineStr"/>
-      <c r="U73" t="inlineStr"/>
-      <c r="V73" t="inlineStr"/>
-      <c r="W73" t="inlineStr"/>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>40/2016/TT-BGTVT · hiệu lực 2017-07-01 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 16. Kiểm định và chứng nhận chất lượng an toàn kỹ thuật và phòng ngừa ô nhiễm môi trường cho công-te-nơ, máy, vật liệu, trang thiết bị sử dụng cho tàu biển trong chế tạo, lắp ráp, nhập khẩu, sửa chữa phục hồi, hoán cải
+2. Hồ sơ đề nghị kiểm định bao gồm:
+a) 01 (một) giấy đề nghị theo Mẫu số 09 tại Phụ lục ban hành kèm theo Thông tư này;
+b) 01 (một) bộ hồ sơ kỹ thuật (bản chính), bao gồm thông số kỹ thuật và các báo cáo kiểm tra, thử công-te-nơ, máy, vật liệu, trang thiết bị.</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 16/2022/TT-BGTVT · hiệu lực 2022-08-15
+4. Sửa đổi, bổ sung điểm b khoản 2 Điều 16 như sau:
+"2. Hồ sơ đề nghị kiểm định bao gồm:
+b) 01 (một) bộ hồ sơ kỹ thuật (bản sao), bao gồm thông số kỹ thuật và các báo cáo kiểm tra, thử công-te-nơ, máy, vật liệu, trang thiết bị."
+[amend] 17/2023/TT-BGTVT · hiệu lực 2023-08-15
+a) Sửa đổi, bổ sung khoản 2 Điều 16 Thông tư số 40/2016/TT-BGTVT đã được sửa đổi, bổ sung tại khoản 4 Điều 10 Thông tư số 16/2022/TT-BGTVT như sau:
+"2. Hồ sơ đề nghị kiểm định bao gồm:
+a) 01 (một) bản chính hoặc biểu mẫu điện tử giấy đề nghị theo Mẫu số 09 tại Phụ lục ban hành kèm theo Thông tư này;
+b) 01 (một) bản sao bộ hồ sơ kỹ thuật bao gồm thông số kỹ thuật và các báo cáo kiểm tra, thử công-te-nơ, máy, vật liệu, trang thiết bị (trường hợp nộp hồ trực tiếp hoặc qua hệ thống bưu chính) hoặc bản sao điện tử (trường hợp nộp hồ sơ qua cổng dịch vụ công trực tuyến hoặc bằng hình thức phù hợp khác)."</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -6669,8 +8508,6 @@
           <t>23/2022/TT-NHNN; 28/2016/TT-NHNN</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -6681,18 +8518,67 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P74" t="inlineStr"/>
-      <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr">
         <is>
           <t>id cũ vilextime:T3:provision:a9deea50-2d53-11f1-9ae2-252c6aade9ea:2016-11-19 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S74" t="inlineStr"/>
-      <c r="T74" t="inlineStr"/>
-      <c r="U74" t="inlineStr"/>
-      <c r="V74" t="inlineStr"/>
-      <c r="W74" t="inlineStr"/>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>21/2014/TT-NHNN · hiệu lực 2014-10-15 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 20. Hồ sơ, trình tự, thủ tục đề nghị cấp phép hoạt động ngoại hối khác trên thị trong nước và quốc tế
+Hồ sơ, trình tự, thủ tục đề nghị cấp phép thực hiện các hoạt động ngoại hối khác trên thị trường trong nước và quốc tế thực hiện như đối với ngân hàng thương mại theo quy định tại khoản 4, 5 Điều 11 và Điều 12 Thông tư này.</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 28/2016/TT-NHNN · hiệu lực 2016-11-18
+19. Điều 20 được sửa đổi, bổ sung như sau:
+“Điều 20. Hồ sơ, trình tự, thủ tục đề nghị chấp thuận hoạt động ngoại hối khác trên thị trong nước và thị trường quốc tế
+Hồ sơ, trình tự, thủ tục đề nghị chấp thuận, chấp thuận gia hạn hoạt động ngoại hối khác trên thị trường trong nước và thị trường quốc tế thực hiện như đối với ngân hàng thương mại theo quy định tại khoản 1, 4, 5 Điều 11 và Điều 12 Thông tư này.”
+20. Điều 21 được sửa đổi, bổ sung như sau:
+“Điều 21. Phạm vi hoạt động ngoại hối của công ty tài chính tổng hợp
+1. Phạm vi hoạt động ngoại hối cơ bản trên thị trường trong nước:
+a) Thực hiện các giao dịch mua bán ngoại tệ giao ngay;
+b) Thực hiện các giao dịch mua, bán ngoại tệ kỳ hạn, giao dịch hoán đổi ngoại tệ, giao dịch quyền chọn mua, bán ngoại tệ;
+c) Nhận tiền gửi bằng ngoại tệ của khách hàng là tổ chức không phải là tổ chức tín dụng; cho vay bằng ngoại tệ đối với khách hàng không phải là tổ chức tín dụng;
+d) Bao thanh toán và bảo lãnh ngân hàng bằng ngoại tệ;
+đ) Phát hành thẻ tín dụng quốc tế;
+e) Chiết khấu, tái chiết khấu các công cụ chuyển nhượng và giấy tờ có giá bằng ngoại tệ;
+g) Dịch vụ nhận và chi trả ngoại tệ; giao cho các tổ chức kinh tế làm đại lý đổi ngoại tệ, đại lý chi, trả ngoại tệ;
+h) Cung cấp các dịch vụ quản lý, bảo quản tài sản bằng ngoại hối; Nhận ủy thác cho vay bằng ngoại tệ;
+i) Đại lý phát hành giấy tờ có giá bằng ngoại tệ;
+k) Cung ứng các dịch vụ tư vấn cho khách hàng về ngoại hối;
+l) Mở tài khoản thanh toán bằng ngoại tệ tại các ngân hàng thương mại, chi nhánh ngân hàng nước ngoài được phép hoạt động ngoại hối;
+m) Vay vốn, cho vay bằng ngoại tệ đối với các tổ chức tín dụng được phép, tổ chức tài chính trong nước;
+n) Gửi tiền, nhận tiền gửi bằng ngoại tệ với các tổ chức tín dụng được phép khác;
+o) Nhận tiền gửi bằng ngoại tệ từ tổ chức tín dụng nước ngoài;
+p) Cho thuê tài chính bằng ngoại tệ.
+2. Phạm vi hoạt động ngoại hối cơ bản trên thị trường quốc tế:
+a) Mua, bán ngoại tệ giao ngay trên thị trường quốc tế;
+b) Thực hiện các giao dịch mua, bán ngoại tệ kỳ hạn, giao dịch hoán đổi ngoại tệ với tổ chức tài chính nước ngoài nhằm mục đích phòng ngừa, hạn chế rủi ro đối với hợp đồng mua bán ngoại tệ kỳ hạn, giao dịch hoán đổi ngoại tệ đã giao kết và thực hiện với khách hàng trong nước;
+c) Cho vay ra nước ngoài đối với khách hàng không phải là tổ chức tín dụng;
+d) Mở tài khoản thanh toán tại ngân hàng nước ngoài để thực hiện hoạt động phát hành thẻ tín dụng;
+đ) Bao thanh toán quốc tế và bảo lãnh ngân hàng bằng ngoại tệ.
+3. Đối với các hoạt động ngoại hối khác trên thị trường trong nước và thị trường quốc tế:
+a) Ngân hàng Nhà nước xem xét, cho phép công ty tài chính tổng hợp thực hiện có thời hạn đối với từng sản phẩm hoặc nhóm sản phẩm cụ thể, bao gồm các hoạt động ngoại hối khác trên thị trường trong nước và thị trường quốc tế ngoài các hoạt động ngoại hối quy định tại khoản 1, 2 Điều này trên cơ sở đáp ứng đủ điều kiện và hồ sơ theo quy định tại khoản 1 Điều 26, khoản 3 Điều 27 Thông tư này;
+b) Sau khi hết thời hạn được phép thực hiện các hoạt động ngoại hối khác trên thị trường trong nước và thị trường quốc tế tại văn bản chấp thuận có thời hạn, trường hợp có nhu cầu tiếp tục thực hiện, trên cơ sở đáp ứng đủ điều kiện và hồ sơ quy định tại khoản 2 Điều 26, khoản 4 Điều 27 Thông tư này và các quy định có liên quan của Ngân hàng Nhà nước, công ty tài chính tổng hợp được Ngân hàng Nhà nước xem xét, cho phép thực hiện các hoạt động ngoại hối này tại văn bản gia hạn văn bản chấp thuận có thời hạn.”
+21. Điều 22 được sửa đổi, bổ sung như sau:
+“Điều 22. Phạm vi hoạt động ngoại hối của công ty tài chính bao thanh toán
+1. Phạm vi hoạt động ngoại hối cơ bản trên thị trường trong nước:
+a) Nhận tiền gửi bằng ngoại tệ của khách hàng là tổ chức không phải là tổ chức tín dụng;
+b) Gửi tiền, nhận tiền gửi bằng ngoại tệ với các tổ chức tín dụng được phép;
+c) Vay vốn bằng ngoại tệ của các tổ chức tín dụng được phép, tổ chức tài chính trong nước;
+d) Chiết khấu, tái chiết khấu các công cụ chuyển nhượng và giấy tờ có giá bằng ngoại tệ;
+đ) Bao thanh toán bằng ngoại tệ;
+e) Cung cấp các dịch vụ quản lý, bảo quản tài sản bằng ngoại hối;
+g) Cung ứng các dịch vụ tư vấn cho khách hàng về ngoại hối;
+h) Mở tài khoản thanh toán bằng ngoại tệ tại các ngân hàng thương mại, chi nhánh ngân hàng nước ngoài được phép hoạt động ngoại hối.
+2. Phạm vi hoạt động ngoại hối cơ bản trên thị trường quốc tế: Bao thanh toán quốc tế.”
+[amend] 23/2022/TT-NHNN · hiệu lực 2023-02-15
+(không tìm được đoạn)</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -6750,8 +8636,6 @@
           <t>12/2018/NĐ-CP; 153/2026/NĐ-CP</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -6762,18 +8646,33 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P75" t="inlineStr"/>
-      <c r="Q75" t="inlineStr"/>
       <c r="R75" t="inlineStr">
         <is>
           <t>câu hỏi ghim mục 2 qua "doanh nghiệp đặt cơ sở trong khu công nghiệp"; các mục khác của danh sách không nói về loại doanh nghiệp này</t>
         </is>
       </c>
-      <c r="S75" t="inlineStr"/>
-      <c r="T75" t="inlineStr"/>
-      <c r="U75" t="inlineStr"/>
-      <c r="V75" t="inlineStr"/>
-      <c r="W75" t="inlineStr"/>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>01/2015/NĐ-CP · hiệu lực 2015-02-16 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 8. Phạm vi cụ thể địa bàn hoạt động hải quan tại các khu vực ngoài cửa khẩu
+2. Các khu công nghiệp, khu kinh tế cửa khẩu có doanh nghiệp sản xuất, kinh doanh hàng hoá chịu sự giám sát, kiểm soát hải quan; khu thương mại tự do, khu chế xuất; trụ sở, kho hàng của doanh nghiệp chế xuất; khu vực ưu đãi hải quan khác; khu vực chuyển phát nhanh hàng hoá xuất khẩu, nhập khẩu.</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 12/2018/NĐ-CP · hiệu lực 2018-03-10
+3. Sửa đổi khoản 2, khoản 8 Điều 8 như sau:
+"2. Các khu công nghiệp, khu kinh tế cửa khẩu có doanh nghiệp sản xuất, kinh doanh hàng hóa chịu sự giám sát, kiểm soát hải quan; khu thương mại tự do, khu chế xuất; trụ sở, kho hàng của doanh nghiệp chế xuất; khu phi thuế quan; khu vực ưu đãi hải quan khác; khu vực hải quan riêng.
+8. Khu vực, địa điểm kiểm tra thực tế hàng hóa xuất khẩu, nhập khẩu tại cơ sở sản xuất, cơ sở gia công lại, công trình."
+[amend] 153/2026/NĐ-CP · hiệu lực 2026-07-05
+Điều 2. Sửa đổi, bổ sung các khoản 2, khoản 3, khoản 5, khoản 8, khoản 9 Điều 8 như sau:
+“2. Trụ sở, kho hàng, cơ sở sản xuất của doanh nghiệp sản xuất, kinh doanh hàng hóa chịu sự giám sát, kiểm soát hải quan tại các khu công nghiệp, khu kinh tế, khu thương mại tự do, khu công nghệ cao, khu công nghệ số tập trung, trung tâm tài chính quốc tế; trụ sở, kho hàng, cơ sở sản xuất của doanh nghiệp chế xuất; trụ sở, kho hàng, cơ sở sản xuất của tổ chức, cá nhân nhập khẩu hàng hoá để gia công, sản xuất xuất khẩu; khu chế xuất; khu phi thuế quan; khu vực ưu đãi hải quan khác; khu vực hải quan riêng.
+3. Khu vực cảng xuất khẩu, nhập khẩu hàng hóa được thành lập trong nội địa, địa điểm thu gom hàng lẻ (CFS); kho hàng không kéo dài, kho ngoại quan, kho bảo thuế, kho bãi chứa hàng hóa xuất khẩu, nhập khẩu, quá cảnh của các tổ chức vận tải kinh doanh và giao nhận hàng hóa xuất khẩu, nhập khẩu, quá cảnh.
+5. Trụ sở người khai hải quan khi kiểm tra sau thông quan hoặc khi kiểm soát hải quan, bao gồm: nơi làm việc, nơi sản xuất, nơi cung ứng các dịch vụ, kho bãi, nhà xưởng, nơi lưu giữ, bảo quản, thuê, gửi hàng hóa xuất khẩu, nhập khẩu của người khai hải quan.
+8. Khu vực, địa điểm kiểm tra thực tế hàng hóa xuất khẩu, nhập khẩu tại cơ sở sản xuất, cơ sở gia công lại, công trình, cơ sở gia công hàng hóa xuất khẩu.
+9. Địa điểm kiểm tra tập trung; địa điểm tập kết, kiểm tra, giám sát hàng hóa xuất khẩu, nhập khẩu theo quy định của pháp luật.”</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -6831,8 +8730,6 @@
           <t>12/2018/NĐ-CP; 153/2026/NĐ-CP</t>
         </is>
       </c>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -6843,18 +8740,33 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P76" t="inlineStr"/>
-      <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr">
         <is>
           <t>câu hỏi ghim mục 2 qua "doanh nghiệp đặt cơ sở trong khu công nghiệp"; các mục khác của danh sách không nói về loại doanh nghiệp này</t>
         </is>
       </c>
-      <c r="S76" t="inlineStr"/>
-      <c r="T76" t="inlineStr"/>
-      <c r="U76" t="inlineStr"/>
-      <c r="V76" t="inlineStr"/>
-      <c r="W76" t="inlineStr"/>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>01/2015/NĐ-CP · hiệu lực 2015-02-16 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 8. Phạm vi cụ thể địa bàn hoạt động hải quan tại các khu vực ngoài cửa khẩu
+2. Các khu công nghiệp, khu kinh tế cửa khẩu có doanh nghiệp sản xuất, kinh doanh hàng hoá chịu sự giám sát, kiểm soát hải quan; khu thương mại tự do, khu chế xuất; trụ sở, kho hàng của doanh nghiệp chế xuất; khu vực ưu đãi hải quan khác; khu vực chuyển phát nhanh hàng hoá xuất khẩu, nhập khẩu.</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 12/2018/NĐ-CP · hiệu lực 2018-03-10
+3. Sửa đổi khoản 2, khoản 8 Điều 8 như sau:
+"2. Các khu công nghiệp, khu kinh tế cửa khẩu có doanh nghiệp sản xuất, kinh doanh hàng hóa chịu sự giám sát, kiểm soát hải quan; khu thương mại tự do, khu chế xuất; trụ sở, kho hàng của doanh nghiệp chế xuất; khu phi thuế quan; khu vực ưu đãi hải quan khác; khu vực hải quan riêng.
+8. Khu vực, địa điểm kiểm tra thực tế hàng hóa xuất khẩu, nhập khẩu tại cơ sở sản xuất, cơ sở gia công lại, công trình."
+[amend] 153/2026/NĐ-CP · hiệu lực 2026-07-05
+Điều 2. Sửa đổi, bổ sung các khoản 2, khoản 3, khoản 5, khoản 8, khoản 9 Điều 8 như sau:
+“2. Trụ sở, kho hàng, cơ sở sản xuất của doanh nghiệp sản xuất, kinh doanh hàng hóa chịu sự giám sát, kiểm soát hải quan tại các khu công nghiệp, khu kinh tế, khu thương mại tự do, khu công nghệ cao, khu công nghệ số tập trung, trung tâm tài chính quốc tế; trụ sở, kho hàng, cơ sở sản xuất của doanh nghiệp chế xuất; trụ sở, kho hàng, cơ sở sản xuất của tổ chức, cá nhân nhập khẩu hàng hoá để gia công, sản xuất xuất khẩu; khu chế xuất; khu phi thuế quan; khu vực ưu đãi hải quan khác; khu vực hải quan riêng.
+3. Khu vực cảng xuất khẩu, nhập khẩu hàng hóa được thành lập trong nội địa, địa điểm thu gom hàng lẻ (CFS); kho hàng không kéo dài, kho ngoại quan, kho bảo thuế, kho bãi chứa hàng hóa xuất khẩu, nhập khẩu, quá cảnh của các tổ chức vận tải kinh doanh và giao nhận hàng hóa xuất khẩu, nhập khẩu, quá cảnh.
+5. Trụ sở người khai hải quan khi kiểm tra sau thông quan hoặc khi kiểm soát hải quan, bao gồm: nơi làm việc, nơi sản xuất, nơi cung ứng các dịch vụ, kho bãi, nhà xưởng, nơi lưu giữ, bảo quản, thuê, gửi hàng hóa xuất khẩu, nhập khẩu của người khai hải quan.
+8. Khu vực, địa điểm kiểm tra thực tế hàng hóa xuất khẩu, nhập khẩu tại cơ sở sản xuất, cơ sở gia công lại, công trình, cơ sở gia công hàng hóa xuất khẩu.
+9. Địa điểm kiểm tra tập trung; địa điểm tập kết, kiểm tra, giám sát hàng hóa xuất khẩu, nhập khẩu theo quy định của pháp luật.”</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -6912,8 +8824,6 @@
           <t>12/2018/NĐ-CP; 153/2026/NĐ-CP</t>
         </is>
       </c>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -6924,18 +8834,33 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P77" t="inlineStr"/>
-      <c r="Q77" t="inlineStr"/>
       <c r="R77" t="inlineStr">
         <is>
           <t>câu hỏi ghim mục 2 qua "doanh nghiệp đặt cơ sở trong khu công nghiệp"; các mục khác của danh sách không nói về loại doanh nghiệp này</t>
         </is>
       </c>
-      <c r="S77" t="inlineStr"/>
-      <c r="T77" t="inlineStr"/>
-      <c r="U77" t="inlineStr"/>
-      <c r="V77" t="inlineStr"/>
-      <c r="W77" t="inlineStr"/>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>01/2015/NĐ-CP · hiệu lực 2015-02-16 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 8. Phạm vi cụ thể địa bàn hoạt động hải quan tại các khu vực ngoài cửa khẩu
+2. Các khu công nghiệp, khu kinh tế cửa khẩu có doanh nghiệp sản xuất, kinh doanh hàng hoá chịu sự giám sát, kiểm soát hải quan; khu thương mại tự do, khu chế xuất; trụ sở, kho hàng của doanh nghiệp chế xuất; khu vực ưu đãi hải quan khác; khu vực chuyển phát nhanh hàng hoá xuất khẩu, nhập khẩu.</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 12/2018/NĐ-CP · hiệu lực 2018-03-10
+3. Sửa đổi khoản 2, khoản 8 Điều 8 như sau:
+"2. Các khu công nghiệp, khu kinh tế cửa khẩu có doanh nghiệp sản xuất, kinh doanh hàng hóa chịu sự giám sát, kiểm soát hải quan; khu thương mại tự do, khu chế xuất; trụ sở, kho hàng của doanh nghiệp chế xuất; khu phi thuế quan; khu vực ưu đãi hải quan khác; khu vực hải quan riêng.
+8. Khu vực, địa điểm kiểm tra thực tế hàng hóa xuất khẩu, nhập khẩu tại cơ sở sản xuất, cơ sở gia công lại, công trình."
+[amend] 153/2026/NĐ-CP · hiệu lực 2026-07-05
+Điều 2. Sửa đổi, bổ sung các khoản 2, khoản 3, khoản 5, khoản 8, khoản 9 Điều 8 như sau:
+“2. Trụ sở, kho hàng, cơ sở sản xuất của doanh nghiệp sản xuất, kinh doanh hàng hóa chịu sự giám sát, kiểm soát hải quan tại các khu công nghiệp, khu kinh tế, khu thương mại tự do, khu công nghệ cao, khu công nghệ số tập trung, trung tâm tài chính quốc tế; trụ sở, kho hàng, cơ sở sản xuất của doanh nghiệp chế xuất; trụ sở, kho hàng, cơ sở sản xuất của tổ chức, cá nhân nhập khẩu hàng hoá để gia công, sản xuất xuất khẩu; khu chế xuất; khu phi thuế quan; khu vực ưu đãi hải quan khác; khu vực hải quan riêng.
+3. Khu vực cảng xuất khẩu, nhập khẩu hàng hóa được thành lập trong nội địa, địa điểm thu gom hàng lẻ (CFS); kho hàng không kéo dài, kho ngoại quan, kho bảo thuế, kho bãi chứa hàng hóa xuất khẩu, nhập khẩu, quá cảnh của các tổ chức vận tải kinh doanh và giao nhận hàng hóa xuất khẩu, nhập khẩu, quá cảnh.
+5. Trụ sở người khai hải quan khi kiểm tra sau thông quan hoặc khi kiểm soát hải quan, bao gồm: nơi làm việc, nơi sản xuất, nơi cung ứng các dịch vụ, kho bãi, nhà xưởng, nơi lưu giữ, bảo quản, thuê, gửi hàng hóa xuất khẩu, nhập khẩu của người khai hải quan.
+8. Khu vực, địa điểm kiểm tra thực tế hàng hóa xuất khẩu, nhập khẩu tại cơ sở sản xuất, cơ sở gia công lại, công trình, cơ sở gia công hàng hóa xuất khẩu.
+9. Địa điểm kiểm tra tập trung; địa điểm tập kết, kiểm tra, giám sát hàng hóa xuất khẩu, nhập khẩu theo quy định của pháp luật.”</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -6998,7 +8923,6 @@
           <t>actor_has_transitional</t>
         </is>
       </c>
-      <c r="M78" t="inlineStr"/>
       <c r="N78" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -7009,18 +8933,48 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P78" t="inlineStr"/>
-      <c r="Q78" t="inlineStr"/>
       <c r="R78" t="inlineStr">
         <is>
           <t>Câu hỏi hỏi chung 'thẩm quyền đối với sổ nhật ký'; mốc 1 là cơ quan cấp sổ, từ mốc 2 là cơ quan đóng dấu treo, giáp lai — chức năng đổi theo văn bản, câu hỏi vẫn bao được; id cũ vilextime:T3:provision:c349619a-2b6a-11f1-b9c9-5749372a62ab:2020-01-02 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S78" t="inlineStr"/>
-      <c r="T78" t="inlineStr"/>
-      <c r="U78" t="inlineStr"/>
-      <c r="V78" t="inlineStr"/>
-      <c r="W78" t="inlineStr"/>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>39/2019/TT-BGTVT · hiệu lực 2020-01-01 → nay · lúc thu thập: Còn hiệu lực
+Điều 20. Tổ chức thực hiện
+3. Cơ quan cấp sổ nhật ký phương tiện: Cục Đường thủy nội địa Việt Nam; Sở Giao thông vận tải; Cảng vụ Hàng hải hoặc đại diện Cảng vụ Hàng hải; Cảng vụ Đường thủy nội địa khu vực hoặc đại diện Cảng vụ Đường thủy nội địa khu vực trực thuộc Cục Đường thủy nội địa Việt Nam; Cảng vụ Đường thủy nội địa hoặc đại diện Cảng vụ Đường thủy nội địa thuộc Sở Giao thông vận tải.</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 33/2022/TT-BGTVT · hiệu lực 2023-02-01
+5. Sửa đổi, bổ sung khoản 3 Điều 20 như sau:
+"3. Cơ quan đóng dấu treo và dấu giáp lai các trang sổ nhật ký hành trình và sổ nhật ký máy: Cục Đường thủy nội địa Việt Nam, Sở Giao thông vận tải, Cảng vụ hàng hải hoặc đại diện Cảng vụ hàng hải, Cảng vụ đường thủy nội địa hoặc đại diện Cảng vụ đường thủy nội địa."
+[amend] 09/2025/TT-BXD · hiệu lực 2025-07-01
+Sửa đổi, bổ sung khoản 3 Điều 20 Thông tư số 39/2019/TT-BGTVT (đã được sửa đổi, bổ sung tại khoản 5 Điều 1 Thông tư 33/2022/TT-BGTVT ) như sau:
+"3. Cơ quan đóng dấu treo và dấu giáp lai các trang sổ nhật ký hành trình và sổ nhật ký máy: Ủy ban nhân dân cấp xã.".
+CHUYỂN TIẾP: Điều 33. Quy định chuyển tiếp
+1. Văn bản, giấy tờ đã được cơ quan, chức danh có thẩm quyền ban hành, cấp trước ngày 01 tháng 7 năm 2025 mà chưa hết hiệu lực hoặc chưa hết thời hạn sử dụng thì tiếp tục được áp dụng, sử dụng theo quy định của pháp luật cho đến khi hết thời hạn hoặc được sửa đổi, bổ sung, thay thế, bãi bỏ, hủy bỏ, thu hồi bởi cơ quan, chức danh tiếp nhận chức năng, nhiệm vụ, quyền hạn hoặc cơ quan, người có thẩm quyền.
+2. Đối với các công việc, hồ sơ thủ tục hành chính liên quan đến chính quyền hai cấp:
+Các công việc, hồ sơ thủ tục hành chính của các cơ quan, đơn vị thuộc chính quyền địa phương cấp huyện đang giải quyết cho cá nhân, tổ chức, doanh nghiệp nếu đến thời điểm ngày 01 tháng 7 năm 2025 mà vẫn chưa hoàn thành hoặc đã hoàn thành trước ngày 01 tháng 7 năm 2025 nhưng sau đó phát sinh vấn đề liên quan cần giải quyết thì Chủ tịch Ủy ban nhân dân cấp tỉnh có thẩm quyền và trách nhiệm phân công cơ quan, đơn vị thuộc chính quyền địa phương cấp xã nơi cư trú của cá nhân hoặc nơi đặt trụ sở giao dịch của tổ chức, doanh nghiệp đang có công việc, hồ sơ thủ tục hành chính cần giải quyết để tiếp tục giải quyết bảo đảm không làm gián đoạn công việc, không ảnh hưởng đến hoạt động bình thường của xã hội, người dân, doanh nghiệp; trường hợp nội dung công việc, hồ sơ thủ tục hành chính đó liên quan đến từ 02 đơn vị hành chính cấp xã mới hình thành sau sắp xếp trở lên hoặc có nội dung phức tạp thì Chủ tịch Ủy ban nhân dân cấp tỉnh có thẩm quyền và trách nhiệm trực tiếp giải quyết hoặc phân công cơ quan chuyên môn, cơ quan hành chính khác thuộc Ủy ban nhân dân cấp mình tiếp tục giải quyết bảo đảm không làm gián đoạn công việc, không ảnh hưởng đến hoạt động bình thường của xã hội, người dân, doanh nghiệp.
+3. Đối với các công việc, hồ sơ thủ tục hành chính liên quan phân cấp nhiệm vụ, thẩm quyền
+Các công việc, hồ sơ thủ tục hành chính đã được cơ quan có thẩm quyền tiếp nhận hồ sơ trước ngày 01 tháng 7 năm 2025 thì cơ quan có thẩm quyền đã tiếp nhận hồ sơ tiếp tục thực hiện theo quy định của văn bản quy phạm pháp luật tại thời điểm tiếp nhận hồ sơ. Trường hợp trả lại hồ sơ để hoàn thiện thì gửi hồ sơ đến cơ quan được phân cấp theo quy định tại Thông tư này để tiếp tục giải quyết thủ tục hành chính theo quy định của Thông tư này.
+4. Quy định chuyển tiếp đối với với nội dung quy định tại Điều 6 Thông tư này:
+a) Đối với công trình cấp nước có phạm vi cấp nước nằm trên địa giới hành chính của 02 đơn vị hành chính cấp xã trở lên, Ủy ban nhân dân cấp tỉnh là cơ quan có thẩm quyền trong thỏa thuận thực hiện dịch vụ cấp nước đã được ký kết với đơn vị cấp nước;
+b) Đối với công trình cấp nước có phạm vi cấp nước nằm trên địa giới hành chính của 01 đơn vị hành chính cấp xã, Ủy ban nhân dân cấp xã là cơ quan có thẩm quyền trong thỏa thuận thực hiện dịch vụ cấp nước đã được ký kết với đơn vị cấp nước.
+5. Quy định chuyển tiếp đối với nội dung quy định tại Điều 10 Thông tư này.
+a) Cấp công trình thuộc dự án đầu tư xây dựng đã được quyết định đầu tư trước ngày 01 tháng 7 năm 2025 được xác định theo quy định của pháp luật tại thời điểm quyết định đầu tư;
+b) Trường hợp dự án, công trình xây dựng đã trình cơ quan chuyên môn về xây dựng thẩm định hoặc thẩm định điều chỉnh Báo cáo nghiên cứu khả thi đầu tư xây dựng, thiết kế xây dựng triển khai sau thiết kế cơ sở trước ngày 01 tháng 7 năm 2025 và đủ điều kiện thẩm định thì việc xác định cấp công trình và áp dụng cấp công trình trong quản lý các hoạt động đầu tư xây dựng được xác định theo quy định của pháp luật tại thời điểm trình thẩm định;
+c) Trường hợp công trình có điều chỉnh thiết kế xây dựng trước ngày 01 tháng 7 năm 2025 nhưng không làm thay đổi về mức độ quan trọng, quy mô công suất, quy mô kết cấu thì cấp công trình được xác định theo quy định của pháp luật tại thời điểm quyết định đầu tư; trường hợp công trình có điều chỉnh thiết kế xây dựng trước ngày 01 tháng 7 năm 2025 mà làm thay đổi về mức độ quan trọng, quy mô công suất, quy mô kết cấu thì cấp công trình được xác định theo quy định [...cắt bớt]
+4. Quy định chuyển tiếp đối với với nội dung quy định tại Điều 6 Thông tư này:
+a) Đối với công trình cấp nước có phạm vi cấp nước nằm trên địa giới hành chính của 02 đơn vị hành chính cấp xã trở lên, Ủy ban nhân dân cấp tỉnh là cơ quan có thẩm quyền trong thỏa thuận thực hiện dịch vụ cấp nước đã được ký kết với đơn vị cấp nước;
+b) Đối với công trình cấp nước có phạm vi cấp nước nằm trên địa giới hành chính của 01 đơn vị hành chính cấp xã, Ủy ban nhân dân cấp xã là cơ quan có thẩm quyền trong thỏa thuận thực hiện dịch vụ cấp nước đã được ký kết với đơn vị cấp nước.
+5. Quy định chuyển tiếp đối với nội dung quy định tại Điều 10 Thông tư này.
+a) Cấp công trình thuộc dự án đầu tư xây dựng đã được quyết định đầu tư trước ngày 01 tháng 7 năm 2025 được xác định theo quy định của pháp luật tại thời điểm quyết định đầu tư;
+b) Trường hợp dự án, công trình xây dựng đã trình cơ quan chuyên môn về xây dựng thẩm định hoặc thẩm định điều chỉnh Báo cáo nghiên cứu khả thi đầu tư xây dựng, thiết kế xây dựng triển khai sau thiết kế cơ sở trước ngày 01 tháng 7 năm 2025 và đủ điều kiện thẩm định thì việc xác định cấp công trình và áp dụng cấp công trình trong quản lý các hoạt động đầu tư xây dựng được xác định theo quy định của pháp luật tại thời điểm trình thẩm định;
+c) Trường hợp công trình có điều ch</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -7083,7 +9037,6 @@
           <t>actor_has_transitional</t>
         </is>
       </c>
-      <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -7094,18 +9047,48 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P79" t="inlineStr"/>
-      <c r="Q79" t="inlineStr"/>
       <c r="R79" t="inlineStr">
         <is>
           <t>Câu hỏi hỏi chung 'thẩm quyền đối với sổ nhật ký'; mốc 1 là cơ quan cấp sổ, từ mốc 2 là cơ quan đóng dấu treo, giáp lai — chức năng đổi theo văn bản, câu hỏi vẫn bao được; id cũ vilextime:T3:provision:c349619a-2b6a-11f1-b9c9-5749372a62ab:2023-02-02 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S79" t="inlineStr"/>
-      <c r="T79" t="inlineStr"/>
-      <c r="U79" t="inlineStr"/>
-      <c r="V79" t="inlineStr"/>
-      <c r="W79" t="inlineStr"/>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>39/2019/TT-BGTVT · hiệu lực 2020-01-01 → nay · lúc thu thập: Còn hiệu lực
+Điều 20. Tổ chức thực hiện
+3. Cơ quan cấp sổ nhật ký phương tiện: Cục Đường thủy nội địa Việt Nam; Sở Giao thông vận tải; Cảng vụ Hàng hải hoặc đại diện Cảng vụ Hàng hải; Cảng vụ Đường thủy nội địa khu vực hoặc đại diện Cảng vụ Đường thủy nội địa khu vực trực thuộc Cục Đường thủy nội địa Việt Nam; Cảng vụ Đường thủy nội địa hoặc đại diện Cảng vụ Đường thủy nội địa thuộc Sở Giao thông vận tải.</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 33/2022/TT-BGTVT · hiệu lực 2023-02-01
+5. Sửa đổi, bổ sung khoản 3 Điều 20 như sau:
+"3. Cơ quan đóng dấu treo và dấu giáp lai các trang sổ nhật ký hành trình và sổ nhật ký máy: Cục Đường thủy nội địa Việt Nam, Sở Giao thông vận tải, Cảng vụ hàng hải hoặc đại diện Cảng vụ hàng hải, Cảng vụ đường thủy nội địa hoặc đại diện Cảng vụ đường thủy nội địa."
+[amend] 09/2025/TT-BXD · hiệu lực 2025-07-01
+Sửa đổi, bổ sung khoản 3 Điều 20 Thông tư số 39/2019/TT-BGTVT (đã được sửa đổi, bổ sung tại khoản 5 Điều 1 Thông tư 33/2022/TT-BGTVT ) như sau:
+"3. Cơ quan đóng dấu treo và dấu giáp lai các trang sổ nhật ký hành trình và sổ nhật ký máy: Ủy ban nhân dân cấp xã.".
+CHUYỂN TIẾP: Điều 33. Quy định chuyển tiếp
+1. Văn bản, giấy tờ đã được cơ quan, chức danh có thẩm quyền ban hành, cấp trước ngày 01 tháng 7 năm 2025 mà chưa hết hiệu lực hoặc chưa hết thời hạn sử dụng thì tiếp tục được áp dụng, sử dụng theo quy định của pháp luật cho đến khi hết thời hạn hoặc được sửa đổi, bổ sung, thay thế, bãi bỏ, hủy bỏ, thu hồi bởi cơ quan, chức danh tiếp nhận chức năng, nhiệm vụ, quyền hạn hoặc cơ quan, người có thẩm quyền.
+2. Đối với các công việc, hồ sơ thủ tục hành chính liên quan đến chính quyền hai cấp:
+Các công việc, hồ sơ thủ tục hành chính của các cơ quan, đơn vị thuộc chính quyền địa phương cấp huyện đang giải quyết cho cá nhân, tổ chức, doanh nghiệp nếu đến thời điểm ngày 01 tháng 7 năm 2025 mà vẫn chưa hoàn thành hoặc đã hoàn thành trước ngày 01 tháng 7 năm 2025 nhưng sau đó phát sinh vấn đề liên quan cần giải quyết thì Chủ tịch Ủy ban nhân dân cấp tỉnh có thẩm quyền và trách nhiệm phân công cơ quan, đơn vị thuộc chính quyền địa phương cấp xã nơi cư trú của cá nhân hoặc nơi đặt trụ sở giao dịch của tổ chức, doanh nghiệp đang có công việc, hồ sơ thủ tục hành chính cần giải quyết để tiếp tục giải quyết bảo đảm không làm gián đoạn công việc, không ảnh hưởng đến hoạt động bình thường của xã hội, người dân, doanh nghiệp; trường hợp nội dung công việc, hồ sơ thủ tục hành chính đó liên quan đến từ 02 đơn vị hành chính cấp xã mới hình thành sau sắp xếp trở lên hoặc có nội dung phức tạp thì Chủ tịch Ủy ban nhân dân cấp tỉnh có thẩm quyền và trách nhiệm trực tiếp giải quyết hoặc phân công cơ quan chuyên môn, cơ quan hành chính khác thuộc Ủy ban nhân dân cấp mình tiếp tục giải quyết bảo đảm không làm gián đoạn công việc, không ảnh hưởng đến hoạt động bình thường của xã hội, người dân, doanh nghiệp.
+3. Đối với các công việc, hồ sơ thủ tục hành chính liên quan phân cấp nhiệm vụ, thẩm quyền
+Các công việc, hồ sơ thủ tục hành chính đã được cơ quan có thẩm quyền tiếp nhận hồ sơ trước ngày 01 tháng 7 năm 2025 thì cơ quan có thẩm quyền đã tiếp nhận hồ sơ tiếp tục thực hiện theo quy định của văn bản quy phạm pháp luật tại thời điểm tiếp nhận hồ sơ. Trường hợp trả lại hồ sơ để hoàn thiện thì gửi hồ sơ đến cơ quan được phân cấp theo quy định tại Thông tư này để tiếp tục giải quyết thủ tục hành chính theo quy định của Thông tư này.
+4. Quy định chuyển tiếp đối với với nội dung quy định tại Điều 6 Thông tư này:
+a) Đối với công trình cấp nước có phạm vi cấp nước nằm trên địa giới hành chính của 02 đơn vị hành chính cấp xã trở lên, Ủy ban nhân dân cấp tỉnh là cơ quan có thẩm quyền trong thỏa thuận thực hiện dịch vụ cấp nước đã được ký kết với đơn vị cấp nước;
+b) Đối với công trình cấp nước có phạm vi cấp nước nằm trên địa giới hành chính của 01 đơn vị hành chính cấp xã, Ủy ban nhân dân cấp xã là cơ quan có thẩm quyền trong thỏa thuận thực hiện dịch vụ cấp nước đã được ký kết với đơn vị cấp nước.
+5. Quy định chuyển tiếp đối với nội dung quy định tại Điều 10 Thông tư này.
+a) Cấp công trình thuộc dự án đầu tư xây dựng đã được quyết định đầu tư trước ngày 01 tháng 7 năm 2025 được xác định theo quy định của pháp luật tại thời điểm quyết định đầu tư;
+b) Trường hợp dự án, công trình xây dựng đã trình cơ quan chuyên môn về xây dựng thẩm định hoặc thẩm định điều chỉnh Báo cáo nghiên cứu khả thi đầu tư xây dựng, thiết kế xây dựng triển khai sau thiết kế cơ sở trước ngày 01 tháng 7 năm 2025 và đủ điều kiện thẩm định thì việc xác định cấp công trình và áp dụng cấp công trình trong quản lý các hoạt động đầu tư xây dựng được xác định theo quy định của pháp luật tại thời điểm trình thẩm định;
+c) Trường hợp công trình có điều chỉnh thiết kế xây dựng trước ngày 01 tháng 7 năm 2025 nhưng không làm thay đổi về mức độ quan trọng, quy mô công suất, quy mô kết cấu thì cấp công trình được xác định theo quy định của pháp luật tại thời điểm quyết định đầu tư; trường hợp công trình có điều chỉnh thiết kế xây dựng trước ngày 01 tháng 7 năm 2025 mà làm thay đổi về mức độ quan trọng, quy mô công suất, quy mô kết cấu thì cấp công trình được xác định theo quy định [...cắt bớt]
+4. Quy định chuyển tiếp đối với với nội dung quy định tại Điều 6 Thông tư này:
+a) Đối với công trình cấp nước có phạm vi cấp nước nằm trên địa giới hành chính của 02 đơn vị hành chính cấp xã trở lên, Ủy ban nhân dân cấp tỉnh là cơ quan có thẩm quyền trong thỏa thuận thực hiện dịch vụ cấp nước đã được ký kết với đơn vị cấp nước;
+b) Đối với công trình cấp nước có phạm vi cấp nước nằm trên địa giới hành chính của 01 đơn vị hành chính cấp xã, Ủy ban nhân dân cấp xã là cơ quan có thẩm quyền trong thỏa thuận thực hiện dịch vụ cấp nước đã được ký kết với đơn vị cấp nước.
+5. Quy định chuyển tiếp đối với nội dung quy định tại Điều 10 Thông tư này.
+a) Cấp công trình thuộc dự án đầu tư xây dựng đã được quyết định đầu tư trước ngày 01 tháng 7 năm 2025 được xác định theo quy định của pháp luật tại thời điểm quyết định đầu tư;
+b) Trường hợp dự án, công trình xây dựng đã trình cơ quan chuyên môn về xây dựng thẩm định hoặc thẩm định điều chỉnh Báo cáo nghiên cứu khả thi đầu tư xây dựng, thiết kế xây dựng triển khai sau thiết kế cơ sở trước ngày 01 tháng 7 năm 2025 và đủ điều kiện thẩm định thì việc xác định cấp công trình và áp dụng cấp công trình trong quản lý các hoạt động đầu tư xây dựng được xác định theo quy định của pháp luật tại thời điểm trình thẩm định;
+c) Trường hợp công trình có điều ch</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -7168,7 +9151,6 @@
           <t>actor_has_transitional</t>
         </is>
       </c>
-      <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -7179,18 +9161,48 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P80" t="inlineStr"/>
-      <c r="Q80" t="inlineStr"/>
       <c r="R80" t="inlineStr">
         <is>
           <t>Câu hỏi hỏi chung 'thẩm quyền đối với sổ nhật ký'; mốc 1 là cơ quan cấp sổ, từ mốc 2 là cơ quan đóng dấu treo, giáp lai — chức năng đổi theo văn bản, câu hỏi vẫn bao được; id cũ vilextime:T3:provision:c349619a-2b6a-11f1-b9c9-5749372a62ab:2025-07-02 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S80" t="inlineStr"/>
-      <c r="T80" t="inlineStr"/>
-      <c r="U80" t="inlineStr"/>
-      <c r="V80" t="inlineStr"/>
-      <c r="W80" t="inlineStr"/>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>39/2019/TT-BGTVT · hiệu lực 2020-01-01 → nay · lúc thu thập: Còn hiệu lực
+Điều 20. Tổ chức thực hiện
+3. Cơ quan cấp sổ nhật ký phương tiện: Cục Đường thủy nội địa Việt Nam; Sở Giao thông vận tải; Cảng vụ Hàng hải hoặc đại diện Cảng vụ Hàng hải; Cảng vụ Đường thủy nội địa khu vực hoặc đại diện Cảng vụ Đường thủy nội địa khu vực trực thuộc Cục Đường thủy nội địa Việt Nam; Cảng vụ Đường thủy nội địa hoặc đại diện Cảng vụ Đường thủy nội địa thuộc Sở Giao thông vận tải.</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 33/2022/TT-BGTVT · hiệu lực 2023-02-01
+5. Sửa đổi, bổ sung khoản 3 Điều 20 như sau:
+"3. Cơ quan đóng dấu treo và dấu giáp lai các trang sổ nhật ký hành trình và sổ nhật ký máy: Cục Đường thủy nội địa Việt Nam, Sở Giao thông vận tải, Cảng vụ hàng hải hoặc đại diện Cảng vụ hàng hải, Cảng vụ đường thủy nội địa hoặc đại diện Cảng vụ đường thủy nội địa."
+[amend] 09/2025/TT-BXD · hiệu lực 2025-07-01
+Sửa đổi, bổ sung khoản 3 Điều 20 Thông tư số 39/2019/TT-BGTVT (đã được sửa đổi, bổ sung tại khoản 5 Điều 1 Thông tư 33/2022/TT-BGTVT ) như sau:
+"3. Cơ quan đóng dấu treo và dấu giáp lai các trang sổ nhật ký hành trình và sổ nhật ký máy: Ủy ban nhân dân cấp xã.".
+CHUYỂN TIẾP: Điều 33. Quy định chuyển tiếp
+1. Văn bản, giấy tờ đã được cơ quan, chức danh có thẩm quyền ban hành, cấp trước ngày 01 tháng 7 năm 2025 mà chưa hết hiệu lực hoặc chưa hết thời hạn sử dụng thì tiếp tục được áp dụng, sử dụng theo quy định của pháp luật cho đến khi hết thời hạn hoặc được sửa đổi, bổ sung, thay thế, bãi bỏ, hủy bỏ, thu hồi bởi cơ quan, chức danh tiếp nhận chức năng, nhiệm vụ, quyền hạn hoặc cơ quan, người có thẩm quyền.
+2. Đối với các công việc, hồ sơ thủ tục hành chính liên quan đến chính quyền hai cấp:
+Các công việc, hồ sơ thủ tục hành chính của các cơ quan, đơn vị thuộc chính quyền địa phương cấp huyện đang giải quyết cho cá nhân, tổ chức, doanh nghiệp nếu đến thời điểm ngày 01 tháng 7 năm 2025 mà vẫn chưa hoàn thành hoặc đã hoàn thành trước ngày 01 tháng 7 năm 2025 nhưng sau đó phát sinh vấn đề liên quan cần giải quyết thì Chủ tịch Ủy ban nhân dân cấp tỉnh có thẩm quyền và trách nhiệm phân công cơ quan, đơn vị thuộc chính quyền địa phương cấp xã nơi cư trú của cá nhân hoặc nơi đặt trụ sở giao dịch của tổ chức, doanh nghiệp đang có công việc, hồ sơ thủ tục hành chính cần giải quyết để tiếp tục giải quyết bảo đảm không làm gián đoạn công việc, không ảnh hưởng đến hoạt động bình thường của xã hội, người dân, doanh nghiệp; trường hợp nội dung công việc, hồ sơ thủ tục hành chính đó liên quan đến từ 02 đơn vị hành chính cấp xã mới hình thành sau sắp xếp trở lên hoặc có nội dung phức tạp thì Chủ tịch Ủy ban nhân dân cấp tỉnh có thẩm quyền và trách nhiệm trực tiếp giải quyết hoặc phân công cơ quan chuyên môn, cơ quan hành chính khác thuộc Ủy ban nhân dân cấp mình tiếp tục giải quyết bảo đảm không làm gián đoạn công việc, không ảnh hưởng đến hoạt động bình thường của xã hội, người dân, doanh nghiệp.
+3. Đối với các công việc, hồ sơ thủ tục hành chính liên quan phân cấp nhiệm vụ, thẩm quyền
+Các công việc, hồ sơ thủ tục hành chính đã được cơ quan có thẩm quyền tiếp nhận hồ sơ trước ngày 01 tháng 7 năm 2025 thì cơ quan có thẩm quyền đã tiếp nhận hồ sơ tiếp tục thực hiện theo quy định của văn bản quy phạm pháp luật tại thời điểm tiếp nhận hồ sơ. Trường hợp trả lại hồ sơ để hoàn thiện thì gửi hồ sơ đến cơ quan được phân cấp theo quy định tại Thông tư này để tiếp tục giải quyết thủ tục hành chính theo quy định của Thông tư này.
+4. Quy định chuyển tiếp đối với với nội dung quy định tại Điều 6 Thông tư này:
+a) Đối với công trình cấp nước có phạm vi cấp nước nằm trên địa giới hành chính của 02 đơn vị hành chính cấp xã trở lên, Ủy ban nhân dân cấp tỉnh là cơ quan có thẩm quyền trong thỏa thuận thực hiện dịch vụ cấp nước đã được ký kết với đơn vị cấp nước;
+b) Đối với công trình cấp nước có phạm vi cấp nước nằm trên địa giới hành chính của 01 đơn vị hành chính cấp xã, Ủy ban nhân dân cấp xã là cơ quan có thẩm quyền trong thỏa thuận thực hiện dịch vụ cấp nước đã được ký kết với đơn vị cấp nước.
+5. Quy định chuyển tiếp đối với nội dung quy định tại Điều 10 Thông tư này.
+a) Cấp công trình thuộc dự án đầu tư xây dựng đã được quyết định đầu tư trước ngày 01 tháng 7 năm 2025 được xác định theo quy định của pháp luật tại thời điểm quyết định đầu tư;
+b) Trường hợp dự án, công trình xây dựng đã trình cơ quan chuyên môn về xây dựng thẩm định hoặc thẩm định điều chỉnh Báo cáo nghiên cứu khả thi đầu tư xây dựng, thiết kế xây dựng triển khai sau thiết kế cơ sở trước ngày 01 tháng 7 năm 2025 và đủ điều kiện thẩm định thì việc xác định cấp công trình và áp dụng cấp công trình trong quản lý các hoạt động đầu tư xây dựng được xác định theo quy định của pháp luật tại thời điểm trình thẩm định;
+c) Trường hợp công trình có điều chỉnh thiết kế xây dựng trước ngày 01 tháng 7 năm 2025 nhưng không làm thay đổi về mức độ quan trọng, quy mô công suất, quy mô kết cấu thì cấp công trình được xác định theo quy định của pháp luật tại thời điểm quyết định đầu tư; trường hợp công trình có điều chỉnh thiết kế xây dựng trước ngày 01 tháng 7 năm 2025 mà làm thay đổi về mức độ quan trọng, quy mô công suất, quy mô kết cấu thì cấp công trình được xác định theo quy định [...cắt bớt]
+4. Quy định chuyển tiếp đối với với nội dung quy định tại Điều 6 Thông tư này:
+a) Đối với công trình cấp nước có phạm vi cấp nước nằm trên địa giới hành chính của 02 đơn vị hành chính cấp xã trở lên, Ủy ban nhân dân cấp tỉnh là cơ quan có thẩm quyền trong thỏa thuận thực hiện dịch vụ cấp nước đã được ký kết với đơn vị cấp nước;
+b) Đối với công trình cấp nước có phạm vi cấp nước nằm trên địa giới hành chính của 01 đơn vị hành chính cấp xã, Ủy ban nhân dân cấp xã là cơ quan có thẩm quyền trong thỏa thuận thực hiện dịch vụ cấp nước đã được ký kết với đơn vị cấp nước.
+5. Quy định chuyển tiếp đối với nội dung quy định tại Điều 10 Thông tư này.
+a) Cấp công trình thuộc dự án đầu tư xây dựng đã được quyết định đầu tư trước ngày 01 tháng 7 năm 2025 được xác định theo quy định của pháp luật tại thời điểm quyết định đầu tư;
+b) Trường hợp dự án, công trình xây dựng đã trình cơ quan chuyên môn về xây dựng thẩm định hoặc thẩm định điều chỉnh Báo cáo nghiên cứu khả thi đầu tư xây dựng, thiết kế xây dựng triển khai sau thiết kế cơ sở trước ngày 01 tháng 7 năm 2025 và đủ điều kiện thẩm định thì việc xác định cấp công trình và áp dụng cấp công trình trong quản lý các hoạt động đầu tư xây dựng được xác định theo quy định của pháp luật tại thời điểm trình thẩm định;
+c) Trường hợp công trình có điều ch</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -7248,7 +9260,6 @@
           <t>06/2017/TT-NHNN; 21/2019/TT-NHNN</t>
         </is>
       </c>
-      <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
           <t>document_ended 2016-03-01 bao_dong_gia</t>
@@ -7264,18 +9275,49 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P81" t="inlineStr"/>
-      <c r="Q81" t="inlineStr"/>
       <c r="R81" t="inlineStr">
         <is>
           <t>id cũ vilextime:T3:provision:ceb9e5a6-df50-11f0-857c-4791e49360cb#k2#a:2015-06-02 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S81" t="inlineStr"/>
-      <c r="T81" t="inlineStr"/>
-      <c r="U81" t="inlineStr"/>
-      <c r="V81" t="inlineStr"/>
-      <c r="W81" t="inlineStr"/>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>04/2015/TT-NHNN · hiệu lực 2015-06-01 → 2024-07-01 · lúc thu thập: Hết hiệu lực toàn bộ
+Điều 31. Điều kiện để trở thành thành viên
+2. Đối với hộ gia đình:
+a) Là hộ gia đình có hộ khẩu thường trú trên địa bàn hoạt động của quỹ tín dụng nhân dân; các thành viên trong hộ có chung tài sản để phục vụ sản xuất, kinh doanh dịch vụ của hộ gia đình;
+b) Người đại diện của hộ gia đình phải được các thành viên của hộ gia đình ủy quyền đại diện bằng văn bản theo quy định của pháp luật và phải đảm bảo các điều kiện theo quy định tại khoản 1 Điều này.</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 06/2017/TT-NHNN · hiệu lực 2017-09-01
+3. Sửa đổi khoản 1, khoản 2 Điều 31 như sau:
+“1. Đối với cá nhân:
+a) Công dân Việt Nam đủ 18 tuổi trở lên, có năng lực hành vi dân sự đầy đủ, đăng ký thường trú trên địa bàn hoạt động của quỹ tín dụng nhân dân;
+b) Cán bộ, công chức, viên chức đang làm việc tại các tổ chức, cơ quan có trụ sở chính đóng trên địa bàn hoạt động của quỹ tín dụng nhân dân. Thành viên của quỹ tín dụng nhân dân là cán bộ, công chức, viên chức không được giữ các chức danh Chủ tịch và thành viên Hội đồng quản trị; Trưởng ban và thành viên Ban kiểm soát; Giám đốc, Phó giám đốc; Kế toán trưởng và các chức danh chuyên môn nghiệp vụ khác trừ trường hợp quy định tại điểm e khoản 2 Điều 20 Thông tư này;
+c) Không thuộc các đối tượng sau đây:
+(i) Đang bị truy cứu trách nhiệm hình sự, đang phải chấp hành bản án, quyết định về hình sự của tòa án; người đã bị kết án từ tội phạm nghiêm trọng trở lên mà chưa được xóa án tích;
+(ii) Cán bộ, công chức, viên chức làm việc ở những ngành, nghề có liên quan đến bí mật nhà nước theo quy định của pháp luật;
+(iii) Sỹ quan, hạ sỹ quan, quân nhân chuyên nghiệp trong các đơn vị lực lượng vũ trang nhân dân;
+d) Các điều kiện khác theo quy định của Điều lệ quỹ tín dụng nhân dân.
+2. Đối với hộ gia đình:
+a) Là hộ gia đình có các thành viên đăng ký thường trú trên địa bàn hoạt động của quỹ tín dụng nhân dân; các thành viên trong hộ có chung tài sản để phục vụ sản xuất, kinh doanh dịch vụ của hộ gia đình;
+b) Người đại diện của hộ gia đình phải được các thành viên của hộ gia đình ủy quyền đại diện bằng văn bản theo quy định của pháp luật và phải đảm bảo các điều kiện theo quy định tại khoản 1 Điều này”.
+[amend] 21/2019/TT-NHNN · hiệu lực 2020-01-01
+17. Khoản 1, khoản 2 Điều 31 được sửa đổi, bổ sung như sau:
+“1. Đối với cá nhân:
+a) Công dân Việt Nam đủ 18 tuổi trở lên, có năng lực hành vi dân sự đầy đủ, thường trú hoặc đăng ký tạm trú trên địa bàn hoạt động của quỹ tín dụng nhân dân. Trường hợp đăng ký tạm trú, cá nhân phải có hoạt động sản xuất, kinh doanh hoặc là người lao động làm việc trên địa bàn hoạt động của quỹ tín dụng nhân dân và phải có tài liệu chứng minh về vấn đề này;
+b) Cán bộ, công chức, viên chức đang làm việc tại các tổ chức, cơ quan có trụ sở chính đóng trên địa bàn hoạt động của quỹ tín dụng nhân dân. Thành viên của quỹ tín dụng nhân dân là cán bộ, công chức, viên chức không được giữ các chức danh Chủ tịch và thành viên Hội đồng quản trị; Trưởng Ban và thành viên Ban kiểm soát; Giám đốc, Phó giám đốc; Kế toán trưởng và các chức danh chuyên môn nghiệp vụ trừ trường hợp được chỉ định theo quy định tại khoản 4 Điều 20 và khoản 4 Điều 24 Thông tư này;
+c) Không thuộc các đối tượng sau đây:
+(i) Đang bị truy cứu trách nhiệm hình sự, đang phải chấp hành bản án, quyết định về hình sự của tòa án; người đã bị kết án từ tội phạm nghiêm trọng trở lên mà chưa được xóa án tích;
+(ii) Cán bộ, công chức, viên chức làm việc ở những ngành, nghề có liên quan đến bí mật nhà nước theo quy định của pháp luật;
+(iii) Sỹ quan, hạ sỹ quan, quân nhân chuyên nghiệp trong các đơn vị lực lượng vũ trang nhân dân.
+2. Đối với hộ gia đình:
+a) Là hộ gia đình có các thành viên thường trú trên địa bàn hoạt động của quỹ tín dụng nhân dân; các thành viên trong hộ có chung tài sản để phục vụ sản xuất, kinh doanh dịch vụ của hộ gia đình;
+b) Người đại diện của hộ gia đình phải được các thành viên của hộ gia đình ủy quyền đại diện bằng văn bản theo quy định của pháp luật và phải đảm bảo các điều kiện theo quy định tại khoản 1 Điều này.”</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -7333,7 +9375,6 @@
           <t>06/2017/TT-NHNN; 21/2019/TT-NHNN</t>
         </is>
       </c>
-      <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr">
         <is>
           <t>document_ended 2016-03-01 bao_dong_gia</t>
@@ -7349,18 +9390,49 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P82" t="inlineStr"/>
-      <c r="Q82" t="inlineStr"/>
       <c r="R82" t="inlineStr">
         <is>
           <t>id cũ vilextime:T3:provision:ceb9e5a6-df50-11f0-857c-4791e49360cb#k2#a:2020-01-02 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S82" t="inlineStr"/>
-      <c r="T82" t="inlineStr"/>
-      <c r="U82" t="inlineStr"/>
-      <c r="V82" t="inlineStr"/>
-      <c r="W82" t="inlineStr"/>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>04/2015/TT-NHNN · hiệu lực 2015-06-01 → 2024-07-01 · lúc thu thập: Hết hiệu lực toàn bộ
+Điều 31. Điều kiện để trở thành thành viên
+2. Đối với hộ gia đình:
+a) Là hộ gia đình có hộ khẩu thường trú trên địa bàn hoạt động của quỹ tín dụng nhân dân; các thành viên trong hộ có chung tài sản để phục vụ sản xuất, kinh doanh dịch vụ của hộ gia đình;
+b) Người đại diện của hộ gia đình phải được các thành viên của hộ gia đình ủy quyền đại diện bằng văn bản theo quy định của pháp luật và phải đảm bảo các điều kiện theo quy định tại khoản 1 Điều này.</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 06/2017/TT-NHNN · hiệu lực 2017-09-01
+3. Sửa đổi khoản 1, khoản 2 Điều 31 như sau:
+“1. Đối với cá nhân:
+a) Công dân Việt Nam đủ 18 tuổi trở lên, có năng lực hành vi dân sự đầy đủ, đăng ký thường trú trên địa bàn hoạt động của quỹ tín dụng nhân dân;
+b) Cán bộ, công chức, viên chức đang làm việc tại các tổ chức, cơ quan có trụ sở chính đóng trên địa bàn hoạt động của quỹ tín dụng nhân dân. Thành viên của quỹ tín dụng nhân dân là cán bộ, công chức, viên chức không được giữ các chức danh Chủ tịch và thành viên Hội đồng quản trị; Trưởng ban và thành viên Ban kiểm soát; Giám đốc, Phó giám đốc; Kế toán trưởng và các chức danh chuyên môn nghiệp vụ khác trừ trường hợp quy định tại điểm e khoản 2 Điều 20 Thông tư này;
+c) Không thuộc các đối tượng sau đây:
+(i) Đang bị truy cứu trách nhiệm hình sự, đang phải chấp hành bản án, quyết định về hình sự của tòa án; người đã bị kết án từ tội phạm nghiêm trọng trở lên mà chưa được xóa án tích;
+(ii) Cán bộ, công chức, viên chức làm việc ở những ngành, nghề có liên quan đến bí mật nhà nước theo quy định của pháp luật;
+(iii) Sỹ quan, hạ sỹ quan, quân nhân chuyên nghiệp trong các đơn vị lực lượng vũ trang nhân dân;
+d) Các điều kiện khác theo quy định của Điều lệ quỹ tín dụng nhân dân.
+2. Đối với hộ gia đình:
+a) Là hộ gia đình có các thành viên đăng ký thường trú trên địa bàn hoạt động của quỹ tín dụng nhân dân; các thành viên trong hộ có chung tài sản để phục vụ sản xuất, kinh doanh dịch vụ của hộ gia đình;
+b) Người đại diện của hộ gia đình phải được các thành viên của hộ gia đình ủy quyền đại diện bằng văn bản theo quy định của pháp luật và phải đảm bảo các điều kiện theo quy định tại khoản 1 Điều này”.
+[amend] 21/2019/TT-NHNN · hiệu lực 2020-01-01
+17. Khoản 1, khoản 2 Điều 31 được sửa đổi, bổ sung như sau:
+“1. Đối với cá nhân:
+a) Công dân Việt Nam đủ 18 tuổi trở lên, có năng lực hành vi dân sự đầy đủ, thường trú hoặc đăng ký tạm trú trên địa bàn hoạt động của quỹ tín dụng nhân dân. Trường hợp đăng ký tạm trú, cá nhân phải có hoạt động sản xuất, kinh doanh hoặc là người lao động làm việc trên địa bàn hoạt động của quỹ tín dụng nhân dân và phải có tài liệu chứng minh về vấn đề này;
+b) Cán bộ, công chức, viên chức đang làm việc tại các tổ chức, cơ quan có trụ sở chính đóng trên địa bàn hoạt động của quỹ tín dụng nhân dân. Thành viên của quỹ tín dụng nhân dân là cán bộ, công chức, viên chức không được giữ các chức danh Chủ tịch và thành viên Hội đồng quản trị; Trưởng Ban và thành viên Ban kiểm soát; Giám đốc, Phó giám đốc; Kế toán trưởng và các chức danh chuyên môn nghiệp vụ trừ trường hợp được chỉ định theo quy định tại khoản 4 Điều 20 và khoản 4 Điều 24 Thông tư này;
+c) Không thuộc các đối tượng sau đây:
+(i) Đang bị truy cứu trách nhiệm hình sự, đang phải chấp hành bản án, quyết định về hình sự của tòa án; người đã bị kết án từ tội phạm nghiêm trọng trở lên mà chưa được xóa án tích;
+(ii) Cán bộ, công chức, viên chức làm việc ở những ngành, nghề có liên quan đến bí mật nhà nước theo quy định của pháp luật;
+(iii) Sỹ quan, hạ sỹ quan, quân nhân chuyên nghiệp trong các đơn vị lực lượng vũ trang nhân dân.
+2. Đối với hộ gia đình:
+a) Là hộ gia đình có các thành viên thường trú trên địa bàn hoạt động của quỹ tín dụng nhân dân; các thành viên trong hộ có chung tài sản để phục vụ sản xuất, kinh doanh dịch vụ của hộ gia đình;
+b) Người đại diện của hộ gia đình phải được các thành viên của hộ gia đình ủy quyền đại diện bằng văn bản theo quy định của pháp luật và phải đảm bảo các điều kiện theo quy định tại khoản 1 Điều này.”</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -7423,7 +9495,6 @@
           <t>split_effective_date</t>
         </is>
       </c>
-      <c r="M83" t="inlineStr"/>
       <c r="N83" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -7434,18 +9505,57 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P83" t="inlineStr"/>
-      <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr">
         <is>
           <t>id cũ vilextime:T3:provision:d427a720-2d53-11f1-a1cc-67f2013d5aa0:2018-02-02 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S83" t="inlineStr"/>
-      <c r="T83" t="inlineStr"/>
-      <c r="U83" t="inlineStr"/>
-      <c r="V83" t="inlineStr"/>
-      <c r="W83" t="inlineStr"/>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>209/2013/NĐ-CP · hiệu lực 2014-01-01 → 2025-07-01 · lúc thu thập: Hết hiệu lực toàn bộ
+Điều 3. Đối tượng không chịu thuế
+11. Sản phẩm xuất khẩu là tài nguyên, khoáng sản khai thác chưa chế biến thành sản phẩm khác.
+Bộ Tài chính chủ trì, phối hợp với các cơ quan liên quan hướng dẫn cụ thể việc xác định tài nguyên, khoáng sản khai thác chưa được chế biến thành sản phẩm khác quy định tại Khoản này.</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 100/2016/NĐ-CP · hiệu lực 2016-07-01
+4. Khoản 11 Điều 3 được sửa đổi, bổ sung như sau:
+“11. Sản phẩm xuất khẩu là tài nguyên, khoáng sản khai thác chưa chế biến thành sản phẩm khác hoặc đã chế biến thành sản phẩm khác nhưng tổng trị giá tài nguyên, khoáng sản cộng với chi phí năng lượng chiếm từ 51% giá thành sản xuất sản phẩm trở lên được chế biến từ tài nguyên, khoáng sản; sản phẩm xuất khẩu là hàng hóa được chế biến từ tài nguyên, khoáng sản có tổng trị giá tài nguyên, khoáng sản cộng với chi phí năng lượng chiếm từ 51% giá thành sản xuất sản phẩm trở lên.
+Tài nguyên, khoáng sản quy định tại khoản này là tài nguyên, khoáng sản có nguồn gốc trong nước gồm: Khoáng sản kim loại; khoáng sản không kim loại; dầu thô; khí thiên nhiên; khí than.
+Trị giá tài nguyên, khoáng sản là giá vốn tài nguyên, khoáng sản đưa vào chế biến; đối với tài nguyên, khoáng sản trực tiếp khai thác là chi phí trực tiếp, gián tiếp khai thác ra tài nguyên khoáng sản; đối với tài nguyên, khoáng sản mua để chế biến là giá thực tế mua cộng chi phí đưa tài nguyên, khoáng sản vào chế biến.
+Chi phí năng lượng gồm: Nhiên liệu, điện năng, nhiệt năng.
+Việc xác định trị giá tài nguyên, khoáng sản và chi phí năng lượng căn cứ vào quyết toán năm trước; trường hợp doanh nghiệp mới thành lập chưa có báo cáo quyết toán năm trước thì căn cứ vào phương án đầu tư.
+Bộ Tài chính quy định chi tiết khoản này.”
+5. Điểm đ khoản 1 Điều 6 được sửa đổi như sau:
+“đ) Các trường hợp không áp dụng mức thuế suất thuế giá trị gia tăng 0% gồm:
+- Chuyển giao công nghệ, chuyển nhượng quyền sở hữu trí tuệ ra nước ngoài;
+- Dịch vụ tái bảo hiểm ra nước ngoài;
+- Dịch vụ cấp tín dụng ra nước ngoài;
+- Chuyển nhượng vốn ra nước ngoài;
+- Đầu tư chứng khoán ra nước ngoài;
+- Dịch vụ tài chính phái sinh;
+- Dịch vụ bưu chính, viễn thông;
+- Sản phẩm xuất khẩu quy định tại khoản 11 Điều 3 Nghị định này;
+- Hàng hóa, dịch vụ cung cấp cho cá nhân không đăng ký kinh doanh trong khu phi thuế quan;
+- Thuốc lá, rượu, bia nhập khẩu sau đó xuất khẩu.”
+6. Điều 10 được sửa đổi, bổ sung như sau:
+“Điều 10. Hoàn thuế giá trị gia tăng
+1. Cơ sở kinh doanh nộp thuế giá trị gia tăng theo phương pháp khấu trừ thuế nếu có số thuế giá trị gia tăng đầu vào chưa được khấu trừ hết trong tháng (đối với trường hợp kê khai theo tháng) hoặc trong quý (đối với trường hợp kê khai theo quý) thì được khấu trừ vào kỳ tiếp theo.
+2. Cơ sở kinh doanh được hoàn thuế đối với dự án đầu tư như sau:
+a) Cơ sở kinh doanh mới thành lập từ dự án đầu tư đã đăng ký kinh doanh, đăng ký nộp thuế giá trị gia tăng theo phương pháp khấu trừ, hoặc dự án tìm kiếm thăm dò và phát triển mỏ dầu khí đang trong giai đoạn đầu tư, chưa đi vào hoạt động, nếu thời gian đầu tư từ 01 năm trở lên thì được hoàn thuế giá trị gia tăng của hàng hóa, dịch vụ sử dụng cho đầu tư theo từng năm, trừ trường hợp quy định tại điểm c khoản này. Trường hợp, nếu số thuế giá trị gia tăng lũy kế của hàng hóa, dịch vụ mua vào sử dụng cho đầu tư từ 300 triệu đồng trở lên thì được hoàn thuế giá trị gia tăng.
+Trường hợp dự án đầu tư của cơ sở kinh doanh đã được cơ quan nhà nước có thẩm quyền thanh tra, kiểm tra, kiểm toán thì cơ quan thuế có thể sử dụng kết quả thanh tra, kiểm tra, kiểm toán để quyết định việc hoàn thuế giá trị gia tăng và phải chịu trách nhiệm về quyết định của mình.
+b) Cơ sở kinh doanh đang hoạt động thuộc đối tượng nộp thuế giá trị gia tăng theo phương pháp khấu trừ có dự án đầu tư mới (trừ dự án đầu tư xây dựng nhà để bán) tại địa bàn tỉnh, thành phố trực thuộc trung ương khác với tỉnh, thành phố nơi đóng trụ sở chính, đang trong giai đoạn đầu tư chưa đi vào hoạt động, chưa đăng ký kinh doanh, chưa đăng ký thuế thì số thuế giá trị gia tăng đầu vào bù trừ với số thuế giá trị gia tăng phải nộp của hoạt động sản xuất kinh doanh tại trụ sở chính, sau khi bù trừ nếu số thuế giá trị gia tăng của hàng hóa, dịch vụ mua vào sử dụng cho đầu tư còn lại từ 300 triệu đồng trở lên thì được hoàn thuế giá trị gia tăng cho dự án đầu tư, trừ trường hợp quy định tại điểm c khoản này. Cơ sở kinh doanh phải kê khai, lập hồ sơ hoàn thuế riêng đối với dự án đầu tư.
+c) Cơ sở kinh doanh không được hoàn thuế giá trị gia tăng mà được kết chuyển số thuế chưa được khấu trừ của dự án đầu tư theo pháp luật về đầu tư sang kỳ tiếp theo đối với các trường hợp:
+- Dự án đầu tư của cơ sở kinh doanh ngành, nghề đầu tư kinh doanh có điều kiện khi chưa đủ các điều kiện kinh doanh theo quy định của Luật đầu tư quy định tại điểm a khoản 1 Điều 13 Luật thuế giá trị gia tăng đã được sửa đổi, bổ sung tại Luật sửa đổi, bổ sung một số điều của Luật thuế giá trị gia tăng, Luật thuế tiêu thụ đặc biệt và Luật quản lý thuế là dự án đầu tư của cơ sở kinh doanh ngành, nghề đầu tư kinh doanh có điều kiện nhưng cơ sở kinh doanh chưa được cấp giấy phép kinh doanh ngành, nghề đầu tư kinh doanh có điều kiện; chưa được cấp giấy chứng nhận đủ điều kiện kinh doanh ngành, nghề đầu tư kinh doanh có điều kiện; chưa có văn bản của cơ quan nhà nước có thẩm quyền cho phép đầu tư kinh doanh ngành, nghề đầu tư kinh doanh có điều kiện; hoặc chưa đáp ứng  [...cắt bớt]
+[amend] 146/2017/NĐ-CP · hiệu lực 2018-02-01
+1. Khoản 11 Điều 3 được sửa đổi, bổ sung như sau:
+“11. Sản phẩm xuất khẩu là tài nguyên, khoáng sản khai thác chưa chế biến thành sản phẩm khác.
+Sản phẩm xuất khẩu là hàng hóa được chế biến trực tiếp từ nguyên liệu chính là tài nguyên, khoáng sản có tổng trị giá tài nguyên, khoáng sản cộng với chi phí năng lượng chiếm từ 51% giá thành sản xuất sản phẩm trở lên trừ các trường hợp sau:
+- Sản phẩm xuất khẩu được chế biến từ tài nguyên, khoáng sản do cơ sở kinh doanh trực tiếp khai thác và chế biến hoặc thuê cơ sở khác chế biến mà trong quy trình chế biến đã thành sản phẩm khác sau đó lại tiếp tục chế biến ra sản phẩm xuất khẩu (quy trình chế biến khép kín hoặc thành lập phân xưởng, nhà máy chế biến theo từng công đoạn) thì sản phẩm xuất khẩu này thuộc đối tượng áp dụng thuế suất thuế giá trị gia tăng 0% nếu đáp ứng được các điều kiện theo quy định tại điểm c khoản 2 Điều 12 Luật thuế g</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -7508,7 +9618,6 @@
           <t>actor_has_transitional</t>
         </is>
       </c>
-      <c r="M84" t="inlineStr"/>
       <c r="N84" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -7519,18 +9628,50 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P84" t="inlineStr"/>
-      <c r="Q84" t="inlineStr"/>
       <c r="R84" t="inlineStr">
         <is>
           <t>Khoản 1 áp cho công ty luật TNHH hai thành viên trở lên và công ty luật hợp danh; khoản 2 là văn phòng luật sư, công ty luật TNHH một thành viên — audit xem câu hỏi 'công ty luật' có cần nêu loại hình; id cũ vilextime:T3:provision:db5da940-2d53-11f1-b8ea-772cb5c62cab:2013-11-29 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S84" t="inlineStr"/>
-      <c r="T84" t="inlineStr"/>
-      <c r="U84" t="inlineStr"/>
-      <c r="V84" t="inlineStr"/>
-      <c r="W84" t="inlineStr"/>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>123/2013/NĐ-CP · hiệu lực 2013-11-28 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 11. Thay đổi người đại diện theo pháp luật của tổ chức hành nghề luật sư
+1. Người đại diện theo pháp luật của công ty luật trách nhiệm hữu hạn hai thành viên trở lên, công ty luật hợp danh phải là luật sư và là thành viên của công ty luật.
+Công ty luật trách nhiệm hữu hạn hai thành viên trở lên và công ty luật hợp danh thay đổi người đại diện theo pháp luật thì trong thời hạn 10 ngày, kể từ ngày quyết định thay đổi, phải gửi văn bản đề nghị thay đổi người đại diện theo pháp luật và Giấy đăng ký hoạt động của công ty luật đến Sở Tư pháp nơi đăng ký hoạt động.
+Thủ tục thay đổi người đại diện theo pháp luật của công ty luật trách nhiệm hữu hạn hai thành viên trở lên, công ty luật hợp doanh được thực hiện theo quy định tại Điều 36 của Luật Luật sư.</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[amend] 112/2025/NĐ-CP · hiệu lực 2025-05-29
+2. Sửa đổi, bổ sung khoản 1 và khoản 2 Điều 11 như sau:
+“1. Người đại diện theo pháp luật của công ty luật trách nhiệm hữu hạn hai thành viên trở lên, công ty luật hợp danh phải là luật sư và là thành viên của công ty luật.
+Công ty luật trách nhiệm hữu hạn hai thành viên trở lên và công ty luật hợp danh thay đổi người đại diện theo pháp luật thì trong thời hạn 10 ngày kể từ ngày quyết định thay đổi, phải đề nghị thay đổi người đại diện theo pháp luật và Giấy đăng ký hoạt động của công ty luật qua dịch vụ bưu chính hoặc trực tiếp đến Sở Tư pháp tỉnh, thành phố trực thuộc trung ương nơi đăng ký hoạt động hoặc trực tuyến trên Cổng Dịch vụ công quốc gia.
+2. Người đại diện theo pháp luật của văn phòng luật sư, công ty luật trách nhiệm hữu hạn một thành viên phải là luật sư chủ sở hữu của văn phòng luật sư, công ty luật.
+Văn phòng luật sư, công ty luật trách nhiệm hữu hạn một thành viên thay đổi người đại diện theo pháp luật thì trong thời hạn 10 ngày kể từ ngày quyết định thay đổi, phải gửi hồ sơ qua dịch vụ bưu chính hoặc trực tiếp đến Sở Tư pháp tỉnh, thành phố trực thuộc trung ương nơi đăng ký hoạt động hoặc trực tuyến trên Cổng Dịch vụ công quốc gia. Hồ sơ gồm 01 bộ:
+a) Giấy đề nghị thay đổi người đại diện theo pháp luật;
+b) Bản chính hoặc bản sao điện tử văn bản thỏa thuận giữa người đại diện theo pháp luật cũ và người dự kiến là đại diện theo pháp luật đối với việc thực hiện các quyền, nghĩa vụ của văn phòng luật sư, công ty luật;
+c) Bản sao kèm bàn chính để đối chiếu hoặc bản sao điện tử hoặc bản sao điện tử có chứng thực từ bản chính hoặc bản sao có chứng thực Thẻ luật sư của người dự kiến là đại diện theo pháp luật.
+Thủ tục thay đổi người đại diện theo pháp luật của văn phòng luật sư, công ty luật trách nhiệm hữu hạn một thành viên được thực hiện theo quy định tại Điều 36 của Luật Luật sư.”.
+CHUYỂN TIẾP: Điều 5. Quy định chuyển tiếp
+1. Trường hợp trước ngày Nghị định này có hiệu lực thi hành, cơ quan có thẩm quyền đã tiếp nhận hồ sơ quy định tại khoản này thì tiếp tục thực hiện theo quy định của văn bản quy phạm pháp luật tại thời điểm tiếp nhận hồ sơ, bao gồm các hồ sơ sau đây:
+a) Cấp, cấp lại, thay đổi nội dung, thu hồi Giấy phép thành lập, Giấy đăng ký hoạt động của Trung tâm trọng tài, Chi nhánh, Văn phòng đại diện của tổ chức trọng tài nước ngoài tại Việt Nam; đăng ký hoạt động, chấm dứt hoạt động của Trung tâm trọng tài, Chi nhánh, Văn phòng đại diện của tổ chức trọng tài nước ngoài tại Việt Nam;
+b) Cấp, cấp lại, thay đổi nội dung, thu hồi Giấy phép thành lập, Giấy đăng ký hoạt động của Trung tâm hoà giải thương mại, Giấy phép thành lập Chi nhánh, Văn phòng đại diện của tổ chức hoà giải thương mại nước ngoài tại Việt Nam; đăng ký hoạt động, chấm dứt hoạt động của Trung tâm hoà giải thương mại, Chi nhánh, Văn phòng đại diện của tổ chức hoà giải thương mại nước ngoài tại Việt Nam;
+c) Cấp, cấp lại, thu hồi Chứng chỉ hành nghề Quản tài viên; đăng ký hành nghề quản lý, thanh lý tài sản với tư cách cá nhân, đối với doanh nghiệp quản lý, thanh lý tài sản;
+d) Thay đổi người đại diện theo pháp luật của văn phòng luật sư, công ty luật trách nhiệm hữu hạn một thành viên, công ty luật trách nhiệm hữu hạn hai thành viên trở lên, công ty luật hợp danh; nội dung Giấy phép thành lập chi nhánh, công ty luật nước ngoài;
+đ) Hợp nhất, sáp nhập, chuyển đổi công ty luật; chuyển đổi văn phòng luật sư; chuyển đổi chi nhánh của tổ chức hành nghề luật sư nước ngoài tại Việt Nam, công ty luật nước ngoài.
+2. Trường hợp cấp lại, thay đổi, thu hồi Giấy phép thành lập Trung tâm hoà giải thương mại, Giấy phép thành lập Chi nhánh, Văn phòng đại diện của tổ chức hoà giải thương mại nước ngoài tại Việt Nam do Bộ Tư pháp cấp trước ngày Nghị định này có hiệu lực thi hành thì Chủ tịch Ủy ban nhân dân tỉnh, thành phố trực thuộc trung ương nơi Trung tâm hoà giải thương mại, Chi nhánh, Văn phòng đại diện của tổ chức hoà giải thương mại nước ngoài tại Việt Nam đặt trụ sở có thẩm quyền cấp lại, thay đổi, thu hồi Giấy phép thành lập trung tâm hoà giải thương mại, Giấy phép thành lập Chi nhánh, Văn phòng đại diện của tổ chức hoà giải thương mại nước ngoài tại Việt Nam đó theo quy định của Nghị định này.
+3. Trường hợp cấp lại, thu hồi chứng chỉ hành nghề Quản tài viên do Bộ Tư pháp cấp trước ngày Nghị định này có hiệu lực thi hành thì Chủ tịch Ủy ban nhân dân tỉnh, thành phố trực thuộc trung ương nơi người được cấp chứng chỉ hành nghề quản tài viên thường trú có thẩm quyền cấp lại, thu hồi chứng chỉ hành nghề Quản tài viên đó theo quy định của Nghị định này.
+4. Trường hợp hồ sơ thay đổi người đại diện theo pháp luật của tổ chức hành nghề luật sư, hợp nhất, sáp nhập công ty luật, chuyển đổi công ty luật, chuyển đổi văn phòng luật sư thành công ty luật, hợp nhất, sáp nhập công ty luật nước ngoài, chuyển đổi chi nhánh của tổ chức hành nghề luật sư nước ngoài thành công ty luật trách nhiệm hữu hạn 100% vốn nước ngoài tại Việt Nam, chuyển đổi công ty luật nước ngoài thành công ty luật Việt Nam, đăng ký thay đổi nội dung Giấy phép thành lập chi nhánh, công ty luật nước ngoài đã được cơ quan có thẩm quyền tiếp nhận trước ngày Nghị định này có hiệu lực thi hành thì cơ quan có thẩm quyền đã tiếp nhận hồ sơ tiếp tục thực hiện theo quy định của văn bản quy phạm pháp luật tại thời điểm tiếp nhận hồ sơ.
+[amend] 18/2026/NĐ-CP · hiệu lực 2026-01-15
+b) Thay thế cụm từ “trong thời hạn 10 ngày” thành “trong thời hạn 08 ngày làm việc” tại khoản 1 và khoản 2 Điều 11, khoản 2 Điều 23a;
+CHUYỂN TIẾP: Điều 16. Điều khoản chuyển tiếp
+1. Đối với hồ sơ đề nghị giải quyết thủ tục hành chính được quy định tại các Điều 1, 2, 3, 4, 5, 6, 7, 8, 9, 10 và 12 Nghị định này đã được cơ quan có thẩm quyền tiếp nhận hoặc đã được đóng dấu bưu chính trước ngày Nghị định này có hiệu lực thì thực hiện theo quy định của pháp luật đang có hiệu lực điều chỉnh trong lĩnh vực đó tại thời điểm hồ sơ được tiếp nhận.
+2. Đối với các hồ sơ đề nghị giải quyết thủ tục hành chính quy định tại Điều 11 Nghị định này:
+a) Trường hợp hồ </t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -7593,7 +9734,6 @@
           <t>actor_has_transitional</t>
         </is>
       </c>
-      <c r="M85" t="inlineStr"/>
       <c r="N85" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -7604,18 +9744,50 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P85" t="inlineStr"/>
-      <c r="Q85" t="inlineStr"/>
       <c r="R85" t="inlineStr">
         <is>
           <t>Khoản 1 áp cho công ty luật TNHH hai thành viên trở lên và công ty luật hợp danh; khoản 2 là văn phòng luật sư, công ty luật TNHH một thành viên — audit xem câu hỏi 'công ty luật' có cần nêu loại hình; id cũ vilextime:T3:provision:db5da940-2d53-11f1-b8ea-772cb5c62cab:2025-05-30 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S85" t="inlineStr"/>
-      <c r="T85" t="inlineStr"/>
-      <c r="U85" t="inlineStr"/>
-      <c r="V85" t="inlineStr"/>
-      <c r="W85" t="inlineStr"/>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>123/2013/NĐ-CP · hiệu lực 2013-11-28 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 11. Thay đổi người đại diện theo pháp luật của tổ chức hành nghề luật sư
+1. Người đại diện theo pháp luật của công ty luật trách nhiệm hữu hạn hai thành viên trở lên, công ty luật hợp danh phải là luật sư và là thành viên của công ty luật.
+Công ty luật trách nhiệm hữu hạn hai thành viên trở lên và công ty luật hợp danh thay đổi người đại diện theo pháp luật thì trong thời hạn 10 ngày, kể từ ngày quyết định thay đổi, phải gửi văn bản đề nghị thay đổi người đại diện theo pháp luật và Giấy đăng ký hoạt động của công ty luật đến Sở Tư pháp nơi đăng ký hoạt động.
+Thủ tục thay đổi người đại diện theo pháp luật của công ty luật trách nhiệm hữu hạn hai thành viên trở lên, công ty luật hợp doanh được thực hiện theo quy định tại Điều 36 của Luật Luật sư.</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[amend] 112/2025/NĐ-CP · hiệu lực 2025-05-29
+2. Sửa đổi, bổ sung khoản 1 và khoản 2 Điều 11 như sau:
+“1. Người đại diện theo pháp luật của công ty luật trách nhiệm hữu hạn hai thành viên trở lên, công ty luật hợp danh phải là luật sư và là thành viên của công ty luật.
+Công ty luật trách nhiệm hữu hạn hai thành viên trở lên và công ty luật hợp danh thay đổi người đại diện theo pháp luật thì trong thời hạn 10 ngày kể từ ngày quyết định thay đổi, phải đề nghị thay đổi người đại diện theo pháp luật và Giấy đăng ký hoạt động của công ty luật qua dịch vụ bưu chính hoặc trực tiếp đến Sở Tư pháp tỉnh, thành phố trực thuộc trung ương nơi đăng ký hoạt động hoặc trực tuyến trên Cổng Dịch vụ công quốc gia.
+2. Người đại diện theo pháp luật của văn phòng luật sư, công ty luật trách nhiệm hữu hạn một thành viên phải là luật sư chủ sở hữu của văn phòng luật sư, công ty luật.
+Văn phòng luật sư, công ty luật trách nhiệm hữu hạn một thành viên thay đổi người đại diện theo pháp luật thì trong thời hạn 10 ngày kể từ ngày quyết định thay đổi, phải gửi hồ sơ qua dịch vụ bưu chính hoặc trực tiếp đến Sở Tư pháp tỉnh, thành phố trực thuộc trung ương nơi đăng ký hoạt động hoặc trực tuyến trên Cổng Dịch vụ công quốc gia. Hồ sơ gồm 01 bộ:
+a) Giấy đề nghị thay đổi người đại diện theo pháp luật;
+b) Bản chính hoặc bản sao điện tử văn bản thỏa thuận giữa người đại diện theo pháp luật cũ và người dự kiến là đại diện theo pháp luật đối với việc thực hiện các quyền, nghĩa vụ của văn phòng luật sư, công ty luật;
+c) Bản sao kèm bàn chính để đối chiếu hoặc bản sao điện tử hoặc bản sao điện tử có chứng thực từ bản chính hoặc bản sao có chứng thực Thẻ luật sư của người dự kiến là đại diện theo pháp luật.
+Thủ tục thay đổi người đại diện theo pháp luật của văn phòng luật sư, công ty luật trách nhiệm hữu hạn một thành viên được thực hiện theo quy định tại Điều 36 của Luật Luật sư.”.
+CHUYỂN TIẾP: Điều 5. Quy định chuyển tiếp
+1. Trường hợp trước ngày Nghị định này có hiệu lực thi hành, cơ quan có thẩm quyền đã tiếp nhận hồ sơ quy định tại khoản này thì tiếp tục thực hiện theo quy định của văn bản quy phạm pháp luật tại thời điểm tiếp nhận hồ sơ, bao gồm các hồ sơ sau đây:
+a) Cấp, cấp lại, thay đổi nội dung, thu hồi Giấy phép thành lập, Giấy đăng ký hoạt động của Trung tâm trọng tài, Chi nhánh, Văn phòng đại diện của tổ chức trọng tài nước ngoài tại Việt Nam; đăng ký hoạt động, chấm dứt hoạt động của Trung tâm trọng tài, Chi nhánh, Văn phòng đại diện của tổ chức trọng tài nước ngoài tại Việt Nam;
+b) Cấp, cấp lại, thay đổi nội dung, thu hồi Giấy phép thành lập, Giấy đăng ký hoạt động của Trung tâm hoà giải thương mại, Giấy phép thành lập Chi nhánh, Văn phòng đại diện của tổ chức hoà giải thương mại nước ngoài tại Việt Nam; đăng ký hoạt động, chấm dứt hoạt động của Trung tâm hoà giải thương mại, Chi nhánh, Văn phòng đại diện của tổ chức hoà giải thương mại nước ngoài tại Việt Nam;
+c) Cấp, cấp lại, thu hồi Chứng chỉ hành nghề Quản tài viên; đăng ký hành nghề quản lý, thanh lý tài sản với tư cách cá nhân, đối với doanh nghiệp quản lý, thanh lý tài sản;
+d) Thay đổi người đại diện theo pháp luật của văn phòng luật sư, công ty luật trách nhiệm hữu hạn một thành viên, công ty luật trách nhiệm hữu hạn hai thành viên trở lên, công ty luật hợp danh; nội dung Giấy phép thành lập chi nhánh, công ty luật nước ngoài;
+đ) Hợp nhất, sáp nhập, chuyển đổi công ty luật; chuyển đổi văn phòng luật sư; chuyển đổi chi nhánh của tổ chức hành nghề luật sư nước ngoài tại Việt Nam, công ty luật nước ngoài.
+2. Trường hợp cấp lại, thay đổi, thu hồi Giấy phép thành lập Trung tâm hoà giải thương mại, Giấy phép thành lập Chi nhánh, Văn phòng đại diện của tổ chức hoà giải thương mại nước ngoài tại Việt Nam do Bộ Tư pháp cấp trước ngày Nghị định này có hiệu lực thi hành thì Chủ tịch Ủy ban nhân dân tỉnh, thành phố trực thuộc trung ương nơi Trung tâm hoà giải thương mại, Chi nhánh, Văn phòng đại diện của tổ chức hoà giải thương mại nước ngoài tại Việt Nam đặt trụ sở có thẩm quyền cấp lại, thay đổi, thu hồi Giấy phép thành lập trung tâm hoà giải thương mại, Giấy phép thành lập Chi nhánh, Văn phòng đại diện của tổ chức hoà giải thương mại nước ngoài tại Việt Nam đó theo quy định của Nghị định này.
+3. Trường hợp cấp lại, thu hồi chứng chỉ hành nghề Quản tài viên do Bộ Tư pháp cấp trước ngày Nghị định này có hiệu lực thi hành thì Chủ tịch Ủy ban nhân dân tỉnh, thành phố trực thuộc trung ương nơi người được cấp chứng chỉ hành nghề quản tài viên thường trú có thẩm quyền cấp lại, thu hồi chứng chỉ hành nghề Quản tài viên đó theo quy định của Nghị định này.
+4. Trường hợp hồ sơ thay đổi người đại diện theo pháp luật của tổ chức hành nghề luật sư, hợp nhất, sáp nhập công ty luật, chuyển đổi công ty luật, chuyển đổi văn phòng luật sư thành công ty luật, hợp nhất, sáp nhập công ty luật nước ngoài, chuyển đổi chi nhánh của tổ chức hành nghề luật sư nước ngoài thành công ty luật trách nhiệm hữu hạn 100% vốn nước ngoài tại Việt Nam, chuyển đổi công ty luật nước ngoài thành công ty luật Việt Nam, đăng ký thay đổi nội dung Giấy phép thành lập chi nhánh, công ty luật nước ngoài đã được cơ quan có thẩm quyền tiếp nhận trước ngày Nghị định này có hiệu lực thi hành thì cơ quan có thẩm quyền đã tiếp nhận hồ sơ tiếp tục thực hiện theo quy định của văn bản quy phạm pháp luật tại thời điểm tiếp nhận hồ sơ.
+[amend] 18/2026/NĐ-CP · hiệu lực 2026-01-15
+b) Thay thế cụm từ “trong thời hạn 10 ngày” thành “trong thời hạn 08 ngày làm việc” tại khoản 1 và khoản 2 Điều 11, khoản 2 Điều 23a;
+CHUYỂN TIẾP: Điều 16. Điều khoản chuyển tiếp
+1. Đối với hồ sơ đề nghị giải quyết thủ tục hành chính được quy định tại các Điều 1, 2, 3, 4, 5, 6, 7, 8, 9, 10 và 12 Nghị định này đã được cơ quan có thẩm quyền tiếp nhận hoặc đã được đóng dấu bưu chính trước ngày Nghị định này có hiệu lực thì thực hiện theo quy định của pháp luật đang có hiệu lực điều chỉnh trong lĩnh vực đó tại thời điểm hồ sơ được tiếp nhận.
+2. Đối với các hồ sơ đề nghị giải quyết thủ tục hành chính quy định tại Điều 11 Nghị định này:
+a) Trường hợp hồ </t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -7678,7 +9850,6 @@
           <t>actor_has_transitional</t>
         </is>
       </c>
-      <c r="M86" t="inlineStr"/>
       <c r="N86" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -7689,18 +9860,50 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P86" t="inlineStr"/>
-      <c r="Q86" t="inlineStr"/>
       <c r="R86" t="inlineStr">
         <is>
           <t>Khoản 1 áp cho công ty luật TNHH hai thành viên trở lên và công ty luật hợp danh; khoản 2 là văn phòng luật sư, công ty luật TNHH một thành viên — audit xem câu hỏi 'công ty luật' có cần nêu loại hình; id cũ vilextime:T3:provision:db5da940-2d53-11f1-b8ea-772cb5c62cab:2026-01-16 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S86" t="inlineStr"/>
-      <c r="T86" t="inlineStr"/>
-      <c r="U86" t="inlineStr"/>
-      <c r="V86" t="inlineStr"/>
-      <c r="W86" t="inlineStr"/>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>123/2013/NĐ-CP · hiệu lực 2013-11-28 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 11. Thay đổi người đại diện theo pháp luật của tổ chức hành nghề luật sư
+1. Người đại diện theo pháp luật của công ty luật trách nhiệm hữu hạn hai thành viên trở lên, công ty luật hợp danh phải là luật sư và là thành viên của công ty luật.
+Công ty luật trách nhiệm hữu hạn hai thành viên trở lên và công ty luật hợp danh thay đổi người đại diện theo pháp luật thì trong thời hạn 10 ngày, kể từ ngày quyết định thay đổi, phải gửi văn bản đề nghị thay đổi người đại diện theo pháp luật và Giấy đăng ký hoạt động của công ty luật đến Sở Tư pháp nơi đăng ký hoạt động.
+Thủ tục thay đổi người đại diện theo pháp luật của công ty luật trách nhiệm hữu hạn hai thành viên trở lên, công ty luật hợp doanh được thực hiện theo quy định tại Điều 36 của Luật Luật sư.</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">[amend] 112/2025/NĐ-CP · hiệu lực 2025-05-29
+2. Sửa đổi, bổ sung khoản 1 và khoản 2 Điều 11 như sau:
+“1. Người đại diện theo pháp luật của công ty luật trách nhiệm hữu hạn hai thành viên trở lên, công ty luật hợp danh phải là luật sư và là thành viên của công ty luật.
+Công ty luật trách nhiệm hữu hạn hai thành viên trở lên và công ty luật hợp danh thay đổi người đại diện theo pháp luật thì trong thời hạn 10 ngày kể từ ngày quyết định thay đổi, phải đề nghị thay đổi người đại diện theo pháp luật và Giấy đăng ký hoạt động của công ty luật qua dịch vụ bưu chính hoặc trực tiếp đến Sở Tư pháp tỉnh, thành phố trực thuộc trung ương nơi đăng ký hoạt động hoặc trực tuyến trên Cổng Dịch vụ công quốc gia.
+2. Người đại diện theo pháp luật của văn phòng luật sư, công ty luật trách nhiệm hữu hạn một thành viên phải là luật sư chủ sở hữu của văn phòng luật sư, công ty luật.
+Văn phòng luật sư, công ty luật trách nhiệm hữu hạn một thành viên thay đổi người đại diện theo pháp luật thì trong thời hạn 10 ngày kể từ ngày quyết định thay đổi, phải gửi hồ sơ qua dịch vụ bưu chính hoặc trực tiếp đến Sở Tư pháp tỉnh, thành phố trực thuộc trung ương nơi đăng ký hoạt động hoặc trực tuyến trên Cổng Dịch vụ công quốc gia. Hồ sơ gồm 01 bộ:
+a) Giấy đề nghị thay đổi người đại diện theo pháp luật;
+b) Bản chính hoặc bản sao điện tử văn bản thỏa thuận giữa người đại diện theo pháp luật cũ và người dự kiến là đại diện theo pháp luật đối với việc thực hiện các quyền, nghĩa vụ của văn phòng luật sư, công ty luật;
+c) Bản sao kèm bàn chính để đối chiếu hoặc bản sao điện tử hoặc bản sao điện tử có chứng thực từ bản chính hoặc bản sao có chứng thực Thẻ luật sư của người dự kiến là đại diện theo pháp luật.
+Thủ tục thay đổi người đại diện theo pháp luật của văn phòng luật sư, công ty luật trách nhiệm hữu hạn một thành viên được thực hiện theo quy định tại Điều 36 của Luật Luật sư.”.
+CHUYỂN TIẾP: Điều 5. Quy định chuyển tiếp
+1. Trường hợp trước ngày Nghị định này có hiệu lực thi hành, cơ quan có thẩm quyền đã tiếp nhận hồ sơ quy định tại khoản này thì tiếp tục thực hiện theo quy định của văn bản quy phạm pháp luật tại thời điểm tiếp nhận hồ sơ, bao gồm các hồ sơ sau đây:
+a) Cấp, cấp lại, thay đổi nội dung, thu hồi Giấy phép thành lập, Giấy đăng ký hoạt động của Trung tâm trọng tài, Chi nhánh, Văn phòng đại diện của tổ chức trọng tài nước ngoài tại Việt Nam; đăng ký hoạt động, chấm dứt hoạt động của Trung tâm trọng tài, Chi nhánh, Văn phòng đại diện của tổ chức trọng tài nước ngoài tại Việt Nam;
+b) Cấp, cấp lại, thay đổi nội dung, thu hồi Giấy phép thành lập, Giấy đăng ký hoạt động của Trung tâm hoà giải thương mại, Giấy phép thành lập Chi nhánh, Văn phòng đại diện của tổ chức hoà giải thương mại nước ngoài tại Việt Nam; đăng ký hoạt động, chấm dứt hoạt động của Trung tâm hoà giải thương mại, Chi nhánh, Văn phòng đại diện của tổ chức hoà giải thương mại nước ngoài tại Việt Nam;
+c) Cấp, cấp lại, thu hồi Chứng chỉ hành nghề Quản tài viên; đăng ký hành nghề quản lý, thanh lý tài sản với tư cách cá nhân, đối với doanh nghiệp quản lý, thanh lý tài sản;
+d) Thay đổi người đại diện theo pháp luật của văn phòng luật sư, công ty luật trách nhiệm hữu hạn một thành viên, công ty luật trách nhiệm hữu hạn hai thành viên trở lên, công ty luật hợp danh; nội dung Giấy phép thành lập chi nhánh, công ty luật nước ngoài;
+đ) Hợp nhất, sáp nhập, chuyển đổi công ty luật; chuyển đổi văn phòng luật sư; chuyển đổi chi nhánh của tổ chức hành nghề luật sư nước ngoài tại Việt Nam, công ty luật nước ngoài.
+2. Trường hợp cấp lại, thay đổi, thu hồi Giấy phép thành lập Trung tâm hoà giải thương mại, Giấy phép thành lập Chi nhánh, Văn phòng đại diện của tổ chức hoà giải thương mại nước ngoài tại Việt Nam do Bộ Tư pháp cấp trước ngày Nghị định này có hiệu lực thi hành thì Chủ tịch Ủy ban nhân dân tỉnh, thành phố trực thuộc trung ương nơi Trung tâm hoà giải thương mại, Chi nhánh, Văn phòng đại diện của tổ chức hoà giải thương mại nước ngoài tại Việt Nam đặt trụ sở có thẩm quyền cấp lại, thay đổi, thu hồi Giấy phép thành lập trung tâm hoà giải thương mại, Giấy phép thành lập Chi nhánh, Văn phòng đại diện của tổ chức hoà giải thương mại nước ngoài tại Việt Nam đó theo quy định của Nghị định này.
+3. Trường hợp cấp lại, thu hồi chứng chỉ hành nghề Quản tài viên do Bộ Tư pháp cấp trước ngày Nghị định này có hiệu lực thi hành thì Chủ tịch Ủy ban nhân dân tỉnh, thành phố trực thuộc trung ương nơi người được cấp chứng chỉ hành nghề quản tài viên thường trú có thẩm quyền cấp lại, thu hồi chứng chỉ hành nghề Quản tài viên đó theo quy định của Nghị định này.
+4. Trường hợp hồ sơ thay đổi người đại diện theo pháp luật của tổ chức hành nghề luật sư, hợp nhất, sáp nhập công ty luật, chuyển đổi công ty luật, chuyển đổi văn phòng luật sư thành công ty luật, hợp nhất, sáp nhập công ty luật nước ngoài, chuyển đổi chi nhánh của tổ chức hành nghề luật sư nước ngoài thành công ty luật trách nhiệm hữu hạn 100% vốn nước ngoài tại Việt Nam, chuyển đổi công ty luật nước ngoài thành công ty luật Việt Nam, đăng ký thay đổi nội dung Giấy phép thành lập chi nhánh, công ty luật nước ngoài đã được cơ quan có thẩm quyền tiếp nhận trước ngày Nghị định này có hiệu lực thi hành thì cơ quan có thẩm quyền đã tiếp nhận hồ sơ tiếp tục thực hiện theo quy định của văn bản quy phạm pháp luật tại thời điểm tiếp nhận hồ sơ.
+[amend] 18/2026/NĐ-CP · hiệu lực 2026-01-15
+b) Thay thế cụm từ “trong thời hạn 10 ngày” thành “trong thời hạn 08 ngày làm việc” tại khoản 1 và khoản 2 Điều 11, khoản 2 Điều 23a;
+CHUYỂN TIẾP: Điều 16. Điều khoản chuyển tiếp
+1. Đối với hồ sơ đề nghị giải quyết thủ tục hành chính được quy định tại các Điều 1, 2, 3, 4, 5, 6, 7, 8, 9, 10 và 12 Nghị định này đã được cơ quan có thẩm quyền tiếp nhận hoặc đã được đóng dấu bưu chính trước ngày Nghị định này có hiệu lực thì thực hiện theo quy định của pháp luật đang có hiệu lực điều chỉnh trong lĩnh vực đó tại thời điểm hồ sơ được tiếp nhận.
+2. Đối với các hồ sơ đề nghị giải quyết thủ tục hành chính quy định tại Điều 11 Nghị định này:
+a) Trường hợp hồ </t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -7758,8 +9961,6 @@
           <t>126/2021/NĐ-CP; 46/2024/NĐ-CP</t>
         </is>
       </c>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr"/>
       <c r="N87" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -7770,18 +9971,87 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P87" t="inlineStr"/>
-      <c r="Q87" t="inlineStr"/>
       <c r="R87" t="inlineStr">
         <is>
           <t>Mốc 1→2 chỉ đổi 'Bán' thành 'Buôn bán' — khác biệt nhỏ nhưng có nghĩa pháp lý; audit xem có coi là đổi đáp án không; id cũ vilextime:T3:provision:de0f8ef2-2c85-11f1-b16a-0dee4373a04b:2022-01-02 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S87" t="inlineStr"/>
-      <c r="T87" t="inlineStr"/>
-      <c r="U87" t="inlineStr"/>
-      <c r="V87" t="inlineStr"/>
-      <c r="W87" t="inlineStr"/>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>99/2013/NĐ-CP · hiệu lực 2013-10-15 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 11. Xâm phạm quyền đối với nhãn hiệu, chỉ dẫn địa lý, tên thương mại, kiểu dáng công nghiệp
+1. Phạt cảnh cáo hoặc phạt tiền từ 500.000 đồng đến 2.000.000 đồng đối với một trong các hành vi sau đây vì mục đích kinh doanh trong trường hợp giá trị hàng hóa, dịch vụ vi phạm đến 3.000.000 đồng:
+a) Bán; chào hàng; vận chuyển, kể cả quá cảnh; tàng trữ; trưng bày để bán hàng hóa, dịch vụ xâm phạm quyền đối với nhãn hiệu, tên thương mại, chỉ dẫn địa lý, kiểu dáng công nghiệp;
+b) Đặt hàng, giao việc, thuê người khác thực hiện hành vi quy định tại Điểm a Khoản này.</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 126/2021/NĐ-CP · hiệu lực 2022-01-01
+a) Sửa đổi, bổ sung điểm a khoản 1 như sau:
+“a) Buôn bán; chào hàng; vận chuyển, kể cả quá cảnh; tàng trữ; trưng bày để bán sản phẩm xâm phạm quyền đối với sáng chế, giải pháp hữu ích, thiết kế bố trí hoặc sản phẩm được sản xuất từ quy trình xâm phạm quyền đối với sáng chế, giải pháp hữu ích;”;
+CHUYỂN TIẾP: 2. Điều khoản chuyển tiếp:
+a) Đối với hành vi vi phạm hành chính trong lĩnh vực sở hữu công nghiệp; tiêu chuẩn, đo lường và chất lượng sản phẩm, hàng hóa; hoạt động khoa học và công nghệ, chuyển giao công nghệ; năng lượng nguyên tử xảy ra trước ngày Nghị định này có hiệu lực, sau đó mới bị phát hiện hoặc đang xem xét, giải quyết mà Nghị định này không quy định trách nhiệm pháp lý hoặc quy định trách nhiệm pháp lý nhẹ hơn thì áp dụng các quy định tại Nghị định này;
+b) Đối với quyết định xử phạt vi phạm hành chính đã được ban hành hoặc đã được thi hành xong trước thời điểm Nghị định này có hiệu lực thi hành mà cá nhân, tổ chức bị xử phạt vi phạm hành chính còn khiếu nại thì áp dụng quy định của Nghị định số 99/2013/NĐ-CP ngày 29 tháng 8 năm 2013 của Chính phủ quy định xử phạt vi phạm hành chính trong lĩnh vực sở hữu công nghiệp, Nghị định số 119/2017/NĐ-CP ngày 01 tháng 11 năm 2017 của Chính phủ quy định xử phạt vi phạm hành chính trong lĩnh vực tiêu chuẩn, đo lường và chất lượng sản phẩm, hàng hóa, Nghị định số 51/2019/NĐ-CP ngày 13 tháng 6 năm 2019 của Chính phủ quy định xử phạt vi phạm hành chính trong hoạt động khoa học và công nghệ, chuyển giao công nghệ, Nghị định số 107/2013/NĐ-CP ngày 20 tháng 9 năm 2013 của Chính phủ quy định xử phạt vi phạm hành chính trong lĩnh vực năng lượng nguyên tử.
+Nơi nhận:
+- Ban Bí thư Trung ương Đảng;
+- Thủ tướng, các Phó Thủ tướng Chính phủ;
+- Các bộ, cơ quan ngang bộ, cơ quan thuộc Chính phủ;
+- HĐND, UBND các tỉnh, thành phố trực thuộc trung ương;
+- Văn phòng Trung ương và các Ban của Đảng;
+- Văn phòng Tổng Bí thư;
+- Văn phòng Chủ tịch nước;
+- Hội đồng Dân tộc và các Ủy ban của Quốc hội;
+- Văn phòng Quốc hội;
+- Tòa án nhân dân tối cao;
+- Viện kiểm sát nhân dân tối cao;
+- Kiểm toán nhà nước;
+- Ủy ban Giám sát tài chính Quốc gia;
+- Ngân hàng Chính sách Xã hội;
+- Ngân hàng Phát triển Việt Nam;
+- Ủy ban trung ương Mặt trận Tổ quốc Việt Nam;
+- Cơ quan trung ương của các đoàn thể;
+- VPCP: BTCN, các PCN, Trợ lý TTg, TGĐ Cổng TTĐT,
+các Vụ, Cục, đơn vị trực thuộc, Công báo;
+- Lưu: VT, KGVX (2b).
+TM. CHÍNH PHỦ
+KT. THỦ TƯỚNG
+PHÓ THỦ TƯỚNG
+(Đã ký)
+Vũ Đức Đam
+[amend] 46/2024/NĐ-CP · hiệu lực 2024-07-01
+a) Sửa đổi, bổ sung điểm a khoản 1 như sau:
+“a) Buôn bán; chào hàng; tàng trữ để bán; trưng bày để bán; vận chuyển không bao gồm quá cảnh sản phẩm xâm phạm quyền đối với sáng chế, giải pháp hữu ích, thiết kế bố trí hoặc sản phẩm được sản xuất từ quy trình xâm phạm quyền đối với sáng chế, giải pháp hữu ích;”.
+CHUYỂN TIẾP: 2. Điều khoản chuyển tiếp:
+Đối với hành vi vi phạm hành chính trong lĩnh vực sở hữu công nghiệp xảy ra trước ngày Nghị định này có hiệu lực thi hành mà sau đó mới bị phát hiện hoặc đang xem xét, giải quyết thì áp dụng Nghị định của Chính phủ về xử phạt vi phạm hành chính có hiệu lực tại thời điểm thực hiện hành vi vi phạm để xử lý, trừ trường hợp Nghị định này không quy định trách nhiệm pháp lý hoặc quy định trách nhiệm pháp lý nhẹ hơn đối với hành vi đã xảy ra thì áp dụng các quy định của Nghị định này để xử lý.
+Đối với quyết định xử phạt vi phạm hành chính đã được ban hành hoặc đã được thi hành xong trước thời điểm Nghị định này có hiệu lực thi hành mà tổ chức, cá nhân bị xử phạt vi phạm hành chính còn khiếu nại thì áp dụng quy định của Nghị định số 99/2013/NĐ-CP ngày 29 tháng 8 năm 2013 của Chính phủ quy định xử phạt vi phạm hành chính trong lĩnh vực sở hữu công nghiệp đã được sửa đổi, bổ sung một số điều theo Nghị định số 126/2021/NĐ-CP ngày 30 tháng 12 năm 2021 của Chính phủ để xem xét, giải quyết./.
+Nơi nhận:
+- Ban Bí thư Trung ương Đảng;
+- Thủ tướng, các Phó Thủ tướng Chính phủ;
+- Các bộ, cơ quan ngang bộ, cơ quan thuộc Chính phủ;
+- HĐND, UBND các tỉnh, thành phố trực thuộc trung ương;
+- Văn phòng Trung ương và các Ban của Đảng;
+- Văn phòng Tổng Bí thư;
+- Văn phòng Chủ tịch nước;
+- Hội đồng Dân tộc và các Ủy ban của Quốc hội;
+- Văn phòng Quốc hội;
+- Tòa án nhân dân tối cao;
+- Viện kiểm sát nhân dân tối cao;
+- Kiểm toán nhà nước;
+- Ủy ban Giám sát tài chính Quốc gia;
+- Ngân hàng Chính sách xã hội;
+- Ngân hàng Phát triển Việt Nam;
+- Ủy ban trung ương Mặt trận Tổ quốc Việt Nam;
+- Cơ quan trung ương của các đoàn thể;
+- VPCP: BTCN, các PCN, Trợ lý TTg, TGĐ Cổng TTĐT,các Vụ, Cục, đơn vị trực thuộc, Công báo;
+- Lưu: VT, KGVX (2).
+TM. CHÍNH PHỦ
+KT. THỦ TƯỚNG
+PHÓ THỦ TƯỚNG
+(Đã ký)
+Trần Lưu Quang</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -7844,7 +10114,6 @@
           <t>actor_has_transitional</t>
         </is>
       </c>
-      <c r="M88" t="inlineStr"/>
       <c r="N88" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -7855,18 +10124,35 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P88" t="inlineStr"/>
-      <c r="Q88" t="inlineStr"/>
       <c r="R88" t="inlineStr">
         <is>
           <t>id cũ vilextime:T3:provision:e20d4360-2c4d-11f1-94e0-875bba306d69:2019-01-02 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S88" t="inlineStr"/>
-      <c r="T88" t="inlineStr"/>
-      <c r="U88" t="inlineStr"/>
-      <c r="V88" t="inlineStr"/>
-      <c r="W88" t="inlineStr"/>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>21/2018/TT-BNNPTNT · hiệu lực 2019-01-01 → 2026-01-01 · lúc thu thập: Hết hiệu lực toàn bộ
+Điều 15. Cục Quản lý chất lượng Nông lâm sản và Thủy sản
+1. Chỉ đạo, tổ chức thực hiện, định kỳ kiểm tra, giám sát hoạt động có liên quan đến việc kiểm tra, xác nhận cam kết hoặc chứng nhận sản phẩm thủy sản xuất khẩu có nguồn gốc từ thủy sản khai thác nhập khẩu.</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 13/2020/TT-BNNPTNT · hiệu lực 2020-12-25
+5. Khoản 1 Điều 15 được sửa đổi như sau:
+"1. Chỉ đạo, tổ chức thực hiện, kiểm tra việc chấp hành các quy định về chống khai thác thủy sản bất hợp pháp, không báo cáo và không theo quy định; xác nhận nguyên liệu, chứng nhận nguồn gốc thủy sản; xác nhận cam kết nguyên liệu thủy sản khai thác nhập khẩu để chế biến xuất khẩu vào thị trường có yêu cầu; hồ sơ truy xuất nguồn gốc nguyên liệu trong quá trình thực hiện các hoạt động lấy mẫu thẩm tra an toàn thực phẩm, thẩm định và chứng nhận lô hàng thủy sản xuất khẩu."
+6. Khoản 8 Điều 17 được sửa đổi như sau:
+"8. Trước ngày 20 hàng tháng, báo cáo Sở Nông nghiệp và Phát triển nông thôn, Tổng cục Thủy sản về kết quả xác nhận nguyên liệu thủy sản khai thác theo Mẫu số 03 Phụ lục VII ban hành kèm theo Thông tư này; lưu trữ hồ sơ liên quan đến việc cấp giấy biên nhận thủy sản bốc dỡ qua cảng, giấy xác nhận nguyên liệu thủy sản khai thác trong thời hạn 36 tháng kể từ ngày xác nhận.Cấp lại Giấy biên nhận thủy sản bốc dỡ qua cảng theo đề nghị của tổ chức cá nhân; số của giấy biên nhận thủy sản bốc dỡ qua cảng được cấp lại trùng với số của bản gốc của giấy biên nhận thủy sản bốc dỡ qua cảng đã cấp và có thêm ký hiệu "R" ở phía sau phần số đã cấp; thời hạn của giấy biên nhận thủy sản bốc dỡ qua cảng cấp lại bằng thời hạn còn lại của giấy biên nhận thủy sản bốc dỡ qua cảng đã cấp tính từ ngày cấp lại."
+7. Khoản 2 Điều 19 được sửa đổi như sau:
+"2. Lưu trữ đầy đủ hồ sơ để truy xuất nguồn gốc, phân biệt các lô nguyên liệu đã sản xuất, lô nguyên liệu chưa sản xuất, còn đang bảo quản trong kho của cơ sở, đảm bảo cơ sở chỉ tiếp nhận, chế biến nguyên liệu có nguồn gốc hợp pháp. Lưu trữ hồ sơ xác nhận nguyên liệu thủy sản khai thác trong nước, chứng nhận nguồn gốc thủy sản khai thác, xác nhận cam kết hoặc chứng nhận sản phẩm thủy sản xuất khẩu có nguồn gốc từ thủy sản khai thác nhập khẩu trong thời hạn 36 tháng kể từ ngày được xác nhận, chứng nhận. Được lựa chọn một trong các cơ quan thẩm quyền được quy định tại Phụ lục IV ban hành theo Thông tư này để nộp hồ sơ đề nghị chứng nhận nguồn gốc thủy sản khai thác."
+CHUYỂN TIẾP: Điều 2. Điều khoản chuyển tiếp
+1. Thuyền trưởng tàu thu mua, chuyển tải đã ghi Nhật ký thu mua, chuyển tải theo mẫu tại Thông tư số 21/2018/TT-BNNPTNT trước ngày Thông tư này có hiệu lực, được sử dụng để thực hiện việc xác nhận, chứng nhận thủy sản cho chuyến biển đó.
+2. Giấy biên nhận thủy sản bốc dỡ qua cảng được cấp trước ngày Thông tư này có hiệu lực thì được tiếp tục sử dụng cho đến khi hết thời hạn ghi trên Giấy biên nhận đã được cấp.
+[amend] 01/2022/TT-BNNPTNT · hiệu lực 2022-03-04
+7. Sửa đổi, bổ sung khoản 1 Điều 15 như sau:
+"1. Chỉ đạo, tổ chức thực hiện, kiểm tra việc chấp hành các quy định về chống khai thác thủy sản bất hợp pháp, không báo cáo và không theo quy định trong phạm vi chức năng, nhiệm vụ được giao đối với hàng thủy sản xuất khẩu vào thị trường có yêu cầu; Xác nhận cam kết, chứng nhận sản phẩm thủy sản xuất khẩu có nguồn gốc từ thủy sản khai thác nhập khẩu để chế biến xuất khẩu vào thị trường có yêu cầu; kiểm tra hồ sơ truy xuất nguồn gốc nguyên liệu đối với hàng thủy sản xuất khẩu vào thị trường có yêu cầu trong quá trình thực hiện các hoạt động lấy mẫu thẩm tra an toàn thực phẩm, thẩm định và chứng nhận lô hàng thủy sản xuất khẩu."</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -7929,7 +10215,6 @@
           <t>actor_has_transitional</t>
         </is>
       </c>
-      <c r="M89" t="inlineStr"/>
       <c r="N89" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -7940,18 +10225,35 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P89" t="inlineStr"/>
-      <c r="Q89" t="inlineStr"/>
       <c r="R89" t="inlineStr">
         <is>
           <t>id cũ vilextime:T3:provision:e20d4360-2c4d-11f1-94e0-875bba306d69:2020-12-26 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S89" t="inlineStr"/>
-      <c r="T89" t="inlineStr"/>
-      <c r="U89" t="inlineStr"/>
-      <c r="V89" t="inlineStr"/>
-      <c r="W89" t="inlineStr"/>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>21/2018/TT-BNNPTNT · hiệu lực 2019-01-01 → 2026-01-01 · lúc thu thập: Hết hiệu lực toàn bộ
+Điều 15. Cục Quản lý chất lượng Nông lâm sản và Thủy sản
+1. Chỉ đạo, tổ chức thực hiện, định kỳ kiểm tra, giám sát hoạt động có liên quan đến việc kiểm tra, xác nhận cam kết hoặc chứng nhận sản phẩm thủy sản xuất khẩu có nguồn gốc từ thủy sản khai thác nhập khẩu.</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 13/2020/TT-BNNPTNT · hiệu lực 2020-12-25
+5. Khoản 1 Điều 15 được sửa đổi như sau:
+"1. Chỉ đạo, tổ chức thực hiện, kiểm tra việc chấp hành các quy định về chống khai thác thủy sản bất hợp pháp, không báo cáo và không theo quy định; xác nhận nguyên liệu, chứng nhận nguồn gốc thủy sản; xác nhận cam kết nguyên liệu thủy sản khai thác nhập khẩu để chế biến xuất khẩu vào thị trường có yêu cầu; hồ sơ truy xuất nguồn gốc nguyên liệu trong quá trình thực hiện các hoạt động lấy mẫu thẩm tra an toàn thực phẩm, thẩm định và chứng nhận lô hàng thủy sản xuất khẩu."
+6. Khoản 8 Điều 17 được sửa đổi như sau:
+"8. Trước ngày 20 hàng tháng, báo cáo Sở Nông nghiệp và Phát triển nông thôn, Tổng cục Thủy sản về kết quả xác nhận nguyên liệu thủy sản khai thác theo Mẫu số 03 Phụ lục VII ban hành kèm theo Thông tư này; lưu trữ hồ sơ liên quan đến việc cấp giấy biên nhận thủy sản bốc dỡ qua cảng, giấy xác nhận nguyên liệu thủy sản khai thác trong thời hạn 36 tháng kể từ ngày xác nhận.Cấp lại Giấy biên nhận thủy sản bốc dỡ qua cảng theo đề nghị của tổ chức cá nhân; số của giấy biên nhận thủy sản bốc dỡ qua cảng được cấp lại trùng với số của bản gốc của giấy biên nhận thủy sản bốc dỡ qua cảng đã cấp và có thêm ký hiệu "R" ở phía sau phần số đã cấp; thời hạn của giấy biên nhận thủy sản bốc dỡ qua cảng cấp lại bằng thời hạn còn lại của giấy biên nhận thủy sản bốc dỡ qua cảng đã cấp tính từ ngày cấp lại."
+7. Khoản 2 Điều 19 được sửa đổi như sau:
+"2. Lưu trữ đầy đủ hồ sơ để truy xuất nguồn gốc, phân biệt các lô nguyên liệu đã sản xuất, lô nguyên liệu chưa sản xuất, còn đang bảo quản trong kho của cơ sở, đảm bảo cơ sở chỉ tiếp nhận, chế biến nguyên liệu có nguồn gốc hợp pháp. Lưu trữ hồ sơ xác nhận nguyên liệu thủy sản khai thác trong nước, chứng nhận nguồn gốc thủy sản khai thác, xác nhận cam kết hoặc chứng nhận sản phẩm thủy sản xuất khẩu có nguồn gốc từ thủy sản khai thác nhập khẩu trong thời hạn 36 tháng kể từ ngày được xác nhận, chứng nhận. Được lựa chọn một trong các cơ quan thẩm quyền được quy định tại Phụ lục IV ban hành theo Thông tư này để nộp hồ sơ đề nghị chứng nhận nguồn gốc thủy sản khai thác."
+CHUYỂN TIẾP: Điều 2. Điều khoản chuyển tiếp
+1. Thuyền trưởng tàu thu mua, chuyển tải đã ghi Nhật ký thu mua, chuyển tải theo mẫu tại Thông tư số 21/2018/TT-BNNPTNT trước ngày Thông tư này có hiệu lực, được sử dụng để thực hiện việc xác nhận, chứng nhận thủy sản cho chuyến biển đó.
+2. Giấy biên nhận thủy sản bốc dỡ qua cảng được cấp trước ngày Thông tư này có hiệu lực thì được tiếp tục sử dụng cho đến khi hết thời hạn ghi trên Giấy biên nhận đã được cấp.
+[amend] 01/2022/TT-BNNPTNT · hiệu lực 2022-03-04
+7. Sửa đổi, bổ sung khoản 1 Điều 15 như sau:
+"1. Chỉ đạo, tổ chức thực hiện, kiểm tra việc chấp hành các quy định về chống khai thác thủy sản bất hợp pháp, không báo cáo và không theo quy định trong phạm vi chức năng, nhiệm vụ được giao đối với hàng thủy sản xuất khẩu vào thị trường có yêu cầu; Xác nhận cam kết, chứng nhận sản phẩm thủy sản xuất khẩu có nguồn gốc từ thủy sản khai thác nhập khẩu để chế biến xuất khẩu vào thị trường có yêu cầu; kiểm tra hồ sơ truy xuất nguồn gốc nguyên liệu đối với hàng thủy sản xuất khẩu vào thị trường có yêu cầu trong quá trình thực hiện các hoạt động lấy mẫu thẩm tra an toàn thực phẩm, thẩm định và chứng nhận lô hàng thủy sản xuất khẩu."</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -8014,7 +10316,6 @@
           <t>actor_has_transitional</t>
         </is>
       </c>
-      <c r="M90" t="inlineStr"/>
       <c r="N90" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -8025,18 +10326,35 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P90" t="inlineStr"/>
-      <c r="Q90" t="inlineStr"/>
       <c r="R90" t="inlineStr">
         <is>
           <t>id cũ vilextime:T3:provision:e20d4360-2c4d-11f1-94e0-875bba306d69:2022-03-05 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S90" t="inlineStr"/>
-      <c r="T90" t="inlineStr"/>
-      <c r="U90" t="inlineStr"/>
-      <c r="V90" t="inlineStr"/>
-      <c r="W90" t="inlineStr"/>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>21/2018/TT-BNNPTNT · hiệu lực 2019-01-01 → 2026-01-01 · lúc thu thập: Hết hiệu lực toàn bộ
+Điều 15. Cục Quản lý chất lượng Nông lâm sản và Thủy sản
+1. Chỉ đạo, tổ chức thực hiện, định kỳ kiểm tra, giám sát hoạt động có liên quan đến việc kiểm tra, xác nhận cam kết hoặc chứng nhận sản phẩm thủy sản xuất khẩu có nguồn gốc từ thủy sản khai thác nhập khẩu.</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 13/2020/TT-BNNPTNT · hiệu lực 2020-12-25
+5. Khoản 1 Điều 15 được sửa đổi như sau:
+"1. Chỉ đạo, tổ chức thực hiện, kiểm tra việc chấp hành các quy định về chống khai thác thủy sản bất hợp pháp, không báo cáo và không theo quy định; xác nhận nguyên liệu, chứng nhận nguồn gốc thủy sản; xác nhận cam kết nguyên liệu thủy sản khai thác nhập khẩu để chế biến xuất khẩu vào thị trường có yêu cầu; hồ sơ truy xuất nguồn gốc nguyên liệu trong quá trình thực hiện các hoạt động lấy mẫu thẩm tra an toàn thực phẩm, thẩm định và chứng nhận lô hàng thủy sản xuất khẩu."
+6. Khoản 8 Điều 17 được sửa đổi như sau:
+"8. Trước ngày 20 hàng tháng, báo cáo Sở Nông nghiệp và Phát triển nông thôn, Tổng cục Thủy sản về kết quả xác nhận nguyên liệu thủy sản khai thác theo Mẫu số 03 Phụ lục VII ban hành kèm theo Thông tư này; lưu trữ hồ sơ liên quan đến việc cấp giấy biên nhận thủy sản bốc dỡ qua cảng, giấy xác nhận nguyên liệu thủy sản khai thác trong thời hạn 36 tháng kể từ ngày xác nhận.Cấp lại Giấy biên nhận thủy sản bốc dỡ qua cảng theo đề nghị của tổ chức cá nhân; số của giấy biên nhận thủy sản bốc dỡ qua cảng được cấp lại trùng với số của bản gốc của giấy biên nhận thủy sản bốc dỡ qua cảng đã cấp và có thêm ký hiệu "R" ở phía sau phần số đã cấp; thời hạn của giấy biên nhận thủy sản bốc dỡ qua cảng cấp lại bằng thời hạn còn lại của giấy biên nhận thủy sản bốc dỡ qua cảng đã cấp tính từ ngày cấp lại."
+7. Khoản 2 Điều 19 được sửa đổi như sau:
+"2. Lưu trữ đầy đủ hồ sơ để truy xuất nguồn gốc, phân biệt các lô nguyên liệu đã sản xuất, lô nguyên liệu chưa sản xuất, còn đang bảo quản trong kho của cơ sở, đảm bảo cơ sở chỉ tiếp nhận, chế biến nguyên liệu có nguồn gốc hợp pháp. Lưu trữ hồ sơ xác nhận nguyên liệu thủy sản khai thác trong nước, chứng nhận nguồn gốc thủy sản khai thác, xác nhận cam kết hoặc chứng nhận sản phẩm thủy sản xuất khẩu có nguồn gốc từ thủy sản khai thác nhập khẩu trong thời hạn 36 tháng kể từ ngày được xác nhận, chứng nhận. Được lựa chọn một trong các cơ quan thẩm quyền được quy định tại Phụ lục IV ban hành theo Thông tư này để nộp hồ sơ đề nghị chứng nhận nguồn gốc thủy sản khai thác."
+CHUYỂN TIẾP: Điều 2. Điều khoản chuyển tiếp
+1. Thuyền trưởng tàu thu mua, chuyển tải đã ghi Nhật ký thu mua, chuyển tải theo mẫu tại Thông tư số 21/2018/TT-BNNPTNT trước ngày Thông tư này có hiệu lực, được sử dụng để thực hiện việc xác nhận, chứng nhận thủy sản cho chuyến biển đó.
+2. Giấy biên nhận thủy sản bốc dỡ qua cảng được cấp trước ngày Thông tư này có hiệu lực thì được tiếp tục sử dụng cho đến khi hết thời hạn ghi trên Giấy biên nhận đã được cấp.
+[amend] 01/2022/TT-BNNPTNT · hiệu lực 2022-03-04
+7. Sửa đổi, bổ sung khoản 1 Điều 15 như sau:
+"1. Chỉ đạo, tổ chức thực hiện, kiểm tra việc chấp hành các quy định về chống khai thác thủy sản bất hợp pháp, không báo cáo và không theo quy định trong phạm vi chức năng, nhiệm vụ được giao đối với hàng thủy sản xuất khẩu vào thị trường có yêu cầu; Xác nhận cam kết, chứng nhận sản phẩm thủy sản xuất khẩu có nguồn gốc từ thủy sản khai thác nhập khẩu để chế biến xuất khẩu vào thị trường có yêu cầu; kiểm tra hồ sơ truy xuất nguồn gốc nguyên liệu đối với hàng thủy sản xuất khẩu vào thị trường có yêu cầu trong quá trình thực hiện các hoạt động lấy mẫu thẩm tra an toàn thực phẩm, thẩm định và chứng nhận lô hàng thủy sản xuất khẩu."</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -8094,8 +10412,6 @@
           <t>15/2024/TT-BTC; 46/2025/TT-BTC</t>
         </is>
       </c>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr"/>
       <c r="N91" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -8106,18 +10422,27 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P91" t="inlineStr"/>
-      <c r="Q91" t="inlineStr"/>
       <c r="R91" t="inlineStr">
         <is>
           <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Nếu một tổ chức mở lớp cập nhật kiến thức cho kiểm toán viên để tính giờ cập nhật, thì hành vi nào của tổ chức đó bị coi là vi phạm về cập nhật kiến thức?»; nhãn cũ khong_dat question_ambiguous: Câu hỏi 'hành vi nào của tổ chức đó bị coi là vi phạm' khớp cả khoản 2 (cập nhật nội dung không phù hợp nội dung đã đăng ký), khoản 3 (báo cáo không trung thực), khoản 5 cùng Điều; khoản 1 chỉ là một hành vi). Câu hỏi chốt tổ chức lớp khi chưa hoàn tất đăng ký/điều kiện/thông báo, chỉ khớp khoản 1; ba đáp án khác nhau; id cũ vilextime:T3:provision:e6c5d5d4-df40-11f0-a50d-ddac3e38e697:2013-01-02 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S91" t="inlineStr"/>
-      <c r="T91" t="inlineStr"/>
-      <c r="U91" t="inlineStr"/>
-      <c r="V91" t="inlineStr"/>
-      <c r="W91" t="inlineStr"/>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>150/2012/TT-BTC · hiệu lực 2013-01-01 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 18. Các hành vi vi phạm về cập nhật kiến thức
+1. Tổ chức cập nhật kiến thức cho kiểm toán viên hành nghề để tính giờ cập nhật kiến thức theo quy định tại Điều 11 Thông tư này khi chưa đăng ký với Bộ Tài chính hoặc đã đăng ký nhưng chưa được Bộ Tài chính chấp thuận.</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 15/2024/TT-BTC · hiệu lực 2024-05-01
+1. Thay thế cụm từ "Bộ Tài chính" tại khoản 2 khoản 3 khoản 4 Điều 2, khoản 1 Điều 6, điểm a điểm đ khoản 1 Điều 7, khoản 1 khoản 2 Điều 9, điểm a khoản 4 Điều 10, điểm c khoản 6 Điều 11, điểm b khoản 1 Điều 12 (đã được sửa đổi tại Khoản 4 Điều 1 Thông tư số 56/2015/TT-BTC ngày 23/4/2015), điểm a khoản 1 Điều 14, khoản 1 khoản 3 khoản 4 khoản 5 khoản 9 Điều 15, khoản 3 Điều 16, Khoản 2, Khoản 5 Điều 17, khoản 1 Điều 18 Thông tư số 150/2012/TT-BTC bằng cụm từ "Cục Quản lý giám sát kế toán, kiểm toán - Bộ Tài chính".
+[amend] 46/2025/TT-BTC · hiệu lực 2025-07-01
+8. Sửa đổi, bổ sung khoản 1 Điều 18 Thông tư số 150/2012/TT-BTC (được sửa đổi, bổ sung tại khoản 1 Điều 1 Thông tư số 15/2024/TT-BTC) như sau:
+"1. Tổ chức cập nhật kiến thức cho kiểm toán viên hành nghề để tính giờ cập nhật kiến thức theo quy định tại Điều 11 Thông tư này khi không đảm bảo điều kiện quy định tại Điều 7 Thông tư này hoặc đã đủ điều kiện nhưng chưa thông báo cho Cục Quản lý, giám sát kế toán, kiểm toán - Bộ Tài chính".</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -8175,8 +10500,6 @@
           <t>15/2024/TT-BTC; 46/2025/TT-BTC</t>
         </is>
       </c>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr"/>
       <c r="N92" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -8187,18 +10510,27 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P92" t="inlineStr"/>
-      <c r="Q92" t="inlineStr"/>
       <c r="R92" t="inlineStr">
         <is>
           <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Nếu một tổ chức mở lớp cập nhật kiến thức cho kiểm toán viên để tính giờ cập nhật, thì hành vi nào của tổ chức đó bị coi là vi phạm về cập nhật kiến thức?»; nhãn cũ khong_dat question_ambiguous: Câu hỏi 'hành vi nào của tổ chức đó bị coi là vi phạm' khớp cả khoản 2 (cập nhật nội dung không phù hợp nội dung đã đăng ký), khoản 3 (báo cáo không trung thực), khoản 5 cùng Điều; khoản 1 chỉ là một hành vi). Câu hỏi chốt tổ chức lớp khi chưa hoàn tất đăng ký/điều kiện/thông báo, chỉ khớp khoản 1; ba đáp án khác nhau; id cũ vilextime:T3:provision:e6c5d5d4-df40-11f0-a50d-ddac3e38e697:2024-05-02 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S92" t="inlineStr"/>
-      <c r="T92" t="inlineStr"/>
-      <c r="U92" t="inlineStr"/>
-      <c r="V92" t="inlineStr"/>
-      <c r="W92" t="inlineStr"/>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>150/2012/TT-BTC · hiệu lực 2013-01-01 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 18. Các hành vi vi phạm về cập nhật kiến thức
+1. Tổ chức cập nhật kiến thức cho kiểm toán viên hành nghề để tính giờ cập nhật kiến thức theo quy định tại Điều 11 Thông tư này khi chưa đăng ký với Bộ Tài chính hoặc đã đăng ký nhưng chưa được Bộ Tài chính chấp thuận.</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 15/2024/TT-BTC · hiệu lực 2024-05-01
+1. Thay thế cụm từ "Bộ Tài chính" tại khoản 2 khoản 3 khoản 4 Điều 2, khoản 1 Điều 6, điểm a điểm đ khoản 1 Điều 7, khoản 1 khoản 2 Điều 9, điểm a khoản 4 Điều 10, điểm c khoản 6 Điều 11, điểm b khoản 1 Điều 12 (đã được sửa đổi tại Khoản 4 Điều 1 Thông tư số 56/2015/TT-BTC ngày 23/4/2015), điểm a khoản 1 Điều 14, khoản 1 khoản 3 khoản 4 khoản 5 khoản 9 Điều 15, khoản 3 Điều 16, Khoản 2, Khoản 5 Điều 17, khoản 1 Điều 18 Thông tư số 150/2012/TT-BTC bằng cụm từ "Cục Quản lý giám sát kế toán, kiểm toán - Bộ Tài chính".
+[amend] 46/2025/TT-BTC · hiệu lực 2025-07-01
+8. Sửa đổi, bổ sung khoản 1 Điều 18 Thông tư số 150/2012/TT-BTC (được sửa đổi, bổ sung tại khoản 1 Điều 1 Thông tư số 15/2024/TT-BTC) như sau:
+"1. Tổ chức cập nhật kiến thức cho kiểm toán viên hành nghề để tính giờ cập nhật kiến thức theo quy định tại Điều 11 Thông tư này khi không đảm bảo điều kiện quy định tại Điều 7 Thông tư này hoặc đã đủ điều kiện nhưng chưa thông báo cho Cục Quản lý, giám sát kế toán, kiểm toán - Bộ Tài chính".</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -8256,8 +10588,6 @@
           <t>15/2024/TT-BTC; 46/2025/TT-BTC</t>
         </is>
       </c>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr"/>
       <c r="N93" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -8268,18 +10598,27 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P93" t="inlineStr"/>
-      <c r="Q93" t="inlineStr"/>
       <c r="R93" t="inlineStr">
         <is>
           <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Nếu một tổ chức mở lớp cập nhật kiến thức cho kiểm toán viên để tính giờ cập nhật, thì hành vi nào của tổ chức đó bị coi là vi phạm về cập nhật kiến thức?»; nhãn cũ khong_dat question_ambiguous: Câu hỏi 'hành vi nào của tổ chức đó bị coi là vi phạm' khớp cả khoản 2 (cập nhật nội dung không phù hợp nội dung đã đăng ký), khoản 3 (báo cáo không trung thực), khoản 5 cùng Điều; khoản 1 chỉ là một hành vi). Câu hỏi chốt tổ chức lớp khi chưa hoàn tất đăng ký/điều kiện/thông báo, chỉ khớp khoản 1; ba đáp án khác nhau; id cũ vilextime:T3:provision:e6c5d5d4-df40-11f0-a50d-ddac3e38e697:2025-07-02 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S93" t="inlineStr"/>
-      <c r="T93" t="inlineStr"/>
-      <c r="U93" t="inlineStr"/>
-      <c r="V93" t="inlineStr"/>
-      <c r="W93" t="inlineStr"/>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>150/2012/TT-BTC · hiệu lực 2013-01-01 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 18. Các hành vi vi phạm về cập nhật kiến thức
+1. Tổ chức cập nhật kiến thức cho kiểm toán viên hành nghề để tính giờ cập nhật kiến thức theo quy định tại Điều 11 Thông tư này khi chưa đăng ký với Bộ Tài chính hoặc đã đăng ký nhưng chưa được Bộ Tài chính chấp thuận.</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 15/2024/TT-BTC · hiệu lực 2024-05-01
+1. Thay thế cụm từ "Bộ Tài chính" tại khoản 2 khoản 3 khoản 4 Điều 2, khoản 1 Điều 6, điểm a điểm đ khoản 1 Điều 7, khoản 1 khoản 2 Điều 9, điểm a khoản 4 Điều 10, điểm c khoản 6 Điều 11, điểm b khoản 1 Điều 12 (đã được sửa đổi tại Khoản 4 Điều 1 Thông tư số 56/2015/TT-BTC ngày 23/4/2015), điểm a khoản 1 Điều 14, khoản 1 khoản 3 khoản 4 khoản 5 khoản 9 Điều 15, khoản 3 Điều 16, Khoản 2, Khoản 5 Điều 17, khoản 1 Điều 18 Thông tư số 150/2012/TT-BTC bằng cụm từ "Cục Quản lý giám sát kế toán, kiểm toán - Bộ Tài chính".
+[amend] 46/2025/TT-BTC · hiệu lực 2025-07-01
+8. Sửa đổi, bổ sung khoản 1 Điều 18 Thông tư số 150/2012/TT-BTC (được sửa đổi, bổ sung tại khoản 1 Điều 1 Thông tư số 15/2024/TT-BTC) như sau:
+"1. Tổ chức cập nhật kiến thức cho kiểm toán viên hành nghề để tính giờ cập nhật kiến thức theo quy định tại Điều 11 Thông tư này khi không đảm bảo điều kiện quy định tại Điều 7 Thông tư này hoặc đã đủ điều kiện nhưng chưa thông báo cho Cục Quản lý, giám sát kế toán, kiểm toán - Bộ Tài chính".</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -8342,7 +10681,6 @@
           <t>actor_has_transitional</t>
         </is>
       </c>
-      <c r="M94" t="inlineStr"/>
       <c r="N94" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -8353,18 +10691,54 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P94" t="inlineStr"/>
-      <c r="Q94" t="inlineStr"/>
       <c r="R94" t="inlineStr">
         <is>
           <t>Hỏi cơ quan và địa chỉ: bốn đáp án khác nhau; id cũ vilextime:T3:provision:ec4a796a-df40-11f0-b831-318b010cb040:2014-10-21 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S94" t="inlineStr"/>
-      <c r="T94" t="inlineStr"/>
-      <c r="U94" t="inlineStr"/>
-      <c r="V94" t="inlineStr"/>
-      <c r="W94" t="inlineStr"/>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>27/2014/TT-BCT · hiệu lực 2014-10-20 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 3. Cấp giấy phép quá cảnh hàng hóa
+2. Đối với hàng hóa thuộc danh mục cấm của Việt Nam nhưng không thuộc danh mục cấm của Campuchia quy định tại Khoản 4 Điều 4 Hiệp định, chủ hàng gửi Đơn đề nghị cho phép quá cảnh hàng hóa (theo mẫu quy định tại Phụ lục IIA ban hành kèm theo Thông tư này) đến Phòng Quản lý Xuất nhập khẩu khu vực thành phố Hồ Chí Minh (Cục Xuất nhập khẩu - Bộ Công Thương). Địa chỉ: 12 Võ Văn Kiệt, quận 1, thành phố Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 24/2024/TT-BCT · hiệu lực 2024-12-25
+4. Thay thế cụm từ "Địa chỉ: 12 Võ Văn Kiệt, quận 1, thành phố Hồ Chí Minh, Việt Nam" bằng cụm từ "Địa chỉ: 12 Nguyễn Thị Minh Khai, phường Đa Kao, Quận 1, Thành phố Hồ Chí Minh, Việt Nam" tại khoản 2 Điều 3.
+[amend] 38/2025/TT-BCT · hiệu lực 2025-07-01
+(không tìm được đoạn)
+CHUYỂN TIẾP: 3. Quy định chuyển tiếp
+Các Giấy phép, Giấy Chứng nhận, Chứng chỉ, văn bản phê duyệt, văn bản chấp thuận đối với các thủ tục hành chính trong các lĩnh vực đã được cơ quan quản lý nhà nước cấp, phê duyệt, chấp thuận trước ngày 01 tháng 7 năm 2025 tiếp tục có hiệu lực đến hết thời hạn tại Giấy phép, Giấy Chứng nhận, Chứng chỉ, văn bản phê duyệt, văn bản chấp thuận theo quy định.
+[amend] 26/2026/TT-BCT · hiệu lực 2026-05-29
+1. Sửa đổi, bổ sung khoản 2 Điều 3 như sau:
+“2. Đối với hàng hóa không thuộc trường hợp quy định tại Khoản 1 Điều này, việc quá cảnh lãnh thổ Việt Nam chỉ được thực hiện sau khi có giấy phép của cơ quan có thẩm quyền.”.
+CHUYỂN TIẾP: Điều 28. Điều khoản chuyển tiếp
+1. Đối với hồ sơ đề nghị giải quyết thủ tục hành chính thuộc các lĩnh vực được quy định tại Thông tư này đã được cơ quan có thẩm quyền tiếp nhận hoặc đã được đóng dấu bưu chính trước ngày Thông tư này có hiệu lực thì thực hiện theo quy định của pháp luật đang có hiệu lực điều chỉnh trong lĩnh vực đó tại thời điểm hồ sơ được tiếp nhận.
+2. Văn bản, giấy tờ đã được cơ quan, chức danh có thẩm quyền ban hành, cấp trước ngày Thông tư này có hiệu lực thi hành mà chưa hết hiệu lực hoặc chưa hết thời hạn sử dụng thì tiếp tục được áp dụng, sử dụng theo quy định của pháp luật cho đến khi hết thời hạn hoặc được sửa đổi, bổ sung, điều chỉnh, gia hạn, cấp lại, thay thế, bãi bỏ, hủy bỏ, thu hồi bởi cơ quan, chức danh tiếp nhận chức năng, nhiệm vụ, quyền hạn hoặc cơ quan, người có thẩm quyền./.
+Nơi nhận:
+- Văn phòng Tổng bí thư;
+- Văn phòng Chủ tịch nước;
+- Văn phòng Quốc hội;
+- Thủ tướng và các Phó Thủ tướng Chính phủ;
+- Các Bộ, cơ quan ngang Bộ, cơ quan thuộc CP;
+- Viện KSNDTC; Tòa án NDTC;
+- Kiểm toán Nhà nước;
+- Các Lãnh đạo Bộ; đơn vị thuộc Bộ;
+- UBND, HĐND các tỉnh, thành phố trực thuộc TW;
+- Các Sở Công Thương;
+- Cục Kiểm tra văn bản và Quản lý xử lý vi phạm hành chính, Bộ Tư pháp;
+- Cục Kiểm soát thủ tục hành chính, Bộ Tư pháp;
+- Website Chính phủ; Website Bộ Công Thương;
+- Công báo;
+- Lưu: VT, VPB (10).
+KT. BỘ TRƯỞNG
+THỨ TRƯỞNG
+(Đã ký)
+Phan Thị Thắng</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -8427,7 +10801,6 @@
           <t>actor_has_transitional</t>
         </is>
       </c>
-      <c r="M95" t="inlineStr"/>
       <c r="N95" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -8438,18 +10811,54 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P95" t="inlineStr"/>
-      <c r="Q95" t="inlineStr"/>
       <c r="R95" t="inlineStr">
         <is>
           <t>Hỏi cơ quan và địa chỉ: bốn đáp án khác nhau; id cũ vilextime:T3:provision:ec4a796a-df40-11f0-b831-318b010cb040:2024-12-26 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S95" t="inlineStr"/>
-      <c r="T95" t="inlineStr"/>
-      <c r="U95" t="inlineStr"/>
-      <c r="V95" t="inlineStr"/>
-      <c r="W95" t="inlineStr"/>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>27/2014/TT-BCT · hiệu lực 2014-10-20 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 3. Cấp giấy phép quá cảnh hàng hóa
+2. Đối với hàng hóa thuộc danh mục cấm của Việt Nam nhưng không thuộc danh mục cấm của Campuchia quy định tại Khoản 4 Điều 4 Hiệp định, chủ hàng gửi Đơn đề nghị cho phép quá cảnh hàng hóa (theo mẫu quy định tại Phụ lục IIA ban hành kèm theo Thông tư này) đến Phòng Quản lý Xuất nhập khẩu khu vực thành phố Hồ Chí Minh (Cục Xuất nhập khẩu - Bộ Công Thương). Địa chỉ: 12 Võ Văn Kiệt, quận 1, thành phố Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 24/2024/TT-BCT · hiệu lực 2024-12-25
+4. Thay thế cụm từ "Địa chỉ: 12 Võ Văn Kiệt, quận 1, thành phố Hồ Chí Minh, Việt Nam" bằng cụm từ "Địa chỉ: 12 Nguyễn Thị Minh Khai, phường Đa Kao, Quận 1, Thành phố Hồ Chí Minh, Việt Nam" tại khoản 2 Điều 3.
+[amend] 38/2025/TT-BCT · hiệu lực 2025-07-01
+(không tìm được đoạn)
+CHUYỂN TIẾP: 3. Quy định chuyển tiếp
+Các Giấy phép, Giấy Chứng nhận, Chứng chỉ, văn bản phê duyệt, văn bản chấp thuận đối với các thủ tục hành chính trong các lĩnh vực đã được cơ quan quản lý nhà nước cấp, phê duyệt, chấp thuận trước ngày 01 tháng 7 năm 2025 tiếp tục có hiệu lực đến hết thời hạn tại Giấy phép, Giấy Chứng nhận, Chứng chỉ, văn bản phê duyệt, văn bản chấp thuận theo quy định.
+[amend] 26/2026/TT-BCT · hiệu lực 2026-05-29
+1. Sửa đổi, bổ sung khoản 2 Điều 3 như sau:
+“2. Đối với hàng hóa không thuộc trường hợp quy định tại Khoản 1 Điều này, việc quá cảnh lãnh thổ Việt Nam chỉ được thực hiện sau khi có giấy phép của cơ quan có thẩm quyền.”.
+CHUYỂN TIẾP: Điều 28. Điều khoản chuyển tiếp
+1. Đối với hồ sơ đề nghị giải quyết thủ tục hành chính thuộc các lĩnh vực được quy định tại Thông tư này đã được cơ quan có thẩm quyền tiếp nhận hoặc đã được đóng dấu bưu chính trước ngày Thông tư này có hiệu lực thì thực hiện theo quy định của pháp luật đang có hiệu lực điều chỉnh trong lĩnh vực đó tại thời điểm hồ sơ được tiếp nhận.
+2. Văn bản, giấy tờ đã được cơ quan, chức danh có thẩm quyền ban hành, cấp trước ngày Thông tư này có hiệu lực thi hành mà chưa hết hiệu lực hoặc chưa hết thời hạn sử dụng thì tiếp tục được áp dụng, sử dụng theo quy định của pháp luật cho đến khi hết thời hạn hoặc được sửa đổi, bổ sung, điều chỉnh, gia hạn, cấp lại, thay thế, bãi bỏ, hủy bỏ, thu hồi bởi cơ quan, chức danh tiếp nhận chức năng, nhiệm vụ, quyền hạn hoặc cơ quan, người có thẩm quyền./.
+Nơi nhận:
+- Văn phòng Tổng bí thư;
+- Văn phòng Chủ tịch nước;
+- Văn phòng Quốc hội;
+- Thủ tướng và các Phó Thủ tướng Chính phủ;
+- Các Bộ, cơ quan ngang Bộ, cơ quan thuộc CP;
+- Viện KSNDTC; Tòa án NDTC;
+- Kiểm toán Nhà nước;
+- Các Lãnh đạo Bộ; đơn vị thuộc Bộ;
+- UBND, HĐND các tỉnh, thành phố trực thuộc TW;
+- Các Sở Công Thương;
+- Cục Kiểm tra văn bản và Quản lý xử lý vi phạm hành chính, Bộ Tư pháp;
+- Cục Kiểm soát thủ tục hành chính, Bộ Tư pháp;
+- Website Chính phủ; Website Bộ Công Thương;
+- Công báo;
+- Lưu: VT, VPB (10).
+KT. BỘ TRƯỞNG
+THỨ TRƯỞNG
+(Đã ký)
+Phan Thị Thắng</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -8512,7 +10921,6 @@
           <t>actor_has_transitional</t>
         </is>
       </c>
-      <c r="M96" t="inlineStr"/>
       <c r="N96" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -8523,18 +10931,54 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P96" t="inlineStr"/>
-      <c r="Q96" t="inlineStr"/>
       <c r="R96" t="inlineStr">
         <is>
           <t>Hỏi cơ quan và địa chỉ: bốn đáp án khác nhau; id cũ vilextime:T3:provision:ec4a796a-df40-11f0-b831-318b010cb040:2025-07-02 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S96" t="inlineStr"/>
-      <c r="T96" t="inlineStr"/>
-      <c r="U96" t="inlineStr"/>
-      <c r="V96" t="inlineStr"/>
-      <c r="W96" t="inlineStr"/>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>27/2014/TT-BCT · hiệu lực 2014-10-20 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 3. Cấp giấy phép quá cảnh hàng hóa
+2. Đối với hàng hóa thuộc danh mục cấm của Việt Nam nhưng không thuộc danh mục cấm của Campuchia quy định tại Khoản 4 Điều 4 Hiệp định, chủ hàng gửi Đơn đề nghị cho phép quá cảnh hàng hóa (theo mẫu quy định tại Phụ lục IIA ban hành kèm theo Thông tư này) đến Phòng Quản lý Xuất nhập khẩu khu vực thành phố Hồ Chí Minh (Cục Xuất nhập khẩu - Bộ Công Thương). Địa chỉ: 12 Võ Văn Kiệt, quận 1, thành phố Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 24/2024/TT-BCT · hiệu lực 2024-12-25
+4. Thay thế cụm từ "Địa chỉ: 12 Võ Văn Kiệt, quận 1, thành phố Hồ Chí Minh, Việt Nam" bằng cụm từ "Địa chỉ: 12 Nguyễn Thị Minh Khai, phường Đa Kao, Quận 1, Thành phố Hồ Chí Minh, Việt Nam" tại khoản 2 Điều 3.
+[amend] 38/2025/TT-BCT · hiệu lực 2025-07-01
+(không tìm được đoạn)
+CHUYỂN TIẾP: 3. Quy định chuyển tiếp
+Các Giấy phép, Giấy Chứng nhận, Chứng chỉ, văn bản phê duyệt, văn bản chấp thuận đối với các thủ tục hành chính trong các lĩnh vực đã được cơ quan quản lý nhà nước cấp, phê duyệt, chấp thuận trước ngày 01 tháng 7 năm 2025 tiếp tục có hiệu lực đến hết thời hạn tại Giấy phép, Giấy Chứng nhận, Chứng chỉ, văn bản phê duyệt, văn bản chấp thuận theo quy định.
+[amend] 26/2026/TT-BCT · hiệu lực 2026-05-29
+1. Sửa đổi, bổ sung khoản 2 Điều 3 như sau:
+“2. Đối với hàng hóa không thuộc trường hợp quy định tại Khoản 1 Điều này, việc quá cảnh lãnh thổ Việt Nam chỉ được thực hiện sau khi có giấy phép của cơ quan có thẩm quyền.”.
+CHUYỂN TIẾP: Điều 28. Điều khoản chuyển tiếp
+1. Đối với hồ sơ đề nghị giải quyết thủ tục hành chính thuộc các lĩnh vực được quy định tại Thông tư này đã được cơ quan có thẩm quyền tiếp nhận hoặc đã được đóng dấu bưu chính trước ngày Thông tư này có hiệu lực thì thực hiện theo quy định của pháp luật đang có hiệu lực điều chỉnh trong lĩnh vực đó tại thời điểm hồ sơ được tiếp nhận.
+2. Văn bản, giấy tờ đã được cơ quan, chức danh có thẩm quyền ban hành, cấp trước ngày Thông tư này có hiệu lực thi hành mà chưa hết hiệu lực hoặc chưa hết thời hạn sử dụng thì tiếp tục được áp dụng, sử dụng theo quy định của pháp luật cho đến khi hết thời hạn hoặc được sửa đổi, bổ sung, điều chỉnh, gia hạn, cấp lại, thay thế, bãi bỏ, hủy bỏ, thu hồi bởi cơ quan, chức danh tiếp nhận chức năng, nhiệm vụ, quyền hạn hoặc cơ quan, người có thẩm quyền./.
+Nơi nhận:
+- Văn phòng Tổng bí thư;
+- Văn phòng Chủ tịch nước;
+- Văn phòng Quốc hội;
+- Thủ tướng và các Phó Thủ tướng Chính phủ;
+- Các Bộ, cơ quan ngang Bộ, cơ quan thuộc CP;
+- Viện KSNDTC; Tòa án NDTC;
+- Kiểm toán Nhà nước;
+- Các Lãnh đạo Bộ; đơn vị thuộc Bộ;
+- UBND, HĐND các tỉnh, thành phố trực thuộc TW;
+- Các Sở Công Thương;
+- Cục Kiểm tra văn bản và Quản lý xử lý vi phạm hành chính, Bộ Tư pháp;
+- Cục Kiểm soát thủ tục hành chính, Bộ Tư pháp;
+- Website Chính phủ; Website Bộ Công Thương;
+- Công báo;
+- Lưu: VT, VPB (10).
+KT. BỘ TRƯỞNG
+THỨ TRƯỞNG
+(Đã ký)
+Phan Thị Thắng</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -8597,7 +11041,6 @@
           <t>actor_has_transitional</t>
         </is>
       </c>
-      <c r="M97" t="inlineStr"/>
       <c r="N97" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -8608,18 +11051,54 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P97" t="inlineStr"/>
-      <c r="Q97" t="inlineStr"/>
       <c r="R97" t="inlineStr">
         <is>
           <t>Hỏi cơ quan và địa chỉ: bốn đáp án khác nhau; id cũ vilextime:T3:provision:ec4a796a-df40-11f0-b831-318b010cb040:2026-05-30 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S97" t="inlineStr"/>
-      <c r="T97" t="inlineStr"/>
-      <c r="U97" t="inlineStr"/>
-      <c r="V97" t="inlineStr"/>
-      <c r="W97" t="inlineStr"/>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>27/2014/TT-BCT · hiệu lực 2014-10-20 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 3. Cấp giấy phép quá cảnh hàng hóa
+2. Đối với hàng hóa thuộc danh mục cấm của Việt Nam nhưng không thuộc danh mục cấm của Campuchia quy định tại Khoản 4 Điều 4 Hiệp định, chủ hàng gửi Đơn đề nghị cho phép quá cảnh hàng hóa (theo mẫu quy định tại Phụ lục IIA ban hành kèm theo Thông tư này) đến Phòng Quản lý Xuất nhập khẩu khu vực thành phố Hồ Chí Minh (Cục Xuất nhập khẩu - Bộ Công Thương). Địa chỉ: 12 Võ Văn Kiệt, quận 1, thành phố Hồ Chí Minh, Việt Nam.</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 24/2024/TT-BCT · hiệu lực 2024-12-25
+4. Thay thế cụm từ "Địa chỉ: 12 Võ Văn Kiệt, quận 1, thành phố Hồ Chí Minh, Việt Nam" bằng cụm từ "Địa chỉ: 12 Nguyễn Thị Minh Khai, phường Đa Kao, Quận 1, Thành phố Hồ Chí Minh, Việt Nam" tại khoản 2 Điều 3.
+[amend] 38/2025/TT-BCT · hiệu lực 2025-07-01
+(không tìm được đoạn)
+CHUYỂN TIẾP: 3. Quy định chuyển tiếp
+Các Giấy phép, Giấy Chứng nhận, Chứng chỉ, văn bản phê duyệt, văn bản chấp thuận đối với các thủ tục hành chính trong các lĩnh vực đã được cơ quan quản lý nhà nước cấp, phê duyệt, chấp thuận trước ngày 01 tháng 7 năm 2025 tiếp tục có hiệu lực đến hết thời hạn tại Giấy phép, Giấy Chứng nhận, Chứng chỉ, văn bản phê duyệt, văn bản chấp thuận theo quy định.
+[amend] 26/2026/TT-BCT · hiệu lực 2026-05-29
+1. Sửa đổi, bổ sung khoản 2 Điều 3 như sau:
+“2. Đối với hàng hóa không thuộc trường hợp quy định tại Khoản 1 Điều này, việc quá cảnh lãnh thổ Việt Nam chỉ được thực hiện sau khi có giấy phép của cơ quan có thẩm quyền.”.
+CHUYỂN TIẾP: Điều 28. Điều khoản chuyển tiếp
+1. Đối với hồ sơ đề nghị giải quyết thủ tục hành chính thuộc các lĩnh vực được quy định tại Thông tư này đã được cơ quan có thẩm quyền tiếp nhận hoặc đã được đóng dấu bưu chính trước ngày Thông tư này có hiệu lực thì thực hiện theo quy định của pháp luật đang có hiệu lực điều chỉnh trong lĩnh vực đó tại thời điểm hồ sơ được tiếp nhận.
+2. Văn bản, giấy tờ đã được cơ quan, chức danh có thẩm quyền ban hành, cấp trước ngày Thông tư này có hiệu lực thi hành mà chưa hết hiệu lực hoặc chưa hết thời hạn sử dụng thì tiếp tục được áp dụng, sử dụng theo quy định của pháp luật cho đến khi hết thời hạn hoặc được sửa đổi, bổ sung, điều chỉnh, gia hạn, cấp lại, thay thế, bãi bỏ, hủy bỏ, thu hồi bởi cơ quan, chức danh tiếp nhận chức năng, nhiệm vụ, quyền hạn hoặc cơ quan, người có thẩm quyền./.
+Nơi nhận:
+- Văn phòng Tổng bí thư;
+- Văn phòng Chủ tịch nước;
+- Văn phòng Quốc hội;
+- Thủ tướng và các Phó Thủ tướng Chính phủ;
+- Các Bộ, cơ quan ngang Bộ, cơ quan thuộc CP;
+- Viện KSNDTC; Tòa án NDTC;
+- Kiểm toán Nhà nước;
+- Các Lãnh đạo Bộ; đơn vị thuộc Bộ;
+- UBND, HĐND các tỉnh, thành phố trực thuộc TW;
+- Các Sở Công Thương;
+- Cục Kiểm tra văn bản và Quản lý xử lý vi phạm hành chính, Bộ Tư pháp;
+- Cục Kiểm soát thủ tục hành chính, Bộ Tư pháp;
+- Website Chính phủ; Website Bộ Công Thương;
+- Công báo;
+- Lưu: VT, VPB (10).
+KT. BỘ TRƯỞNG
+THỨ TRƯỞNG
+(Đã ký)
+Phan Thị Thắng</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -8677,8 +11156,6 @@
           <t>06/2022/TT-NHNN; 22/2024/TT-NHNN</t>
         </is>
       </c>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr"/>
       <c r="N98" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -8689,18 +11166,31 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P98" t="inlineStr"/>
-      <c r="Q98" t="inlineStr"/>
       <c r="R98" t="inlineStr">
         <is>
           <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Việc mua cổ phần dẫn đến trở thành cổ đông lớn của ngân hàng thương mại cần Ngân hàng Nhà nước chấp thuận trong những trường hợp nào?»; nhãn cũ khong_dat question_ambiguous: Khoản 3 chỉ nói trường hợp mua cổ phần khi ngân hàng tăng vốn điều lệ; câu hỏi không nêu trường hợp đó, và khoản 2 cùng Điều là hồ sơ chấp thuận mua, nhận chuyển nhượng cổ phần dẫn đến trở thành cổ đông lớn nói chung). Ba đáp án khác nhau: mốc 1 chỉ mua dẫn tới cổ đông lớn theo Điều 12; mốc 2 thêm mua của cổ đông lớn và ngoại lệ ngoài danh sách đã chấp thuận; mốc 3 bỏ lại trường hợp mua của cổ đông lớn; id cũ vilextime:T3:provision:f2947168-df4f-11f0-b8a1-cba0d0f18fba:2019-02-16 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S98" t="inlineStr"/>
-      <c r="T98" t="inlineStr"/>
-      <c r="U98" t="inlineStr"/>
-      <c r="V98" t="inlineStr"/>
-      <c r="W98" t="inlineStr"/>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>50/2018/TT-NHNN · hiệu lực 2019-02-15 → 2026-02-07 · lúc thu thập: Hết hiệu lực toàn bộ
+Điều 17. Mua, bán, chuyển nhượng cổ phần của cổ đông lớn; mua, bán, chuyển nhượng cổ phần dẫn đến trở thành cổ đông lớn
+3. Việc mua cổ phần của tổ chức, cá nhân dẫn đến tổ chức, cá nhân đó trở thành cổ đông lớn trong trường hợp ngân hàng thương mại cổ phần tăng mức vốn điều lệ, hồ sơ, trình tự, thủ tục thực hiện theo quy định tại Điều 12 Thông tư này.</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 06/2022/TT-NHNN · hiệu lực 2022-08-15
+6. Sửa đổi, bổ sung khoản 3 Điều 17 như sau:
+"3. Việc mua cổ phần của tổ chức, cá nhân dẫn đến tổ chức, cá nhân đó trở thành cổ đông lớn hoặc mua cổ phần của cổ đông lớn trong trường hợp ngân hàng thương mại cổ phần tăng mức vốn điều lệ, hồ sơ, trình tự, thủ tục thực hiện theo quy định tại Điều 12 Thông tư này.Việc mua cổ phần của tổ chức, cá nhân dẫn đến tổ chức, cá nhân đó trở thành cổ đông lớn hoặc mua cổ phần của cổ đông lớn trong trường hợp ngân hàng thương mại cổ phần tăng mức vốn điều lệ mà tổ chức, cá nhân hoặc cổ đông lớn đó không thuộc danh sách cổ đông mua cổ phần của ngân hàng thương mại cổ phần tại điểm d khoản 1 Điều 12 Thông tư này đã được Ngân hàng Nhà nước chấp thuận thì thực hiện theo quy định tại khoản 1, khoản 2 Điều này và khoản 2 Điều 15 Thông tư này. Văn bản chấp thuận của Ngân hàng Nhà nước về việc mua cổ phần này là bộ phận không tách rời của văn bản chấp thuận tăng mức vốn điều lệ."
+CHUYỂN TIẾP: Điều 2. Quy định chuyển tiếp
+Văn bản đề nghị sửa đổi địa điểm đặt trụ sở chính của ngân hàng thương mại, trụ sở của chi nhánh ngân hàng nước ngoài tại Giấy phép đã nộp trước ngày Thông tư này có hiệu lực thi hành được tiếp tục xem xét, xử lý theo quy định của pháp luật tại thời điểm nộp hồ sơ.
+[amend] 22/2024/TT-NHNN · hiệu lực 2024-07-01
+11. Sửa đổi, bổ sung khoản 3 Điều 17 như sau:
+"3. Việc mua cổ phần của tổ chức, cá nhân dẫn đến tổ chức, cá nhân đó trở thành cổ đông lớn trong trường hợp ngân hàng thương mại cổ phần tăng mức vốn điều lệ, hồ sơ, thủ tục thực hiện theo quy định tại Điều 12 Thông tư này.
+Việc mua cổ phần của tổ chức, cá nhân dẫn đến tổ chức, cá nhân đó trở thành cổ đông lớn trong trường hợp ngân hàng thương mại cổ phần tăng mức vốn điều lệ mà tổ chức, cá nhân đó không thuộc danh sách cổ đông mua cổ phần của ngân hàng thương mại cổ phần tại điểm d khoản 1 Điều 12 Thông tư này đã được Ngân hàng Nhà nước chấp thuận thì thực hiện theo quy định tại khoản 1, khoản 2 Điều này và khoản 2 Điều 15 Thông tư này. Văn bản chấp thuận của Ngân hàng Nhà nước về việc mua cổ phần này là bộ phận không tách rời của văn bản chấp thuận tăng mức vốn điều lệ."</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -8758,8 +11248,6 @@
           <t>06/2022/TT-NHNN; 22/2024/TT-NHNN</t>
         </is>
       </c>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr"/>
       <c r="N99" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -8770,18 +11258,31 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P99" t="inlineStr"/>
-      <c r="Q99" t="inlineStr"/>
       <c r="R99" t="inlineStr">
         <is>
           <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Việc mua cổ phần dẫn đến trở thành cổ đông lớn của ngân hàng thương mại cần Ngân hàng Nhà nước chấp thuận trong những trường hợp nào?»; nhãn cũ khong_dat question_ambiguous: Khoản 3 chỉ nói trường hợp mua cổ phần khi ngân hàng tăng vốn điều lệ; câu hỏi không nêu trường hợp đó, và khoản 2 cùng Điều là hồ sơ chấp thuận mua, nhận chuyển nhượng cổ phần dẫn đến trở thành cổ đông lớn nói chung). Ba đáp án khác nhau: mốc 1 chỉ mua dẫn tới cổ đông lớn theo Điều 12; mốc 2 thêm mua của cổ đông lớn và ngoại lệ ngoài danh sách đã chấp thuận; mốc 3 bỏ lại trường hợp mua của cổ đông lớn; id cũ vilextime:T3:provision:f2947168-df4f-11f0-b8a1-cba0d0f18fba:2022-08-16 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S99" t="inlineStr"/>
-      <c r="T99" t="inlineStr"/>
-      <c r="U99" t="inlineStr"/>
-      <c r="V99" t="inlineStr"/>
-      <c r="W99" t="inlineStr"/>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>50/2018/TT-NHNN · hiệu lực 2019-02-15 → 2026-02-07 · lúc thu thập: Hết hiệu lực toàn bộ
+Điều 17. Mua, bán, chuyển nhượng cổ phần của cổ đông lớn; mua, bán, chuyển nhượng cổ phần dẫn đến trở thành cổ đông lớn
+3. Việc mua cổ phần của tổ chức, cá nhân dẫn đến tổ chức, cá nhân đó trở thành cổ đông lớn trong trường hợp ngân hàng thương mại cổ phần tăng mức vốn điều lệ, hồ sơ, trình tự, thủ tục thực hiện theo quy định tại Điều 12 Thông tư này.</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 06/2022/TT-NHNN · hiệu lực 2022-08-15
+6. Sửa đổi, bổ sung khoản 3 Điều 17 như sau:
+"3. Việc mua cổ phần của tổ chức, cá nhân dẫn đến tổ chức, cá nhân đó trở thành cổ đông lớn hoặc mua cổ phần của cổ đông lớn trong trường hợp ngân hàng thương mại cổ phần tăng mức vốn điều lệ, hồ sơ, trình tự, thủ tục thực hiện theo quy định tại Điều 12 Thông tư này.Việc mua cổ phần của tổ chức, cá nhân dẫn đến tổ chức, cá nhân đó trở thành cổ đông lớn hoặc mua cổ phần của cổ đông lớn trong trường hợp ngân hàng thương mại cổ phần tăng mức vốn điều lệ mà tổ chức, cá nhân hoặc cổ đông lớn đó không thuộc danh sách cổ đông mua cổ phần của ngân hàng thương mại cổ phần tại điểm d khoản 1 Điều 12 Thông tư này đã được Ngân hàng Nhà nước chấp thuận thì thực hiện theo quy định tại khoản 1, khoản 2 Điều này và khoản 2 Điều 15 Thông tư này. Văn bản chấp thuận của Ngân hàng Nhà nước về việc mua cổ phần này là bộ phận không tách rời của văn bản chấp thuận tăng mức vốn điều lệ."
+CHUYỂN TIẾP: Điều 2. Quy định chuyển tiếp
+Văn bản đề nghị sửa đổi địa điểm đặt trụ sở chính của ngân hàng thương mại, trụ sở của chi nhánh ngân hàng nước ngoài tại Giấy phép đã nộp trước ngày Thông tư này có hiệu lực thi hành được tiếp tục xem xét, xử lý theo quy định của pháp luật tại thời điểm nộp hồ sơ.
+[amend] 22/2024/TT-NHNN · hiệu lực 2024-07-01
+11. Sửa đổi, bổ sung khoản 3 Điều 17 như sau:
+"3. Việc mua cổ phần của tổ chức, cá nhân dẫn đến tổ chức, cá nhân đó trở thành cổ đông lớn trong trường hợp ngân hàng thương mại cổ phần tăng mức vốn điều lệ, hồ sơ, thủ tục thực hiện theo quy định tại Điều 12 Thông tư này.
+Việc mua cổ phần của tổ chức, cá nhân dẫn đến tổ chức, cá nhân đó trở thành cổ đông lớn trong trường hợp ngân hàng thương mại cổ phần tăng mức vốn điều lệ mà tổ chức, cá nhân đó không thuộc danh sách cổ đông mua cổ phần của ngân hàng thương mại cổ phần tại điểm d khoản 1 Điều 12 Thông tư này đã được Ngân hàng Nhà nước chấp thuận thì thực hiện theo quy định tại khoản 1, khoản 2 Điều này và khoản 2 Điều 15 Thông tư này. Văn bản chấp thuận của Ngân hàng Nhà nước về việc mua cổ phần này là bộ phận không tách rời của văn bản chấp thuận tăng mức vốn điều lệ."</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -8839,8 +11340,6 @@
           <t>06/2022/TT-NHNN; 22/2024/TT-NHNN</t>
         </is>
       </c>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr"/>
       <c r="N100" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -8851,18 +11350,31 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P100" t="inlineStr"/>
-      <c r="Q100" t="inlineStr"/>
       <c r="R100" t="inlineStr">
         <is>
           <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Việc mua cổ phần dẫn đến trở thành cổ đông lớn của ngân hàng thương mại cần Ngân hàng Nhà nước chấp thuận trong những trường hợp nào?»; nhãn cũ khong_dat question_ambiguous: Khoản 3 chỉ nói trường hợp mua cổ phần khi ngân hàng tăng vốn điều lệ; câu hỏi không nêu trường hợp đó, và khoản 2 cùng Điều là hồ sơ chấp thuận mua, nhận chuyển nhượng cổ phần dẫn đến trở thành cổ đông lớn nói chung). Ba đáp án khác nhau: mốc 1 chỉ mua dẫn tới cổ đông lớn theo Điều 12; mốc 2 thêm mua của cổ đông lớn và ngoại lệ ngoài danh sách đã chấp thuận; mốc 3 bỏ lại trường hợp mua của cổ đông lớn; id cũ vilextime:T3:provision:f2947168-df4f-11f0-b8a1-cba0d0f18fba:2024-07-02 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S100" t="inlineStr"/>
-      <c r="T100" t="inlineStr"/>
-      <c r="U100" t="inlineStr"/>
-      <c r="V100" t="inlineStr"/>
-      <c r="W100" t="inlineStr"/>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>50/2018/TT-NHNN · hiệu lực 2019-02-15 → 2026-02-07 · lúc thu thập: Hết hiệu lực toàn bộ
+Điều 17. Mua, bán, chuyển nhượng cổ phần của cổ đông lớn; mua, bán, chuyển nhượng cổ phần dẫn đến trở thành cổ đông lớn
+3. Việc mua cổ phần của tổ chức, cá nhân dẫn đến tổ chức, cá nhân đó trở thành cổ đông lớn trong trường hợp ngân hàng thương mại cổ phần tăng mức vốn điều lệ, hồ sơ, trình tự, thủ tục thực hiện theo quy định tại Điều 12 Thông tư này.</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 06/2022/TT-NHNN · hiệu lực 2022-08-15
+6. Sửa đổi, bổ sung khoản 3 Điều 17 như sau:
+"3. Việc mua cổ phần của tổ chức, cá nhân dẫn đến tổ chức, cá nhân đó trở thành cổ đông lớn hoặc mua cổ phần của cổ đông lớn trong trường hợp ngân hàng thương mại cổ phần tăng mức vốn điều lệ, hồ sơ, trình tự, thủ tục thực hiện theo quy định tại Điều 12 Thông tư này.Việc mua cổ phần của tổ chức, cá nhân dẫn đến tổ chức, cá nhân đó trở thành cổ đông lớn hoặc mua cổ phần của cổ đông lớn trong trường hợp ngân hàng thương mại cổ phần tăng mức vốn điều lệ mà tổ chức, cá nhân hoặc cổ đông lớn đó không thuộc danh sách cổ đông mua cổ phần của ngân hàng thương mại cổ phần tại điểm d khoản 1 Điều 12 Thông tư này đã được Ngân hàng Nhà nước chấp thuận thì thực hiện theo quy định tại khoản 1, khoản 2 Điều này và khoản 2 Điều 15 Thông tư này. Văn bản chấp thuận của Ngân hàng Nhà nước về việc mua cổ phần này là bộ phận không tách rời của văn bản chấp thuận tăng mức vốn điều lệ."
+CHUYỂN TIẾP: Điều 2. Quy định chuyển tiếp
+Văn bản đề nghị sửa đổi địa điểm đặt trụ sở chính của ngân hàng thương mại, trụ sở của chi nhánh ngân hàng nước ngoài tại Giấy phép đã nộp trước ngày Thông tư này có hiệu lực thi hành được tiếp tục xem xét, xử lý theo quy định của pháp luật tại thời điểm nộp hồ sơ.
+[amend] 22/2024/TT-NHNN · hiệu lực 2024-07-01
+11. Sửa đổi, bổ sung khoản 3 Điều 17 như sau:
+"3. Việc mua cổ phần của tổ chức, cá nhân dẫn đến tổ chức, cá nhân đó trở thành cổ đông lớn trong trường hợp ngân hàng thương mại cổ phần tăng mức vốn điều lệ, hồ sơ, thủ tục thực hiện theo quy định tại Điều 12 Thông tư này.
+Việc mua cổ phần của tổ chức, cá nhân dẫn đến tổ chức, cá nhân đó trở thành cổ đông lớn trong trường hợp ngân hàng thương mại cổ phần tăng mức vốn điều lệ mà tổ chức, cá nhân đó không thuộc danh sách cổ đông mua cổ phần của ngân hàng thương mại cổ phần tại điểm d khoản 1 Điều 12 Thông tư này đã được Ngân hàng Nhà nước chấp thuận thì thực hiện theo quy định tại khoản 1, khoản 2 Điều này và khoản 2 Điều 15 Thông tư này. Văn bản chấp thuận của Ngân hàng Nhà nước về việc mua cổ phần này là bộ phận không tách rời của văn bản chấp thuận tăng mức vốn điều lệ."</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -8920,8 +11432,6 @@
           <t>12/2023/TT-BCT; 38/2025/TT-BCT</t>
         </is>
       </c>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr"/>
       <c r="N101" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -8932,18 +11442,43 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P101" t="inlineStr"/>
-      <c r="Q101" t="inlineStr"/>
       <c r="R101" t="inlineStr">
         <is>
           <t>id cũ vilextime:T3:provision:f3c99590-eada-11f0-9062-8d3b36c07159:2018-07-16 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S101" t="inlineStr"/>
-      <c r="T101" t="inlineStr"/>
-      <c r="U101" t="inlineStr"/>
-      <c r="V101" t="inlineStr"/>
-      <c r="W101" t="inlineStr"/>
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>10/2018/TT-BCT · hiệu lực 2018-07-15 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 8. Thu hồi xác nhận kiến thức pháp luật về bán hàng đa cấp
+2. Trình tự, thủ tục thu hồi xác nhận kiến thức pháp luật về bán hàng đa cấp:
+a) Trong thời hạn 10 ngày làm việc kể từ khi xảy ra các trường hợp quy định tại khoản 1 Điều này, Cục Cạnh tranh và Bảo vệ người tiêu dùng ban hành và gửi quyết định thu hồi Xác nhận kiến thức pháp luật về bán hàng đa cấp tới doanh nghiệp. Xác nhận kiến thức pháp luật về bán hàng đa cấp chấm dứt hiệu lực kể từ ngày Cục Cạnh tranh và Bảo vệ người tiêu dùng ban hành quyết định thu hồi.
+b) Cục Cạnh tranh và Bảo vệ người tiêu dùng có trách nhiệm công bố trên trang thông tin điện tử của Cục Cạnh tranh và Bảo vệ người tiêu dùng và Bộ Công Thương việc thu hồi xác nhận kiến thức pháp luật về bán hàng đa cấp của từng doanh nghiệp bán hàng đa cấp.</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 12/2023/TT-BCT · hiệu lực 2023-07-21
+6. Sửa đổi, bổ sung Điều 8 như sau:
+" Điều 8. Thu hồi xác nhận kiến thức pháp luật về bán hàng đa cấp, xác nhận kiến thức cho đầu mối tại địa phương
+1. Ủy ban Cạnh tranh Quốc gia thu hồi xác nhận kiến thức pháp luật về bán hàng đa cấp, kiến thức cho đầu mối tại địa phương trong trường hợp sau:
+a) Phát hiện hồ sơ đăng ký kiểm tra của người được cấp xác nhận có thông tin gian dối;
+b) Doanh nghiệp bán hàng đa cấp chấm dứt hoạt động bán hàng đa cấp;
+c) Người được cấp xác nhận kiến thức pháp luật về bán hàng đa cấp chấm dứt hợp đồng lao động, hợp đồng đào tạo; người được cấp xác nhận kiến thức cho đầu mối tại địa phương chấm dứt vai trò đầu mối tại địa phương với doanh nghiệp bán hàng đa cấp. Doanh nghiệp bán hàng đa cấp có trách nhiệm thông báo cho Cơ quan đã tổ chức kỳ kiểm tra trong 02 ngày làm việc kể từ ngày chấm dứt quan hệ đầu mối tại địa phương hoặc hợp đồng đào tạo với người được cấp xác nhận kiến thức pháp luật về bán hàng đa cấp, kiến thức cho đầu mối tại địa phương.
+2. Trình tự, thủ tục thu hồi xác nhận kiến thức pháp luật về bán hàng đa cấp, xác nhận kiến thức cho đầu mối tại địa phương:
+a) Trong thời hạn 10 ngày làm việc kể từ khi xảy ra các trường hợp quy định tại khoản 1 Điều này, Ủy ban Cạnh tranh Quốc gia ban hành và gửi quyết định thu hồi xác nhận kiến thức pháp luật về bán hàng đa cấp hoặc xác nhận kiến thức cho đầu mối tại địa phương tới doanh nghiệp. Xác nhận kiến thức pháp luật về bán hàng đa cấp hoặc xác nhận kiến thức cho đầu mối tại địa phương chấm dứt hiệu lực kể từ ngày Ủy ban Cạnh tranh Quốc gia ban hành quyết định thu hồi.
+b) Ủy ban Cạnh tranh Quốc gia có trách nhiệm công bố trên trang thông tin điện tử của cơ quan đã tổ chức kỳ kiểm tra việc thu hồi xác nhận kiến thức pháp luật về bán hàng đa cấp hoặc xác nhận kiến thức cho đầu mối tại địa phương của từng doanh nghiệp bán hàng đa cấp."
+[amend] 38/2025/TT-BCT · hiệu lực 2025-07-01
+1. Sửa đổi, bổ sung Điều 8 như sau:
+a) Sửa đổi, bổ sung điểm b khoản 1 như sau:
+“b) Tổ chức đánh giá sự phù hợp được cơ quan có thẩm quyền đánh giá và chỉ định khi đáp ứng các điều kiện tại Nghị định số 74/2018/NĐ-CP ngày 15 tháng 5 năm 2018 của Chính phủ và được sửa đổi, bổ sung tại Nghị định số 154/2018/NĐ-CP ngày 09 tháng 11 năm 2018 của Chính phủ”.
+b) Sửa đổi, bổ sung khoản 2 như sau:
+“2. Các tổ chức đánh giá sự phù hợp đã đăng ký lĩnh vực hoạt động hoặc được cơ quan có thẩm quyền chỉ định phải tuân thủ các quy định về hoạt động đánh giá sự phù hợp và chịu sự kiểm tra, giám sát của cơ quan có thẩm quyền đã cấp Giấy chứng nhận đăng ký lĩnh vực hoạt động hoặc chỉ định.
+Danh sách Tổ chức đánh giá sự phù hợp đã đăng ký lĩnh vực hoạt động hoặc được cơ quan có thẩm quyền chỉ định được đăng tải trên Trang thông tin điện tử của cơ quan có thẩm quyền đã cấp Giấy chứng nhận đăng ký lĩnh vực hoạt động hoặc chỉ định.”
+CHUYỂN TIẾP: 3. Quy định chuyển tiếp
+Các Giấy phép, Giấy Chứng nhận, Chứng chỉ, văn bản phê duyệt, văn bản chấp thuận đối với các thủ tục hành chính trong các lĩnh vực đã được cơ quan quản lý nhà nước cấp, phê duyệt, chấp thuận trước ngày 01 tháng 7 năm 2025 tiếp tục có hiệu lực đến hết thời hạn tại Giấy phép, Giấy Chứng nhận, Chứng chỉ, văn bản phê duyệt, văn bản chấp thuận theo quy định.</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -9021,18 +11556,39 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P102" t="inlineStr"/>
-      <c r="Q102" t="inlineStr"/>
       <c r="R102" t="inlineStr">
         <is>
           <t>Từ mốc 2 câu dẫn gọi Trạm Thú y là 'Cơ quan quản lý chuyên ngành thú y cấp huyện'; id cũ vilextime:T3:provision:f5c84a24-df38-11f0-94cb-634e6f8d12a0:2016-07-02 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S102" t="inlineStr"/>
-      <c r="T102" t="inlineStr"/>
-      <c r="U102" t="inlineStr"/>
-      <c r="V102" t="inlineStr"/>
-      <c r="W102" t="inlineStr"/>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>04/2016/TT-BNNPTNT · hiệu lực 2016-07-01 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 16. Thu hoạch động vật thủy sản trong ổ dịch
+2. Ngay sau khi nhận được thông báo của chủ cơ sở, Trạm Thú y có trách nhiệm:
+a) Phân công cán bộ hướng dẫn, giám sát việc thu hoạch, bảo quản, vận chuyển của cơ sở nuôi có động vật thủy sản mắc bệnh;
+b) Thông báo tên, địa chỉ cơ sở tiếp nhận cho cơ quan quản lý chất lượng nông lâm sản và thủy sản cấp tỉnh nơi tiếp nhận để giám sát tại cơ sở tiếp nhận;
+c) Báo cáo Chi cục Thú y kết quả thực hiện.</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 12/2024/TT-BNNPTNT · hiệu lực 2024-12-12
+23. Sửa đổi, bổ sung điểm a và điểm b khoản 2 Điều 16 như sau:
+“a) Tham mưu cho ủy ban nhân dân cấp huyện hướng dẫn ủy ban nhân dân cấp xã, nhân viên thú y xã và chủ cơ sở nuôi trồng thủy sản thu hoạch động vật thủy sản, giám sát việc thu hoạch và áp dụng các biện pháp phòng chống dịch bệnh động vật theo quy định tại các khoản 1, 2 và khoản 4 Điều 33 Luật Thú y, bảo đảm không làm lây lan dịch bệnh;
+b) Tham mưu cho ủy ban nhân dân cấp huyện chỉ đạo, hướng dẫn chủ cơ sở nuôi trồng thủy sản, người mua bán, vận chuyển động vật thủy sản thực hiện các biện pháp vệ sinh thú y để ngăn chặn dịch bệnh động vật lây lan theo quy định tại khoản 5 Điều 33 Luật Thú y;”.
+CHUYỂN TIẾP: 2. Quy định chuyển tiếp: Đối với các chương trình, kế hoạch, đề án, dự án về phòng chống dịch bệnh động vật thủy sản, quan trắc, cảnh báo môi trường trong nuôi trồng thủy sản đã được cấp có thẩm quyền phê duyệt trước thời điểm Thông tư này có hiệu lực thi hành, tiếp tục triển khai theo chương trình, kế hoạch, đề án, dự án đã được phê duyệt.
+[amend] 10/2025/TT-BNNMT · hiệu lực 2025-07-01
+2. Sửa đổi điểm a và b khoản 2 Điều 16 như sau:
+“a) Hướng dẫn nhân viên thú y xã và chủ cơ sở nuôi trồng thủy sản thu hoạch động vật thủy sản, giám sát việc thu hoạch và áp dụng các biện pháp phòng chống dịch bệnh động vật theo quy định tại các khoản 1, 2 và khoản 4 Điều 33 Luật Thú y, bảo đảm không làm lây lan dịch bệnh;
+b) Chỉ đạo, hướng dẫn chủ cơ sở nuôi trồng thủy sản, người mua bán, vận chuyển động vật thủy sản thực hiện các biện pháp vệ sinh thú y để ngăn chặn dịch bệnh động vật lây lan theo quy định tại khoản 5 Điều 33 Luật Thú y;”
+CHUYỂN TIẾP: Điều 17. Quy định chuyển tiếp
+1. Hồ sơ, biểu mẫu thực hiện thủ tục hành chính đã được cơ quan nhà nước, người có thẩm quyền tiếp nhận trước ngày Thông tư này có hiệu lực mà chưa có kết quả giải quyết thủ tục hành chính thì tiếp tục được giải quyết theo quy định của pháp luật tại thời điểm tiếp nhận; trừ trường hợp tổ chức, cá nhân đề nghị thực hiện theo quy định của Thông tư này.
+2. Các chương trình, kế hoạch, đề án, dự án về phòng chống dịch bệnh động vật thuỷ sản, quan trắc, cảnh báo môi trường trong nuôi trồng thuỷ sản đã được cấp có thẩm quyền phê duyệt trước thời điểm Thông tư này có hiệu lực thi hành, tiếp tục triển khai theo chương trình, kế hoạch, đề án, dự án đã được phê duyệt.
+3. Cơ quan có thẩm quyền cấp, cấp lại Giấy chứng nhận cơ sở đủ điều kiện đăng kiểm tàu cá sau khi được phân quyền, phân cấp có trách nhiệm kiểm tra duy trì điều kiện cơ sở đăng kiểm tàu cá trong thời hạn 24 tháng tính từ ngày Giấy chứng nhận cơ sở đủ điều kiện đăng kiểm tàu cá có hiệu lực.
+4. Đối với dự án thành lập khu bảo tồn biển cấp tỉnh hoặc dự án điều chỉnh ranh giới, diện tích khu bảo tồn biển cấp tỉnh đã tổ chức họp Hội đồng thẩm định liên ngành trước ngày Thông tư này có hiệu lực thì tiếp tục thực hiện cho đến khi Chủ tịch Ủy ban nhân dân cấp tỉnh quyết định thành lập hoặc điều chỉnh ranh giới, diện tích khu bảo tồn biển.</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -9110,18 +11666,39 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P103" t="inlineStr"/>
-      <c r="Q103" t="inlineStr"/>
       <c r="R103" t="inlineStr">
         <is>
           <t>Từ mốc 2 câu dẫn gọi Trạm Thú y là 'Cơ quan quản lý chuyên ngành thú y cấp huyện'; id cũ vilextime:T3:provision:f5c84a24-df38-11f0-94cb-634e6f8d12a0:2024-12-13 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S103" t="inlineStr"/>
-      <c r="T103" t="inlineStr"/>
-      <c r="U103" t="inlineStr"/>
-      <c r="V103" t="inlineStr"/>
-      <c r="W103" t="inlineStr"/>
+      <c r="X103" s="2" t="inlineStr">
+        <is>
+          <t>04/2016/TT-BNNPTNT · hiệu lực 2016-07-01 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 16. Thu hoạch động vật thủy sản trong ổ dịch
+2. Ngay sau khi nhận được thông báo của chủ cơ sở, Trạm Thú y có trách nhiệm:
+a) Phân công cán bộ hướng dẫn, giám sát việc thu hoạch, bảo quản, vận chuyển của cơ sở nuôi có động vật thủy sản mắc bệnh;
+b) Thông báo tên, địa chỉ cơ sở tiếp nhận cho cơ quan quản lý chất lượng nông lâm sản và thủy sản cấp tỉnh nơi tiếp nhận để giám sát tại cơ sở tiếp nhận;
+c) Báo cáo Chi cục Thú y kết quả thực hiện.</t>
+        </is>
+      </c>
+      <c r="Y103" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 12/2024/TT-BNNPTNT · hiệu lực 2024-12-12
+23. Sửa đổi, bổ sung điểm a và điểm b khoản 2 Điều 16 như sau:
+“a) Tham mưu cho ủy ban nhân dân cấp huyện hướng dẫn ủy ban nhân dân cấp xã, nhân viên thú y xã và chủ cơ sở nuôi trồng thủy sản thu hoạch động vật thủy sản, giám sát việc thu hoạch và áp dụng các biện pháp phòng chống dịch bệnh động vật theo quy định tại các khoản 1, 2 và khoản 4 Điều 33 Luật Thú y, bảo đảm không làm lây lan dịch bệnh;
+b) Tham mưu cho ủy ban nhân dân cấp huyện chỉ đạo, hướng dẫn chủ cơ sở nuôi trồng thủy sản, người mua bán, vận chuyển động vật thủy sản thực hiện các biện pháp vệ sinh thú y để ngăn chặn dịch bệnh động vật lây lan theo quy định tại khoản 5 Điều 33 Luật Thú y;”.
+CHUYỂN TIẾP: 2. Quy định chuyển tiếp: Đối với các chương trình, kế hoạch, đề án, dự án về phòng chống dịch bệnh động vật thủy sản, quan trắc, cảnh báo môi trường trong nuôi trồng thủy sản đã được cấp có thẩm quyền phê duyệt trước thời điểm Thông tư này có hiệu lực thi hành, tiếp tục triển khai theo chương trình, kế hoạch, đề án, dự án đã được phê duyệt.
+[amend] 10/2025/TT-BNNMT · hiệu lực 2025-07-01
+2. Sửa đổi điểm a và b khoản 2 Điều 16 như sau:
+“a) Hướng dẫn nhân viên thú y xã và chủ cơ sở nuôi trồng thủy sản thu hoạch động vật thủy sản, giám sát việc thu hoạch và áp dụng các biện pháp phòng chống dịch bệnh động vật theo quy định tại các khoản 1, 2 và khoản 4 Điều 33 Luật Thú y, bảo đảm không làm lây lan dịch bệnh;
+b) Chỉ đạo, hướng dẫn chủ cơ sở nuôi trồng thủy sản, người mua bán, vận chuyển động vật thủy sản thực hiện các biện pháp vệ sinh thú y để ngăn chặn dịch bệnh động vật lây lan theo quy định tại khoản 5 Điều 33 Luật Thú y;”
+CHUYỂN TIẾP: Điều 17. Quy định chuyển tiếp
+1. Hồ sơ, biểu mẫu thực hiện thủ tục hành chính đã được cơ quan nhà nước, người có thẩm quyền tiếp nhận trước ngày Thông tư này có hiệu lực mà chưa có kết quả giải quyết thủ tục hành chính thì tiếp tục được giải quyết theo quy định của pháp luật tại thời điểm tiếp nhận; trừ trường hợp tổ chức, cá nhân đề nghị thực hiện theo quy định của Thông tư này.
+2. Các chương trình, kế hoạch, đề án, dự án về phòng chống dịch bệnh động vật thuỷ sản, quan trắc, cảnh báo môi trường trong nuôi trồng thuỷ sản đã được cấp có thẩm quyền phê duyệt trước thời điểm Thông tư này có hiệu lực thi hành, tiếp tục triển khai theo chương trình, kế hoạch, đề án, dự án đã được phê duyệt.
+3. Cơ quan có thẩm quyền cấp, cấp lại Giấy chứng nhận cơ sở đủ điều kiện đăng kiểm tàu cá sau khi được phân quyền, phân cấp có trách nhiệm kiểm tra duy trì điều kiện cơ sở đăng kiểm tàu cá trong thời hạn 24 tháng tính từ ngày Giấy chứng nhận cơ sở đủ điều kiện đăng kiểm tàu cá có hiệu lực.
+4. Đối với dự án thành lập khu bảo tồn biển cấp tỉnh hoặc dự án điều chỉnh ranh giới, diện tích khu bảo tồn biển cấp tỉnh đã tổ chức họp Hội đồng thẩm định liên ngành trước ngày Thông tư này có hiệu lực thì tiếp tục thực hiện cho đến khi Chủ tịch Ủy ban nhân dân cấp tỉnh quyết định thành lập hoặc điều chỉnh ranh giới, diện tích khu bảo tồn biển.</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -9199,18 +11776,39 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P104" t="inlineStr"/>
-      <c r="Q104" t="inlineStr"/>
       <c r="R104" t="inlineStr">
         <is>
           <t>Từ mốc 2 câu dẫn gọi Trạm Thú y là 'Cơ quan quản lý chuyên ngành thú y cấp huyện'; id cũ vilextime:T3:provision:f5c84a24-df38-11f0-94cb-634e6f8d12a0:2025-07-02 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S104" t="inlineStr"/>
-      <c r="T104" t="inlineStr"/>
-      <c r="U104" t="inlineStr"/>
-      <c r="V104" t="inlineStr"/>
-      <c r="W104" t="inlineStr"/>
+      <c r="X104" s="2" t="inlineStr">
+        <is>
+          <t>04/2016/TT-BNNPTNT · hiệu lực 2016-07-01 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 16. Thu hoạch động vật thủy sản trong ổ dịch
+2. Ngay sau khi nhận được thông báo của chủ cơ sở, Trạm Thú y có trách nhiệm:
+a) Phân công cán bộ hướng dẫn, giám sát việc thu hoạch, bảo quản, vận chuyển của cơ sở nuôi có động vật thủy sản mắc bệnh;
+b) Thông báo tên, địa chỉ cơ sở tiếp nhận cho cơ quan quản lý chất lượng nông lâm sản và thủy sản cấp tỉnh nơi tiếp nhận để giám sát tại cơ sở tiếp nhận;
+c) Báo cáo Chi cục Thú y kết quả thực hiện.</t>
+        </is>
+      </c>
+      <c r="Y104" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 12/2024/TT-BNNPTNT · hiệu lực 2024-12-12
+23. Sửa đổi, bổ sung điểm a và điểm b khoản 2 Điều 16 như sau:
+“a) Tham mưu cho ủy ban nhân dân cấp huyện hướng dẫn ủy ban nhân dân cấp xã, nhân viên thú y xã và chủ cơ sở nuôi trồng thủy sản thu hoạch động vật thủy sản, giám sát việc thu hoạch và áp dụng các biện pháp phòng chống dịch bệnh động vật theo quy định tại các khoản 1, 2 và khoản 4 Điều 33 Luật Thú y, bảo đảm không làm lây lan dịch bệnh;
+b) Tham mưu cho ủy ban nhân dân cấp huyện chỉ đạo, hướng dẫn chủ cơ sở nuôi trồng thủy sản, người mua bán, vận chuyển động vật thủy sản thực hiện các biện pháp vệ sinh thú y để ngăn chặn dịch bệnh động vật lây lan theo quy định tại khoản 5 Điều 33 Luật Thú y;”.
+CHUYỂN TIẾP: 2. Quy định chuyển tiếp: Đối với các chương trình, kế hoạch, đề án, dự án về phòng chống dịch bệnh động vật thủy sản, quan trắc, cảnh báo môi trường trong nuôi trồng thủy sản đã được cấp có thẩm quyền phê duyệt trước thời điểm Thông tư này có hiệu lực thi hành, tiếp tục triển khai theo chương trình, kế hoạch, đề án, dự án đã được phê duyệt.
+[amend] 10/2025/TT-BNNMT · hiệu lực 2025-07-01
+2. Sửa đổi điểm a và b khoản 2 Điều 16 như sau:
+“a) Hướng dẫn nhân viên thú y xã và chủ cơ sở nuôi trồng thủy sản thu hoạch động vật thủy sản, giám sát việc thu hoạch và áp dụng các biện pháp phòng chống dịch bệnh động vật theo quy định tại các khoản 1, 2 và khoản 4 Điều 33 Luật Thú y, bảo đảm không làm lây lan dịch bệnh;
+b) Chỉ đạo, hướng dẫn chủ cơ sở nuôi trồng thủy sản, người mua bán, vận chuyển động vật thủy sản thực hiện các biện pháp vệ sinh thú y để ngăn chặn dịch bệnh động vật lây lan theo quy định tại khoản 5 Điều 33 Luật Thú y;”
+CHUYỂN TIẾP: Điều 17. Quy định chuyển tiếp
+1. Hồ sơ, biểu mẫu thực hiện thủ tục hành chính đã được cơ quan nhà nước, người có thẩm quyền tiếp nhận trước ngày Thông tư này có hiệu lực mà chưa có kết quả giải quyết thủ tục hành chính thì tiếp tục được giải quyết theo quy định của pháp luật tại thời điểm tiếp nhận; trừ trường hợp tổ chức, cá nhân đề nghị thực hiện theo quy định của Thông tư này.
+2. Các chương trình, kế hoạch, đề án, dự án về phòng chống dịch bệnh động vật thuỷ sản, quan trắc, cảnh báo môi trường trong nuôi trồng thuỷ sản đã được cấp có thẩm quyền phê duyệt trước thời điểm Thông tư này có hiệu lực thi hành, tiếp tục triển khai theo chương trình, kế hoạch, đề án, dự án đã được phê duyệt.
+3. Cơ quan có thẩm quyền cấp, cấp lại Giấy chứng nhận cơ sở đủ điều kiện đăng kiểm tàu cá sau khi được phân quyền, phân cấp có trách nhiệm kiểm tra duy trì điều kiện cơ sở đăng kiểm tàu cá trong thời hạn 24 tháng tính từ ngày Giấy chứng nhận cơ sở đủ điều kiện đăng kiểm tàu cá có hiệu lực.
+4. Đối với dự án thành lập khu bảo tồn biển cấp tỉnh hoặc dự án điều chỉnh ranh giới, diện tích khu bảo tồn biển cấp tỉnh đã tổ chức họp Hội đồng thẩm định liên ngành trước ngày Thông tư này có hiệu lực thì tiếp tục thực hiện cho đến khi Chủ tịch Ủy ban nhân dân cấp tỉnh quyết định thành lập hoặc điều chỉnh ranh giới, diện tích khu bảo tồn biển.</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -9268,8 +11866,6 @@
           <t>69/2022/NĐ-CP; 74/2023/NĐ-CP</t>
         </is>
       </c>
-      <c r="L105" t="inlineStr"/>
-      <c r="M105" t="inlineStr"/>
       <c r="N105" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -9280,7 +11876,6 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P105" t="inlineStr"/>
       <c r="Q105" t="inlineStr">
         <is>
           <t>other</t>
@@ -9291,11 +11886,34 @@
           <t>Văn bản đáp án mốc 3 dính cả khoản 3 ('…nêu rõ lý do.3. Khi cấp lại Giấy xác nhận…'); id cũ vilextime:T3:provision:f8d931e0-1df6-11f1-a901-7169bc99fc94:2023-11-28 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S105" t="inlineStr"/>
-      <c r="T105" t="inlineStr"/>
-      <c r="U105" t="inlineStr"/>
-      <c r="V105" t="inlineStr"/>
-      <c r="W105" t="inlineStr"/>
+      <c r="X105" s="2" t="inlineStr">
+        <is>
+          <t>29/2017/NĐ-CP · hiệu lực 2017-07-01 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 14. Cấp lại Giấy xác nhận
+2. Tổ chức tuyển dụng, cung ứng thuyền viên hàng hải nộp trực tiếp hoặc gửi bằng các hình thức phù hợp khác đến Cục Hàng hải Việt Nam văn bản đề nghị cấp lại Giấy xác nhận, trong đó nêu rõ lý do cấp lại kèm theo các tài liệu chứng minh sự thay đổi thông tin về doanh nghiệp) (nếu có). Trong thời hạn 03 ngày làm việc kể từ ngày nhận được văn bản đề nghị, Cục Hàng hải Việt Nam cấp lại Giấy xác nhận; trường hợp không cấp lại phải có văn bản trả lời và nêu rõ lý do.</t>
+        </is>
+      </c>
+      <c r="Y105" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 69/2022/NĐ-CP · hiệu lực 2022-10-30
+2. Sửa đổi, bổ sung khoản 2 Điều 14 như sau:
+"2. Tổ chức tuyển dụng, cung ứng thuyền viên hàng hải gửi trực tiếp hoặc qua hệ thống bưu chính hoặc qua hệ thống dịch vụ công trực tuyến hoặc bằng hình thức phù hợp khác đến Cục Hàng hải Việt Nam 01 bộ hồ sơ đề nghị cấp lại Giấy xác nhận. Hồ sơ bao gồm:
+a) Tờ khai đề nghị cấp lại Giấy xác nhận theo Mẫu số 04 quy định tại Phụ lục ban hành kèm theo Nghị định này;
+b) Bản sao có chứng thực hoặc bản sao kèm bản chính để đối chiếu hoặc bản sao điện tử hoặc bản sao điện tử từ sổ gốc hoặc bản sao điện tử có chứng thực từ bản chính Giấy chứng nhận đăng ký doanh nghiệp (đối với trường hợp thay đổi thông tin về doanh nghiệp);
+c) Bản chính Giấy xác nhận (đối với trường hợp Giấy xác nhận hết thời hạn sử dụng, bị hư hỏng).
+Trong thời hạn 03 ngày làm việc, kể từ ngày nhận được văn bản đề nghị, Cục Hàng hải Việt Nam cấp lại Giấy xác nhận và gửi trực tiếp hoặc qua hệ thống bưu chính hoặc qua hệ thống dịch vụ công trực tuyến hoặc bằng hình thức phù hợp khác đến tổ chức tuyển dụng, cung ứng thuyền viên hàng hải; trường hợp không chấp thuận, Cục Hàng hải Việt Nam phải có văn bản trả lời và nêu rõ lý do."
+[amend] 74/2023/NĐ-CP · hiệu lực 2023-11-27
+8. Sửa đổi, bổ sung khoản 2 và khoản 3 Điều 14 như sau:
+"2. Tổ chức tuyển dụng, cung ứng thuyền viên hàng hải gửi trực tiếp hoặc qua hệ thống bưu chính hoặc qua hệ thống dịch vụ công trực tuyến đến Chi cục Hàng hải Việt Nam 01 bộ hồ sơ đề nghị cấp lại Giấy xác nhận. Hồ sơ bao gồm:
+a) Tờ khai đề nghị cấp lại Giấy xác nhận theo Mẫu số 04 quy định tại Phụ lục ban hành kèm theo Nghị định này;
+b) Bản sao có chứng thực hoặc bản sao kèm bản chính để đối chiếu hoặc bản sao điện tử hoặc bản sao điện tử từ sổ gốc hoặc bản sao điện tử có chứng thực từ bản chính Giấy chứng nhận đăng ký doanh nghiệp (đối với trường hợp thay đổi thông tin về doanh nghiệp);
+Trong thời hạn 03 ngày làm việc, kể từ ngày nhận được văn bản đề nghị, Chi cục Hàng hải Việt Nam cấp lại Giấy xác nhận và trả kết quả trực tiếp hoặc qua hệ thống bưu chính hoặc qua hệ thống dịch vụ công trực tuyến đến tổ chức tuyển dụng, cung ứng thuyền viên hàng hải; trường hợp không chấp thuận, Chi cục Hàng hải Việt Nam phải có văn bản trả lời và nêu rõ lý do.3. Khi cấp lại Giấy xác nhận, Chi cục Hàng hải Việt Nam phải ghi rõ trong Giấy xác nhận mới về việc thay thế Giấy xác nhận cũ và thông báo trên Cổng thông tin điện tử của Chi cục Hàng hải Việt Nam."
+CHUYỂN TIẾP: 2. Điều khoản chuyển tiếp:
+a) Các văn bản chấp thuận, Quyết định, Giấy chứng nhận, Giấy xác nhận đã được cơ quan có thẩm quyền chấp thuận hoặc cấp trước ngày Nghị định này có hiệu lực thi hành thì tiếp tục thực hiện cho đến khi hết thời hạn đã được quy định đối với những văn bản này;
+b) Đối với các hồ sơ đề nghị cấp văn bản chấp thuận, Quyết định, Giấy chứng nhận, Giấy xác nhận đã được cơ quan có thẩm quyền tiếp nhận hồ sơ trước ngày Nghị định này có hiệu lực thi hành thì cơ quan có thẩm quyền đã tiếp nhận hồ sơ tiếp tục thực hiện theo quy định của văn bản quy phạm pháp luật tại thời điểm tiếp nhận hồ sơ;
+c) Cục trưởng Cục Hàng hải Việt Nam có thẩm quyền thu hồi các Giấy chứng nhận; Chi cục trưởng Chi cục Hàng hải Việt Nam có thẩm quyền thu hồi các Giấy xác nhận được cấp trước ngày Nghị định này có hiệu lực thi hành.</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -9358,7 +11976,6 @@
           <t>actor_has_transitional</t>
         </is>
       </c>
-      <c r="M106" t="inlineStr"/>
       <c r="N106" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -9369,18 +11986,29 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P106" t="inlineStr"/>
-      <c r="Q106" t="inlineStr"/>
       <c r="R106" t="inlineStr">
         <is>
           <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Pháp luật về cơ sở dữ liệu quốc gia về khoa học và công nghệ quy định cơ sở dữ liệu tiêu chuẩn đo lường chất lượng do cơ quan nào xây dựng, vận hành?»; nhãn cũ khong_dat group_mismatch: Câu hỏi hỏi cơ quan xây dựng, vận hành: mốc 1 và 2 cùng là Tổng cục Tiêu chuẩn Đo lường Chất lượng (lần sửa 2023 chỉ thêm 'chia sẻ … trực tuyến'), mốc 3 là Ủy ban. Chỉ hai đáp án; có thể chuyển T2 (mốc 2–3)). Hỏi cả cơ quan và cách kết nối: ba đáp án khác nhau; id cũ vilextime:T3:provision:fc52f300-eb84-11f0-ab2c-4f4961cea41c:2017-08-16 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S106" t="inlineStr"/>
-      <c r="T106" t="inlineStr"/>
-      <c r="U106" t="inlineStr"/>
-      <c r="V106" t="inlineStr"/>
-      <c r="W106" t="inlineStr"/>
+      <c r="X106" s="2" t="inlineStr">
+        <is>
+          <t>10/2017/TT-BKHCN · hiệu lực 2017-08-15 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 17. Cơ sở dữ liệu tiêu chuẩn đo lường chất lượng
+2. Cơ sở dữ liệu tiêu chuẩn đo lường chất lượng được xây dựng, quản trị, vận hành và phát triển tại Tổng cục Tiêu chuẩn Đo lường Chất lượng, Bộ Khoa học và Công nghệ và được kết nối với Cơ sở dữ liệu quốc gia về khoa học và công nghệ.</t>
+        </is>
+      </c>
+      <c r="Y106" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 11/2023/TT-BKHCN · hiệu lực 2023-08-10
+b) Sửa đổi, bổ sung khoản 2 như sau:
+"2. Cơ sở dữ liệu về tiêu chuẩn đo lường chất lượng được xây dựng, quản trị, vận hành và phát triển tại Tổng cục Tiêu chuẩn Đo lường Chất lượng, Bộ Khoa học và Công nghệ và được kết nối, chia sẻ với Cơ sở dữ liệu quốc gia về khoa học và công nghệ thông qua phương thức trực tuyến trên môi trường mạng.".
+[amend] 07/2024/TT-BKHCN · hiệu lực 2024-11-22
+Thay thế cụm từ “Tổng cục Tiêu chuẩn Đo lường Chất lượng” bằng cụm từ “Ủy ban Tiêu chuẩn Đo lường Chất lượng Quốc gia” tại khoản 2 Điều 17; khoản 3 Điều 26.
+CHUYỂN TIẾP: Điều 79. Điều khoản chuyển tiếp
+Các nội dung công việc đã giao cho Tổng cục Tiêu chuẩn Đo lường Chất lượng, Tổng cục trưởng Tổng cục Tiêu chuẩn Đo lường Chất lượng thực hiện tại các văn bản quy phạm pháp luật của Bộ trưởng Bộ Khoa học và Công nghệ quy định từ Điều 1 đến Điều 77 của Thông tư này, thì được chuyển giao cho Ủy ban Tiêu chuẩn Đo lường Chất lượng Quốc gia, Chủ tịch Ủy ban Tiêu chuẩn Đo lường Chất lượng Quốc gia để tiếp tục thực hiện.</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -9443,7 +12071,6 @@
           <t>actor_has_transitional</t>
         </is>
       </c>
-      <c r="M107" t="inlineStr"/>
       <c r="N107" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -9454,18 +12081,29 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P107" t="inlineStr"/>
-      <c r="Q107" t="inlineStr"/>
       <c r="R107" t="inlineStr">
         <is>
           <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Pháp luật về cơ sở dữ liệu quốc gia về khoa học và công nghệ quy định cơ sở dữ liệu tiêu chuẩn đo lường chất lượng do cơ quan nào xây dựng, vận hành?»; nhãn cũ khong_dat group_mismatch: Câu hỏi hỏi cơ quan xây dựng, vận hành: mốc 1 và 2 cùng là Tổng cục Tiêu chuẩn Đo lường Chất lượng (lần sửa 2023 chỉ thêm 'chia sẻ … trực tuyến'), mốc 3 là Ủy ban. Chỉ hai đáp án; có thể chuyển T2 (mốc 2–3)). Hỏi cả cơ quan và cách kết nối: ba đáp án khác nhau; id cũ vilextime:T3:provision:fc52f300-eb84-11f0-ab2c-4f4961cea41c:2023-08-11 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S107" t="inlineStr"/>
-      <c r="T107" t="inlineStr"/>
-      <c r="U107" t="inlineStr"/>
-      <c r="V107" t="inlineStr"/>
-      <c r="W107" t="inlineStr"/>
+      <c r="X107" s="2" t="inlineStr">
+        <is>
+          <t>10/2017/TT-BKHCN · hiệu lực 2017-08-15 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 17. Cơ sở dữ liệu tiêu chuẩn đo lường chất lượng
+2. Cơ sở dữ liệu tiêu chuẩn đo lường chất lượng được xây dựng, quản trị, vận hành và phát triển tại Tổng cục Tiêu chuẩn Đo lường Chất lượng, Bộ Khoa học và Công nghệ và được kết nối với Cơ sở dữ liệu quốc gia về khoa học và công nghệ.</t>
+        </is>
+      </c>
+      <c r="Y107" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 11/2023/TT-BKHCN · hiệu lực 2023-08-10
+b) Sửa đổi, bổ sung khoản 2 như sau:
+"2. Cơ sở dữ liệu về tiêu chuẩn đo lường chất lượng được xây dựng, quản trị, vận hành và phát triển tại Tổng cục Tiêu chuẩn Đo lường Chất lượng, Bộ Khoa học và Công nghệ và được kết nối, chia sẻ với Cơ sở dữ liệu quốc gia về khoa học và công nghệ thông qua phương thức trực tuyến trên môi trường mạng.".
+[amend] 07/2024/TT-BKHCN · hiệu lực 2024-11-22
+Thay thế cụm từ “Tổng cục Tiêu chuẩn Đo lường Chất lượng” bằng cụm từ “Ủy ban Tiêu chuẩn Đo lường Chất lượng Quốc gia” tại khoản 2 Điều 17; khoản 3 Điều 26.
+CHUYỂN TIẾP: Điều 79. Điều khoản chuyển tiếp
+Các nội dung công việc đã giao cho Tổng cục Tiêu chuẩn Đo lường Chất lượng, Tổng cục trưởng Tổng cục Tiêu chuẩn Đo lường Chất lượng thực hiện tại các văn bản quy phạm pháp luật của Bộ trưởng Bộ Khoa học và Công nghệ quy định từ Điều 1 đến Điều 77 của Thông tư này, thì được chuyển giao cho Ủy ban Tiêu chuẩn Đo lường Chất lượng Quốc gia, Chủ tịch Ủy ban Tiêu chuẩn Đo lường Chất lượng Quốc gia để tiếp tục thực hiện.</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -9528,7 +12166,6 @@
           <t>actor_has_transitional</t>
         </is>
       </c>
-      <c r="M108" t="inlineStr"/>
       <c r="N108" t="inlineStr">
         <is>
           <t>claude-opus-5-5</t>
@@ -9539,18 +12176,29 @@
           <t>dat</t>
         </is>
       </c>
-      <c r="P108" t="inlineStr"/>
-      <c r="Q108" t="inlineStr"/>
       <c r="R108" t="inlineStr">
         <is>
           <t>Chấm lại 28/09 trên câu hỏi viết lại (câu cũ: «Pháp luật về cơ sở dữ liệu quốc gia về khoa học và công nghệ quy định cơ sở dữ liệu tiêu chuẩn đo lường chất lượng do cơ quan nào xây dựng, vận hành?»; nhãn cũ khong_dat group_mismatch: Câu hỏi hỏi cơ quan xây dựng, vận hành: mốc 1 và 2 cùng là Tổng cục Tiêu chuẩn Đo lường Chất lượng (lần sửa 2023 chỉ thêm 'chia sẻ … trực tuyến'), mốc 3 là Ủy ban. Chỉ hai đáp án; có thể chuyển T2 (mốc 2–3)). Hỏi cả cơ quan và cách kết nối: ba đáp án khác nhau; id cũ vilextime:T3:provision:fc52f300-eb84-11f0-ab2c-4f4961cea41c:2024-11-23 (ngày hỏi dời 29/09, cùng câu hỏi và gold)</t>
         </is>
       </c>
-      <c r="S108" t="inlineStr"/>
-      <c r="T108" t="inlineStr"/>
-      <c r="U108" t="inlineStr"/>
-      <c r="V108" t="inlineStr"/>
-      <c r="W108" t="inlineStr"/>
+      <c r="X108" s="2" t="inlineStr">
+        <is>
+          <t>10/2017/TT-BKHCN · hiệu lực 2017-08-15 → nay · lúc thu thập: Hết hiệu lực một phần
+Điều 17. Cơ sở dữ liệu tiêu chuẩn đo lường chất lượng
+2. Cơ sở dữ liệu tiêu chuẩn đo lường chất lượng được xây dựng, quản trị, vận hành và phát triển tại Tổng cục Tiêu chuẩn Đo lường Chất lượng, Bộ Khoa học và Công nghệ và được kết nối với Cơ sở dữ liệu quốc gia về khoa học và công nghệ.</t>
+        </is>
+      </c>
+      <c r="Y108" s="2" t="inlineStr">
+        <is>
+          <t>[amend] 11/2023/TT-BKHCN · hiệu lực 2023-08-10
+b) Sửa đổi, bổ sung khoản 2 như sau:
+"2. Cơ sở dữ liệu về tiêu chuẩn đo lường chất lượng được xây dựng, quản trị, vận hành và phát triển tại Tổng cục Tiêu chuẩn Đo lường Chất lượng, Bộ Khoa học và Công nghệ và được kết nối, chia sẻ với Cơ sở dữ liệu quốc gia về khoa học và công nghệ thông qua phương thức trực tuyến trên môi trường mạng.".
+[amend] 07/2024/TT-BKHCN · hiệu lực 2024-11-22
+Thay thế cụm từ “Tổng cục Tiêu chuẩn Đo lường Chất lượng” bằng cụm từ “Ủy ban Tiêu chuẩn Đo lường Chất lượng Quốc gia” tại khoản 2 Điều 17; khoản 3 Điều 26.
+CHUYỂN TIẾP: Điều 79. Điều khoản chuyển tiếp
+Các nội dung công việc đã giao cho Tổng cục Tiêu chuẩn Đo lường Chất lượng, Tổng cục trưởng Tổng cục Tiêu chuẩn Đo lường Chất lượng thực hiện tại các văn bản quy phạm pháp luật của Bộ trưởng Bộ Khoa học và Công nghệ quy định từ Điều 1 đến Điều 77 của Thông tư này, thì được chuyển giao cho Ủy ban Tiêu chuẩn Đo lường Chất lượng Quốc gia, Chủ tịch Ủy ban Tiêu chuẩn Đo lường Chất lượng Quốc gia để tiếp tục thực hiện.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
